--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -7151,7 +7151,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-01 23:48:24</t>
+          <t>2026-03-02 23:52:40</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3003</v>
+        <v>1.2831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>398.7</v>
+        <v>397.2</v>
       </c>
       <c r="O2" t="n">
-        <v>15948</v>
+        <v>15888</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-760.503607</v>
+        <v>-820.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20737.1844</v>
+        <v>20385.8928</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.3003</v>
+        <v>1.2831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>10000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5685</v>
+        <v>3.5465</v>
       </c>
       <c r="O3" t="n">
-        <v>35685</v>
+        <v>35465</v>
       </c>
       <c r="P3" t="n">
         <v>3.576275343</v>
@@ -687,7 +687,7 @@
         <v>35762.753425</v>
       </c>
       <c r="S3" t="n">
-        <v>-77.75342499999999</v>
+        <v>-297.753425</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>46401.2055</v>
+        <v>45505.1415</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.3003</v>
+        <v>1.2831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>300</v>
       </c>
       <c r="N4" t="n">
-        <v>66.56</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>19968</v>
+        <v>19812</v>
       </c>
       <c r="P4" t="n">
         <v>65.14093333300001</v>
@@ -767,7 +767,7 @@
         <v>19542.28</v>
       </c>
       <c r="S4" t="n">
-        <v>425.72</v>
+        <v>269.72</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>25964.3904</v>
+        <v>25420.7772</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14575</v>
+        <v>0.1449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.72</v>
+        <v>31.66</v>
       </c>
       <c r="O5" t="n">
-        <v>95160</v>
+        <v>94980</v>
       </c>
       <c r="P5" t="n">
         <v>31.36596519</v>
@@ -847,7 +847,7 @@
         <v>94097.89556999999</v>
       </c>
       <c r="S5" t="n">
-        <v>1062.10443</v>
+        <v>882.10443</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13869.57</v>
+        <v>13762.602</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1817</v>
+        <v>1.1689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>2000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.268</v>
+        <v>4.2195</v>
       </c>
       <c r="O6" t="n">
-        <v>8536</v>
+        <v>8439</v>
       </c>
       <c r="P6" t="n">
         <v>4.66233</v>
@@ -927,7 +927,7 @@
         <v>9324.66</v>
       </c>
       <c r="S6" t="n">
-        <v>-788.66</v>
+        <v>-885.66</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10086.9912</v>
+        <v>9864.347100000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.79051</v>
+        <v>0.78533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.997</v>
+        <v>4.892</v>
       </c>
       <c r="O7" t="n">
-        <v>39976</v>
+        <v>39136</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2664.77315</v>
+        <v>1824.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31601.42776</v>
+        <v>30734.67488</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.79051</v>
+        <v>0.78533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>601.9</v>
+        <v>631.5</v>
       </c>
       <c r="O8" t="n">
-        <v>30095</v>
+        <v>31575</v>
       </c>
       <c r="P8" t="n">
         <v>581.20939584</v>
@@ -1087,7 +1087,7 @@
         <v>29060.469792</v>
       </c>
       <c r="S8" t="n">
-        <v>1034.530208</v>
+        <v>2514.530208</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>23790.39845</v>
+        <v>24796.79475</v>
       </c>
     </row>
     <row r="9">
@@ -1145,29 +1145,29 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>8.414999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="O9" t="n">
-        <v>6311.25</v>
+        <v>8160</v>
       </c>
       <c r="P9" t="n">
-        <v>8.341905548</v>
+        <v>8.311237657</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.341905548</v>
+        <v>8.311237657</v>
       </c>
       <c r="R9" t="n">
-        <v>6256.429161</v>
+        <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>54.820839</v>
+        <v>-151.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>6311.25</v>
+        <v>8160</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>9.06</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>906</v>
+        <v>953</v>
       </c>
       <c r="P10" t="n">
         <v>9.705</v>
@@ -1247,7 +1247,7 @@
         <v>970.5</v>
       </c>
       <c r="S10" t="n">
-        <v>-64.5</v>
+        <v>-17.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>906</v>
+        <v>953</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1432</v>
+        <v>1425.6</v>
       </c>
       <c r="O11" t="n">
-        <v>14320</v>
+        <v>14256</v>
       </c>
       <c r="P11" t="n">
         <v>1474.045</v>
@@ -1327,7 +1327,7 @@
         <v>14740.45</v>
       </c>
       <c r="S11" t="n">
-        <v>-420.45</v>
+        <v>-484.45</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>14320</v>
+        <v>14256</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>311.76</v>
+        <v>306.52</v>
       </c>
       <c r="O12" t="n">
-        <v>31176</v>
+        <v>30652</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1012.5</v>
+        <v>488.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>31176</v>
+        <v>30652</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>61.53</v>
+        <v>60.56</v>
       </c>
       <c r="O13" t="n">
-        <v>9844.799999999999</v>
+        <v>9689.6</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>268.14</v>
+        <v>112.94</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9844.799999999999</v>
+        <v>9689.6</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>26.9</v>
+        <v>26.89</v>
       </c>
       <c r="O14" t="n">
-        <v>10356.5</v>
+        <v>10352.65</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>341.597178</v>
+        <v>337.747178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10356.5</v>
+        <v>10352.65</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>145.4</v>
+        <v>149.25</v>
       </c>
       <c r="O15" t="n">
-        <v>14540</v>
+        <v>14925</v>
       </c>
       <c r="P15" t="n">
         <v>205.3357044</v>
@@ -1647,7 +1647,7 @@
         <v>20533.57044</v>
       </c>
       <c r="S15" t="n">
-        <v>-5993.57044</v>
+        <v>-5608.57044</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>14540</v>
+        <v>14925</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>108.45</v>
+        <v>105.21</v>
       </c>
       <c r="O16" t="n">
-        <v>2169</v>
+        <v>2104.2</v>
       </c>
       <c r="P16" t="n">
         <v>124.315</v>
@@ -1727,7 +1727,7 @@
         <v>2486.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-317.3</v>
+        <v>-382.1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>2169</v>
+        <v>2104.2</v>
       </c>
     </row>
     <row r="17">
@@ -1785,29 +1785,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N17" t="n">
-        <v>177.18</v>
+        <v>175.12</v>
       </c>
       <c r="O17" t="n">
-        <v>53154</v>
+        <v>70048</v>
       </c>
       <c r="P17" t="n">
-        <v>173.59738865</v>
+        <v>173.855759437</v>
       </c>
       <c r="Q17" t="n">
-        <v>173.59738865</v>
+        <v>173.855759437</v>
       </c>
       <c r="R17" t="n">
-        <v>52079.216595</v>
+        <v>69542.30377499999</v>
       </c>
       <c r="S17" t="n">
-        <v>1074.783405</v>
+        <v>505.696225</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>53154</v>
+        <v>70048</v>
       </c>
     </row>
     <row r="18">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.68</v>
+        <v>0.625</v>
       </c>
       <c r="O18" t="n">
-        <v>68</v>
+        <v>62.5</v>
       </c>
       <c r="P18" t="n">
         <v>2.0105125</v>
@@ -1897,7 +1897,7 @@
         <v>201.05125</v>
       </c>
       <c r="S18" t="n">
-        <v>-133.05125</v>
+        <v>-138.55125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>68</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="19">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.275</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>327.5</v>
+        <v>430</v>
       </c>
       <c r="P19" t="n">
         <v>4.4905125</v>
@@ -1987,7 +1987,7 @@
         <v>449.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-121.55125</v>
+        <v>-19.05125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>327.5</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20">
@@ -2055,17 +2055,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>28.7541</v>
+        <v>28.639</v>
       </c>
       <c r="O20" t="n">
-        <v>5750.82</v>
+        <v>5727.8</v>
       </c>
       <c r="P20" t="n">
         <v>23.4605</v>
@@ -2077,7 +2077,7 @@
         <v>4692.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1058.72</v>
+        <v>1035.7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>5750.82</v>
+        <v>5727.8</v>
       </c>
     </row>
     <row r="21">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>21.96</v>
+        <v>22.325</v>
       </c>
       <c r="O21" t="n">
-        <v>4392</v>
+        <v>4465</v>
       </c>
       <c r="P21" t="n">
         <v>20.1374875</v>
@@ -2167,7 +2167,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S21" t="n">
-        <v>364.5025</v>
+        <v>437.5025</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>4392</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="22">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>2.995</v>
       </c>
       <c r="O22" t="n">
-        <v>-335</v>
+        <v>-299.5</v>
       </c>
       <c r="P22" t="n">
         <v>1.7494546</v>
@@ -2257,7 +2257,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S22" t="n">
-        <v>-160.05454</v>
+        <v>-124.55454</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-335</v>
+        <v>-299.5</v>
       </c>
     </row>
     <row r="23">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.205</v>
+        <v>1.105</v>
       </c>
       <c r="O23" t="n">
-        <v>-120.5</v>
+        <v>-110.5</v>
       </c>
       <c r="P23" t="n">
         <v>3.2494546</v>
@@ -2347,7 +2347,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>204.44546</v>
+        <v>214.44546</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-120.5</v>
+        <v>-110.5</v>
       </c>
     </row>
     <row r="24">
@@ -2415,29 +2415,29 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>5.75</v>
+        <v>6.125</v>
       </c>
       <c r="O24" t="n">
-        <v>-575</v>
+        <v>-612.5</v>
       </c>
       <c r="P24" t="n">
-        <v>4.0445796</v>
+        <v>7.5800876</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.0445796</v>
+        <v>7.5800876</v>
       </c>
       <c r="R24" t="n">
-        <v>-404.45796</v>
+        <v>-758.0087600000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-170.54204</v>
+        <v>145.50876</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-575</v>
+        <v>-612.5</v>
       </c>
     </row>
     <row r="25">
@@ -2474,24 +2474,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AMD   260327C00255000</t>
+          <t>AMZN  260327P00190000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 255 C</t>
+          <t>AMZN 27MAR26 190 P</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>255</v>
+        <v>190</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2500,34 +2500,34 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>-70</v>
+        <v>-211</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3442796</v>
+        <v>1.8142796</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.3442796</v>
+        <v>1.8142796</v>
       </c>
       <c r="R25" t="n">
-        <v>-234.42796</v>
+        <v>-181.42796</v>
       </c>
       <c r="S25" t="n">
-        <v>164.42796</v>
+        <v>-29.57204</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-70</v>
+        <v>-211</v>
       </c>
     </row>
     <row r="26">
@@ -2564,24 +2564,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AMZN  260327P00190000</t>
+          <t>AMZN  260327C00235000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 190 P</t>
+          <t>AMZN 27MAR26 235 C</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2590,34 +2590,34 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.9</v>
+        <v>0.625</v>
       </c>
       <c r="O26" t="n">
-        <v>-190</v>
+        <v>-62.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.8142796</v>
+        <v>1.0242796</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.8142796</v>
+        <v>1.0242796</v>
       </c>
       <c r="R26" t="n">
-        <v>-181.42796</v>
+        <v>-102.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.572039999999999</v>
+        <v>39.92796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-190</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="27">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AMZN  260327C00235000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 235 C</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2680,34 +2680,34 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.86</v>
+        <v>6.125</v>
       </c>
       <c r="O27" t="n">
-        <v>-86</v>
+        <v>-612.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.0242796</v>
+        <v>6.8094876</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.0242796</v>
+        <v>6.8094876</v>
       </c>
       <c r="R27" t="n">
-        <v>-102.42796</v>
+        <v>-680.94876</v>
       </c>
       <c r="S27" t="n">
-        <v>16.42796</v>
+        <v>68.44875999999999</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-86</v>
+        <v>-612.5</v>
       </c>
     </row>
     <row r="28">
@@ -2744,60 +2744,60 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GOOGL 260306C00325000</t>
+          <t>GOOGL 260327P00300000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOOGL 06MAR26 325 C</t>
+          <t>GOOGL 27MAR26 300 P</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.96</v>
+        <v>7.775</v>
       </c>
       <c r="O28" t="n">
-        <v>-96</v>
+        <v>-777.5</v>
       </c>
       <c r="P28" t="n">
-        <v>3.7194546</v>
+        <v>5.6794546</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7194546</v>
+        <v>5.6794546</v>
       </c>
       <c r="R28" t="n">
-        <v>-371.94546</v>
+        <v>-567.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>275.94546</v>
+        <v>-209.55454</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-96</v>
+        <v>-777.5</v>
       </c>
     </row>
     <row r="29">
@@ -2834,24 +2834,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00300000</t>
+          <t>GOOGL 260327C00315000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 300 P</t>
+          <t>GOOGL 27MAR26 315 C</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2860,34 +2860,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>6.4471</v>
+        <v>7.025</v>
       </c>
       <c r="O29" t="n">
-        <v>-644.71</v>
+        <v>-702.5</v>
       </c>
       <c r="P29" t="n">
-        <v>5.6794546</v>
+        <v>6.7894876</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.6794546</v>
+        <v>6.7894876</v>
       </c>
       <c r="R29" t="n">
-        <v>-567.94546</v>
+        <v>-678.94876</v>
       </c>
       <c r="S29" t="n">
-        <v>-76.76454</v>
+        <v>-23.55124</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-644.71</v>
+        <v>-702.5</v>
       </c>
     </row>
     <row r="30">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>2.145</v>
       </c>
       <c r="O30" t="n">
-        <v>-280</v>
+        <v>-214.5</v>
       </c>
       <c r="P30" t="n">
         <v>2.1194546</v>
@@ -2977,7 +2977,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>-68.05454</v>
+        <v>-2.55454</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-280</v>
+        <v>-214.5</v>
       </c>
     </row>
     <row r="31">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>4.35</v>
+        <v>5.7</v>
       </c>
       <c r="O31" t="n">
-        <v>-435</v>
+        <v>-570</v>
       </c>
       <c r="P31" t="n">
         <v>5.7894546</v>
@@ -3067,7 +3067,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>143.94546</v>
+        <v>8.945460000000001</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-435</v>
+        <v>-570</v>
       </c>
     </row>
     <row r="32">
@@ -3109,19 +3109,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NFLX  260327P00075000</t>
+          <t>NFLX  260327P00088000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 75 P</t>
+          <t>NFLX 27MAR26 88 P</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -3135,29 +3135,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1631</v>
+        <v>0.945</v>
       </c>
       <c r="O32" t="n">
-        <v>-16.31</v>
+        <v>-189</v>
       </c>
       <c r="P32" t="n">
-        <v>1.3294546</v>
+        <v>0.9454876</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.3294546</v>
+        <v>0.9454876</v>
       </c>
       <c r="R32" t="n">
-        <v>-132.94546</v>
+        <v>-189.09752</v>
       </c>
       <c r="S32" t="n">
-        <v>116.63546</v>
+        <v>0.09752</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-16.31</v>
+        <v>-189</v>
       </c>
     </row>
     <row r="33">
@@ -3199,23 +3199,23 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ORCL  260306C00165000</t>
+          <t>ORCL  260313C00160000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ORCL 06MAR26 165 C</t>
+          <t>ORCL 13MAR26 160 C</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3225,29 +3225,29 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4542</v>
+        <v>5.6927</v>
       </c>
       <c r="O33" t="n">
-        <v>-45.42</v>
+        <v>-569.27</v>
       </c>
       <c r="P33" t="n">
-        <v>1.8094796</v>
+        <v>4.5694876</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8094796</v>
+        <v>4.5694876</v>
       </c>
       <c r="R33" t="n">
-        <v>-180.94796</v>
+        <v>-456.94876</v>
       </c>
       <c r="S33" t="n">
-        <v>135.52796</v>
+        <v>-112.32124</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-45.42</v>
+        <v>-569.27</v>
       </c>
     </row>
     <row r="34">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-2</v>
       </c>
       <c r="N34" t="n">
-        <v>7.8661</v>
+        <v>7.9057</v>
       </c>
       <c r="O34" t="n">
-        <v>-1573.22</v>
+        <v>-1581.14</v>
       </c>
       <c r="P34" t="n">
         <v>6.3644671</v>
@@ -3337,7 +3337,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S34" t="n">
-        <v>-300.32658</v>
+        <v>-308.24658</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1573.22</v>
+        <v>-1581.14</v>
       </c>
     </row>
     <row r="35">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>8.107699999999999</v>
+        <v>8.305</v>
       </c>
       <c r="O35" t="n">
-        <v>-1621.54</v>
+        <v>-1661</v>
       </c>
       <c r="P35" t="n">
         <v>7.3548796</v>
@@ -3427,7 +3427,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S35" t="n">
-        <v>-150.56408</v>
+        <v>-190.02408</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-1621.54</v>
+        <v>-1661</v>
       </c>
     </row>
   </sheetData>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3003</v>
+        <v>1.2831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3611,17 +3611,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>398.7</v>
+        <v>397.2</v>
       </c>
       <c r="O2" t="n">
-        <v>19935</v>
+        <v>19860</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3633,7 +3633,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-1047.956235</v>
+        <v>-1122.956235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25921.4805</v>
+        <v>25482.366</v>
       </c>
     </row>
     <row r="3">
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.3003</v>
+        <v>1.2831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3691,17 +3691,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>12000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5685</v>
+        <v>3.5465</v>
       </c>
       <c r="O3" t="n">
-        <v>42822</v>
+        <v>42558</v>
       </c>
       <c r="P3" t="n">
         <v>3.574177863</v>
@@ -3713,7 +3713,7 @@
         <v>42890.13435</v>
       </c>
       <c r="S3" t="n">
-        <v>-68.13435</v>
+        <v>-332.13435</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>55681.4466</v>
+        <v>54606.1698</v>
       </c>
     </row>
     <row r="4">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.3003</v>
+        <v>1.2831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3771,17 +3771,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>500</v>
       </c>
       <c r="N4" t="n">
-        <v>66.56</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>33280</v>
+        <v>33020</v>
       </c>
       <c r="P4" t="n">
         <v>65.30711724</v>
@@ -3793,7 +3793,7 @@
         <v>32653.55862</v>
       </c>
       <c r="S4" t="n">
-        <v>626.44138</v>
+        <v>366.44138</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>43273.984</v>
+        <v>42367.962</v>
       </c>
     </row>
     <row r="5">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14575</v>
+        <v>0.1449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3851,17 +3851,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.72</v>
+        <v>31.66</v>
       </c>
       <c r="O5" t="n">
-        <v>63440</v>
+        <v>63320</v>
       </c>
       <c r="P5" t="n">
         <v>31.696238595</v>
@@ -3873,7 +3873,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S5" t="n">
-        <v>47.52281</v>
+        <v>-72.47718999999999</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9246.379999999999</v>
+        <v>9175.067999999999</v>
       </c>
     </row>
     <row r="6">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1817</v>
+        <v>1.1689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3931,17 +3931,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>3000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.268</v>
+        <v>4.2195</v>
       </c>
       <c r="O6" t="n">
-        <v>12804</v>
+        <v>12658.5</v>
       </c>
       <c r="P6" t="n">
         <v>4.65841303</v>
@@ -3953,7 +3953,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1171.239091</v>
+        <v>-1316.739091</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>15130.4868</v>
+        <v>14796.52065</v>
       </c>
     </row>
     <row r="7">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1817</v>
+        <v>1.1689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4011,17 +4011,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>1000</v>
       </c>
       <c r="N7" t="n">
-        <v>50.1</v>
+        <v>48.67</v>
       </c>
       <c r="O7" t="n">
-        <v>50100</v>
+        <v>48670</v>
       </c>
       <c r="P7" t="n">
         <v>43.01</v>
@@ -4033,7 +4033,7 @@
         <v>43010</v>
       </c>
       <c r="S7" t="n">
-        <v>7090</v>
+        <v>5660</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>59203.17</v>
+        <v>56890.363</v>
       </c>
     </row>
     <row r="8">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.79051</v>
+        <v>0.78533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4091,17 +4091,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.997</v>
+        <v>4.892</v>
       </c>
       <c r="O8" t="n">
-        <v>49970</v>
+        <v>48920</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4113,7 +4113,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12701.8184</v>
+        <v>11651.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39501.7847</v>
+        <v>38418.3436</v>
       </c>
     </row>
     <row r="9">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.79051</v>
+        <v>0.78533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4171,17 +4171,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>50</v>
       </c>
       <c r="N9" t="n">
-        <v>601.9</v>
+        <v>631.5</v>
       </c>
       <c r="O9" t="n">
-        <v>30095</v>
+        <v>31575</v>
       </c>
       <c r="P9" t="n">
         <v>581.41476</v>
@@ -4193,7 +4193,7 @@
         <v>29070.738</v>
       </c>
       <c r="S9" t="n">
-        <v>1024.262</v>
+        <v>2504.262</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>23790.39845</v>
+        <v>24796.79475</v>
       </c>
     </row>
     <row r="10">
@@ -4251,29 +4251,29 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>8.414999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="O10" t="n">
-        <v>6732</v>
+        <v>8976</v>
       </c>
       <c r="P10" t="n">
-        <v>8.34690969</v>
+        <v>8.311679952</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.34690969</v>
+        <v>8.311679952</v>
       </c>
       <c r="R10" t="n">
-        <v>6677.527752</v>
+        <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>54.472248</v>
+        <v>-166.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6732</v>
+        <v>8976</v>
       </c>
     </row>
     <row r="11">
@@ -4331,17 +4331,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>300</v>
       </c>
       <c r="N11" t="n">
-        <v>9.06</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>2718</v>
+        <v>2859</v>
       </c>
       <c r="P11" t="n">
         <v>11.661666667</v>
@@ -4353,7 +4353,7 @@
         <v>3498.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-780.5</v>
+        <v>-639.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2718</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="12">
@@ -4411,17 +4411,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>1432</v>
+        <v>1425.6</v>
       </c>
       <c r="O12" t="n">
-        <v>28640</v>
+        <v>28512</v>
       </c>
       <c r="P12" t="n">
         <v>1467.02705</v>
@@ -4433,7 +4433,7 @@
         <v>29340.541</v>
       </c>
       <c r="S12" t="n">
-        <v>-700.5410000000001</v>
+        <v>-828.5410000000001</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>28640</v>
+        <v>28512</v>
       </c>
     </row>
     <row r="13">
@@ -4491,17 +4491,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>311.76</v>
+        <v>306.52</v>
       </c>
       <c r="O13" t="n">
-        <v>31176</v>
+        <v>30652</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4513,7 +4513,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2011.755</v>
+        <v>-2535.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>31176</v>
+        <v>30652</v>
       </c>
     </row>
     <row r="14">
@@ -4571,17 +4571,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>61.53</v>
+        <v>60.56</v>
       </c>
       <c r="O14" t="n">
-        <v>9844.799999999999</v>
+        <v>9689.6</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4593,7 +4593,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>212.36</v>
+        <v>57.16</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9844.799999999999</v>
+        <v>9689.6</v>
       </c>
     </row>
     <row r="15">
@@ -4651,17 +4651,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>71.19</v>
+        <v>71.67</v>
       </c>
       <c r="O15" t="n">
-        <v>1199.18</v>
+        <v>1207.27</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4673,7 +4673,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>850.133421</v>
+        <v>858.223421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1199.18</v>
+        <v>1207.27</v>
       </c>
     </row>
     <row r="16">
@@ -4731,17 +4731,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.9</v>
+        <v>26.89</v>
       </c>
       <c r="O16" t="n">
-        <v>10356.5</v>
+        <v>10352.65</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4753,7 +4753,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>347.594112</v>
+        <v>343.744112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10356.5</v>
+        <v>10352.65</v>
       </c>
     </row>
     <row r="17">
@@ -4811,17 +4811,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>300.3</v>
+        <v>297.56</v>
       </c>
       <c r="O17" t="n">
-        <v>30030</v>
+        <v>29756</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4833,7 +4833,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>228</v>
+        <v>-46</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>30030</v>
+        <v>29756</v>
       </c>
     </row>
     <row r="18">
@@ -4891,29 +4891,29 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>177.18</v>
+        <v>175.12</v>
       </c>
       <c r="O18" t="n">
-        <v>70872</v>
+        <v>87560</v>
       </c>
       <c r="P18" t="n">
-        <v>173.889176137</v>
+        <v>174.06142722</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.889176137</v>
+        <v>174.06142722</v>
       </c>
       <c r="R18" t="n">
-        <v>69555.670455</v>
+        <v>87030.71361000001</v>
       </c>
       <c r="S18" t="n">
-        <v>1316.329545</v>
+        <v>529.28639</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>70872</v>
+        <v>87560</v>
       </c>
     </row>
     <row r="19">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.68</v>
+        <v>0.625</v>
       </c>
       <c r="O19" t="n">
-        <v>68</v>
+        <v>62.5</v>
       </c>
       <c r="P19" t="n">
         <v>2.1405125</v>
@@ -5003,7 +5003,7 @@
         <v>214.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-146.05125</v>
+        <v>-151.55125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>68</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.275</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>327.5</v>
+        <v>430</v>
       </c>
       <c r="P20" t="n">
         <v>4.6805125</v>
@@ -5093,7 +5093,7 @@
         <v>468.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-140.55125</v>
+        <v>-38.05125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>327.5</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21">
@@ -5161,17 +5161,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>12.2578</v>
+        <v>12.9657</v>
       </c>
       <c r="O21" t="n">
-        <v>1225.78</v>
+        <v>1296.57</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5183,7 +5183,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>973.72875</v>
+        <v>1044.51875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>1225.78</v>
+        <v>1296.57</v>
       </c>
     </row>
     <row r="22">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.505</v>
+        <v>0.445</v>
       </c>
       <c r="O22" t="n">
-        <v>50.5</v>
+        <v>44.5</v>
       </c>
       <c r="P22" t="n">
         <v>2.6805125</v>
@@ -5273,7 +5273,7 @@
         <v>268.05125</v>
       </c>
       <c r="S22" t="n">
-        <v>-217.55125</v>
+        <v>-223.55125</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>50.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="23">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>28.7541</v>
+        <v>28.639</v>
       </c>
       <c r="O23" t="n">
-        <v>5750.82</v>
+        <v>5727.8</v>
       </c>
       <c r="P23" t="n">
         <v>23.5270125</v>
@@ -5363,7 +5363,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S23" t="n">
-        <v>1045.4175</v>
+        <v>1022.3975</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5750.82</v>
+        <v>5727.8</v>
       </c>
     </row>
     <row r="24">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>21.96</v>
+        <v>22.325</v>
       </c>
       <c r="O24" t="n">
-        <v>4392</v>
+        <v>4465</v>
       </c>
       <c r="P24" t="n">
         <v>20.1350875</v>
@@ -5453,7 +5453,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S24" t="n">
-        <v>364.9825</v>
+        <v>437.9825</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>4392</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="25">
@@ -5521,17 +5521,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.35</v>
+        <v>2.995</v>
       </c>
       <c r="O25" t="n">
-        <v>-335</v>
+        <v>-299.5</v>
       </c>
       <c r="P25" t="n">
         <v>1.7694546</v>
@@ -5543,7 +5543,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>-158.05454</v>
+        <v>-122.55454</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-335</v>
+        <v>-299.5</v>
       </c>
     </row>
     <row r="26">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.205</v>
+        <v>1.105</v>
       </c>
       <c r="O26" t="n">
-        <v>-120.5</v>
+        <v>-110.5</v>
       </c>
       <c r="P26" t="n">
         <v>3.4194546</v>
@@ -5633,7 +5633,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>221.44546</v>
+        <v>231.44546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-120.5</v>
+        <v>-110.5</v>
       </c>
     </row>
     <row r="27">
@@ -5701,17 +5701,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>5.75</v>
+        <v>6.125</v>
       </c>
       <c r="O27" t="n">
-        <v>-575</v>
+        <v>-612.5</v>
       </c>
       <c r="P27" t="n">
         <v>4.1794546</v>
@@ -5723,7 +5723,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>-157.05454</v>
+        <v>-194.55454</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-575</v>
+        <v>-612.5</v>
       </c>
     </row>
     <row r="28">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="O28" t="n">
-        <v>-70</v>
+        <v>-62</v>
       </c>
       <c r="P28" t="n">
         <v>2.3694546</v>
@@ -5813,7 +5813,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>166.94546</v>
+        <v>174.94546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-70</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="29">
@@ -5881,17 +5881,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>-190</v>
+        <v>-211</v>
       </c>
       <c r="P29" t="n">
         <v>1.7994546</v>
@@ -5903,7 +5903,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>-10.05454</v>
+        <v>-31.05454</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-190</v>
+        <v>-211</v>
       </c>
     </row>
     <row r="30">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.86</v>
+        <v>0.625</v>
       </c>
       <c r="O30" t="n">
-        <v>-86</v>
+        <v>-62.5</v>
       </c>
       <c r="P30" t="n">
         <v>1.0594546</v>
@@ -5993,7 +5993,7 @@
         <v>-105.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>19.94546</v>
+        <v>43.44546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-86</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="31">
@@ -6061,17 +6061,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6173</v>
+        <v>0.545</v>
       </c>
       <c r="O31" t="n">
-        <v>-61.73</v>
+        <v>-54.5</v>
       </c>
       <c r="P31" t="n">
         <v>3.6594796</v>
@@ -6083,7 +6083,7 @@
         <v>-365.94796</v>
       </c>
       <c r="S31" t="n">
-        <v>304.21796</v>
+        <v>311.44796</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-61.73</v>
+        <v>-54.5</v>
       </c>
     </row>
     <row r="32">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>2.745</v>
       </c>
       <c r="O32" t="n">
-        <v>-420</v>
+        <v>-274.5</v>
       </c>
       <c r="P32" t="n">
         <v>4.6494796</v>
@@ -6173,7 +6173,7 @@
         <v>-464.94796</v>
       </c>
       <c r="S32" t="n">
-        <v>44.94796</v>
+        <v>190.44796</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-420</v>
+        <v>-274.5</v>
       </c>
     </row>
     <row r="33">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>5.35</v>
+        <v>4.275</v>
       </c>
       <c r="O33" t="n">
-        <v>-535</v>
+        <v>-427.5</v>
       </c>
       <c r="P33" t="n">
         <v>4.4694546</v>
@@ -6263,7 +6263,7 @@
         <v>-446.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>-88.05454</v>
+        <v>19.44546</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-535</v>
+        <v>-427.5</v>
       </c>
     </row>
     <row r="34">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>2.145</v>
       </c>
       <c r="O34" t="n">
-        <v>-280</v>
+        <v>-214.5</v>
       </c>
       <c r="P34" t="n">
         <v>2.1094546</v>
@@ -6353,7 +6353,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-69.05454</v>
+        <v>-3.55454</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-280</v>
+        <v>-214.5</v>
       </c>
     </row>
     <row r="35">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>4.35</v>
+        <v>5.7</v>
       </c>
       <c r="O35" t="n">
-        <v>-435</v>
+        <v>-570</v>
       </c>
       <c r="P35" t="n">
         <v>5.9994546</v>
@@ -6443,7 +6443,7 @@
         <v>-599.94546</v>
       </c>
       <c r="S35" t="n">
-        <v>164.94546</v>
+        <v>29.94546</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-435</v>
+        <v>-570</v>
       </c>
     </row>
     <row r="36">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-1</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1214</v>
+        <v>0.1323</v>
       </c>
       <c r="O36" t="n">
-        <v>-12.14</v>
+        <v>-13.23</v>
       </c>
       <c r="P36" t="n">
         <v>0.8794546</v>
@@ -6533,7 +6533,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S36" t="n">
-        <v>75.80546</v>
+        <v>74.71545999999999</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-12.14</v>
+        <v>-13.23</v>
       </c>
     </row>
     <row r="37">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M37" t="n">
         <v>-1</v>
       </c>
       <c r="N37" t="n">
-        <v>14.0431</v>
+        <v>14.809</v>
       </c>
       <c r="O37" t="n">
-        <v>-1404.31</v>
+        <v>-1480.9</v>
       </c>
       <c r="P37" t="n">
         <v>3.2794546</v>
@@ -6623,7 +6623,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S37" t="n">
-        <v>-1076.36454</v>
+        <v>-1152.95454</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>-1404.31</v>
+        <v>-1480.9</v>
       </c>
     </row>
     <row r="38">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M38" t="n">
         <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>6.075</v>
+        <v>4.05</v>
       </c>
       <c r="O38" t="n">
-        <v>-607.5</v>
+        <v>-405</v>
       </c>
       <c r="P38" t="n">
         <v>3.0294546</v>
@@ -6713,7 +6713,7 @@
         <v>-302.94546</v>
       </c>
       <c r="S38" t="n">
-        <v>-304.55454</v>
+        <v>-102.05454</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>-607.5</v>
+        <v>-405</v>
       </c>
     </row>
     <row r="39">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M39" t="n">
         <v>-1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="O39" t="n">
-        <v>-69</v>
+        <v>-66</v>
       </c>
       <c r="P39" t="n">
         <v>3.6694546</v>
@@ -6803,7 +6803,7 @@
         <v>-366.94546</v>
       </c>
       <c r="S39" t="n">
-        <v>297.94546</v>
+        <v>300.94546</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>-69</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="40">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M40" t="n">
         <v>-2</v>
       </c>
       <c r="N40" t="n">
-        <v>7.8661</v>
+        <v>7.9057</v>
       </c>
       <c r="O40" t="n">
-        <v>-1573.22</v>
+        <v>-1581.14</v>
       </c>
       <c r="P40" t="n">
         <v>6.3929546</v>
@@ -6893,7 +6893,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S40" t="n">
-        <v>-294.62908</v>
+        <v>-302.54908</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>-1573.22</v>
+        <v>-1581.14</v>
       </c>
     </row>
     <row r="41">
@@ -6961,17 +6961,17 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="M41" t="n">
         <v>-2</v>
       </c>
       <c r="N41" t="n">
-        <v>8.107699999999999</v>
+        <v>8.305</v>
       </c>
       <c r="O41" t="n">
-        <v>-1621.54</v>
+        <v>-1661</v>
       </c>
       <c r="P41" t="n">
         <v>7.3496796</v>
@@ -6983,7 +6983,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S41" t="n">
-        <v>-151.60408</v>
+        <v>-191.06408</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>-1621.54</v>
+        <v>-1661</v>
       </c>
     </row>
   </sheetData>
@@ -7043,17 +7043,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$319,678.34</t>
+          <t>$334,122.57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$124,147.47</t>
+          <t>$106,071.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$443,825.81</t>
+          <t>$440,193.68</t>
         </is>
       </c>
     </row>
@@ -7065,17 +7065,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$466,736.27</t>
+          <t>$480,018.21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$97,608.71</t>
+          <t>$77,232.69</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$564,344.98</t>
+          <t>$557,250.89</t>
         </is>
       </c>
     </row>
@@ -7093,17 +7093,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$786,414.61</t>
+          <t>$814,140.78</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$221,756.18</t>
+          <t>$183,303.80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1,008,170.79</t>
+          <t>$997,444.57</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02 23:52:40</t>
+          <t>2026-03-03 23:52:22</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2831</v>
+        <v>1.2788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>397.2</v>
+        <v>392.75</v>
       </c>
       <c r="O2" t="n">
-        <v>15888</v>
+        <v>15710</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-820.503607</v>
+        <v>-998.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20385.8928</v>
+        <v>20089.948</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2831</v>
+        <v>1.2788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>10000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5465</v>
+        <v>3.4845</v>
       </c>
       <c r="O3" t="n">
-        <v>35465</v>
+        <v>34845</v>
       </c>
       <c r="P3" t="n">
         <v>3.576275343</v>
@@ -687,7 +687,7 @@
         <v>35762.753425</v>
       </c>
       <c r="S3" t="n">
-        <v>-297.753425</v>
+        <v>-917.753425</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>45505.1415</v>
+        <v>44559.786</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2831</v>
+        <v>1.2788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,29 +745,29 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="N4" t="n">
-        <v>66.04000000000001</v>
+        <v>62.64</v>
       </c>
       <c r="O4" t="n">
-        <v>19812</v>
+        <v>15660</v>
       </c>
       <c r="P4" t="n">
-        <v>65.14093333300001</v>
+        <v>65.233413332</v>
       </c>
       <c r="Q4" t="n">
-        <v>65.14093333300001</v>
+        <v>65.233413332</v>
       </c>
       <c r="R4" t="n">
-        <v>19542.28</v>
+        <v>16308.353333</v>
       </c>
       <c r="S4" t="n">
-        <v>269.72</v>
+        <v>-648.353333</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>25420.7772</v>
+        <v>20026.008</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1449</v>
+        <v>0.14455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.66</v>
+        <v>31.24</v>
       </c>
       <c r="O5" t="n">
-        <v>94980</v>
+        <v>93720</v>
       </c>
       <c r="P5" t="n">
         <v>31.36596519</v>
@@ -847,7 +847,7 @@
         <v>94097.89556999999</v>
       </c>
       <c r="S5" t="n">
-        <v>882.10443</v>
+        <v>-377.89557</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13762.602</v>
+        <v>13547.226</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1689</v>
+        <v>1.1612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>2000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2195</v>
+        <v>4.095</v>
       </c>
       <c r="O6" t="n">
-        <v>8439</v>
+        <v>8190</v>
       </c>
       <c r="P6" t="n">
         <v>4.66233</v>
@@ -927,7 +927,7 @@
         <v>9324.66</v>
       </c>
       <c r="S6" t="n">
-        <v>-885.66</v>
+        <v>-1134.66</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9864.347100000001</v>
+        <v>9510.228000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78533</v>
+        <v>0.78278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.892</v>
+        <v>4.899</v>
       </c>
       <c r="O7" t="n">
-        <v>39136</v>
+        <v>39192</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1824.77315</v>
+        <v>1880.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30734.67488</v>
+        <v>30678.71376</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78533</v>
+        <v>0.78278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>631.5</v>
+        <v>622.3</v>
       </c>
       <c r="O8" t="n">
-        <v>31575</v>
+        <v>31115</v>
       </c>
       <c r="P8" t="n">
         <v>581.20939584</v>
@@ -1087,7 +1087,7 @@
         <v>29060.469792</v>
       </c>
       <c r="S8" t="n">
-        <v>2514.530208</v>
+        <v>2054.530208</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>24796.79475</v>
+        <v>24356.1997</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>8.16</v>
+        <v>7.865</v>
       </c>
       <c r="O9" t="n">
-        <v>8160</v>
+        <v>7865</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-151.237657</v>
+        <v>-446.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>8160</v>
+        <v>7865</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>9.529999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O10" t="n">
-        <v>953</v>
+        <v>940</v>
       </c>
       <c r="P10" t="n">
         <v>9.705</v>
@@ -1247,7 +1247,7 @@
         <v>970.5</v>
       </c>
       <c r="S10" t="n">
-        <v>-17.5</v>
+        <v>-30.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>953</v>
+        <v>940</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1425.6</v>
+        <v>1410.4</v>
       </c>
       <c r="O11" t="n">
-        <v>14256</v>
+        <v>14104</v>
       </c>
       <c r="P11" t="n">
         <v>1474.045</v>
@@ -1327,7 +1327,7 @@
         <v>14740.45</v>
       </c>
       <c r="S11" t="n">
-        <v>-484.45</v>
+        <v>-636.45</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>14256</v>
+        <v>14104</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>306.52</v>
+        <v>303.58</v>
       </c>
       <c r="O12" t="n">
-        <v>30652</v>
+        <v>30358</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>488.5</v>
+        <v>194.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30652</v>
+        <v>30358</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>60.56</v>
+        <v>58.03</v>
       </c>
       <c r="O13" t="n">
-        <v>9689.6</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>112.94</v>
+        <v>-291.86</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9689.6</v>
+        <v>9284.799999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>26.89</v>
+        <v>25.7761</v>
       </c>
       <c r="O14" t="n">
-        <v>10352.65</v>
+        <v>9923.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>337.747178</v>
+        <v>-91.102822</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10352.65</v>
+        <v>9923.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>149.25</v>
+        <v>149.01</v>
       </c>
       <c r="O15" t="n">
-        <v>14925</v>
+        <v>14901</v>
       </c>
       <c r="P15" t="n">
         <v>205.3357044</v>
@@ -1647,7 +1647,7 @@
         <v>20533.57044</v>
       </c>
       <c r="S15" t="n">
-        <v>-5608.57044</v>
+        <v>-5632.57044</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>14925</v>
+        <v>14901</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>105.21</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>2104.2</v>
+        <v>1756.4</v>
       </c>
       <c r="P16" t="n">
         <v>124.315</v>
@@ -1727,7 +1727,7 @@
         <v>2486.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-382.1</v>
+        <v>-729.9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>2104.2</v>
+        <v>1756.4</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>400</v>
       </c>
       <c r="N17" t="n">
-        <v>175.12</v>
+        <v>171.1</v>
       </c>
       <c r="O17" t="n">
-        <v>70048</v>
+        <v>68440</v>
       </c>
       <c r="P17" t="n">
         <v>173.855759437</v>
@@ -1807,7 +1807,7 @@
         <v>69542.30377499999</v>
       </c>
       <c r="S17" t="n">
-        <v>505.696225</v>
+        <v>-1102.303775</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>70048</v>
+        <v>68440</v>
       </c>
     </row>
     <row r="18">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.625</v>
+        <v>0.51</v>
       </c>
       <c r="O18" t="n">
-        <v>62.5</v>
+        <v>51</v>
       </c>
       <c r="P18" t="n">
         <v>2.0105125</v>
@@ -1897,7 +1897,7 @@
         <v>201.05125</v>
       </c>
       <c r="S18" t="n">
-        <v>-138.55125</v>
+        <v>-150.05125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>62.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="O19" t="n">
-        <v>430</v>
+        <v>610</v>
       </c>
       <c r="P19" t="n">
         <v>4.4905125</v>
@@ -1987,7 +1987,7 @@
         <v>449.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-19.05125</v>
+        <v>160.94875</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>430</v>
+        <v>610</v>
       </c>
     </row>
     <row r="20">
@@ -2055,17 +2055,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>28.639</v>
+        <v>30.57</v>
       </c>
       <c r="O20" t="n">
-        <v>5727.8</v>
+        <v>6114</v>
       </c>
       <c r="P20" t="n">
         <v>23.4605</v>
@@ -2077,7 +2077,7 @@
         <v>4692.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1035.7</v>
+        <v>1421.9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>5727.8</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="21">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>22.325</v>
+        <v>24.015</v>
       </c>
       <c r="O21" t="n">
-        <v>4465</v>
+        <v>4803</v>
       </c>
       <c r="P21" t="n">
         <v>20.1374875</v>
@@ -2167,7 +2167,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S21" t="n">
-        <v>437.5025</v>
+        <v>775.5025000000001</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>4465</v>
+        <v>4803</v>
       </c>
     </row>
     <row r="22">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.995</v>
+        <v>3.275</v>
       </c>
       <c r="O22" t="n">
-        <v>-299.5</v>
+        <v>-327.5</v>
       </c>
       <c r="P22" t="n">
         <v>1.7494546</v>
@@ -2257,7 +2257,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S22" t="n">
-        <v>-124.55454</v>
+        <v>-152.55454</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-299.5</v>
+        <v>-327.5</v>
       </c>
     </row>
     <row r="23">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.105</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-110.5</v>
+        <v>-94</v>
       </c>
       <c r="P23" t="n">
         <v>3.2494546</v>
@@ -2347,7 +2347,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>214.44546</v>
+        <v>230.94546</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-110.5</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="24">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>6.125</v>
+        <v>8.275</v>
       </c>
       <c r="O24" t="n">
-        <v>-612.5</v>
+        <v>-827.5</v>
       </c>
       <c r="P24" t="n">
         <v>7.5800876</v>
@@ -2437,7 +2437,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S24" t="n">
-        <v>145.50876</v>
+        <v>-69.49124</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-612.5</v>
+        <v>-827.5</v>
       </c>
     </row>
     <row r="25">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
-        <v>-211</v>
+        <v>-208</v>
       </c>
       <c r="P25" t="n">
         <v>1.8142796</v>
@@ -2527,7 +2527,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S25" t="n">
-        <v>-29.57204</v>
+        <v>-26.57204</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-211</v>
+        <v>-208</v>
       </c>
     </row>
     <row r="26">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.625</v>
+        <v>0.575</v>
       </c>
       <c r="O26" t="n">
-        <v>-62.5</v>
+        <v>-57.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.0242796</v>
@@ -2617,7 +2617,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>39.92796</v>
+        <v>44.92796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-62.5</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="27">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>6.125</v>
+        <v>6.925</v>
       </c>
       <c r="O27" t="n">
-        <v>-612.5</v>
+        <v>-692.5</v>
       </c>
       <c r="P27" t="n">
         <v>6.8094876</v>
@@ -2707,7 +2707,7 @@
         <v>-680.94876</v>
       </c>
       <c r="S27" t="n">
-        <v>68.44875999999999</v>
+        <v>-11.55124</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-612.5</v>
+        <v>-692.5</v>
       </c>
     </row>
     <row r="28">
@@ -2744,24 +2744,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00300000</t>
+          <t>GOOGL 260327C00315000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 300 P</t>
+          <t>GOOGL 27MAR26 315 C</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2770,34 +2770,34 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>7.775</v>
+        <v>5.825</v>
       </c>
       <c r="O28" t="n">
-        <v>-777.5</v>
+        <v>-582.5</v>
       </c>
       <c r="P28" t="n">
-        <v>5.6794546</v>
+        <v>6.7894876</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.6794546</v>
+        <v>6.7894876</v>
       </c>
       <c r="R28" t="n">
-        <v>-567.94546</v>
+        <v>-678.94876</v>
       </c>
       <c r="S28" t="n">
-        <v>-209.55454</v>
+        <v>96.44875999999999</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-777.5</v>
+        <v>-582.5</v>
       </c>
     </row>
     <row r="29">
@@ -2834,24 +2834,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GOOGL 260327C00315000</t>
+          <t>MSFT  260327P00360000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 315 C</t>
+          <t>MSFT 27MAR26 360 P</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2860,34 +2860,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>7.025</v>
+        <v>1.8514</v>
       </c>
       <c r="O29" t="n">
-        <v>-702.5</v>
+        <v>-185.14</v>
       </c>
       <c r="P29" t="n">
-        <v>6.7894876</v>
+        <v>2.1194546</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.7894876</v>
+        <v>2.1194546</v>
       </c>
       <c r="R29" t="n">
-        <v>-678.94876</v>
+        <v>-211.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>-23.55124</v>
+        <v>26.80546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-702.5</v>
+        <v>-185.14</v>
       </c>
     </row>
     <row r="30">
@@ -2924,24 +2924,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MSFT  260327P00360000</t>
+          <t>MSFT  260327C00415000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 360 P</t>
+          <t>MSFT 27MAR26 415 C</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2950,34 +2950,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.145</v>
+        <v>7.925</v>
       </c>
       <c r="O30" t="n">
-        <v>-214.5</v>
+        <v>-792.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1194546</v>
+        <v>5.7894546</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.1194546</v>
+        <v>5.7894546</v>
       </c>
       <c r="R30" t="n">
-        <v>-211.94546</v>
+        <v>-578.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>-2.55454</v>
+        <v>-213.55454</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-214.5</v>
+        <v>-792.5</v>
       </c>
     </row>
     <row r="31">
@@ -3014,24 +3014,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MSFT  260327C00415000</t>
+          <t>NFLX  260327P00088000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 415 C</t>
+          <t>NFLX 27MAR26 88 P</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>415</v>
+        <v>88</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3040,34 +3040,34 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N31" t="n">
-        <v>5.7</v>
+        <v>0.89</v>
       </c>
       <c r="O31" t="n">
-        <v>-570</v>
+        <v>-178</v>
       </c>
       <c r="P31" t="n">
-        <v>5.7894546</v>
+        <v>0.9454876</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.7894546</v>
+        <v>0.9454876</v>
       </c>
       <c r="R31" t="n">
-        <v>-578.94546</v>
+        <v>-189.09752</v>
       </c>
       <c r="S31" t="n">
-        <v>8.945460000000001</v>
+        <v>11.09752</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-570</v>
+        <v>-178</v>
       </c>
     </row>
     <row r="32">
@@ -3104,60 +3104,60 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NFLX  260327P00088000</t>
+          <t>ORCL  260313C00160000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 88 P</t>
+          <t>ORCL 13MAR26 160 C</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>0.945</v>
+        <v>5.325</v>
       </c>
       <c r="O32" t="n">
-        <v>-189</v>
+        <v>-532.5</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9454876</v>
+        <v>4.5694876</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9454876</v>
+        <v>4.5694876</v>
       </c>
       <c r="R32" t="n">
-        <v>-189.09752</v>
+        <v>-456.94876</v>
       </c>
       <c r="S32" t="n">
-        <v>0.09752</v>
+        <v>-75.55124000000001</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-189</v>
+        <v>-532.5</v>
       </c>
     </row>
     <row r="33">
@@ -3194,60 +3194,60 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ORCL  260313C00160000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ORCL 13MAR26 160 C</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>160</v>
+        <v>425</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>5.6927</v>
+        <v>8.4148</v>
       </c>
       <c r="O33" t="n">
-        <v>-569.27</v>
+        <v>-1682.96</v>
       </c>
       <c r="P33" t="n">
-        <v>4.5694876</v>
+        <v>6.3644671</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.5694876</v>
+        <v>6.3644671</v>
       </c>
       <c r="R33" t="n">
-        <v>-456.94876</v>
+        <v>-1272.89342</v>
       </c>
       <c r="S33" t="n">
-        <v>-112.32124</v>
+        <v>-410.06658</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-569.27</v>
+        <v>-1682.96</v>
       </c>
     </row>
     <row r="34">
@@ -3289,19 +3289,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>SPY   261218P00505000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>SPY 18DEC26 505 P</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>425</v>
+        <v>505</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3315,29 +3315,29 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-2</v>
       </c>
       <c r="N34" t="n">
-        <v>7.9057</v>
+        <v>8.84</v>
       </c>
       <c r="O34" t="n">
-        <v>-1581.14</v>
+        <v>-1768</v>
       </c>
       <c r="P34" t="n">
-        <v>6.3644671</v>
+        <v>7.3548796</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.3644671</v>
+        <v>7.3548796</v>
       </c>
       <c r="R34" t="n">
-        <v>-1272.89342</v>
+        <v>-1470.97592</v>
       </c>
       <c r="S34" t="n">
-        <v>-308.24658</v>
+        <v>-297.02408</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3350,97 +3350,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1581.14</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" t="n">
-        <v>505</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>8.305</v>
-      </c>
-      <c r="O35" t="n">
-        <v>-1661</v>
-      </c>
-      <c r="P35" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="R35" t="n">
-        <v>-1470.97592</v>
-      </c>
-      <c r="S35" t="n">
-        <v>-190.02408</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>-1661</v>
+        <v>-1768</v>
       </c>
     </row>
   </sheetData>
@@ -3581,7 +3491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2831</v>
+        <v>1.2788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3611,17 +3521,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>397.2</v>
+        <v>392.75</v>
       </c>
       <c r="O2" t="n">
-        <v>19860</v>
+        <v>19637.5</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3633,7 +3543,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-1122.956235</v>
+        <v>-1345.456235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3646,7 +3556,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25482.366</v>
+        <v>25112.435</v>
       </c>
     </row>
     <row r="3">
@@ -3661,7 +3571,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2831</v>
+        <v>1.2788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3691,17 +3601,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>12000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5465</v>
+        <v>3.4845</v>
       </c>
       <c r="O3" t="n">
-        <v>42558</v>
+        <v>41814</v>
       </c>
       <c r="P3" t="n">
         <v>3.574177863</v>
@@ -3713,7 +3623,7 @@
         <v>42890.13435</v>
       </c>
       <c r="S3" t="n">
-        <v>-332.13435</v>
+        <v>-1076.13435</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3726,7 +3636,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>54606.1698</v>
+        <v>53471.7432</v>
       </c>
     </row>
     <row r="4">
@@ -3741,7 +3651,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2831</v>
+        <v>1.2788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3771,29 +3681,29 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="N4" t="n">
-        <v>66.04000000000001</v>
+        <v>62.64</v>
       </c>
       <c r="O4" t="n">
-        <v>33020</v>
+        <v>21924</v>
       </c>
       <c r="P4" t="n">
-        <v>65.30711724</v>
+        <v>65.60009794299999</v>
       </c>
       <c r="Q4" t="n">
-        <v>65.30711724</v>
+        <v>65.60009794299999</v>
       </c>
       <c r="R4" t="n">
-        <v>32653.55862</v>
+        <v>22960.03428</v>
       </c>
       <c r="S4" t="n">
-        <v>366.44138</v>
+        <v>-1036.03428</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3806,7 +3716,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>42367.962</v>
+        <v>28036.4112</v>
       </c>
     </row>
     <row r="5">
@@ -3821,7 +3731,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1449</v>
+        <v>0.14455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3851,17 +3761,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.66</v>
+        <v>31.24</v>
       </c>
       <c r="O5" t="n">
-        <v>63320</v>
+        <v>62480</v>
       </c>
       <c r="P5" t="n">
         <v>31.696238595</v>
@@ -3873,7 +3783,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S5" t="n">
-        <v>-72.47718999999999</v>
+        <v>-912.47719</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3886,7 +3796,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9175.067999999999</v>
+        <v>9031.484</v>
       </c>
     </row>
     <row r="6">
@@ -3901,7 +3811,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1689</v>
+        <v>1.1612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3931,17 +3841,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>3000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2195</v>
+        <v>4.095</v>
       </c>
       <c r="O6" t="n">
-        <v>12658.5</v>
+        <v>12285</v>
       </c>
       <c r="P6" t="n">
         <v>4.65841303</v>
@@ -3953,7 +3863,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1316.739091</v>
+        <v>-1690.239091</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3966,7 +3876,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>14796.52065</v>
+        <v>14265.342</v>
       </c>
     </row>
     <row r="7">
@@ -3981,7 +3891,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1689</v>
+        <v>1.1612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4011,17 +3921,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>1000</v>
       </c>
       <c r="N7" t="n">
-        <v>48.67</v>
+        <v>46.75</v>
       </c>
       <c r="O7" t="n">
-        <v>48670</v>
+        <v>46750</v>
       </c>
       <c r="P7" t="n">
         <v>43.01</v>
@@ -4033,7 +3943,7 @@
         <v>43010</v>
       </c>
       <c r="S7" t="n">
-        <v>5660</v>
+        <v>3740</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -4046,7 +3956,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>56890.363</v>
+        <v>54286.1</v>
       </c>
     </row>
     <row r="8">
@@ -4061,7 +3971,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78533</v>
+        <v>0.78278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4091,17 +4001,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.892</v>
+        <v>4.899</v>
       </c>
       <c r="O8" t="n">
-        <v>48920</v>
+        <v>48990</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4113,7 +4023,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11651.8184</v>
+        <v>11721.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4126,7 +4036,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38418.3436</v>
+        <v>38348.3922</v>
       </c>
     </row>
     <row r="9">
@@ -4141,7 +4051,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78533</v>
+        <v>0.78278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4171,17 +4081,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>50</v>
       </c>
       <c r="N9" t="n">
-        <v>631.5</v>
+        <v>622.3</v>
       </c>
       <c r="O9" t="n">
-        <v>31575</v>
+        <v>31115</v>
       </c>
       <c r="P9" t="n">
         <v>581.41476</v>
@@ -4193,7 +4103,7 @@
         <v>29070.738</v>
       </c>
       <c r="S9" t="n">
-        <v>2504.262</v>
+        <v>2044.262</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4206,7 +4116,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>24796.79475</v>
+        <v>24356.1997</v>
       </c>
     </row>
     <row r="10">
@@ -4251,17 +4161,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>8.16</v>
+        <v>7.865</v>
       </c>
       <c r="O10" t="n">
-        <v>8976</v>
+        <v>8651.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4273,7 +4183,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-166.847947</v>
+        <v>-491.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4286,7 +4196,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8976</v>
+        <v>8651.5</v>
       </c>
     </row>
     <row r="11">
@@ -4331,17 +4241,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>300</v>
       </c>
       <c r="N11" t="n">
-        <v>9.529999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2859</v>
+        <v>2820</v>
       </c>
       <c r="P11" t="n">
         <v>11.661666667</v>
@@ -4353,7 +4263,7 @@
         <v>3498.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-639.5</v>
+        <v>-678.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4366,7 +4276,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2859</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="12">
@@ -4411,29 +4321,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N12" t="n">
-        <v>1425.6</v>
+        <v>1410.4</v>
       </c>
       <c r="O12" t="n">
-        <v>28512</v>
+        <v>21156</v>
       </c>
       <c r="P12" t="n">
-        <v>1467.02705</v>
+        <v>1471.727366667</v>
       </c>
       <c r="Q12" t="n">
-        <v>1467.02705</v>
+        <v>1471.727366667</v>
       </c>
       <c r="R12" t="n">
-        <v>29340.541</v>
+        <v>22075.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-828.5410000000001</v>
+        <v>-919.9105</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4446,7 +4356,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>28512</v>
+        <v>21156</v>
       </c>
     </row>
     <row r="13">
@@ -4491,17 +4401,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>306.52</v>
+        <v>303.58</v>
       </c>
       <c r="O13" t="n">
-        <v>30652</v>
+        <v>30358</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4513,7 +4423,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2535.755</v>
+        <v>-2829.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4526,7 +4436,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30652</v>
+        <v>30358</v>
       </c>
     </row>
     <row r="14">
@@ -4571,17 +4481,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>60.56</v>
+        <v>58.03</v>
       </c>
       <c r="O14" t="n">
-        <v>9689.6</v>
+        <v>9284.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4593,7 +4503,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>57.16</v>
+        <v>-347.64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4606,7 +4516,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9689.6</v>
+        <v>9284.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -4651,17 +4561,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>71.67</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>1207.27</v>
+        <v>1169.03</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4673,7 +4583,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>858.223421</v>
+        <v>819.983421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4686,7 +4596,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1207.27</v>
+        <v>1169.03</v>
       </c>
     </row>
     <row r="16">
@@ -4731,17 +4641,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.89</v>
+        <v>25.7761</v>
       </c>
       <c r="O16" t="n">
-        <v>10352.65</v>
+        <v>9923.799999999999</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4753,7 +4663,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>343.744112</v>
+        <v>-85.10588799999999</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4766,7 +4676,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10352.65</v>
+        <v>9923.799999999999</v>
       </c>
     </row>
     <row r="17">
@@ -4811,17 +4721,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>297.56</v>
+        <v>300.26</v>
       </c>
       <c r="O17" t="n">
-        <v>29756</v>
+        <v>30026</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4833,7 +4743,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-46</v>
+        <v>224</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4846,7 +4756,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>29756</v>
+        <v>30026</v>
       </c>
     </row>
     <row r="18">
@@ -4891,17 +4801,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>175.12</v>
+        <v>171.1</v>
       </c>
       <c r="O18" t="n">
-        <v>87560</v>
+        <v>85550</v>
       </c>
       <c r="P18" t="n">
         <v>174.06142722</v>
@@ -4913,7 +4823,7 @@
         <v>87030.71361000001</v>
       </c>
       <c r="S18" t="n">
-        <v>529.28639</v>
+        <v>-1480.71361</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4926,7 +4836,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>87560</v>
+        <v>85550</v>
       </c>
     </row>
     <row r="19">
@@ -4981,17 +4891,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.625</v>
+        <v>0.51</v>
       </c>
       <c r="O19" t="n">
-        <v>62.5</v>
+        <v>51</v>
       </c>
       <c r="P19" t="n">
         <v>2.1405125</v>
@@ -5003,7 +4913,7 @@
         <v>214.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-151.55125</v>
+        <v>-163.05125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -5016,7 +4926,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>62.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -5071,17 +4981,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="O20" t="n">
-        <v>430</v>
+        <v>610</v>
       </c>
       <c r="P20" t="n">
         <v>4.6805125</v>
@@ -5093,7 +5003,7 @@
         <v>468.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-38.05125</v>
+        <v>141.94875</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5106,7 +5016,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>430</v>
+        <v>610</v>
       </c>
     </row>
     <row r="21">
@@ -5161,17 +5071,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>12.9657</v>
+        <v>13.508</v>
       </c>
       <c r="O21" t="n">
-        <v>1296.57</v>
+        <v>1350.8</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5183,7 +5093,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>1044.51875</v>
+        <v>1098.74875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5196,7 +5106,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>1296.57</v>
+        <v>1350.8</v>
       </c>
     </row>
     <row r="22">
@@ -5251,17 +5161,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.445</v>
+        <v>0.27</v>
       </c>
       <c r="O22" t="n">
-        <v>44.5</v>
+        <v>27</v>
       </c>
       <c r="P22" t="n">
         <v>2.6805125</v>
@@ -5273,7 +5183,7 @@
         <v>268.05125</v>
       </c>
       <c r="S22" t="n">
-        <v>-223.55125</v>
+        <v>-241.05125</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5286,7 +5196,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>44.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -5341,17 +5251,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>28.639</v>
+        <v>30.57</v>
       </c>
       <c r="O23" t="n">
-        <v>5727.8</v>
+        <v>6114</v>
       </c>
       <c r="P23" t="n">
         <v>23.5270125</v>
@@ -5363,7 +5273,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S23" t="n">
-        <v>1022.3975</v>
+        <v>1408.5975</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5376,7 +5286,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5727.8</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="24">
@@ -5431,17 +5341,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>22.325</v>
+        <v>24.015</v>
       </c>
       <c r="O24" t="n">
-        <v>4465</v>
+        <v>4803</v>
       </c>
       <c r="P24" t="n">
         <v>20.1350875</v>
@@ -5453,7 +5363,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S24" t="n">
-        <v>437.9825</v>
+        <v>775.9825</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5466,7 +5376,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>4465</v>
+        <v>4803</v>
       </c>
     </row>
     <row r="25">
@@ -5521,17 +5431,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.995</v>
+        <v>3.275</v>
       </c>
       <c r="O25" t="n">
-        <v>-299.5</v>
+        <v>-327.5</v>
       </c>
       <c r="P25" t="n">
         <v>1.7694546</v>
@@ -5543,7 +5453,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>-122.55454</v>
+        <v>-150.55454</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5556,7 +5466,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-299.5</v>
+        <v>-327.5</v>
       </c>
     </row>
     <row r="26">
@@ -5611,17 +5521,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.105</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-110.5</v>
+        <v>-94</v>
       </c>
       <c r="P26" t="n">
         <v>3.4194546</v>
@@ -5633,7 +5543,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>231.44546</v>
+        <v>247.94546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5646,7 +5556,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-110.5</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="27">
@@ -5701,17 +5611,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>6.125</v>
+        <v>8.275</v>
       </c>
       <c r="O27" t="n">
-        <v>-612.5</v>
+        <v>-827.5</v>
       </c>
       <c r="P27" t="n">
         <v>4.1794546</v>
@@ -5723,7 +5633,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>-194.55454</v>
+        <v>-409.55454</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5736,7 +5646,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-612.5</v>
+        <v>-827.5</v>
       </c>
     </row>
     <row r="28">
@@ -5791,17 +5701,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="O28" t="n">
-        <v>-62</v>
+        <v>-38</v>
       </c>
       <c r="P28" t="n">
         <v>2.3694546</v>
@@ -5813,7 +5723,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>174.94546</v>
+        <v>198.94546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5826,7 +5736,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-62</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="29">
@@ -5881,17 +5791,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="O29" t="n">
-        <v>-211</v>
+        <v>-208</v>
       </c>
       <c r="P29" t="n">
         <v>1.7994546</v>
@@ -5903,7 +5813,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>-31.05454</v>
+        <v>-28.05454</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5916,7 +5826,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-211</v>
+        <v>-208</v>
       </c>
     </row>
     <row r="30">
@@ -5971,17 +5881,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.625</v>
+        <v>0.575</v>
       </c>
       <c r="O30" t="n">
-        <v>-62.5</v>
+        <v>-57.5</v>
       </c>
       <c r="P30" t="n">
         <v>1.0594546</v>
@@ -5993,7 +5903,7 @@
         <v>-105.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>43.44546</v>
+        <v>48.44546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -6006,7 +5916,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-62.5</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -6061,17 +5971,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.545</v>
+        <v>0.42</v>
       </c>
       <c r="O31" t="n">
-        <v>-54.5</v>
+        <v>-42</v>
       </c>
       <c r="P31" t="n">
         <v>3.6594796</v>
@@ -6083,7 +5993,7 @@
         <v>-365.94796</v>
       </c>
       <c r="S31" t="n">
-        <v>311.44796</v>
+        <v>323.94796</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6096,7 +6006,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-54.5</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="32">
@@ -6151,17 +6061,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.745</v>
+        <v>2.095</v>
       </c>
       <c r="O32" t="n">
-        <v>-274.5</v>
+        <v>-209.5</v>
       </c>
       <c r="P32" t="n">
         <v>4.6494796</v>
@@ -6173,7 +6083,7 @@
         <v>-464.94796</v>
       </c>
       <c r="S32" t="n">
-        <v>190.44796</v>
+        <v>255.44796</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6186,7 +6096,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-274.5</v>
+        <v>-209.5</v>
       </c>
     </row>
     <row r="33">
@@ -6241,17 +6151,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>4.275</v>
+        <v>5.3</v>
       </c>
       <c r="O33" t="n">
-        <v>-427.5</v>
+        <v>-530</v>
       </c>
       <c r="P33" t="n">
         <v>4.4694546</v>
@@ -6263,7 +6173,7 @@
         <v>-446.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>19.44546</v>
+        <v>-83.05454</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6276,7 +6186,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-427.5</v>
+        <v>-530</v>
       </c>
     </row>
     <row r="34">
@@ -6331,17 +6241,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.145</v>
+        <v>1.8514</v>
       </c>
       <c r="O34" t="n">
-        <v>-214.5</v>
+        <v>-185.14</v>
       </c>
       <c r="P34" t="n">
         <v>2.1094546</v>
@@ -6353,7 +6263,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-3.55454</v>
+        <v>25.80546</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6366,7 +6276,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-214.5</v>
+        <v>-185.14</v>
       </c>
     </row>
     <row r="35">
@@ -6421,17 +6331,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>5.7</v>
+        <v>7.925</v>
       </c>
       <c r="O35" t="n">
-        <v>-570</v>
+        <v>-792.5</v>
       </c>
       <c r="P35" t="n">
         <v>5.9994546</v>
@@ -6443,7 +6353,7 @@
         <v>-599.94546</v>
       </c>
       <c r="S35" t="n">
-        <v>29.94546</v>
+        <v>-192.55454</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6456,7 +6366,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-570</v>
+        <v>-792.5</v>
       </c>
     </row>
     <row r="36">
@@ -6511,17 +6421,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-1</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1323</v>
+        <v>0.1222</v>
       </c>
       <c r="O36" t="n">
-        <v>-13.23</v>
+        <v>-12.22</v>
       </c>
       <c r="P36" t="n">
         <v>0.8794546</v>
@@ -6533,7 +6443,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S36" t="n">
-        <v>74.71545999999999</v>
+        <v>75.72546</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6546,7 +6456,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-13.23</v>
+        <v>-12.22</v>
       </c>
     </row>
     <row r="37">
@@ -6601,17 +6511,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M37" t="n">
         <v>-1</v>
       </c>
       <c r="N37" t="n">
-        <v>14.809</v>
+        <v>15.3637</v>
       </c>
       <c r="O37" t="n">
-        <v>-1480.9</v>
+        <v>-1536.37</v>
       </c>
       <c r="P37" t="n">
         <v>3.2794546</v>
@@ -6623,7 +6533,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S37" t="n">
-        <v>-1152.95454</v>
+        <v>-1208.42454</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -6636,7 +6546,7 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>-1480.9</v>
+        <v>-1536.37</v>
       </c>
     </row>
     <row r="38">
@@ -6691,17 +6601,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M38" t="n">
         <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="O38" t="n">
-        <v>-405</v>
+        <v>-470</v>
       </c>
       <c r="P38" t="n">
         <v>3.0294546</v>
@@ -6713,7 +6623,7 @@
         <v>-302.94546</v>
       </c>
       <c r="S38" t="n">
-        <v>-102.05454</v>
+        <v>-167.05454</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -6726,7 +6636,7 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>-405</v>
+        <v>-470</v>
       </c>
     </row>
     <row r="39">
@@ -6781,17 +6691,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M39" t="n">
         <v>-1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.66</v>
+        <v>0.4</v>
       </c>
       <c r="O39" t="n">
-        <v>-66</v>
+        <v>-40</v>
       </c>
       <c r="P39" t="n">
         <v>3.6694546</v>
@@ -6803,7 +6713,7 @@
         <v>-366.94546</v>
       </c>
       <c r="S39" t="n">
-        <v>300.94546</v>
+        <v>326.94546</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -6816,7 +6726,7 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>-66</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="40">
@@ -6871,17 +6781,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M40" t="n">
         <v>-2</v>
       </c>
       <c r="N40" t="n">
-        <v>7.9057</v>
+        <v>8.4148</v>
       </c>
       <c r="O40" t="n">
-        <v>-1581.14</v>
+        <v>-1682.96</v>
       </c>
       <c r="P40" t="n">
         <v>6.3929546</v>
@@ -6893,7 +6803,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S40" t="n">
-        <v>-302.54908</v>
+        <v>-404.36908</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6906,7 +6816,7 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>-1581.14</v>
+        <v>-1682.96</v>
       </c>
     </row>
     <row r="41">
@@ -6961,17 +6871,17 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="M41" t="n">
         <v>-2</v>
       </c>
       <c r="N41" t="n">
-        <v>8.305</v>
+        <v>8.84</v>
       </c>
       <c r="O41" t="n">
-        <v>-1661</v>
+        <v>-1768</v>
       </c>
       <c r="P41" t="n">
         <v>7.3496796</v>
@@ -6983,7 +6893,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S41" t="n">
-        <v>-191.06408</v>
+        <v>-298.06408</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6996,7 +6906,7 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>-1661</v>
+        <v>-1768</v>
       </c>
     </row>
   </sheetData>
@@ -7043,17 +6953,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$334,122.57</t>
+          <t>$323,990.51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$106,071.11</t>
+          <t>$108,786.87</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$440,193.68</t>
+          <t>$432,777.38</t>
         </is>
       </c>
     </row>
@@ -7065,17 +6975,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$480,018.21</t>
+          <t>$449,981.85</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$77,232.69</t>
+          <t>$96,384.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$557,250.89</t>
+          <t>$546,366.07</t>
         </is>
       </c>
     </row>
@@ -7093,17 +7003,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$814,140.78</t>
+          <t>$773,972.36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$183,303.80</t>
+          <t>$205,171.10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$997,444.57</t>
+          <t>$979,143.45</t>
         </is>
       </c>
     </row>
@@ -7151,11 +7061,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-03 23:52:22</t>
+          <t>2026-03-04 23:53:49</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
         <v>40</v>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2788</v>
+        <v>1.2835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>392.75</v>
+        <v>401.1</v>
       </c>
       <c r="O2" t="n">
-        <v>15710</v>
+        <v>16044</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-998.503607</v>
+        <v>-664.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20089.948</v>
+        <v>20592.474</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2788</v>
+        <v>1.2835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>10000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4845</v>
+        <v>3.5335</v>
       </c>
       <c r="O3" t="n">
-        <v>34845</v>
+        <v>35335</v>
       </c>
       <c r="P3" t="n">
         <v>3.576275343</v>
@@ -687,7 +687,7 @@
         <v>35762.753425</v>
       </c>
       <c r="S3" t="n">
-        <v>-917.753425</v>
+        <v>-427.753425</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>44559.786</v>
+        <v>45352.4725</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2788</v>
+        <v>1.2835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>250</v>
       </c>
       <c r="N4" t="n">
-        <v>62.64</v>
+        <v>63.67</v>
       </c>
       <c r="O4" t="n">
-        <v>15660</v>
+        <v>15917.5</v>
       </c>
       <c r="P4" t="n">
         <v>65.233413332</v>
@@ -767,7 +767,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S4" t="n">
-        <v>-648.353333</v>
+        <v>-390.853333</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>20026.008</v>
+        <v>20430.11125</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14455</v>
+        <v>0.14504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.24</v>
+        <v>30.96</v>
       </c>
       <c r="O5" t="n">
-        <v>93720</v>
+        <v>92880</v>
       </c>
       <c r="P5" t="n">
         <v>31.36596519</v>
@@ -847,7 +847,7 @@
         <v>94097.89556999999</v>
       </c>
       <c r="S5" t="n">
-        <v>-377.89557</v>
+        <v>-1217.89557</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13547.226</v>
+        <v>13471.3152</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1612</v>
+        <v>1.1635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>2000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.095</v>
+        <v>4.147</v>
       </c>
       <c r="O6" t="n">
-        <v>8190</v>
+        <v>8294</v>
       </c>
       <c r="P6" t="n">
         <v>4.66233</v>
@@ -927,7 +927,7 @@
         <v>9324.66</v>
       </c>
       <c r="S6" t="n">
-        <v>-1134.66</v>
+        <v>-1030.66</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9510.228000000001</v>
+        <v>9650.069</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78278</v>
+        <v>0.78401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SPDR STRAITS TIMES INDEX ETF</t>
+          <t>STATE STRT SPDR STRAITS TIME</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.899</v>
+        <v>4.809</v>
       </c>
       <c r="O7" t="n">
-        <v>39192</v>
+        <v>38472</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1880.77315</v>
+        <v>1160.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30678.71376</v>
+        <v>30162.43272</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78278</v>
+        <v>0.78401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,29 +1065,29 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>622.3</v>
+        <v>606.3</v>
       </c>
       <c r="O8" t="n">
-        <v>31115</v>
+        <v>45472.5</v>
       </c>
       <c r="P8" t="n">
-        <v>581.20939584</v>
+        <v>589.78798656</v>
       </c>
       <c r="Q8" t="n">
-        <v>581.20939584</v>
+        <v>589.78798656</v>
       </c>
       <c r="R8" t="n">
-        <v>29060.469792</v>
+        <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>2054.530208</v>
+        <v>1238.401008</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>24356.1997</v>
+        <v>35650.894725</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.865</v>
+        <v>7.76</v>
       </c>
       <c r="O9" t="n">
-        <v>7865</v>
+        <v>7760</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-446.237657</v>
+        <v>-551.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7865</v>
+        <v>7760</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>9.4</v>
+        <v>10.07</v>
       </c>
       <c r="O10" t="n">
-        <v>940</v>
+        <v>1007</v>
       </c>
       <c r="P10" t="n">
         <v>9.705</v>
@@ -1247,7 +1247,7 @@
         <v>970.5</v>
       </c>
       <c r="S10" t="n">
-        <v>-30.5</v>
+        <v>36.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>940</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1410.4</v>
+        <v>1435.6</v>
       </c>
       <c r="O11" t="n">
-        <v>14104</v>
+        <v>14356</v>
       </c>
       <c r="P11" t="n">
         <v>1474.045</v>
@@ -1327,7 +1327,7 @@
         <v>14740.45</v>
       </c>
       <c r="S11" t="n">
-        <v>-636.45</v>
+        <v>-384.45</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>14104</v>
+        <v>14356</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>303.58</v>
+        <v>303.13</v>
       </c>
       <c r="O12" t="n">
-        <v>30358</v>
+        <v>30313</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>194.5</v>
+        <v>149.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30358</v>
+        <v>30313</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>58.03</v>
+        <v>58.72</v>
       </c>
       <c r="O13" t="n">
-        <v>9284.799999999999</v>
+        <v>9395.200000000001</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-291.86</v>
+        <v>-181.46</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9284.799999999999</v>
+        <v>9395.200000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>25.7761</v>
+        <v>26.5453</v>
       </c>
       <c r="O14" t="n">
-        <v>9923.799999999999</v>
+        <v>10219.94</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>-91.102822</v>
+        <v>205.037178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9923.799999999999</v>
+        <v>10219.94</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>149.01</v>
+        <v>152.37</v>
       </c>
       <c r="O15" t="n">
-        <v>14901</v>
+        <v>15237</v>
       </c>
       <c r="P15" t="n">
         <v>205.3357044</v>
@@ -1647,7 +1647,7 @@
         <v>20533.57044</v>
       </c>
       <c r="S15" t="n">
-        <v>-5632.57044</v>
+        <v>-5296.57044</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>14901</v>
+        <v>15237</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>87.81999999999999</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>1756.4</v>
+        <v>1765.2</v>
       </c>
       <c r="P16" t="n">
         <v>124.315</v>
@@ -1727,7 +1727,7 @@
         <v>2486.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-729.9</v>
+        <v>-721.1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1756.4</v>
+        <v>1765.2</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>400</v>
       </c>
       <c r="N17" t="n">
-        <v>171.1</v>
+        <v>173.76</v>
       </c>
       <c r="O17" t="n">
-        <v>68440</v>
+        <v>69504</v>
       </c>
       <c r="P17" t="n">
         <v>173.855759437</v>
@@ -1807,7 +1807,7 @@
         <v>69542.30377499999</v>
       </c>
       <c r="S17" t="n">
-        <v>-1102.303775</v>
+        <v>-38.303775</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>68440</v>
+        <v>69504</v>
       </c>
     </row>
     <row r="18">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="O18" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="P18" t="n">
         <v>2.0105125</v>
@@ -1897,7 +1897,7 @@
         <v>201.05125</v>
       </c>
       <c r="S18" t="n">
-        <v>-150.05125</v>
+        <v>-164.05125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>6.1</v>
+        <v>6.175</v>
       </c>
       <c r="O19" t="n">
-        <v>610</v>
+        <v>617.5</v>
       </c>
       <c r="P19" t="n">
         <v>4.4905125</v>
@@ -1987,7 +1987,7 @@
         <v>449.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>160.94875</v>
+        <v>168.44875</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>610</v>
+        <v>617.5</v>
       </c>
     </row>
     <row r="20">
@@ -2055,17 +2055,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>30.57</v>
+        <v>27.5466</v>
       </c>
       <c r="O20" t="n">
-        <v>6114</v>
+        <v>5509.32</v>
       </c>
       <c r="P20" t="n">
         <v>23.4605</v>
@@ -2077,7 +2077,7 @@
         <v>4692.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1421.9</v>
+        <v>817.22</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>6114</v>
+        <v>5509.32</v>
       </c>
     </row>
     <row r="21">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>24.015</v>
+        <v>22.12</v>
       </c>
       <c r="O21" t="n">
-        <v>4803</v>
+        <v>4424</v>
       </c>
       <c r="P21" t="n">
         <v>20.1374875</v>
@@ -2167,7 +2167,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S21" t="n">
-        <v>775.5025000000001</v>
+        <v>396.5025</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>4803</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="22">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.275</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>-327.5</v>
+        <v>-310</v>
       </c>
       <c r="P22" t="n">
         <v>1.7494546</v>
@@ -2257,7 +2257,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S22" t="n">
-        <v>-152.55454</v>
+        <v>-135.05454</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-327.5</v>
+        <v>-310</v>
       </c>
     </row>
     <row r="23">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="O23" t="n">
-        <v>-94</v>
+        <v>-73</v>
       </c>
       <c r="P23" t="n">
         <v>3.2494546</v>
@@ -2347,7 +2347,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>230.94546</v>
+        <v>251.94546</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-94</v>
+        <v>-73</v>
       </c>
     </row>
     <row r="24">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>8.275</v>
+        <v>4.925</v>
       </c>
       <c r="O24" t="n">
-        <v>-827.5</v>
+        <v>-492.5</v>
       </c>
       <c r="P24" t="n">
         <v>7.5800876</v>
@@ -2437,7 +2437,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-69.49124</v>
+        <v>265.50876</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-827.5</v>
+        <v>-492.5</v>
       </c>
     </row>
     <row r="25">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>1.0704</v>
       </c>
       <c r="O25" t="n">
-        <v>-208</v>
+        <v>-107.04</v>
       </c>
       <c r="P25" t="n">
         <v>1.8142796</v>
@@ -2527,7 +2527,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S25" t="n">
-        <v>-26.57204</v>
+        <v>74.38796000000001</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-208</v>
+        <v>-107.04</v>
       </c>
     </row>
     <row r="26">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.575</v>
+        <v>1.255</v>
       </c>
       <c r="O26" t="n">
-        <v>-57.5</v>
+        <v>-125.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.0242796</v>
@@ -2617,7 +2617,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>44.92796</v>
+        <v>-23.07204</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-57.5</v>
+        <v>-125.5</v>
       </c>
     </row>
     <row r="27">
@@ -2685,29 +2685,29 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N27" t="n">
-        <v>6.925</v>
+        <v>6.5496</v>
       </c>
       <c r="O27" t="n">
-        <v>-692.5</v>
+        <v>-1309.92</v>
       </c>
       <c r="P27" t="n">
-        <v>6.8094876</v>
+        <v>6.6394751</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.8094876</v>
+        <v>6.6394751</v>
       </c>
       <c r="R27" t="n">
-        <v>-680.94876</v>
+        <v>-1327.89502</v>
       </c>
       <c r="S27" t="n">
-        <v>-11.55124</v>
+        <v>17.97502</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-692.5</v>
+        <v>-1309.92</v>
       </c>
     </row>
     <row r="28">
@@ -2775,17 +2775,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>5.825</v>
+        <v>5.175</v>
       </c>
       <c r="O28" t="n">
-        <v>-582.5</v>
+        <v>-517.5</v>
       </c>
       <c r="P28" t="n">
         <v>6.7894876</v>
@@ -2797,7 +2797,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S28" t="n">
-        <v>96.44875999999999</v>
+        <v>161.44876</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-582.5</v>
+        <v>-517.5</v>
       </c>
     </row>
     <row r="29">
@@ -2865,17 +2865,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.8514</v>
+        <v>1.645</v>
       </c>
       <c r="O29" t="n">
-        <v>-185.14</v>
+        <v>-164.5</v>
       </c>
       <c r="P29" t="n">
         <v>2.1194546</v>
@@ -2887,7 +2887,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>26.80546</v>
+        <v>47.44546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-185.14</v>
+        <v>-164.5</v>
       </c>
     </row>
     <row r="30">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>7.925</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>-792.5</v>
+        <v>-805</v>
       </c>
       <c r="P30" t="n">
         <v>5.7894546</v>
@@ -2977,7 +2977,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>-213.55454</v>
+        <v>-226.05454</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-792.5</v>
+        <v>-805</v>
       </c>
     </row>
     <row r="31">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.89</v>
+        <v>0.65</v>
       </c>
       <c r="O31" t="n">
-        <v>-178</v>
+        <v>-130</v>
       </c>
       <c r="P31" t="n">
         <v>0.9454876</v>
@@ -3067,7 +3067,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S31" t="n">
-        <v>11.09752</v>
+        <v>59.09752</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-178</v>
+        <v>-130</v>
       </c>
     </row>
     <row r="32">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>5.325</v>
+        <v>6.3216</v>
       </c>
       <c r="O32" t="n">
-        <v>-532.5</v>
+        <v>-632.16</v>
       </c>
       <c r="P32" t="n">
         <v>4.5694876</v>
@@ -3157,7 +3157,7 @@
         <v>-456.94876</v>
       </c>
       <c r="S32" t="n">
-        <v>-75.55124000000001</v>
+        <v>-175.21124</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-532.5</v>
+        <v>-632.16</v>
       </c>
     </row>
     <row r="33">
@@ -3225,17 +3225,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>8.4148</v>
+        <v>7.5836</v>
       </c>
       <c r="O33" t="n">
-        <v>-1682.96</v>
+        <v>-1516.72</v>
       </c>
       <c r="P33" t="n">
         <v>6.3644671</v>
@@ -3247,7 +3247,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S33" t="n">
-        <v>-410.06658</v>
+        <v>-243.82658</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1682.96</v>
+        <v>-1516.72</v>
       </c>
     </row>
     <row r="34">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-2</v>
       </c>
       <c r="N34" t="n">
-        <v>8.84</v>
+        <v>8.115</v>
       </c>
       <c r="O34" t="n">
-        <v>-1768</v>
+        <v>-1623</v>
       </c>
       <c r="P34" t="n">
         <v>7.3548796</v>
@@ -3337,7 +3337,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S34" t="n">
-        <v>-297.02408</v>
+        <v>-152.02408</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1768</v>
+        <v>-1623</v>
       </c>
     </row>
   </sheetData>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2788</v>
+        <v>1.2835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3521,17 +3521,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>392.75</v>
+        <v>401.1</v>
       </c>
       <c r="O2" t="n">
-        <v>19637.5</v>
+        <v>20055</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3543,7 +3543,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-1345.456235</v>
+        <v>-927.956235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25112.435</v>
+        <v>25740.5925</v>
       </c>
     </row>
     <row r="3">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2788</v>
+        <v>1.2835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3601,17 +3601,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>12000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4845</v>
+        <v>3.5335</v>
       </c>
       <c r="O3" t="n">
-        <v>41814</v>
+        <v>42402</v>
       </c>
       <c r="P3" t="n">
         <v>3.574177863</v>
@@ -3623,7 +3623,7 @@
         <v>42890.13435</v>
       </c>
       <c r="S3" t="n">
-        <v>-1076.13435</v>
+        <v>-488.13435</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>53471.7432</v>
+        <v>54422.967</v>
       </c>
     </row>
     <row r="4">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2788</v>
+        <v>1.2835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3681,17 +3681,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>350</v>
       </c>
       <c r="N4" t="n">
-        <v>62.64</v>
+        <v>63.67</v>
       </c>
       <c r="O4" t="n">
-        <v>21924</v>
+        <v>22284.5</v>
       </c>
       <c r="P4" t="n">
         <v>65.60009794299999</v>
@@ -3703,7 +3703,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S4" t="n">
-        <v>-1036.03428</v>
+        <v>-675.53428</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>28036.4112</v>
+        <v>28602.15575</v>
       </c>
     </row>
     <row r="5">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14455</v>
+        <v>0.14504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3761,17 +3761,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.24</v>
+        <v>30.96</v>
       </c>
       <c r="O5" t="n">
-        <v>62480</v>
+        <v>61920</v>
       </c>
       <c r="P5" t="n">
         <v>31.696238595</v>
@@ -3783,7 +3783,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S5" t="n">
-        <v>-912.47719</v>
+        <v>-1472.47719</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9031.484</v>
+        <v>8980.8768</v>
       </c>
     </row>
     <row r="6">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1612</v>
+        <v>1.1635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3841,17 +3841,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>3000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.095</v>
+        <v>4.147</v>
       </c>
       <c r="O6" t="n">
-        <v>12285</v>
+        <v>12441</v>
       </c>
       <c r="P6" t="n">
         <v>4.65841303</v>
@@ -3863,7 +3863,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1690.239091</v>
+        <v>-1534.239091</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>14265.342</v>
+        <v>14475.1035</v>
       </c>
     </row>
     <row r="7">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1612</v>
+        <v>1.1635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3921,17 +3921,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>1000</v>
       </c>
       <c r="N7" t="n">
-        <v>46.75</v>
+        <v>48.12</v>
       </c>
       <c r="O7" t="n">
-        <v>46750</v>
+        <v>48120</v>
       </c>
       <c r="P7" t="n">
         <v>43.01</v>
@@ -3943,7 +3943,7 @@
         <v>43010</v>
       </c>
       <c r="S7" t="n">
-        <v>3740</v>
+        <v>5110</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>54286.1</v>
+        <v>55987.62</v>
       </c>
     </row>
     <row r="8">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78278</v>
+        <v>0.78401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SPDR STRAITS TIMES INDEX ETF</t>
+          <t>STATE STRT SPDR STRAITS TIME</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -4001,17 +4001,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.899</v>
+        <v>4.809</v>
       </c>
       <c r="O8" t="n">
-        <v>48990</v>
+        <v>48090</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4023,7 +4023,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11721.8184</v>
+        <v>10821.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38348.3922</v>
+        <v>37703.0409</v>
       </c>
     </row>
     <row r="9">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78278</v>
+        <v>0.78401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4081,29 +4081,29 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>622.3</v>
+        <v>606.3</v>
       </c>
       <c r="O9" t="n">
-        <v>31115</v>
+        <v>45472.5</v>
       </c>
       <c r="P9" t="n">
-        <v>581.41476</v>
+        <v>589.644672</v>
       </c>
       <c r="Q9" t="n">
-        <v>581.41476</v>
+        <v>589.644672</v>
       </c>
       <c r="R9" t="n">
-        <v>29070.738</v>
+        <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>2044.262</v>
+        <v>1249.1496</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>24356.1997</v>
+        <v>35650.894725</v>
       </c>
     </row>
     <row r="10">
@@ -4161,17 +4161,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.865</v>
+        <v>7.76</v>
       </c>
       <c r="O10" t="n">
-        <v>8651.5</v>
+        <v>8536</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4183,7 +4183,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-491.347947</v>
+        <v>-606.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8651.5</v>
+        <v>8536</v>
       </c>
     </row>
     <row r="11">
@@ -4241,17 +4241,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>300</v>
       </c>
       <c r="N11" t="n">
-        <v>9.4</v>
+        <v>10.07</v>
       </c>
       <c r="O11" t="n">
-        <v>2820</v>
+        <v>3021</v>
       </c>
       <c r="P11" t="n">
         <v>11.661666667</v>
@@ -4263,7 +4263,7 @@
         <v>3498.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-678.5</v>
+        <v>-477.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2820</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="12">
@@ -4321,17 +4321,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>15</v>
       </c>
       <c r="N12" t="n">
-        <v>1410.4</v>
+        <v>1435.6</v>
       </c>
       <c r="O12" t="n">
-        <v>21156</v>
+        <v>21534</v>
       </c>
       <c r="P12" t="n">
         <v>1471.727366667</v>
@@ -4343,7 +4343,7 @@
         <v>22075.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-919.9105</v>
+        <v>-541.9105</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>21156</v>
+        <v>21534</v>
       </c>
     </row>
     <row r="13">
@@ -4401,17 +4401,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>303.58</v>
+        <v>303.13</v>
       </c>
       <c r="O13" t="n">
-        <v>30358</v>
+        <v>30313</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4423,7 +4423,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2829.755</v>
+        <v>-2874.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30358</v>
+        <v>30313</v>
       </c>
     </row>
     <row r="14">
@@ -4481,17 +4481,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>58.03</v>
+        <v>58.72</v>
       </c>
       <c r="O14" t="n">
-        <v>9284.799999999999</v>
+        <v>9395.200000000001</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4503,7 +4503,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-347.64</v>
+        <v>-237.24</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9284.799999999999</v>
+        <v>9395.200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4561,17 +4561,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>69.40000000000001</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>1169.03</v>
+        <v>1164.82</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4583,7 +4583,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>819.983421</v>
+        <v>815.773421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1169.03</v>
+        <v>1164.82</v>
       </c>
     </row>
     <row r="16">
@@ -4641,17 +4641,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>25.7761</v>
+        <v>26.5453</v>
       </c>
       <c r="O16" t="n">
-        <v>9923.799999999999</v>
+        <v>10219.94</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4663,7 +4663,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>-85.10588799999999</v>
+        <v>211.034112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>9923.799999999999</v>
+        <v>10219.94</v>
       </c>
     </row>
     <row r="17">
@@ -4721,17 +4721,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>300.26</v>
+        <v>299.39</v>
       </c>
       <c r="O17" t="n">
-        <v>30026</v>
+        <v>29939</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4743,7 +4743,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>224</v>
+        <v>137</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>30026</v>
+        <v>29939</v>
       </c>
     </row>
     <row r="18">
@@ -4801,17 +4801,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>171.1</v>
+        <v>173.76</v>
       </c>
       <c r="O18" t="n">
-        <v>85550</v>
+        <v>86880</v>
       </c>
       <c r="P18" t="n">
         <v>174.06142722</v>
@@ -4823,7 +4823,7 @@
         <v>87030.71361000001</v>
       </c>
       <c r="S18" t="n">
-        <v>-1480.71361</v>
+        <v>-150.71361</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>85550</v>
+        <v>86880</v>
       </c>
     </row>
     <row r="19">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="O19" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="P19" t="n">
         <v>2.1405125</v>
@@ -4913,7 +4913,7 @@
         <v>214.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-163.05125</v>
+        <v>-177.05125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>6.175</v>
       </c>
       <c r="O20" t="n">
-        <v>610</v>
+        <v>617.5</v>
       </c>
       <c r="P20" t="n">
         <v>4.6805125</v>
@@ -5003,7 +5003,7 @@
         <v>468.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>141.94875</v>
+        <v>149.44875</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>610</v>
+        <v>617.5</v>
       </c>
     </row>
     <row r="21">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>13.508</v>
+        <v>14.3469</v>
       </c>
       <c r="O21" t="n">
-        <v>1350.8</v>
+        <v>1434.69</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5093,7 +5093,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>1098.74875</v>
+        <v>1182.63875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>1350.8</v>
+        <v>1434.69</v>
       </c>
     </row>
     <row r="22">
@@ -5161,17 +5161,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="O22" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P22" t="n">
         <v>2.6805125</v>
@@ -5183,7 +5183,7 @@
         <v>268.05125</v>
       </c>
       <c r="S22" t="n">
-        <v>-241.05125</v>
+        <v>-239.05125</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>30.57</v>
+        <v>27.5466</v>
       </c>
       <c r="O23" t="n">
-        <v>6114</v>
+        <v>5509.32</v>
       </c>
       <c r="P23" t="n">
         <v>23.5270125</v>
@@ -5273,7 +5273,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S23" t="n">
-        <v>1408.5975</v>
+        <v>803.9175</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>6114</v>
+        <v>5509.32</v>
       </c>
     </row>
     <row r="24">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>24.015</v>
+        <v>22.12</v>
       </c>
       <c r="O24" t="n">
-        <v>4803</v>
+        <v>4424</v>
       </c>
       <c r="P24" t="n">
         <v>20.1350875</v>
@@ -5363,7 +5363,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S24" t="n">
-        <v>775.9825</v>
+        <v>396.9825</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>4803</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="25">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.275</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>-327.5</v>
+        <v>-310</v>
       </c>
       <c r="P25" t="n">
         <v>1.7694546</v>
@@ -5453,7 +5453,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>-150.55454</v>
+        <v>-133.05454</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-327.5</v>
+        <v>-310</v>
       </c>
     </row>
     <row r="26">
@@ -5521,17 +5521,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="O26" t="n">
-        <v>-94</v>
+        <v>-73</v>
       </c>
       <c r="P26" t="n">
         <v>3.4194546</v>
@@ -5543,7 +5543,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>247.94546</v>
+        <v>268.94546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-94</v>
+        <v>-73</v>
       </c>
     </row>
     <row r="27">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>8.275</v>
+        <v>4.925</v>
       </c>
       <c r="O27" t="n">
-        <v>-827.5</v>
+        <v>-492.5</v>
       </c>
       <c r="P27" t="n">
         <v>4.1794546</v>
@@ -5633,7 +5633,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>-409.55454</v>
+        <v>-74.55454</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-827.5</v>
+        <v>-492.5</v>
       </c>
     </row>
     <row r="28">
@@ -5701,17 +5701,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.38</v>
+        <v>0.625</v>
       </c>
       <c r="O28" t="n">
-        <v>-38</v>
+        <v>-62.5</v>
       </c>
       <c r="P28" t="n">
         <v>2.3694546</v>
@@ -5723,7 +5723,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>198.94546</v>
+        <v>174.44546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-38</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="29">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.08</v>
+        <v>1.0704</v>
       </c>
       <c r="O29" t="n">
-        <v>-208</v>
+        <v>-107.04</v>
       </c>
       <c r="P29" t="n">
         <v>1.7994546</v>
@@ -5813,7 +5813,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>-28.05454</v>
+        <v>72.90546000000001</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-208</v>
+        <v>-107.04</v>
       </c>
     </row>
     <row r="30">
@@ -5881,17 +5881,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.575</v>
+        <v>1.255</v>
       </c>
       <c r="O30" t="n">
-        <v>-57.5</v>
+        <v>-125.5</v>
       </c>
       <c r="P30" t="n">
         <v>1.0594546</v>
@@ -5903,7 +5903,7 @@
         <v>-105.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>48.44546</v>
+        <v>-19.55454</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-57.5</v>
+        <v>-125.5</v>
       </c>
     </row>
     <row r="31">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GOOGL 260304P00295000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GOOGL 04MAR26 295 P</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -5971,29 +5971,29 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.42</v>
+        <v>6.5496</v>
       </c>
       <c r="O31" t="n">
-        <v>-42</v>
+        <v>-654.96</v>
       </c>
       <c r="P31" t="n">
-        <v>3.6594796</v>
+        <v>5.9694626</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6594796</v>
+        <v>5.9694626</v>
       </c>
       <c r="R31" t="n">
-        <v>-365.94796</v>
+        <v>-596.9462600000001</v>
       </c>
       <c r="S31" t="n">
-        <v>323.94796</v>
+        <v>-58.01374</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-42</v>
+        <v>-654.96</v>
       </c>
     </row>
     <row r="32">
@@ -6061,17 +6061,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.095</v>
+        <v>1.75</v>
       </c>
       <c r="O32" t="n">
-        <v>-209.5</v>
+        <v>-175</v>
       </c>
       <c r="P32" t="n">
         <v>4.6494796</v>
@@ -6083,7 +6083,7 @@
         <v>-464.94796</v>
       </c>
       <c r="S32" t="n">
-        <v>255.44796</v>
+        <v>289.94796</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-209.5</v>
+        <v>-175</v>
       </c>
     </row>
     <row r="33">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>5.3</v>
+        <v>4.275</v>
       </c>
       <c r="O33" t="n">
-        <v>-530</v>
+        <v>-427.5</v>
       </c>
       <c r="P33" t="n">
         <v>4.4694546</v>
@@ -6173,7 +6173,7 @@
         <v>-446.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>-83.05454</v>
+        <v>19.44546</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-530</v>
+        <v>-427.5</v>
       </c>
     </row>
     <row r="34">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>1.8514</v>
+        <v>1.645</v>
       </c>
       <c r="O34" t="n">
-        <v>-185.14</v>
+        <v>-164.5</v>
       </c>
       <c r="P34" t="n">
         <v>2.1094546</v>
@@ -6263,7 +6263,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>25.80546</v>
+        <v>46.44546</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-185.14</v>
+        <v>-164.5</v>
       </c>
     </row>
     <row r="35">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>7.925</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>-792.5</v>
+        <v>-805</v>
       </c>
       <c r="P35" t="n">
         <v>5.9994546</v>
@@ -6353,7 +6353,7 @@
         <v>-599.94546</v>
       </c>
       <c r="S35" t="n">
-        <v>-192.55454</v>
+        <v>-205.05454</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-792.5</v>
+        <v>-805</v>
       </c>
     </row>
     <row r="36">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-1</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1222</v>
+        <v>0.103</v>
       </c>
       <c r="O36" t="n">
-        <v>-12.22</v>
+        <v>-10.3</v>
       </c>
       <c r="P36" t="n">
         <v>0.8794546</v>
@@ -6443,7 +6443,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S36" t="n">
-        <v>75.72546</v>
+        <v>77.64546</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-12.22</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="37">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M37" t="n">
         <v>-1</v>
       </c>
       <c r="N37" t="n">
-        <v>15.3637</v>
+        <v>16.2435</v>
       </c>
       <c r="O37" t="n">
-        <v>-1536.37</v>
+        <v>-1624.35</v>
       </c>
       <c r="P37" t="n">
         <v>3.2794546</v>
@@ -6533,7 +6533,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S37" t="n">
-        <v>-1208.42454</v>
+        <v>-1296.40454</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>-1536.37</v>
+        <v>-1624.35</v>
       </c>
     </row>
     <row r="38">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M38" t="n">
         <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="O38" t="n">
-        <v>-470</v>
+        <v>-380</v>
       </c>
       <c r="P38" t="n">
         <v>3.0294546</v>
@@ -6623,7 +6623,7 @@
         <v>-302.94546</v>
       </c>
       <c r="S38" t="n">
-        <v>-167.05454</v>
+        <v>-77.05454</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>-470</v>
+        <v>-380</v>
       </c>
     </row>
     <row r="39">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M39" t="n">
         <v>-1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="O39" t="n">
-        <v>-40</v>
+        <v>-46</v>
       </c>
       <c r="P39" t="n">
         <v>3.6694546</v>
@@ -6713,7 +6713,7 @@
         <v>-366.94546</v>
       </c>
       <c r="S39" t="n">
-        <v>326.94546</v>
+        <v>320.94546</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>-40</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="40">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M40" t="n">
         <v>-2</v>
       </c>
       <c r="N40" t="n">
-        <v>8.4148</v>
+        <v>7.5836</v>
       </c>
       <c r="O40" t="n">
-        <v>-1682.96</v>
+        <v>-1516.72</v>
       </c>
       <c r="P40" t="n">
         <v>6.3929546</v>
@@ -6803,7 +6803,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S40" t="n">
-        <v>-404.36908</v>
+        <v>-238.12908</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>-1682.96</v>
+        <v>-1516.72</v>
       </c>
     </row>
     <row r="41">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="M41" t="n">
         <v>-2</v>
       </c>
       <c r="N41" t="n">
-        <v>8.84</v>
+        <v>8.115</v>
       </c>
       <c r="O41" t="n">
-        <v>-1768</v>
+        <v>-1623</v>
       </c>
       <c r="P41" t="n">
         <v>7.3496796</v>
@@ -6893,7 +6893,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S41" t="n">
-        <v>-298.06408</v>
+        <v>-153.06408</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>-1768</v>
+        <v>-1623</v>
       </c>
     </row>
   </sheetData>
@@ -6953,17 +6953,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$323,990.51</t>
+          <t>$337,648.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$108,786.87</t>
+          <t>$97,825.65</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$432,777.38</t>
+          <t>$435,473.74</t>
         </is>
       </c>
     </row>
@@ -6975,17 +6975,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$449,981.85</t>
+          <t>$466,019.85</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$96,384.23</t>
+          <t>$85,389.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$546,366.07</t>
+          <t>$551,409.19</t>
         </is>
       </c>
     </row>
@@ -7003,17 +7003,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$773,972.36</t>
+          <t>$803,667.94</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$205,171.10</t>
+          <t>$183,214.99</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$979,143.45</t>
+          <t>$986,882.93</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-04 23:53:49</t>
+          <t>2026-03-06 00:04:03</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2835</v>
+        <v>1.2804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>401.1</v>
+        <v>398.9</v>
       </c>
       <c r="O2" t="n">
-        <v>16044</v>
+        <v>15956</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-664.503607</v>
+        <v>-752.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20592.474</v>
+        <v>20430.0624</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2835</v>
+        <v>1.2804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>10000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5335</v>
+        <v>3.493</v>
       </c>
       <c r="O3" t="n">
-        <v>35335</v>
+        <v>34930</v>
       </c>
       <c r="P3" t="n">
         <v>3.576275343</v>
@@ -687,7 +687,7 @@
         <v>35762.753425</v>
       </c>
       <c r="S3" t="n">
-        <v>-427.753425</v>
+        <v>-832.753425</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>45352.4725</v>
+        <v>44724.372</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2835</v>
+        <v>1.2804</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>250</v>
       </c>
       <c r="N4" t="n">
-        <v>63.67</v>
+        <v>62.09</v>
       </c>
       <c r="O4" t="n">
-        <v>15917.5</v>
+        <v>15522.5</v>
       </c>
       <c r="P4" t="n">
         <v>65.233413332</v>
@@ -767,7 +767,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S4" t="n">
-        <v>-390.853333</v>
+        <v>-785.853333</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>20430.11125</v>
+        <v>19875.009</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14504</v>
+        <v>0.14455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>30.96</v>
+        <v>31.24</v>
       </c>
       <c r="O5" t="n">
-        <v>92880</v>
+        <v>93720</v>
       </c>
       <c r="P5" t="n">
         <v>31.36596519</v>
@@ -847,7 +847,7 @@
         <v>94097.89556999999</v>
       </c>
       <c r="S5" t="n">
-        <v>-1217.89557</v>
+        <v>-377.89557</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13471.3152</v>
+        <v>13547.226</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1635</v>
+        <v>1.1609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>2000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.147</v>
+        <v>4.1275</v>
       </c>
       <c r="O6" t="n">
-        <v>8294</v>
+        <v>8255</v>
       </c>
       <c r="P6" t="n">
         <v>4.66233</v>
@@ -927,7 +927,7 @@
         <v>9324.66</v>
       </c>
       <c r="S6" t="n">
-        <v>-1030.66</v>
+        <v>-1069.66</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9650.069</v>
+        <v>9583.229499999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78401</v>
+        <v>0.78051</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.809</v>
+        <v>4.846</v>
       </c>
       <c r="O7" t="n">
-        <v>38472</v>
+        <v>38768</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1160.77315</v>
+        <v>1456.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30162.43272</v>
+        <v>30258.81168</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78401</v>
+        <v>0.78051</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>606.3</v>
+        <v>606.7</v>
       </c>
       <c r="O8" t="n">
-        <v>45472.5</v>
+        <v>45502.5</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>1238.401008</v>
+        <v>1268.401008</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>35650.894725</v>
+        <v>35515.156275</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.76</v>
+        <v>7.89</v>
       </c>
       <c r="O9" t="n">
-        <v>7760</v>
+        <v>7890</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-551.237657</v>
+        <v>-421.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7760</v>
+        <v>7890</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>10.07</v>
+        <v>9.81</v>
       </c>
       <c r="O10" t="n">
-        <v>1007</v>
+        <v>981</v>
       </c>
       <c r="P10" t="n">
         <v>9.705</v>
@@ -1247,7 +1247,7 @@
         <v>970.5</v>
       </c>
       <c r="S10" t="n">
-        <v>36.5</v>
+        <v>10.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1007</v>
+        <v>981</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1435.6</v>
+        <v>1433.4</v>
       </c>
       <c r="O11" t="n">
-        <v>14356</v>
+        <v>14334</v>
       </c>
       <c r="P11" t="n">
         <v>1474.045</v>
@@ -1327,7 +1327,7 @@
         <v>14740.45</v>
       </c>
       <c r="S11" t="n">
-        <v>-384.45</v>
+        <v>-406.45</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>14356</v>
+        <v>14334</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>303.13</v>
+        <v>300.88</v>
       </c>
       <c r="O12" t="n">
-        <v>30313</v>
+        <v>30088</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>149.5</v>
+        <v>-75.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30313</v>
+        <v>30088</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>58.72</v>
+        <v>57.79</v>
       </c>
       <c r="O13" t="n">
-        <v>9395.200000000001</v>
+        <v>9246.4</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-181.46</v>
+        <v>-330.26</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9395.200000000001</v>
+        <v>9246.4</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>26.5453</v>
+        <v>26.063</v>
       </c>
       <c r="O14" t="n">
-        <v>10219.94</v>
+        <v>10034.26</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>205.037178</v>
+        <v>19.357178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10219.94</v>
+        <v>10034.26</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>152.37</v>
+        <v>154.79</v>
       </c>
       <c r="O15" t="n">
-        <v>15237</v>
+        <v>15479</v>
       </c>
       <c r="P15" t="n">
         <v>205.3357044</v>
@@ -1647,7 +1647,7 @@
         <v>20533.57044</v>
       </c>
       <c r="S15" t="n">
-        <v>-5296.57044</v>
+        <v>-5054.57044</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>15237</v>
+        <v>15479</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>88.26000000000001</v>
+        <v>95.52</v>
       </c>
       <c r="O16" t="n">
-        <v>1765.2</v>
+        <v>1910.4</v>
       </c>
       <c r="P16" t="n">
         <v>124.315</v>
@@ -1727,7 +1727,7 @@
         <v>2486.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-721.1</v>
+        <v>-575.9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1765.2</v>
+        <v>1910.4</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>400</v>
       </c>
       <c r="N17" t="n">
-        <v>173.76</v>
+        <v>171.56</v>
       </c>
       <c r="O17" t="n">
-        <v>69504</v>
+        <v>68624</v>
       </c>
       <c r="P17" t="n">
         <v>173.855759437</v>
@@ -1807,7 +1807,7 @@
         <v>69542.30377499999</v>
       </c>
       <c r="S17" t="n">
-        <v>-38.303775</v>
+        <v>-918.303775</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>69504</v>
+        <v>68624</v>
       </c>
     </row>
     <row r="18">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.37</v>
+        <v>0.265</v>
       </c>
       <c r="O18" t="n">
-        <v>37</v>
+        <v>26.5</v>
       </c>
       <c r="P18" t="n">
         <v>2.0105125</v>
@@ -1897,7 +1897,7 @@
         <v>201.05125</v>
       </c>
       <c r="S18" t="n">
-        <v>-164.05125</v>
+        <v>-174.55125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>37</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="19">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>6.175</v>
+        <v>7.875</v>
       </c>
       <c r="O19" t="n">
-        <v>617.5</v>
+        <v>787.5</v>
       </c>
       <c r="P19" t="n">
         <v>4.4905125</v>
@@ -1987,7 +1987,7 @@
         <v>449.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>168.44875</v>
+        <v>338.44875</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>617.5</v>
+        <v>787.5</v>
       </c>
     </row>
     <row r="20">
@@ -2055,17 +2055,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>27.5466</v>
+        <v>28.7188</v>
       </c>
       <c r="O20" t="n">
-        <v>5509.32</v>
+        <v>5743.76</v>
       </c>
       <c r="P20" t="n">
         <v>23.4605</v>
@@ -2077,7 +2077,7 @@
         <v>4692.1</v>
       </c>
       <c r="S20" t="n">
-        <v>817.22</v>
+        <v>1051.66</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>5509.32</v>
+        <v>5743.76</v>
       </c>
     </row>
     <row r="21">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>22.12</v>
+        <v>23.615</v>
       </c>
       <c r="O21" t="n">
-        <v>4424</v>
+        <v>4723</v>
       </c>
       <c r="P21" t="n">
         <v>20.1374875</v>
@@ -2167,7 +2167,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S21" t="n">
-        <v>396.5025</v>
+        <v>695.5025000000001</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>4424</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="22">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>-310</v>
+        <v>-360</v>
       </c>
       <c r="P22" t="n">
         <v>1.7494546</v>
@@ -2257,7 +2257,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S22" t="n">
-        <v>-135.05454</v>
+        <v>-185.05454</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-310</v>
+        <v>-360</v>
       </c>
     </row>
     <row r="23">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.73</v>
+        <v>0.485</v>
       </c>
       <c r="O23" t="n">
-        <v>-73</v>
+        <v>-48.5</v>
       </c>
       <c r="P23" t="n">
         <v>3.2494546</v>
@@ -2347,7 +2347,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>251.94546</v>
+        <v>276.44546</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-73</v>
+        <v>-48.5</v>
       </c>
     </row>
     <row r="24">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.925</v>
+        <v>5.175</v>
       </c>
       <c r="O24" t="n">
-        <v>-492.5</v>
+        <v>-517.5</v>
       </c>
       <c r="P24" t="n">
         <v>7.5800876</v>
@@ -2437,7 +2437,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S24" t="n">
-        <v>265.50876</v>
+        <v>240.50876</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-492.5</v>
+        <v>-517.5</v>
       </c>
     </row>
     <row r="25">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.0704</v>
+        <v>0.885</v>
       </c>
       <c r="O25" t="n">
-        <v>-107.04</v>
+        <v>-88.5</v>
       </c>
       <c r="P25" t="n">
         <v>1.8142796</v>
@@ -2527,7 +2527,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S25" t="n">
-        <v>74.38796000000001</v>
+        <v>92.92796</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-107.04</v>
+        <v>-88.5</v>
       </c>
     </row>
     <row r="26">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.255</v>
+        <v>1.44</v>
       </c>
       <c r="O26" t="n">
-        <v>-125.5</v>
+        <v>-144</v>
       </c>
       <c r="P26" t="n">
         <v>1.0242796</v>
@@ -2617,7 +2617,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>-23.07204</v>
+        <v>-41.57204</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-125.5</v>
+        <v>-144</v>
       </c>
     </row>
     <row r="27">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-2</v>
       </c>
       <c r="N27" t="n">
-        <v>6.5496</v>
+        <v>6.975</v>
       </c>
       <c r="O27" t="n">
-        <v>-1309.92</v>
+        <v>-1395</v>
       </c>
       <c r="P27" t="n">
         <v>6.6394751</v>
@@ -2707,7 +2707,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S27" t="n">
-        <v>17.97502</v>
+        <v>-67.10498</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-1309.92</v>
+        <v>-1395</v>
       </c>
     </row>
     <row r="28">
@@ -2775,17 +2775,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>5.175</v>
+        <v>3.975</v>
       </c>
       <c r="O28" t="n">
-        <v>-517.5</v>
+        <v>-397.5</v>
       </c>
       <c r="P28" t="n">
         <v>6.7894876</v>
@@ -2797,7 +2797,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S28" t="n">
-        <v>161.44876</v>
+        <v>281.44876</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-517.5</v>
+        <v>-397.5</v>
       </c>
     </row>
     <row r="29">
@@ -2865,17 +2865,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.645</v>
+        <v>1.24</v>
       </c>
       <c r="O29" t="n">
-        <v>-164.5</v>
+        <v>-124</v>
       </c>
       <c r="P29" t="n">
         <v>2.1194546</v>
@@ -2887,7 +2887,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>47.44546</v>
+        <v>87.94546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-164.5</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="30">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>8.050000000000001</v>
+        <v>10.175</v>
       </c>
       <c r="O30" t="n">
-        <v>-805</v>
+        <v>-1017.5</v>
       </c>
       <c r="P30" t="n">
         <v>5.7894546</v>
@@ -2977,7 +2977,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>-226.05454</v>
+        <v>-438.55454</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-805</v>
+        <v>-1017.5</v>
       </c>
     </row>
     <row r="31">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="O31" t="n">
-        <v>-130</v>
+        <v>-126</v>
       </c>
       <c r="P31" t="n">
         <v>0.9454876</v>
@@ -3067,7 +3067,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S31" t="n">
-        <v>59.09752</v>
+        <v>63.09752</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-130</v>
+        <v>-126</v>
       </c>
     </row>
     <row r="32">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>6.3216</v>
+        <v>6.85</v>
       </c>
       <c r="O32" t="n">
-        <v>-632.16</v>
+        <v>-685</v>
       </c>
       <c r="P32" t="n">
         <v>4.5694876</v>
@@ -3157,7 +3157,7 @@
         <v>-456.94876</v>
       </c>
       <c r="S32" t="n">
-        <v>-175.21124</v>
+        <v>-228.05124</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-632.16</v>
+        <v>-685</v>
       </c>
     </row>
     <row r="33">
@@ -3225,17 +3225,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>7.5836</v>
+        <v>7.9639</v>
       </c>
       <c r="O33" t="n">
-        <v>-1516.72</v>
+        <v>-1592.78</v>
       </c>
       <c r="P33" t="n">
         <v>6.3644671</v>
@@ -3247,7 +3247,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S33" t="n">
-        <v>-243.82658</v>
+        <v>-319.88658</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1516.72</v>
+        <v>-1592.78</v>
       </c>
     </row>
     <row r="34">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-2</v>
       </c>
       <c r="N34" t="n">
-        <v>8.115</v>
+        <v>8.715</v>
       </c>
       <c r="O34" t="n">
-        <v>-1623</v>
+        <v>-1743</v>
       </c>
       <c r="P34" t="n">
         <v>7.3548796</v>
@@ -3337,7 +3337,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S34" t="n">
-        <v>-152.02408</v>
+        <v>-272.02408</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1623</v>
+        <v>-1743</v>
       </c>
     </row>
   </sheetData>
@@ -3364,7 +3364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2835</v>
+        <v>1.2804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3521,17 +3521,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>401.1</v>
+        <v>398.9</v>
       </c>
       <c r="O2" t="n">
-        <v>20055</v>
+        <v>19945</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3543,7 +3543,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-927.956235</v>
+        <v>-1037.956235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25740.5925</v>
+        <v>25537.578</v>
       </c>
     </row>
     <row r="3">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2835</v>
+        <v>1.2804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3601,17 +3601,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>12000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5335</v>
+        <v>3.493</v>
       </c>
       <c r="O3" t="n">
-        <v>42402</v>
+        <v>41916</v>
       </c>
       <c r="P3" t="n">
         <v>3.574177863</v>
@@ -3623,7 +3623,7 @@
         <v>42890.13435</v>
       </c>
       <c r="S3" t="n">
-        <v>-488.13435</v>
+        <v>-974.13435</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>54422.967</v>
+        <v>53669.2464</v>
       </c>
     </row>
     <row r="4">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2835</v>
+        <v>1.2804</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3681,17 +3681,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>350</v>
       </c>
       <c r="N4" t="n">
-        <v>63.67</v>
+        <v>62.09</v>
       </c>
       <c r="O4" t="n">
-        <v>22284.5</v>
+        <v>21731.5</v>
       </c>
       <c r="P4" t="n">
         <v>65.60009794299999</v>
@@ -3703,7 +3703,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S4" t="n">
-        <v>-675.53428</v>
+        <v>-1228.53428</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>28602.15575</v>
+        <v>27825.0126</v>
       </c>
     </row>
     <row r="5">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14504</v>
+        <v>0.14455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3761,17 +3761,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>30.96</v>
+        <v>31.24</v>
       </c>
       <c r="O5" t="n">
-        <v>61920</v>
+        <v>62480</v>
       </c>
       <c r="P5" t="n">
         <v>31.696238595</v>
@@ -3783,7 +3783,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S5" t="n">
-        <v>-1472.47719</v>
+        <v>-912.47719</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>8980.8768</v>
+        <v>9031.484</v>
       </c>
     </row>
     <row r="6">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1635</v>
+        <v>1.1609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3841,17 +3841,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>3000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.147</v>
+        <v>4.1275</v>
       </c>
       <c r="O6" t="n">
-        <v>12441</v>
+        <v>12382.5</v>
       </c>
       <c r="P6" t="n">
         <v>4.65841303</v>
@@ -3863,7 +3863,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1534.239091</v>
+        <v>-1592.739091</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>14475.1035</v>
+        <v>14374.84425</v>
       </c>
     </row>
     <row r="7">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1635</v>
+        <v>1.1609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3921,17 +3921,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>1000</v>
       </c>
       <c r="N7" t="n">
-        <v>48.12</v>
+        <v>45.89</v>
       </c>
       <c r="O7" t="n">
-        <v>48120</v>
+        <v>45890</v>
       </c>
       <c r="P7" t="n">
         <v>43.01</v>
@@ -3943,7 +3943,7 @@
         <v>43010</v>
       </c>
       <c r="S7" t="n">
-        <v>5110</v>
+        <v>2880</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>55987.62</v>
+        <v>53273.701</v>
       </c>
     </row>
     <row r="8">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78401</v>
+        <v>0.78051</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4001,17 +4001,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.809</v>
+        <v>4.846</v>
       </c>
       <c r="O8" t="n">
-        <v>48090</v>
+        <v>48460</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4023,7 +4023,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>10821.8184</v>
+        <v>11191.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37703.0409</v>
+        <v>37823.5146</v>
       </c>
     </row>
     <row r="9">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78401</v>
+        <v>0.78051</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4081,17 +4081,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>606.3</v>
+        <v>606.7</v>
       </c>
       <c r="O9" t="n">
-        <v>45472.5</v>
+        <v>45502.5</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4103,7 +4103,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>1249.1496</v>
+        <v>1279.1496</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>35650.894725</v>
+        <v>35515.156275</v>
       </c>
     </row>
     <row r="10">
@@ -4161,17 +4161,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.76</v>
+        <v>7.89</v>
       </c>
       <c r="O10" t="n">
-        <v>8536</v>
+        <v>8679</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4183,7 +4183,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-606.847947</v>
+        <v>-463.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8536</v>
+        <v>8679</v>
       </c>
     </row>
     <row r="11">
@@ -4241,17 +4241,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>300</v>
       </c>
       <c r="N11" t="n">
-        <v>10.07</v>
+        <v>9.81</v>
       </c>
       <c r="O11" t="n">
-        <v>3021</v>
+        <v>2943</v>
       </c>
       <c r="P11" t="n">
         <v>11.661666667</v>
@@ -4263,7 +4263,7 @@
         <v>3498.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-477.5</v>
+        <v>-555.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>3021</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="12">
@@ -4321,17 +4321,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>15</v>
       </c>
       <c r="N12" t="n">
-        <v>1435.6</v>
+        <v>1433.4</v>
       </c>
       <c r="O12" t="n">
-        <v>21534</v>
+        <v>21501</v>
       </c>
       <c r="P12" t="n">
         <v>1471.727366667</v>
@@ -4343,7 +4343,7 @@
         <v>22075.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-541.9105</v>
+        <v>-574.9105</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>21534</v>
+        <v>21501</v>
       </c>
     </row>
     <row r="13">
@@ -4401,17 +4401,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>303.13</v>
+        <v>300.88</v>
       </c>
       <c r="O13" t="n">
-        <v>30313</v>
+        <v>30088</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4423,7 +4423,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2874.755</v>
+        <v>-3099.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30313</v>
+        <v>30088</v>
       </c>
     </row>
     <row r="14">
@@ -4481,17 +4481,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>58.72</v>
+        <v>57.79</v>
       </c>
       <c r="O14" t="n">
-        <v>9395.200000000001</v>
+        <v>9246.4</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4503,7 +4503,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-237.24</v>
+        <v>-386.04</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9395.200000000001</v>
+        <v>9246.4</v>
       </c>
     </row>
     <row r="15">
@@ -4561,17 +4561,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>69.15000000000001</v>
+        <v>68.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1164.82</v>
+        <v>1146.29</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4583,7 +4583,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>815.773421</v>
+        <v>797.243421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1164.82</v>
+        <v>1146.29</v>
       </c>
     </row>
     <row r="16">
@@ -4641,17 +4641,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.5453</v>
+        <v>26.063</v>
       </c>
       <c r="O16" t="n">
-        <v>10219.94</v>
+        <v>10034.26</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4663,7 +4663,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>211.034112</v>
+        <v>25.354112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10219.94</v>
+        <v>10034.26</v>
       </c>
     </row>
     <row r="17">
@@ -4721,17 +4721,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>299.39</v>
+        <v>293.55</v>
       </c>
       <c r="O17" t="n">
-        <v>29939</v>
+        <v>29355</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4743,7 +4743,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>137</v>
+        <v>-447</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>29939</v>
+        <v>29355</v>
       </c>
     </row>
     <row r="18">
@@ -4801,17 +4801,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>173.76</v>
+        <v>171.56</v>
       </c>
       <c r="O18" t="n">
-        <v>86880</v>
+        <v>85780</v>
       </c>
       <c r="P18" t="n">
         <v>174.06142722</v>
@@ -4823,7 +4823,7 @@
         <v>87030.71361000001</v>
       </c>
       <c r="S18" t="n">
-        <v>-150.71361</v>
+        <v>-1250.71361</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>86880</v>
+        <v>85780</v>
       </c>
     </row>
     <row r="19">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.37</v>
+        <v>0.265</v>
       </c>
       <c r="O19" t="n">
-        <v>37</v>
+        <v>26.5</v>
       </c>
       <c r="P19" t="n">
         <v>2.1405125</v>
@@ -4913,7 +4913,7 @@
         <v>214.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-177.05125</v>
+        <v>-187.55125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>37</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="20">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>6.175</v>
+        <v>7.875</v>
       </c>
       <c r="O20" t="n">
-        <v>617.5</v>
+        <v>787.5</v>
       </c>
       <c r="P20" t="n">
         <v>4.6805125</v>
@@ -5003,7 +5003,7 @@
         <v>468.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>149.44875</v>
+        <v>319.44875</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>617.5</v>
+        <v>787.5</v>
       </c>
     </row>
     <row r="21">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>14.3469</v>
+        <v>14.8202</v>
       </c>
       <c r="O21" t="n">
-        <v>1434.69</v>
+        <v>1482.02</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5093,7 +5093,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>1182.63875</v>
+        <v>1229.96875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>1434.69</v>
+        <v>1482.02</v>
       </c>
     </row>
     <row r="22">
@@ -5161,17 +5161,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.29</v>
+        <v>0.225</v>
       </c>
       <c r="O22" t="n">
-        <v>29</v>
+        <v>22.5</v>
       </c>
       <c r="P22" t="n">
         <v>2.6805125</v>
@@ -5183,7 +5183,7 @@
         <v>268.05125</v>
       </c>
       <c r="S22" t="n">
-        <v>-239.05125</v>
+        <v>-245.55125</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>29</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="23">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>27.5466</v>
+        <v>28.7188</v>
       </c>
       <c r="O23" t="n">
-        <v>5509.32</v>
+        <v>5743.76</v>
       </c>
       <c r="P23" t="n">
         <v>23.5270125</v>
@@ -5273,7 +5273,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S23" t="n">
-        <v>803.9175</v>
+        <v>1038.3575</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5509.32</v>
+        <v>5743.76</v>
       </c>
     </row>
     <row r="24">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>22.12</v>
+        <v>23.615</v>
       </c>
       <c r="O24" t="n">
-        <v>4424</v>
+        <v>4723</v>
       </c>
       <c r="P24" t="n">
         <v>20.1350875</v>
@@ -5363,7 +5363,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S24" t="n">
-        <v>396.9825</v>
+        <v>695.9825</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>4424</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="25">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O25" t="n">
-        <v>-310</v>
+        <v>-360</v>
       </c>
       <c r="P25" t="n">
         <v>1.7694546</v>
@@ -5453,7 +5453,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>-133.05454</v>
+        <v>-183.05454</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-310</v>
+        <v>-360</v>
       </c>
     </row>
     <row r="26">
@@ -5521,17 +5521,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.73</v>
+        <v>0.485</v>
       </c>
       <c r="O26" t="n">
-        <v>-73</v>
+        <v>-48.5</v>
       </c>
       <c r="P26" t="n">
         <v>3.4194546</v>
@@ -5543,7 +5543,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>268.94546</v>
+        <v>293.44546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-73</v>
+        <v>-48.5</v>
       </c>
     </row>
     <row r="27">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>4.925</v>
+        <v>5.175</v>
       </c>
       <c r="O27" t="n">
-        <v>-492.5</v>
+        <v>-517.5</v>
       </c>
       <c r="P27" t="n">
         <v>4.1794546</v>
@@ -5633,7 +5633,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>-74.55454</v>
+        <v>-99.55454</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-492.5</v>
+        <v>-517.5</v>
       </c>
     </row>
     <row r="28">
@@ -5701,17 +5701,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.625</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>-62.5</v>
+        <v>-39</v>
       </c>
       <c r="P28" t="n">
         <v>2.3694546</v>
@@ -5723,7 +5723,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>174.44546</v>
+        <v>197.94546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-62.5</v>
+        <v>-39</v>
       </c>
     </row>
     <row r="29">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.0704</v>
+        <v>0.885</v>
       </c>
       <c r="O29" t="n">
-        <v>-107.04</v>
+        <v>-88.5</v>
       </c>
       <c r="P29" t="n">
         <v>1.7994546</v>
@@ -5813,7 +5813,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>72.90546000000001</v>
+        <v>91.44546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-107.04</v>
+        <v>-88.5</v>
       </c>
     </row>
     <row r="30">
@@ -5850,24 +5850,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AMZN  260327C00235000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 235 C</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -5876,34 +5876,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.255</v>
+        <v>6.975</v>
       </c>
       <c r="O30" t="n">
-        <v>-125.5</v>
+        <v>-697.5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.0594546</v>
+        <v>5.9694626</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.0594546</v>
+        <v>5.9694626</v>
       </c>
       <c r="R30" t="n">
-        <v>-105.94546</v>
+        <v>-596.9462600000001</v>
       </c>
       <c r="S30" t="n">
-        <v>-19.55454</v>
+        <v>-100.55374</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-125.5</v>
+        <v>-697.5</v>
       </c>
     </row>
     <row r="31">
@@ -5940,24 +5940,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00295000</t>
+          <t>GOOGL 260327C00330000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 295 P</t>
+          <t>GOOGL 27MAR26 330 C</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -5966,34 +5966,34 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>6.5496</v>
+        <v>1.195</v>
       </c>
       <c r="O31" t="n">
-        <v>-654.96</v>
+        <v>-119.5</v>
       </c>
       <c r="P31" t="n">
-        <v>5.9694626</v>
+        <v>4.6494796</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.9694626</v>
+        <v>4.6494796</v>
       </c>
       <c r="R31" t="n">
-        <v>-596.9462600000001</v>
+        <v>-464.94796</v>
       </c>
       <c r="S31" t="n">
-        <v>-58.01374</v>
+        <v>345.44796</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-654.96</v>
+        <v>-119.5</v>
       </c>
     </row>
     <row r="32">
@@ -6035,19 +6035,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GOOGL 260327C00330000</t>
+          <t>JPM   260327C00310000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 330 C</t>
+          <t>JPM 27MAR26 310 C</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -6061,29 +6061,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.75</v>
+        <v>2.555</v>
       </c>
       <c r="O32" t="n">
-        <v>-175</v>
+        <v>-255.5</v>
       </c>
       <c r="P32" t="n">
-        <v>4.6494796</v>
+        <v>4.4694546</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.6494796</v>
+        <v>4.4694546</v>
       </c>
       <c r="R32" t="n">
-        <v>-464.94796</v>
+        <v>-446.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>289.94796</v>
+        <v>191.44546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-175</v>
+        <v>-255.5</v>
       </c>
     </row>
     <row r="33">
@@ -6120,24 +6120,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JPM   260327C00310000</t>
+          <t>MSFT  260327P00360000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>JPM 27MAR26 310 C</t>
+          <t>MSFT 27MAR26 360 P</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -6146,34 +6146,34 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>4.275</v>
+        <v>1.24</v>
       </c>
       <c r="O33" t="n">
-        <v>-427.5</v>
+        <v>-124</v>
       </c>
       <c r="P33" t="n">
-        <v>4.4694546</v>
+        <v>2.1094546</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.4694546</v>
+        <v>2.1094546</v>
       </c>
       <c r="R33" t="n">
-        <v>-446.94546</v>
+        <v>-210.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>19.44546</v>
+        <v>86.94546</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-427.5</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="34">
@@ -6210,24 +6210,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MSFT  260327P00360000</t>
+          <t>MSFT  260327C00415000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 360 P</t>
+          <t>MSFT 27MAR26 415 C</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -6236,34 +6236,34 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>1.645</v>
+        <v>10.175</v>
       </c>
       <c r="O34" t="n">
-        <v>-164.5</v>
+        <v>-1017.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1094546</v>
+        <v>5.9994546</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.1094546</v>
+        <v>5.9994546</v>
       </c>
       <c r="R34" t="n">
-        <v>-210.94546</v>
+        <v>-599.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>46.44546</v>
+        <v>-417.55454</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-164.5</v>
+        <v>-1017.5</v>
       </c>
     </row>
     <row r="35">
@@ -6300,24 +6300,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MSFT  260327C00415000</t>
+          <t>NFLX  260327P00072000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 415 C</t>
+          <t>NFLX 27MAR26 72 P</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>415</v>
+        <v>72</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -6326,34 +6326,34 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>8.050000000000001</v>
+        <v>0.0955</v>
       </c>
       <c r="O35" t="n">
-        <v>-805</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="P35" t="n">
-        <v>5.9994546</v>
+        <v>0.8794546</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.9994546</v>
+        <v>0.8794546</v>
       </c>
       <c r="R35" t="n">
-        <v>-599.94546</v>
+        <v>-87.94546</v>
       </c>
       <c r="S35" t="n">
-        <v>-205.05454</v>
+        <v>78.39546</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-805</v>
+        <v>-9.550000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -6390,24 +6390,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NFLX  260327P00072000</t>
+          <t>NFLX  260327C00083000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 72 P</t>
+          <t>NFLX 27MAR26 83 C</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -6416,34 +6416,34 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-1</v>
       </c>
       <c r="N36" t="n">
-        <v>0.103</v>
+        <v>16.7161</v>
       </c>
       <c r="O36" t="n">
-        <v>-10.3</v>
+        <v>-1671.61</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8794546</v>
+        <v>3.2794546</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8794546</v>
+        <v>3.2794546</v>
       </c>
       <c r="R36" t="n">
-        <v>-87.94546</v>
+        <v>-327.94546</v>
       </c>
       <c r="S36" t="n">
-        <v>77.64546</v>
+        <v>-1343.66454</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-10.3</v>
+        <v>-1671.61</v>
       </c>
     </row>
     <row r="37">
@@ -6480,24 +6480,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NFLX  260327C00083000</t>
+          <t>NVDA  260327P00170000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 83 C</t>
+          <t>NVDA 27MAR26 170 P</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -6506,34 +6506,34 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M37" t="n">
         <v>-1</v>
       </c>
       <c r="N37" t="n">
-        <v>16.2435</v>
+        <v>3.475</v>
       </c>
       <c r="O37" t="n">
-        <v>-1624.35</v>
+        <v>-347.5</v>
       </c>
       <c r="P37" t="n">
-        <v>3.2794546</v>
+        <v>3.0294546</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2794546</v>
+        <v>3.0294546</v>
       </c>
       <c r="R37" t="n">
-        <v>-327.94546</v>
+        <v>-302.94546</v>
       </c>
       <c r="S37" t="n">
-        <v>-1296.40454</v>
+        <v>-44.55454</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>-1624.35</v>
+        <v>-347.5</v>
       </c>
     </row>
     <row r="38">
@@ -6570,24 +6570,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NVDA  260327P00170000</t>
+          <t>NVDA  260327C00215000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NVDA 27MAR26 170 P</t>
+          <t>NVDA 27MAR26 215 C</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -6596,34 +6596,34 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M38" t="n">
         <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.8</v>
+        <v>0.385</v>
       </c>
       <c r="O38" t="n">
-        <v>-380</v>
+        <v>-38.5</v>
       </c>
       <c r="P38" t="n">
-        <v>3.0294546</v>
+        <v>3.6694546</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.0294546</v>
+        <v>3.6694546</v>
       </c>
       <c r="R38" t="n">
-        <v>-302.94546</v>
+        <v>-366.94546</v>
       </c>
       <c r="S38" t="n">
-        <v>-77.05454</v>
+        <v>328.44546</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>-380</v>
+        <v>-38.5</v>
       </c>
     </row>
     <row r="39">
@@ -6660,60 +6660,60 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NVDA  260327C00215000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>NVDA 27MAR26 215 C</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>215</v>
+        <v>425</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N39" t="n">
-        <v>0.46</v>
+        <v>7.9639</v>
       </c>
       <c r="O39" t="n">
-        <v>-46</v>
+        <v>-1592.78</v>
       </c>
       <c r="P39" t="n">
-        <v>3.6694546</v>
+        <v>6.3929546</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6694546</v>
+        <v>6.3929546</v>
       </c>
       <c r="R39" t="n">
-        <v>-366.94546</v>
+        <v>-1278.59092</v>
       </c>
       <c r="S39" t="n">
-        <v>320.94546</v>
+        <v>-314.18908</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>-46</v>
+        <v>-1592.78</v>
       </c>
     </row>
     <row r="40">
@@ -6755,19 +6755,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>SPY   261218P00505000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>SPY 18DEC26 505 P</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>425</v>
+        <v>505</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -6781,29 +6781,29 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M40" t="n">
         <v>-2</v>
       </c>
       <c r="N40" t="n">
-        <v>7.5836</v>
+        <v>8.715</v>
       </c>
       <c r="O40" t="n">
-        <v>-1516.72</v>
+        <v>-1743</v>
       </c>
       <c r="P40" t="n">
-        <v>6.3929546</v>
+        <v>7.3496796</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.3929546</v>
+        <v>7.3496796</v>
       </c>
       <c r="R40" t="n">
-        <v>-1278.59092</v>
+        <v>-1469.93592</v>
       </c>
       <c r="S40" t="n">
-        <v>-238.12908</v>
+        <v>-273.06408</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6816,97 +6816,7 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>-1516.72</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" t="n">
-        <v>505</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N41" t="n">
-        <v>8.115</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-1623</v>
-      </c>
-      <c r="P41" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="R41" t="n">
-        <v>-1469.93592</v>
-      </c>
-      <c r="S41" t="n">
-        <v>-153.06408</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>-1623</v>
+        <v>-1743</v>
       </c>
     </row>
   </sheetData>
@@ -6953,17 +6863,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$337,648.09</t>
+          <t>$335,562.41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$97,825.65</t>
+          <t>$97,673.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$435,473.74</t>
+          <t>$433,236.02</t>
         </is>
       </c>
     </row>
@@ -6975,17 +6885,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$466,019.85</t>
+          <t>$459,938.33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$85,389.34</t>
+          <t>$84,913.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$551,409.19</t>
+          <t>$544,852.31</t>
         </is>
       </c>
     </row>
@@ -7003,17 +6913,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$803,667.94</t>
+          <t>$795,500.73</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$183,214.99</t>
+          <t>$182,587.59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$986,882.93</t>
+          <t>$978,088.32</t>
         </is>
       </c>
     </row>
@@ -7061,14 +6971,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06 00:04:03</t>
+          <t>2026-03-06 23:51:49</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2804</v>
+        <v>1.2887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>398.9</v>
+        <v>397.2</v>
       </c>
       <c r="O2" t="n">
-        <v>15956</v>
+        <v>15888</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-752.503607</v>
+        <v>-820.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20430.0624</v>
+        <v>20474.8656</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2804</v>
+        <v>1.2887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>10000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.493</v>
+        <v>3.465</v>
       </c>
       <c r="O3" t="n">
-        <v>34930</v>
+        <v>34650</v>
       </c>
       <c r="P3" t="n">
         <v>3.576275343</v>
@@ -687,7 +687,7 @@
         <v>35762.753425</v>
       </c>
       <c r="S3" t="n">
-        <v>-832.753425</v>
+        <v>-1112.753425</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>44724.372</v>
+        <v>44653.455</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2804</v>
+        <v>1.2887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>250</v>
       </c>
       <c r="N4" t="n">
-        <v>62.09</v>
+        <v>61.94</v>
       </c>
       <c r="O4" t="n">
-        <v>15522.5</v>
+        <v>15485</v>
       </c>
       <c r="P4" t="n">
         <v>65.233413332</v>
@@ -767,7 +767,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S4" t="n">
-        <v>-785.853333</v>
+        <v>-823.353333</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>19875.009</v>
+        <v>19955.5195</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14455</v>
+        <v>0.14478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.24</v>
+        <v>31.28</v>
       </c>
       <c r="O5" t="n">
-        <v>93720</v>
+        <v>93840</v>
       </c>
       <c r="P5" t="n">
         <v>31.36596519</v>
@@ -847,7 +847,7 @@
         <v>94097.89556999999</v>
       </c>
       <c r="S5" t="n">
-        <v>-377.89557</v>
+        <v>-257.89557</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13547.226</v>
+        <v>13586.1552</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1609</v>
+        <v>1.1617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>2000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1275</v>
+        <v>4.1675</v>
       </c>
       <c r="O6" t="n">
-        <v>8255</v>
+        <v>8335</v>
       </c>
       <c r="P6" t="n">
         <v>4.66233</v>
@@ -927,7 +927,7 @@
         <v>9324.66</v>
       </c>
       <c r="S6" t="n">
-        <v>-1069.66</v>
+        <v>-989.66</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9583.229499999999</v>
+        <v>9682.7695</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78051</v>
+        <v>0.78171</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.846</v>
+        <v>4.852</v>
       </c>
       <c r="O7" t="n">
-        <v>38768</v>
+        <v>38816</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1456.77315</v>
+        <v>1504.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30258.81168</v>
+        <v>30342.85536</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78051</v>
+        <v>0.78171</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>606.7</v>
+        <v>600.1900000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>45502.5</v>
+        <v>45014.25</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>1268.401008</v>
+        <v>780.151008</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>35515.156275</v>
+        <v>35188.0893675</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.89</v>
+        <v>7.91</v>
       </c>
       <c r="O9" t="n">
-        <v>7890</v>
+        <v>7910</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-421.237657</v>
+        <v>-401.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7890</v>
+        <v>7910</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>9.81</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>981</v>
+        <v>939</v>
       </c>
       <c r="P10" t="n">
         <v>9.705</v>
@@ -1247,7 +1247,7 @@
         <v>970.5</v>
       </c>
       <c r="S10" t="n">
-        <v>10.5</v>
+        <v>-31.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>981</v>
+        <v>939</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1433.4</v>
+        <v>1423.2</v>
       </c>
       <c r="O11" t="n">
-        <v>14334</v>
+        <v>14232</v>
       </c>
       <c r="P11" t="n">
         <v>1474.045</v>
@@ -1327,7 +1327,7 @@
         <v>14740.45</v>
       </c>
       <c r="S11" t="n">
-        <v>-406.45</v>
+        <v>-508.45</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>14334</v>
+        <v>14232</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>300.88</v>
+        <v>298.52</v>
       </c>
       <c r="O12" t="n">
-        <v>30088</v>
+        <v>29852</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-75.5</v>
+        <v>-311.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30088</v>
+        <v>29852</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>57.79</v>
+        <v>57.06</v>
       </c>
       <c r="O13" t="n">
-        <v>9246.4</v>
+        <v>9129.6</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-330.26</v>
+        <v>-447.06</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9246.4</v>
+        <v>9129.6</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>26.063</v>
+        <v>25.834</v>
       </c>
       <c r="O14" t="n">
-        <v>10034.26</v>
+        <v>9946.09</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>19.357178</v>
+        <v>-68.812822</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10034.26</v>
+        <v>9946.09</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>154.79</v>
+        <v>152.96</v>
       </c>
       <c r="O15" t="n">
-        <v>15479</v>
+        <v>15296</v>
       </c>
       <c r="P15" t="n">
         <v>205.3357044</v>
@@ -1647,7 +1647,7 @@
         <v>20533.57044</v>
       </c>
       <c r="S15" t="n">
-        <v>-5054.57044</v>
+        <v>-5237.57044</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>15479</v>
+        <v>15296</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>95.52</v>
+        <v>91.98</v>
       </c>
       <c r="O16" t="n">
-        <v>1910.4</v>
+        <v>1839.6</v>
       </c>
       <c r="P16" t="n">
         <v>124.315</v>
@@ -1727,7 +1727,7 @@
         <v>2486.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-575.9</v>
+        <v>-646.7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1910.4</v>
+        <v>1839.6</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>400</v>
       </c>
       <c r="N17" t="n">
-        <v>171.56</v>
+        <v>170.36</v>
       </c>
       <c r="O17" t="n">
-        <v>68624</v>
+        <v>68144</v>
       </c>
       <c r="P17" t="n">
         <v>173.855759437</v>
@@ -1807,7 +1807,7 @@
         <v>69542.30377499999</v>
       </c>
       <c r="S17" t="n">
-        <v>-918.303775</v>
+        <v>-1398.303775</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>68624</v>
+        <v>68144</v>
       </c>
     </row>
     <row r="18">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.265</v>
+        <v>0.215</v>
       </c>
       <c r="O18" t="n">
-        <v>26.5</v>
+        <v>21.5</v>
       </c>
       <c r="P18" t="n">
         <v>2.0105125</v>
@@ -1897,7 +1897,7 @@
         <v>201.05125</v>
       </c>
       <c r="S18" t="n">
-        <v>-174.55125</v>
+        <v>-179.55125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>26.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="19">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>7.875</v>
+        <v>7.45</v>
       </c>
       <c r="O19" t="n">
-        <v>787.5</v>
+        <v>745</v>
       </c>
       <c r="P19" t="n">
         <v>4.4905125</v>
@@ -1987,7 +1987,7 @@
         <v>449.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>338.44875</v>
+        <v>295.94875</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>787.5</v>
+        <v>745</v>
       </c>
     </row>
     <row r="20">
@@ -2055,17 +2055,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>28.7188</v>
+        <v>33.0144</v>
       </c>
       <c r="O20" t="n">
-        <v>5743.76</v>
+        <v>6602.88</v>
       </c>
       <c r="P20" t="n">
         <v>23.4605</v>
@@ -2077,7 +2077,7 @@
         <v>4692.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1051.66</v>
+        <v>1910.78</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>5743.76</v>
+        <v>6602.88</v>
       </c>
     </row>
     <row r="21">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>23.615</v>
+        <v>27.86</v>
       </c>
       <c r="O21" t="n">
-        <v>4723</v>
+        <v>5572</v>
       </c>
       <c r="P21" t="n">
         <v>20.1374875</v>
@@ -2167,7 +2167,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S21" t="n">
-        <v>695.5025000000001</v>
+        <v>1544.5025</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>4723</v>
+        <v>5572</v>
       </c>
     </row>
     <row r="22">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="O22" t="n">
-        <v>-360</v>
+        <v>-490</v>
       </c>
       <c r="P22" t="n">
         <v>1.7494546</v>
@@ -2257,7 +2257,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S22" t="n">
-        <v>-185.05454</v>
+        <v>-315.05454</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-360</v>
+        <v>-490</v>
       </c>
     </row>
     <row r="23">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.485</v>
+        <v>0.37</v>
       </c>
       <c r="O23" t="n">
-        <v>-48.5</v>
+        <v>-37</v>
       </c>
       <c r="P23" t="n">
         <v>3.2494546</v>
@@ -2347,7 +2347,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>276.44546</v>
+        <v>287.94546</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-48.5</v>
+        <v>-37</v>
       </c>
     </row>
     <row r="24">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>5.175</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-517.5</v>
+        <v>-817.5</v>
       </c>
       <c r="P24" t="n">
         <v>7.5800876</v>
@@ -2437,7 +2437,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S24" t="n">
-        <v>240.50876</v>
+        <v>-59.49124</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-517.5</v>
+        <v>-817.5</v>
       </c>
     </row>
     <row r="25">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.885</v>
+        <v>2.215</v>
       </c>
       <c r="O25" t="n">
-        <v>-88.5</v>
+        <v>-221.5</v>
       </c>
       <c r="P25" t="n">
         <v>1.8142796</v>
@@ -2527,7 +2527,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S25" t="n">
-        <v>92.92796</v>
+        <v>-40.07204</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-88.5</v>
+        <v>-221.5</v>
       </c>
     </row>
     <row r="26">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.44</v>
+        <v>0.925</v>
       </c>
       <c r="O26" t="n">
-        <v>-144</v>
+        <v>-92.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.0242796</v>
@@ -2617,7 +2617,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>-41.57204</v>
+        <v>9.927960000000001</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-144</v>
+        <v>-92.5</v>
       </c>
     </row>
     <row r="27">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-2</v>
       </c>
       <c r="N27" t="n">
-        <v>6.975</v>
+        <v>8.545</v>
       </c>
       <c r="O27" t="n">
-        <v>-1395</v>
+        <v>-1709</v>
       </c>
       <c r="P27" t="n">
         <v>6.6394751</v>
@@ -2707,7 +2707,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S27" t="n">
-        <v>-67.10498</v>
+        <v>-381.10498</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-1395</v>
+        <v>-1709</v>
       </c>
     </row>
     <row r="28">
@@ -2775,17 +2775,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.975</v>
+        <v>3.5417</v>
       </c>
       <c r="O28" t="n">
-        <v>-397.5</v>
+        <v>-354.17</v>
       </c>
       <c r="P28" t="n">
         <v>6.7894876</v>
@@ -2797,7 +2797,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S28" t="n">
-        <v>281.44876</v>
+        <v>324.77876</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-397.5</v>
+        <v>-354.17</v>
       </c>
     </row>
     <row r="29">
@@ -2865,17 +2865,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
-        <v>-124</v>
+        <v>-185</v>
       </c>
       <c r="P29" t="n">
         <v>2.1194546</v>
@@ -2887,7 +2887,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>87.94546</v>
+        <v>26.94546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-124</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="30">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>10.175</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>-1017.5</v>
+        <v>-970</v>
       </c>
       <c r="P30" t="n">
         <v>5.7894546</v>
@@ -2977,7 +2977,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>-438.55454</v>
+        <v>-391.05454</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-1017.5</v>
+        <v>-970</v>
       </c>
     </row>
     <row r="31">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.63</v>
+        <v>0.675</v>
       </c>
       <c r="O31" t="n">
-        <v>-126</v>
+        <v>-135</v>
       </c>
       <c r="P31" t="n">
         <v>0.9454876</v>
@@ -3067,7 +3067,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S31" t="n">
-        <v>63.09752</v>
+        <v>54.09752</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-126</v>
+        <v>-135</v>
       </c>
     </row>
     <row r="32">
@@ -3104,60 +3104,60 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ORCL  260313C00160000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ORCL 13MAR26 160 C</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>160</v>
+        <v>425</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>6.85</v>
+        <v>9.49</v>
       </c>
       <c r="O32" t="n">
-        <v>-685</v>
+        <v>-1898</v>
       </c>
       <c r="P32" t="n">
-        <v>4.5694876</v>
+        <v>6.3644671</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.5694876</v>
+        <v>6.3644671</v>
       </c>
       <c r="R32" t="n">
-        <v>-456.94876</v>
+        <v>-1272.89342</v>
       </c>
       <c r="S32" t="n">
-        <v>-228.05124</v>
+        <v>-625.10658</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-685</v>
+        <v>-1898</v>
       </c>
     </row>
     <row r="33">
@@ -3199,19 +3199,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>SPY   261218P00505000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>SPY 18DEC26 505 P</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>425</v>
+        <v>505</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3225,29 +3225,29 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>7.9639</v>
+        <v>10.643</v>
       </c>
       <c r="O33" t="n">
-        <v>-1592.78</v>
+        <v>-2128.6</v>
       </c>
       <c r="P33" t="n">
-        <v>6.3644671</v>
+        <v>7.3548796</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.3644671</v>
+        <v>7.3548796</v>
       </c>
       <c r="R33" t="n">
-        <v>-1272.89342</v>
+        <v>-1470.97592</v>
       </c>
       <c r="S33" t="n">
-        <v>-319.88658</v>
+        <v>-657.62408</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3260,97 +3260,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1592.78</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" t="n">
-        <v>505</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>8.715</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-1743</v>
-      </c>
-      <c r="P34" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="R34" t="n">
-        <v>-1470.97592</v>
-      </c>
-      <c r="S34" t="n">
-        <v>-272.02408</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>-1743</v>
+        <v>-2128.6</v>
       </c>
     </row>
   </sheetData>
@@ -3364,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3491,7 +3401,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2804</v>
+        <v>1.2887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3521,17 +3431,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>398.9</v>
+        <v>397.2</v>
       </c>
       <c r="O2" t="n">
-        <v>19945</v>
+        <v>19860</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3543,7 +3453,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-1037.956235</v>
+        <v>-1122.956235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3556,7 +3466,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25537.578</v>
+        <v>25593.582</v>
       </c>
     </row>
     <row r="3">
@@ -3571,7 +3481,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2804</v>
+        <v>1.2887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3601,17 +3511,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>12000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.493</v>
+        <v>3.465</v>
       </c>
       <c r="O3" t="n">
-        <v>41916</v>
+        <v>41580</v>
       </c>
       <c r="P3" t="n">
         <v>3.574177863</v>
@@ -3623,7 +3533,7 @@
         <v>42890.13435</v>
       </c>
       <c r="S3" t="n">
-        <v>-974.13435</v>
+        <v>-1310.13435</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3636,7 +3546,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>53669.2464</v>
+        <v>53584.146</v>
       </c>
     </row>
     <row r="4">
@@ -3651,7 +3561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2804</v>
+        <v>1.2887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3681,17 +3591,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>350</v>
       </c>
       <c r="N4" t="n">
-        <v>62.09</v>
+        <v>61.94</v>
       </c>
       <c r="O4" t="n">
-        <v>21731.5</v>
+        <v>21679</v>
       </c>
       <c r="P4" t="n">
         <v>65.60009794299999</v>
@@ -3703,7 +3613,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S4" t="n">
-        <v>-1228.53428</v>
+        <v>-1281.03428</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3716,7 +3626,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>27825.0126</v>
+        <v>27937.7273</v>
       </c>
     </row>
     <row r="5">
@@ -3731,7 +3641,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14455</v>
+        <v>0.14478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3761,17 +3671,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.24</v>
+        <v>31.28</v>
       </c>
       <c r="O5" t="n">
-        <v>62480</v>
+        <v>62560</v>
       </c>
       <c r="P5" t="n">
         <v>31.696238595</v>
@@ -3783,7 +3693,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S5" t="n">
-        <v>-912.47719</v>
+        <v>-832.47719</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3796,7 +3706,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9031.484</v>
+        <v>9057.436799999999</v>
       </c>
     </row>
     <row r="6">
@@ -3811,7 +3721,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1609</v>
+        <v>1.1617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3841,17 +3751,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>3000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1275</v>
+        <v>4.1675</v>
       </c>
       <c r="O6" t="n">
-        <v>12382.5</v>
+        <v>12502.5</v>
       </c>
       <c r="P6" t="n">
         <v>4.65841303</v>
@@ -3863,7 +3773,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1592.739091</v>
+        <v>-1472.739091</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3876,7 +3786,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>14374.84425</v>
+        <v>14524.15425</v>
       </c>
     </row>
     <row r="7">
@@ -3891,7 +3801,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1609</v>
+        <v>1.1617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3921,17 +3831,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>1000</v>
       </c>
       <c r="N7" t="n">
-        <v>45.89</v>
+        <v>46.17</v>
       </c>
       <c r="O7" t="n">
-        <v>45890</v>
+        <v>46170</v>
       </c>
       <c r="P7" t="n">
         <v>43.01</v>
@@ -3943,7 +3853,7 @@
         <v>43010</v>
       </c>
       <c r="S7" t="n">
-        <v>2880</v>
+        <v>3160</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3956,7 +3866,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>53273.701</v>
+        <v>53635.689</v>
       </c>
     </row>
     <row r="8">
@@ -3971,7 +3881,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78051</v>
+        <v>0.78171</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4001,17 +3911,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.846</v>
+        <v>4.852</v>
       </c>
       <c r="O8" t="n">
-        <v>48460</v>
+        <v>48520</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4023,7 +3933,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11191.8184</v>
+        <v>11251.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4036,7 +3946,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37823.5146</v>
+        <v>37928.5692</v>
       </c>
     </row>
     <row r="9">
@@ -4051,7 +3961,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78051</v>
+        <v>0.78171</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4081,17 +3991,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>606.7</v>
+        <v>600.1900000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>45502.5</v>
+        <v>45014.25</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4103,7 +4013,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>1279.1496</v>
+        <v>790.8996</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4116,7 +4026,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>35515.156275</v>
+        <v>35188.0893675</v>
       </c>
     </row>
     <row r="10">
@@ -4161,17 +4071,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.89</v>
+        <v>7.91</v>
       </c>
       <c r="O10" t="n">
-        <v>8679</v>
+        <v>8701</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4183,7 +4093,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-463.847947</v>
+        <v>-441.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4196,7 +4106,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8679</v>
+        <v>8701</v>
       </c>
     </row>
     <row r="11">
@@ -4241,17 +4151,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>300</v>
       </c>
       <c r="N11" t="n">
-        <v>9.81</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>2943</v>
+        <v>2817</v>
       </c>
       <c r="P11" t="n">
         <v>11.661666667</v>
@@ -4263,7 +4173,7 @@
         <v>3498.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-555.5</v>
+        <v>-681.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4276,7 +4186,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2943</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="12">
@@ -4321,17 +4231,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>15</v>
       </c>
       <c r="N12" t="n">
-        <v>1433.4</v>
+        <v>1423.2</v>
       </c>
       <c r="O12" t="n">
-        <v>21501</v>
+        <v>21348</v>
       </c>
       <c r="P12" t="n">
         <v>1471.727366667</v>
@@ -4343,7 +4253,7 @@
         <v>22075.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-574.9105</v>
+        <v>-727.9105</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4356,7 +4266,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>21501</v>
+        <v>21348</v>
       </c>
     </row>
     <row r="13">
@@ -4401,17 +4311,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>300.88</v>
+        <v>298.52</v>
       </c>
       <c r="O13" t="n">
-        <v>30088</v>
+        <v>29852</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4423,7 +4333,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-3099.755</v>
+        <v>-3335.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4436,7 +4346,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30088</v>
+        <v>29852</v>
       </c>
     </row>
     <row r="14">
@@ -4481,17 +4391,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>57.79</v>
+        <v>57.06</v>
       </c>
       <c r="O14" t="n">
-        <v>9246.4</v>
+        <v>9129.6</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4503,7 +4413,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-386.04</v>
+        <v>-502.84</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4516,7 +4426,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9246.4</v>
+        <v>9129.6</v>
       </c>
     </row>
     <row r="15">
@@ -4561,17 +4471,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>68.05</v>
+        <v>66.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1146.29</v>
+        <v>1123.55</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4583,7 +4493,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>797.243421</v>
+        <v>774.503421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4596,7 +4506,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1146.29</v>
+        <v>1123.55</v>
       </c>
     </row>
     <row r="16">
@@ -4641,17 +4551,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.063</v>
+        <v>25.834</v>
       </c>
       <c r="O16" t="n">
-        <v>10034.26</v>
+        <v>9946.09</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4663,7 +4573,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>25.354112</v>
+        <v>-62.815888</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4676,7 +4586,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10034.26</v>
+        <v>9946.09</v>
       </c>
     </row>
     <row r="17">
@@ -4721,17 +4631,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>293.55</v>
+        <v>289.48</v>
       </c>
       <c r="O17" t="n">
-        <v>29355</v>
+        <v>28948</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4743,7 +4653,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-447</v>
+        <v>-854</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4756,7 +4666,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>29355</v>
+        <v>28948</v>
       </c>
     </row>
     <row r="18">
@@ -4801,17 +4711,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>171.56</v>
+        <v>170.36</v>
       </c>
       <c r="O18" t="n">
-        <v>85780</v>
+        <v>85180</v>
       </c>
       <c r="P18" t="n">
         <v>174.06142722</v>
@@ -4823,7 +4733,7 @@
         <v>87030.71361000001</v>
       </c>
       <c r="S18" t="n">
-        <v>-1250.71361</v>
+        <v>-1850.71361</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4836,7 +4746,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>85780</v>
+        <v>85180</v>
       </c>
     </row>
     <row r="19">
@@ -4891,17 +4801,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.265</v>
+        <v>0.215</v>
       </c>
       <c r="O19" t="n">
-        <v>26.5</v>
+        <v>21.5</v>
       </c>
       <c r="P19" t="n">
         <v>2.1405125</v>
@@ -4913,7 +4823,7 @@
         <v>214.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-187.55125</v>
+        <v>-192.55125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4926,7 +4836,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>26.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="20">
@@ -4981,17 +4891,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>7.875</v>
+        <v>7.45</v>
       </c>
       <c r="O20" t="n">
-        <v>787.5</v>
+        <v>745</v>
       </c>
       <c r="P20" t="n">
         <v>4.6805125</v>
@@ -5003,7 +4913,7 @@
         <v>468.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>319.44875</v>
+        <v>276.94875</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5016,7 +4926,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>787.5</v>
+        <v>745</v>
       </c>
     </row>
     <row r="21">
@@ -5071,17 +4981,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>14.8202</v>
+        <v>14.6481</v>
       </c>
       <c r="O21" t="n">
-        <v>1482.02</v>
+        <v>1464.81</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5093,7 +5003,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>1229.96875</v>
+        <v>1212.75875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5106,7 +5016,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>1482.02</v>
+        <v>1464.81</v>
       </c>
     </row>
     <row r="22">
@@ -5161,17 +5071,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.225</v>
+        <v>0.165</v>
       </c>
       <c r="O22" t="n">
-        <v>22.5</v>
+        <v>16.5</v>
       </c>
       <c r="P22" t="n">
         <v>2.6805125</v>
@@ -5183,7 +5093,7 @@
         <v>268.05125</v>
       </c>
       <c r="S22" t="n">
-        <v>-245.55125</v>
+        <v>-251.55125</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5196,7 +5106,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>22.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="23">
@@ -5251,17 +5161,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>28.7188</v>
+        <v>33.0144</v>
       </c>
       <c r="O23" t="n">
-        <v>5743.76</v>
+        <v>6602.88</v>
       </c>
       <c r="P23" t="n">
         <v>23.5270125</v>
@@ -5273,7 +5183,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S23" t="n">
-        <v>1038.3575</v>
+        <v>1897.4775</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5286,7 +5196,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5743.76</v>
+        <v>6602.88</v>
       </c>
     </row>
     <row r="24">
@@ -5341,17 +5251,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>23.615</v>
+        <v>27.86</v>
       </c>
       <c r="O24" t="n">
-        <v>4723</v>
+        <v>5572</v>
       </c>
       <c r="P24" t="n">
         <v>20.1350875</v>
@@ -5363,7 +5273,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S24" t="n">
-        <v>695.9825</v>
+        <v>1544.9825</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5376,7 +5286,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>4723</v>
+        <v>5572</v>
       </c>
     </row>
     <row r="25">
@@ -5431,17 +5341,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
-        <v>-360</v>
+        <v>-490</v>
       </c>
       <c r="P25" t="n">
         <v>1.7694546</v>
@@ -5453,7 +5363,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>-183.05454</v>
+        <v>-313.05454</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5466,7 +5376,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-360</v>
+        <v>-490</v>
       </c>
     </row>
     <row r="26">
@@ -5521,17 +5431,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.485</v>
+        <v>0.37</v>
       </c>
       <c r="O26" t="n">
-        <v>-48.5</v>
+        <v>-37</v>
       </c>
       <c r="P26" t="n">
         <v>3.4194546</v>
@@ -5543,7 +5453,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>293.44546</v>
+        <v>304.94546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5556,7 +5466,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-48.5</v>
+        <v>-37</v>
       </c>
     </row>
     <row r="27">
@@ -5611,17 +5521,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>5.175</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-517.5</v>
+        <v>-817.5</v>
       </c>
       <c r="P27" t="n">
         <v>4.1794546</v>
@@ -5633,7 +5543,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>-99.55454</v>
+        <v>-399.55454</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5646,7 +5556,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-517.5</v>
+        <v>-817.5</v>
       </c>
     </row>
     <row r="28">
@@ -5701,17 +5611,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="O28" t="n">
-        <v>-39</v>
+        <v>-27</v>
       </c>
       <c r="P28" t="n">
         <v>2.3694546</v>
@@ -5723,7 +5633,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>197.94546</v>
+        <v>209.94546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5736,7 +5646,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-39</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="29">
@@ -5791,17 +5701,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.885</v>
+        <v>2.215</v>
       </c>
       <c r="O29" t="n">
-        <v>-88.5</v>
+        <v>-221.5</v>
       </c>
       <c r="P29" t="n">
         <v>1.7994546</v>
@@ -5813,7 +5723,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>91.44546</v>
+        <v>-41.55454</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5826,7 +5736,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-88.5</v>
+        <v>-221.5</v>
       </c>
     </row>
     <row r="30">
@@ -5881,17 +5791,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>6.975</v>
+        <v>8.545</v>
       </c>
       <c r="O30" t="n">
-        <v>-697.5</v>
+        <v>-854.5</v>
       </c>
       <c r="P30" t="n">
         <v>5.9694626</v>
@@ -5903,7 +5813,7 @@
         <v>-596.9462600000001</v>
       </c>
       <c r="S30" t="n">
-        <v>-100.55374</v>
+        <v>-257.55374</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5916,7 +5826,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-697.5</v>
+        <v>-854.5</v>
       </c>
     </row>
     <row r="31">
@@ -5971,17 +5881,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.195</v>
+        <v>1.055</v>
       </c>
       <c r="O31" t="n">
-        <v>-119.5</v>
+        <v>-105.5</v>
       </c>
       <c r="P31" t="n">
         <v>4.6494796</v>
@@ -5993,7 +5903,7 @@
         <v>-464.94796</v>
       </c>
       <c r="S31" t="n">
-        <v>345.44796</v>
+        <v>359.44796</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6006,7 +5916,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-119.5</v>
+        <v>-105.5</v>
       </c>
     </row>
     <row r="32">
@@ -6061,17 +5971,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.555</v>
+        <v>1.84</v>
       </c>
       <c r="O32" t="n">
-        <v>-255.5</v>
+        <v>-184</v>
       </c>
       <c r="P32" t="n">
         <v>4.4694546</v>
@@ -6083,7 +5993,7 @@
         <v>-446.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>191.44546</v>
+        <v>262.94546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6096,7 +6006,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-255.5</v>
+        <v>-184</v>
       </c>
     </row>
     <row r="33">
@@ -6151,17 +6061,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="O33" t="n">
-        <v>-124</v>
+        <v>-185</v>
       </c>
       <c r="P33" t="n">
         <v>2.1094546</v>
@@ -6173,7 +6083,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>86.94546</v>
+        <v>25.94546</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6186,7 +6096,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-124</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="34">
@@ -6241,17 +6151,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>10.175</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>-1017.5</v>
+        <v>-970</v>
       </c>
       <c r="P34" t="n">
         <v>5.9994546</v>
@@ -6263,7 +6173,7 @@
         <v>-599.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-417.55454</v>
+        <v>-370.05454</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6276,7 +6186,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1017.5</v>
+        <v>-970</v>
       </c>
     </row>
     <row r="35">
@@ -6331,17 +6241,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0955</v>
+        <v>0.101</v>
       </c>
       <c r="O35" t="n">
-        <v>-9.550000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="P35" t="n">
         <v>0.8794546</v>
@@ -6353,7 +6263,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S35" t="n">
-        <v>78.39546</v>
+        <v>77.84546</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6366,7 +6276,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-9.550000000000001</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="36">
@@ -6421,17 +6331,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-1</v>
       </c>
       <c r="N36" t="n">
-        <v>16.7161</v>
+        <v>16.5492</v>
       </c>
       <c r="O36" t="n">
-        <v>-1671.61</v>
+        <v>-1654.92</v>
       </c>
       <c r="P36" t="n">
         <v>3.2794546</v>
@@ -6443,7 +6353,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S36" t="n">
-        <v>-1343.66454</v>
+        <v>-1326.97454</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6456,7 +6366,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-1671.61</v>
+        <v>-1654.92</v>
       </c>
     </row>
     <row r="37">
@@ -6480,24 +6390,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NVDA  260327P00170000</t>
+          <t>NVDA  260327C00215000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NVDA 27MAR26 170 P</t>
+          <t>NVDA 27MAR26 215 C</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -6506,34 +6416,34 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M37" t="n">
         <v>-1</v>
       </c>
       <c r="N37" t="n">
-        <v>3.475</v>
+        <v>0.255</v>
       </c>
       <c r="O37" t="n">
-        <v>-347.5</v>
+        <v>-25.5</v>
       </c>
       <c r="P37" t="n">
-        <v>3.0294546</v>
+        <v>3.6694546</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.0294546</v>
+        <v>3.6694546</v>
       </c>
       <c r="R37" t="n">
-        <v>-302.94546</v>
+        <v>-366.94546</v>
       </c>
       <c r="S37" t="n">
-        <v>-44.55454</v>
+        <v>341.44546</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -6546,7 +6456,7 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>-347.5</v>
+        <v>-25.5</v>
       </c>
     </row>
     <row r="38">
@@ -6570,60 +6480,60 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NVDA  260327C00215000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NVDA 27MAR26 215 C</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>215</v>
+        <v>425</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N38" t="n">
-        <v>0.385</v>
+        <v>9.49</v>
       </c>
       <c r="O38" t="n">
-        <v>-38.5</v>
+        <v>-1898</v>
       </c>
       <c r="P38" t="n">
-        <v>3.6694546</v>
+        <v>6.3929546</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6694546</v>
+        <v>6.3929546</v>
       </c>
       <c r="R38" t="n">
-        <v>-366.94546</v>
+        <v>-1278.59092</v>
       </c>
       <c r="S38" t="n">
-        <v>328.44546</v>
+        <v>-619.40908</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -6636,7 +6546,7 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>-38.5</v>
+        <v>-1898</v>
       </c>
     </row>
     <row r="39">
@@ -6665,19 +6575,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>SPY   261218P00505000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>SPY 18DEC26 505 P</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>425</v>
+        <v>505</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -6691,29 +6601,29 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="M39" t="n">
         <v>-2</v>
       </c>
       <c r="N39" t="n">
-        <v>7.9639</v>
+        <v>10.643</v>
       </c>
       <c r="O39" t="n">
-        <v>-1592.78</v>
+        <v>-2128.6</v>
       </c>
       <c r="P39" t="n">
-        <v>6.3929546</v>
+        <v>7.3496796</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.3929546</v>
+        <v>7.3496796</v>
       </c>
       <c r="R39" t="n">
-        <v>-1278.59092</v>
+        <v>-1469.93592</v>
       </c>
       <c r="S39" t="n">
-        <v>-314.18908</v>
+        <v>-658.66408</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -6726,97 +6636,7 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>-1592.78</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" t="n">
-        <v>505</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N40" t="n">
-        <v>8.715</v>
-      </c>
-      <c r="O40" t="n">
-        <v>-1743</v>
-      </c>
-      <c r="P40" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="R40" t="n">
-        <v>-1469.93592</v>
-      </c>
-      <c r="S40" t="n">
-        <v>-273.06408</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>-1743</v>
+        <v>-2128.6</v>
       </c>
     </row>
   </sheetData>
@@ -6863,17 +6683,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$335,562.41</t>
+          <t>$335,075.11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$97,673.61</t>
+          <t>$96,859.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$433,236.02</t>
+          <t>$431,934.72</t>
         </is>
       </c>
     </row>
@@ -6885,17 +6705,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$459,938.33</t>
+          <t>$459,308.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$84,913.98</t>
+          <t>$84,469.68</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$544,852.31</t>
+          <t>$543,777.89</t>
         </is>
       </c>
     </row>
@@ -6913,17 +6733,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$795,500.73</t>
+          <t>$794,383.31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$182,587.59</t>
+          <t>$181,329.30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$978,088.32</t>
+          <t>$975,712.61</t>
         </is>
       </c>
     </row>
@@ -6971,14 +6791,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06 23:51:49</t>
+          <t>2026-03-07 23:39:50</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -6791,7 +6791,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-07 23:39:50</t>
+          <t>2026-03-08 23:40:30</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2887</v>
+        <v>1.2865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>397.2</v>
+        <v>393.85</v>
       </c>
       <c r="O2" t="n">
-        <v>15888</v>
+        <v>15754</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-820.503607</v>
+        <v>-954.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20474.8656</v>
+        <v>20267.521</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2887</v>
+        <v>1.2865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -649,12 +649,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WORLD</t>
+          <t>XMME</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UBS ETF W UCITS HCHF ACC</t>
+          <t>X MSCI EM 1C</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -665,29 +665,29 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>10000</v>
+        <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>3.465</v>
+        <v>61.75</v>
       </c>
       <c r="O3" t="n">
-        <v>34650</v>
+        <v>15437.5</v>
       </c>
       <c r="P3" t="n">
-        <v>3.576275343</v>
+        <v>65.233413332</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.576275343</v>
+        <v>65.233413332</v>
       </c>
       <c r="R3" t="n">
-        <v>35762.753425</v>
+        <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-1112.753425</v>
+        <v>-870.853333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>44653.455</v>
+        <v>19860.34375</v>
       </c>
     </row>
     <row r="4">
@@ -711,11 +711,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2887</v>
+        <v>0.14517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -729,12 +729,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>XMME</t>
+          <t>82846</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>X MSCI EM 1C</t>
+          <t>ISHARES CORE CSI 300 ETF</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -745,29 +745,29 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="N4" t="n">
-        <v>61.94</v>
+        <v>31.02</v>
       </c>
       <c r="O4" t="n">
-        <v>15485</v>
+        <v>93060</v>
       </c>
       <c r="P4" t="n">
-        <v>65.233413332</v>
+        <v>31.36596519</v>
       </c>
       <c r="Q4" t="n">
-        <v>65.233413332</v>
+        <v>31.36596519</v>
       </c>
       <c r="R4" t="n">
-        <v>16308.353333</v>
+        <v>94097.89556999999</v>
       </c>
       <c r="S4" t="n">
-        <v>-823.353333</v>
+        <v>-1037.89557</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -776,11 +776,11 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>SEHK</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>19955.5195</v>
+        <v>13509.5202</v>
       </c>
     </row>
     <row r="5">
@@ -791,11 +791,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14478</v>
+        <v>1.1636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>82846</t>
+          <t>CBUK</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ISHARES CORE CSI 300 ETF</t>
+          <t>ISHARES CHINA TECH USD ACC</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -825,29 +825,29 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.28</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>93840</v>
+        <v>8400</v>
       </c>
       <c r="P5" t="n">
-        <v>31.36596519</v>
+        <v>4.66233</v>
       </c>
       <c r="Q5" t="n">
-        <v>31.36596519</v>
+        <v>4.66233</v>
       </c>
       <c r="R5" t="n">
-        <v>94097.89556999999</v>
+        <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-257.89557</v>
+        <v>-924.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -856,11 +856,11 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SEHK</t>
+          <t>IBIS2</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13586.1552</v>
+        <v>9774.24</v>
       </c>
     </row>
     <row r="6">
@@ -871,11 +871,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1617</v>
+        <v>0.78456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -889,12 +889,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CBUK</t>
+          <t>ES3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ISHARES CHINA TECH USD ACC</t>
+          <t>STATE STRT SPDR STRAITS TIME</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -905,29 +905,29 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1675</v>
+        <v>4.75</v>
       </c>
       <c r="O6" t="n">
-        <v>8335</v>
+        <v>38000</v>
       </c>
       <c r="P6" t="n">
-        <v>4.66233</v>
+        <v>4.663903356</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.66233</v>
+        <v>4.663903356</v>
       </c>
       <c r="R6" t="n">
-        <v>9324.66</v>
+        <v>37311.22685</v>
       </c>
       <c r="S6" t="n">
-        <v>-989.66</v>
+        <v>688.77315</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -936,11 +936,11 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>IBIS2</t>
+          <t>SGX</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9682.7695</v>
+        <v>29813.28</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78171</v>
+        <v>0.78456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES3</t>
+          <t>GSD</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>STATE STRT SPDR STRAITS TIME</t>
+          <t>SPDR GOLD SHARES</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -985,29 +985,29 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>8000</v>
+        <v>75</v>
       </c>
       <c r="N7" t="n">
-        <v>4.852</v>
+        <v>600.98</v>
       </c>
       <c r="O7" t="n">
-        <v>38816</v>
+        <v>45073.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4.663903356</v>
+        <v>589.78798656</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.663903356</v>
+        <v>589.78798656</v>
       </c>
       <c r="R7" t="n">
-        <v>37311.22685</v>
+        <v>44234.098992</v>
       </c>
       <c r="S7" t="n">
-        <v>1504.77315</v>
+        <v>839.401008</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30342.85536</v>
+        <v>35362.86516</v>
       </c>
     </row>
     <row r="8">
@@ -1031,11 +1031,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78171</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GSD</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SPDR GOLD SHARES</t>
+          <t>GLOBAL X CHINA ROBOTICS</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1065,29 +1065,29 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="N8" t="n">
-        <v>600.1900000000001</v>
+        <v>7.77</v>
       </c>
       <c r="O8" t="n">
-        <v>45014.25</v>
+        <v>7770</v>
       </c>
       <c r="P8" t="n">
-        <v>589.78798656</v>
+        <v>8.311237657</v>
       </c>
       <c r="Q8" t="n">
-        <v>589.78798656</v>
+        <v>8.311237657</v>
       </c>
       <c r="R8" t="n">
-        <v>44234.098992</v>
+        <v>8311.237657</v>
       </c>
       <c r="S8" t="n">
-        <v>780.151008</v>
+        <v>-541.237657</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1096,11 +1096,11 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SGX</t>
+          <t>SEHK</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>35188.0893675</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="9">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GLOBAL X CHINA ROBOTICS</t>
+          <t>AGNICO EAGLE MINES LTD</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1145,29 +1145,29 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="N9" t="n">
-        <v>7.91</v>
+        <v>224.75</v>
       </c>
       <c r="O9" t="n">
-        <v>7910</v>
+        <v>6742.5</v>
       </c>
       <c r="P9" t="n">
-        <v>8.311237657</v>
+        <v>218.103333333</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.311237657</v>
+        <v>218.103333333</v>
       </c>
       <c r="R9" t="n">
-        <v>8311.237657</v>
+        <v>6543.1</v>
       </c>
       <c r="S9" t="n">
-        <v>-401.237657</v>
+        <v>199.4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SEHK</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7910</v>
+        <v>6742.5</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>9.390000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="O10" t="n">
-        <v>939</v>
+        <v>951</v>
       </c>
       <c r="P10" t="n">
         <v>9.705</v>
@@ -1247,7 +1247,7 @@
         <v>970.5</v>
       </c>
       <c r="S10" t="n">
-        <v>-31.5</v>
+        <v>-19.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>939</v>
+        <v>951</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1423.2</v>
+        <v>1416</v>
       </c>
       <c r="O11" t="n">
-        <v>14232</v>
+        <v>14160</v>
       </c>
       <c r="P11" t="n">
         <v>1474.045</v>
@@ -1327,7 +1327,7 @@
         <v>14740.45</v>
       </c>
       <c r="S11" t="n">
-        <v>-508.45</v>
+        <v>-580.45</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>14232</v>
+        <v>14160</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>298.52</v>
+        <v>306.36</v>
       </c>
       <c r="O12" t="n">
-        <v>29852</v>
+        <v>30636</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-311.5</v>
+        <v>472.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>29852</v>
+        <v>30636</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>57.06</v>
+        <v>56.8</v>
       </c>
       <c r="O13" t="n">
-        <v>9129.6</v>
+        <v>9088</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-447.06</v>
+        <v>-488.66</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9129.6</v>
+        <v>9088</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>25.834</v>
+        <v>26.2184</v>
       </c>
       <c r="O14" t="n">
-        <v>9946.09</v>
+        <v>10094.08</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>-68.812822</v>
+        <v>79.177178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9946.09</v>
+        <v>10094.08</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>152.96</v>
+        <v>151.56</v>
       </c>
       <c r="O15" t="n">
-        <v>15296</v>
+        <v>15156</v>
       </c>
       <c r="P15" t="n">
         <v>205.3357044</v>
@@ -1647,7 +1647,7 @@
         <v>20533.57044</v>
       </c>
       <c r="S15" t="n">
-        <v>-5237.57044</v>
+        <v>-5377.57044</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>15296</v>
+        <v>15156</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>91.98</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>1839.6</v>
+        <v>1802</v>
       </c>
       <c r="P16" t="n">
         <v>124.315</v>
@@ -1727,7 +1727,7 @@
         <v>2486.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-646.7</v>
+        <v>-684.3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1839.6</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>400</v>
       </c>
       <c r="N17" t="n">
-        <v>170.36</v>
+        <v>169.82</v>
       </c>
       <c r="O17" t="n">
-        <v>68144</v>
+        <v>67928</v>
       </c>
       <c r="P17" t="n">
         <v>173.855759437</v>
@@ -1807,7 +1807,7 @@
         <v>69542.30377499999</v>
       </c>
       <c r="S17" t="n">
-        <v>-1398.303775</v>
+        <v>-1614.303775</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>68144</v>
+        <v>67928</v>
       </c>
     </row>
     <row r="18">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.215</v>
+        <v>0.165</v>
       </c>
       <c r="O18" t="n">
-        <v>21.5</v>
+        <v>16.5</v>
       </c>
       <c r="P18" t="n">
         <v>2.0105125</v>
@@ -1897,7 +1897,7 @@
         <v>201.05125</v>
       </c>
       <c r="S18" t="n">
-        <v>-179.55125</v>
+        <v>-184.55125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>21.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="19">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>7.45</v>
+        <v>6.275</v>
       </c>
       <c r="O19" t="n">
-        <v>745</v>
+        <v>627.5</v>
       </c>
       <c r="P19" t="n">
         <v>4.4905125</v>
@@ -1987,7 +1987,7 @@
         <v>449.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>295.94875</v>
+        <v>178.44875</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>745</v>
+        <v>627.5</v>
       </c>
     </row>
     <row r="20">
@@ -2055,17 +2055,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>33.0144</v>
+        <v>29.7625</v>
       </c>
       <c r="O20" t="n">
-        <v>6602.88</v>
+        <v>5952.5</v>
       </c>
       <c r="P20" t="n">
         <v>23.4605</v>
@@ -2077,7 +2077,7 @@
         <v>4692.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1910.78</v>
+        <v>1260.4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>6602.88</v>
+        <v>5952.5</v>
       </c>
     </row>
     <row r="21">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>27.86</v>
+        <v>25.075</v>
       </c>
       <c r="O21" t="n">
-        <v>5572</v>
+        <v>5015</v>
       </c>
       <c r="P21" t="n">
         <v>20.1374875</v>
@@ -2167,7 +2167,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S21" t="n">
-        <v>1544.5025</v>
+        <v>987.5025000000001</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>5572</v>
+        <v>5015</v>
       </c>
     </row>
     <row r="22">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-1</v>
       </c>
       <c r="N22" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>-490</v>
+        <v>-325</v>
       </c>
       <c r="P22" t="n">
         <v>1.7494546</v>
@@ -2257,7 +2257,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S22" t="n">
-        <v>-315.05454</v>
+        <v>-150.05454</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-490</v>
+        <v>-325</v>
       </c>
     </row>
     <row r="23">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="O23" t="n">
-        <v>-37</v>
+        <v>-29</v>
       </c>
       <c r="P23" t="n">
         <v>3.2494546</v>
@@ -2347,7 +2347,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>287.94546</v>
+        <v>295.94546</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-37</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="24">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>8.175000000000001</v>
+        <v>3.93</v>
       </c>
       <c r="O24" t="n">
-        <v>-817.5</v>
+        <v>-393</v>
       </c>
       <c r="P24" t="n">
         <v>7.5800876</v>
@@ -2437,7 +2437,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-59.49124</v>
+        <v>365.00876</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-817.5</v>
+        <v>-393</v>
       </c>
     </row>
     <row r="25">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.215</v>
+        <v>1.195</v>
       </c>
       <c r="O25" t="n">
-        <v>-221.5</v>
+        <v>-119.5</v>
       </c>
       <c r="P25" t="n">
         <v>1.8142796</v>
@@ -2527,7 +2527,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S25" t="n">
-        <v>-40.07204</v>
+        <v>61.92796</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-221.5</v>
+        <v>-119.5</v>
       </c>
     </row>
     <row r="26">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.925</v>
+        <v>0.55</v>
       </c>
       <c r="O26" t="n">
-        <v>-92.5</v>
+        <v>-55</v>
       </c>
       <c r="P26" t="n">
         <v>1.0242796</v>
@@ -2617,7 +2617,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>9.927960000000001</v>
+        <v>47.42796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-92.5</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="27">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-2</v>
       </c>
       <c r="N27" t="n">
-        <v>8.545</v>
+        <v>4.625</v>
       </c>
       <c r="O27" t="n">
-        <v>-1709</v>
+        <v>-925</v>
       </c>
       <c r="P27" t="n">
         <v>6.6394751</v>
@@ -2707,7 +2707,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S27" t="n">
-        <v>-381.10498</v>
+        <v>402.89502</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-1709</v>
+        <v>-925</v>
       </c>
     </row>
     <row r="28">
@@ -2775,17 +2775,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5417</v>
+        <v>5.175</v>
       </c>
       <c r="O28" t="n">
-        <v>-354.17</v>
+        <v>-517.5</v>
       </c>
       <c r="P28" t="n">
         <v>6.7894876</v>
@@ -2797,7 +2797,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S28" t="n">
-        <v>324.77876</v>
+        <v>161.44876</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-354.17</v>
+        <v>-517.5</v>
       </c>
     </row>
     <row r="29">
@@ -2865,17 +2865,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.85</v>
+        <v>1.07</v>
       </c>
       <c r="O29" t="n">
-        <v>-185</v>
+        <v>-107</v>
       </c>
       <c r="P29" t="n">
         <v>2.1194546</v>
@@ -2887,7 +2887,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>26.94546</v>
+        <v>104.94546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-185</v>
+        <v>-107</v>
       </c>
     </row>
     <row r="30">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4899</v>
       </c>
       <c r="O30" t="n">
-        <v>-970</v>
+        <v>-848.99</v>
       </c>
       <c r="P30" t="n">
         <v>5.7894546</v>
@@ -2977,7 +2977,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>-391.05454</v>
+        <v>-270.04454</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-970</v>
+        <v>-848.99</v>
       </c>
     </row>
     <row r="31">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.675</v>
+        <v>0.525</v>
       </c>
       <c r="O31" t="n">
-        <v>-135</v>
+        <v>-105</v>
       </c>
       <c r="P31" t="n">
         <v>0.9454876</v>
@@ -3067,7 +3067,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S31" t="n">
-        <v>54.09752</v>
+        <v>84.09752</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-135</v>
+        <v>-105</v>
       </c>
     </row>
     <row r="32">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>9.49</v>
+        <v>8.401300000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>-1898</v>
+        <v>-1680.26</v>
       </c>
       <c r="P32" t="n">
         <v>6.3644671</v>
@@ -3157,7 +3157,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S32" t="n">
-        <v>-625.10658</v>
+        <v>-407.36658</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-1898</v>
+        <v>-1680.26</v>
       </c>
     </row>
     <row r="33">
@@ -3225,17 +3225,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>10.643</v>
+        <v>9.270200000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>-2128.6</v>
+        <v>-1854.04</v>
       </c>
       <c r="P33" t="n">
         <v>7.3548796</v>
@@ -3247,7 +3247,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S33" t="n">
-        <v>-657.62408</v>
+        <v>-383.06408</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-2128.6</v>
+        <v>-1854.04</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2887</v>
+        <v>1.2865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3431,17 +3431,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>397.2</v>
+        <v>393.85</v>
       </c>
       <c r="O2" t="n">
-        <v>19860</v>
+        <v>19692.5</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3453,7 +3453,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-1122.956235</v>
+        <v>-1290.456235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25593.582</v>
+        <v>25334.40125</v>
       </c>
     </row>
     <row r="3">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2887</v>
+        <v>1.2865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3511,29 +3511,29 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.465</v>
+        <v>3.447</v>
       </c>
       <c r="O3" t="n">
-        <v>41580</v>
+        <v>17235</v>
       </c>
       <c r="P3" t="n">
-        <v>3.574177863</v>
+        <v>3.57250536</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.574177863</v>
+        <v>3.57250536</v>
       </c>
       <c r="R3" t="n">
-        <v>42890.13435</v>
+        <v>17862.5268</v>
       </c>
       <c r="S3" t="n">
-        <v>-1310.13435</v>
+        <v>-627.5268</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>53584.146</v>
+        <v>22172.8275</v>
       </c>
     </row>
     <row r="4">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2887</v>
+        <v>1.2865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>350</v>
       </c>
       <c r="N4" t="n">
-        <v>61.94</v>
+        <v>61.75</v>
       </c>
       <c r="O4" t="n">
-        <v>21679</v>
+        <v>21612.5</v>
       </c>
       <c r="P4" t="n">
         <v>65.60009794299999</v>
@@ -3613,7 +3613,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S4" t="n">
-        <v>-1281.03428</v>
+        <v>-1347.53428</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>27937.7273</v>
+        <v>27804.48125</v>
       </c>
     </row>
     <row r="5">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14478</v>
+        <v>0.14517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3671,17 +3671,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.28</v>
+        <v>31.02</v>
       </c>
       <c r="O5" t="n">
-        <v>62560</v>
+        <v>62040</v>
       </c>
       <c r="P5" t="n">
         <v>31.696238595</v>
@@ -3693,7 +3693,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S5" t="n">
-        <v>-832.47719</v>
+        <v>-1352.47719</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9057.436799999999</v>
+        <v>9006.346799999999</v>
       </c>
     </row>
     <row r="6">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1617</v>
+        <v>1.1636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3751,17 +3751,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>3000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1675</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>12502.5</v>
+        <v>12600</v>
       </c>
       <c r="P6" t="n">
         <v>4.65841303</v>
@@ -3773,7 +3773,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1472.739091</v>
+        <v>-1375.239091</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>14524.15425</v>
+        <v>14661.36</v>
       </c>
     </row>
     <row r="7">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1617</v>
+        <v>1.1636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,17 +3831,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>1000</v>
       </c>
       <c r="N7" t="n">
-        <v>46.17</v>
+        <v>45.51</v>
       </c>
       <c r="O7" t="n">
-        <v>46170</v>
+        <v>45510</v>
       </c>
       <c r="P7" t="n">
         <v>43.01</v>
@@ -3853,7 +3853,7 @@
         <v>43010</v>
       </c>
       <c r="S7" t="n">
-        <v>3160</v>
+        <v>2500</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>53635.689</v>
+        <v>52955.436</v>
       </c>
     </row>
     <row r="8">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78171</v>
+        <v>0.78456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3911,17 +3911,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.852</v>
+        <v>4.75</v>
       </c>
       <c r="O8" t="n">
-        <v>48520</v>
+        <v>47500</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -3933,7 +3933,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11251.8184</v>
+        <v>10231.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37928.5692</v>
+        <v>37266.6</v>
       </c>
     </row>
     <row r="9">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78171</v>
+        <v>0.78456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3991,17 +3991,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>600.1900000000001</v>
+        <v>600.98</v>
       </c>
       <c r="O9" t="n">
-        <v>45014.25</v>
+        <v>45073.5</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4013,7 +4013,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>790.8996</v>
+        <v>850.1496</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>35188.0893675</v>
+        <v>35362.86516</v>
       </c>
     </row>
     <row r="10">
@@ -4071,17 +4071,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.91</v>
+        <v>7.77</v>
       </c>
       <c r="O10" t="n">
-        <v>8701</v>
+        <v>8547</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4093,7 +4093,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-441.847947</v>
+        <v>-595.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8701</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="11">
@@ -4130,17 +4130,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BITO</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PROSHARES BITCOIN ETF-USD</t>
+          <t>AGNICO EAGLE MINES LTD</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -4151,29 +4151,29 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>9.390000000000001</v>
+        <v>224.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2817</v>
+        <v>6742.5</v>
       </c>
       <c r="P11" t="n">
-        <v>11.661666667</v>
+        <v>217.973333333</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.661666667</v>
+        <v>217.973333333</v>
       </c>
       <c r="R11" t="n">
-        <v>3498.5</v>
+        <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-681.5</v>
+        <v>203.3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4182,11 +4182,11 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2817</v>
+        <v>6742.5</v>
       </c>
     </row>
     <row r="12">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CSNDX</t>
+          <t>BITO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ISHARES NASDAQ 100 USD ACC</t>
+          <t>PROSHARES BITCOIN ETF-USD</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -4231,29 +4231,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>1423.2</v>
+        <v>9.51</v>
       </c>
       <c r="O12" t="n">
-        <v>21348</v>
+        <v>2853</v>
       </c>
       <c r="P12" t="n">
-        <v>1471.727366667</v>
+        <v>11.661666667</v>
       </c>
       <c r="Q12" t="n">
-        <v>1471.727366667</v>
+        <v>11.661666667</v>
       </c>
       <c r="R12" t="n">
-        <v>22075.9105</v>
+        <v>3498.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-727.9105</v>
+        <v>-645.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4262,11 +4262,11 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>21348</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="13">
@@ -4290,17 +4290,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CSNDX</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ALPHABET INC-CL A</t>
+          <t>ISHARES NASDAQ 100 USD ACC</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -4311,29 +4311,29 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="N13" t="n">
-        <v>298.52</v>
+        <v>1416</v>
       </c>
       <c r="O13" t="n">
-        <v>29852</v>
+        <v>21240</v>
       </c>
       <c r="P13" t="n">
-        <v>331.87755</v>
+        <v>1471.727366667</v>
       </c>
       <c r="Q13" t="n">
-        <v>331.87755</v>
+        <v>1471.727366667</v>
       </c>
       <c r="R13" t="n">
-        <v>33187.755</v>
+        <v>22075.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-3335.755</v>
+        <v>-835.9105</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4342,11 +4342,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>EBS</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>29852</v>
+        <v>21240</v>
       </c>
     </row>
     <row r="14">
@@ -4370,17 +4370,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GRDU</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FT NSDQ CLN EDG SMRT GRID</t>
+          <t>ALPHABET INC-CL A</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -4391,29 +4391,29 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>57.06</v>
+        <v>306.36</v>
       </c>
       <c r="O14" t="n">
-        <v>9129.6</v>
+        <v>30636</v>
       </c>
       <c r="P14" t="n">
-        <v>60.20275</v>
+        <v>331.87755</v>
       </c>
       <c r="Q14" t="n">
-        <v>60.20275</v>
+        <v>331.87755</v>
       </c>
       <c r="R14" t="n">
-        <v>9632.440000000001</v>
+        <v>33187.755</v>
       </c>
       <c r="S14" t="n">
-        <v>-502.84</v>
+        <v>-2551.755</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4422,11 +4422,11 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9129.6</v>
+        <v>30636</v>
       </c>
     </row>
     <row r="15">
@@ -4450,17 +4450,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>GRDU</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>INTERACTIVE BROKERS GRO-CL A</t>
+          <t>FT NSDQ CLN EDG SMRT GRID</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -4471,29 +4471,29 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>16.8448</v>
+        <v>160</v>
       </c>
       <c r="N15" t="n">
-        <v>66.7</v>
+        <v>56.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1123.55</v>
+        <v>9088</v>
       </c>
       <c r="P15" t="n">
-        <v>20.721325216</v>
+        <v>60.20275</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.721325216</v>
+        <v>60.20275</v>
       </c>
       <c r="R15" t="n">
-        <v>349.046579</v>
+        <v>9632.440000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>774.503421</v>
+        <v>-544.4400000000001</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4502,11 +4502,11 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1123.55</v>
+        <v>9088</v>
       </c>
     </row>
     <row r="16">
@@ -4530,17 +4530,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>INRA</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ISHAR GL CL EN TR UCI ETF-US</t>
+          <t>INTERACTIVE BROKERS GRO-CL A</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -4551,29 +4551,29 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>385</v>
+        <v>16.8448</v>
       </c>
       <c r="N16" t="n">
-        <v>25.834</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>9946.09</v>
+        <v>1136.86</v>
       </c>
       <c r="P16" t="n">
-        <v>25.997158151</v>
+        <v>20.721325216</v>
       </c>
       <c r="Q16" t="n">
-        <v>25.997158151</v>
+        <v>20.721325216</v>
       </c>
       <c r="R16" t="n">
-        <v>10008.905888</v>
+        <v>349.046579</v>
       </c>
       <c r="S16" t="n">
-        <v>-62.815888</v>
+        <v>787.8134209999999</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4582,11 +4582,11 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>AEB</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>9946.09</v>
+        <v>1136.86</v>
       </c>
     </row>
     <row r="17">
@@ -4610,17 +4610,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>INRA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JPMORGAN CHASE &amp; CO</t>
+          <t>ISHAR GL CL EN TR UCI ETF-US</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -4631,29 +4631,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>100</v>
+        <v>385</v>
       </c>
       <c r="N17" t="n">
-        <v>289.48</v>
+        <v>26.2184</v>
       </c>
       <c r="O17" t="n">
-        <v>28948</v>
+        <v>10094.08</v>
       </c>
       <c r="P17" t="n">
-        <v>298.02</v>
+        <v>25.997158151</v>
       </c>
       <c r="Q17" t="n">
-        <v>298.02</v>
+        <v>25.997158151</v>
       </c>
       <c r="R17" t="n">
-        <v>29802</v>
+        <v>10008.905888</v>
       </c>
       <c r="S17" t="n">
-        <v>-854</v>
+        <v>85.17411199999999</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4662,11 +4662,11 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>AEB</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28948</v>
+        <v>10094.08</v>
       </c>
     </row>
     <row r="18">
@@ -4690,17 +4690,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>JPMORGAN CHASE &amp; CO</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4711,29 +4711,29 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>170.36</v>
+        <v>289.92</v>
       </c>
       <c r="O18" t="n">
-        <v>85180</v>
+        <v>28992</v>
       </c>
       <c r="P18" t="n">
-        <v>174.06142722</v>
+        <v>298.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>174.06142722</v>
+        <v>298.02</v>
       </c>
       <c r="R18" t="n">
-        <v>87030.71361000001</v>
+        <v>29802</v>
       </c>
       <c r="S18" t="n">
-        <v>-1850.71361</v>
+        <v>-810</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4742,11 +4742,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>85180</v>
+        <v>28992</v>
       </c>
     </row>
     <row r="19">
@@ -4765,65 +4765,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OPT</t>
+          <t>STK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AAPL  260327C00290000</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 290 C</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" t="n">
-        <v>290</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="N19" t="n">
-        <v>0.215</v>
+        <v>169.82</v>
       </c>
       <c r="O19" t="n">
-        <v>21.5</v>
+        <v>84910</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1405125</v>
+        <v>174.06142722</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1405125</v>
+        <v>174.06142722</v>
       </c>
       <c r="R19" t="n">
-        <v>214.05125</v>
+        <v>87030.71361000001</v>
       </c>
       <c r="S19" t="n">
-        <v>-192.55125</v>
+        <v>-2120.71361</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4832,11 +4822,11 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>21.5</v>
+        <v>84910</v>
       </c>
     </row>
     <row r="20">
@@ -4865,19 +4855,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MSFT  260327C00420000</t>
+          <t>AAPL  260327C00290000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 420 C</t>
+          <t>AAPL 27MAR26 290 C</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>420</v>
+        <v>290</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -4891,29 +4881,29 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>7.45</v>
+        <v>0.165</v>
       </c>
       <c r="O20" t="n">
-        <v>745</v>
+        <v>16.5</v>
       </c>
       <c r="P20" t="n">
-        <v>4.6805125</v>
+        <v>2.1405125</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.6805125</v>
+        <v>2.1405125</v>
       </c>
       <c r="R20" t="n">
-        <v>468.05125</v>
+        <v>214.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>276.94875</v>
+        <v>-197.55125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -4926,7 +4916,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>745</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="21">
@@ -4981,17 +4971,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>14.6481</v>
+        <v>13.8611</v>
       </c>
       <c r="O21" t="n">
-        <v>1464.81</v>
+        <v>1386.11</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5003,7 +4993,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>1212.75875</v>
+        <v>1134.05875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5016,7 +5006,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>1464.81</v>
+        <v>1386.11</v>
       </c>
     </row>
     <row r="22">
@@ -5040,60 +5030,60 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NVDA  260327C00220000</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NVDA 27MAR26 220 C</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>220</v>
+        <v>560</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.165</v>
+        <v>29.7625</v>
       </c>
       <c r="O22" t="n">
-        <v>16.5</v>
+        <v>5952.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6805125</v>
+        <v>23.5270125</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.6805125</v>
+        <v>23.5270125</v>
       </c>
       <c r="R22" t="n">
-        <v>268.05125</v>
+        <v>4705.4025</v>
       </c>
       <c r="S22" t="n">
-        <v>-251.55125</v>
+        <v>1247.0975</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5106,7 +5096,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>16.5</v>
+        <v>5952.5</v>
       </c>
     </row>
     <row r="23">
@@ -5135,19 +5125,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>QQQ   261218P00560000</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 560 P</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>560</v>
+        <v>620</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -5161,29 +5151,29 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>33.0144</v>
+        <v>25.075</v>
       </c>
       <c r="O23" t="n">
-        <v>6602.88</v>
+        <v>5015</v>
       </c>
       <c r="P23" t="n">
-        <v>23.5270125</v>
+        <v>20.1350875</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.5270125</v>
+        <v>20.1350875</v>
       </c>
       <c r="R23" t="n">
-        <v>4705.4025</v>
+        <v>4027.0175</v>
       </c>
       <c r="S23" t="n">
-        <v>1897.4775</v>
+        <v>987.9825</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5196,7 +5186,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>6602.88</v>
+        <v>5015</v>
       </c>
     </row>
     <row r="24">
@@ -5225,23 +5215,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SPY   261218P00620000</t>
+          <t>AAPL  260327P00250000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 620 P</t>
+          <t>AAPL 27MAR26 250 P</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>620</v>
+        <v>250</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -5251,33 +5241,33 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>27.86</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>5572</v>
+        <v>-325</v>
       </c>
       <c r="P24" t="n">
-        <v>20.1350875</v>
+        <v>1.7694546</v>
       </c>
       <c r="Q24" t="n">
-        <v>20.1350875</v>
+        <v>1.7694546</v>
       </c>
       <c r="R24" t="n">
-        <v>4027.0175</v>
+        <v>-176.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>1544.9825</v>
+        <v>-148.05454</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -5286,7 +5276,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>5572</v>
+        <v>-325</v>
       </c>
     </row>
     <row r="25">
@@ -5310,24 +5300,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AAPL  260327P00250000</t>
+          <t>AAPL  260327C00285000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 250 P</t>
+          <t>AAPL 27MAR26 285 C</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -5336,34 +5326,34 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>4.9</v>
+        <v>0.29</v>
       </c>
       <c r="O25" t="n">
-        <v>-490</v>
+        <v>-29</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7694546</v>
+        <v>3.4194546</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.7694546</v>
+        <v>3.4194546</v>
       </c>
       <c r="R25" t="n">
-        <v>-176.94546</v>
+        <v>-341.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>-313.05454</v>
+        <v>312.94546</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5376,7 +5366,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-490</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="26">
@@ -5400,24 +5390,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AAPL  260327C00285000</t>
+          <t>AMD   260327P00185000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 285 C</t>
+          <t>AMD 27MAR26 185 P</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -5426,34 +5416,34 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.37</v>
+        <v>3.93</v>
       </c>
       <c r="O26" t="n">
-        <v>-37</v>
+        <v>-393</v>
       </c>
       <c r="P26" t="n">
-        <v>3.4194546</v>
+        <v>4.1794546</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4194546</v>
+        <v>4.1794546</v>
       </c>
       <c r="R26" t="n">
-        <v>-341.94546</v>
+        <v>-417.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>304.94546</v>
+        <v>24.94546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5466,7 +5456,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-37</v>
+        <v>-393</v>
       </c>
     </row>
     <row r="27">
@@ -5490,24 +5480,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AMD   260327P00185000</t>
+          <t>AMD   260327C00255000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 185 P</t>
+          <t>AMD 27MAR26 255 C</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>185</v>
+        <v>255</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5516,34 +5506,34 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>8.175000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="O27" t="n">
-        <v>-817.5</v>
+        <v>-29</v>
       </c>
       <c r="P27" t="n">
-        <v>4.1794546</v>
+        <v>2.3694546</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.1794546</v>
+        <v>2.3694546</v>
       </c>
       <c r="R27" t="n">
-        <v>-417.94546</v>
+        <v>-236.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>-399.55454</v>
+        <v>207.94546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5556,7 +5546,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-817.5</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="28">
@@ -5580,24 +5570,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AMD   260327C00255000</t>
+          <t>AMZN  260327P00190000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 255 C</t>
+          <t>AMZN 27MAR26 190 P</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>255</v>
+        <v>190</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -5606,34 +5596,34 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.27</v>
+        <v>1.195</v>
       </c>
       <c r="O28" t="n">
-        <v>-27</v>
+        <v>-119.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3694546</v>
+        <v>1.7994546</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3694546</v>
+        <v>1.7994546</v>
       </c>
       <c r="R28" t="n">
-        <v>-236.94546</v>
+        <v>-179.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>209.94546</v>
+        <v>60.44546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5646,7 +5636,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-27</v>
+        <v>-119.5</v>
       </c>
     </row>
     <row r="29">
@@ -5675,19 +5665,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AMZN  260327P00190000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 190 P</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>190</v>
+        <v>295</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -5701,29 +5691,29 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.215</v>
+        <v>4.625</v>
       </c>
       <c r="O29" t="n">
-        <v>-221.5</v>
+        <v>-462.5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.7994546</v>
+        <v>5.9694626</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.7994546</v>
+        <v>5.9694626</v>
       </c>
       <c r="R29" t="n">
-        <v>-179.94546</v>
+        <v>-596.9462600000001</v>
       </c>
       <c r="S29" t="n">
-        <v>-41.55454</v>
+        <v>134.44626</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5736,7 +5726,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-221.5</v>
+        <v>-462.5</v>
       </c>
     </row>
     <row r="30">
@@ -5760,24 +5750,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00295000</t>
+          <t>GOOGL 260327C00315000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 295 P</t>
+          <t>GOOGL 27MAR26 315 C</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -5786,34 +5776,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>8.545</v>
+        <v>5.175</v>
       </c>
       <c r="O30" t="n">
-        <v>-854.5</v>
+        <v>-517.5</v>
       </c>
       <c r="P30" t="n">
-        <v>5.9694626</v>
+        <v>3.2300876</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.9694626</v>
+        <v>3.2300876</v>
       </c>
       <c r="R30" t="n">
-        <v>-596.9462600000001</v>
+        <v>-323.00876</v>
       </c>
       <c r="S30" t="n">
-        <v>-257.55374</v>
+        <v>-194.49124</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5826,7 +5816,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-854.5</v>
+        <v>-517.5</v>
       </c>
     </row>
     <row r="31">
@@ -5855,19 +5845,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GOOGL 260327C00330000</t>
+          <t>JPM   260327C00310000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 330 C</t>
+          <t>JPM 27MAR26 310 C</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -5881,29 +5871,29 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.055</v>
+        <v>1.305</v>
       </c>
       <c r="O31" t="n">
-        <v>-105.5</v>
+        <v>-130.5</v>
       </c>
       <c r="P31" t="n">
-        <v>4.6494796</v>
+        <v>4.4694546</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.6494796</v>
+        <v>4.4694546</v>
       </c>
       <c r="R31" t="n">
-        <v>-464.94796</v>
+        <v>-446.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>359.44796</v>
+        <v>316.44546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -5916,7 +5906,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-105.5</v>
+        <v>-130.5</v>
       </c>
     </row>
     <row r="32">
@@ -5940,24 +5930,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JPM   260327C00310000</t>
+          <t>MSFT  260327P00360000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>JPM 27MAR26 310 C</t>
+          <t>MSFT 27MAR26 360 P</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -5966,34 +5956,34 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.84</v>
+        <v>1.07</v>
       </c>
       <c r="O32" t="n">
-        <v>-184</v>
+        <v>-107</v>
       </c>
       <c r="P32" t="n">
-        <v>4.4694546</v>
+        <v>2.1094546</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.4694546</v>
+        <v>2.1094546</v>
       </c>
       <c r="R32" t="n">
-        <v>-446.94546</v>
+        <v>-210.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>262.94546</v>
+        <v>103.94546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6006,7 +5996,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-184</v>
+        <v>-107</v>
       </c>
     </row>
     <row r="33">
@@ -6035,19 +6025,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MSFT  260327P00360000</t>
+          <t>NFLX  260327P00072000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 360 P</t>
+          <t>NFLX 27MAR26 72 P</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>360</v>
+        <v>72</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -6061,29 +6051,29 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>1.85</v>
+        <v>0.079</v>
       </c>
       <c r="O33" t="n">
-        <v>-185</v>
+        <v>-7.9</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1094546</v>
+        <v>0.8794546</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.1094546</v>
+        <v>0.8794546</v>
       </c>
       <c r="R33" t="n">
-        <v>-210.94546</v>
+        <v>-87.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>25.94546</v>
+        <v>80.04546000000001</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6096,7 +6086,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-185</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="34">
@@ -6125,19 +6115,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MSFT  260327C00415000</t>
+          <t>NFLX  260327C00083000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 415 C</t>
+          <t>NFLX 27MAR26 83 C</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -6151,29 +6141,29 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>9.699999999999999</v>
+        <v>15.785</v>
       </c>
       <c r="O34" t="n">
-        <v>-970</v>
+        <v>-1578.5</v>
       </c>
       <c r="P34" t="n">
-        <v>5.9994546</v>
+        <v>3.2794546</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.9994546</v>
+        <v>3.2794546</v>
       </c>
       <c r="R34" t="n">
-        <v>-599.94546</v>
+        <v>-327.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-370.05454</v>
+        <v>-1250.55454</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6186,7 +6176,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-970</v>
+        <v>-1578.5</v>
       </c>
     </row>
     <row r="35">
@@ -6215,23 +6205,23 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NFLX  260327P00072000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 72 P</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>72</v>
+        <v>425</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6241,29 +6231,29 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>0.101</v>
+        <v>8.401300000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>-10.1</v>
+        <v>-1680.26</v>
       </c>
       <c r="P35" t="n">
-        <v>0.8794546</v>
+        <v>6.3929546</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.8794546</v>
+        <v>6.3929546</v>
       </c>
       <c r="R35" t="n">
-        <v>-87.94546</v>
+        <v>-1278.59092</v>
       </c>
       <c r="S35" t="n">
-        <v>77.84546</v>
+        <v>-401.66908</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6276,7 +6266,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-10.1</v>
+        <v>-1680.26</v>
       </c>
     </row>
     <row r="36">
@@ -6300,60 +6290,60 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NFLX  260327C00083000</t>
+          <t>SPY   261218P00505000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 83 C</t>
+          <t>SPY 18DEC26 505 P</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>83</v>
+        <v>505</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>16.5492</v>
+        <v>9.270200000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>-1654.92</v>
+        <v>-1854.04</v>
       </c>
       <c r="P36" t="n">
-        <v>3.2794546</v>
+        <v>7.3496796</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2794546</v>
+        <v>7.3496796</v>
       </c>
       <c r="R36" t="n">
-        <v>-327.94546</v>
+        <v>-1469.93592</v>
       </c>
       <c r="S36" t="n">
-        <v>-1326.97454</v>
+        <v>-384.10408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6366,277 +6356,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-1654.92</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>NVDA  260327C00215000</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>NVDA 27MAR26 215 C</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" t="n">
-        <v>215</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="O37" t="n">
-        <v>-25.5</v>
-      </c>
-      <c r="P37" t="n">
-        <v>3.6694546</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.6694546</v>
-      </c>
-      <c r="R37" t="n">
-        <v>-366.94546</v>
-      </c>
-      <c r="S37" t="n">
-        <v>341.44546</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>-25.5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>QQQ   261218P00425000</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>QQQ 18DEC26 425 P</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" t="n">
-        <v>425</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N38" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="O38" t="n">
-        <v>-1898</v>
-      </c>
-      <c r="P38" t="n">
-        <v>6.3929546</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>6.3929546</v>
-      </c>
-      <c r="R38" t="n">
-        <v>-1278.59092</v>
-      </c>
-      <c r="S38" t="n">
-        <v>-619.40908</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>-1898</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" t="n">
-        <v>505</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N39" t="n">
-        <v>10.643</v>
-      </c>
-      <c r="O39" t="n">
-        <v>-2128.6</v>
-      </c>
-      <c r="P39" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="R39" t="n">
-        <v>-1469.93592</v>
-      </c>
-      <c r="S39" t="n">
-        <v>-658.66408</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>-2128.6</v>
+        <v>-1854.04</v>
       </c>
     </row>
   </sheetData>
@@ -6683,17 +6403,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$335,075.11</t>
+          <t>$297,567.56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$96,859.61</t>
+          <t>$134,112.59</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$431,934.72</t>
+          <t>$431,680.15</t>
         </is>
       </c>
     </row>
@@ -6705,17 +6425,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$459,308.20</t>
+          <t>$433,940.17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$84,469.68</t>
+          <t>$108,814.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$543,777.89</t>
+          <t>$542,754.61</t>
         </is>
       </c>
     </row>
@@ -6733,17 +6453,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$794,383.31</t>
+          <t>$731,507.73</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$181,329.30</t>
+          <t>$242,927.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$975,712.61</t>
+          <t>$974,434.76</t>
         </is>
       </c>
     </row>
@@ -6791,14 +6511,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-08 23:40:30</t>
+          <t>2026-03-10 23:41:55</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2865</v>
+        <v>1.2844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>393.85</v>
+        <v>401.35</v>
       </c>
       <c r="O2" t="n">
-        <v>15754</v>
+        <v>16054</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-954.503607</v>
+        <v>-654.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20267.521</v>
+        <v>20619.7576</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2865</v>
+        <v>1.2844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>61.75</v>
+        <v>63.72</v>
       </c>
       <c r="O3" t="n">
-        <v>15437.5</v>
+        <v>15930</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-870.853333</v>
+        <v>-378.353333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>19860.34375</v>
+        <v>20460.492</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14517</v>
+        <v>0.14534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.02</v>
+        <v>31.42</v>
       </c>
       <c r="O4" t="n">
-        <v>93060</v>
+        <v>94260</v>
       </c>
       <c r="P4" t="n">
         <v>31.36596519</v>
@@ -767,7 +767,7 @@
         <v>94097.89556999999</v>
       </c>
       <c r="S4" t="n">
-        <v>-1037.89557</v>
+        <v>162.10443</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>13509.5202</v>
+        <v>13699.7484</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1636</v>
+        <v>1.161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.3585</v>
       </c>
       <c r="O5" t="n">
-        <v>8400</v>
+        <v>8717</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-924.66</v>
+        <v>-607.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9774.24</v>
+        <v>10120.437</v>
       </c>
     </row>
     <row r="6">
@@ -871,11 +871,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.78456</v>
+        <v>1.161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -884,17 +884,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>GDR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES3</t>
+          <t>HY9H</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>STATE STRT SPDR STRAITS TIME</t>
+          <t>SK HYNIX INC-GDS</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -905,29 +905,29 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8000</v>
+        <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>4.75</v>
+        <v>560</v>
       </c>
       <c r="O6" t="n">
-        <v>38000</v>
+        <v>8400</v>
       </c>
       <c r="P6" t="n">
-        <v>4.663903356</v>
+        <v>556.278</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.663903356</v>
+        <v>556.278</v>
       </c>
       <c r="R6" t="n">
-        <v>37311.22685</v>
+        <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>688.77315</v>
+        <v>55.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -936,11 +936,11 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SGX</t>
+          <t>FWB2</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>29813.28</v>
+        <v>9752.4</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78456</v>
+        <v>0.78537</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GSD</t>
+          <t>ES3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SPDR GOLD SHARES</t>
+          <t>STATE STRT SPDR STRAITS TIME</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -985,29 +985,29 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>75</v>
+        <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>600.98</v>
+        <v>4.87</v>
       </c>
       <c r="O7" t="n">
-        <v>45073.5</v>
+        <v>38960</v>
       </c>
       <c r="P7" t="n">
-        <v>589.78798656</v>
+        <v>4.663903356</v>
       </c>
       <c r="Q7" t="n">
-        <v>589.78798656</v>
+        <v>4.663903356</v>
       </c>
       <c r="R7" t="n">
-        <v>44234.098992</v>
+        <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>839.401008</v>
+        <v>1648.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>35362.86516</v>
+        <v>30598.0152</v>
       </c>
     </row>
     <row r="8">
@@ -1031,11 +1031,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.78537</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>GSD</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GLOBAL X CHINA ROBOTICS</t>
+          <t>SPDR GOLD SHARES</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1065,29 +1065,29 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>7.77</v>
+        <v>606.7</v>
       </c>
       <c r="O8" t="n">
-        <v>7770</v>
+        <v>45502.5</v>
       </c>
       <c r="P8" t="n">
-        <v>8.311237657</v>
+        <v>589.78798656</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.311237657</v>
+        <v>589.78798656</v>
       </c>
       <c r="R8" t="n">
-        <v>8311.237657</v>
+        <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-541.237657</v>
+        <v>1268.401008</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1096,11 +1096,11 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SEHK</t>
+          <t>SGX</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>7770</v>
+        <v>35736.298425</v>
       </c>
     </row>
     <row r="9">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AGNICO EAGLE MINES LTD</t>
+          <t>GLOBAL X CHINA ROBOTICS</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1145,29 +1145,29 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>224.75</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>6742.5</v>
+        <v>8000</v>
       </c>
       <c r="P9" t="n">
-        <v>218.103333333</v>
+        <v>8.311237657</v>
       </c>
       <c r="Q9" t="n">
-        <v>218.103333333</v>
+        <v>8.311237657</v>
       </c>
       <c r="R9" t="n">
-        <v>6543.1</v>
+        <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>199.4</v>
+        <v>-311.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>SEHK</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>6742.5</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="10">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BITO</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PROSHARES BITCOIN ETF-USD</t>
+          <t>AGNICO EAGLE MINES LTD</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1225,29 +1225,29 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>9.51</v>
+        <v>226.94</v>
       </c>
       <c r="O10" t="n">
-        <v>951</v>
+        <v>6808.2</v>
       </c>
       <c r="P10" t="n">
-        <v>9.705</v>
+        <v>218.103333333</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.705</v>
+        <v>218.103333333</v>
       </c>
       <c r="R10" t="n">
-        <v>970.5</v>
+        <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-19.5</v>
+        <v>265.1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1256,11 +1256,11 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>951</v>
+        <v>6808.2</v>
       </c>
     </row>
     <row r="11">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSNDX</t>
+          <t>BITO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ISHARES NASDAQ 100 USD ACC</t>
+          <t>PROSHARES BITCOIN ETF-USD</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1305,29 +1305,29 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>1416</v>
+        <v>9.65</v>
       </c>
       <c r="O11" t="n">
-        <v>14160</v>
+        <v>965</v>
       </c>
       <c r="P11" t="n">
-        <v>1474.045</v>
+        <v>9.705</v>
       </c>
       <c r="Q11" t="n">
-        <v>1474.045</v>
+        <v>9.705</v>
       </c>
       <c r="R11" t="n">
-        <v>14740.45</v>
+        <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-580.45</v>
+        <v>-5.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1336,11 +1336,11 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>14160</v>
+        <v>965</v>
       </c>
     </row>
     <row r="12">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CSNDX</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ALPHABET INC-CL A</t>
+          <t>ISHARES NASDAQ 100 USD ACC</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1385,29 +1385,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>306.36</v>
+        <v>1443.4</v>
       </c>
       <c r="O12" t="n">
-        <v>30636</v>
+        <v>14434</v>
       </c>
       <c r="P12" t="n">
-        <v>301.635</v>
+        <v>1474.045</v>
       </c>
       <c r="Q12" t="n">
-        <v>301.635</v>
+        <v>1474.045</v>
       </c>
       <c r="R12" t="n">
-        <v>30163.5</v>
+        <v>14740.45</v>
       </c>
       <c r="S12" t="n">
-        <v>472.5</v>
+        <v>-306.45</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1416,11 +1416,11 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>EBS</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30636</v>
+        <v>14434</v>
       </c>
     </row>
     <row r="13">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GRDU</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FT NSDQ CLN EDG SMRT GRID</t>
+          <t>ALPHABET INC-CL A</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1465,29 +1465,29 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>56.8</v>
+        <v>307.04</v>
       </c>
       <c r="O13" t="n">
-        <v>9088</v>
+        <v>30704</v>
       </c>
       <c r="P13" t="n">
-        <v>59.854125</v>
+        <v>301.635</v>
       </c>
       <c r="Q13" t="n">
-        <v>59.854125</v>
+        <v>301.635</v>
       </c>
       <c r="R13" t="n">
-        <v>9576.66</v>
+        <v>30163.5</v>
       </c>
       <c r="S13" t="n">
-        <v>-488.66</v>
+        <v>540.5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9088</v>
+        <v>30704</v>
       </c>
     </row>
     <row r="14">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>INRA</t>
+          <t>GRDU</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ISHAR GL CL EN TR UCI ETF-US</t>
+          <t>FT NSDQ CLN EDG SMRT GRID</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1545,29 +1545,29 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>385</v>
+        <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>26.2184</v>
+        <v>58.645</v>
       </c>
       <c r="O14" t="n">
-        <v>10094.08</v>
+        <v>9383.200000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>26.012734603</v>
+        <v>59.854125</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.012734603</v>
+        <v>59.854125</v>
       </c>
       <c r="R14" t="n">
-        <v>10014.902822</v>
+        <v>9576.66</v>
       </c>
       <c r="S14" t="n">
-        <v>79.177178</v>
+        <v>-193.46</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1576,11 +1576,11 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>AEB</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10094.08</v>
+        <v>9383.200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1604,17 +1604,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>INRA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ORACLE CORP</t>
+          <t>ISHAR GL CL EN TR UCI ETF-US</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1625,29 +1625,29 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>385</v>
       </c>
       <c r="N15" t="n">
-        <v>151.56</v>
+        <v>27.0491</v>
       </c>
       <c r="O15" t="n">
-        <v>15156</v>
+        <v>10413.9</v>
       </c>
       <c r="P15" t="n">
-        <v>205.3357044</v>
+        <v>26.012734603</v>
       </c>
       <c r="Q15" t="n">
-        <v>205.3357044</v>
+        <v>26.012734603</v>
       </c>
       <c r="R15" t="n">
-        <v>20533.57044</v>
+        <v>10014.902822</v>
       </c>
       <c r="S15" t="n">
-        <v>-5377.57044</v>
+        <v>398.997178</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1656,11 +1656,11 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>AEB</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>15156</v>
+        <v>10413.9</v>
       </c>
     </row>
     <row r="16">
@@ -1684,17 +1684,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ADR</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SEA LTD-ADR</t>
+          <t>ORACLE CORP</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1705,29 +1705,29 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N16" t="n">
-        <v>90.09999999999999</v>
+        <v>149.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1802</v>
+        <v>10458</v>
       </c>
       <c r="P16" t="n">
-        <v>124.315</v>
+        <v>204.330714286</v>
       </c>
       <c r="Q16" t="n">
-        <v>124.315</v>
+        <v>204.330714286</v>
       </c>
       <c r="R16" t="n">
-        <v>2486.3</v>
+        <v>14303.15</v>
       </c>
       <c r="S16" t="n">
-        <v>-684.3</v>
+        <v>-3845.15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1802</v>
+        <v>10458</v>
       </c>
     </row>
     <row r="17">
@@ -1764,17 +1764,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>SEA LTD-ADR</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1785,29 +1785,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>169.82</v>
+        <v>89.17</v>
       </c>
       <c r="O17" t="n">
-        <v>67928</v>
+        <v>1783.4</v>
       </c>
       <c r="P17" t="n">
-        <v>173.855759437</v>
+        <v>124.315</v>
       </c>
       <c r="Q17" t="n">
-        <v>173.855759437</v>
+        <v>124.315</v>
       </c>
       <c r="R17" t="n">
-        <v>69542.30377499999</v>
+        <v>2486.3</v>
       </c>
       <c r="S17" t="n">
-        <v>-1614.303775</v>
+        <v>-702.9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>67928</v>
+        <v>1783.4</v>
       </c>
     </row>
     <row r="18">
@@ -1839,65 +1839,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OPT</t>
+          <t>STK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AAPL  260327C00290000</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 290 C</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" t="n">
-        <v>290</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>0.165</v>
+        <v>173.04</v>
       </c>
       <c r="O18" t="n">
-        <v>16.5</v>
+        <v>86520</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0105125</v>
+        <v>173.59385355</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.0105125</v>
+        <v>173.59385355</v>
       </c>
       <c r="R18" t="n">
-        <v>201.05125</v>
+        <v>86796.926775</v>
       </c>
       <c r="S18" t="n">
-        <v>-184.55125</v>
+        <v>-276.926775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1906,11 +1896,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>16.5</v>
+        <v>86520</v>
       </c>
     </row>
     <row r="19">
@@ -1939,19 +1929,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MSFT  260327C00420000</t>
+          <t>AAPL  260327C00290000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 420 C</t>
+          <t>AAPL 27MAR26 290 C</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>420</v>
+        <v>290</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1965,29 +1955,29 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>6.275</v>
+        <v>0.17</v>
       </c>
       <c r="O19" t="n">
-        <v>627.5</v>
+        <v>17</v>
       </c>
       <c r="P19" t="n">
-        <v>4.4905125</v>
+        <v>2.0105125</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.4905125</v>
+        <v>2.0105125</v>
       </c>
       <c r="R19" t="n">
-        <v>449.05125</v>
+        <v>201.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>178.44875</v>
+        <v>-184.05125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +1990,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>627.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -2024,60 +2014,60 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>QQQ   261218P00560000</t>
+          <t>MSFT  260327C00420000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 560 P</t>
+          <t>MSFT 27MAR26 420 C</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>29.7625</v>
+        <v>4.45</v>
       </c>
       <c r="O20" t="n">
-        <v>5952.5</v>
+        <v>445</v>
       </c>
       <c r="P20" t="n">
-        <v>23.4605</v>
+        <v>4.4905125</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.4605</v>
+        <v>4.4905125</v>
       </c>
       <c r="R20" t="n">
-        <v>4692.1</v>
+        <v>449.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>1260.4</v>
+        <v>-4.05125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2080,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>5952.5</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21">
@@ -2119,19 +2109,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SPY   261218P00620000</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 620 P</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>620</v>
+        <v>560</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2145,29 +2135,29 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>25.075</v>
+        <v>29.7208</v>
       </c>
       <c r="O21" t="n">
-        <v>5015</v>
+        <v>5944.16</v>
       </c>
       <c r="P21" t="n">
-        <v>20.1374875</v>
+        <v>23.4605</v>
       </c>
       <c r="Q21" t="n">
-        <v>20.1374875</v>
+        <v>23.4605</v>
       </c>
       <c r="R21" t="n">
-        <v>4027.4975</v>
+        <v>4692.1</v>
       </c>
       <c r="S21" t="n">
-        <v>987.5025000000001</v>
+        <v>1252.06</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2170,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>5015</v>
+        <v>5944.16</v>
       </c>
     </row>
     <row r="22">
@@ -2209,23 +2199,23 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AAPL  260327P00250000</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 250 P</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>250</v>
+        <v>620</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2235,33 +2225,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>25.84</v>
       </c>
       <c r="O22" t="n">
-        <v>-325</v>
+        <v>5168</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7494546</v>
+        <v>20.1374875</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.7494546</v>
+        <v>20.1374875</v>
       </c>
       <c r="R22" t="n">
-        <v>-174.94546</v>
+        <v>4027.4975</v>
       </c>
       <c r="S22" t="n">
-        <v>-150.05454</v>
+        <v>1140.5025</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2270,7 +2260,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-325</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="23">
@@ -2294,24 +2284,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AAPL  260327C00285000</t>
+          <t>AAPL  260327P00250000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 285 C</t>
+          <t>AAPL 27MAR26 250 P</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2320,34 +2310,34 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.29</v>
+        <v>2.85</v>
       </c>
       <c r="O23" t="n">
-        <v>-29</v>
+        <v>-285</v>
       </c>
       <c r="P23" t="n">
-        <v>3.2494546</v>
+        <v>1.7494546</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2494546</v>
+        <v>1.7494546</v>
       </c>
       <c r="R23" t="n">
-        <v>-324.94546</v>
+        <v>-174.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>295.94546</v>
+        <v>-110.05454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2350,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-29</v>
+        <v>-285</v>
       </c>
     </row>
     <row r="24">
@@ -2384,24 +2374,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AMD   260327P00185000</t>
+          <t>AAPL  260327C00285000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 185 P</t>
+          <t>AAPL 27MAR26 285 C</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2410,34 +2400,34 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.93</v>
+        <v>0.27</v>
       </c>
       <c r="O24" t="n">
-        <v>-393</v>
+        <v>-27</v>
       </c>
       <c r="P24" t="n">
-        <v>7.5800876</v>
+        <v>3.2494546</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.5800876</v>
+        <v>3.2494546</v>
       </c>
       <c r="R24" t="n">
-        <v>-758.0087600000001</v>
+        <v>-324.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>365.00876</v>
+        <v>297.94546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2440,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-393</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="25">
@@ -2479,19 +2469,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AMZN  260327P00190000</t>
+          <t>AMD   260327P00185000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 190 P</t>
+          <t>AMD 27MAR26 185 P</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2505,29 +2495,29 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.195</v>
+        <v>3.875</v>
       </c>
       <c r="O25" t="n">
-        <v>-119.5</v>
+        <v>-387.5</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8142796</v>
+        <v>7.5800876</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.8142796</v>
+        <v>7.5800876</v>
       </c>
       <c r="R25" t="n">
-        <v>-181.42796</v>
+        <v>-758.0087600000001</v>
       </c>
       <c r="S25" t="n">
-        <v>61.92796</v>
+        <v>370.50876</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2530,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-119.5</v>
+        <v>-387.5</v>
       </c>
     </row>
     <row r="26">
@@ -2564,24 +2554,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AMZN  260327C00235000</t>
+          <t>AMZN  260327P00190000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 235 C</t>
+          <t>AMZN 27MAR26 190 P</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2590,34 +2580,34 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.55</v>
+        <v>1.08</v>
       </c>
       <c r="O26" t="n">
-        <v>-55</v>
+        <v>-108</v>
       </c>
       <c r="P26" t="n">
-        <v>1.0242796</v>
+        <v>1.8142796</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.0242796</v>
+        <v>1.8142796</v>
       </c>
       <c r="R26" t="n">
-        <v>-102.42796</v>
+        <v>-181.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>47.42796</v>
+        <v>73.42796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2620,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-55</v>
+        <v>-108</v>
       </c>
     </row>
     <row r="27">
@@ -2654,24 +2644,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00295000</t>
+          <t>AMZN  260327C00235000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 295 P</t>
+          <t>AMZN 27MAR26 235 C</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>295</v>
+        <v>235</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2680,34 +2670,34 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>4.625</v>
+        <v>0.46</v>
       </c>
       <c r="O27" t="n">
-        <v>-925</v>
+        <v>-46</v>
       </c>
       <c r="P27" t="n">
-        <v>6.6394751</v>
+        <v>1.0242796</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.6394751</v>
+        <v>1.0242796</v>
       </c>
       <c r="R27" t="n">
-        <v>-1327.89502</v>
+        <v>-102.42796</v>
       </c>
       <c r="S27" t="n">
-        <v>402.89502</v>
+        <v>56.42796</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2710,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-925</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="28">
@@ -2744,24 +2734,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GOOGL 260327C00315000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 315 C</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2770,34 +2760,34 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N28" t="n">
-        <v>5.175</v>
+        <v>4.1785</v>
       </c>
       <c r="O28" t="n">
-        <v>-517.5</v>
+        <v>-835.7</v>
       </c>
       <c r="P28" t="n">
-        <v>6.7894876</v>
+        <v>6.6394751</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.7894876</v>
+        <v>6.6394751</v>
       </c>
       <c r="R28" t="n">
-        <v>-678.94876</v>
+        <v>-1327.89502</v>
       </c>
       <c r="S28" t="n">
-        <v>161.44876</v>
+        <v>492.19502</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2800,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-517.5</v>
+        <v>-835.7</v>
       </c>
     </row>
     <row r="29">
@@ -2834,24 +2824,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MSFT  260327P00360000</t>
+          <t>GOOGL 260327C00315000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 360 P</t>
+          <t>GOOGL 27MAR26 315 C</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2860,34 +2850,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.07</v>
+        <v>5.1442</v>
       </c>
       <c r="O29" t="n">
-        <v>-107</v>
+        <v>-514.42</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1194546</v>
+        <v>6.7894876</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1194546</v>
+        <v>6.7894876</v>
       </c>
       <c r="R29" t="n">
-        <v>-211.94546</v>
+        <v>-678.94876</v>
       </c>
       <c r="S29" t="n">
-        <v>104.94546</v>
+        <v>164.52876</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2890,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-107</v>
+        <v>-514.42</v>
       </c>
     </row>
     <row r="30">
@@ -2924,24 +2914,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MSFT  260327C00415000</t>
+          <t>MSFT  260327P00360000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 415 C</t>
+          <t>MSFT 27MAR26 360 P</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>415</v>
+        <v>360</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2950,34 +2940,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>8.4899</v>
+        <v>1.19</v>
       </c>
       <c r="O30" t="n">
-        <v>-848.99</v>
+        <v>-119</v>
       </c>
       <c r="P30" t="n">
-        <v>5.7894546</v>
+        <v>2.1194546</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.7894546</v>
+        <v>2.1194546</v>
       </c>
       <c r="R30" t="n">
-        <v>-578.94546</v>
+        <v>-211.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>-270.04454</v>
+        <v>92.94546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2980,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-848.99</v>
+        <v>-119</v>
       </c>
     </row>
     <row r="31">
@@ -3014,24 +3004,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NFLX  260327P00088000</t>
+          <t>MSFT  260327C00415000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 88 P</t>
+          <t>MSFT 27MAR26 415 C</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>88</v>
+        <v>415</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3040,34 +3030,34 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.525</v>
+        <v>6.275</v>
       </c>
       <c r="O31" t="n">
-        <v>-105</v>
+        <v>-627.5</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9454876</v>
+        <v>5.7894546</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9454876</v>
+        <v>5.7894546</v>
       </c>
       <c r="R31" t="n">
-        <v>-189.09752</v>
+        <v>-578.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>84.09752</v>
+        <v>-48.55454</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3070,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-105</v>
+        <v>-627.5</v>
       </c>
     </row>
     <row r="32">
@@ -3109,23 +3099,23 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>NFLX  260327P00088000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>NFLX 27MAR26 88 P</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>425</v>
+        <v>88</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3135,29 +3125,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>8.401300000000001</v>
+        <v>0.615</v>
       </c>
       <c r="O32" t="n">
-        <v>-1680.26</v>
+        <v>-123</v>
       </c>
       <c r="P32" t="n">
-        <v>6.3644671</v>
+        <v>0.9454876</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.3644671</v>
+        <v>0.9454876</v>
       </c>
       <c r="R32" t="n">
-        <v>-1272.89342</v>
+        <v>-189.09752</v>
       </c>
       <c r="S32" t="n">
-        <v>-407.36658</v>
+        <v>66.09752</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3160,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-1680.26</v>
+        <v>-123</v>
       </c>
     </row>
     <row r="33">
@@ -3199,19 +3189,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SPY   261218P00505000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 505 P</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>505</v>
+        <v>425</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3225,42 +3215,132 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>9.270200000000001</v>
+        <v>8.4092</v>
       </c>
       <c r="O33" t="n">
-        <v>-1854.04</v>
+        <v>-1681.84</v>
       </c>
       <c r="P33" t="n">
+        <v>6.3644671</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6.3644671</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-1272.89342</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-408.94658</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>-1681.84</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>U2739721</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SPY   261218P00505000</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SPY 18DEC26 505 P</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" t="n">
+        <v>505</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>9.635</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-1927</v>
+      </c>
+      <c r="P34" t="n">
         <v>7.3548796</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q34" t="n">
         <v>7.3548796</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>-1470.97592</v>
       </c>
-      <c r="S33" t="n">
-        <v>-383.06408</v>
-      </c>
-      <c r="T33" t="inlineStr">
+      <c r="S34" t="n">
+        <v>-456.02408</v>
+      </c>
+      <c r="T34" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="V33" t="n">
-        <v>-1854.04</v>
+      <c r="V34" t="n">
+        <v>-1927</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3401,7 +3481,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2865</v>
+        <v>1.2844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3431,17 +3511,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>393.85</v>
+        <v>401.35</v>
       </c>
       <c r="O2" t="n">
-        <v>19692.5</v>
+        <v>20067.5</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3453,7 +3533,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-1290.456235</v>
+        <v>-915.456235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3466,7 +3546,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25334.40125</v>
+        <v>25774.697</v>
       </c>
     </row>
     <row r="3">
@@ -3481,7 +3561,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2865</v>
+        <v>1.2844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3511,17 +3591,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>5000</v>
       </c>
       <c r="N3" t="n">
-        <v>3.447</v>
+        <v>3.5075</v>
       </c>
       <c r="O3" t="n">
-        <v>17235</v>
+        <v>17537.5</v>
       </c>
       <c r="P3" t="n">
         <v>3.57250536</v>
@@ -3533,7 +3613,7 @@
         <v>17862.5268</v>
       </c>
       <c r="S3" t="n">
-        <v>-627.5268</v>
+        <v>-325.0268</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3546,7 +3626,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>22172.8275</v>
+        <v>22525.165</v>
       </c>
     </row>
     <row r="4">
@@ -3561,7 +3641,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2865</v>
+        <v>1.2844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3591,17 +3671,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>350</v>
       </c>
       <c r="N4" t="n">
-        <v>61.75</v>
+        <v>63.72</v>
       </c>
       <c r="O4" t="n">
-        <v>21612.5</v>
+        <v>22302</v>
       </c>
       <c r="P4" t="n">
         <v>65.60009794299999</v>
@@ -3613,7 +3693,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S4" t="n">
-        <v>-1347.53428</v>
+        <v>-658.03428</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3626,7 +3706,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>27804.48125</v>
+        <v>28644.6888</v>
       </c>
     </row>
     <row r="5">
@@ -3641,7 +3721,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14517</v>
+        <v>0.14534</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3671,17 +3751,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.02</v>
+        <v>31.42</v>
       </c>
       <c r="O5" t="n">
-        <v>62040</v>
+        <v>62840</v>
       </c>
       <c r="P5" t="n">
         <v>31.696238595</v>
@@ -3693,7 +3773,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S5" t="n">
-        <v>-1352.47719</v>
+        <v>-552.47719</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3706,7 +3786,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9006.346799999999</v>
+        <v>9133.1656</v>
       </c>
     </row>
     <row r="6">
@@ -3721,7 +3801,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1636</v>
+        <v>1.161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3751,17 +3831,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>3000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.3585</v>
       </c>
       <c r="O6" t="n">
-        <v>12600</v>
+        <v>13075.5</v>
       </c>
       <c r="P6" t="n">
         <v>4.65841303</v>
@@ -3773,7 +3853,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1375.239091</v>
+        <v>-899.739091</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3786,7 +3866,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>14661.36</v>
+        <v>15180.6555</v>
       </c>
     </row>
     <row r="7">
@@ -3801,7 +3881,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1636</v>
+        <v>1.161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,17 +3911,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>1000</v>
       </c>
       <c r="N7" t="n">
-        <v>45.51</v>
+        <v>46.77</v>
       </c>
       <c r="O7" t="n">
-        <v>45510</v>
+        <v>46770</v>
       </c>
       <c r="P7" t="n">
         <v>43.01</v>
@@ -3853,7 +3933,7 @@
         <v>43010</v>
       </c>
       <c r="S7" t="n">
-        <v>2500</v>
+        <v>3760</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3866,7 +3946,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>52955.436</v>
+        <v>54299.97</v>
       </c>
     </row>
     <row r="8">
@@ -3877,11 +3957,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78456</v>
+        <v>1.161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3890,17 +3970,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>GDR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES3</t>
+          <t>HY9H</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>STATE STRT SPDR STRAITS TIME</t>
+          <t>SK HYNIX INC-GDS</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3911,29 +3991,29 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10000</v>
+        <v>15</v>
       </c>
       <c r="N8" t="n">
-        <v>4.75</v>
+        <v>560</v>
       </c>
       <c r="O8" t="n">
-        <v>47500</v>
+        <v>8400</v>
       </c>
       <c r="P8" t="n">
-        <v>3.72681816</v>
+        <v>556.278</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.72681816</v>
+        <v>556.278</v>
       </c>
       <c r="R8" t="n">
-        <v>37268.1816</v>
+        <v>8344.17</v>
       </c>
       <c r="S8" t="n">
-        <v>10231.8184</v>
+        <v>55.83</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -3942,11 +4022,11 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SGX</t>
+          <t>FWB2</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37266.6</v>
+        <v>9752.4</v>
       </c>
     </row>
     <row r="9">
@@ -3961,7 +4041,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78456</v>
+        <v>0.78537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3975,12 +4055,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GSD</t>
+          <t>ES3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SPDR GOLD SHARES</t>
+          <t>STATE STRT SPDR STRAITS TIME</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -3991,29 +4071,29 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>75</v>
+        <v>10000</v>
       </c>
       <c r="N9" t="n">
-        <v>600.98</v>
+        <v>4.87</v>
       </c>
       <c r="O9" t="n">
-        <v>45073.5</v>
+        <v>48700</v>
       </c>
       <c r="P9" t="n">
-        <v>589.644672</v>
+        <v>3.72681816</v>
       </c>
       <c r="Q9" t="n">
-        <v>589.644672</v>
+        <v>3.72681816</v>
       </c>
       <c r="R9" t="n">
-        <v>44223.3504</v>
+        <v>37268.1816</v>
       </c>
       <c r="S9" t="n">
-        <v>850.1496</v>
+        <v>11431.8184</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4026,7 +4106,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>35362.86516</v>
+        <v>38247.519</v>
       </c>
     </row>
     <row r="10">
@@ -4037,11 +4117,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0.78537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4055,12 +4135,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>GSD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GLOBAL X CHINA ROBOTICS</t>
+          <t>SPDR GOLD SHARES</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -4071,29 +4151,29 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1100</v>
+        <v>75</v>
       </c>
       <c r="N10" t="n">
-        <v>7.77</v>
+        <v>606.7</v>
       </c>
       <c r="O10" t="n">
-        <v>8547</v>
+        <v>45502.5</v>
       </c>
       <c r="P10" t="n">
-        <v>8.311679952</v>
+        <v>589.644672</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.311679952</v>
+        <v>589.644672</v>
       </c>
       <c r="R10" t="n">
-        <v>9142.847947</v>
+        <v>44223.3504</v>
       </c>
       <c r="S10" t="n">
-        <v>-595.847947</v>
+        <v>1279.1496</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4102,11 +4182,11 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SEHK</t>
+          <t>SGX</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8547</v>
+        <v>35736.298425</v>
       </c>
     </row>
     <row r="11">
@@ -4130,17 +4210,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AGNICO EAGLE MINES LTD</t>
+          <t>GLOBAL X CHINA ROBOTICS</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -4151,29 +4231,29 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>30</v>
+        <v>1100</v>
       </c>
       <c r="N11" t="n">
-        <v>224.75</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>6742.5</v>
+        <v>8800</v>
       </c>
       <c r="P11" t="n">
-        <v>217.973333333</v>
+        <v>8.311679952</v>
       </c>
       <c r="Q11" t="n">
-        <v>217.973333333</v>
+        <v>8.311679952</v>
       </c>
       <c r="R11" t="n">
-        <v>6539.2</v>
+        <v>9142.847947</v>
       </c>
       <c r="S11" t="n">
-        <v>203.3</v>
+        <v>-342.847947</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4182,11 +4262,11 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>SEHK</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6742.5</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="12">
@@ -4210,17 +4290,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BITO</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PROSHARES BITCOIN ETF-USD</t>
+          <t>AGNICO EAGLE MINES LTD</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -4231,29 +4311,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="N12" t="n">
-        <v>9.51</v>
+        <v>226.94</v>
       </c>
       <c r="O12" t="n">
-        <v>2853</v>
+        <v>6808.2</v>
       </c>
       <c r="P12" t="n">
-        <v>11.661666667</v>
+        <v>217.973333333</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.661666667</v>
+        <v>217.973333333</v>
       </c>
       <c r="R12" t="n">
-        <v>3498.5</v>
+        <v>6539.2</v>
       </c>
       <c r="S12" t="n">
-        <v>-645.5</v>
+        <v>269</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4262,11 +4342,11 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2853</v>
+        <v>6808.2</v>
       </c>
     </row>
     <row r="13">
@@ -4295,12 +4375,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CSNDX</t>
+          <t>BITO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ISHARES NASDAQ 100 USD ACC</t>
+          <t>PROSHARES BITCOIN ETF-USD</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -4311,29 +4391,29 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="N13" t="n">
-        <v>1416</v>
+        <v>9.65</v>
       </c>
       <c r="O13" t="n">
-        <v>21240</v>
+        <v>2895</v>
       </c>
       <c r="P13" t="n">
-        <v>1471.727366667</v>
+        <v>11.661666667</v>
       </c>
       <c r="Q13" t="n">
-        <v>1471.727366667</v>
+        <v>11.661666667</v>
       </c>
       <c r="R13" t="n">
-        <v>22075.9105</v>
+        <v>3498.5</v>
       </c>
       <c r="S13" t="n">
-        <v>-835.9105</v>
+        <v>-603.5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4342,11 +4422,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>21240</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="14">
@@ -4370,17 +4450,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CSNDX</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ALPHABET INC-CL A</t>
+          <t>ISHARES NASDAQ 100 USD ACC</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -4391,29 +4471,29 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="N14" t="n">
-        <v>306.36</v>
+        <v>1443.4</v>
       </c>
       <c r="O14" t="n">
-        <v>30636</v>
+        <v>21651</v>
       </c>
       <c r="P14" t="n">
-        <v>331.87755</v>
+        <v>1471.727366667</v>
       </c>
       <c r="Q14" t="n">
-        <v>331.87755</v>
+        <v>1471.727366667</v>
       </c>
       <c r="R14" t="n">
-        <v>33187.755</v>
+        <v>22075.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>-2551.755</v>
+        <v>-424.9105</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4422,11 +4502,11 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>EBS</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>30636</v>
+        <v>21651</v>
       </c>
     </row>
     <row r="15">
@@ -4450,17 +4530,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GRDU</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FT NSDQ CLN EDG SMRT GRID</t>
+          <t>ALPHABET INC-CL A</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -4471,29 +4551,29 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>56.8</v>
+        <v>307.04</v>
       </c>
       <c r="O15" t="n">
-        <v>9088</v>
+        <v>30704</v>
       </c>
       <c r="P15" t="n">
-        <v>60.20275</v>
+        <v>331.87755</v>
       </c>
       <c r="Q15" t="n">
-        <v>60.20275</v>
+        <v>331.87755</v>
       </c>
       <c r="R15" t="n">
-        <v>9632.440000000001</v>
+        <v>33187.755</v>
       </c>
       <c r="S15" t="n">
-        <v>-544.4400000000001</v>
+        <v>-2483.755</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4502,11 +4582,11 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>9088</v>
+        <v>30704</v>
       </c>
     </row>
     <row r="16">
@@ -4530,17 +4610,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>GRDU</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>INTERACTIVE BROKERS GRO-CL A</t>
+          <t>FT NSDQ CLN EDG SMRT GRID</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -4551,29 +4631,29 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>16.8448</v>
+        <v>160</v>
       </c>
       <c r="N16" t="n">
-        <v>67.48999999999999</v>
+        <v>58.645</v>
       </c>
       <c r="O16" t="n">
-        <v>1136.86</v>
+        <v>9383.200000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>20.721325216</v>
+        <v>60.20275</v>
       </c>
       <c r="Q16" t="n">
-        <v>20.721325216</v>
+        <v>60.20275</v>
       </c>
       <c r="R16" t="n">
-        <v>349.046579</v>
+        <v>9632.440000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>787.8134209999999</v>
+        <v>-249.24</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4582,11 +4662,11 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1136.86</v>
+        <v>9383.200000000001</v>
       </c>
     </row>
     <row r="17">
@@ -4610,17 +4690,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>INRA</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ISHAR GL CL EN TR UCI ETF-US</t>
+          <t>INTERACTIVE BROKERS GRO-CL A</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -4631,29 +4711,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>385</v>
+        <v>16.8448</v>
       </c>
       <c r="N17" t="n">
-        <v>26.2184</v>
+        <v>68.5</v>
       </c>
       <c r="O17" t="n">
-        <v>10094.08</v>
+        <v>1153.87</v>
       </c>
       <c r="P17" t="n">
-        <v>25.997158151</v>
+        <v>20.721325216</v>
       </c>
       <c r="Q17" t="n">
-        <v>25.997158151</v>
+        <v>20.721325216</v>
       </c>
       <c r="R17" t="n">
-        <v>10008.905888</v>
+        <v>349.046579</v>
       </c>
       <c r="S17" t="n">
-        <v>85.17411199999999</v>
+        <v>804.8234210000001</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4662,11 +4742,11 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>AEB</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>10094.08</v>
+        <v>1153.87</v>
       </c>
     </row>
     <row r="18">
@@ -4690,17 +4770,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>INRA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>JPMORGAN CHASE &amp; CO</t>
+          <t>ISHAR GL CL EN TR UCI ETF-US</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4711,29 +4791,29 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>385</v>
       </c>
       <c r="N18" t="n">
-        <v>289.92</v>
+        <v>27.0491</v>
       </c>
       <c r="O18" t="n">
-        <v>28992</v>
+        <v>10413.9</v>
       </c>
       <c r="P18" t="n">
-        <v>298.02</v>
+        <v>25.997158151</v>
       </c>
       <c r="Q18" t="n">
-        <v>298.02</v>
+        <v>25.997158151</v>
       </c>
       <c r="R18" t="n">
-        <v>29802</v>
+        <v>10008.905888</v>
       </c>
       <c r="S18" t="n">
-        <v>-810</v>
+        <v>404.994112</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4742,11 +4822,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>AEB</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>28992</v>
+        <v>10413.9</v>
       </c>
     </row>
     <row r="19">
@@ -4770,17 +4850,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>JPMORGAN CHASE &amp; CO</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4791,29 +4871,29 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>169.82</v>
+        <v>288.73</v>
       </c>
       <c r="O19" t="n">
-        <v>84910</v>
+        <v>28873</v>
       </c>
       <c r="P19" t="n">
-        <v>174.06142722</v>
+        <v>298.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>174.06142722</v>
+        <v>298.02</v>
       </c>
       <c r="R19" t="n">
-        <v>87030.71361000001</v>
+        <v>29802</v>
       </c>
       <c r="S19" t="n">
-        <v>-2120.71361</v>
+        <v>-929</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4822,11 +4902,11 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>84910</v>
+        <v>28873</v>
       </c>
     </row>
     <row r="20">
@@ -4845,65 +4925,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OPT</t>
+          <t>STK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AAPL  260327C00290000</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 290 C</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" t="n">
-        <v>290</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="N20" t="n">
-        <v>0.165</v>
+        <v>173.04</v>
       </c>
       <c r="O20" t="n">
-        <v>16.5</v>
+        <v>103824</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1405125</v>
+        <v>173.846763275</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.1405125</v>
+        <v>173.846763275</v>
       </c>
       <c r="R20" t="n">
-        <v>214.05125</v>
+        <v>104308.057965</v>
       </c>
       <c r="S20" t="n">
-        <v>-197.55125</v>
+        <v>-484.057965</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -4912,11 +4982,11 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>16.5</v>
+        <v>103824</v>
       </c>
     </row>
     <row r="21">
@@ -4945,19 +5015,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NFLX  260327C00085000</t>
+          <t>AAPL  260327C00290000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 85 C</t>
+          <t>AAPL 27MAR26 290 C</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>85</v>
+        <v>290</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -4971,29 +5041,29 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>13.8611</v>
+        <v>0.17</v>
       </c>
       <c r="O21" t="n">
-        <v>1386.11</v>
+        <v>17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5205125</v>
+        <v>2.1405125</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5205125</v>
+        <v>2.1405125</v>
       </c>
       <c r="R21" t="n">
-        <v>252.05125</v>
+        <v>214.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>1134.05875</v>
+        <v>-197.05125</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5006,7 +5076,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>1386.11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -5030,60 +5100,60 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>QQQ   261218P00560000</t>
+          <t>NFLX  260327C00085000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 560 P</t>
+          <t>NFLX 27MAR26 85 C</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>560</v>
+        <v>85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>29.7625</v>
+        <v>12.4467</v>
       </c>
       <c r="O22" t="n">
-        <v>5952.5</v>
+        <v>1244.67</v>
       </c>
       <c r="P22" t="n">
-        <v>23.5270125</v>
+        <v>2.5205125</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.5270125</v>
+        <v>2.5205125</v>
       </c>
       <c r="R22" t="n">
-        <v>4705.4025</v>
+        <v>252.05125</v>
       </c>
       <c r="S22" t="n">
-        <v>1247.0975</v>
+        <v>992.61875</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5096,7 +5166,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5952.5</v>
+        <v>1244.67</v>
       </c>
     </row>
     <row r="23">
@@ -5125,19 +5195,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SPY   261218P00620000</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 620 P</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>620</v>
+        <v>560</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -5151,29 +5221,29 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>25.075</v>
+        <v>29.7208</v>
       </c>
       <c r="O23" t="n">
-        <v>5015</v>
+        <v>5944.16</v>
       </c>
       <c r="P23" t="n">
-        <v>20.1350875</v>
+        <v>23.5270125</v>
       </c>
       <c r="Q23" t="n">
-        <v>20.1350875</v>
+        <v>23.5270125</v>
       </c>
       <c r="R23" t="n">
-        <v>4027.0175</v>
+        <v>4705.4025</v>
       </c>
       <c r="S23" t="n">
-        <v>987.9825</v>
+        <v>1238.7575</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5186,7 +5256,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5015</v>
+        <v>5944.16</v>
       </c>
     </row>
     <row r="24">
@@ -5215,23 +5285,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AAPL  260327P00250000</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 250 P</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>250</v>
+        <v>620</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -5241,33 +5311,33 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>25.84</v>
       </c>
       <c r="O24" t="n">
-        <v>-325</v>
+        <v>5168</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7694546</v>
+        <v>20.1350875</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.7694546</v>
+        <v>20.1350875</v>
       </c>
       <c r="R24" t="n">
-        <v>-176.94546</v>
+        <v>4027.0175</v>
       </c>
       <c r="S24" t="n">
-        <v>-148.05454</v>
+        <v>1140.9825</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -5276,7 +5346,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-325</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="25">
@@ -5300,24 +5370,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AAPL  260327C00285000</t>
+          <t>AAPL  260327P00250000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 285 C</t>
+          <t>AAPL 27MAR26 250 P</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -5326,34 +5396,34 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.29</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
-        <v>-29</v>
+        <v>-285</v>
       </c>
       <c r="P25" t="n">
-        <v>3.4194546</v>
+        <v>1.7694546</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4194546</v>
+        <v>1.7694546</v>
       </c>
       <c r="R25" t="n">
-        <v>-341.94546</v>
+        <v>-176.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>312.94546</v>
+        <v>-108.05454</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5366,7 +5436,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-29</v>
+        <v>-285</v>
       </c>
     </row>
     <row r="26">
@@ -5390,24 +5460,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AMD   260327P00185000</t>
+          <t>AAPL  260327C00285000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 185 P</t>
+          <t>AAPL 27MAR26 285 C</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -5416,34 +5486,34 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.93</v>
+        <v>0.27</v>
       </c>
       <c r="O26" t="n">
-        <v>-393</v>
+        <v>-27</v>
       </c>
       <c r="P26" t="n">
-        <v>4.1794546</v>
+        <v>3.4194546</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.1794546</v>
+        <v>3.4194546</v>
       </c>
       <c r="R26" t="n">
-        <v>-417.94546</v>
+        <v>-341.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>24.94546</v>
+        <v>314.94546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5456,7 +5526,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-393</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="27">
@@ -5480,24 +5550,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AMD   260327C00255000</t>
+          <t>AMD   260327P00185000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 255 C</t>
+          <t>AMD 27MAR26 185 P</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5506,34 +5576,34 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.29</v>
+        <v>3.875</v>
       </c>
       <c r="O27" t="n">
-        <v>-29</v>
+        <v>-387.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3694546</v>
+        <v>4.1794546</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.3694546</v>
+        <v>4.1794546</v>
       </c>
       <c r="R27" t="n">
-        <v>-236.94546</v>
+        <v>-417.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>207.94546</v>
+        <v>30.44546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5546,7 +5616,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-29</v>
+        <v>-387.5</v>
       </c>
     </row>
     <row r="28">
@@ -5570,24 +5640,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AMZN  260327P00190000</t>
+          <t>AMD   260327C00255000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 190 P</t>
+          <t>AMD 27MAR26 255 C</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -5596,34 +5666,34 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.195</v>
+        <v>0.265</v>
       </c>
       <c r="O28" t="n">
-        <v>-119.5</v>
+        <v>-26.5</v>
       </c>
       <c r="P28" t="n">
-        <v>1.7994546</v>
+        <v>2.3694546</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.7994546</v>
+        <v>2.3694546</v>
       </c>
       <c r="R28" t="n">
-        <v>-179.94546</v>
+        <v>-236.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>60.44546</v>
+        <v>210.44546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5636,7 +5706,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-119.5</v>
+        <v>-26.5</v>
       </c>
     </row>
     <row r="29">
@@ -5665,19 +5735,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00295000</t>
+          <t>AMZN  260327P00190000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 295 P</t>
+          <t>AMZN 27MAR26 190 P</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>295</v>
+        <v>190</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -5691,29 +5761,29 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>4.625</v>
+        <v>1.08</v>
       </c>
       <c r="O29" t="n">
-        <v>-462.5</v>
+        <v>-108</v>
       </c>
       <c r="P29" t="n">
-        <v>5.9694626</v>
+        <v>1.7994546</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.9694626</v>
+        <v>1.7994546</v>
       </c>
       <c r="R29" t="n">
-        <v>-596.9462600000001</v>
+        <v>-179.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>134.44626</v>
+        <v>71.94546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5726,7 +5796,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-462.5</v>
+        <v>-108</v>
       </c>
     </row>
     <row r="30">
@@ -5750,24 +5820,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GOOGL 260327C00315000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 315 C</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -5776,34 +5846,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>5.175</v>
+        <v>4.1785</v>
       </c>
       <c r="O30" t="n">
-        <v>-517.5</v>
+        <v>-417.85</v>
       </c>
       <c r="P30" t="n">
-        <v>3.2300876</v>
+        <v>5.9694626</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2300876</v>
+        <v>5.9694626</v>
       </c>
       <c r="R30" t="n">
-        <v>-323.00876</v>
+        <v>-596.9462600000001</v>
       </c>
       <c r="S30" t="n">
-        <v>-194.49124</v>
+        <v>179.09626</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5816,7 +5886,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-517.5</v>
+        <v>-417.85</v>
       </c>
     </row>
     <row r="31">
@@ -5845,19 +5915,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JPM   260327C00310000</t>
+          <t>GOOGL 260327C00315000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>JPM 27MAR26 310 C</t>
+          <t>GOOGL 27MAR26 315 C</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -5871,29 +5941,29 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.305</v>
+        <v>5.1442</v>
       </c>
       <c r="O31" t="n">
-        <v>-130.5</v>
+        <v>-514.42</v>
       </c>
       <c r="P31" t="n">
-        <v>4.4694546</v>
+        <v>3.2300876</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.4694546</v>
+        <v>3.2300876</v>
       </c>
       <c r="R31" t="n">
-        <v>-446.94546</v>
+        <v>-323.00876</v>
       </c>
       <c r="S31" t="n">
-        <v>316.44546</v>
+        <v>-191.41124</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -5906,7 +5976,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-130.5</v>
+        <v>-514.42</v>
       </c>
     </row>
     <row r="32">
@@ -5930,24 +6000,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MSFT  260327P00360000</t>
+          <t>JPM   260327C00297500</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 360 P</t>
+          <t>JPM 27MAR26 297.5 C</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>360</v>
+        <v>297.5</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -5956,34 +6026,34 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.07</v>
+        <v>4.1596</v>
       </c>
       <c r="O32" t="n">
-        <v>-107</v>
+        <v>-415.96</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1094546</v>
+        <v>4.8394876</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.1094546</v>
+        <v>4.8394876</v>
       </c>
       <c r="R32" t="n">
-        <v>-210.94546</v>
+        <v>-483.94876</v>
       </c>
       <c r="S32" t="n">
-        <v>103.94546</v>
+        <v>67.98876</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -5996,7 +6066,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-107</v>
+        <v>-415.96</v>
       </c>
     </row>
     <row r="33">
@@ -6025,19 +6095,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NFLX  260327P00072000</t>
+          <t>MSFT  260327P00360000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 72 P</t>
+          <t>MSFT 27MAR26 360 P</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>72</v>
+        <v>360</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -6051,29 +6121,29 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>0.079</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>-7.9</v>
+        <v>-119</v>
       </c>
       <c r="P33" t="n">
-        <v>0.8794546</v>
+        <v>2.1094546</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8794546</v>
+        <v>2.1094546</v>
       </c>
       <c r="R33" t="n">
-        <v>-87.94546</v>
+        <v>-210.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>80.04546000000001</v>
+        <v>91.94546</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6086,7 +6156,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-7.9</v>
+        <v>-119</v>
       </c>
     </row>
     <row r="34">
@@ -6110,24 +6180,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NFLX  260327C00083000</t>
+          <t>NFLX  260327P00072000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 83 C</t>
+          <t>NFLX 27MAR26 72 P</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -6136,34 +6206,34 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>15.785</v>
+        <v>0.0636</v>
       </c>
       <c r="O34" t="n">
-        <v>-1578.5</v>
+        <v>-6.36</v>
       </c>
       <c r="P34" t="n">
-        <v>3.2794546</v>
+        <v>0.8794546</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2794546</v>
+        <v>0.8794546</v>
       </c>
       <c r="R34" t="n">
-        <v>-327.94546</v>
+        <v>-87.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-1250.55454</v>
+        <v>81.58546</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6176,7 +6246,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1578.5</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="35">
@@ -6200,60 +6270,60 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>NFLX  260327C00083000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>NFLX 27MAR26 83 C</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>8.401300000000001</v>
+        <v>14.3393</v>
       </c>
       <c r="O35" t="n">
-        <v>-1680.26</v>
+        <v>-1433.93</v>
       </c>
       <c r="P35" t="n">
-        <v>6.3929546</v>
+        <v>3.2794546</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.3929546</v>
+        <v>3.2794546</v>
       </c>
       <c r="R35" t="n">
-        <v>-1278.59092</v>
+        <v>-327.94546</v>
       </c>
       <c r="S35" t="n">
-        <v>-401.66908</v>
+        <v>-1105.98454</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6266,7 +6336,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-1680.26</v>
+        <v>-1433.93</v>
       </c>
     </row>
     <row r="36">
@@ -6295,19 +6365,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SPY   261218P00505000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 505 P</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>505</v>
+        <v>425</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -6321,42 +6391,132 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>9.270200000000001</v>
+        <v>8.4092</v>
       </c>
       <c r="O36" t="n">
-        <v>-1854.04</v>
+        <v>-1681.84</v>
       </c>
       <c r="P36" t="n">
+        <v>6.3929546</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>6.3929546</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-1278.59092</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-403.24908</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>-1681.84</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>U6565621</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SPY   261218P00505000</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SPY 18DEC26 505 P</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" t="n">
+        <v>505</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9.635</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-1927</v>
+      </c>
+      <c r="P37" t="n">
         <v>7.3496796</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q37" t="n">
         <v>7.3496796</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>-1469.93592</v>
       </c>
-      <c r="S36" t="n">
-        <v>-384.10408</v>
-      </c>
-      <c r="T36" t="inlineStr">
+      <c r="S37" t="n">
+        <v>-457.06408</v>
+      </c>
+      <c r="T37" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="V36" t="n">
-        <v>-1854.04</v>
+      <c r="V37" t="n">
+        <v>-1927</v>
       </c>
     </row>
   </sheetData>
@@ -6403,17 +6563,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$297,567.56</t>
+          <t>$325,349.05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$134,112.59</t>
+          <t>$111,582.72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$431,680.15</t>
+          <t>$436,931.77</t>
         </is>
       </c>
     </row>
@@ -6425,17 +6585,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$433,940.17</t>
+          <t>$468,824.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$108,814.44</t>
+          <t>$82,198.68</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$542,754.61</t>
+          <t>$551,022.88</t>
         </is>
       </c>
     </row>
@@ -6453,17 +6613,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$731,507.73</t>
+          <t>$794,173.25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$242,927.03</t>
+          <t>$193,781.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$974,434.76</t>
+          <t>$987,954.65</t>
         </is>
       </c>
     </row>
@@ -6511,14 +6671,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-10 23:41:55</t>
+          <t>2026-03-11 23:42:03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2844</v>
+        <v>1.2811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>401.35</v>
+        <v>398.6</v>
       </c>
       <c r="O2" t="n">
-        <v>16054</v>
+        <v>15944</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-654.503607</v>
+        <v>-764.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20619.7576</v>
+        <v>20425.8584</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2844</v>
+        <v>1.2811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>63.72</v>
+        <v>63.2</v>
       </c>
       <c r="O3" t="n">
-        <v>15930</v>
+        <v>15800</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-378.353333</v>
+        <v>-508.353333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>20460.492</v>
+        <v>20241.38</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14534</v>
+        <v>0.14542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.42</v>
+        <v>31.56</v>
       </c>
       <c r="O4" t="n">
-        <v>94260</v>
+        <v>94680</v>
       </c>
       <c r="P4" t="n">
         <v>31.36596519</v>
@@ -767,7 +767,7 @@
         <v>94097.89556999999</v>
       </c>
       <c r="S4" t="n">
-        <v>162.10443</v>
+        <v>582.10443</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>13699.7484</v>
+        <v>13768.3656</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.161</v>
+        <v>1.1567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3585</v>
+        <v>4.3175</v>
       </c>
       <c r="O5" t="n">
-        <v>8717</v>
+        <v>8635</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-607.66</v>
+        <v>-689.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>10120.437</v>
+        <v>9988.104500000001</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.161</v>
+        <v>1.1567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="O6" t="n">
-        <v>8400</v>
+        <v>8460</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>55.83</v>
+        <v>115.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9752.4</v>
+        <v>9785.682000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78537</v>
+        <v>0.78478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.87</v>
+        <v>4.85</v>
       </c>
       <c r="O7" t="n">
-        <v>38960</v>
+        <v>38800</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1648.77315</v>
+        <v>1488.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30598.0152</v>
+        <v>30449.464</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78537</v>
+        <v>0.78478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>606.7</v>
+        <v>607</v>
       </c>
       <c r="O8" t="n">
-        <v>45502.5</v>
+        <v>45525</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>1268.401008</v>
+        <v>1290.901008</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>35736.298425</v>
+        <v>35727.1095</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>7.985</v>
       </c>
       <c r="O9" t="n">
-        <v>8000</v>
+        <v>7985</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-311.237657</v>
+        <v>-326.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>8000</v>
+        <v>7985</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>226.94</v>
+        <v>222.81</v>
       </c>
       <c r="O10" t="n">
-        <v>6808.2</v>
+        <v>6684.3</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>265.1</v>
+        <v>141.2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6808.2</v>
+        <v>6684.3</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.65</v>
+        <v>9.73</v>
       </c>
       <c r="O11" t="n">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.5</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>965</v>
+        <v>973</v>
       </c>
     </row>
     <row r="12">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CSNDX</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ISHARES NASDAQ 100 USD ACC</t>
+          <t>ALPHABET INC-CL A</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1385,29 +1385,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>1443.4</v>
+        <v>308.7</v>
       </c>
       <c r="O12" t="n">
-        <v>14434</v>
+        <v>30870</v>
       </c>
       <c r="P12" t="n">
-        <v>1474.045</v>
+        <v>301.635</v>
       </c>
       <c r="Q12" t="n">
-        <v>1474.045</v>
+        <v>301.635</v>
       </c>
       <c r="R12" t="n">
-        <v>14740.45</v>
+        <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-306.45</v>
+        <v>706.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1416,11 +1416,11 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>14434</v>
+        <v>30870</v>
       </c>
     </row>
     <row r="13">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GRDU</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ALPHABET INC-CL A</t>
+          <t>FT NSDQ CLN EDG SMRT GRID</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1465,29 +1465,29 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>307.04</v>
+        <v>58.27</v>
       </c>
       <c r="O13" t="n">
-        <v>30704</v>
+        <v>9323.200000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>301.635</v>
+        <v>59.854125</v>
       </c>
       <c r="Q13" t="n">
-        <v>301.635</v>
+        <v>59.854125</v>
       </c>
       <c r="R13" t="n">
-        <v>30163.5</v>
+        <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>540.5</v>
+        <v>-253.46</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30704</v>
+        <v>9323.200000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GRDU</t>
+          <t>INRA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FT NSDQ CLN EDG SMRT GRID</t>
+          <t>ISHAR GL CL EN TR UCI ETF-US</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1545,29 +1545,29 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>160</v>
+        <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>58.645</v>
+        <v>27.3423</v>
       </c>
       <c r="O14" t="n">
-        <v>9383.200000000001</v>
+        <v>10526.79</v>
       </c>
       <c r="P14" t="n">
-        <v>59.854125</v>
+        <v>26.012734603</v>
       </c>
       <c r="Q14" t="n">
-        <v>59.854125</v>
+        <v>26.012734603</v>
       </c>
       <c r="R14" t="n">
-        <v>9576.66</v>
+        <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>-193.46</v>
+        <v>511.887178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1576,11 +1576,11 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>AEB</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9383.200000000001</v>
+        <v>10526.79</v>
       </c>
     </row>
     <row r="15">
@@ -1604,17 +1604,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>INRA</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ISHAR GL CL EN TR UCI ETF-US</t>
+          <t>ORACLE CORP</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1625,29 +1625,29 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>385</v>
+        <v>70</v>
       </c>
       <c r="N15" t="n">
-        <v>27.0491</v>
+        <v>163.12</v>
       </c>
       <c r="O15" t="n">
-        <v>10413.9</v>
+        <v>11418.4</v>
       </c>
       <c r="P15" t="n">
-        <v>26.012734603</v>
+        <v>204.330714286</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.012734603</v>
+        <v>204.330714286</v>
       </c>
       <c r="R15" t="n">
-        <v>10014.902822</v>
+        <v>14303.15</v>
       </c>
       <c r="S15" t="n">
-        <v>398.997178</v>
+        <v>-2884.75</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1656,11 +1656,11 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>AEB</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>10413.9</v>
+        <v>11418.4</v>
       </c>
     </row>
     <row r="16">
@@ -1684,17 +1684,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ORACLE CORP</t>
+          <t>SEA LTD-ADR</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1705,29 +1705,29 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>149.4</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>10458</v>
+        <v>1756.4</v>
       </c>
       <c r="P16" t="n">
-        <v>204.330714286</v>
+        <v>124.315</v>
       </c>
       <c r="Q16" t="n">
-        <v>204.330714286</v>
+        <v>124.315</v>
       </c>
       <c r="R16" t="n">
-        <v>14303.15</v>
+        <v>2486.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-3845.15</v>
+        <v>-729.9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10458</v>
+        <v>1756.4</v>
       </c>
     </row>
     <row r="17">
@@ -1764,17 +1764,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADR</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SEA LTD-ADR</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1785,29 +1785,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="N17" t="n">
-        <v>89.17</v>
+        <v>171.26</v>
       </c>
       <c r="O17" t="n">
-        <v>1783.4</v>
+        <v>85630</v>
       </c>
       <c r="P17" t="n">
-        <v>124.315</v>
+        <v>173.59385355</v>
       </c>
       <c r="Q17" t="n">
-        <v>124.315</v>
+        <v>173.59385355</v>
       </c>
       <c r="R17" t="n">
-        <v>2486.3</v>
+        <v>86796.926775</v>
       </c>
       <c r="S17" t="n">
-        <v>-702.9</v>
+        <v>-1166.926775</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1783.4</v>
+        <v>85630</v>
       </c>
     </row>
     <row r="18">
@@ -1839,55 +1839,65 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>AAPL  260327C00290000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>AAPL 27MAR26 290 C</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I18" t="n">
+        <v>290</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>173.04</v>
+        <v>0.125</v>
       </c>
       <c r="O18" t="n">
-        <v>86520</v>
+        <v>12.5</v>
       </c>
       <c r="P18" t="n">
-        <v>173.59385355</v>
+        <v>2.0105125</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.59385355</v>
+        <v>2.0105125</v>
       </c>
       <c r="R18" t="n">
-        <v>86796.926775</v>
+        <v>201.05125</v>
       </c>
       <c r="S18" t="n">
-        <v>-276.926775</v>
+        <v>-188.55125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1896,11 +1906,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>86520</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="19">
@@ -1929,19 +1939,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AAPL  260327C00290000</t>
+          <t>MSFT  260327C00420000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 290 C</t>
+          <t>MSFT 27MAR26 420 C</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>290</v>
+        <v>420</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1955,29 +1965,29 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.17</v>
+        <v>3.275</v>
       </c>
       <c r="O19" t="n">
-        <v>17</v>
+        <v>327.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0105125</v>
+        <v>4.4905125</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.0105125</v>
+        <v>4.4905125</v>
       </c>
       <c r="R19" t="n">
-        <v>201.05125</v>
+        <v>449.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-184.05125</v>
+        <v>-121.55125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1990,7 +2000,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>17</v>
+        <v>327.5</v>
       </c>
     </row>
     <row r="20">
@@ -2014,60 +2024,60 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MSFT  260327C00420000</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 420 C</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>420</v>
+        <v>560</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.45</v>
+        <v>29.2202</v>
       </c>
       <c r="O20" t="n">
-        <v>445</v>
+        <v>5844.04</v>
       </c>
       <c r="P20" t="n">
-        <v>4.4905125</v>
+        <v>23.4605</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4905125</v>
+        <v>23.4605</v>
       </c>
       <c r="R20" t="n">
-        <v>449.05125</v>
+        <v>4692.1</v>
       </c>
       <c r="S20" t="n">
-        <v>-4.05125</v>
+        <v>1151.94</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2080,7 +2090,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>445</v>
+        <v>5844.04</v>
       </c>
     </row>
     <row r="21">
@@ -2109,19 +2119,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>QQQ   261218P00560000</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 560 P</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>560</v>
+        <v>620</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2135,29 +2145,29 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>29.7208</v>
+        <v>25.245</v>
       </c>
       <c r="O21" t="n">
-        <v>5944.16</v>
+        <v>5049</v>
       </c>
       <c r="P21" t="n">
-        <v>23.4605</v>
+        <v>20.1374875</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.4605</v>
+        <v>20.1374875</v>
       </c>
       <c r="R21" t="n">
-        <v>4692.1</v>
+        <v>4027.4975</v>
       </c>
       <c r="S21" t="n">
-        <v>1252.06</v>
+        <v>1021.5025</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2170,7 +2180,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>5944.16</v>
+        <v>5049</v>
       </c>
     </row>
     <row r="22">
@@ -2199,23 +2209,23 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SPY   261218P00620000</t>
+          <t>AAPL  260327P00250000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 620 P</t>
+          <t>AAPL 27MAR26 250 P</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>620</v>
+        <v>250</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2225,33 +2235,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="N22" t="n">
-        <v>25.84</v>
+        <v>2.53</v>
       </c>
       <c r="O22" t="n">
-        <v>5168</v>
+        <v>-253</v>
       </c>
       <c r="P22" t="n">
-        <v>20.1374875</v>
+        <v>1.7494546</v>
       </c>
       <c r="Q22" t="n">
-        <v>20.1374875</v>
+        <v>1.7494546</v>
       </c>
       <c r="R22" t="n">
-        <v>4027.4975</v>
+        <v>-174.94546</v>
       </c>
       <c r="S22" t="n">
-        <v>1140.5025</v>
+        <v>-78.05454</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2260,7 +2270,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5168</v>
+        <v>-253</v>
       </c>
     </row>
     <row r="23">
@@ -2284,24 +2294,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AAPL  260327P00250000</t>
+          <t>AAPL  260327C00285000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 250 P</t>
+          <t>AAPL 27MAR26 285 C</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2310,34 +2320,34 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.85</v>
+        <v>0.215</v>
       </c>
       <c r="O23" t="n">
-        <v>-285</v>
+        <v>-21.5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7494546</v>
+        <v>3.2494546</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.7494546</v>
+        <v>3.2494546</v>
       </c>
       <c r="R23" t="n">
-        <v>-174.94546</v>
+        <v>-324.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>-110.05454</v>
+        <v>303.44546</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2350,7 +2360,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-285</v>
+        <v>-21.5</v>
       </c>
     </row>
     <row r="24">
@@ -2374,24 +2384,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AAPL  260327C00285000</t>
+          <t>AMD   260327P00185000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 285 C</t>
+          <t>AMD 27MAR26 185 P</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2400,34 +2410,34 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.27</v>
+        <v>3.314</v>
       </c>
       <c r="O24" t="n">
-        <v>-27</v>
+        <v>-331.4</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2494546</v>
+        <v>7.5800876</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2494546</v>
+        <v>7.5800876</v>
       </c>
       <c r="R24" t="n">
-        <v>-324.94546</v>
+        <v>-758.0087600000001</v>
       </c>
       <c r="S24" t="n">
-        <v>297.94546</v>
+        <v>426.60876</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2440,7 +2450,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-27</v>
+        <v>-331.4</v>
       </c>
     </row>
     <row r="25">
@@ -2469,19 +2479,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AMD   260327P00185000</t>
+          <t>AMZN  260327P00190000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 185 P</t>
+          <t>AMZN 27MAR26 190 P</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2495,29 +2505,29 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.875</v>
+        <v>0.9527</v>
       </c>
       <c r="O25" t="n">
-        <v>-387.5</v>
+        <v>-95.27</v>
       </c>
       <c r="P25" t="n">
-        <v>7.5800876</v>
+        <v>1.8142796</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.5800876</v>
+        <v>1.8142796</v>
       </c>
       <c r="R25" t="n">
-        <v>-758.0087600000001</v>
+        <v>-181.42796</v>
       </c>
       <c r="S25" t="n">
-        <v>370.50876</v>
+        <v>86.15796</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2530,7 +2540,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-387.5</v>
+        <v>-95.27</v>
       </c>
     </row>
     <row r="26">
@@ -2554,24 +2564,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AMZN  260327P00190000</t>
+          <t>AMZN  260327C00235000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 190 P</t>
+          <t>AMZN 27MAR26 235 C</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2580,34 +2590,34 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.08</v>
+        <v>0.32</v>
       </c>
       <c r="O26" t="n">
-        <v>-108</v>
+        <v>-32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.8142796</v>
+        <v>1.0242796</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.8142796</v>
+        <v>1.0242796</v>
       </c>
       <c r="R26" t="n">
-        <v>-181.42796</v>
+        <v>-102.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>73.42796</v>
+        <v>70.42796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2620,7 +2630,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-108</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="27">
@@ -2644,24 +2654,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AMZN  260327C00235000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 235 C</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2670,34 +2680,34 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.46</v>
+        <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>-46</v>
+        <v>-670</v>
       </c>
       <c r="P27" t="n">
-        <v>1.0242796</v>
+        <v>6.6394751</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.0242796</v>
+        <v>6.6394751</v>
       </c>
       <c r="R27" t="n">
-        <v>-102.42796</v>
+        <v>-1327.89502</v>
       </c>
       <c r="S27" t="n">
-        <v>56.42796</v>
+        <v>657.89502</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2710,7 +2720,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-46</v>
+        <v>-670</v>
       </c>
     </row>
     <row r="28">
@@ -2734,24 +2744,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00295000</t>
+          <t>GOOGL 260327C00315000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 295 P</t>
+          <t>GOOGL 27MAR26 315 C</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2760,34 +2770,34 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1785</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
-        <v>-835.7</v>
+        <v>-520</v>
       </c>
       <c r="P28" t="n">
-        <v>6.6394751</v>
+        <v>6.7894876</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.6394751</v>
+        <v>6.7894876</v>
       </c>
       <c r="R28" t="n">
-        <v>-1327.89502</v>
+        <v>-678.94876</v>
       </c>
       <c r="S28" t="n">
-        <v>492.19502</v>
+        <v>158.94876</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2800,7 +2810,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-835.7</v>
+        <v>-520</v>
       </c>
     </row>
     <row r="29">
@@ -2824,24 +2834,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GOOGL 260327C00315000</t>
+          <t>MSFT  260327P00360000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 315 C</t>
+          <t>MSFT 27MAR26 360 P</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2850,34 +2860,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>5.1442</v>
+        <v>0.89</v>
       </c>
       <c r="O29" t="n">
-        <v>-514.42</v>
+        <v>-89</v>
       </c>
       <c r="P29" t="n">
-        <v>6.7894876</v>
+        <v>2.1194546</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.7894876</v>
+        <v>2.1194546</v>
       </c>
       <c r="R29" t="n">
-        <v>-678.94876</v>
+        <v>-211.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>164.52876</v>
+        <v>122.94546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2890,7 +2900,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-514.42</v>
+        <v>-89</v>
       </c>
     </row>
     <row r="30">
@@ -2914,24 +2924,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MSFT  260327P00360000</t>
+          <t>MSFT  260327C00415000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 360 P</t>
+          <t>MSFT 27MAR26 415 C</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2940,34 +2950,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.19</v>
+        <v>4.9</v>
       </c>
       <c r="O30" t="n">
-        <v>-119</v>
+        <v>-490</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1194546</v>
+        <v>5.7894546</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.1194546</v>
+        <v>5.7894546</v>
       </c>
       <c r="R30" t="n">
-        <v>-211.94546</v>
+        <v>-578.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>92.94546</v>
+        <v>88.94546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2980,7 +2990,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-119</v>
+        <v>-490</v>
       </c>
     </row>
     <row r="31">
@@ -3004,24 +3014,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MSFT  260327C00415000</t>
+          <t>NFLX  260327P00088000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 415 C</t>
+          <t>NFLX 27MAR26 88 P</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>415</v>
+        <v>88</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3030,34 +3040,34 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N31" t="n">
-        <v>6.275</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>-627.5</v>
+        <v>-138</v>
       </c>
       <c r="P31" t="n">
-        <v>5.7894546</v>
+        <v>0.9454876</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.7894546</v>
+        <v>0.9454876</v>
       </c>
       <c r="R31" t="n">
-        <v>-578.94546</v>
+        <v>-189.09752</v>
       </c>
       <c r="S31" t="n">
-        <v>-48.55454</v>
+        <v>51.09752</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3070,7 +3080,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-627.5</v>
+        <v>-138</v>
       </c>
     </row>
     <row r="32">
@@ -3099,23 +3109,23 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NFLX  260327P00088000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 88 P</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>88</v>
+        <v>425</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3125,29 +3135,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>0.615</v>
+        <v>8.1219</v>
       </c>
       <c r="O32" t="n">
-        <v>-123</v>
+        <v>-1624.38</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9454876</v>
+        <v>6.3644671</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9454876</v>
+        <v>6.3644671</v>
       </c>
       <c r="R32" t="n">
-        <v>-189.09752</v>
+        <v>-1272.89342</v>
       </c>
       <c r="S32" t="n">
-        <v>66.09752</v>
+        <v>-351.48658</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3160,7 +3170,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-123</v>
+        <v>-1624.38</v>
       </c>
     </row>
     <row r="33">
@@ -3189,19 +3199,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>SPY   261218P00505000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>SPY 18DEC26 505 P</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>425</v>
+        <v>505</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3215,29 +3225,29 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>8.4092</v>
+        <v>9.19</v>
       </c>
       <c r="O33" t="n">
-        <v>-1681.84</v>
+        <v>-1838</v>
       </c>
       <c r="P33" t="n">
-        <v>6.3644671</v>
+        <v>7.3548796</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.3644671</v>
+        <v>7.3548796</v>
       </c>
       <c r="R33" t="n">
-        <v>-1272.89342</v>
+        <v>-1470.97592</v>
       </c>
       <c r="S33" t="n">
-        <v>-408.94658</v>
+        <v>-367.02408</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3250,97 +3260,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1681.84</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" t="n">
-        <v>505</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>9.635</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-1927</v>
-      </c>
-      <c r="P34" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="R34" t="n">
-        <v>-1470.97592</v>
-      </c>
-      <c r="S34" t="n">
-        <v>-456.02408</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>-1927</v>
+        <v>-1838</v>
       </c>
     </row>
   </sheetData>
@@ -3354,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3481,7 +3401,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2844</v>
+        <v>1.2811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3511,17 +3431,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>401.35</v>
+        <v>398.6</v>
       </c>
       <c r="O2" t="n">
-        <v>20067.5</v>
+        <v>19930</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3533,7 +3453,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-915.456235</v>
+        <v>-1052.956235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3546,7 +3466,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25774.697</v>
+        <v>25532.323</v>
       </c>
     </row>
     <row r="3">
@@ -3561,7 +3481,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2844</v>
+        <v>1.2811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3575,12 +3495,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WORLD</t>
+          <t>XMME</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UBS ETF W UCITS HCHF ACC</t>
+          <t>X MSCI EM 1C</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3591,29 +3511,29 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>5000</v>
+        <v>350</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5075</v>
+        <v>63.2</v>
       </c>
       <c r="O3" t="n">
-        <v>17537.5</v>
+        <v>22120</v>
       </c>
       <c r="P3" t="n">
-        <v>3.57250536</v>
+        <v>65.60009794299999</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.57250536</v>
+        <v>65.60009794299999</v>
       </c>
       <c r="R3" t="n">
-        <v>17862.5268</v>
+        <v>22960.03428</v>
       </c>
       <c r="S3" t="n">
-        <v>-325.0268</v>
+        <v>-840.03428</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3626,7 +3546,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>22525.165</v>
+        <v>28337.932</v>
       </c>
     </row>
     <row r="4">
@@ -3637,11 +3557,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2844</v>
+        <v>0.14542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3655,12 +3575,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>XMME</t>
+          <t>82846</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>X MSCI EM 1C</t>
+          <t>ISHARES CORE CSI 300 ETF</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3671,29 +3591,29 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>350</v>
+        <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>63.72</v>
+        <v>31.56</v>
       </c>
       <c r="O4" t="n">
-        <v>22302</v>
+        <v>63120</v>
       </c>
       <c r="P4" t="n">
-        <v>65.60009794299999</v>
+        <v>31.696238595</v>
       </c>
       <c r="Q4" t="n">
-        <v>65.60009794299999</v>
+        <v>31.696238595</v>
       </c>
       <c r="R4" t="n">
-        <v>22960.03428</v>
+        <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-658.03428</v>
+        <v>-272.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3702,11 +3622,11 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>SEHK</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>28644.6888</v>
+        <v>9178.910399999999</v>
       </c>
     </row>
     <row r="5">
@@ -3717,11 +3637,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.14534</v>
+        <v>1.1567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3735,12 +3655,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>82846</t>
+          <t>CBUK</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ISHARES CORE CSI 300 ETF</t>
+          <t>ISHARES CHINA TECH USD ACC</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3751,29 +3671,29 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>31.42</v>
+        <v>4.3175</v>
       </c>
       <c r="O5" t="n">
-        <v>62840</v>
+        <v>12952.5</v>
       </c>
       <c r="P5" t="n">
-        <v>31.696238595</v>
+        <v>4.65841303</v>
       </c>
       <c r="Q5" t="n">
-        <v>31.696238595</v>
+        <v>4.65841303</v>
       </c>
       <c r="R5" t="n">
-        <v>63392.47719</v>
+        <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-552.47719</v>
+        <v>-1022.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3782,11 +3702,11 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SEHK</t>
+          <t>IBIS2</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9133.1656</v>
+        <v>14982.15675</v>
       </c>
     </row>
     <row r="6">
@@ -3801,7 +3721,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.161</v>
+        <v>1.1567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3810,17 +3730,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CBUK</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ISHARES CHINA TECH USD ACC</t>
+          <t>DHL GROUP</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3831,29 +3751,29 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3585</v>
+        <v>46.28</v>
       </c>
       <c r="O6" t="n">
-        <v>13075.5</v>
+        <v>46280</v>
       </c>
       <c r="P6" t="n">
-        <v>4.65841303</v>
+        <v>43.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.65841303</v>
+        <v>43.01</v>
       </c>
       <c r="R6" t="n">
-        <v>13975.239091</v>
+        <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>-899.739091</v>
+        <v>3270</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3862,11 +3782,11 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>IBIS2</t>
+          <t>IBIS</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>15180.6555</v>
+        <v>53532.076</v>
       </c>
     </row>
     <row r="7">
@@ -3881,7 +3801,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.161</v>
+        <v>1.1567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3890,17 +3810,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>GDR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>HY9H</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DHL GROUP</t>
+          <t>SK HYNIX INC-GDS</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3911,29 +3831,29 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>46.77</v>
+        <v>564</v>
       </c>
       <c r="O7" t="n">
-        <v>46770</v>
+        <v>8460</v>
       </c>
       <c r="P7" t="n">
-        <v>43.01</v>
+        <v>556.278</v>
       </c>
       <c r="Q7" t="n">
-        <v>43.01</v>
+        <v>556.278</v>
       </c>
       <c r="R7" t="n">
-        <v>43010</v>
+        <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>3760</v>
+        <v>115.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3942,11 +3862,11 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>IBIS</t>
+          <t>FWB2</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>54299.97</v>
+        <v>9785.682000000001</v>
       </c>
     </row>
     <row r="8">
@@ -3957,11 +3877,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.161</v>
+        <v>0.78478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3970,17 +3890,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GDR</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HY9H</t>
+          <t>ES3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SK HYNIX INC-GDS</t>
+          <t>STATE STRT SPDR STRAITS TIME</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3991,29 +3911,29 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>15</v>
+        <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>560</v>
+        <v>4.85</v>
       </c>
       <c r="O8" t="n">
-        <v>8400</v>
+        <v>48500</v>
       </c>
       <c r="P8" t="n">
-        <v>556.278</v>
+        <v>3.72681816</v>
       </c>
       <c r="Q8" t="n">
-        <v>556.278</v>
+        <v>3.72681816</v>
       </c>
       <c r="R8" t="n">
-        <v>8344.17</v>
+        <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>55.83</v>
+        <v>11231.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4022,11 +3942,11 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>FWB2</t>
+          <t>SGX</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>9752.4</v>
+        <v>38061.83</v>
       </c>
     </row>
     <row r="9">
@@ -4041,7 +3961,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78537</v>
+        <v>0.78478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4055,12 +3975,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES3</t>
+          <t>GSD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>STATE STRT SPDR STRAITS TIME</t>
+          <t>SPDR GOLD SHARES</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -4071,29 +3991,29 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>10000</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.87</v>
+        <v>607</v>
       </c>
       <c r="O9" t="n">
-        <v>48700</v>
+        <v>45525</v>
       </c>
       <c r="P9" t="n">
-        <v>3.72681816</v>
+        <v>589.644672</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.72681816</v>
+        <v>589.644672</v>
       </c>
       <c r="R9" t="n">
-        <v>37268.1816</v>
+        <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>11431.8184</v>
+        <v>1301.6496</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4106,7 +4026,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>38247.519</v>
+        <v>35727.1095</v>
       </c>
     </row>
     <row r="10">
@@ -4117,11 +4037,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.78537</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4135,12 +4055,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GSD</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SPDR GOLD SHARES</t>
+          <t>GLOBAL X CHINA ROBOTICS</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -4151,29 +4071,29 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>75</v>
+        <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>606.7</v>
+        <v>7.985</v>
       </c>
       <c r="O10" t="n">
-        <v>45502.5</v>
+        <v>8783.5</v>
       </c>
       <c r="P10" t="n">
-        <v>589.644672</v>
+        <v>8.311679952</v>
       </c>
       <c r="Q10" t="n">
-        <v>589.644672</v>
+        <v>8.311679952</v>
       </c>
       <c r="R10" t="n">
-        <v>44223.3504</v>
+        <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>1279.1496</v>
+        <v>-359.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4182,11 +4102,11 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SGX</t>
+          <t>SEHK</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>35736.298425</v>
+        <v>8783.5</v>
       </c>
     </row>
     <row r="11">
@@ -4210,17 +4130,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GLOBAL X CHINA ROBOTICS</t>
+          <t>AGNICO EAGLE MINES LTD</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -4231,29 +4151,29 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1100</v>
+        <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>222.81</v>
       </c>
       <c r="O11" t="n">
-        <v>8800</v>
+        <v>6684.3</v>
       </c>
       <c r="P11" t="n">
-        <v>8.311679952</v>
+        <v>217.973333333</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.311679952</v>
+        <v>217.973333333</v>
       </c>
       <c r="R11" t="n">
-        <v>9142.847947</v>
+        <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-342.847947</v>
+        <v>145.1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4262,11 +4182,11 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SEHK</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>8800</v>
+        <v>6684.3</v>
       </c>
     </row>
     <row r="12">
@@ -4290,17 +4210,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>BITO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AGNICO EAGLE MINES LTD</t>
+          <t>PROSHARES BITCOIN ETF-USD</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -4311,29 +4231,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>226.94</v>
+        <v>9.73</v>
       </c>
       <c r="O12" t="n">
-        <v>6808.2</v>
+        <v>2919</v>
       </c>
       <c r="P12" t="n">
-        <v>217.973333333</v>
+        <v>11.661666667</v>
       </c>
       <c r="Q12" t="n">
-        <v>217.973333333</v>
+        <v>11.661666667</v>
       </c>
       <c r="R12" t="n">
-        <v>6539.2</v>
+        <v>3498.5</v>
       </c>
       <c r="S12" t="n">
-        <v>269</v>
+        <v>-579.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4342,11 +4262,11 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>6808.2</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="13">
@@ -4370,17 +4290,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BITO</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PROSHARES BITCOIN ETF-USD</t>
+          <t>ALPHABET INC-CL A</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -4391,29 +4311,29 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>9.65</v>
+        <v>308.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2895</v>
+        <v>30870</v>
       </c>
       <c r="P13" t="n">
-        <v>11.661666667</v>
+        <v>331.87755</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.661666667</v>
+        <v>331.87755</v>
       </c>
       <c r="R13" t="n">
-        <v>3498.5</v>
+        <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-603.5</v>
+        <v>-2317.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4422,11 +4342,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>2895</v>
+        <v>30870</v>
       </c>
     </row>
     <row r="14">
@@ -4455,12 +4375,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CSNDX</t>
+          <t>GRDU</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ISHARES NASDAQ 100 USD ACC</t>
+          <t>FT NSDQ CLN EDG SMRT GRID</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -4471,29 +4391,29 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>1443.4</v>
+        <v>58.27</v>
       </c>
       <c r="O14" t="n">
-        <v>21651</v>
+        <v>9323.200000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1471.727366667</v>
+        <v>60.20275</v>
       </c>
       <c r="Q14" t="n">
-        <v>1471.727366667</v>
+        <v>60.20275</v>
       </c>
       <c r="R14" t="n">
-        <v>22075.9105</v>
+        <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-424.9105</v>
+        <v>-309.24</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4502,11 +4422,11 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>21651</v>
+        <v>9323.200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4535,12 +4455,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ALPHABET INC-CL A</t>
+          <t>INTERACTIVE BROKERS GRO-CL A</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -4551,29 +4471,29 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>307.04</v>
+        <v>68.39</v>
       </c>
       <c r="O15" t="n">
-        <v>30704</v>
+        <v>1152.02</v>
       </c>
       <c r="P15" t="n">
-        <v>331.87755</v>
+        <v>20.721325216</v>
       </c>
       <c r="Q15" t="n">
-        <v>331.87755</v>
+        <v>20.721325216</v>
       </c>
       <c r="R15" t="n">
-        <v>33187.755</v>
+        <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>-2483.755</v>
+        <v>802.973421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4586,7 +4506,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>30704</v>
+        <v>1152.02</v>
       </c>
     </row>
     <row r="16">
@@ -4615,12 +4535,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GRDU</t>
+          <t>INRA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FT NSDQ CLN EDG SMRT GRID</t>
+          <t>ISHAR GL CL EN TR UCI ETF-US</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -4631,29 +4551,29 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>160</v>
+        <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>58.645</v>
+        <v>27.3423</v>
       </c>
       <c r="O16" t="n">
-        <v>9383.200000000001</v>
+        <v>10526.79</v>
       </c>
       <c r="P16" t="n">
-        <v>60.20275</v>
+        <v>25.997158151</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.20275</v>
+        <v>25.997158151</v>
       </c>
       <c r="R16" t="n">
-        <v>9632.440000000001</v>
+        <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>-249.24</v>
+        <v>517.884112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4662,11 +4582,11 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>AEB</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>9383.200000000001</v>
+        <v>10526.79</v>
       </c>
     </row>
     <row r="17">
@@ -4695,12 +4615,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>INTERACTIVE BROKERS GRO-CL A</t>
+          <t>JPMORGAN CHASE &amp; CO</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -4711,29 +4631,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>16.8448</v>
+        <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>68.5</v>
+        <v>287.52</v>
       </c>
       <c r="O17" t="n">
-        <v>1153.87</v>
+        <v>28752</v>
       </c>
       <c r="P17" t="n">
-        <v>20.721325216</v>
+        <v>298.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.721325216</v>
+        <v>298.02</v>
       </c>
       <c r="R17" t="n">
-        <v>349.046579</v>
+        <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>804.8234210000001</v>
+        <v>-1050</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4742,11 +4662,11 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1153.87</v>
+        <v>28752</v>
       </c>
     </row>
     <row r="18">
@@ -4775,12 +4695,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>INRA</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ISHAR GL CL EN TR UCI ETF-US</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4791,29 +4711,29 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>385</v>
+        <v>600</v>
       </c>
       <c r="N18" t="n">
-        <v>27.0491</v>
+        <v>171.26</v>
       </c>
       <c r="O18" t="n">
-        <v>10413.9</v>
+        <v>102756</v>
       </c>
       <c r="P18" t="n">
-        <v>25.997158151</v>
+        <v>173.846763275</v>
       </c>
       <c r="Q18" t="n">
-        <v>25.997158151</v>
+        <v>173.846763275</v>
       </c>
       <c r="R18" t="n">
-        <v>10008.905888</v>
+        <v>104308.057965</v>
       </c>
       <c r="S18" t="n">
-        <v>404.994112</v>
+        <v>-1552.057965</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4822,11 +4742,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>AEB</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>10413.9</v>
+        <v>102756</v>
       </c>
     </row>
     <row r="19">
@@ -4845,55 +4765,65 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AAPL  260327C00290000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>JPMORGAN CHASE &amp; CO</t>
+          <t>AAPL 27MAR26 290 C</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>290</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>288.73</v>
+        <v>0.125</v>
       </c>
       <c r="O19" t="n">
-        <v>28873</v>
+        <v>12.5</v>
       </c>
       <c r="P19" t="n">
-        <v>298.02</v>
+        <v>2.1405125</v>
       </c>
       <c r="Q19" t="n">
-        <v>298.02</v>
+        <v>2.1405125</v>
       </c>
       <c r="R19" t="n">
-        <v>29802</v>
+        <v>214.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-929</v>
+        <v>-201.55125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4902,11 +4832,11 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>28873</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="20">
@@ -4925,55 +4855,65 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>NFLX  260327C00085000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>NFLX 27MAR26 85 C</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I20" t="n">
+        <v>85</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>173.04</v>
+        <v>10.4728</v>
       </c>
       <c r="O20" t="n">
-        <v>103824</v>
+        <v>1047.28</v>
       </c>
       <c r="P20" t="n">
-        <v>173.846763275</v>
+        <v>2.5205125</v>
       </c>
       <c r="Q20" t="n">
-        <v>173.846763275</v>
+        <v>2.5205125</v>
       </c>
       <c r="R20" t="n">
-        <v>104308.057965</v>
+        <v>252.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-484.057965</v>
+        <v>795.22875</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -4982,11 +4922,11 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>103824</v>
+        <v>1047.28</v>
       </c>
     </row>
     <row r="21">
@@ -5010,60 +4950,60 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AAPL  260327C00290000</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 290 C</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>290</v>
+        <v>560</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.17</v>
+        <v>29.2202</v>
       </c>
       <c r="O21" t="n">
-        <v>17</v>
+        <v>5844.04</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1405125</v>
+        <v>23.5270125</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1405125</v>
+        <v>23.5270125</v>
       </c>
       <c r="R21" t="n">
-        <v>214.05125</v>
+        <v>4705.4025</v>
       </c>
       <c r="S21" t="n">
-        <v>-197.05125</v>
+        <v>1138.6375</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5076,7 +5016,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>17</v>
+        <v>5844.04</v>
       </c>
     </row>
     <row r="22">
@@ -5100,60 +5040,60 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NFLX  260327C00085000</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 85 C</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>85</v>
+        <v>620</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>12.4467</v>
+        <v>25.245</v>
       </c>
       <c r="O22" t="n">
-        <v>1244.67</v>
+        <v>5049</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5205125</v>
+        <v>20.1350875</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5205125</v>
+        <v>20.1350875</v>
       </c>
       <c r="R22" t="n">
-        <v>252.05125</v>
+        <v>4027.0175</v>
       </c>
       <c r="S22" t="n">
-        <v>992.61875</v>
+        <v>1021.9825</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5166,7 +5106,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>1244.67</v>
+        <v>5049</v>
       </c>
     </row>
     <row r="23">
@@ -5195,23 +5135,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>QQQ   261218P00560000</t>
+          <t>AAPL  260327P00250000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 560 P</t>
+          <t>AAPL 27MAR26 250 P</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>560</v>
+        <v>250</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -5221,33 +5161,33 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>29.7208</v>
+        <v>2.53</v>
       </c>
       <c r="O23" t="n">
-        <v>5944.16</v>
+        <v>-253</v>
       </c>
       <c r="P23" t="n">
-        <v>23.5270125</v>
+        <v>1.7694546</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.5270125</v>
+        <v>1.7694546</v>
       </c>
       <c r="R23" t="n">
-        <v>4705.4025</v>
+        <v>-176.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>1238.7575</v>
+        <v>-76.05454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -5256,7 +5196,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5944.16</v>
+        <v>-253</v>
       </c>
     </row>
     <row r="24">
@@ -5280,64 +5220,64 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SPY   261218P00620000</t>
+          <t>AAPL  260327C00285000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 620 P</t>
+          <t>AAPL 27MAR26 285 C</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>620</v>
+        <v>285</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>25.84</v>
+        <v>0.215</v>
       </c>
       <c r="O24" t="n">
-        <v>5168</v>
+        <v>-21.5</v>
       </c>
       <c r="P24" t="n">
-        <v>20.1350875</v>
+        <v>3.4194546</v>
       </c>
       <c r="Q24" t="n">
-        <v>20.1350875</v>
+        <v>3.4194546</v>
       </c>
       <c r="R24" t="n">
-        <v>4027.0175</v>
+        <v>-341.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>1140.9825</v>
+        <v>320.44546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -5346,7 +5286,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>5168</v>
+        <v>-21.5</v>
       </c>
     </row>
     <row r="25">
@@ -5375,19 +5315,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AAPL  260327P00250000</t>
+          <t>AMD   260327P00185000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 250 P</t>
+          <t>AMD 27MAR26 185 P</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -5401,29 +5341,29 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.85</v>
+        <v>3.314</v>
       </c>
       <c r="O25" t="n">
-        <v>-285</v>
+        <v>-331.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7694546</v>
+        <v>4.1794546</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.7694546</v>
+        <v>4.1794546</v>
       </c>
       <c r="R25" t="n">
-        <v>-176.94546</v>
+        <v>-417.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>-108.05454</v>
+        <v>86.54546000000001</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5436,7 +5376,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-285</v>
+        <v>-331.4</v>
       </c>
     </row>
     <row r="26">
@@ -5465,19 +5405,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AAPL  260327C00285000</t>
+          <t>AMD   260327C00255000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 285 C</t>
+          <t>AMD 27MAR26 255 C</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -5491,29 +5431,29 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.27</v>
+        <v>0.235</v>
       </c>
       <c r="O26" t="n">
-        <v>-27</v>
+        <v>-23.5</v>
       </c>
       <c r="P26" t="n">
-        <v>3.4194546</v>
+        <v>2.3694546</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4194546</v>
+        <v>2.3694546</v>
       </c>
       <c r="R26" t="n">
-        <v>-341.94546</v>
+        <v>-236.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>314.94546</v>
+        <v>213.44546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5526,7 +5466,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-27</v>
+        <v>-23.5</v>
       </c>
     </row>
     <row r="27">
@@ -5555,19 +5495,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AMD   260327P00185000</t>
+          <t>AMZN  260327P00190000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 185 P</t>
+          <t>AMZN 27MAR26 190 P</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5581,29 +5521,29 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.875</v>
+        <v>0.9527</v>
       </c>
       <c r="O27" t="n">
-        <v>-387.5</v>
+        <v>-95.27</v>
       </c>
       <c r="P27" t="n">
-        <v>4.1794546</v>
+        <v>1.7994546</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.1794546</v>
+        <v>1.7994546</v>
       </c>
       <c r="R27" t="n">
-        <v>-417.94546</v>
+        <v>-179.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>30.44546</v>
+        <v>84.67546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5616,7 +5556,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-387.5</v>
+        <v>-95.27</v>
       </c>
     </row>
     <row r="28">
@@ -5640,24 +5580,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AMD   260327C00255000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 255 C</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -5666,34 +5606,34 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.265</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>-26.5</v>
+        <v>-335</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3694546</v>
+        <v>5.9694626</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3694546</v>
+        <v>5.9694626</v>
       </c>
       <c r="R28" t="n">
-        <v>-236.94546</v>
+        <v>-596.9462600000001</v>
       </c>
       <c r="S28" t="n">
-        <v>210.44546</v>
+        <v>261.94626</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5706,7 +5646,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-26.5</v>
+        <v>-335</v>
       </c>
     </row>
     <row r="29">
@@ -5730,24 +5670,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AMZN  260327P00190000</t>
+          <t>GOOGL 260327C00315000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 190 P</t>
+          <t>GOOGL 27MAR26 315 C</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -5756,34 +5696,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.08</v>
+        <v>5.2</v>
       </c>
       <c r="O29" t="n">
-        <v>-108</v>
+        <v>-520</v>
       </c>
       <c r="P29" t="n">
-        <v>1.7994546</v>
+        <v>3.2300876</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.7994546</v>
+        <v>3.2300876</v>
       </c>
       <c r="R29" t="n">
-        <v>-179.94546</v>
+        <v>-323.00876</v>
       </c>
       <c r="S29" t="n">
-        <v>71.94546</v>
+        <v>-196.99124</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5796,7 +5736,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-108</v>
+        <v>-520</v>
       </c>
     </row>
     <row r="30">
@@ -5820,24 +5760,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00295000</t>
+          <t>JPM   260327C00297500</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 295 P</t>
+          <t>JPM 27MAR26 297.5 C</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>295</v>
+        <v>297.5</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -5846,34 +5786,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1785</v>
+        <v>3.566</v>
       </c>
       <c r="O30" t="n">
-        <v>-417.85</v>
+        <v>-356.6</v>
       </c>
       <c r="P30" t="n">
-        <v>5.9694626</v>
+        <v>4.8394876</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.9694626</v>
+        <v>4.8394876</v>
       </c>
       <c r="R30" t="n">
-        <v>-596.9462600000001</v>
+        <v>-483.94876</v>
       </c>
       <c r="S30" t="n">
-        <v>179.09626</v>
+        <v>127.34876</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5886,7 +5826,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-417.85</v>
+        <v>-356.6</v>
       </c>
     </row>
     <row r="31">
@@ -5910,24 +5850,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GOOGL 260327C00315000</t>
+          <t>MSFT  260327P00360000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 315 C</t>
+          <t>MSFT 27MAR26 360 P</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -5936,34 +5876,34 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>5.1442</v>
+        <v>0.89</v>
       </c>
       <c r="O31" t="n">
-        <v>-514.42</v>
+        <v>-89</v>
       </c>
       <c r="P31" t="n">
-        <v>3.2300876</v>
+        <v>2.1094546</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2300876</v>
+        <v>2.1094546</v>
       </c>
       <c r="R31" t="n">
-        <v>-323.00876</v>
+        <v>-210.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>-191.41124</v>
+        <v>121.94546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -5976,7 +5916,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-514.42</v>
+        <v>-89</v>
       </c>
     </row>
     <row r="32">
@@ -6000,24 +5940,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JPM   260327C00297500</t>
+          <t>NFLX  260327P00072000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>JPM 27MAR26 297.5 C</t>
+          <t>NFLX 27MAR26 72 P</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>297.5</v>
+        <v>72</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -6026,34 +5966,34 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>4.1596</v>
+        <v>0.0529</v>
       </c>
       <c r="O32" t="n">
-        <v>-415.96</v>
+        <v>-5.29</v>
       </c>
       <c r="P32" t="n">
-        <v>4.8394876</v>
+        <v>0.8794546</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.8394876</v>
+        <v>0.8794546</v>
       </c>
       <c r="R32" t="n">
-        <v>-483.94876</v>
+        <v>-87.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>67.98876</v>
+        <v>82.65546000000001</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6066,7 +6006,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-415.96</v>
+        <v>-5.29</v>
       </c>
     </row>
     <row r="33">
@@ -6090,24 +6030,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MSFT  260327P00360000</t>
+          <t>NFLX  260327C00083000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 360 P</t>
+          <t>NFLX 27MAR26 83 C</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>360</v>
+        <v>83</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -6116,34 +6056,34 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>1.19</v>
+        <v>12.355</v>
       </c>
       <c r="O33" t="n">
-        <v>-119</v>
+        <v>-1235.5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1094546</v>
+        <v>3.2794546</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.1094546</v>
+        <v>3.2794546</v>
       </c>
       <c r="R33" t="n">
-        <v>-210.94546</v>
+        <v>-327.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>91.94546</v>
+        <v>-907.55454</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6156,7 +6096,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-119</v>
+        <v>-1235.5</v>
       </c>
     </row>
     <row r="34">
@@ -6185,23 +6125,23 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NFLX  260327P00072000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 72 P</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>72</v>
+        <v>425</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -6211,29 +6151,29 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0636</v>
+        <v>8.1219</v>
       </c>
       <c r="O34" t="n">
-        <v>-6.36</v>
+        <v>-1624.38</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8794546</v>
+        <v>6.3929546</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8794546</v>
+        <v>6.3929546</v>
       </c>
       <c r="R34" t="n">
-        <v>-87.94546</v>
+        <v>-1278.59092</v>
       </c>
       <c r="S34" t="n">
-        <v>81.58546</v>
+        <v>-345.78908</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6246,7 +6186,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-6.36</v>
+        <v>-1624.38</v>
       </c>
     </row>
     <row r="35">
@@ -6270,60 +6210,60 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NFLX  260327C00083000</t>
+          <t>SPY   261218P00505000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 83 C</t>
+          <t>SPY 18DEC26 505 P</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>83</v>
+        <v>505</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>14.3393</v>
+        <v>9.19</v>
       </c>
       <c r="O35" t="n">
-        <v>-1433.93</v>
+        <v>-1838</v>
       </c>
       <c r="P35" t="n">
-        <v>3.2794546</v>
+        <v>7.3496796</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2794546</v>
+        <v>7.3496796</v>
       </c>
       <c r="R35" t="n">
-        <v>-327.94546</v>
+        <v>-1469.93592</v>
       </c>
       <c r="S35" t="n">
-        <v>-1105.98454</v>
+        <v>-368.06408</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6336,187 +6276,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-1433.93</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>QQQ   261218P00425000</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>QQQ 18DEC26 425 P</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" t="n">
-        <v>425</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N36" t="n">
-        <v>8.4092</v>
-      </c>
-      <c r="O36" t="n">
-        <v>-1681.84</v>
-      </c>
-      <c r="P36" t="n">
-        <v>6.3929546</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6.3929546</v>
-      </c>
-      <c r="R36" t="n">
-        <v>-1278.59092</v>
-      </c>
-      <c r="S36" t="n">
-        <v>-403.24908</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>-1681.84</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" t="n">
-        <v>505</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N37" t="n">
-        <v>9.635</v>
-      </c>
-      <c r="O37" t="n">
-        <v>-1927</v>
-      </c>
-      <c r="P37" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="R37" t="n">
-        <v>-1469.93592</v>
-      </c>
-      <c r="S37" t="n">
-        <v>-457.06408</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>-1927</v>
+        <v>-1838</v>
       </c>
     </row>
   </sheetData>
@@ -6563,17 +6323,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$325,349.05</t>
+          <t>$310,683.54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$111,582.72</t>
+          <t>$125,785.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$436,931.77</t>
+          <t>$436,468.57</t>
         </is>
       </c>
     </row>
@@ -6585,17 +6345,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$468,824.20</t>
+          <t>$422,129.21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$82,198.68</t>
+          <t>$125,869.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$551,022.88</t>
+          <t>$547,998.36</t>
         </is>
       </c>
     </row>
@@ -6613,17 +6373,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$794,173.25</t>
+          <t>$732,812.75</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$193,781.40</t>
+          <t>$251,654.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$987,954.65</t>
+          <t>$984,466.93</t>
         </is>
       </c>
     </row>
@@ -6671,14 +6431,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-11 23:42:03</t>
+          <t>2026-03-12 23:42:32</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2811</v>
+        <v>1.2721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>398.6</v>
+        <v>393.55</v>
       </c>
       <c r="O2" t="n">
-        <v>15944</v>
+        <v>15742</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-764.503607</v>
+        <v>-966.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20425.8584</v>
+        <v>20025.3982</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2811</v>
+        <v>1.2721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>63.2</v>
+        <v>62.01</v>
       </c>
       <c r="O3" t="n">
-        <v>15800</v>
+        <v>15502.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-508.353333</v>
+        <v>-805.853333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>20241.38</v>
+        <v>19720.73025</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14542</v>
+        <v>0.14531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.56</v>
+        <v>31.48</v>
       </c>
       <c r="O4" t="n">
-        <v>94680</v>
+        <v>94440</v>
       </c>
       <c r="P4" t="n">
         <v>31.36596519</v>
@@ -767,7 +767,7 @@
         <v>94097.89556999999</v>
       </c>
       <c r="S4" t="n">
-        <v>582.10443</v>
+        <v>342.10443</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>13768.3656</v>
+        <v>13723.0764</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1567</v>
+        <v>1.1511</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3175</v>
+        <v>4.31</v>
       </c>
       <c r="O5" t="n">
-        <v>8635</v>
+        <v>8620</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-689.66</v>
+        <v>-704.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9988.104500000001</v>
+        <v>9922.482</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1567</v>
+        <v>1.1511</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>564</v>
+        <v>520</v>
       </c>
       <c r="O6" t="n">
-        <v>8460</v>
+        <v>7800</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>115.83</v>
+        <v>-544.17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9785.682000000001</v>
+        <v>8978.58</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78478</v>
+        <v>0.78183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30449.464</v>
+        <v>30335.004</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78478</v>
+        <v>0.78183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>607</v>
+        <v>606.9</v>
       </c>
       <c r="O8" t="n">
-        <v>45525</v>
+        <v>45517.5</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>1290.901008</v>
+        <v>1283.401008</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>35727.1095</v>
+        <v>35586.947025</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.985</v>
+        <v>7.85</v>
       </c>
       <c r="O9" t="n">
-        <v>7985</v>
+        <v>7850</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-326.237657</v>
+        <v>-461.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7985</v>
+        <v>7850</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>222.81</v>
+        <v>218.24</v>
       </c>
       <c r="O10" t="n">
-        <v>6684.3</v>
+        <v>6547.2</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>141.2</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6684.3</v>
+        <v>6547.2</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.73</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>308.7</v>
+        <v>303.55</v>
       </c>
       <c r="O12" t="n">
-        <v>30870</v>
+        <v>30355</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>706.5</v>
+        <v>191.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30870</v>
+        <v>30355</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>58.27</v>
+        <v>57.79</v>
       </c>
       <c r="O13" t="n">
-        <v>9323.200000000001</v>
+        <v>9246.4</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-253.46</v>
+        <v>-330.26</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9323.200000000001</v>
+        <v>9246.4</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>27.3423</v>
+        <v>27.2889</v>
       </c>
       <c r="O14" t="n">
-        <v>10526.79</v>
+        <v>10506.23</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>511.887178</v>
+        <v>491.327178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10526.79</v>
+        <v>10506.23</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>70</v>
       </c>
       <c r="N15" t="n">
-        <v>163.12</v>
+        <v>159.16</v>
       </c>
       <c r="O15" t="n">
-        <v>11418.4</v>
+        <v>11141.2</v>
       </c>
       <c r="P15" t="n">
         <v>204.330714286</v>
@@ -1647,7 +1647,7 @@
         <v>14303.15</v>
       </c>
       <c r="S15" t="n">
-        <v>-2884.75</v>
+        <v>-3161.95</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>11418.4</v>
+        <v>11141.2</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>87.81999999999999</v>
+        <v>85.16</v>
       </c>
       <c r="O16" t="n">
-        <v>1756.4</v>
+        <v>1703.2</v>
       </c>
       <c r="P16" t="n">
         <v>124.315</v>
@@ -1727,7 +1727,7 @@
         <v>2486.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-729.9</v>
+        <v>-783.1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1756.4</v>
+        <v>1703.2</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>500</v>
       </c>
       <c r="N17" t="n">
-        <v>171.26</v>
+        <v>169.36</v>
       </c>
       <c r="O17" t="n">
-        <v>85630</v>
+        <v>84680</v>
       </c>
       <c r="P17" t="n">
         <v>173.59385355</v>
@@ -1807,7 +1807,7 @@
         <v>86796.926775</v>
       </c>
       <c r="S17" t="n">
-        <v>-1166.926775</v>
+        <v>-2116.926775</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>85630</v>
+        <v>84680</v>
       </c>
     </row>
     <row r="18">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.125</v>
+        <v>0.0553</v>
       </c>
       <c r="O18" t="n">
-        <v>12.5</v>
+        <v>5.53</v>
       </c>
       <c r="P18" t="n">
         <v>2.0105125</v>
@@ -1897,7 +1897,7 @@
         <v>201.05125</v>
       </c>
       <c r="S18" t="n">
-        <v>-188.55125</v>
+        <v>-195.52125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>12.5</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="19">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.275</v>
+        <v>2.705</v>
       </c>
       <c r="O19" t="n">
-        <v>327.5</v>
+        <v>270.5</v>
       </c>
       <c r="P19" t="n">
         <v>4.4905125</v>
@@ -1987,7 +1987,7 @@
         <v>449.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-121.55125</v>
+        <v>-178.55125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>327.5</v>
+        <v>270.5</v>
       </c>
     </row>
     <row r="20">
@@ -2055,17 +2055,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>29.2202</v>
+        <v>32.8108</v>
       </c>
       <c r="O20" t="n">
-        <v>5844.04</v>
+        <v>6562.16</v>
       </c>
       <c r="P20" t="n">
         <v>23.4605</v>
@@ -2077,7 +2077,7 @@
         <v>4692.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1151.94</v>
+        <v>1870.06</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>5844.04</v>
+        <v>6562.16</v>
       </c>
     </row>
     <row r="21">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>25.245</v>
+        <v>28.645</v>
       </c>
       <c r="O21" t="n">
-        <v>5049</v>
+        <v>5729</v>
       </c>
       <c r="P21" t="n">
         <v>20.1374875</v>
@@ -2167,7 +2167,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S21" t="n">
-        <v>1021.5025</v>
+        <v>1701.5025</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>5049</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="22">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.53</v>
+        <v>3.875</v>
       </c>
       <c r="O22" t="n">
-        <v>-253</v>
+        <v>-387.5</v>
       </c>
       <c r="P22" t="n">
         <v>1.7494546</v>
@@ -2257,7 +2257,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S22" t="n">
-        <v>-78.05454</v>
+        <v>-212.55454</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-253</v>
+        <v>-387.5</v>
       </c>
     </row>
     <row r="23">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.215</v>
+        <v>0.1258</v>
       </c>
       <c r="O23" t="n">
-        <v>-21.5</v>
+        <v>-12.58</v>
       </c>
       <c r="P23" t="n">
         <v>3.2494546</v>
@@ -2347,7 +2347,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>303.44546</v>
+        <v>312.36546</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-21.5</v>
+        <v>-12.58</v>
       </c>
     </row>
     <row r="24">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.314</v>
+        <v>4.625</v>
       </c>
       <c r="O24" t="n">
-        <v>-331.4</v>
+        <v>-462.5</v>
       </c>
       <c r="P24" t="n">
         <v>7.5800876</v>
@@ -2437,7 +2437,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S24" t="n">
-        <v>426.60876</v>
+        <v>295.50876</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-331.4</v>
+        <v>-462.5</v>
       </c>
     </row>
     <row r="25">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9527</v>
+        <v>1.3651</v>
       </c>
       <c r="O25" t="n">
-        <v>-95.27</v>
+        <v>-136.51</v>
       </c>
       <c r="P25" t="n">
         <v>1.8142796</v>
@@ -2527,7 +2527,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S25" t="n">
-        <v>86.15796</v>
+        <v>44.91796</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-95.27</v>
+        <v>-136.51</v>
       </c>
     </row>
     <row r="26">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.32</v>
+        <v>0.225</v>
       </c>
       <c r="O26" t="n">
-        <v>-32</v>
+        <v>-22.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.0242796</v>
@@ -2617,7 +2617,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>70.42796</v>
+        <v>79.92796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-32</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="27">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.35</v>
+        <v>4.8593</v>
       </c>
       <c r="O27" t="n">
-        <v>-670</v>
+        <v>-971.86</v>
       </c>
       <c r="P27" t="n">
         <v>6.6394751</v>
@@ -2707,7 +2707,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S27" t="n">
-        <v>657.89502</v>
+        <v>356.03502</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-670</v>
+        <v>-971.86</v>
       </c>
     </row>
     <row r="28">
@@ -2775,17 +2775,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>3.375</v>
       </c>
       <c r="O28" t="n">
-        <v>-520</v>
+        <v>-337.5</v>
       </c>
       <c r="P28" t="n">
         <v>6.7894876</v>
@@ -2797,7 +2797,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S28" t="n">
-        <v>158.94876</v>
+        <v>341.44876</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-520</v>
+        <v>-337.5</v>
       </c>
     </row>
     <row r="29">
@@ -2865,17 +2865,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.89</v>
+        <v>1.055</v>
       </c>
       <c r="O29" t="n">
-        <v>-89</v>
+        <v>-105.5</v>
       </c>
       <c r="P29" t="n">
         <v>2.1194546</v>
@@ -2887,7 +2887,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>122.94546</v>
+        <v>106.44546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-89</v>
+        <v>-105.5</v>
       </c>
     </row>
     <row r="30">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="O30" t="n">
-        <v>-490</v>
+        <v>-410</v>
       </c>
       <c r="P30" t="n">
         <v>5.7894546</v>
@@ -2977,7 +2977,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>88.94546</v>
+        <v>168.94546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-490</v>
+        <v>-410</v>
       </c>
     </row>
     <row r="31">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="O31" t="n">
-        <v>-138</v>
+        <v>-148.2</v>
       </c>
       <c r="P31" t="n">
         <v>0.9454876</v>
@@ -3067,7 +3067,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S31" t="n">
-        <v>51.09752</v>
+        <v>40.89752</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-138</v>
+        <v>-148.2</v>
       </c>
     </row>
     <row r="32">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>8.1219</v>
+        <v>9.205</v>
       </c>
       <c r="O32" t="n">
-        <v>-1624.38</v>
+        <v>-1841</v>
       </c>
       <c r="P32" t="n">
         <v>6.3644671</v>
@@ -3157,7 +3157,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S32" t="n">
-        <v>-351.48658</v>
+        <v>-568.10658</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-1624.38</v>
+        <v>-1841</v>
       </c>
     </row>
     <row r="33">
@@ -3225,17 +3225,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>9.19</v>
+        <v>10.41</v>
       </c>
       <c r="O33" t="n">
-        <v>-1838</v>
+        <v>-2082</v>
       </c>
       <c r="P33" t="n">
         <v>7.3548796</v>
@@ -3247,7 +3247,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S33" t="n">
-        <v>-367.02408</v>
+        <v>-611.02408</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1838</v>
+        <v>-2082</v>
       </c>
     </row>
   </sheetData>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2811</v>
+        <v>1.2721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3431,17 +3431,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>398.6</v>
+        <v>393.55</v>
       </c>
       <c r="O2" t="n">
-        <v>19930</v>
+        <v>19677.5</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3453,7 +3453,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-1052.956235</v>
+        <v>-1305.456235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25532.323</v>
+        <v>25031.74775</v>
       </c>
     </row>
     <row r="3">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2811</v>
+        <v>1.2721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3511,17 +3511,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>350</v>
       </c>
       <c r="N3" t="n">
-        <v>63.2</v>
+        <v>62.01</v>
       </c>
       <c r="O3" t="n">
-        <v>22120</v>
+        <v>21703.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.60009794299999</v>
@@ -3533,7 +3533,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S3" t="n">
-        <v>-840.03428</v>
+        <v>-1256.53428</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>28337.932</v>
+        <v>27609.02235</v>
       </c>
     </row>
     <row r="4">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14542</v>
+        <v>0.14531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.56</v>
+        <v>31.48</v>
       </c>
       <c r="O4" t="n">
-        <v>63120</v>
+        <v>62960</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -3613,7 +3613,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-272.47719</v>
+        <v>-432.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9178.910399999999</v>
+        <v>9148.7176</v>
       </c>
     </row>
     <row r="5">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1567</v>
+        <v>1.1511</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3671,17 +3671,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3175</v>
+        <v>4.31</v>
       </c>
       <c r="O5" t="n">
-        <v>12952.5</v>
+        <v>12930</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -3693,7 +3693,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1022.739091</v>
+        <v>-1045.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14982.15675</v>
+        <v>14883.723</v>
       </c>
     </row>
     <row r="6">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1567</v>
+        <v>1.1511</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3751,17 +3751,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.28</v>
+        <v>45.94</v>
       </c>
       <c r="O6" t="n">
-        <v>46280</v>
+        <v>45940</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -3773,7 +3773,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>3270</v>
+        <v>2930</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>53532.076</v>
+        <v>52881.534</v>
       </c>
     </row>
     <row r="7">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1567</v>
+        <v>1.1511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,17 +3831,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>564</v>
+        <v>520</v>
       </c>
       <c r="O7" t="n">
-        <v>8460</v>
+        <v>7800</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -3853,7 +3853,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>115.83</v>
+        <v>-544.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>9785.682000000001</v>
+        <v>8978.58</v>
       </c>
     </row>
     <row r="8">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78478</v>
+        <v>0.78183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38061.83</v>
+        <v>37918.755</v>
       </c>
     </row>
     <row r="9">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78478</v>
+        <v>0.78183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3991,17 +3991,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>607</v>
+        <v>606.9</v>
       </c>
       <c r="O9" t="n">
-        <v>45525</v>
+        <v>45517.5</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4013,7 +4013,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>1301.6496</v>
+        <v>1294.1496</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>35727.1095</v>
+        <v>35586.947025</v>
       </c>
     </row>
     <row r="10">
@@ -4071,17 +4071,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.985</v>
+        <v>7.85</v>
       </c>
       <c r="O10" t="n">
-        <v>8783.5</v>
+        <v>8635</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4093,7 +4093,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-359.347947</v>
+        <v>-507.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8783.5</v>
+        <v>8635</v>
       </c>
     </row>
     <row r="11">
@@ -4151,17 +4151,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>222.81</v>
+        <v>218.24</v>
       </c>
       <c r="O11" t="n">
-        <v>6684.3</v>
+        <v>6547.2</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -4173,7 +4173,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>145.1</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6684.3</v>
+        <v>6547.2</v>
       </c>
     </row>
     <row r="12">
@@ -4231,17 +4231,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>9.73</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>2919</v>
+        <v>2910</v>
       </c>
       <c r="P12" t="n">
         <v>11.661666667</v>
@@ -4253,7 +4253,7 @@
         <v>3498.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-579.5</v>
+        <v>-588.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2919</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="13">
@@ -4311,17 +4311,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>308.7</v>
+        <v>303.55</v>
       </c>
       <c r="O13" t="n">
-        <v>30870</v>
+        <v>30355</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4333,7 +4333,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2317.755</v>
+        <v>-2832.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30870</v>
+        <v>30355</v>
       </c>
     </row>
     <row r="14">
@@ -4391,17 +4391,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>58.27</v>
+        <v>57.79</v>
       </c>
       <c r="O14" t="n">
-        <v>9323.200000000001</v>
+        <v>9246.4</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4413,7 +4413,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-309.24</v>
+        <v>-386.04</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9323.200000000001</v>
+        <v>9246.4</v>
       </c>
     </row>
     <row r="15">
@@ -4471,17 +4471,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>68.39</v>
+        <v>66.92</v>
       </c>
       <c r="O15" t="n">
-        <v>1152.02</v>
+        <v>1127.25</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4493,7 +4493,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>802.973421</v>
+        <v>778.203421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1152.02</v>
+        <v>1127.25</v>
       </c>
     </row>
     <row r="16">
@@ -4551,17 +4551,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.3423</v>
+        <v>27.2889</v>
       </c>
       <c r="O16" t="n">
-        <v>10526.79</v>
+        <v>10506.23</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4573,7 +4573,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>517.884112</v>
+        <v>497.324112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10526.79</v>
+        <v>10506.23</v>
       </c>
     </row>
     <row r="17">
@@ -4631,17 +4631,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>287.52</v>
+        <v>282.89</v>
       </c>
       <c r="O17" t="n">
-        <v>28752</v>
+        <v>28289</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4653,7 +4653,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-1050</v>
+        <v>-1513</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28752</v>
+        <v>28289</v>
       </c>
     </row>
     <row r="18">
@@ -4711,17 +4711,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>600</v>
       </c>
       <c r="N18" t="n">
-        <v>171.26</v>
+        <v>169.36</v>
       </c>
       <c r="O18" t="n">
-        <v>102756</v>
+        <v>101616</v>
       </c>
       <c r="P18" t="n">
         <v>173.846763275</v>
@@ -4733,7 +4733,7 @@
         <v>104308.057965</v>
       </c>
       <c r="S18" t="n">
-        <v>-1552.057965</v>
+        <v>-2692.057965</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>102756</v>
+        <v>101616</v>
       </c>
     </row>
     <row r="19">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.125</v>
+        <v>0.0553</v>
       </c>
       <c r="O19" t="n">
-        <v>12.5</v>
+        <v>5.53</v>
       </c>
       <c r="P19" t="n">
         <v>2.1405125</v>
@@ -4823,7 +4823,7 @@
         <v>214.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-201.55125</v>
+        <v>-208.52125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>12.5</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="20">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>10.4728</v>
+        <v>9.780799999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>1047.28</v>
+        <v>978.08</v>
       </c>
       <c r="P20" t="n">
         <v>2.5205125</v>
@@ -4913,7 +4913,7 @@
         <v>252.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>795.22875</v>
+        <v>726.0287499999999</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>1047.28</v>
+        <v>978.08</v>
       </c>
     </row>
     <row r="21">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>29.2202</v>
+        <v>32.8108</v>
       </c>
       <c r="O21" t="n">
-        <v>5844.04</v>
+        <v>6562.16</v>
       </c>
       <c r="P21" t="n">
         <v>23.5270125</v>
@@ -5003,7 +5003,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S21" t="n">
-        <v>1138.6375</v>
+        <v>1856.7575</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>5844.04</v>
+        <v>6562.16</v>
       </c>
     </row>
     <row r="22">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>25.245</v>
+        <v>28.645</v>
       </c>
       <c r="O22" t="n">
-        <v>5049</v>
+        <v>5729</v>
       </c>
       <c r="P22" t="n">
         <v>20.1350875</v>
@@ -5093,7 +5093,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S22" t="n">
-        <v>1021.9825</v>
+        <v>1701.9825</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5049</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="23">
@@ -5161,17 +5161,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.53</v>
+        <v>3.875</v>
       </c>
       <c r="O23" t="n">
-        <v>-253</v>
+        <v>-387.5</v>
       </c>
       <c r="P23" t="n">
         <v>1.7694546</v>
@@ -5183,7 +5183,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>-76.05454</v>
+        <v>-210.55454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-253</v>
+        <v>-387.5</v>
       </c>
     </row>
     <row r="24">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.215</v>
+        <v>0.1258</v>
       </c>
       <c r="O24" t="n">
-        <v>-21.5</v>
+        <v>-12.58</v>
       </c>
       <c r="P24" t="n">
         <v>3.4194546</v>
@@ -5273,7 +5273,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>320.44546</v>
+        <v>329.36546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-21.5</v>
+        <v>-12.58</v>
       </c>
     </row>
     <row r="25">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.314</v>
+        <v>4.625</v>
       </c>
       <c r="O25" t="n">
-        <v>-331.4</v>
+        <v>-462.5</v>
       </c>
       <c r="P25" t="n">
         <v>4.1794546</v>
@@ -5363,7 +5363,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>86.54546000000001</v>
+        <v>-44.55454</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-331.4</v>
+        <v>-462.5</v>
       </c>
     </row>
     <row r="26">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.235</v>
+        <v>0.1239</v>
       </c>
       <c r="O26" t="n">
-        <v>-23.5</v>
+        <v>-12.39</v>
       </c>
       <c r="P26" t="n">
         <v>2.3694546</v>
@@ -5453,7 +5453,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>213.44546</v>
+        <v>224.55546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-23.5</v>
+        <v>-12.39</v>
       </c>
     </row>
     <row r="27">
@@ -5521,17 +5521,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.9527</v>
+        <v>1.3651</v>
       </c>
       <c r="O27" t="n">
-        <v>-95.27</v>
+        <v>-136.51</v>
       </c>
       <c r="P27" t="n">
         <v>1.7994546</v>
@@ -5543,7 +5543,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>84.67546</v>
+        <v>43.43546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-95.27</v>
+        <v>-136.51</v>
       </c>
     </row>
     <row r="28">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.35</v>
+        <v>4.8593</v>
       </c>
       <c r="O28" t="n">
-        <v>-335</v>
+        <v>-485.93</v>
       </c>
       <c r="P28" t="n">
         <v>5.9694626</v>
@@ -5633,7 +5633,7 @@
         <v>-596.9462600000001</v>
       </c>
       <c r="S28" t="n">
-        <v>261.94626</v>
+        <v>111.01626</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-335</v>
+        <v>-485.93</v>
       </c>
     </row>
     <row r="29">
@@ -5701,17 +5701,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>5.2</v>
+        <v>3.375</v>
       </c>
       <c r="O29" t="n">
-        <v>-520</v>
+        <v>-337.5</v>
       </c>
       <c r="P29" t="n">
         <v>3.2300876</v>
@@ -5723,7 +5723,7 @@
         <v>-323.00876</v>
       </c>
       <c r="S29" t="n">
-        <v>-196.99124</v>
+        <v>-14.49124</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-520</v>
+        <v>-337.5</v>
       </c>
     </row>
     <row r="30">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.566</v>
+        <v>2.415</v>
       </c>
       <c r="O30" t="n">
-        <v>-356.6</v>
+        <v>-241.5</v>
       </c>
       <c r="P30" t="n">
         <v>4.8394876</v>
@@ -5813,7 +5813,7 @@
         <v>-483.94876</v>
       </c>
       <c r="S30" t="n">
-        <v>127.34876</v>
+        <v>242.44876</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-356.6</v>
+        <v>-241.5</v>
       </c>
     </row>
     <row r="31">
@@ -5881,17 +5881,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.89</v>
+        <v>1.055</v>
       </c>
       <c r="O31" t="n">
-        <v>-89</v>
+        <v>-105.5</v>
       </c>
       <c r="P31" t="n">
         <v>2.1094546</v>
@@ -5903,7 +5903,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>121.94546</v>
+        <v>105.44546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-89</v>
+        <v>-105.5</v>
       </c>
     </row>
     <row r="32">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0529</v>
+        <v>0.037</v>
       </c>
       <c r="O32" t="n">
-        <v>-5.29</v>
+        <v>-3.7</v>
       </c>
       <c r="P32" t="n">
         <v>0.8794546</v>
@@ -5993,7 +5993,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>82.65546000000001</v>
+        <v>84.24545999999999</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-5.29</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="33">
@@ -6061,17 +6061,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>12.355</v>
+        <v>11.6541</v>
       </c>
       <c r="O33" t="n">
-        <v>-1235.5</v>
+        <v>-1165.41</v>
       </c>
       <c r="P33" t="n">
         <v>3.2794546</v>
@@ -6083,7 +6083,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>-907.55454</v>
+        <v>-837.4645400000001</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1235.5</v>
+        <v>-1165.41</v>
       </c>
     </row>
     <row r="34">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-2</v>
       </c>
       <c r="N34" t="n">
-        <v>8.1219</v>
+        <v>9.205</v>
       </c>
       <c r="O34" t="n">
-        <v>-1624.38</v>
+        <v>-1841</v>
       </c>
       <c r="P34" t="n">
         <v>6.3929546</v>
@@ -6173,7 +6173,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S34" t="n">
-        <v>-345.78908</v>
+        <v>-562.40908</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1624.38</v>
+        <v>-1841</v>
       </c>
     </row>
     <row r="35">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>9.19</v>
+        <v>10.41</v>
       </c>
       <c r="O35" t="n">
-        <v>-1838</v>
+        <v>-2082</v>
       </c>
       <c r="P35" t="n">
         <v>7.3496796</v>
@@ -6263,7 +6263,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S35" t="n">
-        <v>-368.06408</v>
+        <v>-612.06408</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-1838</v>
+        <v>-2082</v>
       </c>
     </row>
   </sheetData>
@@ -6323,17 +6323,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$310,683.54</t>
+          <t>$306,940.99</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$125,785.03</t>
+          <t>$125,379.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$436,468.57</t>
+          <t>$432,320.08</t>
         </is>
       </c>
     </row>
@@ -6345,17 +6345,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$422,129.21</t>
+          <t>$417,271.86</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$125,869.15</t>
+          <t>$125,320.37</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$547,998.36</t>
+          <t>$542,592.23</t>
         </is>
       </c>
     </row>
@@ -6373,17 +6373,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$732,812.75</t>
+          <t>$724,212.84</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$251,654.17</t>
+          <t>$250,699.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$984,466.93</t>
+          <t>$974,912.31</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12 23:42:32</t>
+          <t>2026-03-13 23:42:58</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2721</v>
+        <v>1.2636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>393.55</v>
+        <v>390.35</v>
       </c>
       <c r="O2" t="n">
-        <v>15742</v>
+        <v>15614</v>
       </c>
       <c r="P2" t="n">
         <v>417.712590175</v>
@@ -607,7 +607,7 @@
         <v>16708.503607</v>
       </c>
       <c r="S2" t="n">
-        <v>-966.503607</v>
+        <v>-1094.503607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20025.3982</v>
+        <v>19729.8504</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2721</v>
+        <v>1.2636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>62.01</v>
+        <v>62.15</v>
       </c>
       <c r="O3" t="n">
-        <v>15502.5</v>
+        <v>15537.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-805.853333</v>
+        <v>-770.853333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>19720.73025</v>
+        <v>19633.185</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14531</v>
+        <v>0.1448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.48</v>
+        <v>31.42</v>
       </c>
       <c r="O4" t="n">
-        <v>94440</v>
+        <v>94260</v>
       </c>
       <c r="P4" t="n">
         <v>31.36596519</v>
@@ -767,7 +767,7 @@
         <v>94097.89556999999</v>
       </c>
       <c r="S4" t="n">
-        <v>342.10443</v>
+        <v>162.10443</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>13723.0764</v>
+        <v>13648.848</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1511</v>
+        <v>1.1417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.31</v>
+        <v>4.346</v>
       </c>
       <c r="O5" t="n">
-        <v>8620</v>
+        <v>8692</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-704.66</v>
+        <v>-632.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9922.482</v>
+        <v>9923.6564</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1511</v>
+        <v>1.1417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="O6" t="n">
-        <v>7800</v>
+        <v>7980</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>-544.17</v>
+        <v>-364.17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>8978.58</v>
+        <v>9110.766</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78183</v>
+        <v>0.779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.85</v>
+        <v>4.836</v>
       </c>
       <c r="O7" t="n">
-        <v>38800</v>
+        <v>38688</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1488.77315</v>
+        <v>1376.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30335.004</v>
+        <v>30137.952</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78183</v>
+        <v>0.779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>606.9</v>
+        <v>598.6</v>
       </c>
       <c r="O8" t="n">
-        <v>45517.5</v>
+        <v>44895</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>1283.401008</v>
+        <v>660.901008</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>35586.947025</v>
+        <v>34973.205</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.85</v>
+        <v>7.735</v>
       </c>
       <c r="O9" t="n">
-        <v>7850</v>
+        <v>7735</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-461.237657</v>
+        <v>-576.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7850</v>
+        <v>7735</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>218.24</v>
+        <v>207.54</v>
       </c>
       <c r="O10" t="n">
-        <v>6547.2</v>
+        <v>6226.2</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>-316.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6547.2</v>
+        <v>6226.2</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5</v>
+        <v>9.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>303.55</v>
+        <v>302.28</v>
       </c>
       <c r="O12" t="n">
-        <v>30355</v>
+        <v>30228</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>191.5</v>
+        <v>64.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30355</v>
+        <v>30228</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>57.79</v>
+        <v>56.96</v>
       </c>
       <c r="O13" t="n">
-        <v>9246.4</v>
+        <v>9113.6</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-330.26</v>
+        <v>-463.06</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9246.4</v>
+        <v>9113.6</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>27.2889</v>
+        <v>27.1048</v>
       </c>
       <c r="O14" t="n">
-        <v>10506.23</v>
+        <v>10435.35</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>491.327178</v>
+        <v>420.447178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10506.23</v>
+        <v>10435.35</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>70</v>
       </c>
       <c r="N15" t="n">
-        <v>159.16</v>
+        <v>155.11</v>
       </c>
       <c r="O15" t="n">
-        <v>11141.2</v>
+        <v>10857.7</v>
       </c>
       <c r="P15" t="n">
         <v>204.330714286</v>
@@ -1647,7 +1647,7 @@
         <v>14303.15</v>
       </c>
       <c r="S15" t="n">
-        <v>-3161.95</v>
+        <v>-3445.45</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>11141.2</v>
+        <v>10857.7</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>85.16</v>
+        <v>86</v>
       </c>
       <c r="O16" t="n">
-        <v>1703.2</v>
+        <v>1720</v>
       </c>
       <c r="P16" t="n">
         <v>124.315</v>
@@ -1727,7 +1727,7 @@
         <v>2486.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-783.1</v>
+        <v>-766.3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1703.2</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>500</v>
       </c>
       <c r="N17" t="n">
-        <v>169.36</v>
+        <v>167.82</v>
       </c>
       <c r="O17" t="n">
-        <v>84680</v>
+        <v>83910</v>
       </c>
       <c r="P17" t="n">
         <v>173.59385355</v>
@@ -1807,7 +1807,7 @@
         <v>86796.926775</v>
       </c>
       <c r="S17" t="n">
-        <v>-2116.926775</v>
+        <v>-2886.926775</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>84680</v>
+        <v>83910</v>
       </c>
     </row>
     <row r="18">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0553</v>
+        <v>0.0255</v>
       </c>
       <c r="O18" t="n">
-        <v>5.53</v>
+        <v>2.55</v>
       </c>
       <c r="P18" t="n">
         <v>2.0105125</v>
@@ -1897,7 +1897,7 @@
         <v>201.05125</v>
       </c>
       <c r="S18" t="n">
-        <v>-195.52125</v>
+        <v>-198.50125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>5.53</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="19">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.705</v>
+        <v>1.235</v>
       </c>
       <c r="O19" t="n">
-        <v>270.5</v>
+        <v>123.5</v>
       </c>
       <c r="P19" t="n">
         <v>4.4905125</v>
@@ -1987,7 +1987,7 @@
         <v>449.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-178.55125</v>
+        <v>-325.55125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>270.5</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="20">
@@ -2055,17 +2055,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>32.8108</v>
+        <v>34.125</v>
       </c>
       <c r="O20" t="n">
-        <v>6562.16</v>
+        <v>6825</v>
       </c>
       <c r="P20" t="n">
         <v>23.4605</v>
@@ -2077,7 +2077,7 @@
         <v>4692.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1870.06</v>
+        <v>2132.9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>6562.16</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="21">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>28.645</v>
+        <v>29.87</v>
       </c>
       <c r="O21" t="n">
-        <v>5729</v>
+        <v>5974</v>
       </c>
       <c r="P21" t="n">
         <v>20.1374875</v>
@@ -2167,7 +2167,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S21" t="n">
-        <v>1701.5025</v>
+        <v>1946.5025</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>5729</v>
+        <v>5974</v>
       </c>
     </row>
     <row r="22">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.875</v>
+        <v>5.75</v>
       </c>
       <c r="O22" t="n">
-        <v>-387.5</v>
+        <v>-575</v>
       </c>
       <c r="P22" t="n">
         <v>1.7494546</v>
@@ -2257,7 +2257,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S22" t="n">
-        <v>-212.55454</v>
+        <v>-400.05454</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-387.5</v>
+        <v>-575</v>
       </c>
     </row>
     <row r="23">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1258</v>
+        <v>0.0542</v>
       </c>
       <c r="O23" t="n">
-        <v>-12.58</v>
+        <v>-5.42</v>
       </c>
       <c r="P23" t="n">
         <v>3.2494546</v>
@@ -2347,7 +2347,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>312.36546</v>
+        <v>319.52546</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-12.58</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="24">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.625</v>
+        <v>5.075</v>
       </c>
       <c r="O24" t="n">
-        <v>-462.5</v>
+        <v>-507.5</v>
       </c>
       <c r="P24" t="n">
         <v>7.5800876</v>
@@ -2437,7 +2437,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S24" t="n">
-        <v>295.50876</v>
+        <v>250.50876</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-462.5</v>
+        <v>-507.5</v>
       </c>
     </row>
     <row r="25">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.3651</v>
+        <v>1.35</v>
       </c>
       <c r="O25" t="n">
-        <v>-136.51</v>
+        <v>-135</v>
       </c>
       <c r="P25" t="n">
         <v>1.8142796</v>
@@ -2527,7 +2527,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S25" t="n">
-        <v>44.91796</v>
+        <v>46.42796</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-136.51</v>
+        <v>-135</v>
       </c>
     </row>
     <row r="26">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.225</v>
+        <v>0.155</v>
       </c>
       <c r="O26" t="n">
-        <v>-22.5</v>
+        <v>-15.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.0242796</v>
@@ -2617,7 +2617,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>79.92796</v>
+        <v>86.92796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-22.5</v>
+        <v>-15.5</v>
       </c>
     </row>
     <row r="27">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-2</v>
       </c>
       <c r="N27" t="n">
-        <v>4.8593</v>
+        <v>4.825</v>
       </c>
       <c r="O27" t="n">
-        <v>-971.86</v>
+        <v>-965</v>
       </c>
       <c r="P27" t="n">
         <v>6.6394751</v>
@@ -2707,7 +2707,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S27" t="n">
-        <v>356.03502</v>
+        <v>362.89502</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-971.86</v>
+        <v>-965</v>
       </c>
     </row>
     <row r="28">
@@ -2775,17 +2775,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.375</v>
+        <v>2.635</v>
       </c>
       <c r="O28" t="n">
-        <v>-337.5</v>
+        <v>-263.5</v>
       </c>
       <c r="P28" t="n">
         <v>6.7894876</v>
@@ -2797,7 +2797,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S28" t="n">
-        <v>341.44876</v>
+        <v>415.44876</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-337.5</v>
+        <v>-263.5</v>
       </c>
     </row>
     <row r="29">
@@ -2865,17 +2865,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.055</v>
+        <v>1.22</v>
       </c>
       <c r="O29" t="n">
-        <v>-105.5</v>
+        <v>-122</v>
       </c>
       <c r="P29" t="n">
         <v>2.1194546</v>
@@ -2887,7 +2887,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S29" t="n">
-        <v>106.44546</v>
+        <v>89.94546</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-105.5</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="30">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1</v>
+        <v>2.02</v>
       </c>
       <c r="O30" t="n">
-        <v>-410</v>
+        <v>-202</v>
       </c>
       <c r="P30" t="n">
         <v>5.7894546</v>
@@ -2977,7 +2977,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>168.94546</v>
+        <v>376.94546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-410</v>
+        <v>-202</v>
       </c>
     </row>
     <row r="31">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.741</v>
+        <v>0.55</v>
       </c>
       <c r="O31" t="n">
-        <v>-148.2</v>
+        <v>-110</v>
       </c>
       <c r="P31" t="n">
         <v>0.9454876</v>
@@ -3067,7 +3067,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S31" t="n">
-        <v>40.89752</v>
+        <v>79.09752</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-148.2</v>
+        <v>-110</v>
       </c>
     </row>
     <row r="32">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>9.205</v>
+        <v>9.695399999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>-1841</v>
+        <v>-1939.08</v>
       </c>
       <c r="P32" t="n">
         <v>6.3644671</v>
@@ -3157,7 +3157,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S32" t="n">
-        <v>-568.10658</v>
+        <v>-666.18658</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-1841</v>
+        <v>-1939.08</v>
       </c>
     </row>
     <row r="33">
@@ -3225,17 +3225,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>10.41</v>
+        <v>10.795</v>
       </c>
       <c r="O33" t="n">
-        <v>-2082</v>
+        <v>-2159</v>
       </c>
       <c r="P33" t="n">
         <v>7.3548796</v>
@@ -3247,7 +3247,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S33" t="n">
-        <v>-611.02408</v>
+        <v>-688.02408</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-2082</v>
+        <v>-2159</v>
       </c>
     </row>
   </sheetData>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2721</v>
+        <v>1.2636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3431,17 +3431,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>393.55</v>
+        <v>390.35</v>
       </c>
       <c r="O2" t="n">
-        <v>19677.5</v>
+        <v>19517.5</v>
       </c>
       <c r="P2" t="n">
         <v>419.6591247</v>
@@ -3453,7 +3453,7 @@
         <v>20982.956235</v>
       </c>
       <c r="S2" t="n">
-        <v>-1305.456235</v>
+        <v>-1465.456235</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25031.74775</v>
+        <v>24662.313</v>
       </c>
     </row>
     <row r="3">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2721</v>
+        <v>1.2636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3511,17 +3511,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>350</v>
       </c>
       <c r="N3" t="n">
-        <v>62.01</v>
+        <v>62.15</v>
       </c>
       <c r="O3" t="n">
-        <v>21703.5</v>
+        <v>21752.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.60009794299999</v>
@@ -3533,7 +3533,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S3" t="n">
-        <v>-1256.53428</v>
+        <v>-1207.53428</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>27609.02235</v>
+        <v>27486.459</v>
       </c>
     </row>
     <row r="4">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14531</v>
+        <v>0.1448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.48</v>
+        <v>31.42</v>
       </c>
       <c r="O4" t="n">
-        <v>62960</v>
+        <v>62840</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -3613,7 +3613,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-432.47719</v>
+        <v>-552.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9148.7176</v>
+        <v>9099.232</v>
       </c>
     </row>
     <row r="5">
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1511</v>
+        <v>1.1417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3671,17 +3671,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.31</v>
+        <v>4.346</v>
       </c>
       <c r="O5" t="n">
-        <v>12930</v>
+        <v>13038</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -3693,7 +3693,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1045.239091</v>
+        <v>-937.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14883.723</v>
+        <v>14885.4846</v>
       </c>
     </row>
     <row r="6">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1511</v>
+        <v>1.1417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3751,17 +3751,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>45.94</v>
+        <v>45.05</v>
       </c>
       <c r="O6" t="n">
-        <v>45940</v>
+        <v>45050</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -3773,7 +3773,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>2930</v>
+        <v>2040</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>52881.534</v>
+        <v>51433.585</v>
       </c>
     </row>
     <row r="7">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1511</v>
+        <v>1.1417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,17 +3831,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="O7" t="n">
-        <v>7800</v>
+        <v>7980</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -3853,7 +3853,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>-544.17</v>
+        <v>-364.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>8978.58</v>
+        <v>9110.766</v>
       </c>
     </row>
     <row r="8">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78183</v>
+        <v>0.779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3911,17 +3911,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.85</v>
+        <v>4.836</v>
       </c>
       <c r="O8" t="n">
-        <v>48500</v>
+        <v>48360</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -3933,7 +3933,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11231.8184</v>
+        <v>11091.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37918.755</v>
+        <v>37672.44</v>
       </c>
     </row>
     <row r="9">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78183</v>
+        <v>0.779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3991,17 +3991,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>606.9</v>
+        <v>598.6</v>
       </c>
       <c r="O9" t="n">
-        <v>45517.5</v>
+        <v>44895</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4013,7 +4013,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.1496</v>
+        <v>671.6496</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>35586.947025</v>
+        <v>34973.205</v>
       </c>
     </row>
     <row r="10">
@@ -4071,17 +4071,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.85</v>
+        <v>7.735</v>
       </c>
       <c r="O10" t="n">
-        <v>8635</v>
+        <v>8508.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4093,7 +4093,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-507.847947</v>
+        <v>-634.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8635</v>
+        <v>8508.5</v>
       </c>
     </row>
     <row r="11">
@@ -4151,17 +4151,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>218.24</v>
+        <v>207.54</v>
       </c>
       <c r="O11" t="n">
-        <v>6547.2</v>
+        <v>6226.2</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -4173,7 +4173,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>-313</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6547.2</v>
+        <v>6226.2</v>
       </c>
     </row>
     <row r="12">
@@ -4231,17 +4231,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>2910</v>
+        <v>2940</v>
       </c>
       <c r="P12" t="n">
         <v>11.661666667</v>
@@ -4253,7 +4253,7 @@
         <v>3498.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-588.5</v>
+        <v>-558.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2910</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="13">
@@ -4311,17 +4311,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>303.55</v>
+        <v>302.28</v>
       </c>
       <c r="O13" t="n">
-        <v>30355</v>
+        <v>30228</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4333,7 +4333,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2832.755</v>
+        <v>-2959.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30355</v>
+        <v>30228</v>
       </c>
     </row>
     <row r="14">
@@ -4391,17 +4391,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>57.79</v>
+        <v>56.96</v>
       </c>
       <c r="O14" t="n">
-        <v>9246.4</v>
+        <v>9113.6</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4413,7 +4413,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-386.04</v>
+        <v>-518.84</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9246.4</v>
+        <v>9113.6</v>
       </c>
     </row>
     <row r="15">
@@ -4471,17 +4471,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>66.92</v>
+        <v>66.19</v>
       </c>
       <c r="O15" t="n">
-        <v>1127.25</v>
+        <v>1114.96</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4493,7 +4493,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>778.203421</v>
+        <v>765.913421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1127.25</v>
+        <v>1114.96</v>
       </c>
     </row>
     <row r="16">
@@ -4551,17 +4551,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.2889</v>
+        <v>27.1048</v>
       </c>
       <c r="O16" t="n">
-        <v>10506.23</v>
+        <v>10435.35</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4573,7 +4573,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>497.324112</v>
+        <v>426.444112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10506.23</v>
+        <v>10435.35</v>
       </c>
     </row>
     <row r="17">
@@ -4631,17 +4631,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>282.89</v>
+        <v>283.44</v>
       </c>
       <c r="O17" t="n">
-        <v>28289</v>
+        <v>28344</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4653,7 +4653,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-1513</v>
+        <v>-1458</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28289</v>
+        <v>28344</v>
       </c>
     </row>
     <row r="18">
@@ -4711,17 +4711,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>600</v>
       </c>
       <c r="N18" t="n">
-        <v>169.36</v>
+        <v>167.82</v>
       </c>
       <c r="O18" t="n">
-        <v>101616</v>
+        <v>100692</v>
       </c>
       <c r="P18" t="n">
         <v>173.846763275</v>
@@ -4733,7 +4733,7 @@
         <v>104308.057965</v>
       </c>
       <c r="S18" t="n">
-        <v>-2692.057965</v>
+        <v>-3616.057965</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>101616</v>
+        <v>100692</v>
       </c>
     </row>
     <row r="19">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0553</v>
+        <v>0.0255</v>
       </c>
       <c r="O19" t="n">
-        <v>5.53</v>
+        <v>2.55</v>
       </c>
       <c r="P19" t="n">
         <v>2.1405125</v>
@@ -4823,7 +4823,7 @@
         <v>214.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-208.52125</v>
+        <v>-211.50125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>5.53</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="20">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>9.780799999999999</v>
+        <v>10.7764</v>
       </c>
       <c r="O20" t="n">
-        <v>978.08</v>
+        <v>1077.64</v>
       </c>
       <c r="P20" t="n">
         <v>2.5205125</v>
@@ -4913,7 +4913,7 @@
         <v>252.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>726.0287499999999</v>
+        <v>825.58875</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>978.08</v>
+        <v>1077.64</v>
       </c>
     </row>
     <row r="21">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>32.8108</v>
+        <v>34.125</v>
       </c>
       <c r="O21" t="n">
-        <v>6562.16</v>
+        <v>6825</v>
       </c>
       <c r="P21" t="n">
         <v>23.5270125</v>
@@ -5003,7 +5003,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S21" t="n">
-        <v>1856.7575</v>
+        <v>2119.5975</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>6562.16</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="22">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>28.645</v>
+        <v>29.87</v>
       </c>
       <c r="O22" t="n">
-        <v>5729</v>
+        <v>5974</v>
       </c>
       <c r="P22" t="n">
         <v>20.1350875</v>
@@ -5093,7 +5093,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S22" t="n">
-        <v>1701.9825</v>
+        <v>1946.9825</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5729</v>
+        <v>5974</v>
       </c>
     </row>
     <row r="23">
@@ -5161,17 +5161,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.875</v>
+        <v>5.75</v>
       </c>
       <c r="O23" t="n">
-        <v>-387.5</v>
+        <v>-575</v>
       </c>
       <c r="P23" t="n">
         <v>1.7694546</v>
@@ -5183,7 +5183,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>-210.55454</v>
+        <v>-398.05454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-387.5</v>
+        <v>-575</v>
       </c>
     </row>
     <row r="24">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1258</v>
+        <v>0.0542</v>
       </c>
       <c r="O24" t="n">
-        <v>-12.58</v>
+        <v>-5.42</v>
       </c>
       <c r="P24" t="n">
         <v>3.4194546</v>
@@ -5273,7 +5273,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>329.36546</v>
+        <v>336.52546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-12.58</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="25">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>4.625</v>
+        <v>5.075</v>
       </c>
       <c r="O25" t="n">
-        <v>-462.5</v>
+        <v>-507.5</v>
       </c>
       <c r="P25" t="n">
         <v>4.1794546</v>
@@ -5363,7 +5363,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>-44.55454</v>
+        <v>-89.55454</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-462.5</v>
+        <v>-507.5</v>
       </c>
     </row>
     <row r="26">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1239</v>
+        <v>0.065</v>
       </c>
       <c r="O26" t="n">
-        <v>-12.39</v>
+        <v>-6.5</v>
       </c>
       <c r="P26" t="n">
         <v>2.3694546</v>
@@ -5453,7 +5453,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>224.55546</v>
+        <v>230.44546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-12.39</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="27">
@@ -5521,17 +5521,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.3651</v>
+        <v>1.35</v>
       </c>
       <c r="O27" t="n">
-        <v>-136.51</v>
+        <v>-135</v>
       </c>
       <c r="P27" t="n">
         <v>1.7994546</v>
@@ -5543,7 +5543,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>43.43546</v>
+        <v>44.94546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-136.51</v>
+        <v>-135</v>
       </c>
     </row>
     <row r="28">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8593</v>
+        <v>4.825</v>
       </c>
       <c r="O28" t="n">
-        <v>-485.93</v>
+        <v>-482.5</v>
       </c>
       <c r="P28" t="n">
         <v>5.9694626</v>
@@ -5633,7 +5633,7 @@
         <v>-596.9462600000001</v>
       </c>
       <c r="S28" t="n">
-        <v>111.01626</v>
+        <v>114.44626</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-485.93</v>
+        <v>-482.5</v>
       </c>
     </row>
     <row r="29">
@@ -5701,17 +5701,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.375</v>
+        <v>2.635</v>
       </c>
       <c r="O29" t="n">
-        <v>-337.5</v>
+        <v>-263.5</v>
       </c>
       <c r="P29" t="n">
         <v>3.2300876</v>
@@ -5723,7 +5723,7 @@
         <v>-323.00876</v>
       </c>
       <c r="S29" t="n">
-        <v>-14.49124</v>
+        <v>59.50876</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-337.5</v>
+        <v>-263.5</v>
       </c>
     </row>
     <row r="30">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.415</v>
+        <v>2.26</v>
       </c>
       <c r="O30" t="n">
-        <v>-241.5</v>
+        <v>-226</v>
       </c>
       <c r="P30" t="n">
         <v>4.8394876</v>
@@ -5813,7 +5813,7 @@
         <v>-483.94876</v>
       </c>
       <c r="S30" t="n">
-        <v>242.44876</v>
+        <v>257.94876</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-241.5</v>
+        <v>-226</v>
       </c>
     </row>
     <row r="31">
@@ -5881,17 +5881,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.055</v>
+        <v>1.22</v>
       </c>
       <c r="O31" t="n">
-        <v>-105.5</v>
+        <v>-122</v>
       </c>
       <c r="P31" t="n">
         <v>2.1094546</v>
@@ -5903,7 +5903,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>105.44546</v>
+        <v>88.94546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-105.5</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="32">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>0.037</v>
+        <v>0.0289</v>
       </c>
       <c r="O32" t="n">
-        <v>-3.7</v>
+        <v>-2.89</v>
       </c>
       <c r="P32" t="n">
         <v>0.8794546</v>
@@ -5993,7 +5993,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>84.24545999999999</v>
+        <v>85.05546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-3.7</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="33">
@@ -6061,17 +6061,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>11.6541</v>
+        <v>12.6799</v>
       </c>
       <c r="O33" t="n">
-        <v>-1165.41</v>
+        <v>-1267.99</v>
       </c>
       <c r="P33" t="n">
         <v>3.2794546</v>
@@ -6083,7 +6083,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>-837.4645400000001</v>
+        <v>-940.04454</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1165.41</v>
+        <v>-1267.99</v>
       </c>
     </row>
     <row r="34">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-2</v>
       </c>
       <c r="N34" t="n">
-        <v>9.205</v>
+        <v>9.695399999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>-1841</v>
+        <v>-1939.08</v>
       </c>
       <c r="P34" t="n">
         <v>6.3929546</v>
@@ -6173,7 +6173,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S34" t="n">
-        <v>-562.40908</v>
+        <v>-660.4890799999999</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1841</v>
+        <v>-1939.08</v>
       </c>
     </row>
     <row r="35">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>10.41</v>
+        <v>10.795</v>
       </c>
       <c r="O35" t="n">
-        <v>-2082</v>
+        <v>-2159</v>
       </c>
       <c r="P35" t="n">
         <v>7.3496796</v>
@@ -6263,7 +6263,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S35" t="n">
-        <v>-612.06408</v>
+        <v>-689.06408</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-2082</v>
+        <v>-2159</v>
       </c>
     </row>
   </sheetData>
@@ -6323,17 +6323,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$306,940.99</t>
+          <t>$304,289.36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$125,379.10</t>
+          <t>$124,994.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$432,320.08</t>
+          <t>$429,283.39</t>
         </is>
       </c>
     </row>
@@ -6345,17 +6345,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$417,271.86</t>
+          <t>$413,112.90</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$125,320.37</t>
+          <t>$124,799.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$542,592.23</t>
+          <t>$537,912.90</t>
         </is>
       </c>
     </row>
@@ -6373,17 +6373,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$724,212.84</t>
+          <t>$717,402.27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$250,699.47</t>
+          <t>$249,794.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$974,912.31</t>
+          <t>$967,196.29</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13 23:42:58</t>
+          <t>2026-03-14 23:42:41</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -6431,7 +6431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-14 23:42:41</t>
+          <t>2026-03-15 23:43:25</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -6431,7 +6431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-15 23:43:25</t>
+          <t>2026-03-16 23:42:49</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2636</v>
+        <v>1.2695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,29 +585,29 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>390.35</v>
+        <v>392.9</v>
       </c>
       <c r="O2" t="n">
-        <v>15614</v>
+        <v>23574</v>
       </c>
       <c r="P2" t="n">
-        <v>417.712590175</v>
+        <v>408.869226783</v>
       </c>
       <c r="Q2" t="n">
-        <v>417.712590175</v>
+        <v>408.869226783</v>
       </c>
       <c r="R2" t="n">
-        <v>16708.503607</v>
+        <v>24532.153607</v>
       </c>
       <c r="S2" t="n">
-        <v>-1094.503607</v>
+        <v>-958.153607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>19729.8504</v>
+        <v>29927.193</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2636</v>
+        <v>1.2695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>62.15</v>
+        <v>63.41</v>
       </c>
       <c r="O3" t="n">
-        <v>15537.5</v>
+        <v>15852.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-770.853333</v>
+        <v>-455.853333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>19633.185</v>
+        <v>20124.74875</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1448</v>
+        <v>0.14517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,29 +745,29 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.42</v>
+        <v>31.32</v>
       </c>
       <c r="O4" t="n">
-        <v>94260</v>
+        <v>62640</v>
       </c>
       <c r="P4" t="n">
-        <v>31.36596519</v>
+        <v>31.70624688</v>
       </c>
       <c r="Q4" t="n">
-        <v>31.36596519</v>
+        <v>31.70624688</v>
       </c>
       <c r="R4" t="n">
-        <v>94097.89556999999</v>
+        <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>162.10443</v>
+        <v>-772.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>13648.848</v>
+        <v>9093.4488</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1417</v>
+        <v>1.1505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.346</v>
+        <v>4.397</v>
       </c>
       <c r="O5" t="n">
-        <v>8692</v>
+        <v>8794</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-632.66</v>
+        <v>-530.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9923.6564</v>
+        <v>10117.497</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1417</v>
+        <v>1.1505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>532</v>
+        <v>602</v>
       </c>
       <c r="O6" t="n">
-        <v>7980</v>
+        <v>9030</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>-364.17</v>
+        <v>685.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9110.766</v>
+        <v>10389.015</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.779</v>
+        <v>0.78256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.836</v>
+        <v>4.86</v>
       </c>
       <c r="O7" t="n">
-        <v>38688</v>
+        <v>38880</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1376.77315</v>
+        <v>1568.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30137.952</v>
+        <v>30425.9328</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.779</v>
+        <v>0.78256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>598.6</v>
+        <v>587</v>
       </c>
       <c r="O8" t="n">
-        <v>44895</v>
+        <v>44025</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>660.901008</v>
+        <v>-209.098992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>34973.205</v>
+        <v>34452.204</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.735</v>
+        <v>7.675</v>
       </c>
       <c r="O9" t="n">
-        <v>7735</v>
+        <v>7675</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-576.237657</v>
+        <v>-636.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7735</v>
+        <v>7675</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>207.54</v>
+        <v>210.16</v>
       </c>
       <c r="O10" t="n">
-        <v>6226.2</v>
+        <v>6304.8</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-316.9</v>
+        <v>-238.3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6226.2</v>
+        <v>6304.8</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.19</v>
       </c>
       <c r="O11" t="n">
-        <v>980</v>
+        <v>1019</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>9.5</v>
+        <v>48.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>980</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>302.28</v>
+        <v>305.56</v>
       </c>
       <c r="O12" t="n">
-        <v>30228</v>
+        <v>30556</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>64.5</v>
+        <v>392.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30228</v>
+        <v>30556</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>56.96</v>
+        <v>57.43</v>
       </c>
       <c r="O13" t="n">
-        <v>9113.6</v>
+        <v>9188.799999999999</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-463.06</v>
+        <v>-387.86</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9113.6</v>
+        <v>9188.799999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>27.1048</v>
+        <v>27.0902</v>
       </c>
       <c r="O14" t="n">
-        <v>10435.35</v>
+        <v>10429.73</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>420.447178</v>
+        <v>414.827178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10435.35</v>
+        <v>10429.73</v>
       </c>
     </row>
     <row r="15">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ORACLE CORP</t>
+          <t>NVIDIA CORP</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1625,29 +1625,29 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>155.11</v>
+        <v>183.22</v>
       </c>
       <c r="O15" t="n">
-        <v>10857.7</v>
+        <v>18322</v>
       </c>
       <c r="P15" t="n">
-        <v>204.330714286</v>
+        <v>184.285</v>
       </c>
       <c r="Q15" t="n">
-        <v>204.330714286</v>
+        <v>184.285</v>
       </c>
       <c r="R15" t="n">
-        <v>14303.15</v>
+        <v>18428.5</v>
       </c>
       <c r="S15" t="n">
-        <v>-3445.45</v>
+        <v>-106.5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1656,11 +1656,11 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>10857.7</v>
+        <v>18322</v>
       </c>
     </row>
     <row r="16">
@@ -1684,17 +1684,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ADR</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SEA LTD-ADR</t>
+          <t>ORACLE CORP</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1705,29 +1705,29 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>86</v>
+        <v>155.97</v>
       </c>
       <c r="O16" t="n">
-        <v>1720</v>
+        <v>7798.5</v>
       </c>
       <c r="P16" t="n">
-        <v>124.315</v>
+        <v>197.085</v>
       </c>
       <c r="Q16" t="n">
-        <v>124.315</v>
+        <v>197.085</v>
       </c>
       <c r="R16" t="n">
-        <v>2486.3</v>
+        <v>9854.25</v>
       </c>
       <c r="S16" t="n">
-        <v>-766.3</v>
+        <v>-2055.75</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1720</v>
+        <v>7798.5</v>
       </c>
     </row>
     <row r="17">
@@ -1764,17 +1764,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>SEA LTD-ADR</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1785,29 +1785,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>167.82</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>83910</v>
+        <v>1751.4</v>
       </c>
       <c r="P17" t="n">
-        <v>173.59385355</v>
+        <v>124.315</v>
       </c>
       <c r="Q17" t="n">
-        <v>173.59385355</v>
+        <v>124.315</v>
       </c>
       <c r="R17" t="n">
-        <v>86796.926775</v>
+        <v>2486.3</v>
       </c>
       <c r="S17" t="n">
-        <v>-2886.926775</v>
+        <v>-734.9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>83910</v>
+        <v>1751.4</v>
       </c>
     </row>
     <row r="18">
@@ -1839,65 +1839,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OPT</t>
+          <t>STK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AAPL  260327C00290000</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 290 C</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" t="n">
-        <v>290</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0255</v>
+        <v>169.14</v>
       </c>
       <c r="O18" t="n">
-        <v>2.55</v>
+        <v>84570</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0105125</v>
+        <v>173.59385355</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.0105125</v>
+        <v>173.59385355</v>
       </c>
       <c r="R18" t="n">
-        <v>201.05125</v>
+        <v>86796.926775</v>
       </c>
       <c r="S18" t="n">
-        <v>-198.50125</v>
+        <v>-2226.926775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1906,11 +1896,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>2.55</v>
+        <v>84570</v>
       </c>
     </row>
     <row r="19">
@@ -1939,19 +1929,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MSFT  260327C00420000</t>
+          <t>AAPL  260327C00290000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 420 C</t>
+          <t>AAPL 27MAR26 290 C</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>420</v>
+        <v>290</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1965,29 +1955,29 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.235</v>
+        <v>0.0238</v>
       </c>
       <c r="O19" t="n">
-        <v>123.5</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>4.4905125</v>
+        <v>2.0105125</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.4905125</v>
+        <v>2.0105125</v>
       </c>
       <c r="R19" t="n">
-        <v>449.05125</v>
+        <v>201.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-325.55125</v>
+        <v>-198.67125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2000,7 +1990,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>123.5</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="20">
@@ -2024,60 +2014,60 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>QQQ   261218P00560000</t>
+          <t>MSFT  260327C00420000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 560 P</t>
+          <t>MSFT 27MAR26 420 C</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>34.125</v>
+        <v>1.16</v>
       </c>
       <c r="O20" t="n">
-        <v>6825</v>
+        <v>116</v>
       </c>
       <c r="P20" t="n">
-        <v>23.4605</v>
+        <v>4.4905125</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.4605</v>
+        <v>4.4905125</v>
       </c>
       <c r="R20" t="n">
-        <v>4692.1</v>
+        <v>449.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>2132.9</v>
+        <v>-333.05125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2090,7 +2080,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>6825</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
@@ -2119,19 +2109,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SPY   261218P00620000</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 620 P</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>620</v>
+        <v>560</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2145,29 +2135,29 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>29.87</v>
+        <v>30.9185</v>
       </c>
       <c r="O21" t="n">
-        <v>5974</v>
+        <v>6183.7</v>
       </c>
       <c r="P21" t="n">
-        <v>20.1374875</v>
+        <v>23.4605</v>
       </c>
       <c r="Q21" t="n">
-        <v>20.1374875</v>
+        <v>23.4605</v>
       </c>
       <c r="R21" t="n">
-        <v>4027.4975</v>
+        <v>4692.1</v>
       </c>
       <c r="S21" t="n">
-        <v>1946.5025</v>
+        <v>1491.6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2180,7 +2170,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>5974</v>
+        <v>6183.7</v>
       </c>
     </row>
     <row r="22">
@@ -2209,23 +2199,23 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AAPL  260327P00250000</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 250 P</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>250</v>
+        <v>620</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2235,33 +2225,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>5.75</v>
+        <v>26.75</v>
       </c>
       <c r="O22" t="n">
-        <v>-575</v>
+        <v>5350</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7494546</v>
+        <v>20.1374875</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.7494546</v>
+        <v>20.1374875</v>
       </c>
       <c r="R22" t="n">
-        <v>-174.94546</v>
+        <v>4027.4975</v>
       </c>
       <c r="S22" t="n">
-        <v>-400.05454</v>
+        <v>1322.5025</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2270,7 +2260,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-575</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="23">
@@ -2294,24 +2284,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AAPL  260327C00285000</t>
+          <t>AAPL  260327P00250000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 285 C</t>
+          <t>AAPL 27MAR26 250 P</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2320,34 +2310,34 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0542</v>
+        <v>3.5518</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.42</v>
+        <v>-355.18</v>
       </c>
       <c r="P23" t="n">
-        <v>3.2494546</v>
+        <v>1.7494546</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2494546</v>
+        <v>1.7494546</v>
       </c>
       <c r="R23" t="n">
-        <v>-324.94546</v>
+        <v>-174.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>319.52546</v>
+        <v>-180.23454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2360,7 +2350,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-5.42</v>
+        <v>-355.18</v>
       </c>
     </row>
     <row r="24">
@@ -2384,24 +2374,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AMD   260327P00185000</t>
+          <t>AAPL  260327C00285000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 185 P</t>
+          <t>AAPL 27MAR26 285 C</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2410,34 +2400,34 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>5.075</v>
+        <v>0.0309</v>
       </c>
       <c r="O24" t="n">
-        <v>-507.5</v>
+        <v>-3.09</v>
       </c>
       <c r="P24" t="n">
-        <v>7.5800876</v>
+        <v>3.2494546</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.5800876</v>
+        <v>3.2494546</v>
       </c>
       <c r="R24" t="n">
-        <v>-758.0087600000001</v>
+        <v>-324.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>250.50876</v>
+        <v>321.85546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2450,7 +2440,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-507.5</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="25">
@@ -2479,19 +2469,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AMZN  260327P00190000</t>
+          <t>AMD   260327P00185000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 190 P</t>
+          <t>AMD 27MAR26 185 P</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2505,29 +2495,29 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.35</v>
+        <v>3.5516</v>
       </c>
       <c r="O25" t="n">
-        <v>-135</v>
+        <v>-355.16</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8142796</v>
+        <v>7.5800876</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.8142796</v>
+        <v>7.5800876</v>
       </c>
       <c r="R25" t="n">
-        <v>-181.42796</v>
+        <v>-758.0087600000001</v>
       </c>
       <c r="S25" t="n">
-        <v>46.42796</v>
+        <v>402.84876</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2540,7 +2530,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-135</v>
+        <v>-355.16</v>
       </c>
     </row>
     <row r="26">
@@ -2564,24 +2554,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AMZN  260327C00235000</t>
+          <t>AMZN  260327P00190000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 235 C</t>
+          <t>AMZN 27MAR26 190 P</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2590,34 +2580,34 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.155</v>
+        <v>0.635</v>
       </c>
       <c r="O26" t="n">
-        <v>-15.5</v>
+        <v>-63.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.0242796</v>
+        <v>1.8142796</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.0242796</v>
+        <v>1.8142796</v>
       </c>
       <c r="R26" t="n">
-        <v>-102.42796</v>
+        <v>-181.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>86.92796</v>
+        <v>117.92796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2630,7 +2620,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-15.5</v>
+        <v>-63.5</v>
       </c>
     </row>
     <row r="27">
@@ -2654,24 +2644,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00295000</t>
+          <t>AMZN  260327C00235000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 295 P</t>
+          <t>AMZN 27MAR26 235 C</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>295</v>
+        <v>235</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2680,34 +2670,34 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>4.825</v>
+        <v>0.11</v>
       </c>
       <c r="O27" t="n">
-        <v>-965</v>
+        <v>-11</v>
       </c>
       <c r="P27" t="n">
-        <v>6.6394751</v>
+        <v>1.0242796</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.6394751</v>
+        <v>1.0242796</v>
       </c>
       <c r="R27" t="n">
-        <v>-1327.89502</v>
+        <v>-102.42796</v>
       </c>
       <c r="S27" t="n">
-        <v>362.89502</v>
+        <v>91.42796</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2720,7 +2710,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-965</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="28">
@@ -2744,24 +2734,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GOOGL 260327C00315000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 315 C</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2770,34 +2760,34 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.635</v>
+        <v>2.9196</v>
       </c>
       <c r="O28" t="n">
-        <v>-263.5</v>
+        <v>-583.92</v>
       </c>
       <c r="P28" t="n">
-        <v>6.7894876</v>
+        <v>6.6394751</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.7894876</v>
+        <v>6.6394751</v>
       </c>
       <c r="R28" t="n">
-        <v>-678.94876</v>
+        <v>-1327.89502</v>
       </c>
       <c r="S28" t="n">
-        <v>415.44876</v>
+        <v>743.97502</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2810,7 +2800,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-263.5</v>
+        <v>-583.92</v>
       </c>
     </row>
     <row r="29">
@@ -2834,24 +2824,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MSFT  260327P00360000</t>
+          <t>GOOGL 260327C00315000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 360 P</t>
+          <t>GOOGL 27MAR26 315 C</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2860,34 +2850,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.22</v>
+        <v>2.555</v>
       </c>
       <c r="O29" t="n">
-        <v>-122</v>
+        <v>-255.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1194546</v>
+        <v>6.7894876</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1194546</v>
+        <v>6.7894876</v>
       </c>
       <c r="R29" t="n">
-        <v>-211.94546</v>
+        <v>-678.94876</v>
       </c>
       <c r="S29" t="n">
-        <v>89.94546</v>
+        <v>423.44876</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2900,7 +2890,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-122</v>
+        <v>-255.5</v>
       </c>
     </row>
     <row r="30">
@@ -2924,24 +2914,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MSFT  260327C00415000</t>
+          <t>MSFT  260327P00360000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 415 C</t>
+          <t>MSFT 27MAR26 360 P</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>415</v>
+        <v>360</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2950,34 +2940,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.02</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>-202</v>
+        <v>-56.5</v>
       </c>
       <c r="P30" t="n">
-        <v>5.7894546</v>
+        <v>2.1194546</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.7894546</v>
+        <v>2.1194546</v>
       </c>
       <c r="R30" t="n">
-        <v>-578.94546</v>
+        <v>-211.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>376.94546</v>
+        <v>155.44546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2990,7 +2980,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-202</v>
+        <v>-56.5</v>
       </c>
     </row>
     <row r="31">
@@ -3014,24 +3004,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NFLX  260327P00088000</t>
+          <t>MSFT  260327C00415000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 88 P</t>
+          <t>MSFT 27MAR26 415 C</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>88</v>
+        <v>415</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3040,34 +3030,34 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.55</v>
+        <v>2.01</v>
       </c>
       <c r="O31" t="n">
-        <v>-110</v>
+        <v>-201</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9454876</v>
+        <v>5.7894546</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9454876</v>
+        <v>5.7894546</v>
       </c>
       <c r="R31" t="n">
-        <v>-189.09752</v>
+        <v>-578.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>79.09752</v>
+        <v>377.94546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3080,7 +3070,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-110</v>
+        <v>-201</v>
       </c>
     </row>
     <row r="32">
@@ -3109,23 +3099,23 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>NFLX  260327P00088000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>NFLX 27MAR26 88 P</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>425</v>
+        <v>88</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3135,29 +3125,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>9.695399999999999</v>
+        <v>0.42</v>
       </c>
       <c r="O32" t="n">
-        <v>-1939.08</v>
+        <v>-84</v>
       </c>
       <c r="P32" t="n">
-        <v>6.3644671</v>
+        <v>0.9454876</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.3644671</v>
+        <v>0.9454876</v>
       </c>
       <c r="R32" t="n">
-        <v>-1272.89342</v>
+        <v>-189.09752</v>
       </c>
       <c r="S32" t="n">
-        <v>-666.18658</v>
+        <v>105.09752</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3170,7 +3160,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-1939.08</v>
+        <v>-84</v>
       </c>
     </row>
     <row r="33">
@@ -3199,19 +3189,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SPY   261218P00505000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 505 P</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>505</v>
+        <v>425</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3225,42 +3215,312 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>10.795</v>
+        <v>8.604699999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>-2159</v>
+        <v>-1720.94</v>
       </c>
       <c r="P33" t="n">
+        <v>6.3644671</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6.3644671</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-1272.89342</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-448.04658</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>-1720.94</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>U2739721</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SMH   260327P00370000</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SMH 27MAR26 370 P</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" t="n">
+        <v>370</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-483</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4.1794876</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.1794876</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-417.94876</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-65.05124000000001</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>-483</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>U2739721</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SMH   260327C00420000</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SMH 27MAR26 420 C</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" t="n">
+        <v>420</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-247</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.8794876</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.8794876</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-287.94876</v>
+      </c>
+      <c r="S35" t="n">
+        <v>40.94876</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>-247</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>U2739721</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SPY   261218P00505000</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SPY 18DEC26 505 P</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" t="n">
+        <v>505</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-1916</v>
+      </c>
+      <c r="P36" t="n">
         <v>7.3548796</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q36" t="n">
         <v>7.3548796</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R36" t="n">
         <v>-1470.97592</v>
       </c>
-      <c r="S33" t="n">
-        <v>-688.02408</v>
-      </c>
-      <c r="T33" t="inlineStr">
+      <c r="S36" t="n">
+        <v>-445.02408</v>
+      </c>
+      <c r="T36" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="V33" t="n">
-        <v>-2159</v>
+      <c r="V36" t="n">
+        <v>-1916</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3401,7 +3661,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2636</v>
+        <v>1.2695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3431,29 +3691,29 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>390.35</v>
+        <v>392.9</v>
       </c>
       <c r="O2" t="n">
-        <v>19517.5</v>
+        <v>31432</v>
       </c>
       <c r="P2" t="n">
-        <v>419.6591247</v>
+        <v>409.022784188</v>
       </c>
       <c r="Q2" t="n">
-        <v>419.6591247</v>
+        <v>409.022784188</v>
       </c>
       <c r="R2" t="n">
-        <v>20982.956235</v>
+        <v>32721.822735</v>
       </c>
       <c r="S2" t="n">
-        <v>-1465.456235</v>
+        <v>-1289.822735</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3466,7 +3726,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>24662.313</v>
+        <v>39902.924</v>
       </c>
     </row>
     <row r="3">
@@ -3481,7 +3741,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2636</v>
+        <v>1.2695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3511,17 +3771,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>350</v>
       </c>
       <c r="N3" t="n">
-        <v>62.15</v>
+        <v>63.41</v>
       </c>
       <c r="O3" t="n">
-        <v>21752.5</v>
+        <v>22193.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.60009794299999</v>
@@ -3533,7 +3793,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S3" t="n">
-        <v>-1207.53428</v>
+        <v>-766.53428</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3546,7 +3806,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>27486.459</v>
+        <v>28174.64825</v>
       </c>
     </row>
     <row r="4">
@@ -3561,7 +3821,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1448</v>
+        <v>0.14517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3591,17 +3851,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.42</v>
+        <v>31.32</v>
       </c>
       <c r="O4" t="n">
-        <v>62840</v>
+        <v>62640</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -3613,7 +3873,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-552.47719</v>
+        <v>-752.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3626,7 +3886,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9099.232</v>
+        <v>9093.4488</v>
       </c>
     </row>
     <row r="5">
@@ -3641,7 +3901,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1417</v>
+        <v>1.1505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3671,17 +3931,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.346</v>
+        <v>4.397</v>
       </c>
       <c r="O5" t="n">
-        <v>13038</v>
+        <v>13191</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -3693,7 +3953,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-937.239091</v>
+        <v>-784.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3706,7 +3966,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14885.4846</v>
+        <v>15176.2455</v>
       </c>
     </row>
     <row r="6">
@@ -3721,7 +3981,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1417</v>
+        <v>1.1505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3751,17 +4011,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>45.05</v>
+        <v>45.12</v>
       </c>
       <c r="O6" t="n">
-        <v>45050</v>
+        <v>45120</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -3773,7 +4033,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>2040</v>
+        <v>2110</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -3786,7 +4046,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>51433.585</v>
+        <v>51910.56</v>
       </c>
     </row>
     <row r="7">
@@ -3801,7 +4061,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1417</v>
+        <v>1.1505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,17 +4091,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>532</v>
+        <v>602</v>
       </c>
       <c r="O7" t="n">
-        <v>7980</v>
+        <v>9030</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -3853,7 +4113,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>-364.17</v>
+        <v>685.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3866,7 +4126,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>9110.766</v>
+        <v>10389.015</v>
       </c>
     </row>
     <row r="8">
@@ -3881,7 +4141,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.779</v>
+        <v>0.78256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3911,17 +4171,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.836</v>
+        <v>4.86</v>
       </c>
       <c r="O8" t="n">
-        <v>48360</v>
+        <v>48600</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -3933,7 +4193,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11091.8184</v>
+        <v>11331.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -3946,7 +4206,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37672.44</v>
+        <v>38032.416</v>
       </c>
     </row>
     <row r="9">
@@ -3961,7 +4221,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.779</v>
+        <v>0.78256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3991,17 +4251,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>598.6</v>
+        <v>587</v>
       </c>
       <c r="O9" t="n">
-        <v>44895</v>
+        <v>44025</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4013,7 +4273,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>671.6496</v>
+        <v>-198.3504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4026,7 +4286,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>34973.205</v>
+        <v>34452.204</v>
       </c>
     </row>
     <row r="10">
@@ -4071,17 +4331,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.735</v>
+        <v>7.675</v>
       </c>
       <c r="O10" t="n">
-        <v>8508.5</v>
+        <v>8442.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4093,7 +4353,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-634.347947</v>
+        <v>-700.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4106,7 +4366,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8508.5</v>
+        <v>8442.5</v>
       </c>
     </row>
     <row r="11">
@@ -4151,17 +4411,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>207.54</v>
+        <v>210.16</v>
       </c>
       <c r="O11" t="n">
-        <v>6226.2</v>
+        <v>6304.8</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -4173,7 +4433,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-313</v>
+        <v>-234.4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4186,7 +4446,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6226.2</v>
+        <v>6304.8</v>
       </c>
     </row>
     <row r="12">
@@ -4231,17 +4491,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.19</v>
       </c>
       <c r="O12" t="n">
-        <v>2940</v>
+        <v>3057</v>
       </c>
       <c r="P12" t="n">
         <v>11.661666667</v>
@@ -4253,7 +4513,7 @@
         <v>3498.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-558.5</v>
+        <v>-441.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4266,7 +4526,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2940</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="13">
@@ -4311,17 +4571,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>302.28</v>
+        <v>305.56</v>
       </c>
       <c r="O13" t="n">
-        <v>30228</v>
+        <v>30556</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4333,7 +4593,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2959.755</v>
+        <v>-2631.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4346,7 +4606,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30228</v>
+        <v>30556</v>
       </c>
     </row>
     <row r="14">
@@ -4391,17 +4651,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>56.96</v>
+        <v>57.43</v>
       </c>
       <c r="O14" t="n">
-        <v>9113.6</v>
+        <v>9188.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4413,7 +4673,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-518.84</v>
+        <v>-443.64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4426,7 +4686,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9113.6</v>
+        <v>9188.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -4471,17 +4731,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>66.19</v>
+        <v>68.28</v>
       </c>
       <c r="O15" t="n">
-        <v>1114.96</v>
+        <v>1150.16</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4493,7 +4753,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>765.913421</v>
+        <v>801.113421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4506,7 +4766,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1114.96</v>
+        <v>1150.16</v>
       </c>
     </row>
     <row r="16">
@@ -4551,17 +4811,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.1048</v>
+        <v>27.0902</v>
       </c>
       <c r="O16" t="n">
-        <v>10435.35</v>
+        <v>10429.73</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4573,7 +4833,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>426.444112</v>
+        <v>420.824112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4586,7 +4846,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10435.35</v>
+        <v>10429.73</v>
       </c>
     </row>
     <row r="17">
@@ -4631,17 +4891,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>283.44</v>
+        <v>286.16</v>
       </c>
       <c r="O17" t="n">
-        <v>28344</v>
+        <v>28616</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4653,7 +4913,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-1458</v>
+        <v>-1186</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4666,7 +4926,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28344</v>
+        <v>28616</v>
       </c>
     </row>
     <row r="18">
@@ -4690,17 +4950,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>NVIDIA CORP</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4711,29 +4971,29 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>167.82</v>
+        <v>183.22</v>
       </c>
       <c r="O18" t="n">
-        <v>100692</v>
+        <v>18322</v>
       </c>
       <c r="P18" t="n">
-        <v>173.846763275</v>
+        <v>184.355</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.846763275</v>
+        <v>184.355</v>
       </c>
       <c r="R18" t="n">
-        <v>104308.057965</v>
+        <v>18435.5</v>
       </c>
       <c r="S18" t="n">
-        <v>-3616.057965</v>
+        <v>-113.5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -4742,11 +5002,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>100692</v>
+        <v>18322</v>
       </c>
     </row>
     <row r="19">
@@ -4765,65 +5025,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OPT</t>
+          <t>STK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AAPL  260327C00290000</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 290 C</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" t="n">
-        <v>290</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0255</v>
+        <v>169.14</v>
       </c>
       <c r="O19" t="n">
-        <v>2.55</v>
+        <v>101484</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1405125</v>
+        <v>173.846763275</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1405125</v>
+        <v>173.846763275</v>
       </c>
       <c r="R19" t="n">
-        <v>214.05125</v>
+        <v>104308.057965</v>
       </c>
       <c r="S19" t="n">
-        <v>-211.50125</v>
+        <v>-2824.057965</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4832,11 +5082,11 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>2.55</v>
+        <v>101484</v>
       </c>
     </row>
     <row r="20">
@@ -4865,19 +5115,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NFLX  260327C00085000</t>
+          <t>AAPL  260327C00290000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 85 C</t>
+          <t>AAPL 27MAR26 290 C</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>85</v>
+        <v>290</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -4891,29 +5141,29 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>10.7764</v>
+        <v>0.0238</v>
       </c>
       <c r="O20" t="n">
-        <v>1077.64</v>
+        <v>2.38</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5205125</v>
+        <v>2.1405125</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5205125</v>
+        <v>2.1405125</v>
       </c>
       <c r="R20" t="n">
-        <v>252.05125</v>
+        <v>214.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>825.58875</v>
+        <v>-211.67125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -4926,7 +5176,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>1077.64</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="21">
@@ -4950,60 +5200,60 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>QQQ   261218P00560000</t>
+          <t>NFLX  260327C00085000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 560 P</t>
+          <t>NFLX 27MAR26 85 C</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>560</v>
+        <v>85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>34.125</v>
+        <v>10.5606</v>
       </c>
       <c r="O21" t="n">
-        <v>6825</v>
+        <v>1056.06</v>
       </c>
       <c r="P21" t="n">
-        <v>23.5270125</v>
+        <v>2.5205125</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.5270125</v>
+        <v>2.5205125</v>
       </c>
       <c r="R21" t="n">
-        <v>4705.4025</v>
+        <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>2119.5975</v>
+        <v>804.00875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5016,7 +5266,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>6825</v>
+        <v>1056.06</v>
       </c>
     </row>
     <row r="22">
@@ -5045,19 +5295,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SPY   261218P00620000</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 620 P</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>620</v>
+        <v>560</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -5071,29 +5321,29 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>29.87</v>
+        <v>30.9185</v>
       </c>
       <c r="O22" t="n">
-        <v>5974</v>
+        <v>6183.7</v>
       </c>
       <c r="P22" t="n">
-        <v>20.1350875</v>
+        <v>23.5270125</v>
       </c>
       <c r="Q22" t="n">
-        <v>20.1350875</v>
+        <v>23.5270125</v>
       </c>
       <c r="R22" t="n">
-        <v>4027.0175</v>
+        <v>4705.4025</v>
       </c>
       <c r="S22" t="n">
-        <v>1946.9825</v>
+        <v>1478.2975</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5106,7 +5356,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5974</v>
+        <v>6183.7</v>
       </c>
     </row>
     <row r="23">
@@ -5135,23 +5385,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AAPL  260327P00250000</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 250 P</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>250</v>
+        <v>620</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -5161,33 +5411,33 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>5.75</v>
+        <v>26.75</v>
       </c>
       <c r="O23" t="n">
-        <v>-575</v>
+        <v>5350</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7694546</v>
+        <v>20.1350875</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.7694546</v>
+        <v>20.1350875</v>
       </c>
       <c r="R23" t="n">
-        <v>-176.94546</v>
+        <v>4027.0175</v>
       </c>
       <c r="S23" t="n">
-        <v>-398.05454</v>
+        <v>1322.9825</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -5196,7 +5446,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-575</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="24">
@@ -5220,24 +5470,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AAPL  260327C00285000</t>
+          <t>AAPL  260327P00250000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 285 C</t>
+          <t>AAPL 27MAR26 250 P</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -5246,34 +5496,34 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0542</v>
+        <v>3.5518</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.42</v>
+        <v>-355.18</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4194546</v>
+        <v>1.7694546</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4194546</v>
+        <v>1.7694546</v>
       </c>
       <c r="R24" t="n">
-        <v>-341.94546</v>
+        <v>-176.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>336.52546</v>
+        <v>-178.23454</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5286,7 +5536,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-5.42</v>
+        <v>-355.18</v>
       </c>
     </row>
     <row r="25">
@@ -5310,24 +5560,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AMD   260327P00185000</t>
+          <t>AAPL  260327C00285000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 185 P</t>
+          <t>AAPL 27MAR26 285 C</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -5336,34 +5586,34 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>5.075</v>
+        <v>0.0309</v>
       </c>
       <c r="O25" t="n">
-        <v>-507.5</v>
+        <v>-3.09</v>
       </c>
       <c r="P25" t="n">
-        <v>4.1794546</v>
+        <v>3.4194546</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1794546</v>
+        <v>3.4194546</v>
       </c>
       <c r="R25" t="n">
-        <v>-417.94546</v>
+        <v>-341.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>-89.55454</v>
+        <v>338.85546</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5376,7 +5626,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-507.5</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="26">
@@ -5400,24 +5650,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AMD   260327C00255000</t>
+          <t>AMD   260327P00185000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AMD 27MAR26 255 C</t>
+          <t>AMD 27MAR26 185 P</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -5426,34 +5676,34 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.065</v>
+        <v>3.5516</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.5</v>
+        <v>-355.16</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3694546</v>
+        <v>4.1794546</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3694546</v>
+        <v>4.1794546</v>
       </c>
       <c r="R26" t="n">
-        <v>-236.94546</v>
+        <v>-417.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>230.44546</v>
+        <v>62.78546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5466,7 +5716,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-6.5</v>
+        <v>-355.16</v>
       </c>
     </row>
     <row r="27">
@@ -5490,24 +5740,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AMZN  260327P00190000</t>
+          <t>AMD   260327C00255000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AMZN 27MAR26 190 P</t>
+          <t>AMD 27MAR26 255 C</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5516,34 +5766,34 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.35</v>
+        <v>0.053</v>
       </c>
       <c r="O27" t="n">
-        <v>-135</v>
+        <v>-5.3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.7994546</v>
+        <v>2.3694546</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.7994546</v>
+        <v>2.3694546</v>
       </c>
       <c r="R27" t="n">
-        <v>-179.94546</v>
+        <v>-236.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>44.94546</v>
+        <v>231.64546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5556,7 +5806,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-135</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="28">
@@ -5585,19 +5835,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GOOGL 260327P00295000</t>
+          <t>AMZN  260327P00190000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 295 P</t>
+          <t>AMZN 27MAR26 190 P</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>295</v>
+        <v>190</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -5611,29 +5861,29 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.825</v>
+        <v>0.635</v>
       </c>
       <c r="O28" t="n">
-        <v>-482.5</v>
+        <v>-63.5</v>
       </c>
       <c r="P28" t="n">
-        <v>5.9694626</v>
+        <v>1.7994546</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.9694626</v>
+        <v>1.7994546</v>
       </c>
       <c r="R28" t="n">
-        <v>-596.9462600000001</v>
+        <v>-179.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>114.44626</v>
+        <v>116.44546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5646,7 +5896,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-482.5</v>
+        <v>-63.5</v>
       </c>
     </row>
     <row r="29">
@@ -5670,24 +5920,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GOOGL 260327C00315000</t>
+          <t>GOOGL 260327P00295000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GOOGL 27MAR26 315 C</t>
+          <t>GOOGL 27MAR26 295 P</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -5696,34 +5946,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.635</v>
+        <v>2.9196</v>
       </c>
       <c r="O29" t="n">
-        <v>-263.5</v>
+        <v>-291.96</v>
       </c>
       <c r="P29" t="n">
-        <v>3.2300876</v>
+        <v>5.9694626</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2300876</v>
+        <v>5.9694626</v>
       </c>
       <c r="R29" t="n">
-        <v>-323.00876</v>
+        <v>-596.9462600000001</v>
       </c>
       <c r="S29" t="n">
-        <v>59.50876</v>
+        <v>304.98626</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5736,7 +5986,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-263.5</v>
+        <v>-291.96</v>
       </c>
     </row>
     <row r="30">
@@ -5765,19 +6015,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JPM   260327C00297500</t>
+          <t>GOOGL 260327C00315000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>JPM 27MAR26 297.5 C</t>
+          <t>GOOGL 27MAR26 315 C</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>297.5</v>
+        <v>315</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -5791,29 +6041,29 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.26</v>
+        <v>2.555</v>
       </c>
       <c r="O30" t="n">
-        <v>-226</v>
+        <v>-255.5</v>
       </c>
       <c r="P30" t="n">
-        <v>4.8394876</v>
+        <v>3.2300876</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.8394876</v>
+        <v>3.2300876</v>
       </c>
       <c r="R30" t="n">
-        <v>-483.94876</v>
+        <v>-323.00876</v>
       </c>
       <c r="S30" t="n">
-        <v>257.94876</v>
+        <v>67.50876</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5826,7 +6076,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-226</v>
+        <v>-255.5</v>
       </c>
     </row>
     <row r="31">
@@ -5850,24 +6100,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MSFT  260327P00360000</t>
+          <t>JPM   260327C00297500</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MSFT 27MAR26 360 P</t>
+          <t>JPM 27MAR26 297.5 C</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>360</v>
+        <v>297.5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -5876,34 +6126,34 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.22</v>
+        <v>1.895</v>
       </c>
       <c r="O31" t="n">
-        <v>-122</v>
+        <v>-189.5</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1094546</v>
+        <v>4.8394876</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.1094546</v>
+        <v>4.8394876</v>
       </c>
       <c r="R31" t="n">
-        <v>-210.94546</v>
+        <v>-483.94876</v>
       </c>
       <c r="S31" t="n">
-        <v>88.94546</v>
+        <v>294.44876</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -5916,7 +6166,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-122</v>
+        <v>-189.5</v>
       </c>
     </row>
     <row r="32">
@@ -5945,19 +6195,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NFLX  260327P00072000</t>
+          <t>MSFT  260327P00360000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 72 P</t>
+          <t>MSFT 27MAR26 360 P</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>72</v>
+        <v>360</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -5971,29 +6221,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0289</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.89</v>
+        <v>-56.5</v>
       </c>
       <c r="P32" t="n">
-        <v>0.8794546</v>
+        <v>2.1094546</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.8794546</v>
+        <v>2.1094546</v>
       </c>
       <c r="R32" t="n">
-        <v>-87.94546</v>
+        <v>-210.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>85.05546</v>
+        <v>154.44546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6006,7 +6256,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-2.89</v>
+        <v>-56.5</v>
       </c>
     </row>
     <row r="33">
@@ -6030,24 +6280,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NFLX  260327C00083000</t>
+          <t>NFLX  260327P00072000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 83 C</t>
+          <t>NFLX 27MAR26 72 P</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -6056,34 +6306,34 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>12.6799</v>
+        <v>0.0249</v>
       </c>
       <c r="O33" t="n">
-        <v>-1267.99</v>
+        <v>-2.49</v>
       </c>
       <c r="P33" t="n">
-        <v>3.2794546</v>
+        <v>0.8794546</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2794546</v>
+        <v>0.8794546</v>
       </c>
       <c r="R33" t="n">
-        <v>-327.94546</v>
+        <v>-87.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>-940.04454</v>
+        <v>85.45546</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6096,7 +6346,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1267.99</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="34">
@@ -6120,60 +6370,60 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>NFLX  260327C00083000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>NFLX 27MAR26 83 C</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>9.695399999999999</v>
+        <v>12.4813</v>
       </c>
       <c r="O34" t="n">
-        <v>-1939.08</v>
+        <v>-1248.13</v>
       </c>
       <c r="P34" t="n">
-        <v>6.3929546</v>
+        <v>3.2794546</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.3929546</v>
+        <v>3.2794546</v>
       </c>
       <c r="R34" t="n">
-        <v>-1278.59092</v>
+        <v>-327.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-660.4890799999999</v>
+        <v>-920.18454</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6186,7 +6436,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1939.08</v>
+        <v>-1248.13</v>
       </c>
     </row>
     <row r="35">
@@ -6215,19 +6465,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SPY   261218P00505000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 505 P</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>505</v>
+        <v>425</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -6241,42 +6491,132 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>10.795</v>
+        <v>8.604699999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>-2159</v>
+        <v>-1720.94</v>
       </c>
       <c r="P35" t="n">
+        <v>6.3929546</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>6.3929546</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-1278.59092</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-442.34908</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>-1720.94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>U6565621</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SPY   261218P00505000</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SPY 18DEC26 505 P</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" t="n">
+        <v>505</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-1916</v>
+      </c>
+      <c r="P36" t="n">
         <v>7.3496796</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q36" t="n">
         <v>7.3496796</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>-1469.93592</v>
       </c>
-      <c r="S35" t="n">
-        <v>-689.06408</v>
-      </c>
-      <c r="T35" t="inlineStr">
+      <c r="S36" t="n">
+        <v>-446.06408</v>
+      </c>
+      <c r="T36" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="V35" t="n">
-        <v>-2159</v>
+      <c r="V36" t="n">
+        <v>-1916</v>
       </c>
     </row>
   </sheetData>
@@ -6323,17 +6663,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$304,289.36</t>
+          <t>$327,461.56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$124,994.03</t>
+          <t>$105,312.60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$429,283.39</t>
+          <t>$432,774.16</t>
         </is>
       </c>
     </row>
@@ -6345,17 +6685,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$413,112.90</t>
+          <t>$450,811.34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$124,799.99</t>
+          <t>$91,948.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$537,912.90</t>
+          <t>$542,759.96</t>
         </is>
       </c>
     </row>
@@ -6373,17 +6713,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$717,402.27</t>
+          <t>$778,272.90</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$249,794.02</t>
+          <t>$197,261.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$967,196.29</t>
+          <t>$975,534.12</t>
         </is>
       </c>
     </row>
@@ -6431,14 +6771,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16 23:42:49</t>
+          <t>2026-03-17 23:45:04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2695</v>
+        <v>1.2744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>392.9</v>
+        <v>395.55</v>
       </c>
       <c r="O2" t="n">
-        <v>23574</v>
+        <v>23733</v>
       </c>
       <c r="P2" t="n">
         <v>408.869226783</v>
@@ -607,7 +607,7 @@
         <v>24532.153607</v>
       </c>
       <c r="S2" t="n">
-        <v>-958.153607</v>
+        <v>-799.153607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>29927.193</v>
+        <v>30245.3352</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2695</v>
+        <v>1.2744</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>63.41</v>
+        <v>63.65</v>
       </c>
       <c r="O3" t="n">
-        <v>15852.5</v>
+        <v>15912.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-455.853333</v>
+        <v>-395.853333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>20124.74875</v>
+        <v>20278.89</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14517</v>
+        <v>0.14529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.32</v>
+        <v>31.22</v>
       </c>
       <c r="O4" t="n">
-        <v>62640</v>
+        <v>62440</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-772.49376</v>
+        <v>-972.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9093.4488</v>
+        <v>9071.9076</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1505</v>
+        <v>1.1541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.397</v>
+        <v>4.3185</v>
       </c>
       <c r="O5" t="n">
-        <v>8794</v>
+        <v>8637</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-530.66</v>
+        <v>-687.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>10117.497</v>
+        <v>9967.9617</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1505</v>
+        <v>1.1541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="O6" t="n">
-        <v>9030</v>
+        <v>8850</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>685.83</v>
+        <v>505.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10389.015</v>
+        <v>10213.785</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78256</v>
+        <v>0.78345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.86</v>
+        <v>4.923</v>
       </c>
       <c r="O7" t="n">
-        <v>38880</v>
+        <v>39384</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1568.77315</v>
+        <v>2072.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30425.9328</v>
+        <v>30855.3948</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78256</v>
+        <v>0.78345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>587</v>
+        <v>589.7</v>
       </c>
       <c r="O8" t="n">
-        <v>44025</v>
+        <v>44227.5</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-209.098992</v>
+        <v>-6.598992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>34452.204</v>
+        <v>34650.034875</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.675</v>
+        <v>7.605</v>
       </c>
       <c r="O9" t="n">
-        <v>7675</v>
+        <v>7605</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-636.237657</v>
+        <v>-706.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7675</v>
+        <v>7605</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>210.16</v>
+        <v>209.45</v>
       </c>
       <c r="O10" t="n">
-        <v>6304.8</v>
+        <v>6283.5</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-238.3</v>
+        <v>-259.6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6304.8</v>
+        <v>6283.5</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.19</v>
+        <v>10.26</v>
       </c>
       <c r="O11" t="n">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>48.5</v>
+        <v>55.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1019</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>305.56</v>
+        <v>310.92</v>
       </c>
       <c r="O12" t="n">
-        <v>30556</v>
+        <v>31092</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>392.5</v>
+        <v>928.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30556</v>
+        <v>31092</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>57.43</v>
+        <v>57.79</v>
       </c>
       <c r="O13" t="n">
-        <v>9188.799999999999</v>
+        <v>9246.4</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-387.86</v>
+        <v>-330.26</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9188.799999999999</v>
+        <v>9246.4</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>27.0902</v>
+        <v>27.4876</v>
       </c>
       <c r="O14" t="n">
-        <v>10429.73</v>
+        <v>10582.73</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>414.827178</v>
+        <v>567.827178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10429.73</v>
+        <v>10582.73</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>183.22</v>
+        <v>181.93</v>
       </c>
       <c r="O15" t="n">
-        <v>18322</v>
+        <v>18193</v>
       </c>
       <c r="P15" t="n">
         <v>184.285</v>
@@ -1647,7 +1647,7 @@
         <v>18428.5</v>
       </c>
       <c r="S15" t="n">
-        <v>-106.5</v>
+        <v>-235.5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>18322</v>
+        <v>18193</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>155.97</v>
+        <v>154.69</v>
       </c>
       <c r="O16" t="n">
-        <v>7798.5</v>
+        <v>7734.5</v>
       </c>
       <c r="P16" t="n">
         <v>197.085</v>
@@ -1727,7 +1727,7 @@
         <v>9854.25</v>
       </c>
       <c r="S16" t="n">
-        <v>-2055.75</v>
+        <v>-2119.75</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>7798.5</v>
+        <v>7734.5</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>87.56999999999999</v>
+        <v>87.59</v>
       </c>
       <c r="O17" t="n">
-        <v>1751.4</v>
+        <v>1751.8</v>
       </c>
       <c r="P17" t="n">
         <v>124.315</v>
@@ -1807,7 +1807,7 @@
         <v>2486.3</v>
       </c>
       <c r="S17" t="n">
-        <v>-734.9</v>
+        <v>-734.5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1751.4</v>
+        <v>1751.8</v>
       </c>
     </row>
     <row r="18">
@@ -1865,17 +1865,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>169.14</v>
+        <v>170.42</v>
       </c>
       <c r="O18" t="n">
-        <v>84570</v>
+        <v>85210</v>
       </c>
       <c r="P18" t="n">
         <v>173.59385355</v>
@@ -1887,7 +1887,7 @@
         <v>86796.926775</v>
       </c>
       <c r="S18" t="n">
-        <v>-2226.926775</v>
+        <v>-1586.926775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>84570</v>
+        <v>85210</v>
       </c>
     </row>
     <row r="19">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0238</v>
+        <v>0.0076</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>0.76</v>
       </c>
       <c r="P19" t="n">
         <v>2.0105125</v>
@@ -1977,7 +1977,7 @@
         <v>201.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-198.67125</v>
+        <v>-200.29125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>2.38</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="20">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.16</v>
+        <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="P20" t="n">
         <v>4.4905125</v>
@@ -2067,7 +2067,7 @@
         <v>449.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-333.05125</v>
+        <v>-375.05125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
@@ -2135,17 +2135,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>30.9185</v>
+        <v>29.3544</v>
       </c>
       <c r="O21" t="n">
-        <v>6183.7</v>
+        <v>5870.88</v>
       </c>
       <c r="P21" t="n">
         <v>23.4605</v>
@@ -2157,7 +2157,7 @@
         <v>4692.1</v>
       </c>
       <c r="S21" t="n">
-        <v>1491.6</v>
+        <v>1178.78</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>6183.7</v>
+        <v>5870.88</v>
       </c>
     </row>
     <row r="22">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>26.75</v>
+        <v>25.74</v>
       </c>
       <c r="O22" t="n">
-        <v>5350</v>
+        <v>5148</v>
       </c>
       <c r="P22" t="n">
         <v>20.1374875</v>
@@ -2247,7 +2247,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S22" t="n">
-        <v>1322.5025</v>
+        <v>1120.5025</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5350</v>
+        <v>5148</v>
       </c>
     </row>
     <row r="23">
@@ -2315,17 +2315,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5518</v>
+        <v>2.61</v>
       </c>
       <c r="O23" t="n">
-        <v>-355.18</v>
+        <v>-261</v>
       </c>
       <c r="P23" t="n">
         <v>1.7494546</v>
@@ -2337,7 +2337,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>-180.23454</v>
+        <v>-86.05454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-355.18</v>
+        <v>-261</v>
       </c>
     </row>
     <row r="24">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0309</v>
+        <v>0.026</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.09</v>
+        <v>-2.6</v>
       </c>
       <c r="P24" t="n">
         <v>3.2494546</v>
@@ -2427,7 +2427,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>321.85546</v>
+        <v>322.34546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-3.09</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="25">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5516</v>
+        <v>2.795</v>
       </c>
       <c r="O25" t="n">
-        <v>-355.16</v>
+        <v>-279.5</v>
       </c>
       <c r="P25" t="n">
         <v>7.5800876</v>
@@ -2517,7 +2517,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S25" t="n">
-        <v>402.84876</v>
+        <v>478.50876</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-355.16</v>
+        <v>-279.5</v>
       </c>
     </row>
     <row r="26">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.635</v>
+        <v>0.28</v>
       </c>
       <c r="O26" t="n">
-        <v>-63.5</v>
+        <v>-28</v>
       </c>
       <c r="P26" t="n">
         <v>1.8142796</v>
@@ -2607,7 +2607,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>117.92796</v>
+        <v>153.42796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-63.5</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="27">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="O27" t="n">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="P27" t="n">
         <v>1.0242796</v>
@@ -2697,7 +2697,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S27" t="n">
-        <v>91.42796</v>
+        <v>88.42796</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-11</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="28">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9196</v>
+        <v>1.4291</v>
       </c>
       <c r="O28" t="n">
-        <v>-583.92</v>
+        <v>-285.82</v>
       </c>
       <c r="P28" t="n">
         <v>6.6394751</v>
@@ -2787,7 +2787,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S28" t="n">
-        <v>743.97502</v>
+        <v>1042.07502</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-583.92</v>
+        <v>-285.82</v>
       </c>
     </row>
     <row r="29">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.555</v>
+        <v>3.7578</v>
       </c>
       <c r="O29" t="n">
-        <v>-255.5</v>
+        <v>-375.78</v>
       </c>
       <c r="P29" t="n">
         <v>6.7894876</v>
@@ -2877,7 +2877,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S29" t="n">
-        <v>423.44876</v>
+        <v>303.16876</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-255.5</v>
+        <v>-375.78</v>
       </c>
     </row>
     <row r="30">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="O30" t="n">
-        <v>-56.5</v>
+        <v>-36</v>
       </c>
       <c r="P30" t="n">
         <v>2.1194546</v>
@@ -2967,7 +2967,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>155.44546</v>
+        <v>175.94546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-56.5</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="31">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.01</v>
+        <v>1.375</v>
       </c>
       <c r="O31" t="n">
-        <v>-201</v>
+        <v>-137.5</v>
       </c>
       <c r="P31" t="n">
         <v>5.7894546</v>
@@ -3057,7 +3057,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>377.94546</v>
+        <v>441.44546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-201</v>
+        <v>-137.5</v>
       </c>
     </row>
     <row r="32">
@@ -3125,17 +3125,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="O32" t="n">
-        <v>-84</v>
+        <v>-74</v>
       </c>
       <c r="P32" t="n">
         <v>0.9454876</v>
@@ -3147,7 +3147,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S32" t="n">
-        <v>105.09752</v>
+        <v>115.09752</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-84</v>
+        <v>-74</v>
       </c>
     </row>
     <row r="33">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>8.604699999999999</v>
+        <v>8.049099999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>-1720.94</v>
+        <v>-1609.82</v>
       </c>
       <c r="P33" t="n">
         <v>6.3644671</v>
@@ -3237,7 +3237,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S33" t="n">
-        <v>-448.04658</v>
+        <v>-336.92658</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1720.94</v>
+        <v>-1609.82</v>
       </c>
     </row>
     <row r="34">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>4.83</v>
+        <v>3.2859</v>
       </c>
       <c r="O34" t="n">
-        <v>-483</v>
+        <v>-328.59</v>
       </c>
       <c r="P34" t="n">
         <v>4.1794876</v>
@@ -3327,7 +3327,7 @@
         <v>-417.94876</v>
       </c>
       <c r="S34" t="n">
-        <v>-65.05124000000001</v>
+        <v>89.35876</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-483</v>
+        <v>-328.59</v>
       </c>
     </row>
     <row r="35">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.47</v>
+        <v>2.085</v>
       </c>
       <c r="O35" t="n">
-        <v>-247</v>
+        <v>-208.5</v>
       </c>
       <c r="P35" t="n">
         <v>2.8794876</v>
@@ -3417,7 +3417,7 @@
         <v>-287.94876</v>
       </c>
       <c r="S35" t="n">
-        <v>40.94876</v>
+        <v>79.44875999999999</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-247</v>
+        <v>-208.5</v>
       </c>
     </row>
     <row r="36">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>9.58</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>-1916</v>
+        <v>-1828</v>
       </c>
       <c r="P36" t="n">
         <v>7.3548796</v>
@@ -3507,7 +3507,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S36" t="n">
-        <v>-445.02408</v>
+        <v>-357.02408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-1916</v>
+        <v>-1828</v>
       </c>
     </row>
   </sheetData>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2695</v>
+        <v>1.2744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3691,17 +3691,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>392.9</v>
+        <v>395.55</v>
       </c>
       <c r="O2" t="n">
-        <v>31432</v>
+        <v>31644</v>
       </c>
       <c r="P2" t="n">
         <v>409.022784188</v>
@@ -3713,7 +3713,7 @@
         <v>32721.822735</v>
       </c>
       <c r="S2" t="n">
-        <v>-1289.822735</v>
+        <v>-1077.822735</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>39902.924</v>
+        <v>40327.1136</v>
       </c>
     </row>
     <row r="3">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2695</v>
+        <v>1.2744</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3771,17 +3771,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>350</v>
       </c>
       <c r="N3" t="n">
-        <v>63.41</v>
+        <v>63.65</v>
       </c>
       <c r="O3" t="n">
-        <v>22193.5</v>
+        <v>22277.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.60009794299999</v>
@@ -3793,7 +3793,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S3" t="n">
-        <v>-766.53428</v>
+        <v>-682.53428</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>28174.64825</v>
+        <v>28390.446</v>
       </c>
     </row>
     <row r="4">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14517</v>
+        <v>0.14529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3851,17 +3851,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.32</v>
+        <v>31.22</v>
       </c>
       <c r="O4" t="n">
-        <v>62640</v>
+        <v>62440</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -3873,7 +3873,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-752.47719</v>
+        <v>-952.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9093.4488</v>
+        <v>9071.9076</v>
       </c>
     </row>
     <row r="5">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1505</v>
+        <v>1.1541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3931,17 +3931,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.397</v>
+        <v>4.3185</v>
       </c>
       <c r="O5" t="n">
-        <v>13191</v>
+        <v>12955.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -3953,7 +3953,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-784.239091</v>
+        <v>-1019.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>15176.2455</v>
+        <v>14951.94255</v>
       </c>
     </row>
     <row r="6">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1505</v>
+        <v>1.1541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4011,17 +4011,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>45.12</v>
+        <v>44.66</v>
       </c>
       <c r="O6" t="n">
-        <v>45120</v>
+        <v>44660</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -4033,7 +4033,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>2110</v>
+        <v>1650</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>51910.56</v>
+        <v>51542.10599999999</v>
       </c>
     </row>
     <row r="7">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1505</v>
+        <v>1.1541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4091,17 +4091,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="O7" t="n">
-        <v>9030</v>
+        <v>8850</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -4113,7 +4113,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>685.83</v>
+        <v>505.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>10389.015</v>
+        <v>10213.785</v>
       </c>
     </row>
     <row r="8">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78256</v>
+        <v>0.78345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4171,17 +4171,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.86</v>
+        <v>4.923</v>
       </c>
       <c r="O8" t="n">
-        <v>48600</v>
+        <v>49230</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4193,7 +4193,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11331.8184</v>
+        <v>11961.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38032.416</v>
+        <v>38569.2435</v>
       </c>
     </row>
     <row r="9">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78256</v>
+        <v>0.78345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4251,17 +4251,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>587</v>
+        <v>589.7</v>
       </c>
       <c r="O9" t="n">
-        <v>44025</v>
+        <v>44227.5</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4273,7 +4273,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-198.3504</v>
+        <v>4.1496</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>34452.204</v>
+        <v>34650.034875</v>
       </c>
     </row>
     <row r="10">
@@ -4331,17 +4331,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.675</v>
+        <v>7.605</v>
       </c>
       <c r="O10" t="n">
-        <v>8442.5</v>
+        <v>8365.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4353,7 +4353,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-700.347947</v>
+        <v>-777.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8442.5</v>
+        <v>8365.5</v>
       </c>
     </row>
     <row r="11">
@@ -4411,17 +4411,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>210.16</v>
+        <v>209.45</v>
       </c>
       <c r="O11" t="n">
-        <v>6304.8</v>
+        <v>6283.5</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -4433,7 +4433,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-234.4</v>
+        <v>-255.7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6304.8</v>
+        <v>6283.5</v>
       </c>
     </row>
     <row r="12">
@@ -4491,17 +4491,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>10.19</v>
+        <v>10.26</v>
       </c>
       <c r="O12" t="n">
-        <v>3057</v>
+        <v>3078</v>
       </c>
       <c r="P12" t="n">
         <v>11.661666667</v>
@@ -4513,7 +4513,7 @@
         <v>3498.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-441.5</v>
+        <v>-420.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>3057</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="13">
@@ -4571,17 +4571,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>305.56</v>
+        <v>310.92</v>
       </c>
       <c r="O13" t="n">
-        <v>30556</v>
+        <v>31092</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4593,7 +4593,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2631.755</v>
+        <v>-2095.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30556</v>
+        <v>31092</v>
       </c>
     </row>
     <row r="14">
@@ -4651,17 +4651,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>57.43</v>
+        <v>57.79</v>
       </c>
       <c r="O14" t="n">
-        <v>9188.799999999999</v>
+        <v>9246.4</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4673,7 +4673,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-443.64</v>
+        <v>-386.04</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9188.799999999999</v>
+        <v>9246.4</v>
       </c>
     </row>
     <row r="15">
@@ -4731,17 +4731,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>68.28</v>
+        <v>68.63</v>
       </c>
       <c r="O15" t="n">
-        <v>1150.16</v>
+        <v>1156.06</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4753,7 +4753,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>801.113421</v>
+        <v>807.013421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1150.16</v>
+        <v>1156.06</v>
       </c>
     </row>
     <row r="16">
@@ -4811,17 +4811,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.0902</v>
+        <v>27.4876</v>
       </c>
       <c r="O16" t="n">
-        <v>10429.73</v>
+        <v>10582.73</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4833,7 +4833,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>420.824112</v>
+        <v>573.824112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10429.73</v>
+        <v>10582.73</v>
       </c>
     </row>
     <row r="17">
@@ -4891,17 +4891,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>286.16</v>
+        <v>286.89</v>
       </c>
       <c r="O17" t="n">
-        <v>28616</v>
+        <v>28689</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4913,7 +4913,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-1186</v>
+        <v>-1113</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28616</v>
+        <v>28689</v>
       </c>
     </row>
     <row r="18">
@@ -4971,17 +4971,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>183.22</v>
+        <v>181.93</v>
       </c>
       <c r="O18" t="n">
-        <v>18322</v>
+        <v>18193</v>
       </c>
       <c r="P18" t="n">
         <v>184.355</v>
@@ -4993,7 +4993,7 @@
         <v>18435.5</v>
       </c>
       <c r="S18" t="n">
-        <v>-113.5</v>
+        <v>-242.5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>18322</v>
+        <v>18193</v>
       </c>
     </row>
     <row r="19">
@@ -5051,17 +5051,17 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>600</v>
       </c>
       <c r="N19" t="n">
-        <v>169.14</v>
+        <v>170.42</v>
       </c>
       <c r="O19" t="n">
-        <v>101484</v>
+        <v>102252</v>
       </c>
       <c r="P19" t="n">
         <v>173.846763275</v>
@@ -5073,7 +5073,7 @@
         <v>104308.057965</v>
       </c>
       <c r="S19" t="n">
-        <v>-2824.057965</v>
+        <v>-2056.057965</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>101484</v>
+        <v>102252</v>
       </c>
     </row>
     <row r="20">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0238</v>
+        <v>0.0076</v>
       </c>
       <c r="O20" t="n">
-        <v>2.38</v>
+        <v>0.76</v>
       </c>
       <c r="P20" t="n">
         <v>2.1405125</v>
@@ -5163,7 +5163,7 @@
         <v>214.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-211.67125</v>
+        <v>-213.29125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>2.38</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="21">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>10.5606</v>
+        <v>9.667</v>
       </c>
       <c r="O21" t="n">
-        <v>1056.06</v>
+        <v>966.7</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5253,7 +5253,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>804.00875</v>
+        <v>714.6487499999999</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>1056.06</v>
+        <v>966.7</v>
       </c>
     </row>
     <row r="22">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>30.9185</v>
+        <v>29.3544</v>
       </c>
       <c r="O22" t="n">
-        <v>6183.7</v>
+        <v>5870.88</v>
       </c>
       <c r="P22" t="n">
         <v>23.5270125</v>
@@ -5343,7 +5343,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S22" t="n">
-        <v>1478.2975</v>
+        <v>1165.4775</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>6183.7</v>
+        <v>5870.88</v>
       </c>
     </row>
     <row r="23">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>26.75</v>
+        <v>25.74</v>
       </c>
       <c r="O23" t="n">
-        <v>5350</v>
+        <v>5148</v>
       </c>
       <c r="P23" t="n">
         <v>20.1350875</v>
@@ -5433,7 +5433,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S23" t="n">
-        <v>1322.9825</v>
+        <v>1120.9825</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5350</v>
+        <v>5148</v>
       </c>
     </row>
     <row r="24">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5518</v>
+        <v>2.61</v>
       </c>
       <c r="O24" t="n">
-        <v>-355.18</v>
+        <v>-261</v>
       </c>
       <c r="P24" t="n">
         <v>1.7694546</v>
@@ -5523,7 +5523,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>-178.23454</v>
+        <v>-84.05454</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-355.18</v>
+        <v>-261</v>
       </c>
     </row>
     <row r="25">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0309</v>
+        <v>0.026</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.09</v>
+        <v>-2.6</v>
       </c>
       <c r="P25" t="n">
         <v>3.4194546</v>
@@ -5613,7 +5613,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>338.85546</v>
+        <v>339.34546</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-3.09</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="26">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5516</v>
+        <v>2.795</v>
       </c>
       <c r="O26" t="n">
-        <v>-355.16</v>
+        <v>-279.5</v>
       </c>
       <c r="P26" t="n">
         <v>4.1794546</v>
@@ -5703,7 +5703,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>62.78546</v>
+        <v>138.44546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-355.16</v>
+        <v>-279.5</v>
       </c>
     </row>
     <row r="27">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.053</v>
+        <v>0.0256</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.3</v>
+        <v>-2.56</v>
       </c>
       <c r="P27" t="n">
         <v>2.3694546</v>
@@ -5793,7 +5793,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>231.64546</v>
+        <v>234.38546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-5.3</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="28">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.635</v>
+        <v>0.28</v>
       </c>
       <c r="O28" t="n">
-        <v>-63.5</v>
+        <v>-28</v>
       </c>
       <c r="P28" t="n">
         <v>1.7994546</v>
@@ -5883,7 +5883,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>116.44546</v>
+        <v>151.94546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-63.5</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="29">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9196</v>
+        <v>1.4291</v>
       </c>
       <c r="O29" t="n">
-        <v>-291.96</v>
+        <v>-142.91</v>
       </c>
       <c r="P29" t="n">
         <v>5.9694626</v>
@@ -5973,7 +5973,7 @@
         <v>-596.9462600000001</v>
       </c>
       <c r="S29" t="n">
-        <v>304.98626</v>
+        <v>454.03626</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-291.96</v>
+        <v>-142.91</v>
       </c>
     </row>
     <row r="30">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.555</v>
+        <v>3.7578</v>
       </c>
       <c r="O30" t="n">
-        <v>-255.5</v>
+        <v>-375.78</v>
       </c>
       <c r="P30" t="n">
         <v>3.2300876</v>
@@ -6063,7 +6063,7 @@
         <v>-323.00876</v>
       </c>
       <c r="S30" t="n">
-        <v>67.50876</v>
+        <v>-52.77124</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-255.5</v>
+        <v>-375.78</v>
       </c>
     </row>
     <row r="31">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.895</v>
+        <v>1.64</v>
       </c>
       <c r="O31" t="n">
-        <v>-189.5</v>
+        <v>-164</v>
       </c>
       <c r="P31" t="n">
         <v>4.8394876</v>
@@ -6153,7 +6153,7 @@
         <v>-483.94876</v>
       </c>
       <c r="S31" t="n">
-        <v>294.44876</v>
+        <v>319.94876</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-189.5</v>
+        <v>-164</v>
       </c>
     </row>
     <row r="32">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="O32" t="n">
-        <v>-56.5</v>
+        <v>-36</v>
       </c>
       <c r="P32" t="n">
         <v>2.1094546</v>
@@ -6243,7 +6243,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>154.44546</v>
+        <v>174.94546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-56.5</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="33">
@@ -6311,17 +6311,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0249</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>-2.49</v>
+        <v>-0.82</v>
       </c>
       <c r="P33" t="n">
         <v>0.8794546</v>
@@ -6333,7 +6333,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>85.45546</v>
+        <v>87.12546</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-2.49</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="34">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>12.4813</v>
+        <v>11.6102</v>
       </c>
       <c r="O34" t="n">
-        <v>-1248.13</v>
+        <v>-1161.02</v>
       </c>
       <c r="P34" t="n">
         <v>3.2794546</v>
@@ -6423,7 +6423,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-920.18454</v>
+        <v>-833.07454</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1248.13</v>
+        <v>-1161.02</v>
       </c>
     </row>
     <row r="35">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>8.604699999999999</v>
+        <v>8.049099999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>-1720.94</v>
+        <v>-1609.82</v>
       </c>
       <c r="P35" t="n">
         <v>6.3929546</v>
@@ -6513,7 +6513,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S35" t="n">
-        <v>-442.34908</v>
+        <v>-331.22908</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-1720.94</v>
+        <v>-1609.82</v>
       </c>
     </row>
     <row r="36">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>9.58</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>-1916</v>
+        <v>-1828</v>
       </c>
       <c r="P36" t="n">
         <v>7.3496796</v>
@@ -6603,7 +6603,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S36" t="n">
-        <v>-446.06408</v>
+        <v>-358.06408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-1916</v>
+        <v>-1828</v>
       </c>
     </row>
   </sheetData>
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$327,461.56</t>
+          <t>$329,632.77</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$105,312.60</t>
+          <t>$105,471.68</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$432,774.16</t>
+          <t>$435,104.45</t>
         </is>
       </c>
     </row>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$450,811.34</t>
+          <t>$452,749.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$91,948.61</t>
+          <t>$92,140.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$542,759.96</t>
+          <t>$544,889.58</t>
         </is>
       </c>
     </row>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$778,272.90</t>
+          <t>$782,381.87</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$197,261.22</t>
+          <t>$197,612.16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$975,534.12</t>
+          <t>$979,994.03</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17 23:45:04</t>
+          <t>2026-03-18 23:42:30</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2744</v>
+        <v>1.2606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>395.55</v>
+        <v>393.25</v>
       </c>
       <c r="O2" t="n">
-        <v>23733</v>
+        <v>23595</v>
       </c>
       <c r="P2" t="n">
         <v>408.869226783</v>
@@ -607,7 +607,7 @@
         <v>24532.153607</v>
       </c>
       <c r="S2" t="n">
-        <v>-799.153607</v>
+        <v>-937.153607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>30245.3352</v>
+        <v>29743.857</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2744</v>
+        <v>1.2606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>63.65</v>
+        <v>63.29</v>
       </c>
       <c r="O3" t="n">
-        <v>15912.5</v>
+        <v>15822.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-395.853333</v>
+        <v>-485.853333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>20278.89</v>
+        <v>19945.8435</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14529</v>
+        <v>0.14491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9071.9076</v>
+        <v>9048.180400000001</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1541</v>
+        <v>1.1452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3185</v>
+        <v>4.29</v>
       </c>
       <c r="O5" t="n">
-        <v>8637</v>
+        <v>8580</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-687.66</v>
+        <v>-744.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9967.9617</v>
+        <v>9825.816000000001</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1541</v>
+        <v>1.1452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="O6" t="n">
-        <v>8850</v>
+        <v>9120</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>505.83</v>
+        <v>775.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10213.785</v>
+        <v>10444.224</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78345</v>
+        <v>0.77884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.923</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>39384</v>
+        <v>40000</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2072.77315</v>
+        <v>2688.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30855.3948</v>
+        <v>31153.6</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78345</v>
+        <v>0.77884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>589.7</v>
+        <v>585.5</v>
       </c>
       <c r="O8" t="n">
-        <v>44227.5</v>
+        <v>43912.5</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-6.598992</v>
+        <v>-321.598992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>34650.034875</v>
+        <v>34200.8115</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.605</v>
+        <v>7.64</v>
       </c>
       <c r="O9" t="n">
-        <v>7605</v>
+        <v>7640</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-706.237657</v>
+        <v>-671.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7605</v>
+        <v>7640</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>209.45</v>
+        <v>196.09</v>
       </c>
       <c r="O10" t="n">
-        <v>6283.5</v>
+        <v>5882.7</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-259.6</v>
+        <v>-660.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6283.5</v>
+        <v>5882.7</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.26</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>1026</v>
+        <v>978</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>55.5</v>
+        <v>7.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1026</v>
+        <v>978</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>310.92</v>
+        <v>307.69</v>
       </c>
       <c r="O12" t="n">
-        <v>31092</v>
+        <v>30769</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>928.5</v>
+        <v>605.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>31092</v>
+        <v>30769</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>57.79</v>
+        <v>57.83</v>
       </c>
       <c r="O13" t="n">
-        <v>9246.4</v>
+        <v>9252.799999999999</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-330.26</v>
+        <v>-323.86</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9246.4</v>
+        <v>9252.799999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>27.4876</v>
+        <v>27.252</v>
       </c>
       <c r="O14" t="n">
-        <v>10582.73</v>
+        <v>10492.02</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>567.827178</v>
+        <v>477.117178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10582.73</v>
+        <v>10492.02</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>181.93</v>
+        <v>180.4</v>
       </c>
       <c r="O15" t="n">
-        <v>18193</v>
+        <v>18040</v>
       </c>
       <c r="P15" t="n">
         <v>184.285</v>
@@ -1647,7 +1647,7 @@
         <v>18428.5</v>
       </c>
       <c r="S15" t="n">
-        <v>-235.5</v>
+        <v>-388.5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>18193</v>
+        <v>18040</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>154.69</v>
+        <v>152.9</v>
       </c>
       <c r="O16" t="n">
-        <v>7734.5</v>
+        <v>7645</v>
       </c>
       <c r="P16" t="n">
         <v>197.085</v>
@@ -1727,7 +1727,7 @@
         <v>9854.25</v>
       </c>
       <c r="S16" t="n">
-        <v>-2119.75</v>
+        <v>-2209.25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>7734.5</v>
+        <v>7645</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>87.59</v>
+        <v>84.47</v>
       </c>
       <c r="O17" t="n">
-        <v>1751.8</v>
+        <v>1689.4</v>
       </c>
       <c r="P17" t="n">
         <v>124.315</v>
@@ -1807,7 +1807,7 @@
         <v>2486.3</v>
       </c>
       <c r="S17" t="n">
-        <v>-734.5</v>
+        <v>-796.9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1751.8</v>
+        <v>1689.4</v>
       </c>
     </row>
     <row r="18">
@@ -1865,17 +1865,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>170.42</v>
+        <v>169.02</v>
       </c>
       <c r="O18" t="n">
-        <v>85210</v>
+        <v>84510</v>
       </c>
       <c r="P18" t="n">
         <v>173.59385355</v>
@@ -1887,7 +1887,7 @@
         <v>86796.926775</v>
       </c>
       <c r="S18" t="n">
-        <v>-1586.926775</v>
+        <v>-2286.926775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>85210</v>
+        <v>84510</v>
       </c>
     </row>
     <row r="19">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0076</v>
+        <v>0.0202</v>
       </c>
       <c r="O19" t="n">
-        <v>0.76</v>
+        <v>2.02</v>
       </c>
       <c r="P19" t="n">
         <v>2.0105125</v>
@@ -1977,7 +1977,7 @@
         <v>201.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-200.29125</v>
+        <v>-199.03125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.76</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="20">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.74</v>
+        <v>0.31</v>
       </c>
       <c r="O20" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="P20" t="n">
         <v>4.4905125</v>
@@ -2067,7 +2067,7 @@
         <v>449.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-375.05125</v>
+        <v>-418.05125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
@@ -2135,17 +2135,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>29.3544</v>
+        <v>32.8324</v>
       </c>
       <c r="O21" t="n">
-        <v>5870.88</v>
+        <v>6566.48</v>
       </c>
       <c r="P21" t="n">
         <v>23.4605</v>
@@ -2157,7 +2157,7 @@
         <v>4692.1</v>
       </c>
       <c r="S21" t="n">
-        <v>1178.78</v>
+        <v>1874.38</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>5870.88</v>
+        <v>6566.48</v>
       </c>
     </row>
     <row r="22">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>25.74</v>
+        <v>29.22</v>
       </c>
       <c r="O22" t="n">
-        <v>5148</v>
+        <v>5844</v>
       </c>
       <c r="P22" t="n">
         <v>20.1374875</v>
@@ -2247,7 +2247,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S22" t="n">
-        <v>1120.5025</v>
+        <v>1816.5025</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5148</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="23">
@@ -2315,17 +2315,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.61</v>
+        <v>4.35</v>
       </c>
       <c r="O23" t="n">
-        <v>-261</v>
+        <v>-435</v>
       </c>
       <c r="P23" t="n">
         <v>1.7494546</v>
@@ -2337,7 +2337,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>-86.05454</v>
+        <v>-260.05454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-261</v>
+        <v>-435</v>
       </c>
     </row>
     <row r="24">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.026</v>
+        <v>0.03</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="P24" t="n">
         <v>3.2494546</v>
@@ -2427,7 +2427,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>322.34546</v>
+        <v>321.94546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="25">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.795</v>
+        <v>2.285</v>
       </c>
       <c r="O25" t="n">
-        <v>-279.5</v>
+        <v>-228.5</v>
       </c>
       <c r="P25" t="n">
         <v>7.5800876</v>
@@ -2517,7 +2517,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S25" t="n">
-        <v>478.50876</v>
+        <v>529.5087600000001</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-279.5</v>
+        <v>-228.5</v>
       </c>
     </row>
     <row r="26">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="O26" t="n">
-        <v>-28</v>
+        <v>-46</v>
       </c>
       <c r="P26" t="n">
         <v>1.8142796</v>
@@ -2607,7 +2607,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>153.42796</v>
+        <v>135.42796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-28</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="27">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.14</v>
+        <v>0.0707</v>
       </c>
       <c r="O27" t="n">
-        <v>-14</v>
+        <v>-7.07</v>
       </c>
       <c r="P27" t="n">
         <v>1.0242796</v>
@@ -2697,7 +2697,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S27" t="n">
-        <v>88.42796</v>
+        <v>95.35796000000001</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-14</v>
+        <v>-7.07</v>
       </c>
     </row>
     <row r="28">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.4291</v>
+        <v>2.0557</v>
       </c>
       <c r="O28" t="n">
-        <v>-285.82</v>
+        <v>-411.14</v>
       </c>
       <c r="P28" t="n">
         <v>6.6394751</v>
@@ -2787,7 +2787,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S28" t="n">
-        <v>1042.07502</v>
+        <v>916.7550199999999</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-285.82</v>
+        <v>-411.14</v>
       </c>
     </row>
     <row r="29">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.7578</v>
+        <v>2.605</v>
       </c>
       <c r="O29" t="n">
-        <v>-375.78</v>
+        <v>-260.5</v>
       </c>
       <c r="P29" t="n">
         <v>6.7894876</v>
@@ -2877,7 +2877,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S29" t="n">
-        <v>303.16876</v>
+        <v>418.44876</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-375.78</v>
+        <v>-260.5</v>
       </c>
     </row>
     <row r="30">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="O30" t="n">
-        <v>-36</v>
+        <v>-63</v>
       </c>
       <c r="P30" t="n">
         <v>2.1194546</v>
@@ -2967,7 +2967,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>175.94546</v>
+        <v>148.94546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-36</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="31">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.375</v>
+        <v>0.55</v>
       </c>
       <c r="O31" t="n">
-        <v>-137.5</v>
+        <v>-55</v>
       </c>
       <c r="P31" t="n">
         <v>5.7894546</v>
@@ -3057,7 +3057,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>441.44546</v>
+        <v>523.94546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-137.5</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="32">
@@ -3125,17 +3125,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="O32" t="n">
-        <v>-74</v>
+        <v>-66</v>
       </c>
       <c r="P32" t="n">
         <v>0.9454876</v>
@@ -3147,7 +3147,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S32" t="n">
-        <v>115.09752</v>
+        <v>123.09752</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-74</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="33">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>8.049099999999999</v>
+        <v>9.1724</v>
       </c>
       <c r="O33" t="n">
-        <v>-1609.82</v>
+        <v>-1834.48</v>
       </c>
       <c r="P33" t="n">
         <v>6.3644671</v>
@@ -3237,7 +3237,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S33" t="n">
-        <v>-336.92658</v>
+        <v>-561.58658</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1609.82</v>
+        <v>-1834.48</v>
       </c>
     </row>
     <row r="34">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2859</v>
+        <v>3.925</v>
       </c>
       <c r="O34" t="n">
-        <v>-328.59</v>
+        <v>-392.5</v>
       </c>
       <c r="P34" t="n">
         <v>4.1794876</v>
@@ -3327,7 +3327,7 @@
         <v>-417.94876</v>
       </c>
       <c r="S34" t="n">
-        <v>89.35876</v>
+        <v>25.44876</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-328.59</v>
+        <v>-392.5</v>
       </c>
     </row>
     <row r="35">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.085</v>
+        <v>1.6603</v>
       </c>
       <c r="O35" t="n">
-        <v>-208.5</v>
+        <v>-166.03</v>
       </c>
       <c r="P35" t="n">
         <v>2.8794876</v>
@@ -3417,7 +3417,7 @@
         <v>-287.94876</v>
       </c>
       <c r="S35" t="n">
-        <v>79.44875999999999</v>
+        <v>121.91876</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-208.5</v>
+        <v>-166.03</v>
       </c>
     </row>
     <row r="36">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>9.140000000000001</v>
+        <v>10.48</v>
       </c>
       <c r="O36" t="n">
-        <v>-1828</v>
+        <v>-2096</v>
       </c>
       <c r="P36" t="n">
         <v>7.3548796</v>
@@ -3507,7 +3507,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S36" t="n">
-        <v>-357.02408</v>
+        <v>-625.02408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-1828</v>
+        <v>-2096</v>
       </c>
     </row>
   </sheetData>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2744</v>
+        <v>1.2606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3691,17 +3691,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>395.55</v>
+        <v>393.25</v>
       </c>
       <c r="O2" t="n">
-        <v>31644</v>
+        <v>31460</v>
       </c>
       <c r="P2" t="n">
         <v>409.022784188</v>
@@ -3713,7 +3713,7 @@
         <v>32721.822735</v>
       </c>
       <c r="S2" t="n">
-        <v>-1077.822735</v>
+        <v>-1261.822735</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>40327.1136</v>
+        <v>39658.476</v>
       </c>
     </row>
     <row r="3">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2744</v>
+        <v>1.2606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3771,17 +3771,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>350</v>
       </c>
       <c r="N3" t="n">
-        <v>63.65</v>
+        <v>63.29</v>
       </c>
       <c r="O3" t="n">
-        <v>22277.5</v>
+        <v>22151.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.60009794299999</v>
@@ -3793,7 +3793,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S3" t="n">
-        <v>-682.53428</v>
+        <v>-808.53428</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>28390.446</v>
+        <v>27924.1809</v>
       </c>
     </row>
     <row r="4">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14529</v>
+        <v>0.14491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9071.9076</v>
+        <v>9048.180400000001</v>
       </c>
     </row>
     <row r="5">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1541</v>
+        <v>1.1452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3931,17 +3931,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3185</v>
+        <v>4.29</v>
       </c>
       <c r="O5" t="n">
-        <v>12955.5</v>
+        <v>12870</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -3953,7 +3953,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1019.739091</v>
+        <v>-1105.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14951.94255</v>
+        <v>14738.724</v>
       </c>
     </row>
     <row r="6">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1541</v>
+        <v>1.1452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4011,17 +4011,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>44.66</v>
+        <v>45.36</v>
       </c>
       <c r="O6" t="n">
-        <v>44660</v>
+        <v>45360</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -4033,7 +4033,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>1650</v>
+        <v>2350</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>51542.10599999999</v>
+        <v>51946.272</v>
       </c>
     </row>
     <row r="7">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1541</v>
+        <v>1.1452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4091,17 +4091,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="O7" t="n">
-        <v>8850</v>
+        <v>9120</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -4113,7 +4113,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>505.83</v>
+        <v>775.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>10213.785</v>
+        <v>10444.224</v>
       </c>
     </row>
     <row r="8">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78345</v>
+        <v>0.77884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4171,17 +4171,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.923</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>49230</v>
+        <v>50000</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4193,7 +4193,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11961.8184</v>
+        <v>12731.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38569.2435</v>
+        <v>38942</v>
       </c>
     </row>
     <row r="9">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78345</v>
+        <v>0.77884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4251,17 +4251,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>589.7</v>
+        <v>585.5</v>
       </c>
       <c r="O9" t="n">
-        <v>44227.5</v>
+        <v>43912.5</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4273,7 +4273,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1496</v>
+        <v>-310.8504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>34650.034875</v>
+        <v>34200.8115</v>
       </c>
     </row>
     <row r="10">
@@ -4331,17 +4331,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.605</v>
+        <v>7.64</v>
       </c>
       <c r="O10" t="n">
-        <v>8365.5</v>
+        <v>8404</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4353,7 +4353,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-777.347947</v>
+        <v>-738.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8365.5</v>
+        <v>8404</v>
       </c>
     </row>
     <row r="11">
@@ -4411,17 +4411,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>209.45</v>
+        <v>196.09</v>
       </c>
       <c r="O11" t="n">
-        <v>6283.5</v>
+        <v>5882.7</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -4433,7 +4433,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-255.7</v>
+        <v>-656.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6283.5</v>
+        <v>5882.7</v>
       </c>
     </row>
     <row r="12">
@@ -4491,17 +4491,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>10.26</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>3078</v>
+        <v>2934</v>
       </c>
       <c r="P12" t="n">
         <v>11.661666667</v>
@@ -4513,7 +4513,7 @@
         <v>3498.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-420.5</v>
+        <v>-564.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>3078</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="13">
@@ -4571,17 +4571,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>310.92</v>
+        <v>307.69</v>
       </c>
       <c r="O13" t="n">
-        <v>31092</v>
+        <v>30769</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4593,7 +4593,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2095.755</v>
+        <v>-2418.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>31092</v>
+        <v>30769</v>
       </c>
     </row>
     <row r="14">
@@ -4651,17 +4651,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>57.79</v>
+        <v>57.83</v>
       </c>
       <c r="O14" t="n">
-        <v>9246.4</v>
+        <v>9252.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4673,7 +4673,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-386.04</v>
+        <v>-379.64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9246.4</v>
+        <v>9252.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -4731,17 +4731,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>68.63</v>
+        <v>68.45</v>
       </c>
       <c r="O15" t="n">
-        <v>1156.06</v>
+        <v>1153.03</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4753,7 +4753,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>807.013421</v>
+        <v>803.983421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1156.06</v>
+        <v>1153.03</v>
       </c>
     </row>
     <row r="16">
@@ -4811,17 +4811,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.4876</v>
+        <v>27.252</v>
       </c>
       <c r="O16" t="n">
-        <v>10582.73</v>
+        <v>10492.02</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4833,7 +4833,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>573.824112</v>
+        <v>483.114112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10582.73</v>
+        <v>10492.02</v>
       </c>
     </row>
     <row r="17">
@@ -4891,17 +4891,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>286.89</v>
+        <v>287.74</v>
       </c>
       <c r="O17" t="n">
-        <v>28689</v>
+        <v>28774</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4913,7 +4913,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-1113</v>
+        <v>-1028</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28689</v>
+        <v>28774</v>
       </c>
     </row>
     <row r="18">
@@ -4971,17 +4971,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>181.93</v>
+        <v>180.4</v>
       </c>
       <c r="O18" t="n">
-        <v>18193</v>
+        <v>18040</v>
       </c>
       <c r="P18" t="n">
         <v>184.355</v>
@@ -4993,7 +4993,7 @@
         <v>18435.5</v>
       </c>
       <c r="S18" t="n">
-        <v>-242.5</v>
+        <v>-395.5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>18193</v>
+        <v>18040</v>
       </c>
     </row>
     <row r="19">
@@ -5051,17 +5051,17 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>600</v>
       </c>
       <c r="N19" t="n">
-        <v>170.42</v>
+        <v>169.02</v>
       </c>
       <c r="O19" t="n">
-        <v>102252</v>
+        <v>101412</v>
       </c>
       <c r="P19" t="n">
         <v>173.846763275</v>
@@ -5073,7 +5073,7 @@
         <v>104308.057965</v>
       </c>
       <c r="S19" t="n">
-        <v>-2056.057965</v>
+        <v>-2896.057965</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>102252</v>
+        <v>101412</v>
       </c>
     </row>
     <row r="20">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0076</v>
+        <v>0.0202</v>
       </c>
       <c r="O20" t="n">
-        <v>0.76</v>
+        <v>2.02</v>
       </c>
       <c r="P20" t="n">
         <v>2.1405125</v>
@@ -5163,7 +5163,7 @@
         <v>214.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-213.29125</v>
+        <v>-212.03125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.76</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="21">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>9.667</v>
+        <v>9.979100000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>966.7</v>
+        <v>997.91</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5253,7 +5253,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>714.6487499999999</v>
+        <v>745.85875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>966.7</v>
+        <v>997.91</v>
       </c>
     </row>
     <row r="22">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>29.3544</v>
+        <v>32.8324</v>
       </c>
       <c r="O22" t="n">
-        <v>5870.88</v>
+        <v>6566.48</v>
       </c>
       <c r="P22" t="n">
         <v>23.5270125</v>
@@ -5343,7 +5343,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S22" t="n">
-        <v>1165.4775</v>
+        <v>1861.0775</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5870.88</v>
+        <v>6566.48</v>
       </c>
     </row>
     <row r="23">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>25.74</v>
+        <v>29.22</v>
       </c>
       <c r="O23" t="n">
-        <v>5148</v>
+        <v>5844</v>
       </c>
       <c r="P23" t="n">
         <v>20.1350875</v>
@@ -5433,7 +5433,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S23" t="n">
-        <v>1120.9825</v>
+        <v>1816.9825</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5148</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="24">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.61</v>
+        <v>4.35</v>
       </c>
       <c r="O24" t="n">
-        <v>-261</v>
+        <v>-435</v>
       </c>
       <c r="P24" t="n">
         <v>1.7694546</v>
@@ -5523,7 +5523,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>-84.05454</v>
+        <v>-258.05454</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-261</v>
+        <v>-435</v>
       </c>
     </row>
     <row r="25">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.026</v>
+        <v>0.03</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="P25" t="n">
         <v>3.4194546</v>
@@ -5613,7 +5613,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>339.34546</v>
+        <v>338.94546</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="26">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.795</v>
+        <v>2.285</v>
       </c>
       <c r="O26" t="n">
-        <v>-279.5</v>
+        <v>-228.5</v>
       </c>
       <c r="P26" t="n">
         <v>4.1794546</v>
@@ -5703,7 +5703,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>138.44546</v>
+        <v>189.44546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-279.5</v>
+        <v>-228.5</v>
       </c>
     </row>
     <row r="27">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0256</v>
+        <v>0.0308</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.56</v>
+        <v>-3.08</v>
       </c>
       <c r="P27" t="n">
         <v>2.3694546</v>
@@ -5793,7 +5793,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>234.38546</v>
+        <v>233.86546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-2.56</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="28">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="O28" t="n">
-        <v>-28</v>
+        <v>-46</v>
       </c>
       <c r="P28" t="n">
         <v>1.7994546</v>
@@ -5883,7 +5883,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>151.94546</v>
+        <v>133.94546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-28</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="29">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4291</v>
+        <v>2.0557</v>
       </c>
       <c r="O29" t="n">
-        <v>-142.91</v>
+        <v>-205.57</v>
       </c>
       <c r="P29" t="n">
         <v>5.9694626</v>
@@ -5973,7 +5973,7 @@
         <v>-596.9462600000001</v>
       </c>
       <c r="S29" t="n">
-        <v>454.03626</v>
+        <v>391.37626</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-142.91</v>
+        <v>-205.57</v>
       </c>
     </row>
     <row r="30">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.7578</v>
+        <v>2.605</v>
       </c>
       <c r="O30" t="n">
-        <v>-375.78</v>
+        <v>-260.5</v>
       </c>
       <c r="P30" t="n">
         <v>3.2300876</v>
@@ -6063,7 +6063,7 @@
         <v>-323.00876</v>
       </c>
       <c r="S30" t="n">
-        <v>-52.77124</v>
+        <v>62.50876</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-375.78</v>
+        <v>-260.5</v>
       </c>
     </row>
     <row r="31">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.64</v>
+        <v>1.945</v>
       </c>
       <c r="O31" t="n">
-        <v>-164</v>
+        <v>-194.5</v>
       </c>
       <c r="P31" t="n">
         <v>4.8394876</v>
@@ -6153,7 +6153,7 @@
         <v>-483.94876</v>
       </c>
       <c r="S31" t="n">
-        <v>319.94876</v>
+        <v>289.44876</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-164</v>
+        <v>-194.5</v>
       </c>
     </row>
     <row r="32">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="O32" t="n">
-        <v>-36</v>
+        <v>-63</v>
       </c>
       <c r="P32" t="n">
         <v>2.1094546</v>
@@ -6243,7 +6243,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>174.94546</v>
+        <v>147.94546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-36</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="33">
@@ -6311,17 +6311,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.82</v>
+        <v>-1.4</v>
       </c>
       <c r="P33" t="n">
         <v>0.8794546</v>
@@ -6333,7 +6333,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>87.12546</v>
+        <v>86.54546000000001</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-0.82</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="34">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>11.6102</v>
+        <v>11.9182</v>
       </c>
       <c r="O34" t="n">
-        <v>-1161.02</v>
+        <v>-1191.82</v>
       </c>
       <c r="P34" t="n">
         <v>3.2794546</v>
@@ -6423,7 +6423,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-833.07454</v>
+        <v>-863.87454</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1161.02</v>
+        <v>-1191.82</v>
       </c>
     </row>
     <row r="35">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>8.049099999999999</v>
+        <v>9.1724</v>
       </c>
       <c r="O35" t="n">
-        <v>-1609.82</v>
+        <v>-1834.48</v>
       </c>
       <c r="P35" t="n">
         <v>6.3929546</v>
@@ -6513,7 +6513,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S35" t="n">
-        <v>-331.22908</v>
+        <v>-555.88908</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-1609.82</v>
+        <v>-1834.48</v>
       </c>
     </row>
     <row r="36">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>9.140000000000001</v>
+        <v>10.48</v>
       </c>
       <c r="O36" t="n">
-        <v>-1828</v>
+        <v>-2096</v>
       </c>
       <c r="P36" t="n">
         <v>7.3496796</v>
@@ -6603,7 +6603,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S36" t="n">
-        <v>-358.06408</v>
+        <v>-626.06408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-1828</v>
+        <v>-2096</v>
       </c>
     </row>
   </sheetData>
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$329,632.77</t>
+          <t>$327,640.53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$105,471.68</t>
+          <t>$104,942.16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$435,104.45</t>
+          <t>$432,582.69</t>
         </is>
       </c>
     </row>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$452,749.10</t>
+          <t>$450,863.98</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$92,140.48</t>
+          <t>$91,455.04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$544,889.58</t>
+          <t>$542,319.02</t>
         </is>
       </c>
     </row>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$782,381.87</t>
+          <t>$778,504.51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$197,612.16</t>
+          <t>$196,397.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$979,994.03</t>
+          <t>$974,901.71</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18 23:42:30</t>
+          <t>2026-03-19 23:43:17</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2606</v>
+        <v>1.2688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>393.25</v>
+        <v>387.25</v>
       </c>
       <c r="O2" t="n">
-        <v>23595</v>
+        <v>23235</v>
       </c>
       <c r="P2" t="n">
         <v>408.869226783</v>
@@ -607,7 +607,7 @@
         <v>24532.153607</v>
       </c>
       <c r="S2" t="n">
-        <v>-937.153607</v>
+        <v>-1297.153607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>29743.857</v>
+        <v>29480.568</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2606</v>
+        <v>1.2688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>63.29</v>
+        <v>62.39</v>
       </c>
       <c r="O3" t="n">
-        <v>15822.5</v>
+        <v>15597.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-485.853333</v>
+        <v>-710.853333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>19945.8435</v>
+        <v>19790.108</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14491</v>
+        <v>0.14534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.22</v>
+        <v>30.74</v>
       </c>
       <c r="O4" t="n">
-        <v>62440</v>
+        <v>61480</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-972.49376</v>
+        <v>-1932.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9048.180400000001</v>
+        <v>8935.503199999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1452</v>
+        <v>1.1589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.29</v>
+        <v>4.196</v>
       </c>
       <c r="O5" t="n">
-        <v>8580</v>
+        <v>8392</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-744.66</v>
+        <v>-932.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9825.816000000001</v>
+        <v>9725.488800000001</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1452</v>
+        <v>1.1589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="O6" t="n">
-        <v>9120</v>
+        <v>8910</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>775.83</v>
+        <v>565.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10444.224</v>
+        <v>10325.799</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.77884</v>
+        <v>0.78291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>4.967</v>
       </c>
       <c r="O7" t="n">
-        <v>40000</v>
+        <v>39736</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2688.77315</v>
+        <v>2424.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31153.6</v>
+        <v>31109.71176</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77884</v>
+        <v>0.78291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>585.5</v>
+        <v>555.1</v>
       </c>
       <c r="O8" t="n">
-        <v>43912.5</v>
+        <v>41632.5</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-321.598992</v>
+        <v>-2601.598992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>34200.8115</v>
+        <v>32594.500575</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.64</v>
+        <v>7.41</v>
       </c>
       <c r="O9" t="n">
-        <v>7640</v>
+        <v>7410</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-671.237657</v>
+        <v>-901.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7640</v>
+        <v>7410</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>196.09</v>
+        <v>184.78</v>
       </c>
       <c r="O10" t="n">
-        <v>5882.7</v>
+        <v>5543.4</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-660.4</v>
+        <v>-999.7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>5882.7</v>
+        <v>5543.4</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="O11" t="n">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>7.5</v>
+        <v>-3.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>978</v>
+        <v>967</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>307.69</v>
+        <v>307.13</v>
       </c>
       <c r="O12" t="n">
-        <v>30769</v>
+        <v>30713</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>605.5</v>
+        <v>549.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30769</v>
+        <v>30713</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>57.83</v>
+        <v>56.73</v>
       </c>
       <c r="O13" t="n">
-        <v>9252.799999999999</v>
+        <v>9076.799999999999</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-323.86</v>
+        <v>-499.86</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9252.799999999999</v>
+        <v>9076.799999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>27.252</v>
+        <v>27.1226</v>
       </c>
       <c r="O14" t="n">
-        <v>10492.02</v>
+        <v>10442.2</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>477.117178</v>
+        <v>427.297178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10492.02</v>
+        <v>10442.2</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>180.4</v>
+        <v>178.56</v>
       </c>
       <c r="O15" t="n">
-        <v>18040</v>
+        <v>17856</v>
       </c>
       <c r="P15" t="n">
         <v>184.285</v>
@@ -1647,7 +1647,7 @@
         <v>18428.5</v>
       </c>
       <c r="S15" t="n">
-        <v>-388.5</v>
+        <v>-572.5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>18040</v>
+        <v>17856</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>152.9</v>
+        <v>155.52</v>
       </c>
       <c r="O16" t="n">
-        <v>7645</v>
+        <v>7776</v>
       </c>
       <c r="P16" t="n">
         <v>197.085</v>
@@ -1727,7 +1727,7 @@
         <v>9854.25</v>
       </c>
       <c r="S16" t="n">
-        <v>-2209.25</v>
+        <v>-2078.25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>7645</v>
+        <v>7776</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>84.47</v>
+        <v>80.98</v>
       </c>
       <c r="O17" t="n">
-        <v>1689.4</v>
+        <v>1619.6</v>
       </c>
       <c r="P17" t="n">
         <v>124.315</v>
@@ -1807,7 +1807,7 @@
         <v>2486.3</v>
       </c>
       <c r="S17" t="n">
-        <v>-796.9</v>
+        <v>-866.7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1689.4</v>
+        <v>1619.6</v>
       </c>
     </row>
     <row r="18">
@@ -1865,17 +1865,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>169.02</v>
+        <v>166.46</v>
       </c>
       <c r="O18" t="n">
-        <v>84510</v>
+        <v>83230</v>
       </c>
       <c r="P18" t="n">
         <v>173.59385355</v>
@@ -1887,7 +1887,7 @@
         <v>86796.926775</v>
       </c>
       <c r="S18" t="n">
-        <v>-2286.926775</v>
+        <v>-3566.926775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>84510</v>
+        <v>83230</v>
       </c>
     </row>
     <row r="19">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0202</v>
+        <v>0.0011</v>
       </c>
       <c r="O19" t="n">
-        <v>2.02</v>
+        <v>0.11</v>
       </c>
       <c r="P19" t="n">
         <v>2.0105125</v>
@@ -1977,7 +1977,7 @@
         <v>201.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-199.03125</v>
+        <v>-200.94125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>2.02</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="20">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.31</v>
+        <v>0.125</v>
       </c>
       <c r="O20" t="n">
-        <v>31</v>
+        <v>12.5</v>
       </c>
       <c r="P20" t="n">
         <v>4.4905125</v>
@@ -2067,7 +2067,7 @@
         <v>449.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-418.05125</v>
+        <v>-436.55125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>31</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="21">
@@ -2135,17 +2135,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>32.8324</v>
+        <v>33.0337</v>
       </c>
       <c r="O21" t="n">
-        <v>6566.48</v>
+        <v>6606.74</v>
       </c>
       <c r="P21" t="n">
         <v>23.4605</v>
@@ -2157,7 +2157,7 @@
         <v>4692.1</v>
       </c>
       <c r="S21" t="n">
-        <v>1874.38</v>
+        <v>1914.64</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>6566.48</v>
+        <v>6606.74</v>
       </c>
     </row>
     <row r="22">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>29.22</v>
+        <v>29.305</v>
       </c>
       <c r="O22" t="n">
-        <v>5844</v>
+        <v>5861</v>
       </c>
       <c r="P22" t="n">
         <v>20.1374875</v>
@@ -2247,7 +2247,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S22" t="n">
-        <v>1816.5025</v>
+        <v>1833.5025</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5844</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="23">
@@ -2315,17 +2315,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>4.35</v>
+        <v>4.3391</v>
       </c>
       <c r="O23" t="n">
-        <v>-435</v>
+        <v>-433.91</v>
       </c>
       <c r="P23" t="n">
         <v>1.7494546</v>
@@ -2337,7 +2337,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>-260.05454</v>
+        <v>-258.96454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-435</v>
+        <v>-433.91</v>
       </c>
     </row>
     <row r="24">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.03</v>
+        <v>0.0045</v>
       </c>
       <c r="O24" t="n">
-        <v>-3</v>
+        <v>-0.45</v>
       </c>
       <c r="P24" t="n">
         <v>3.2494546</v>
@@ -2427,7 +2427,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>321.94546</v>
+        <v>324.49546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-3</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="25">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.285</v>
+        <v>1.185</v>
       </c>
       <c r="O25" t="n">
-        <v>-228.5</v>
+        <v>-118.5</v>
       </c>
       <c r="P25" t="n">
         <v>7.5800876</v>
@@ -2517,7 +2517,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S25" t="n">
-        <v>529.5087600000001</v>
+        <v>639.5087600000001</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-228.5</v>
+        <v>-118.5</v>
       </c>
     </row>
     <row r="26">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.46</v>
+        <v>0.385</v>
       </c>
       <c r="O26" t="n">
-        <v>-46</v>
+        <v>-38.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.8142796</v>
@@ -2607,7 +2607,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>135.42796</v>
+        <v>142.92796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-46</v>
+        <v>-38.5</v>
       </c>
     </row>
     <row r="27">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0707</v>
+        <v>0.056</v>
       </c>
       <c r="O27" t="n">
-        <v>-7.07</v>
+        <v>-5.6</v>
       </c>
       <c r="P27" t="n">
         <v>1.0242796</v>
@@ -2697,7 +2697,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S27" t="n">
-        <v>95.35796000000001</v>
+        <v>96.82796</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-7.07</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="28">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.0557</v>
+        <v>1.752</v>
       </c>
       <c r="O28" t="n">
-        <v>-411.14</v>
+        <v>-350.4</v>
       </c>
       <c r="P28" t="n">
         <v>6.6394751</v>
@@ -2787,7 +2787,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S28" t="n">
-        <v>916.7550199999999</v>
+        <v>977.49502</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-411.14</v>
+        <v>-350.4</v>
       </c>
     </row>
     <row r="29">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.605</v>
+        <v>2.065</v>
       </c>
       <c r="O29" t="n">
-        <v>-260.5</v>
+        <v>-206.5</v>
       </c>
       <c r="P29" t="n">
         <v>6.7894876</v>
@@ -2877,7 +2877,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S29" t="n">
-        <v>418.44876</v>
+        <v>472.44876</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-260.5</v>
+        <v>-206.5</v>
       </c>
     </row>
     <row r="30">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.63</v>
+        <v>0.475</v>
       </c>
       <c r="O30" t="n">
-        <v>-63</v>
+        <v>-47.5</v>
       </c>
       <c r="P30" t="n">
         <v>2.1194546</v>
@@ -2967,7 +2967,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>148.94546</v>
+        <v>164.44546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-63</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="31">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.55</v>
+        <v>0.225</v>
       </c>
       <c r="O31" t="n">
-        <v>-55</v>
+        <v>-22.5</v>
       </c>
       <c r="P31" t="n">
         <v>5.7894546</v>
@@ -3057,7 +3057,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>523.94546</v>
+        <v>556.44546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-55</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="32">
@@ -3125,17 +3125,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>0.33</v>
+        <v>0.595</v>
       </c>
       <c r="O32" t="n">
-        <v>-66</v>
+        <v>-119</v>
       </c>
       <c r="P32" t="n">
         <v>0.9454876</v>
@@ -3147,7 +3147,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S32" t="n">
-        <v>123.09752</v>
+        <v>70.09752</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-66</v>
+        <v>-119</v>
       </c>
     </row>
     <row r="33">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>9.1724</v>
+        <v>9.07</v>
       </c>
       <c r="O33" t="n">
-        <v>-1834.48</v>
+        <v>-1814</v>
       </c>
       <c r="P33" t="n">
         <v>6.3644671</v>
@@ -3237,7 +3237,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S33" t="n">
-        <v>-561.58658</v>
+        <v>-541.10658</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1834.48</v>
+        <v>-1814</v>
       </c>
     </row>
     <row r="34">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.925</v>
+        <v>2.8208</v>
       </c>
       <c r="O34" t="n">
-        <v>-392.5</v>
+        <v>-282.08</v>
       </c>
       <c r="P34" t="n">
         <v>4.1794876</v>
@@ -3327,7 +3327,7 @@
         <v>-417.94876</v>
       </c>
       <c r="S34" t="n">
-        <v>25.44876</v>
+        <v>135.86876</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-392.5</v>
+        <v>-282.08</v>
       </c>
     </row>
     <row r="35">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.6603</v>
+        <v>1.195</v>
       </c>
       <c r="O35" t="n">
-        <v>-166.03</v>
+        <v>-119.5</v>
       </c>
       <c r="P35" t="n">
         <v>2.8794876</v>
@@ -3417,7 +3417,7 @@
         <v>-287.94876</v>
       </c>
       <c r="S35" t="n">
-        <v>121.91876</v>
+        <v>168.44876</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-166.03</v>
+        <v>-119.5</v>
       </c>
     </row>
     <row r="36">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>10.48</v>
+        <v>10.215</v>
       </c>
       <c r="O36" t="n">
-        <v>-2096</v>
+        <v>-2043</v>
       </c>
       <c r="P36" t="n">
         <v>7.3548796</v>
@@ -3507,7 +3507,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S36" t="n">
-        <v>-625.02408</v>
+        <v>-572.02408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-2096</v>
+        <v>-2043</v>
       </c>
     </row>
   </sheetData>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2606</v>
+        <v>1.2688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3691,17 +3691,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>393.25</v>
+        <v>387.25</v>
       </c>
       <c r="O2" t="n">
-        <v>31460</v>
+        <v>30980</v>
       </c>
       <c r="P2" t="n">
         <v>409.022784188</v>
@@ -3713,7 +3713,7 @@
         <v>32721.822735</v>
       </c>
       <c r="S2" t="n">
-        <v>-1261.822735</v>
+        <v>-1741.822735</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>39658.476</v>
+        <v>39307.424</v>
       </c>
     </row>
     <row r="3">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2606</v>
+        <v>1.2688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3771,17 +3771,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>350</v>
       </c>
       <c r="N3" t="n">
-        <v>63.29</v>
+        <v>62.39</v>
       </c>
       <c r="O3" t="n">
-        <v>22151.5</v>
+        <v>21836.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.60009794299999</v>
@@ -3793,7 +3793,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S3" t="n">
-        <v>-808.53428</v>
+        <v>-1123.53428</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>27924.1809</v>
+        <v>27706.1512</v>
       </c>
     </row>
     <row r="4">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14491</v>
+        <v>0.14534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3851,17 +3851,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.22</v>
+        <v>30.74</v>
       </c>
       <c r="O4" t="n">
-        <v>62440</v>
+        <v>61480</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -3873,7 +3873,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-952.47719</v>
+        <v>-1912.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9048.180400000001</v>
+        <v>8935.503199999999</v>
       </c>
     </row>
     <row r="5">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1452</v>
+        <v>1.1589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3931,17 +3931,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.29</v>
+        <v>4.196</v>
       </c>
       <c r="O5" t="n">
-        <v>12870</v>
+        <v>12588</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -3953,7 +3953,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1105.239091</v>
+        <v>-1387.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14738.724</v>
+        <v>14588.2332</v>
       </c>
     </row>
     <row r="6">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1452</v>
+        <v>1.1589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4011,17 +4011,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>45.36</v>
+        <v>43.93</v>
       </c>
       <c r="O6" t="n">
-        <v>45360</v>
+        <v>43930</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -4033,7 +4033,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>2350</v>
+        <v>920</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>51946.272</v>
+        <v>50910.477</v>
       </c>
     </row>
     <row r="7">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1452</v>
+        <v>1.1589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4091,17 +4091,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="O7" t="n">
-        <v>9120</v>
+        <v>8910</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -4113,7 +4113,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>775.83</v>
+        <v>565.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>10444.224</v>
+        <v>10325.799</v>
       </c>
     </row>
     <row r="8">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77884</v>
+        <v>0.78291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4171,17 +4171,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>4.967</v>
       </c>
       <c r="O8" t="n">
-        <v>50000</v>
+        <v>49670</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4193,7 +4193,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12731.8184</v>
+        <v>12401.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38942</v>
+        <v>38887.1397</v>
       </c>
     </row>
     <row r="9">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.77884</v>
+        <v>0.78291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4251,17 +4251,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>585.5</v>
+        <v>555.1</v>
       </c>
       <c r="O9" t="n">
-        <v>43912.5</v>
+        <v>41632.5</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4273,7 +4273,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-310.8504</v>
+        <v>-2590.8504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>34200.8115</v>
+        <v>32594.500575</v>
       </c>
     </row>
     <row r="10">
@@ -4331,17 +4331,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.64</v>
+        <v>7.41</v>
       </c>
       <c r="O10" t="n">
-        <v>8404</v>
+        <v>8151</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4353,7 +4353,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-738.847947</v>
+        <v>-991.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8404</v>
+        <v>8151</v>
       </c>
     </row>
     <row r="11">
@@ -4411,17 +4411,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>196.09</v>
+        <v>184.78</v>
       </c>
       <c r="O11" t="n">
-        <v>5882.7</v>
+        <v>5543.4</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -4433,7 +4433,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-656.5</v>
+        <v>-995.8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5882.7</v>
+        <v>5543.4</v>
       </c>
     </row>
     <row r="12">
@@ -4491,17 +4491,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>9.779999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="O12" t="n">
-        <v>2934</v>
+        <v>2901</v>
       </c>
       <c r="P12" t="n">
         <v>11.661666667</v>
@@ -4513,7 +4513,7 @@
         <v>3498.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-564.5</v>
+        <v>-597.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2934</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="13">
@@ -4571,17 +4571,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>307.69</v>
+        <v>307.13</v>
       </c>
       <c r="O13" t="n">
-        <v>30769</v>
+        <v>30713</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4593,7 +4593,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2418.755</v>
+        <v>-2474.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30769</v>
+        <v>30713</v>
       </c>
     </row>
     <row r="14">
@@ -4651,17 +4651,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>57.83</v>
+        <v>56.73</v>
       </c>
       <c r="O14" t="n">
-        <v>9252.799999999999</v>
+        <v>9076.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4673,7 +4673,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-379.64</v>
+        <v>-555.64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9252.799999999999</v>
+        <v>9076.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -4731,17 +4731,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>68.45</v>
+        <v>67.69</v>
       </c>
       <c r="O15" t="n">
-        <v>1153.03</v>
+        <v>1140.22</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4753,7 +4753,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>803.983421</v>
+        <v>791.173421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1153.03</v>
+        <v>1140.22</v>
       </c>
     </row>
     <row r="16">
@@ -4811,17 +4811,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.252</v>
+        <v>27.1226</v>
       </c>
       <c r="O16" t="n">
-        <v>10492.02</v>
+        <v>10442.2</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4833,7 +4833,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>483.114112</v>
+        <v>433.294112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10492.02</v>
+        <v>10442.2</v>
       </c>
     </row>
     <row r="17">
@@ -4891,17 +4891,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>287.74</v>
+        <v>287.97</v>
       </c>
       <c r="O17" t="n">
-        <v>28774</v>
+        <v>28797</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4913,7 +4913,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-1028</v>
+        <v>-1005</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28774</v>
+        <v>28797</v>
       </c>
     </row>
     <row r="18">
@@ -4971,17 +4971,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>180.4</v>
+        <v>178.56</v>
       </c>
       <c r="O18" t="n">
-        <v>18040</v>
+        <v>17856</v>
       </c>
       <c r="P18" t="n">
         <v>184.355</v>
@@ -4993,7 +4993,7 @@
         <v>18435.5</v>
       </c>
       <c r="S18" t="n">
-        <v>-395.5</v>
+        <v>-579.5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>18040</v>
+        <v>17856</v>
       </c>
     </row>
     <row r="19">
@@ -5051,17 +5051,17 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>600</v>
       </c>
       <c r="N19" t="n">
-        <v>169.02</v>
+        <v>166.46</v>
       </c>
       <c r="O19" t="n">
-        <v>101412</v>
+        <v>99876</v>
       </c>
       <c r="P19" t="n">
         <v>173.846763275</v>
@@ -5073,7 +5073,7 @@
         <v>104308.057965</v>
       </c>
       <c r="S19" t="n">
-        <v>-2896.057965</v>
+        <v>-4432.057965</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>101412</v>
+        <v>99876</v>
       </c>
     </row>
     <row r="20">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0202</v>
+        <v>0.0011</v>
       </c>
       <c r="O20" t="n">
-        <v>2.02</v>
+        <v>0.11</v>
       </c>
       <c r="P20" t="n">
         <v>2.1405125</v>
@@ -5163,7 +5163,7 @@
         <v>214.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-212.03125</v>
+        <v>-213.94125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>2.02</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="21">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>9.979100000000001</v>
+        <v>7.115</v>
       </c>
       <c r="O21" t="n">
-        <v>997.91</v>
+        <v>711.5</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5253,7 +5253,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>745.85875</v>
+        <v>459.44875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>997.91</v>
+        <v>711.5</v>
       </c>
     </row>
     <row r="22">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>32.8324</v>
+        <v>33.0337</v>
       </c>
       <c r="O22" t="n">
-        <v>6566.48</v>
+        <v>6606.74</v>
       </c>
       <c r="P22" t="n">
         <v>23.5270125</v>
@@ -5343,7 +5343,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S22" t="n">
-        <v>1861.0775</v>
+        <v>1901.3375</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>6566.48</v>
+        <v>6606.74</v>
       </c>
     </row>
     <row r="23">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>29.22</v>
+        <v>29.305</v>
       </c>
       <c r="O23" t="n">
-        <v>5844</v>
+        <v>5861</v>
       </c>
       <c r="P23" t="n">
         <v>20.1350875</v>
@@ -5433,7 +5433,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S23" t="n">
-        <v>1816.9825</v>
+        <v>1833.9825</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5844</v>
+        <v>5861</v>
       </c>
     </row>
     <row r="24">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.35</v>
+        <v>4.3391</v>
       </c>
       <c r="O24" t="n">
-        <v>-435</v>
+        <v>-433.91</v>
       </c>
       <c r="P24" t="n">
         <v>1.7694546</v>
@@ -5523,7 +5523,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>-258.05454</v>
+        <v>-256.96454</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-435</v>
+        <v>-433.91</v>
       </c>
     </row>
     <row r="25">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.03</v>
+        <v>0.0045</v>
       </c>
       <c r="O25" t="n">
-        <v>-3</v>
+        <v>-0.45</v>
       </c>
       <c r="P25" t="n">
         <v>3.4194546</v>
@@ -5613,7 +5613,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>338.94546</v>
+        <v>341.49546</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-3</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="26">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.285</v>
+        <v>1.185</v>
       </c>
       <c r="O26" t="n">
-        <v>-228.5</v>
+        <v>-118.5</v>
       </c>
       <c r="P26" t="n">
         <v>4.1794546</v>
@@ -5703,7 +5703,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>189.44546</v>
+        <v>299.44546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-228.5</v>
+        <v>-118.5</v>
       </c>
     </row>
     <row r="27">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0308</v>
+        <v>0.0357</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.08</v>
+        <v>-3.57</v>
       </c>
       <c r="P27" t="n">
         <v>2.3694546</v>
@@ -5793,7 +5793,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>233.86546</v>
+        <v>233.37546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-3.08</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="28">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.46</v>
+        <v>0.385</v>
       </c>
       <c r="O28" t="n">
-        <v>-46</v>
+        <v>-38.5</v>
       </c>
       <c r="P28" t="n">
         <v>1.7994546</v>
@@ -5883,7 +5883,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>133.94546</v>
+        <v>141.44546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-46</v>
+        <v>-38.5</v>
       </c>
     </row>
     <row r="29">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.0557</v>
+        <v>1.752</v>
       </c>
       <c r="O29" t="n">
-        <v>-205.57</v>
+        <v>-175.2</v>
       </c>
       <c r="P29" t="n">
         <v>5.9694626</v>
@@ -5973,7 +5973,7 @@
         <v>-596.9462600000001</v>
       </c>
       <c r="S29" t="n">
-        <v>391.37626</v>
+        <v>421.74626</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-205.57</v>
+        <v>-175.2</v>
       </c>
     </row>
     <row r="30">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.605</v>
+        <v>2.065</v>
       </c>
       <c r="O30" t="n">
-        <v>-260.5</v>
+        <v>-206.5</v>
       </c>
       <c r="P30" t="n">
         <v>3.2300876</v>
@@ -6063,7 +6063,7 @@
         <v>-323.00876</v>
       </c>
       <c r="S30" t="n">
-        <v>62.50876</v>
+        <v>116.50876</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-260.5</v>
+        <v>-206.5</v>
       </c>
     </row>
     <row r="31">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.945</v>
+        <v>1.525</v>
       </c>
       <c r="O31" t="n">
-        <v>-194.5</v>
+        <v>-152.5</v>
       </c>
       <c r="P31" t="n">
         <v>4.8394876</v>
@@ -6153,7 +6153,7 @@
         <v>-483.94876</v>
       </c>
       <c r="S31" t="n">
-        <v>289.44876</v>
+        <v>331.44876</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-194.5</v>
+        <v>-152.5</v>
       </c>
     </row>
     <row r="32">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>0.63</v>
+        <v>0.475</v>
       </c>
       <c r="O32" t="n">
-        <v>-63</v>
+        <v>-47.5</v>
       </c>
       <c r="P32" t="n">
         <v>2.1094546</v>
@@ -6243,7 +6243,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>147.94546</v>
+        <v>163.44546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-63</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="33">
@@ -6311,17 +6311,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>0.014</v>
+        <v>0.0145</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.4</v>
+        <v>-1.45</v>
       </c>
       <c r="P33" t="n">
         <v>0.8794546</v>
@@ -6333,7 +6333,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>86.54546000000001</v>
+        <v>86.49545999999999</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1.4</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="34">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>11.9182</v>
+        <v>9.0097</v>
       </c>
       <c r="O34" t="n">
-        <v>-1191.82</v>
+        <v>-900.97</v>
       </c>
       <c r="P34" t="n">
         <v>3.2794546</v>
@@ -6423,7 +6423,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-863.87454</v>
+        <v>-573.02454</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-1191.82</v>
+        <v>-900.97</v>
       </c>
     </row>
     <row r="35">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>9.1724</v>
+        <v>9.07</v>
       </c>
       <c r="O35" t="n">
-        <v>-1834.48</v>
+        <v>-1814</v>
       </c>
       <c r="P35" t="n">
         <v>6.3929546</v>
@@ -6513,7 +6513,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S35" t="n">
-        <v>-555.88908</v>
+        <v>-535.40908</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-1834.48</v>
+        <v>-1814</v>
       </c>
     </row>
     <row r="36">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>10.48</v>
+        <v>10.215</v>
       </c>
       <c r="O36" t="n">
-        <v>-2096</v>
+        <v>-2043</v>
       </c>
       <c r="P36" t="n">
         <v>7.3496796</v>
@@ -6603,7 +6603,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S36" t="n">
-        <v>-626.06408</v>
+        <v>-573.06408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-2096</v>
+        <v>-2043</v>
       </c>
     </row>
   </sheetData>
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$327,640.53</t>
+          <t>$323,474.59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$104,942.16</t>
+          <t>$105,313.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$432,582.69</t>
+          <t>$428,788.50</t>
         </is>
       </c>
     </row>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$450,863.98</t>
+          <t>$444,995.15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$91,455.04</t>
+          <t>$91,954.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$542,319.02</t>
+          <t>$536,949.26</t>
         </is>
       </c>
     </row>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$778,504.51</t>
+          <t>$768,469.74</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$196,397.20</t>
+          <t>$197,268.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$974,901.71</t>
+          <t>$965,737.76</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19 23:43:17</t>
+          <t>2026-03-20 23:43:07</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2688</v>
+        <v>1.269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>387.25</v>
+        <v>383.6</v>
       </c>
       <c r="O2" t="n">
-        <v>23235</v>
+        <v>23016</v>
       </c>
       <c r="P2" t="n">
         <v>408.869226783</v>
@@ -607,7 +607,7 @@
         <v>24532.153607</v>
       </c>
       <c r="S2" t="n">
-        <v>-1297.153607</v>
+        <v>-1516.153607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>29480.568</v>
+        <v>29207.304</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2688</v>
+        <v>1.269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>62.39</v>
+        <v>61</v>
       </c>
       <c r="O3" t="n">
-        <v>15597.5</v>
+        <v>15250</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-710.853333</v>
+        <v>-1058.353333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>19790.108</v>
+        <v>19352.25</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14534</v>
+        <v>0.1448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.74</v>
+        <v>30.62</v>
       </c>
       <c r="O4" t="n">
-        <v>61480</v>
+        <v>61240</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-1932.49376</v>
+        <v>-2172.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8935.503199999999</v>
+        <v>8867.552000000001</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1589</v>
+        <v>1.1571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.196</v>
+        <v>4.1015</v>
       </c>
       <c r="O5" t="n">
-        <v>8392</v>
+        <v>8203</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-932.66</v>
+        <v>-1121.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9725.488800000001</v>
+        <v>9491.6913</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1589</v>
+        <v>1.1571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>594</v>
+        <v>548</v>
       </c>
       <c r="O6" t="n">
-        <v>8910</v>
+        <v>8220</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>565.83</v>
+        <v>-124.17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10325.799</v>
+        <v>9511.362000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78291</v>
+        <v>0.7798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.967</v>
+        <v>4.95</v>
       </c>
       <c r="O7" t="n">
-        <v>39736</v>
+        <v>39600</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2424.77315</v>
+        <v>2288.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31109.71176</v>
+        <v>30880.08</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78291</v>
+        <v>0.7798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>555.1</v>
+        <v>551.99</v>
       </c>
       <c r="O8" t="n">
-        <v>41632.5</v>
+        <v>41399.25</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-2601.598992</v>
+        <v>-2834.848992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>32594.500575</v>
+        <v>32283.13515</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.41</v>
+        <v>7.36</v>
       </c>
       <c r="O9" t="n">
-        <v>7410</v>
+        <v>7360</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-901.237657</v>
+        <v>-951.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7410</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>184.78</v>
+        <v>179.13</v>
       </c>
       <c r="O10" t="n">
-        <v>5543.4</v>
+        <v>5373.9</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-999.7</v>
+        <v>-1169.2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>5543.4</v>
+        <v>5373.9</v>
       </c>
     </row>
     <row r="11">
@@ -1305,7 +1305,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>307.13</v>
+        <v>301</v>
       </c>
       <c r="O12" t="n">
-        <v>30713</v>
+        <v>30100</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>549.5</v>
+        <v>-63.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30713</v>
+        <v>30100</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>56.73</v>
+        <v>56.05</v>
       </c>
       <c r="O13" t="n">
-        <v>9076.799999999999</v>
+        <v>8968</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-499.86</v>
+        <v>-608.66</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9076.799999999999</v>
+        <v>8968</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>27.1226</v>
+        <v>27.1359</v>
       </c>
       <c r="O14" t="n">
-        <v>10442.2</v>
+        <v>10447.32</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>427.297178</v>
+        <v>432.417178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10442.2</v>
+        <v>10447.32</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>178.56</v>
+        <v>172.7</v>
       </c>
       <c r="O15" t="n">
-        <v>17856</v>
+        <v>17270</v>
       </c>
       <c r="P15" t="n">
         <v>184.285</v>
@@ -1647,7 +1647,7 @@
         <v>18428.5</v>
       </c>
       <c r="S15" t="n">
-        <v>-572.5</v>
+        <v>-1158.5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>17856</v>
+        <v>17270</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>155.52</v>
+        <v>149.68</v>
       </c>
       <c r="O16" t="n">
-        <v>7776</v>
+        <v>7484</v>
       </c>
       <c r="P16" t="n">
         <v>197.085</v>
@@ -1727,7 +1727,7 @@
         <v>9854.25</v>
       </c>
       <c r="S16" t="n">
-        <v>-2078.25</v>
+        <v>-2370.25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>7776</v>
+        <v>7484</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>80.98</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>1619.6</v>
+        <v>1577</v>
       </c>
       <c r="P17" t="n">
         <v>124.315</v>
@@ -1807,7 +1807,7 @@
         <v>2486.3</v>
       </c>
       <c r="S17" t="n">
-        <v>-866.7</v>
+        <v>-909.3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1619.6</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="18">
@@ -1865,17 +1865,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>166.46</v>
+        <v>164.9</v>
       </c>
       <c r="O18" t="n">
-        <v>83230</v>
+        <v>82450</v>
       </c>
       <c r="P18" t="n">
         <v>173.59385355</v>
@@ -1887,7 +1887,7 @@
         <v>86796.926775</v>
       </c>
       <c r="S18" t="n">
-        <v>-3566.926775</v>
+        <v>-4346.926775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>83230</v>
+        <v>82450</v>
       </c>
     </row>
     <row r="19">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="P19" t="n">
         <v>2.0105125</v>
@@ -1977,7 +1977,7 @@
         <v>201.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-200.94125</v>
+        <v>-200.95125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="20">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.125</v>
+        <v>0.1064</v>
       </c>
       <c r="O20" t="n">
-        <v>12.5</v>
+        <v>10.64</v>
       </c>
       <c r="P20" t="n">
         <v>4.4905125</v>
@@ -2067,7 +2067,7 @@
         <v>449.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-436.55125</v>
+        <v>-438.41125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>12.5</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="21">
@@ -2135,17 +2135,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>33.0337</v>
+        <v>37.5848</v>
       </c>
       <c r="O21" t="n">
-        <v>6606.74</v>
+        <v>7516.96</v>
       </c>
       <c r="P21" t="n">
         <v>23.4605</v>
@@ -2157,7 +2157,7 @@
         <v>4692.1</v>
       </c>
       <c r="S21" t="n">
-        <v>1914.64</v>
+        <v>2824.86</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>6606.74</v>
+        <v>7516.96</v>
       </c>
     </row>
     <row r="22">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>29.305</v>
+        <v>33.415</v>
       </c>
       <c r="O22" t="n">
-        <v>5861</v>
+        <v>6683</v>
       </c>
       <c r="P22" t="n">
         <v>20.1374875</v>
@@ -2247,7 +2247,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S22" t="n">
-        <v>1833.5025</v>
+        <v>2655.5025</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>5861</v>
+        <v>6683</v>
       </c>
     </row>
     <row r="23">
@@ -2315,17 +2315,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3391</v>
+        <v>4.3746</v>
       </c>
       <c r="O23" t="n">
-        <v>-433.91</v>
+        <v>-437.46</v>
       </c>
       <c r="P23" t="n">
         <v>1.7494546</v>
@@ -2337,7 +2337,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>-258.96454</v>
+        <v>-262.51454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-433.91</v>
+        <v>-437.46</v>
       </c>
     </row>
     <row r="24">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0045</v>
+        <v>0.004</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="P24" t="n">
         <v>3.2494546</v>
@@ -2427,7 +2427,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>324.49546</v>
+        <v>324.54546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="25">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.185</v>
+        <v>1.4161</v>
       </c>
       <c r="O25" t="n">
-        <v>-118.5</v>
+        <v>-141.61</v>
       </c>
       <c r="P25" t="n">
         <v>7.5800876</v>
@@ -2517,7 +2517,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S25" t="n">
-        <v>639.5087600000001</v>
+        <v>616.39876</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-118.5</v>
+        <v>-141.61</v>
       </c>
     </row>
     <row r="26">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.385</v>
+        <v>0.525</v>
       </c>
       <c r="O26" t="n">
-        <v>-38.5</v>
+        <v>-52.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.8142796</v>
@@ -2607,7 +2607,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>142.92796</v>
+        <v>128.92796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-38.5</v>
+        <v>-52.5</v>
       </c>
     </row>
     <row r="27">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.056</v>
+        <v>0.0362</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.6</v>
+        <v>-3.62</v>
       </c>
       <c r="P27" t="n">
         <v>1.0242796</v>
@@ -2697,7 +2697,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S27" t="n">
-        <v>96.82796</v>
+        <v>98.80795999999999</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-5.6</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="28">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.752</v>
+        <v>2.865</v>
       </c>
       <c r="O28" t="n">
-        <v>-350.4</v>
+        <v>-573</v>
       </c>
       <c r="P28" t="n">
         <v>6.6394751</v>
@@ -2787,7 +2787,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S28" t="n">
-        <v>977.49502</v>
+        <v>754.89502</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-350.4</v>
+        <v>-573</v>
       </c>
     </row>
     <row r="29">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.065</v>
+        <v>0.615</v>
       </c>
       <c r="O29" t="n">
-        <v>-206.5</v>
+        <v>-61.5</v>
       </c>
       <c r="P29" t="n">
         <v>6.7894876</v>
@@ -2877,7 +2877,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S29" t="n">
-        <v>472.44876</v>
+        <v>617.44876</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-206.5</v>
+        <v>-61.5</v>
       </c>
     </row>
     <row r="30">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.475</v>
+        <v>0.755</v>
       </c>
       <c r="O30" t="n">
-        <v>-47.5</v>
+        <v>-75.5</v>
       </c>
       <c r="P30" t="n">
         <v>2.1194546</v>
@@ -2967,7 +2967,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>164.44546</v>
+        <v>136.44546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-47.5</v>
+        <v>-75.5</v>
       </c>
     </row>
     <row r="31">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.225</v>
+        <v>0.145</v>
       </c>
       <c r="O31" t="n">
-        <v>-22.5</v>
+        <v>-14.5</v>
       </c>
       <c r="P31" t="n">
         <v>5.7894546</v>
@@ -3057,7 +3057,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>556.44546</v>
+        <v>564.44546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-22.5</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="32">
@@ -3125,17 +3125,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>0.595</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>-119</v>
+        <v>-113</v>
       </c>
       <c r="P32" t="n">
         <v>0.9454876</v>
@@ -3147,7 +3147,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S32" t="n">
-        <v>70.09752</v>
+        <v>76.09752</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-119</v>
+        <v>-113</v>
       </c>
     </row>
     <row r="33">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>9.07</v>
+        <v>10.4844</v>
       </c>
       <c r="O33" t="n">
-        <v>-1814</v>
+        <v>-2096.88</v>
       </c>
       <c r="P33" t="n">
         <v>6.3644671</v>
@@ -3237,7 +3237,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S33" t="n">
-        <v>-541.10658</v>
+        <v>-823.98658</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1814</v>
+        <v>-2096.88</v>
       </c>
     </row>
     <row r="34">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8208</v>
+        <v>4.3251</v>
       </c>
       <c r="O34" t="n">
-        <v>-282.08</v>
+        <v>-432.51</v>
       </c>
       <c r="P34" t="n">
         <v>4.1794876</v>
@@ -3327,7 +3327,7 @@
         <v>-417.94876</v>
       </c>
       <c r="S34" t="n">
-        <v>135.86876</v>
+        <v>-14.56124</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-282.08</v>
+        <v>-432.51</v>
       </c>
     </row>
     <row r="35">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.195</v>
+        <v>0.5182</v>
       </c>
       <c r="O35" t="n">
-        <v>-119.5</v>
+        <v>-51.82</v>
       </c>
       <c r="P35" t="n">
         <v>2.8794876</v>
@@ -3417,7 +3417,7 @@
         <v>-287.94876</v>
       </c>
       <c r="S35" t="n">
-        <v>168.44876</v>
+        <v>236.12876</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-119.5</v>
+        <v>-51.82</v>
       </c>
     </row>
     <row r="36">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>10.215</v>
+        <v>11.625</v>
       </c>
       <c r="O36" t="n">
-        <v>-2043</v>
+        <v>-2325</v>
       </c>
       <c r="P36" t="n">
         <v>7.3548796</v>
@@ -3507,7 +3507,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S36" t="n">
-        <v>-572.02408</v>
+        <v>-854.02408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-2043</v>
+        <v>-2325</v>
       </c>
     </row>
   </sheetData>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2688</v>
+        <v>1.269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3691,17 +3691,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>387.25</v>
+        <v>383.6</v>
       </c>
       <c r="O2" t="n">
-        <v>30980</v>
+        <v>30688</v>
       </c>
       <c r="P2" t="n">
         <v>409.022784188</v>
@@ -3713,7 +3713,7 @@
         <v>32721.822735</v>
       </c>
       <c r="S2" t="n">
-        <v>-1741.822735</v>
+        <v>-2033.822735</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>39307.424</v>
+        <v>38943.072</v>
       </c>
     </row>
     <row r="3">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2688</v>
+        <v>1.269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3771,17 +3771,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>350</v>
       </c>
       <c r="N3" t="n">
-        <v>62.39</v>
+        <v>61</v>
       </c>
       <c r="O3" t="n">
-        <v>21836.5</v>
+        <v>21350</v>
       </c>
       <c r="P3" t="n">
         <v>65.60009794299999</v>
@@ -3793,7 +3793,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S3" t="n">
-        <v>-1123.53428</v>
+        <v>-1610.03428</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>27706.1512</v>
+        <v>27093.15</v>
       </c>
     </row>
     <row r="4">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14534</v>
+        <v>0.1448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3851,17 +3851,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.74</v>
+        <v>30.62</v>
       </c>
       <c r="O4" t="n">
-        <v>61480</v>
+        <v>61240</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -3873,7 +3873,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-1912.47719</v>
+        <v>-2152.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8935.503199999999</v>
+        <v>8867.552000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1589</v>
+        <v>1.1571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3931,17 +3931,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.196</v>
+        <v>4.1015</v>
       </c>
       <c r="O5" t="n">
-        <v>12588</v>
+        <v>12304.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -3953,7 +3953,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1387.239091</v>
+        <v>-1670.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14588.2332</v>
+        <v>14237.53695</v>
       </c>
     </row>
     <row r="6">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1589</v>
+        <v>1.1571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4011,17 +4011,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>43.93</v>
+        <v>43.99</v>
       </c>
       <c r="O6" t="n">
-        <v>43930</v>
+        <v>43990</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -4033,7 +4033,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>920</v>
+        <v>980</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>50910.477</v>
+        <v>50900.829</v>
       </c>
     </row>
     <row r="7">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1589</v>
+        <v>1.1571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4091,17 +4091,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>594</v>
+        <v>548</v>
       </c>
       <c r="O7" t="n">
-        <v>8910</v>
+        <v>8220</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -4113,7 +4113,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>565.83</v>
+        <v>-124.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>10325.799</v>
+        <v>9511.362000000001</v>
       </c>
     </row>
     <row r="8">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78291</v>
+        <v>0.7798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4171,17 +4171,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.967</v>
+        <v>4.95</v>
       </c>
       <c r="O8" t="n">
-        <v>49670</v>
+        <v>49500</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4193,7 +4193,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12401.8184</v>
+        <v>12231.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38887.1397</v>
+        <v>38600.10000000001</v>
       </c>
     </row>
     <row r="9">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78291</v>
+        <v>0.7798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4251,17 +4251,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>555.1</v>
+        <v>551.99</v>
       </c>
       <c r="O9" t="n">
-        <v>41632.5</v>
+        <v>41399.25</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4273,7 +4273,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-2590.8504</v>
+        <v>-2824.1004</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>32594.500575</v>
+        <v>32283.13515</v>
       </c>
     </row>
     <row r="10">
@@ -4331,17 +4331,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.41</v>
+        <v>7.36</v>
       </c>
       <c r="O10" t="n">
-        <v>8151</v>
+        <v>8096</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4353,7 +4353,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-991.847947</v>
+        <v>-1046.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8151</v>
+        <v>8096</v>
       </c>
     </row>
     <row r="11">
@@ -4411,17 +4411,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>184.78</v>
+        <v>179.13</v>
       </c>
       <c r="O11" t="n">
-        <v>5543.4</v>
+        <v>5373.9</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -4433,7 +4433,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-995.8</v>
+        <v>-1165.3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5543.4</v>
+        <v>5373.9</v>
       </c>
     </row>
     <row r="12">
@@ -4491,7 +4491,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -4571,17 +4571,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>307.13</v>
+        <v>301</v>
       </c>
       <c r="O13" t="n">
-        <v>30713</v>
+        <v>30100</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4593,7 +4593,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2474.755</v>
+        <v>-3087.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30713</v>
+        <v>30100</v>
       </c>
     </row>
     <row r="14">
@@ -4651,17 +4651,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>56.73</v>
+        <v>56.05</v>
       </c>
       <c r="O14" t="n">
-        <v>9076.799999999999</v>
+        <v>8968</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4673,7 +4673,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-555.64</v>
+        <v>-664.4400000000001</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9076.799999999999</v>
+        <v>8968</v>
       </c>
     </row>
     <row r="15">
@@ -4731,17 +4731,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>67.69</v>
+        <v>65.47</v>
       </c>
       <c r="O15" t="n">
-        <v>1140.22</v>
+        <v>1102.83</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4753,7 +4753,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>791.173421</v>
+        <v>753.783421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1140.22</v>
+        <v>1102.83</v>
       </c>
     </row>
     <row r="16">
@@ -4811,17 +4811,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.1226</v>
+        <v>27.1359</v>
       </c>
       <c r="O16" t="n">
-        <v>10442.2</v>
+        <v>10447.32</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4833,7 +4833,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>433.294112</v>
+        <v>438.414112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10442.2</v>
+        <v>10447.32</v>
       </c>
     </row>
     <row r="17">
@@ -4891,17 +4891,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>287.97</v>
+        <v>286.56</v>
       </c>
       <c r="O17" t="n">
-        <v>28797</v>
+        <v>28656</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4913,7 +4913,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-1005</v>
+        <v>-1146</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28797</v>
+        <v>28656</v>
       </c>
     </row>
     <row r="18">
@@ -4971,17 +4971,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>178.56</v>
+        <v>172.7</v>
       </c>
       <c r="O18" t="n">
-        <v>17856</v>
+        <v>17270</v>
       </c>
       <c r="P18" t="n">
         <v>184.355</v>
@@ -4993,7 +4993,7 @@
         <v>18435.5</v>
       </c>
       <c r="S18" t="n">
-        <v>-579.5</v>
+        <v>-1165.5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>17856</v>
+        <v>17270</v>
       </c>
     </row>
     <row r="19">
@@ -5051,17 +5051,17 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>600</v>
       </c>
       <c r="N19" t="n">
-        <v>166.46</v>
+        <v>164.9</v>
       </c>
       <c r="O19" t="n">
-        <v>99876</v>
+        <v>98940</v>
       </c>
       <c r="P19" t="n">
         <v>173.846763275</v>
@@ -5073,7 +5073,7 @@
         <v>104308.057965</v>
       </c>
       <c r="S19" t="n">
-        <v>-4432.057965</v>
+        <v>-5368.057965</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>99876</v>
+        <v>98940</v>
       </c>
     </row>
     <row r="20">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="P20" t="n">
         <v>2.1405125</v>
@@ -5163,7 +5163,7 @@
         <v>214.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-213.94125</v>
+        <v>-213.95125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>7.115</v>
+        <v>7.1275</v>
       </c>
       <c r="O21" t="n">
-        <v>711.5</v>
+        <v>712.75</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5253,7 +5253,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>459.44875</v>
+        <v>460.69875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>711.5</v>
+        <v>712.75</v>
       </c>
     </row>
     <row r="22">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>33.0337</v>
+        <v>37.5848</v>
       </c>
       <c r="O22" t="n">
-        <v>6606.74</v>
+        <v>7516.96</v>
       </c>
       <c r="P22" t="n">
         <v>23.5270125</v>
@@ -5343,7 +5343,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S22" t="n">
-        <v>1901.3375</v>
+        <v>2811.5575</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>6606.74</v>
+        <v>7516.96</v>
       </c>
     </row>
     <row r="23">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>29.305</v>
+        <v>33.415</v>
       </c>
       <c r="O23" t="n">
-        <v>5861</v>
+        <v>6683</v>
       </c>
       <c r="P23" t="n">
         <v>20.1350875</v>
@@ -5433,7 +5433,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S23" t="n">
-        <v>1833.9825</v>
+        <v>2655.9825</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>5861</v>
+        <v>6683</v>
       </c>
     </row>
     <row r="24">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3391</v>
+        <v>4.3746</v>
       </c>
       <c r="O24" t="n">
-        <v>-433.91</v>
+        <v>-437.46</v>
       </c>
       <c r="P24" t="n">
         <v>1.7694546</v>
@@ -5523,7 +5523,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>-256.96454</v>
+        <v>-260.51454</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-433.91</v>
+        <v>-437.46</v>
       </c>
     </row>
     <row r="25">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0045</v>
+        <v>0.004</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="P25" t="n">
         <v>3.4194546</v>
@@ -5613,7 +5613,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>341.49546</v>
+        <v>341.54546</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="26">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.185</v>
+        <v>1.4161</v>
       </c>
       <c r="O26" t="n">
-        <v>-118.5</v>
+        <v>-141.61</v>
       </c>
       <c r="P26" t="n">
         <v>4.1794546</v>
@@ -5703,7 +5703,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>299.44546</v>
+        <v>276.33546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-118.5</v>
+        <v>-141.61</v>
       </c>
     </row>
     <row r="27">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0357</v>
+        <v>0.0153</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.57</v>
+        <v>-1.53</v>
       </c>
       <c r="P27" t="n">
         <v>2.3694546</v>
@@ -5793,7 +5793,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>233.37546</v>
+        <v>235.41546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-3.57</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="28">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.385</v>
+        <v>0.525</v>
       </c>
       <c r="O28" t="n">
-        <v>-38.5</v>
+        <v>-52.5</v>
       </c>
       <c r="P28" t="n">
         <v>1.7994546</v>
@@ -5883,7 +5883,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>141.44546</v>
+        <v>127.44546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-38.5</v>
+        <v>-52.5</v>
       </c>
     </row>
     <row r="29">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.752</v>
+        <v>2.865</v>
       </c>
       <c r="O29" t="n">
-        <v>-175.2</v>
+        <v>-286.5</v>
       </c>
       <c r="P29" t="n">
         <v>5.9694626</v>
@@ -5973,7 +5973,7 @@
         <v>-596.9462600000001</v>
       </c>
       <c r="S29" t="n">
-        <v>421.74626</v>
+        <v>310.44626</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-175.2</v>
+        <v>-286.5</v>
       </c>
     </row>
     <row r="30">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.065</v>
+        <v>0.615</v>
       </c>
       <c r="O30" t="n">
-        <v>-206.5</v>
+        <v>-61.5</v>
       </c>
       <c r="P30" t="n">
         <v>3.2300876</v>
@@ -6063,7 +6063,7 @@
         <v>-323.00876</v>
       </c>
       <c r="S30" t="n">
-        <v>116.50876</v>
+        <v>261.50876</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-206.5</v>
+        <v>-61.5</v>
       </c>
     </row>
     <row r="31">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.525</v>
+        <v>1.12</v>
       </c>
       <c r="O31" t="n">
-        <v>-152.5</v>
+        <v>-112</v>
       </c>
       <c r="P31" t="n">
         <v>4.8394876</v>
@@ -6153,7 +6153,7 @@
         <v>-483.94876</v>
       </c>
       <c r="S31" t="n">
-        <v>331.44876</v>
+        <v>371.94876</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-152.5</v>
+        <v>-112</v>
       </c>
     </row>
     <row r="32">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>0.475</v>
+        <v>0.755</v>
       </c>
       <c r="O32" t="n">
-        <v>-47.5</v>
+        <v>-75.5</v>
       </c>
       <c r="P32" t="n">
         <v>2.1094546</v>
@@ -6243,7 +6243,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>163.44546</v>
+        <v>135.44546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-47.5</v>
+        <v>-75.5</v>
       </c>
     </row>
     <row r="33">
@@ -6311,17 +6311,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.45</v>
+        <v>-1.8</v>
       </c>
       <c r="P33" t="n">
         <v>0.8794546</v>
@@ -6333,7 +6333,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>86.49545999999999</v>
+        <v>86.14546</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1.45</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="34">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>9.0097</v>
+        <v>9.0213</v>
       </c>
       <c r="O34" t="n">
-        <v>-900.97</v>
+        <v>-902.13</v>
       </c>
       <c r="P34" t="n">
         <v>3.2794546</v>
@@ -6423,7 +6423,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-573.02454</v>
+        <v>-574.18454</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-900.97</v>
+        <v>-902.13</v>
       </c>
     </row>
     <row r="35">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>9.07</v>
+        <v>10.4844</v>
       </c>
       <c r="O35" t="n">
-        <v>-1814</v>
+        <v>-2096.88</v>
       </c>
       <c r="P35" t="n">
         <v>6.3929546</v>
@@ -6513,7 +6513,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S35" t="n">
-        <v>-535.40908</v>
+        <v>-818.28908</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-1814</v>
+        <v>-2096.88</v>
       </c>
     </row>
     <row r="36">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>10.215</v>
+        <v>11.625</v>
       </c>
       <c r="O36" t="n">
-        <v>-2043</v>
+        <v>-2325</v>
       </c>
       <c r="P36" t="n">
         <v>7.3496796</v>
@@ -6603,7 +6603,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S36" t="n">
-        <v>-573.06408</v>
+        <v>-855.06408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-2043</v>
+        <v>-2325</v>
       </c>
     </row>
   </sheetData>
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$323,474.59</t>
+          <t>$319,421.99</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$105,313.91</t>
+          <t>$105,183.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$428,788.50</t>
+          <t>$424,605.41</t>
         </is>
       </c>
     </row>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$444,995.15</t>
+          <t>$440,709.79</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$91,954.11</t>
+          <t>$91,744.94</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$536,949.26</t>
+          <t>$532,454.72</t>
         </is>
       </c>
     </row>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$768,469.74</t>
+          <t>$760,131.78</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$197,268.02</t>
+          <t>$196,928.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$965,737.76</t>
+          <t>$957,060.13</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-20 23:43:07</t>
+          <t>2026-03-21 23:41:09</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -6771,7 +6771,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-21 23:41:09</t>
+          <t>2026-03-22 23:43:21</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -6771,7 +6771,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:21</t>
+          <t>2026-03-23 23:45:28</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.269</v>
+        <v>1.2716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>383.6</v>
+        <v>384.7</v>
       </c>
       <c r="O2" t="n">
-        <v>23016</v>
+        <v>23082</v>
       </c>
       <c r="P2" t="n">
         <v>408.869226783</v>
@@ -607,7 +607,7 @@
         <v>24532.153607</v>
       </c>
       <c r="S2" t="n">
-        <v>-1516.153607</v>
+        <v>-1450.153607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>29207.304</v>
+        <v>29351.0712</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.269</v>
+        <v>1.2716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>61</v>
+        <v>61.59</v>
       </c>
       <c r="O3" t="n">
-        <v>15250</v>
+        <v>15397.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.233413332</v>
@@ -687,7 +687,7 @@
         <v>16308.353333</v>
       </c>
       <c r="S3" t="n">
-        <v>-1058.353333</v>
+        <v>-910.853333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>19352.25</v>
+        <v>19579.461</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1448</v>
+        <v>0.14524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.62</v>
+        <v>29.62</v>
       </c>
       <c r="O4" t="n">
-        <v>61240</v>
+        <v>59240</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-2172.49376</v>
+        <v>-4172.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8867.552000000001</v>
+        <v>8604.017600000001</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1571</v>
+        <v>1.1612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1015</v>
+        <v>4.068</v>
       </c>
       <c r="O5" t="n">
-        <v>8203</v>
+        <v>8136</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1121.66</v>
+        <v>-1188.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9491.6913</v>
+        <v>9447.5232</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1571</v>
+        <v>1.1612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="O6" t="n">
-        <v>8220</v>
+        <v>8640</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>-124.17</v>
+        <v>295.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9511.362000000001</v>
+        <v>10032.768</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7798</v>
+        <v>0.78446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.95</v>
+        <v>4.835</v>
       </c>
       <c r="O7" t="n">
-        <v>39600</v>
+        <v>38680</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2288.77315</v>
+        <v>1368.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30880.08</v>
+        <v>30342.9128</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7798</v>
+        <v>0.78446</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>551.99</v>
+        <v>501.6</v>
       </c>
       <c r="O8" t="n">
-        <v>41399.25</v>
+        <v>37620</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-2834.848992</v>
+        <v>-6614.098992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>32283.13515</v>
+        <v>29511.3852</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.36</v>
+        <v>7.015</v>
       </c>
       <c r="O9" t="n">
-        <v>7360</v>
+        <v>7015</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-951.237657</v>
+        <v>-1296.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7360</v>
+        <v>7015</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>179.13</v>
+        <v>184.04</v>
       </c>
       <c r="O10" t="n">
-        <v>5373.9</v>
+        <v>5521.2</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-1169.2</v>
+        <v>-1021.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>5373.9</v>
+        <v>5521.2</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.67</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.5</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>967</v>
+        <v>972</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>301</v>
+        <v>302.06</v>
       </c>
       <c r="O12" t="n">
-        <v>30100</v>
+        <v>30206</v>
       </c>
       <c r="P12" t="n">
         <v>301.635</v>
@@ -1407,7 +1407,7 @@
         <v>30163.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-63.5</v>
+        <v>42.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30100</v>
+        <v>30206</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>56.05</v>
+        <v>56.96</v>
       </c>
       <c r="O13" t="n">
-        <v>8968</v>
+        <v>9113.6</v>
       </c>
       <c r="P13" t="n">
         <v>59.854125</v>
@@ -1487,7 +1487,7 @@
         <v>9576.66</v>
       </c>
       <c r="S13" t="n">
-        <v>-608.66</v>
+        <v>-463.06</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>8968</v>
+        <v>9113.6</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>385</v>
       </c>
       <c r="N14" t="n">
-        <v>27.1359</v>
+        <v>26.6753</v>
       </c>
       <c r="O14" t="n">
-        <v>10447.32</v>
+        <v>10269.99</v>
       </c>
       <c r="P14" t="n">
         <v>26.012734603</v>
@@ -1567,7 +1567,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S14" t="n">
-        <v>432.417178</v>
+        <v>255.087178</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10447.32</v>
+        <v>10269.99</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>172.7</v>
+        <v>175.64</v>
       </c>
       <c r="O15" t="n">
-        <v>17270</v>
+        <v>17564</v>
       </c>
       <c r="P15" t="n">
         <v>184.285</v>
@@ -1647,7 +1647,7 @@
         <v>18428.5</v>
       </c>
       <c r="S15" t="n">
-        <v>-1158.5</v>
+        <v>-864.5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>17270</v>
+        <v>17564</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>149.68</v>
+        <v>154.34</v>
       </c>
       <c r="O16" t="n">
-        <v>7484</v>
+        <v>7717</v>
       </c>
       <c r="P16" t="n">
         <v>197.085</v>
@@ -1727,7 +1727,7 @@
         <v>9854.25</v>
       </c>
       <c r="S16" t="n">
-        <v>-2370.25</v>
+        <v>-2137.25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>7484</v>
+        <v>7717</v>
       </c>
     </row>
     <row r="17">
@@ -1785,17 +1785,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>78.84999999999999</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>1577</v>
+        <v>1595.8</v>
       </c>
       <c r="P17" t="n">
         <v>124.315</v>
@@ -1807,7 +1807,7 @@
         <v>2486.3</v>
       </c>
       <c r="S17" t="n">
-        <v>-909.3</v>
+        <v>-890.5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1577</v>
+        <v>1595.8</v>
       </c>
     </row>
     <row r="18">
@@ -1865,17 +1865,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>164.9</v>
+        <v>166.22</v>
       </c>
       <c r="O18" t="n">
-        <v>82450</v>
+        <v>83110</v>
       </c>
       <c r="P18" t="n">
         <v>173.59385355</v>
@@ -1887,7 +1887,7 @@
         <v>86796.926775</v>
       </c>
       <c r="S18" t="n">
-        <v>-4346.926775</v>
+        <v>-3686.926775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>82450</v>
+        <v>83110</v>
       </c>
     </row>
     <row r="19">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.001</v>
+        <v>0.0001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="P19" t="n">
         <v>2.0105125</v>
@@ -1977,7 +1977,7 @@
         <v>201.05125</v>
       </c>
       <c r="S19" t="n">
-        <v>-200.95125</v>
+        <v>-201.04125</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1064</v>
+        <v>0.0307</v>
       </c>
       <c r="O20" t="n">
-        <v>10.64</v>
+        <v>3.07</v>
       </c>
       <c r="P20" t="n">
         <v>4.4905125</v>
@@ -2067,7 +2067,7 @@
         <v>449.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-438.41125</v>
+        <v>-445.98125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>10.64</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="21">
@@ -2135,17 +2135,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>37.5848</v>
+        <v>33.8519</v>
       </c>
       <c r="O21" t="n">
-        <v>7516.96</v>
+        <v>6770.38</v>
       </c>
       <c r="P21" t="n">
         <v>23.4605</v>
@@ -2157,7 +2157,7 @@
         <v>4692.1</v>
       </c>
       <c r="S21" t="n">
-        <v>2824.86</v>
+        <v>2078.28</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>7516.96</v>
+        <v>6770.38</v>
       </c>
     </row>
     <row r="22">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>33.415</v>
+        <v>30.02</v>
       </c>
       <c r="O22" t="n">
-        <v>6683</v>
+        <v>6004</v>
       </c>
       <c r="P22" t="n">
         <v>20.1374875</v>
@@ -2247,7 +2247,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S22" t="n">
-        <v>2655.5025</v>
+        <v>1976.5025</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>6683</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="23">
@@ -2315,17 +2315,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3746</v>
+        <v>2.545</v>
       </c>
       <c r="O23" t="n">
-        <v>-437.46</v>
+        <v>-254.5</v>
       </c>
       <c r="P23" t="n">
         <v>1.7494546</v>
@@ -2337,7 +2337,7 @@
         <v>-174.94546</v>
       </c>
       <c r="S23" t="n">
-        <v>-262.51454</v>
+        <v>-79.55454</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>-437.46</v>
+        <v>-254.5</v>
       </c>
     </row>
     <row r="24">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.004</v>
+        <v>0.0001</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4</v>
+        <v>-0.01</v>
       </c>
       <c r="P24" t="n">
         <v>3.2494546</v>
@@ -2427,7 +2427,7 @@
         <v>-324.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>324.54546</v>
+        <v>324.93546</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-0.4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="25">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.4161</v>
+        <v>0.705</v>
       </c>
       <c r="O25" t="n">
-        <v>-141.61</v>
+        <v>-70.5</v>
       </c>
       <c r="P25" t="n">
         <v>7.5800876</v>
@@ -2517,7 +2517,7 @@
         <v>-758.0087600000001</v>
       </c>
       <c r="S25" t="n">
-        <v>616.39876</v>
+        <v>687.5087600000001</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-141.61</v>
+        <v>-70.5</v>
       </c>
     </row>
     <row r="26">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.525</v>
+        <v>0.115</v>
       </c>
       <c r="O26" t="n">
-        <v>-52.5</v>
+        <v>-11.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.8142796</v>
@@ -2607,7 +2607,7 @@
         <v>-181.42796</v>
       </c>
       <c r="S26" t="n">
-        <v>128.92796</v>
+        <v>169.92796</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-52.5</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="27">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0362</v>
+        <v>0.0152</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.62</v>
+        <v>-1.52</v>
       </c>
       <c r="P27" t="n">
         <v>1.0242796</v>
@@ -2697,7 +2697,7 @@
         <v>-102.42796</v>
       </c>
       <c r="S27" t="n">
-        <v>98.80795999999999</v>
+        <v>100.90796</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-3.62</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="28">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.865</v>
+        <v>1.875</v>
       </c>
       <c r="O28" t="n">
-        <v>-573</v>
+        <v>-375</v>
       </c>
       <c r="P28" t="n">
         <v>6.6394751</v>
@@ -2787,7 +2787,7 @@
         <v>-1327.89502</v>
       </c>
       <c r="S28" t="n">
-        <v>754.89502</v>
+        <v>952.89502</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-573</v>
+        <v>-375</v>
       </c>
     </row>
     <row r="29">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.615</v>
+        <v>0.4</v>
       </c>
       <c r="O29" t="n">
-        <v>-61.5</v>
+        <v>-40</v>
       </c>
       <c r="P29" t="n">
         <v>6.7894876</v>
@@ -2877,7 +2877,7 @@
         <v>-678.94876</v>
       </c>
       <c r="S29" t="n">
-        <v>617.44876</v>
+        <v>638.94876</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-61.5</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="30">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.755</v>
+        <v>0.34</v>
       </c>
       <c r="O30" t="n">
-        <v>-75.5</v>
+        <v>-34</v>
       </c>
       <c r="P30" t="n">
         <v>2.1194546</v>
@@ -2967,7 +2967,7 @@
         <v>-211.94546</v>
       </c>
       <c r="S30" t="n">
-        <v>136.44546</v>
+        <v>177.94546</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-75.5</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="31">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.145</v>
+        <v>0.045</v>
       </c>
       <c r="O31" t="n">
-        <v>-14.5</v>
+        <v>-4.5</v>
       </c>
       <c r="P31" t="n">
         <v>5.7894546</v>
@@ -3057,7 +3057,7 @@
         <v>-578.94546</v>
       </c>
       <c r="S31" t="n">
-        <v>564.44546</v>
+        <v>574.44546</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-14.5</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="32">
@@ -3125,17 +3125,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-2</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="O32" t="n">
-        <v>-113</v>
+        <v>-38</v>
       </c>
       <c r="P32" t="n">
         <v>0.9454876</v>
@@ -3147,7 +3147,7 @@
         <v>-189.09752</v>
       </c>
       <c r="S32" t="n">
-        <v>76.09752</v>
+        <v>151.09752</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-113</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="33">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-2</v>
       </c>
       <c r="N33" t="n">
-        <v>10.4844</v>
+        <v>9.285</v>
       </c>
       <c r="O33" t="n">
-        <v>-2096.88</v>
+        <v>-1857</v>
       </c>
       <c r="P33" t="n">
         <v>6.3644671</v>
@@ -3237,7 +3237,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S33" t="n">
-        <v>-823.98658</v>
+        <v>-584.10658</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-2096.88</v>
+        <v>-1857</v>
       </c>
     </row>
     <row r="34">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>4.3251</v>
+        <v>1.915</v>
       </c>
       <c r="O34" t="n">
-        <v>-432.51</v>
+        <v>-191.5</v>
       </c>
       <c r="P34" t="n">
         <v>4.1794876</v>
@@ -3327,7 +3327,7 @@
         <v>-417.94876</v>
       </c>
       <c r="S34" t="n">
-        <v>-14.56124</v>
+        <v>226.44876</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-432.51</v>
+        <v>-191.5</v>
       </c>
     </row>
     <row r="35">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>0.5182</v>
+        <v>0.4796</v>
       </c>
       <c r="O35" t="n">
-        <v>-51.82</v>
+        <v>-47.96</v>
       </c>
       <c r="P35" t="n">
         <v>2.8794876</v>
@@ -3417,7 +3417,7 @@
         <v>-287.94876</v>
       </c>
       <c r="S35" t="n">
-        <v>236.12876</v>
+        <v>239.98876</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-51.82</v>
+        <v>-47.96</v>
       </c>
     </row>
     <row r="36">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>11.625</v>
+        <v>10.365</v>
       </c>
       <c r="O36" t="n">
-        <v>-2325</v>
+        <v>-2073</v>
       </c>
       <c r="P36" t="n">
         <v>7.3548796</v>
@@ -3507,7 +3507,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S36" t="n">
-        <v>-854.02408</v>
+        <v>-602.02408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-2325</v>
+        <v>-2073</v>
       </c>
     </row>
   </sheetData>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.269</v>
+        <v>1.2716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3691,17 +3691,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>383.6</v>
+        <v>384.7</v>
       </c>
       <c r="O2" t="n">
-        <v>30688</v>
+        <v>30776</v>
       </c>
       <c r="P2" t="n">
         <v>409.022784188</v>
@@ -3713,7 +3713,7 @@
         <v>32721.822735</v>
       </c>
       <c r="S2" t="n">
-        <v>-2033.822735</v>
+        <v>-1945.822735</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>38943.072</v>
+        <v>39134.76160000001</v>
       </c>
     </row>
     <row r="3">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.269</v>
+        <v>1.2716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3771,17 +3771,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>350</v>
       </c>
       <c r="N3" t="n">
-        <v>61</v>
+        <v>61.59</v>
       </c>
       <c r="O3" t="n">
-        <v>21350</v>
+        <v>21556.5</v>
       </c>
       <c r="P3" t="n">
         <v>65.60009794299999</v>
@@ -3793,7 +3793,7 @@
         <v>22960.03428</v>
       </c>
       <c r="S3" t="n">
-        <v>-1610.03428</v>
+        <v>-1403.53428</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>27093.15</v>
+        <v>27411.2454</v>
       </c>
     </row>
     <row r="4">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1448</v>
+        <v>0.14524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3851,17 +3851,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.62</v>
+        <v>29.62</v>
       </c>
       <c r="O4" t="n">
-        <v>61240</v>
+        <v>59240</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -3873,7 +3873,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-2152.47719</v>
+        <v>-4152.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8867.552000000001</v>
+        <v>8604.017600000001</v>
       </c>
     </row>
     <row r="5">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1571</v>
+        <v>1.1612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3931,17 +3931,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1015</v>
+        <v>4.068</v>
       </c>
       <c r="O5" t="n">
-        <v>12304.5</v>
+        <v>12204</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -3953,7 +3953,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1670.739091</v>
+        <v>-1771.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14237.53695</v>
+        <v>14171.2848</v>
       </c>
     </row>
     <row r="6">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1571</v>
+        <v>1.1612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4011,17 +4011,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>43.99</v>
+        <v>44.55</v>
       </c>
       <c r="O6" t="n">
-        <v>43990</v>
+        <v>44550</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -4033,7 +4033,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>980</v>
+        <v>1540</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>50900.829</v>
+        <v>51731.46</v>
       </c>
     </row>
     <row r="7">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1571</v>
+        <v>1.1612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4091,17 +4091,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="O7" t="n">
-        <v>8220</v>
+        <v>8640</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -4113,7 +4113,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>-124.17</v>
+        <v>295.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>9511.362000000001</v>
+        <v>10032.768</v>
       </c>
     </row>
     <row r="8">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7798</v>
+        <v>0.78446</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4171,17 +4171,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.95</v>
+        <v>4.835</v>
       </c>
       <c r="O8" t="n">
-        <v>49500</v>
+        <v>48350</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4193,7 +4193,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12231.8184</v>
+        <v>11081.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38600.10000000001</v>
+        <v>37928.641</v>
       </c>
     </row>
     <row r="9">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7798</v>
+        <v>0.78446</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4251,17 +4251,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>551.99</v>
+        <v>501.6</v>
       </c>
       <c r="O9" t="n">
-        <v>41399.25</v>
+        <v>37620</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4273,7 +4273,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-2824.1004</v>
+        <v>-6603.3504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>32283.13515</v>
+        <v>29511.3852</v>
       </c>
     </row>
     <row r="10">
@@ -4331,17 +4331,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.36</v>
+        <v>7.015</v>
       </c>
       <c r="O10" t="n">
-        <v>8096</v>
+        <v>7716.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4353,7 +4353,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1046.847947</v>
+        <v>-1426.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8096</v>
+        <v>7716.5</v>
       </c>
     </row>
     <row r="11">
@@ -4411,17 +4411,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>179.13</v>
+        <v>184.04</v>
       </c>
       <c r="O11" t="n">
-        <v>5373.9</v>
+        <v>5521.2</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -4433,7 +4433,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-1165.3</v>
+        <v>-1018</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5373.9</v>
+        <v>5521.2</v>
       </c>
     </row>
     <row r="12">
@@ -4491,17 +4491,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>300</v>
       </c>
       <c r="N12" t="n">
-        <v>9.67</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>2901</v>
+        <v>2916</v>
       </c>
       <c r="P12" t="n">
         <v>11.661666667</v>
@@ -4513,7 +4513,7 @@
         <v>3498.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-597.5</v>
+        <v>-582.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2901</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="13">
@@ -4571,17 +4571,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>301</v>
+        <v>302.06</v>
       </c>
       <c r="O13" t="n">
-        <v>30100</v>
+        <v>30206</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4593,7 +4593,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-3087.755</v>
+        <v>-2981.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30100</v>
+        <v>30206</v>
       </c>
     </row>
     <row r="14">
@@ -4651,17 +4651,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>56.05</v>
+        <v>56.96</v>
       </c>
       <c r="O14" t="n">
-        <v>8968</v>
+        <v>9113.6</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4673,7 +4673,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-664.4400000000001</v>
+        <v>-518.84</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>8968</v>
+        <v>9113.6</v>
       </c>
     </row>
     <row r="15">
@@ -4731,17 +4731,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>65.47</v>
+        <v>67.84</v>
       </c>
       <c r="O15" t="n">
-        <v>1102.83</v>
+        <v>1142.75</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4753,7 +4753,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>753.783421</v>
+        <v>793.703421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1102.83</v>
+        <v>1142.75</v>
       </c>
     </row>
     <row r="16">
@@ -4811,17 +4811,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.1359</v>
+        <v>26.6753</v>
       </c>
       <c r="O16" t="n">
-        <v>10447.32</v>
+        <v>10269.99</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4833,7 +4833,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>438.414112</v>
+        <v>261.084112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10447.32</v>
+        <v>10269.99</v>
       </c>
     </row>
     <row r="17">
@@ -4891,17 +4891,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>286.56</v>
+        <v>289.91</v>
       </c>
       <c r="O17" t="n">
-        <v>28656</v>
+        <v>28991</v>
       </c>
       <c r="P17" t="n">
         <v>298.02</v>
@@ -4913,7 +4913,7 @@
         <v>29802</v>
       </c>
       <c r="S17" t="n">
-        <v>-1146</v>
+        <v>-811</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28656</v>
+        <v>28991</v>
       </c>
     </row>
     <row r="18">
@@ -4971,17 +4971,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>172.7</v>
+        <v>175.64</v>
       </c>
       <c r="O18" t="n">
-        <v>17270</v>
+        <v>17564</v>
       </c>
       <c r="P18" t="n">
         <v>184.355</v>
@@ -4993,7 +4993,7 @@
         <v>18435.5</v>
       </c>
       <c r="S18" t="n">
-        <v>-1165.5</v>
+        <v>-871.5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>17270</v>
+        <v>17564</v>
       </c>
     </row>
     <row r="19">
@@ -5051,17 +5051,17 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>600</v>
       </c>
       <c r="N19" t="n">
-        <v>164.9</v>
+        <v>166.22</v>
       </c>
       <c r="O19" t="n">
-        <v>98940</v>
+        <v>99732</v>
       </c>
       <c r="P19" t="n">
         <v>173.846763275</v>
@@ -5073,7 +5073,7 @@
         <v>104308.057965</v>
       </c>
       <c r="S19" t="n">
-        <v>-5368.057965</v>
+        <v>-4576.057965</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>98940</v>
+        <v>99732</v>
       </c>
     </row>
     <row r="20">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.001</v>
+        <v>0.0001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="P20" t="n">
         <v>2.1405125</v>
@@ -5163,7 +5163,7 @@
         <v>214.05125</v>
       </c>
       <c r="S20" t="n">
-        <v>-213.95125</v>
+        <v>-214.04125</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>7.1275</v>
+        <v>8.513500000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>712.75</v>
+        <v>851.35</v>
       </c>
       <c r="P21" t="n">
         <v>2.5205125</v>
@@ -5253,7 +5253,7 @@
         <v>252.05125</v>
       </c>
       <c r="S21" t="n">
-        <v>460.69875</v>
+        <v>599.29875</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>712.75</v>
+        <v>851.35</v>
       </c>
     </row>
     <row r="22">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>37.5848</v>
+        <v>33.8519</v>
       </c>
       <c r="O22" t="n">
-        <v>7516.96</v>
+        <v>6770.38</v>
       </c>
       <c r="P22" t="n">
         <v>23.5270125</v>
@@ -5343,7 +5343,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S22" t="n">
-        <v>2811.5575</v>
+        <v>2064.9775</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>7516.96</v>
+        <v>6770.38</v>
       </c>
     </row>
     <row r="23">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>33.415</v>
+        <v>30.02</v>
       </c>
       <c r="O23" t="n">
-        <v>6683</v>
+        <v>6004</v>
       </c>
       <c r="P23" t="n">
         <v>20.1350875</v>
@@ -5433,7 +5433,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S23" t="n">
-        <v>2655.9825</v>
+        <v>1976.9825</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>6683</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="24">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>-1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3746</v>
+        <v>2.545</v>
       </c>
       <c r="O24" t="n">
-        <v>-437.46</v>
+        <v>-254.5</v>
       </c>
       <c r="P24" t="n">
         <v>1.7694546</v>
@@ -5523,7 +5523,7 @@
         <v>-176.94546</v>
       </c>
       <c r="S24" t="n">
-        <v>-260.51454</v>
+        <v>-77.55454</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>-437.46</v>
+        <v>-254.5</v>
       </c>
     </row>
     <row r="25">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.004</v>
+        <v>0.0001</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4</v>
+        <v>-0.01</v>
       </c>
       <c r="P25" t="n">
         <v>3.4194546</v>
@@ -5613,7 +5613,7 @@
         <v>-341.94546</v>
       </c>
       <c r="S25" t="n">
-        <v>341.54546</v>
+        <v>341.93546</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>-0.4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="26">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4161</v>
+        <v>0.705</v>
       </c>
       <c r="O26" t="n">
-        <v>-141.61</v>
+        <v>-70.5</v>
       </c>
       <c r="P26" t="n">
         <v>4.1794546</v>
@@ -5703,7 +5703,7 @@
         <v>-417.94546</v>
       </c>
       <c r="S26" t="n">
-        <v>276.33546</v>
+        <v>347.44546</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>-141.61</v>
+        <v>-70.5</v>
       </c>
     </row>
     <row r="27">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>-1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0153</v>
+        <v>0.0002</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.53</v>
+        <v>-0.02</v>
       </c>
       <c r="P27" t="n">
         <v>2.3694546</v>
@@ -5793,7 +5793,7 @@
         <v>-236.94546</v>
       </c>
       <c r="S27" t="n">
-        <v>235.41546</v>
+        <v>236.92546</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>-1.53</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="28">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>-1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.525</v>
+        <v>0.115</v>
       </c>
       <c r="O28" t="n">
-        <v>-52.5</v>
+        <v>-11.5</v>
       </c>
       <c r="P28" t="n">
         <v>1.7994546</v>
@@ -5883,7 +5883,7 @@
         <v>-179.94546</v>
       </c>
       <c r="S28" t="n">
-        <v>127.44546</v>
+        <v>168.44546</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>-52.5</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="29">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.865</v>
+        <v>1.875</v>
       </c>
       <c r="O29" t="n">
-        <v>-286.5</v>
+        <v>-187.5</v>
       </c>
       <c r="P29" t="n">
         <v>5.9694626</v>
@@ -5973,7 +5973,7 @@
         <v>-596.9462600000001</v>
       </c>
       <c r="S29" t="n">
-        <v>310.44626</v>
+        <v>409.44626</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>-286.5</v>
+        <v>-187.5</v>
       </c>
     </row>
     <row r="30">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.615</v>
+        <v>0.4</v>
       </c>
       <c r="O30" t="n">
-        <v>-61.5</v>
+        <v>-40</v>
       </c>
       <c r="P30" t="n">
         <v>3.2300876</v>
@@ -6063,7 +6063,7 @@
         <v>-323.00876</v>
       </c>
       <c r="S30" t="n">
-        <v>261.50876</v>
+        <v>283.00876</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>-61.5</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="31">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>-1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.12</v>
+        <v>1.305</v>
       </c>
       <c r="O31" t="n">
-        <v>-112</v>
+        <v>-130.5</v>
       </c>
       <c r="P31" t="n">
         <v>4.8394876</v>
@@ -6153,7 +6153,7 @@
         <v>-483.94876</v>
       </c>
       <c r="S31" t="n">
-        <v>371.94876</v>
+        <v>353.44876</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>-112</v>
+        <v>-130.5</v>
       </c>
     </row>
     <row r="32">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>0.755</v>
+        <v>0.34</v>
       </c>
       <c r="O32" t="n">
-        <v>-75.5</v>
+        <v>-34</v>
       </c>
       <c r="P32" t="n">
         <v>2.1094546</v>
@@ -6243,7 +6243,7 @@
         <v>-210.94546</v>
       </c>
       <c r="S32" t="n">
-        <v>135.44546</v>
+        <v>176.94546</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>-75.5</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="33">
@@ -6311,17 +6311,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M33" t="n">
         <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>0.018</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.8</v>
+        <v>-0.79</v>
       </c>
       <c r="P33" t="n">
         <v>0.8794546</v>
@@ -6333,7 +6333,7 @@
         <v>-87.94546</v>
       </c>
       <c r="S33" t="n">
-        <v>86.14546</v>
+        <v>87.15546000000001</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>-1.8</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="34">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>-1</v>
       </c>
       <c r="N34" t="n">
-        <v>9.0213</v>
+        <v>10.4879</v>
       </c>
       <c r="O34" t="n">
-        <v>-902.13</v>
+        <v>-1048.79</v>
       </c>
       <c r="P34" t="n">
         <v>3.2794546</v>
@@ -6423,7 +6423,7 @@
         <v>-327.94546</v>
       </c>
       <c r="S34" t="n">
-        <v>-574.18454</v>
+        <v>-720.8445400000001</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>-902.13</v>
+        <v>-1048.79</v>
       </c>
     </row>
     <row r="35">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>-2</v>
       </c>
       <c r="N35" t="n">
-        <v>10.4844</v>
+        <v>9.285</v>
       </c>
       <c r="O35" t="n">
-        <v>-2096.88</v>
+        <v>-1857</v>
       </c>
       <c r="P35" t="n">
         <v>6.3929546</v>
@@ -6513,7 +6513,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S35" t="n">
-        <v>-818.28908</v>
+        <v>-578.40908</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>-2096.88</v>
+        <v>-1857</v>
       </c>
     </row>
     <row r="36">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>-2</v>
       </c>
       <c r="N36" t="n">
-        <v>11.625</v>
+        <v>10.365</v>
       </c>
       <c r="O36" t="n">
-        <v>-2325</v>
+        <v>-2073</v>
       </c>
       <c r="P36" t="n">
         <v>7.3496796</v>
@@ -6603,7 +6603,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S36" t="n">
-        <v>-855.06408</v>
+        <v>-603.06408</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>-2325</v>
+        <v>-2073</v>
       </c>
     </row>
   </sheetData>
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$319,421.99</t>
+          <t>$317,732.20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$105,183.42</t>
+          <t>$105,439.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$424,605.41</t>
+          <t>$423,171.39</t>
         </is>
       </c>
     </row>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$440,709.79</t>
+          <t>$439,616.23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$91,744.94</t>
+          <t>$92,135.58</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$532,454.72</t>
+          <t>$531,751.81</t>
         </is>
       </c>
     </row>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$760,131.78</t>
+          <t>$757,348.43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$196,928.35</t>
+          <t>$197,574.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$957,060.13</t>
+          <t>$954,923.20</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24 01:33:58</t>
+          <t>2026-03-24 23:44:49</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2716</v>
+        <v>1.2686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,29 +585,29 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>384.7</v>
+        <v>383.4</v>
       </c>
       <c r="O2" t="n">
-        <v>23082</v>
+        <v>19170</v>
       </c>
       <c r="P2" t="n">
-        <v>408.869226783</v>
+        <v>406.7530481</v>
       </c>
       <c r="Q2" t="n">
-        <v>408.869226783</v>
+        <v>406.7530481</v>
       </c>
       <c r="R2" t="n">
-        <v>24532.153607</v>
+        <v>20337.652405</v>
       </c>
       <c r="S2" t="n">
-        <v>-1450.153607</v>
+        <v>-1167.652405</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>29351.0712</v>
+        <v>24319.062</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2716</v>
+        <v>1.2686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,29 +665,29 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>61.59</v>
+        <v>61.71</v>
       </c>
       <c r="O3" t="n">
-        <v>15397.5</v>
+        <v>12342</v>
       </c>
       <c r="P3" t="n">
-        <v>65.233413332</v>
+        <v>65.372133335</v>
       </c>
       <c r="Q3" t="n">
-        <v>65.233413332</v>
+        <v>65.372133335</v>
       </c>
       <c r="R3" t="n">
-        <v>16308.353333</v>
+        <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-910.853333</v>
+        <v>-732.426667</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>19579.461</v>
+        <v>15657.0612</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14524</v>
+        <v>0.14508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>29.62</v>
+        <v>30.02</v>
       </c>
       <c r="O4" t="n">
-        <v>59240</v>
+        <v>60040</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-4172.49376</v>
+        <v>-3372.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8604.017600000001</v>
+        <v>8710.6032</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1612</v>
+        <v>1.1607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.068</v>
+        <v>4.0705</v>
       </c>
       <c r="O5" t="n">
-        <v>8136</v>
+        <v>8141</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1188.66</v>
+        <v>-1183.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9447.5232</v>
+        <v>9449.2587</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1612</v>
+        <v>1.1607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="O6" t="n">
-        <v>8640</v>
+        <v>8550</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>295.83</v>
+        <v>205.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10032.768</v>
+        <v>9923.985000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78446</v>
+        <v>0.78248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.835</v>
+        <v>4.88</v>
       </c>
       <c r="O7" t="n">
-        <v>38680</v>
+        <v>39040</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1368.77315</v>
+        <v>1728.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30342.9128</v>
+        <v>30548.0192</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78446</v>
+        <v>0.78248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>501.6</v>
+        <v>517.5</v>
       </c>
       <c r="O8" t="n">
-        <v>37620</v>
+        <v>38812.5</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-6614.098992</v>
+        <v>-5421.598992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>29511.3852</v>
+        <v>30370.005</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.015</v>
+        <v>7.08</v>
       </c>
       <c r="O9" t="n">
-        <v>7015</v>
+        <v>7080</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-1296.237657</v>
+        <v>-1231.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7015</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>184.04</v>
+        <v>183.49</v>
       </c>
       <c r="O10" t="n">
-        <v>5521.2</v>
+        <v>5504.7</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-1021.9</v>
+        <v>-1038.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>5521.2</v>
+        <v>5504.7</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.720000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>972</v>
+        <v>955</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>-15.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>972</v>
+        <v>955</v>
       </c>
     </row>
     <row r="12">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GRDU</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ALPHABET INC-CL A</t>
+          <t>FT NSDQ CLN EDG SMRT GRID</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1385,29 +1385,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>302.06</v>
+        <v>56.98</v>
       </c>
       <c r="O12" t="n">
-        <v>30206</v>
+        <v>9116.799999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>301.635</v>
+        <v>59.854125</v>
       </c>
       <c r="Q12" t="n">
-        <v>301.635</v>
+        <v>59.854125</v>
       </c>
       <c r="R12" t="n">
-        <v>30163.5</v>
+        <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>42.5</v>
+        <v>-459.86</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1416,11 +1416,11 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30206</v>
+        <v>9116.799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GRDU</t>
+          <t>INRA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FT NSDQ CLN EDG SMRT GRID</t>
+          <t>ISHAR GL CL EN TR UCI ETF-US</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1465,29 +1465,29 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>160</v>
+        <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>56.96</v>
+        <v>26.8773</v>
       </c>
       <c r="O13" t="n">
-        <v>9113.6</v>
+        <v>10347.76</v>
       </c>
       <c r="P13" t="n">
-        <v>59.854125</v>
+        <v>26.012734603</v>
       </c>
       <c r="Q13" t="n">
-        <v>59.854125</v>
+        <v>26.012734603</v>
       </c>
       <c r="R13" t="n">
-        <v>9576.66</v>
+        <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>-463.06</v>
+        <v>332.857178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>AEB</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>9113.6</v>
+        <v>10347.76</v>
       </c>
     </row>
     <row r="14">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>INRA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ISHAR GL CL EN TR UCI ETF-US</t>
+          <t>SEA LTD-ADR</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1545,29 +1545,29 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>385</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>26.6753</v>
+        <v>78.31</v>
       </c>
       <c r="O14" t="n">
-        <v>10269.99</v>
+        <v>1566.2</v>
       </c>
       <c r="P14" t="n">
-        <v>26.012734603</v>
+        <v>124.315</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.012734603</v>
+        <v>124.315</v>
       </c>
       <c r="R14" t="n">
-        <v>10014.902822</v>
+        <v>2486.3</v>
       </c>
       <c r="S14" t="n">
-        <v>255.087178</v>
+        <v>-920.1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1576,11 +1576,11 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>AEB</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10269.99</v>
+        <v>1566.2</v>
       </c>
     </row>
     <row r="15">
@@ -1604,17 +1604,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NVIDIA CORP</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1625,29 +1625,29 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N15" t="n">
-        <v>175.64</v>
+        <v>166.08</v>
       </c>
       <c r="O15" t="n">
-        <v>17564</v>
+        <v>66432</v>
       </c>
       <c r="P15" t="n">
-        <v>184.285</v>
+        <v>174.135899437</v>
       </c>
       <c r="Q15" t="n">
-        <v>184.285</v>
+        <v>174.135899437</v>
       </c>
       <c r="R15" t="n">
-        <v>18428.5</v>
+        <v>69654.359775</v>
       </c>
       <c r="S15" t="n">
-        <v>-864.5</v>
+        <v>-3222.359775</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1656,11 +1656,11 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>17564</v>
+        <v>66432</v>
       </c>
     </row>
     <row r="16">
@@ -1679,55 +1679,65 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ORACLE CORP</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I16" t="n">
+        <v>560</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>154.34</v>
+        <v>35.44</v>
       </c>
       <c r="O16" t="n">
-        <v>7717</v>
+        <v>7088</v>
       </c>
       <c r="P16" t="n">
-        <v>197.085</v>
+        <v>23.4605</v>
       </c>
       <c r="Q16" t="n">
-        <v>197.085</v>
+        <v>23.4605</v>
       </c>
       <c r="R16" t="n">
-        <v>9854.25</v>
+        <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>-2137.25</v>
+        <v>2395.9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1736,11 +1746,11 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>7717</v>
+        <v>7088</v>
       </c>
     </row>
     <row r="17">
@@ -1759,55 +1769,65 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADR</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SEA LTD-ADR</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I17" t="n">
+        <v>620</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>79.79000000000001</v>
+        <v>31.045</v>
       </c>
       <c r="O17" t="n">
-        <v>1595.8</v>
+        <v>6209</v>
       </c>
       <c r="P17" t="n">
-        <v>124.315</v>
+        <v>20.1374875</v>
       </c>
       <c r="Q17" t="n">
-        <v>124.315</v>
+        <v>20.1374875</v>
       </c>
       <c r="R17" t="n">
-        <v>2486.3</v>
+        <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>-890.5</v>
+        <v>2181.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1816,11 +1836,11 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1595.8</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="18">
@@ -1839,68 +1859,78 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I18" t="n">
+        <v>425</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>500</v>
+        <v>-2</v>
       </c>
       <c r="N18" t="n">
-        <v>166.22</v>
+        <v>9.7484</v>
       </c>
       <c r="O18" t="n">
-        <v>83110</v>
+        <v>-1949.68</v>
       </c>
       <c r="P18" t="n">
-        <v>173.59385355</v>
+        <v>6.3644671</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.59385355</v>
+        <v>6.3644671</v>
       </c>
       <c r="R18" t="n">
-        <v>86796.926775</v>
+        <v>-1272.89342</v>
       </c>
       <c r="S18" t="n">
-        <v>-3686.926775</v>
+        <v>-676.78658</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>83110</v>
+        <v>-1949.68</v>
       </c>
     </row>
     <row r="19">
@@ -1924,64 +1954,64 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AAPL  260327C00290000</t>
+          <t>SPY   261218P00505000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 290 C</t>
+          <t>SPY 18DEC26 505 P</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>290</v>
+        <v>505</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0001</v>
+        <v>10.72</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01</v>
+        <v>-2144</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0105125</v>
+        <v>7.3548796</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.0105125</v>
+        <v>7.3548796</v>
       </c>
       <c r="R19" t="n">
-        <v>201.05125</v>
+        <v>-1470.97592</v>
       </c>
       <c r="S19" t="n">
-        <v>-201.04125</v>
+        <v>-673.02408</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -1990,1537 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>MSFT  260327C00420000</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MSFT 27MAR26 420 C</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" t="n">
-        <v>420</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.0307</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="P20" t="n">
-        <v>4.4905125</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.4905125</v>
-      </c>
-      <c r="R20" t="n">
-        <v>449.05125</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-445.98125</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>QQQ   261218P00560000</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>QQQ 18DEC26 560 P</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>100</v>
-      </c>
-      <c r="I21" t="n">
-        <v>560</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>33.8519</v>
-      </c>
-      <c r="O21" t="n">
-        <v>6770.38</v>
-      </c>
-      <c r="P21" t="n">
-        <v>23.4605</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>23.4605</v>
-      </c>
-      <c r="R21" t="n">
-        <v>4692.1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2078.28</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>6770.38</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SPY   261218P00620000</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 620 P</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I22" t="n">
-        <v>620</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>30.02</v>
-      </c>
-      <c r="O22" t="n">
-        <v>6004</v>
-      </c>
-      <c r="P22" t="n">
-        <v>20.1374875</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>20.1374875</v>
-      </c>
-      <c r="R22" t="n">
-        <v>4027.4975</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1976.5025</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>6004</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>AAPL  260327P00250000</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AAPL 27MAR26 250 P</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" t="n">
-        <v>250</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.545</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-254.5</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.7494546</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.7494546</v>
-      </c>
-      <c r="R23" t="n">
-        <v>-174.94546</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-79.55454</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>-254.5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>AAPL  260327C00285000</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>AAPL 27MAR26 285 C</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" t="n">
-        <v>285</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3.2494546</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.2494546</v>
-      </c>
-      <c r="R24" t="n">
-        <v>-324.94546</v>
-      </c>
-      <c r="S24" t="n">
-        <v>324.93546</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>AMD   260327P00185000</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>AMD 27MAR26 185 P</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>100</v>
-      </c>
-      <c r="I25" t="n">
-        <v>185</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-70.5</v>
-      </c>
-      <c r="P25" t="n">
-        <v>7.5800876</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7.5800876</v>
-      </c>
-      <c r="R25" t="n">
-        <v>-758.0087600000001</v>
-      </c>
-      <c r="S25" t="n">
-        <v>687.5087600000001</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>-70.5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>AMZN  260327P00190000</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>AMZN 27MAR26 190 P</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" t="n">
-        <v>190</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.8142796</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.8142796</v>
-      </c>
-      <c r="R26" t="n">
-        <v>-181.42796</v>
-      </c>
-      <c r="S26" t="n">
-        <v>169.92796</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>AMZN  260327C00235000</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>AMZN 27MAR26 235 C</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>100</v>
-      </c>
-      <c r="I27" t="n">
-        <v>235</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.0242796</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.0242796</v>
-      </c>
-      <c r="R27" t="n">
-        <v>-102.42796</v>
-      </c>
-      <c r="S27" t="n">
-        <v>100.90796</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>GOOGL 260327P00295000</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>GOOGL 27MAR26 295 P</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" t="n">
-        <v>295</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-375</v>
-      </c>
-      <c r="P28" t="n">
-        <v>6.6394751</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6.6394751</v>
-      </c>
-      <c r="R28" t="n">
-        <v>-1327.89502</v>
-      </c>
-      <c r="S28" t="n">
-        <v>952.89502</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>-375</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>GOOGL 260327C00315000</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>GOOGL 27MAR26 315 C</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" t="n">
-        <v>315</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-40</v>
-      </c>
-      <c r="P29" t="n">
-        <v>6.7894876</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6.7894876</v>
-      </c>
-      <c r="R29" t="n">
-        <v>-678.94876</v>
-      </c>
-      <c r="S29" t="n">
-        <v>638.94876</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>MSFT  260327P00360000</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>MSFT 27MAR26 360 P</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>100</v>
-      </c>
-      <c r="I30" t="n">
-        <v>360</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-34</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.1194546</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.1194546</v>
-      </c>
-      <c r="R30" t="n">
-        <v>-211.94546</v>
-      </c>
-      <c r="S30" t="n">
-        <v>177.94546</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>-34</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>MSFT  260327C00415000</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>MSFT 27MAR26 415 C</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" t="n">
-        <v>415</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="P31" t="n">
-        <v>5.7894546</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5.7894546</v>
-      </c>
-      <c r="R31" t="n">
-        <v>-578.94546</v>
-      </c>
-      <c r="S31" t="n">
-        <v>574.44546</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>NFLX  260327P00088000</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>NFLX 27MAR26 88 P</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I32" t="n">
-        <v>88</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="O32" t="n">
-        <v>-38</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.9454876</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.9454876</v>
-      </c>
-      <c r="R32" t="n">
-        <v>-189.09752</v>
-      </c>
-      <c r="S32" t="n">
-        <v>151.09752</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>-38</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>QQQ   261218P00425000</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>QQQ 18DEC26 425 P</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" t="n">
-        <v>425</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>9.285</v>
-      </c>
-      <c r="O33" t="n">
-        <v>-1857</v>
-      </c>
-      <c r="P33" t="n">
-        <v>6.3644671</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>6.3644671</v>
-      </c>
-      <c r="R33" t="n">
-        <v>-1272.89342</v>
-      </c>
-      <c r="S33" t="n">
-        <v>-584.10658</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>-1857</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>SMH   260327P00370000</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>SMH 27MAR26 370 P</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" t="n">
-        <v>370</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.915</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-191.5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>4.1794876</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4.1794876</v>
-      </c>
-      <c r="R34" t="n">
-        <v>-417.94876</v>
-      </c>
-      <c r="S34" t="n">
-        <v>226.44876</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>-191.5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>SMH   260327C00420000</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>SMH 27MAR26 420 C</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" t="n">
-        <v>420</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.4796</v>
-      </c>
-      <c r="O35" t="n">
-        <v>-47.96</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.8794876</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.8794876</v>
-      </c>
-      <c r="R35" t="n">
-        <v>-287.94876</v>
-      </c>
-      <c r="S35" t="n">
-        <v>239.98876</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>-47.96</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" t="n">
-        <v>505</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N36" t="n">
-        <v>10.365</v>
-      </c>
-      <c r="O36" t="n">
-        <v>-2073</v>
-      </c>
-      <c r="P36" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="R36" t="n">
-        <v>-1470.97592</v>
-      </c>
-      <c r="S36" t="n">
-        <v>-602.02408</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>-2073</v>
+        <v>-2144</v>
       </c>
     </row>
   </sheetData>
@@ -3534,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3661,7 +2161,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2716</v>
+        <v>1.2686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3691,29 +2191,29 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>384.7</v>
+        <v>383.4</v>
       </c>
       <c r="O2" t="n">
-        <v>30776</v>
+        <v>26838</v>
       </c>
       <c r="P2" t="n">
-        <v>409.022784188</v>
+        <v>407.503306971</v>
       </c>
       <c r="Q2" t="n">
-        <v>409.022784188</v>
+        <v>407.503306971</v>
       </c>
       <c r="R2" t="n">
-        <v>32721.822735</v>
+        <v>28525.231488</v>
       </c>
       <c r="S2" t="n">
-        <v>-1945.822735</v>
+        <v>-1687.231488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -3726,7 +2226,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>39134.76160000001</v>
+        <v>34046.6868</v>
       </c>
     </row>
     <row r="3">
@@ -3741,7 +2241,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2716</v>
+        <v>1.2686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3771,29 +2271,29 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>61.59</v>
+        <v>61.71</v>
       </c>
       <c r="O3" t="n">
-        <v>21556.5</v>
+        <v>18513</v>
       </c>
       <c r="P3" t="n">
-        <v>65.60009794299999</v>
+        <v>65.76286500000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>65.60009794299999</v>
+        <v>65.76286500000001</v>
       </c>
       <c r="R3" t="n">
-        <v>22960.03428</v>
+        <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-1403.53428</v>
+        <v>-1215.8595</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -3806,7 +2306,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>27411.2454</v>
+        <v>23485.5918</v>
       </c>
     </row>
     <row r="4">
@@ -3821,7 +2321,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14524</v>
+        <v>0.14508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3851,17 +2351,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>29.62</v>
+        <v>30.02</v>
       </c>
       <c r="O4" t="n">
-        <v>59240</v>
+        <v>60040</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -3873,7 +2373,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-4152.47719</v>
+        <v>-3352.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3886,7 +2386,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8604.017600000001</v>
+        <v>8710.6032</v>
       </c>
     </row>
     <row r="5">
@@ -3901,7 +2401,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1612</v>
+        <v>1.1607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3931,17 +2431,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.068</v>
+        <v>4.0705</v>
       </c>
       <c r="O5" t="n">
-        <v>12204</v>
+        <v>12211.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -3953,7 +2453,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1771.239091</v>
+        <v>-1763.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -3966,7 +2466,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14171.2848</v>
+        <v>14173.88805</v>
       </c>
     </row>
     <row r="6">
@@ -3981,7 +2481,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1612</v>
+        <v>1.1607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4011,17 +2511,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>44.55</v>
+        <v>44.82</v>
       </c>
       <c r="O6" t="n">
-        <v>44550</v>
+        <v>44820</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -4033,7 +2533,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>1540</v>
+        <v>1810</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -4046,7 +2546,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>51731.46</v>
+        <v>52022.574</v>
       </c>
     </row>
     <row r="7">
@@ -4061,7 +2561,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1612</v>
+        <v>1.1607</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4091,17 +2591,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="O7" t="n">
-        <v>8640</v>
+        <v>8550</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -4113,7 +2613,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>295.83</v>
+        <v>205.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -4126,7 +2626,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>10032.768</v>
+        <v>9923.985000000001</v>
       </c>
     </row>
     <row r="8">
@@ -4141,7 +2641,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78446</v>
+        <v>0.78248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4171,17 +2671,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.835</v>
+        <v>4.88</v>
       </c>
       <c r="O8" t="n">
-        <v>48350</v>
+        <v>48800</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -4193,7 +2693,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11081.8184</v>
+        <v>11531.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4206,7 +2706,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37928.641</v>
+        <v>38185.024</v>
       </c>
     </row>
     <row r="9">
@@ -4221,7 +2721,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78446</v>
+        <v>0.78248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4251,17 +2751,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>501.6</v>
+        <v>517.5</v>
       </c>
       <c r="O9" t="n">
-        <v>37620</v>
+        <v>38812.5</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -4273,7 +2773,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-6603.3504</v>
+        <v>-5410.8504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4286,7 +2786,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>29511.3852</v>
+        <v>30370.005</v>
       </c>
     </row>
     <row r="10">
@@ -4331,17 +2831,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.015</v>
+        <v>7.08</v>
       </c>
       <c r="O10" t="n">
-        <v>7716.5</v>
+        <v>7788</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -4353,7 +2853,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1426.347947</v>
+        <v>-1354.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -4366,7 +2866,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>7716.5</v>
+        <v>7788</v>
       </c>
     </row>
     <row r="11">
@@ -4411,17 +2911,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>184.04</v>
+        <v>183.49</v>
       </c>
       <c r="O11" t="n">
-        <v>5521.2</v>
+        <v>5504.7</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -4433,7 +2933,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-1018</v>
+        <v>-1034.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4446,7 +2946,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5521.2</v>
+        <v>5504.7</v>
       </c>
     </row>
     <row r="12">
@@ -4491,29 +2991,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.720000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>2916</v>
+        <v>1910</v>
       </c>
       <c r="P12" t="n">
-        <v>11.661666667</v>
+        <v>11.1425</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.661666667</v>
+        <v>11.1425</v>
       </c>
       <c r="R12" t="n">
-        <v>3498.5</v>
+        <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-582.5</v>
+        <v>-318.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4526,7 +3026,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2916</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="13">
@@ -4571,17 +3071,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>302.06</v>
+        <v>290.44</v>
       </c>
       <c r="O13" t="n">
-        <v>30206</v>
+        <v>29044</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -4593,7 +3093,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2981.755</v>
+        <v>-4143.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4606,7 +3106,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>30206</v>
+        <v>29044</v>
       </c>
     </row>
     <row r="14">
@@ -4651,17 +3151,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>56.96</v>
+        <v>56.98</v>
       </c>
       <c r="O14" t="n">
-        <v>9113.6</v>
+        <v>9116.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -4673,7 +3173,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-518.84</v>
+        <v>-515.64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4686,7 +3186,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9113.6</v>
+        <v>9116.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -4731,17 +3231,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>67.84</v>
+        <v>66.12</v>
       </c>
       <c r="O15" t="n">
-        <v>1142.75</v>
+        <v>1113.78</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -4753,7 +3253,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>793.703421</v>
+        <v>764.733421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4766,7 +3266,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1142.75</v>
+        <v>1113.78</v>
       </c>
     </row>
     <row r="16">
@@ -4811,17 +3311,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.6753</v>
+        <v>26.8773</v>
       </c>
       <c r="O16" t="n">
-        <v>10269.99</v>
+        <v>10347.76</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -4833,7 +3333,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>261.084112</v>
+        <v>338.854112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -4846,7 +3346,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10269.99</v>
+        <v>10347.76</v>
       </c>
     </row>
     <row r="17">
@@ -4870,17 +3370,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JPMORGAN CHASE &amp; CO</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -4891,29 +3391,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="N17" t="n">
-        <v>289.91</v>
+        <v>166.08</v>
       </c>
       <c r="O17" t="n">
-        <v>28991</v>
+        <v>83040</v>
       </c>
       <c r="P17" t="n">
-        <v>298.02</v>
+        <v>174.0753942</v>
       </c>
       <c r="Q17" t="n">
-        <v>298.02</v>
+        <v>174.0753942</v>
       </c>
       <c r="R17" t="n">
-        <v>29802</v>
+        <v>87037.6971</v>
       </c>
       <c r="S17" t="n">
-        <v>-811</v>
+        <v>-3997.6971</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4922,11 +3422,11 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>28991</v>
+        <v>83040</v>
       </c>
     </row>
     <row r="18">
@@ -4945,55 +3445,65 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>COMMON</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NVIDIA CORP</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I18" t="n">
+        <v>560</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>175.64</v>
+        <v>35.44</v>
       </c>
       <c r="O18" t="n">
-        <v>17564</v>
+        <v>7088</v>
       </c>
       <c r="P18" t="n">
-        <v>184.355</v>
+        <v>23.5270125</v>
       </c>
       <c r="Q18" t="n">
-        <v>184.355</v>
+        <v>23.5270125</v>
       </c>
       <c r="R18" t="n">
-        <v>18435.5</v>
+        <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>-871.5</v>
+        <v>2382.5975</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5002,11 +3512,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>17564</v>
+        <v>7088</v>
       </c>
     </row>
     <row r="19">
@@ -5025,55 +3535,65 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>620</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>166.22</v>
+        <v>31.045</v>
       </c>
       <c r="O19" t="n">
-        <v>99732</v>
+        <v>6209</v>
       </c>
       <c r="P19" t="n">
-        <v>173.846763275</v>
+        <v>20.1350875</v>
       </c>
       <c r="Q19" t="n">
-        <v>173.846763275</v>
+        <v>20.1350875</v>
       </c>
       <c r="R19" t="n">
-        <v>104308.057965</v>
+        <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>-4576.057965</v>
+        <v>2181.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -5082,11 +3602,11 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>99732</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="20">
@@ -5110,64 +3630,64 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AAPL  260327C00290000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AAPL 27MAR26 290 C</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>290</v>
+        <v>425</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0001</v>
+        <v>9.7484</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01</v>
+        <v>-1949.68</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1405125</v>
+        <v>6.3929546</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.1405125</v>
+        <v>6.3929546</v>
       </c>
       <c r="R20" t="n">
-        <v>214.05125</v>
+        <v>-1278.59092</v>
       </c>
       <c r="S20" t="n">
-        <v>-214.04125</v>
+        <v>-671.08908</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -5176,7 +3696,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.01</v>
+        <v>-1949.68</v>
       </c>
     </row>
     <row r="21">
@@ -5200,64 +3720,64 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NFLX  260327C00085000</t>
+          <t>SPY   261218P00505000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NFLX 27MAR26 85 C</t>
+          <t>SPY 18DEC26 505 P</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>85</v>
+        <v>505</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>8.513500000000001</v>
+        <v>10.72</v>
       </c>
       <c r="O21" t="n">
-        <v>851.35</v>
+        <v>-2144</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5205125</v>
+        <v>7.3496796</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5205125</v>
+        <v>7.3496796</v>
       </c>
       <c r="R21" t="n">
-        <v>252.05125</v>
+        <v>-1469.93592</v>
       </c>
       <c r="S21" t="n">
-        <v>599.29875</v>
+        <v>-674.06408</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -5266,1357 +3786,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>851.35</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>QQQ   261218P00560000</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>QQQ 18DEC26 560 P</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I22" t="n">
-        <v>560</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>33.8519</v>
-      </c>
-      <c r="O22" t="n">
-        <v>6770.38</v>
-      </c>
-      <c r="P22" t="n">
-        <v>23.5270125</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>23.5270125</v>
-      </c>
-      <c r="R22" t="n">
-        <v>4705.4025</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2064.9775</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>6770.38</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SPY   261218P00620000</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 620 P</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" t="n">
-        <v>620</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>30.02</v>
-      </c>
-      <c r="O23" t="n">
-        <v>6004</v>
-      </c>
-      <c r="P23" t="n">
-        <v>20.1350875</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>20.1350875</v>
-      </c>
-      <c r="R23" t="n">
-        <v>4027.0175</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1976.9825</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>6004</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>AAPL  260327P00250000</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>AAPL 27MAR26 250 P</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" t="n">
-        <v>250</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.545</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-254.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.7694546</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.7694546</v>
-      </c>
-      <c r="R24" t="n">
-        <v>-176.94546</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-77.55454</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>-254.5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>AAPL  260327C00285000</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>AAPL 27MAR26 285 C</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>100</v>
-      </c>
-      <c r="I25" t="n">
-        <v>285</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3.4194546</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.4194546</v>
-      </c>
-      <c r="R25" t="n">
-        <v>-341.94546</v>
-      </c>
-      <c r="S25" t="n">
-        <v>341.93546</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>AMD   260327P00185000</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>AMD 27MAR26 185 P</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" t="n">
-        <v>185</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-70.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>4.1794546</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.1794546</v>
-      </c>
-      <c r="R26" t="n">
-        <v>-417.94546</v>
-      </c>
-      <c r="S26" t="n">
-        <v>347.44546</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V26" t="n">
-        <v>-70.5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>AMD   260327C00255000</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>AMD 27MAR26 255 C</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>100</v>
-      </c>
-      <c r="I27" t="n">
-        <v>255</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.3694546</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.3694546</v>
-      </c>
-      <c r="R27" t="n">
-        <v>-236.94546</v>
-      </c>
-      <c r="S27" t="n">
-        <v>236.92546</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>AMZN  260327P00190000</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>AMZN 27MAR26 190 P</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" t="n">
-        <v>190</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.7994546</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.7994546</v>
-      </c>
-      <c r="R28" t="n">
-        <v>-179.94546</v>
-      </c>
-      <c r="S28" t="n">
-        <v>168.44546</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>GOOGL 260327P00295000</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>GOOGL 27MAR26 295 P</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" t="n">
-        <v>295</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-187.5</v>
-      </c>
-      <c r="P29" t="n">
-        <v>5.9694626</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.9694626</v>
-      </c>
-      <c r="R29" t="n">
-        <v>-596.9462600000001</v>
-      </c>
-      <c r="S29" t="n">
-        <v>409.44626</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>-187.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>GOOGL 260327C00315000</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>GOOGL 27MAR26 315 C</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>100</v>
-      </c>
-      <c r="I30" t="n">
-        <v>315</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-40</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3.2300876</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.2300876</v>
-      </c>
-      <c r="R30" t="n">
-        <v>-323.00876</v>
-      </c>
-      <c r="S30" t="n">
-        <v>283.00876</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>JPM   260327C00297500</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>JPM 27MAR26 297.5 C</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" t="n">
-        <v>297.5</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.305</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-130.5</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4.8394876</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.8394876</v>
-      </c>
-      <c r="R31" t="n">
-        <v>-483.94876</v>
-      </c>
-      <c r="S31" t="n">
-        <v>353.44876</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>-130.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>MSFT  260327P00360000</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>MSFT 27MAR26 360 P</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I32" t="n">
-        <v>360</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="O32" t="n">
-        <v>-34</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.1094546</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.1094546</v>
-      </c>
-      <c r="R32" t="n">
-        <v>-210.94546</v>
-      </c>
-      <c r="S32" t="n">
-        <v>176.94546</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>-34</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>NFLX  260327P00072000</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NFLX 27MAR26 72 P</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" t="n">
-        <v>72</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="O33" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0.8794546</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.8794546</v>
-      </c>
-      <c r="R33" t="n">
-        <v>-87.94546</v>
-      </c>
-      <c r="S33" t="n">
-        <v>87.15546000000001</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>NFLX  260327C00083000</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>NFLX 27MAR26 83 C</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" t="n">
-        <v>83</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>10.4879</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-1048.79</v>
-      </c>
-      <c r="P34" t="n">
-        <v>3.2794546</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.2794546</v>
-      </c>
-      <c r="R34" t="n">
-        <v>-327.94546</v>
-      </c>
-      <c r="S34" t="n">
-        <v>-720.8445400000001</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>-1048.79</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>QQQ   261218P00425000</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>QQQ 18DEC26 425 P</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" t="n">
-        <v>425</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>9.285</v>
-      </c>
-      <c r="O35" t="n">
-        <v>-1857</v>
-      </c>
-      <c r="P35" t="n">
-        <v>6.3929546</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.3929546</v>
-      </c>
-      <c r="R35" t="n">
-        <v>-1278.59092</v>
-      </c>
-      <c r="S35" t="n">
-        <v>-578.40908</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>-1857</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" t="n">
-        <v>505</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N36" t="n">
-        <v>10.365</v>
-      </c>
-      <c r="O36" t="n">
-        <v>-2073</v>
-      </c>
-      <c r="P36" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="R36" t="n">
-        <v>-1469.93592</v>
-      </c>
-      <c r="S36" t="n">
-        <v>-603.06408</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>-2073</v>
+        <v>-2144</v>
       </c>
     </row>
   </sheetData>
@@ -6663,17 +3833,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$317,732.20</t>
+          <t>$239,183.77</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$105,439.19</t>
+          <t>$184,039.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$423,171.39</t>
+          <t>$423,223.11</t>
         </is>
       </c>
     </row>
@@ -6685,17 +3855,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$439,616.23</t>
+          <t>$367,986.72</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$92,135.58</t>
+          <t>$164,422.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$531,751.81</t>
+          <t>$532,408.83</t>
         </is>
       </c>
     </row>
@@ -6713,17 +3883,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$757,348.43</t>
+          <t>$607,170.49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$197,574.77</t>
+          <t>$348,461.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$954,923.20</t>
+          <t>$955,631.94</t>
         </is>
       </c>
     </row>
@@ -6771,14 +3941,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24 23:44:49</t>
+          <t>2026-03-25 23:46:34</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -3941,7 +3941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25 23:46:34</t>
+          <t>2026-03-26 03:42:35</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2686</v>
+        <v>1.2632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>383.4</v>
+        <v>384.8</v>
       </c>
       <c r="O2" t="n">
-        <v>19170</v>
+        <v>19240</v>
       </c>
       <c r="P2" t="n">
         <v>406.7530481</v>
@@ -607,7 +607,7 @@
         <v>20337.652405</v>
       </c>
       <c r="S2" t="n">
-        <v>-1167.652405</v>
+        <v>-1097.652405</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>24319.062</v>
+        <v>24303.968</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2686</v>
+        <v>1.2632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>61.71</v>
+        <v>62.69</v>
       </c>
       <c r="O3" t="n">
-        <v>12342</v>
+        <v>12538</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-732.426667</v>
+        <v>-536.426667</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15657.0612</v>
+        <v>15838.0016</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14508</v>
+        <v>0.14484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.02</v>
+        <v>30.44</v>
       </c>
       <c r="O4" t="n">
-        <v>60040</v>
+        <v>60880</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-3372.49376</v>
+        <v>-2532.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8710.6032</v>
+        <v>8817.859199999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1607</v>
+        <v>1.1559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.0705</v>
+        <v>4.18</v>
       </c>
       <c r="O5" t="n">
-        <v>8141</v>
+        <v>8360</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1183.66</v>
+        <v>-964.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9449.2587</v>
+        <v>9663.323999999999</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1607</v>
+        <v>1.1559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="O6" t="n">
-        <v>8550</v>
+        <v>8430</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>205.83</v>
+        <v>85.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9923.985000000001</v>
+        <v>9744.236999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78248</v>
+        <v>0.78037</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.88</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>39040</v>
+        <v>39200</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1728.77315</v>
+        <v>1888.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30548.0192</v>
+        <v>30590.504</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78248</v>
+        <v>0.78037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>517.5</v>
+        <v>535.51</v>
       </c>
       <c r="O8" t="n">
-        <v>38812.5</v>
+        <v>40163.25</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-5421.598992</v>
+        <v>-4070.848992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>30370.005</v>
+        <v>31342.1954025</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.08</v>
+        <v>7.19</v>
       </c>
       <c r="O9" t="n">
-        <v>7080</v>
+        <v>7190</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-1231.237657</v>
+        <v>-1121.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7080</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>183.49</v>
+        <v>192.07</v>
       </c>
       <c r="O10" t="n">
-        <v>5504.7</v>
+        <v>5762.1</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-1038.4</v>
+        <v>-781</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>5504.7</v>
+        <v>5762.1</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.550000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="O11" t="n">
-        <v>955</v>
+        <v>975</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-15.5</v>
+        <v>4.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>955</v>
+        <v>975</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>56.98</v>
+        <v>58.19</v>
       </c>
       <c r="O12" t="n">
-        <v>9116.799999999999</v>
+        <v>9310.4</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>-459.86</v>
+        <v>-266.26</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9116.799999999999</v>
+        <v>9310.4</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>26.8773</v>
+        <v>27.6463</v>
       </c>
       <c r="O13" t="n">
-        <v>10347.76</v>
+        <v>10643.83</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>332.857178</v>
+        <v>628.927178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10347.76</v>
+        <v>10643.83</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>78.31</v>
+        <v>82.47</v>
       </c>
       <c r="O14" t="n">
-        <v>1566.2</v>
+        <v>1649.4</v>
       </c>
       <c r="P14" t="n">
         <v>124.315</v>
@@ -1567,7 +1567,7 @@
         <v>2486.3</v>
       </c>
       <c r="S14" t="n">
-        <v>-920.1</v>
+        <v>-836.9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1566.2</v>
+        <v>1649.4</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>400</v>
       </c>
       <c r="N15" t="n">
-        <v>166.08</v>
+        <v>167.4</v>
       </c>
       <c r="O15" t="n">
-        <v>66432</v>
+        <v>66960</v>
       </c>
       <c r="P15" t="n">
         <v>174.135899437</v>
@@ -1647,7 +1647,7 @@
         <v>69654.359775</v>
       </c>
       <c r="S15" t="n">
-        <v>-3222.359775</v>
+        <v>-2694.359775</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>66432</v>
+        <v>66960</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>35.44</v>
+        <v>33.8661</v>
       </c>
       <c r="O16" t="n">
-        <v>7088</v>
+        <v>6773.22</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2395.9</v>
+        <v>2081.12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>7088</v>
+        <v>6773.22</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>31.045</v>
+        <v>29.555</v>
       </c>
       <c r="O17" t="n">
-        <v>6209</v>
+        <v>5911</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>2181.5025</v>
+        <v>1883.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>6209</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-2</v>
       </c>
       <c r="N18" t="n">
-        <v>9.7484</v>
+        <v>9.1579</v>
       </c>
       <c r="O18" t="n">
-        <v>-1949.68</v>
+        <v>-1831.58</v>
       </c>
       <c r="P18" t="n">
         <v>6.3644671</v>
@@ -1917,7 +1917,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S18" t="n">
-        <v>-676.78658</v>
+        <v>-558.68658</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-1949.68</v>
+        <v>-1831.58</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-2</v>
       </c>
       <c r="N19" t="n">
-        <v>10.72</v>
+        <v>10.11</v>
       </c>
       <c r="O19" t="n">
-        <v>-2144</v>
+        <v>-2022</v>
       </c>
       <c r="P19" t="n">
         <v>7.3548796</v>
@@ -2007,7 +2007,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S19" t="n">
-        <v>-673.02408</v>
+        <v>-551.02408</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-2144</v>
+        <v>-2022</v>
       </c>
     </row>
   </sheetData>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2686</v>
+        <v>1.2632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2191,17 +2191,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>383.4</v>
+        <v>384.8</v>
       </c>
       <c r="O2" t="n">
-        <v>26838</v>
+        <v>26936</v>
       </c>
       <c r="P2" t="n">
         <v>407.503306971</v>
@@ -2213,7 +2213,7 @@
         <v>28525.231488</v>
       </c>
       <c r="S2" t="n">
-        <v>-1687.231488</v>
+        <v>-1589.231488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>34046.6868</v>
+        <v>34025.5552</v>
       </c>
     </row>
     <row r="3">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2686</v>
+        <v>1.2632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2271,17 +2271,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>61.71</v>
+        <v>62.69</v>
       </c>
       <c r="O3" t="n">
-        <v>18513</v>
+        <v>18807</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2293,7 +2293,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-1215.8595</v>
+        <v>-921.8595</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23485.5918</v>
+        <v>23757.0024</v>
       </c>
     </row>
     <row r="4">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14508</v>
+        <v>0.14484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2351,17 +2351,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.02</v>
+        <v>30.44</v>
       </c>
       <c r="O4" t="n">
-        <v>60040</v>
+        <v>60880</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2373,7 +2373,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-3352.47719</v>
+        <v>-2512.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8710.6032</v>
+        <v>8817.859199999999</v>
       </c>
     </row>
     <row r="5">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1607</v>
+        <v>1.1559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2431,17 +2431,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.0705</v>
+        <v>4.18</v>
       </c>
       <c r="O5" t="n">
-        <v>12211.5</v>
+        <v>12540</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2453,7 +2453,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1763.739091</v>
+        <v>-1435.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14173.88805</v>
+        <v>14494.986</v>
       </c>
     </row>
     <row r="6">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1607</v>
+        <v>1.1559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>44.82</v>
+        <v>44.98</v>
       </c>
       <c r="O6" t="n">
-        <v>44820</v>
+        <v>44980</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2533,7 +2533,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>1810</v>
+        <v>1970</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>52022.574</v>
+        <v>51992.382</v>
       </c>
     </row>
     <row r="7">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1607</v>
+        <v>1.1559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2591,17 +2591,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="O7" t="n">
-        <v>8550</v>
+        <v>8430</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2613,7 +2613,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>205.83</v>
+        <v>85.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>9923.985000000001</v>
+        <v>9744.236999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78248</v>
+        <v>0.78037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2671,17 +2671,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.88</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>48800</v>
+        <v>49000</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2693,7 +2693,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11531.8184</v>
+        <v>11731.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38185.024</v>
+        <v>38238.13</v>
       </c>
     </row>
     <row r="9">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78248</v>
+        <v>0.78037</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2751,17 +2751,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>517.5</v>
+        <v>535.51</v>
       </c>
       <c r="O9" t="n">
-        <v>38812.5</v>
+        <v>40163.25</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -2773,7 +2773,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-5410.8504</v>
+        <v>-4060.1004</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>30370.005</v>
+        <v>31342.1954025</v>
       </c>
     </row>
     <row r="10">
@@ -2831,17 +2831,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.08</v>
+        <v>7.19</v>
       </c>
       <c r="O10" t="n">
-        <v>7788</v>
+        <v>7909</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -2853,7 +2853,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1354.847947</v>
+        <v>-1233.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>7788</v>
+        <v>7909</v>
       </c>
     </row>
     <row r="11">
@@ -2911,17 +2911,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>183.49</v>
+        <v>192.07</v>
       </c>
       <c r="O11" t="n">
-        <v>5504.7</v>
+        <v>5762.1</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -2933,7 +2933,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-1034.5</v>
+        <v>-777.1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5504.7</v>
+        <v>5762.1</v>
       </c>
     </row>
     <row r="12">
@@ -2991,17 +2991,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.550000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1910</v>
+        <v>1950</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3013,7 +3013,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-318.5</v>
+        <v>-278.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1910</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="13">
@@ -3071,17 +3071,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>290.44</v>
+        <v>290.93</v>
       </c>
       <c r="O13" t="n">
-        <v>29044</v>
+        <v>29093</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -3093,7 +3093,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-4143.755</v>
+        <v>-4094.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>29044</v>
+        <v>29093</v>
       </c>
     </row>
     <row r="14">
@@ -3151,17 +3151,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>56.98</v>
+        <v>58.19</v>
       </c>
       <c r="O14" t="n">
-        <v>9116.799999999999</v>
+        <v>9310.4</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3173,7 +3173,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-515.64</v>
+        <v>-322.04</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9116.799999999999</v>
+        <v>9310.4</v>
       </c>
     </row>
     <row r="15">
@@ -3231,17 +3231,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>66.12</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>1113.78</v>
+        <v>1156.9</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3253,7 +3253,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>764.733421</v>
+        <v>807.853421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1113.78</v>
+        <v>1156.9</v>
       </c>
     </row>
     <row r="16">
@@ -3311,17 +3311,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.8773</v>
+        <v>27.6463</v>
       </c>
       <c r="O16" t="n">
-        <v>10347.76</v>
+        <v>10643.83</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3333,7 +3333,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>338.854112</v>
+        <v>634.924112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10347.76</v>
+        <v>10643.83</v>
       </c>
     </row>
     <row r="17">
@@ -3391,17 +3391,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>500</v>
       </c>
       <c r="N17" t="n">
-        <v>166.08</v>
+        <v>167.4</v>
       </c>
       <c r="O17" t="n">
-        <v>83040</v>
+        <v>83700</v>
       </c>
       <c r="P17" t="n">
         <v>174.0753942</v>
@@ -3413,7 +3413,7 @@
         <v>87037.6971</v>
       </c>
       <c r="S17" t="n">
-        <v>-3997.6971</v>
+        <v>-3337.6971</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>83040</v>
+        <v>83700</v>
       </c>
     </row>
     <row r="18">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>35.44</v>
+        <v>33.8661</v>
       </c>
       <c r="O18" t="n">
-        <v>7088</v>
+        <v>6773.22</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3503,7 +3503,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>2382.5975</v>
+        <v>2067.8175</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>7088</v>
+        <v>6773.22</v>
       </c>
     </row>
     <row r="19">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>31.045</v>
+        <v>29.555</v>
       </c>
       <c r="O19" t="n">
-        <v>6209</v>
+        <v>5911</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3593,7 +3593,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>2181.9825</v>
+        <v>1883.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>6209</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="20">
@@ -3661,17 +3661,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>9.7484</v>
+        <v>9.1579</v>
       </c>
       <c r="O20" t="n">
-        <v>-1949.68</v>
+        <v>-1831.58</v>
       </c>
       <c r="P20" t="n">
         <v>6.3929546</v>
@@ -3683,7 +3683,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S20" t="n">
-        <v>-671.08908</v>
+        <v>-552.9890799999999</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1949.68</v>
+        <v>-1831.58</v>
       </c>
     </row>
     <row r="21">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>10.72</v>
+        <v>10.11</v>
       </c>
       <c r="O21" t="n">
-        <v>-2144</v>
+        <v>-2022</v>
       </c>
       <c r="P21" t="n">
         <v>7.3496796</v>
@@ -3773,7 +3773,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S21" t="n">
-        <v>-674.06408</v>
+        <v>-552.06408</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-2144</v>
+        <v>-2022</v>
       </c>
     </row>
   </sheetData>
@@ -3833,17 +3833,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$239,183.77</t>
+          <t>$241,621.46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$184,039.34</t>
+          <t>$183,780.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$423,223.11</t>
+          <t>$425,401.66</t>
         </is>
       </c>
     </row>
@@ -3855,17 +3855,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$367,986.72</t>
+          <t>$370,768.22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$164,422.11</t>
+          <t>$164,095.39</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$532,408.83</t>
+          <t>$534,863.61</t>
         </is>
       </c>
     </row>
@@ -3883,17 +3883,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$607,170.49</t>
+          <t>$612,389.68</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$348,461.45</t>
+          <t>$347,875.59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$955,631.94</t>
+          <t>$960,265.26</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 03:42:35</t>
+          <t>2026-03-26 23:45:25</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2632</v>
+        <v>1.2575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>384.8</v>
+        <v>378.7</v>
       </c>
       <c r="O2" t="n">
-        <v>19240</v>
+        <v>18935</v>
       </c>
       <c r="P2" t="n">
         <v>406.7530481</v>
@@ -607,7 +607,7 @@
         <v>20337.652405</v>
       </c>
       <c r="S2" t="n">
-        <v>-1097.652405</v>
+        <v>-1402.652405</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>24303.968</v>
+        <v>23810.7625</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2632</v>
+        <v>1.2575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>62.69</v>
+        <v>61.7</v>
       </c>
       <c r="O3" t="n">
-        <v>12538</v>
+        <v>12340</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-536.426667</v>
+        <v>-734.426667</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15838.0016</v>
+        <v>15517.55</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14484</v>
+        <v>0.14451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.44</v>
+        <v>30.06</v>
       </c>
       <c r="O4" t="n">
-        <v>60880</v>
+        <v>60120</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-2532.49376</v>
+        <v>-3292.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8817.859199999999</v>
+        <v>8687.941199999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1559</v>
+        <v>1.1528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.18</v>
+        <v>4.058</v>
       </c>
       <c r="O5" t="n">
-        <v>8360</v>
+        <v>8116</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-964.66</v>
+        <v>-1208.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9663.323999999999</v>
+        <v>9356.1248</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1559</v>
+        <v>1.1528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>562</v>
+        <v>528</v>
       </c>
       <c r="O6" t="n">
-        <v>8430</v>
+        <v>7920</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>85.83</v>
+        <v>-424.17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9744.236999999999</v>
+        <v>9130.175999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78037</v>
+        <v>0.77791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30590.504</v>
+        <v>30494.072</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78037</v>
+        <v>0.77791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>535.51</v>
+        <v>522.3</v>
       </c>
       <c r="O8" t="n">
-        <v>40163.25</v>
+        <v>39172.5</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-4070.848992</v>
+        <v>-5061.598992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31342.1954025</v>
+        <v>30472.679475</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.19</v>
+        <v>7.045</v>
       </c>
       <c r="O9" t="n">
-        <v>7190</v>
+        <v>7045</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-1121.237657</v>
+        <v>-1266.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7190</v>
+        <v>7045</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>192.07</v>
+        <v>187.56</v>
       </c>
       <c r="O10" t="n">
-        <v>5762.1</v>
+        <v>5626.8</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-781</v>
+        <v>-916.3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>5762.1</v>
+        <v>5626.8</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.75</v>
+        <v>9.42</v>
       </c>
       <c r="O11" t="n">
-        <v>975</v>
+        <v>942</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>4.5</v>
+        <v>-28.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>975</v>
+        <v>942</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>58.19</v>
+        <v>56.48</v>
       </c>
       <c r="O12" t="n">
-        <v>9310.4</v>
+        <v>9036.799999999999</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>-266.26</v>
+        <v>-539.86</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9310.4</v>
+        <v>9036.799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>27.6463</v>
+        <v>26.9704</v>
       </c>
       <c r="O13" t="n">
-        <v>10643.83</v>
+        <v>10383.6</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>628.927178</v>
+        <v>368.697178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10643.83</v>
+        <v>10383.6</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>82.47</v>
+        <v>79.86</v>
       </c>
       <c r="O14" t="n">
-        <v>1649.4</v>
+        <v>1597.2</v>
       </c>
       <c r="P14" t="n">
         <v>124.315</v>
@@ -1567,7 +1567,7 @@
         <v>2486.3</v>
       </c>
       <c r="S14" t="n">
-        <v>-836.9</v>
+        <v>-889.1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1649.4</v>
+        <v>1597.2</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>400</v>
       </c>
       <c r="N15" t="n">
-        <v>167.4</v>
+        <v>164.82</v>
       </c>
       <c r="O15" t="n">
-        <v>66960</v>
+        <v>65928</v>
       </c>
       <c r="P15" t="n">
         <v>174.135899437</v>
@@ -1647,7 +1647,7 @@
         <v>69654.359775</v>
       </c>
       <c r="S15" t="n">
-        <v>-2694.359775</v>
+        <v>-3726.359775</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>66960</v>
+        <v>65928</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>33.8661</v>
+        <v>38.9897</v>
       </c>
       <c r="O16" t="n">
-        <v>6773.22</v>
+        <v>7797.94</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2081.12</v>
+        <v>3105.84</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>6773.22</v>
+        <v>7797.94</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>29.555</v>
+        <v>33.645</v>
       </c>
       <c r="O17" t="n">
-        <v>5911</v>
+        <v>6729</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>1883.5025</v>
+        <v>2701.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>5911</v>
+        <v>6729</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-2</v>
       </c>
       <c r="N18" t="n">
-        <v>9.1579</v>
+        <v>10.6266</v>
       </c>
       <c r="O18" t="n">
-        <v>-1831.58</v>
+        <v>-2125.32</v>
       </c>
       <c r="P18" t="n">
         <v>6.3644671</v>
@@ -1917,7 +1917,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S18" t="n">
-        <v>-558.68658</v>
+        <v>-852.4265799999999</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-1831.58</v>
+        <v>-2125.32</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-2</v>
       </c>
       <c r="N19" t="n">
-        <v>10.11</v>
+        <v>11.555</v>
       </c>
       <c r="O19" t="n">
-        <v>-2022</v>
+        <v>-2311</v>
       </c>
       <c r="P19" t="n">
         <v>7.3548796</v>
@@ -2007,7 +2007,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S19" t="n">
-        <v>-551.02408</v>
+        <v>-840.02408</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-2022</v>
+        <v>-2311</v>
       </c>
     </row>
   </sheetData>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2632</v>
+        <v>1.2575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2191,17 +2191,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>384.8</v>
+        <v>378.7</v>
       </c>
       <c r="O2" t="n">
-        <v>26936</v>
+        <v>26509</v>
       </c>
       <c r="P2" t="n">
         <v>407.503306971</v>
@@ -2213,7 +2213,7 @@
         <v>28525.231488</v>
       </c>
       <c r="S2" t="n">
-        <v>-1589.231488</v>
+        <v>-2016.231488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>34025.5552</v>
+        <v>33335.0675</v>
       </c>
     </row>
     <row r="3">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2632</v>
+        <v>1.2575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2271,17 +2271,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>62.69</v>
+        <v>61.7</v>
       </c>
       <c r="O3" t="n">
-        <v>18807</v>
+        <v>18510</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2293,7 +2293,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-921.8595</v>
+        <v>-1218.8595</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23757.0024</v>
+        <v>23276.325</v>
       </c>
     </row>
     <row r="4">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14484</v>
+        <v>0.14451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2351,17 +2351,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.44</v>
+        <v>30.06</v>
       </c>
       <c r="O4" t="n">
-        <v>60880</v>
+        <v>60120</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2373,7 +2373,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-2512.47719</v>
+        <v>-3272.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8817.859199999999</v>
+        <v>8687.941199999999</v>
       </c>
     </row>
     <row r="5">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1559</v>
+        <v>1.1528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2431,17 +2431,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.18</v>
+        <v>4.058</v>
       </c>
       <c r="O5" t="n">
-        <v>12540</v>
+        <v>12174</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2453,7 +2453,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1435.239091</v>
+        <v>-1801.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14494.986</v>
+        <v>14034.1872</v>
       </c>
     </row>
     <row r="6">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1559</v>
+        <v>1.1528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>44.98</v>
+        <v>44.72</v>
       </c>
       <c r="O6" t="n">
-        <v>44980</v>
+        <v>44720</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2533,7 +2533,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>1970</v>
+        <v>1710</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>51992.382</v>
+        <v>51553.216</v>
       </c>
     </row>
     <row r="7">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1559</v>
+        <v>1.1528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2591,17 +2591,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>562</v>
+        <v>528</v>
       </c>
       <c r="O7" t="n">
-        <v>8430</v>
+        <v>7920</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2613,7 +2613,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>85.83</v>
+        <v>-424.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>9744.236999999999</v>
+        <v>9130.175999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78037</v>
+        <v>0.77791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38238.13</v>
+        <v>38117.59</v>
       </c>
     </row>
     <row r="9">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78037</v>
+        <v>0.77791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2751,17 +2751,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>535.51</v>
+        <v>522.3</v>
       </c>
       <c r="O9" t="n">
-        <v>40163.25</v>
+        <v>39172.5</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -2773,7 +2773,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-4060.1004</v>
+        <v>-5050.8504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>31342.1954025</v>
+        <v>30472.679475</v>
       </c>
     </row>
     <row r="10">
@@ -2831,17 +2831,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.19</v>
+        <v>7.045</v>
       </c>
       <c r="O10" t="n">
-        <v>7909</v>
+        <v>7749.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -2853,7 +2853,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1233.847947</v>
+        <v>-1393.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>7909</v>
+        <v>7749.5</v>
       </c>
     </row>
     <row r="11">
@@ -2911,17 +2911,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>192.07</v>
+        <v>187.56</v>
       </c>
       <c r="O11" t="n">
-        <v>5762.1</v>
+        <v>5626.8</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -2933,7 +2933,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-777.1</v>
+        <v>-912.4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5762.1</v>
+        <v>5626.8</v>
       </c>
     </row>
     <row r="12">
@@ -2991,17 +2991,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>9.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1950</v>
+        <v>1884</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3013,7 +3013,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-278.5</v>
+        <v>-344.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1950</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="13">
@@ -3071,17 +3071,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>290.93</v>
+        <v>280.92</v>
       </c>
       <c r="O13" t="n">
-        <v>29093</v>
+        <v>28092</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -3093,7 +3093,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-4094.755</v>
+        <v>-5095.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>29093</v>
+        <v>28092</v>
       </c>
     </row>
     <row r="14">
@@ -3151,17 +3151,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>58.19</v>
+        <v>56.48</v>
       </c>
       <c r="O14" t="n">
-        <v>9310.4</v>
+        <v>9036.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3173,7 +3173,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-322.04</v>
+        <v>-595.64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9310.4</v>
+        <v>9036.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -3231,17 +3231,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>68.68000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1156.9</v>
+        <v>1115.13</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3253,7 +3253,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>807.853421</v>
+        <v>766.083421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1156.9</v>
+        <v>1115.13</v>
       </c>
     </row>
     <row r="16">
@@ -3311,17 +3311,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.6463</v>
+        <v>26.9704</v>
       </c>
       <c r="O16" t="n">
-        <v>10643.83</v>
+        <v>10383.6</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3333,7 +3333,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>634.924112</v>
+        <v>374.694112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10643.83</v>
+        <v>10383.6</v>
       </c>
     </row>
     <row r="17">
@@ -3391,17 +3391,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>500</v>
       </c>
       <c r="N17" t="n">
-        <v>167.4</v>
+        <v>164.82</v>
       </c>
       <c r="O17" t="n">
-        <v>83700</v>
+        <v>82410</v>
       </c>
       <c r="P17" t="n">
         <v>174.0753942</v>
@@ -3413,7 +3413,7 @@
         <v>87037.6971</v>
       </c>
       <c r="S17" t="n">
-        <v>-3337.6971</v>
+        <v>-4627.6971</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>83700</v>
+        <v>82410</v>
       </c>
     </row>
     <row r="18">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>33.8661</v>
+        <v>38.9897</v>
       </c>
       <c r="O18" t="n">
-        <v>6773.22</v>
+        <v>7797.94</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3503,7 +3503,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>2067.8175</v>
+        <v>3092.5375</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>6773.22</v>
+        <v>7797.94</v>
       </c>
     </row>
     <row r="19">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>29.555</v>
+        <v>33.645</v>
       </c>
       <c r="O19" t="n">
-        <v>5911</v>
+        <v>6729</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3593,7 +3593,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>1883.9825</v>
+        <v>2701.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>5911</v>
+        <v>6729</v>
       </c>
     </row>
     <row r="20">
@@ -3661,17 +3661,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>9.1579</v>
+        <v>10.6266</v>
       </c>
       <c r="O20" t="n">
-        <v>-1831.58</v>
+        <v>-2125.32</v>
       </c>
       <c r="P20" t="n">
         <v>6.3929546</v>
@@ -3683,7 +3683,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S20" t="n">
-        <v>-552.9890799999999</v>
+        <v>-846.72908</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1831.58</v>
+        <v>-2125.32</v>
       </c>
     </row>
     <row r="21">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>10.11</v>
+        <v>11.555</v>
       </c>
       <c r="O21" t="n">
-        <v>-2022</v>
+        <v>-2311</v>
       </c>
       <c r="P21" t="n">
         <v>7.3496796</v>
@@ -3773,7 +3773,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S21" t="n">
-        <v>-552.06408</v>
+        <v>-841.06408</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-2022</v>
+        <v>-2311</v>
       </c>
     </row>
   </sheetData>
@@ -3833,17 +3833,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$241,621.46</t>
+          <t>$238,119.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$183,780.20</t>
+          <t>$183,495.39</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$425,401.66</t>
+          <t>$421,614.72</t>
         </is>
       </c>
     </row>
@@ -3855,17 +3855,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$370,768.22</t>
+          <t>$364,995.63</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$164,095.39</t>
+          <t>$163,734.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$534,863.61</t>
+          <t>$528,730.09</t>
         </is>
       </c>
     </row>
@@ -3883,17 +3883,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$612,389.68</t>
+          <t>$603,114.96</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$347,875.59</t>
+          <t>$347,229.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$960,265.26</t>
+          <t>$950,344.81</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 23:45:25</t>
+          <t>2026-03-27 23:44:59</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -3941,7 +3941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-28 23:44:47</t>
+          <t>2026-03-29 23:45:48</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -3941,7 +3941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-29 23:45:48</t>
+          <t>2026-03-30 23:47:15</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2515</v>
+        <v>1.2508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>370.5</v>
+        <v>368.7</v>
       </c>
       <c r="O2" t="n">
-        <v>18525</v>
+        <v>18435</v>
       </c>
       <c r="P2" t="n">
         <v>406.7530481</v>
@@ -607,7 +607,7 @@
         <v>20337.652405</v>
       </c>
       <c r="S2" t="n">
-        <v>-1812.652405</v>
+        <v>-1902.652405</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>23184.0375</v>
+        <v>23058.498</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2515</v>
+        <v>1.2508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>60.73</v>
+        <v>60.94</v>
       </c>
       <c r="O3" t="n">
-        <v>12146</v>
+        <v>12188</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-928.426667</v>
+        <v>-886.426667</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15200.719</v>
+        <v>15244.7504</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14452</v>
+        <v>0.14458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.24</v>
+        <v>30.1</v>
       </c>
       <c r="O4" t="n">
-        <v>60480</v>
+        <v>60200</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-2932.49376</v>
+        <v>-3212.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8740.569600000001</v>
+        <v>8703.715999999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.151</v>
+        <v>1.1462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.045</v>
+        <v>4.0525</v>
       </c>
       <c r="O5" t="n">
-        <v>8090</v>
+        <v>8105</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1234.66</v>
+        <v>-1219.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9311.59</v>
+        <v>9289.951000000001</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.151</v>
+        <v>1.1462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>514</v>
+        <v>472</v>
       </c>
       <c r="O6" t="n">
-        <v>7710</v>
+        <v>7080</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>-634.17</v>
+        <v>-1264.17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>8874.210000000001</v>
+        <v>8115.096</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7758</v>
+        <v>0.77441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30411.36</v>
+        <v>30356.872</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7758</v>
+        <v>0.77441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>524.11</v>
+        <v>537.6</v>
       </c>
       <c r="O8" t="n">
-        <v>39308.25</v>
+        <v>40320</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-4925.848992</v>
+        <v>-3914.098992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>30495.34035</v>
+        <v>31224.2112</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.08</v>
+        <v>7.005</v>
       </c>
       <c r="O9" t="n">
-        <v>7080</v>
+        <v>7005</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-1231.237657</v>
+        <v>-1306.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7080</v>
+        <v>7005</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>193.4</v>
+        <v>191.86</v>
       </c>
       <c r="O10" t="n">
-        <v>5802</v>
+        <v>5755.8</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-741.1</v>
+        <v>-787.3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>5802</v>
+        <v>5755.8</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.07</v>
+        <v>9.15</v>
       </c>
       <c r="O11" t="n">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-63.5</v>
+        <v>-55.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>907</v>
+        <v>915</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>55.295</v>
+        <v>54.83</v>
       </c>
       <c r="O12" t="n">
-        <v>8847.200000000001</v>
+        <v>8772.799999999999</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>-729.46</v>
+        <v>-803.86</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>8847.200000000001</v>
+        <v>8772.799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>26.5515</v>
+        <v>26.1059</v>
       </c>
       <c r="O13" t="n">
-        <v>10222.33</v>
+        <v>10050.77</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>207.427178</v>
+        <v>35.867178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10222.33</v>
+        <v>10050.77</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>78.16</v>
+        <v>78.31</v>
       </c>
       <c r="O14" t="n">
-        <v>1563.2</v>
+        <v>1566.2</v>
       </c>
       <c r="P14" t="n">
         <v>124.315</v>
@@ -1567,7 +1567,7 @@
         <v>2486.3</v>
       </c>
       <c r="S14" t="n">
-        <v>-923.1</v>
+        <v>-920.1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1563.2</v>
+        <v>1566.2</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>400</v>
       </c>
       <c r="N15" t="n">
-        <v>162.4</v>
+        <v>162.5</v>
       </c>
       <c r="O15" t="n">
-        <v>64960</v>
+        <v>65000</v>
       </c>
       <c r="P15" t="n">
         <v>174.135899437</v>
@@ -1647,7 +1647,7 @@
         <v>69654.359775</v>
       </c>
       <c r="S15" t="n">
-        <v>-4694.359775</v>
+        <v>-4654.359775</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>64960</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>44.0648</v>
+        <v>45.335</v>
       </c>
       <c r="O16" t="n">
-        <v>8812.959999999999</v>
+        <v>9067</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>4120.86</v>
+        <v>4374.9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>8812.959999999999</v>
+        <v>9067</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>38.66</v>
+        <v>38.87</v>
       </c>
       <c r="O17" t="n">
-        <v>7732</v>
+        <v>7774</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>3704.5025</v>
+        <v>3746.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>7732</v>
+        <v>7774</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-2</v>
       </c>
       <c r="N18" t="n">
-        <v>11.7422</v>
+        <v>12.1559</v>
       </c>
       <c r="O18" t="n">
-        <v>-2348.44</v>
+        <v>-2431.18</v>
       </c>
       <c r="P18" t="n">
         <v>6.3644671</v>
@@ -1917,7 +1917,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S18" t="n">
-        <v>-1075.54658</v>
+        <v>-1158.28658</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-2348.44</v>
+        <v>-2431.18</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-2</v>
       </c>
       <c r="N19" t="n">
-        <v>13.32</v>
+        <v>13.15</v>
       </c>
       <c r="O19" t="n">
-        <v>-2664</v>
+        <v>-2630</v>
       </c>
       <c r="P19" t="n">
         <v>7.3548796</v>
@@ -2007,7 +2007,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S19" t="n">
-        <v>-1193.02408</v>
+        <v>-1159.02408</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-2664</v>
+        <v>-2630</v>
       </c>
     </row>
   </sheetData>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2515</v>
+        <v>1.2508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2191,17 +2191,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>370.5</v>
+        <v>368.7</v>
       </c>
       <c r="O2" t="n">
-        <v>25935</v>
+        <v>25809</v>
       </c>
       <c r="P2" t="n">
         <v>407.503306971</v>
@@ -2213,7 +2213,7 @@
         <v>28525.231488</v>
       </c>
       <c r="S2" t="n">
-        <v>-2590.231488</v>
+        <v>-2716.231488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>32457.6525</v>
+        <v>32281.8972</v>
       </c>
     </row>
     <row r="3">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2515</v>
+        <v>1.2508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2271,17 +2271,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>60.73</v>
+        <v>60.94</v>
       </c>
       <c r="O3" t="n">
-        <v>18219</v>
+        <v>18282</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2293,7 +2293,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-1509.8595</v>
+        <v>-1446.8595</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>22801.0785</v>
+        <v>22867.1256</v>
       </c>
     </row>
     <row r="4">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14452</v>
+        <v>0.14458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2351,17 +2351,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.24</v>
+        <v>30.1</v>
       </c>
       <c r="O4" t="n">
-        <v>60480</v>
+        <v>60200</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2373,7 +2373,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-2912.47719</v>
+        <v>-3192.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8740.569600000001</v>
+        <v>8703.715999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.151</v>
+        <v>1.1462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2431,17 +2431,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.045</v>
+        <v>4.0525</v>
       </c>
       <c r="O5" t="n">
-        <v>12135</v>
+        <v>12157.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2453,7 +2453,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1840.239091</v>
+        <v>-1817.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13967.385</v>
+        <v>13934.9265</v>
       </c>
     </row>
     <row r="6">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.151</v>
+        <v>1.1462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>44.17</v>
+        <v>44.71</v>
       </c>
       <c r="O6" t="n">
-        <v>44170</v>
+        <v>44710</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2533,7 +2533,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>1160</v>
+        <v>1700</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>50839.67</v>
+        <v>51246.60200000001</v>
       </c>
     </row>
     <row r="7">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.151</v>
+        <v>1.1462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2591,17 +2591,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>514</v>
+        <v>472</v>
       </c>
       <c r="O7" t="n">
-        <v>7710</v>
+        <v>7080</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2613,7 +2613,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>-634.17</v>
+        <v>-1264.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>8874.210000000001</v>
+        <v>8115.096</v>
       </c>
     </row>
     <row r="8">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7758</v>
+        <v>0.77441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38014.2</v>
+        <v>37946.09</v>
       </c>
     </row>
     <row r="9">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7758</v>
+        <v>0.77441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2751,17 +2751,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>524.11</v>
+        <v>537.6</v>
       </c>
       <c r="O9" t="n">
-        <v>39308.25</v>
+        <v>40320</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -2773,7 +2773,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-4915.1004</v>
+        <v>-3903.3504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>30495.34035</v>
+        <v>31224.2112</v>
       </c>
     </row>
     <row r="10">
@@ -2831,17 +2831,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.08</v>
+        <v>7.005</v>
       </c>
       <c r="O10" t="n">
-        <v>7788</v>
+        <v>7705.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -2853,7 +2853,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1354.847947</v>
+        <v>-1437.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>7788</v>
+        <v>7705.5</v>
       </c>
     </row>
     <row r="11">
@@ -2911,17 +2911,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>193.4</v>
+        <v>191.86</v>
       </c>
       <c r="O11" t="n">
-        <v>5802</v>
+        <v>5755.8</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -2933,7 +2933,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-737.2</v>
+        <v>-783.4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5802</v>
+        <v>5755.8</v>
       </c>
     </row>
     <row r="12">
@@ -2991,17 +2991,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.07</v>
+        <v>9.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1814</v>
+        <v>1830</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3013,7 +3013,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-414.5</v>
+        <v>-398.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1814</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="13">
@@ -3071,17 +3071,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>274.34</v>
+        <v>273.5</v>
       </c>
       <c r="O13" t="n">
-        <v>27434</v>
+        <v>27350</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -3093,7 +3093,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-5753.755</v>
+        <v>-5837.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>27434</v>
+        <v>27350</v>
       </c>
     </row>
     <row r="14">
@@ -3151,17 +3151,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>55.295</v>
+        <v>54.83</v>
       </c>
       <c r="O14" t="n">
-        <v>8847.200000000001</v>
+        <v>8772.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3173,7 +3173,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-785.24</v>
+        <v>-859.64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>8847.200000000001</v>
+        <v>8772.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -3231,17 +3231,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>64.2</v>
+        <v>63.69</v>
       </c>
       <c r="O15" t="n">
-        <v>1081.44</v>
+        <v>1072.85</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3253,7 +3253,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>732.393421</v>
+        <v>723.803421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1081.44</v>
+        <v>1072.85</v>
       </c>
     </row>
     <row r="16">
@@ -3311,17 +3311,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.5515</v>
+        <v>26.1059</v>
       </c>
       <c r="O16" t="n">
-        <v>10222.33</v>
+        <v>10050.77</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3333,7 +3333,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>213.424112</v>
+        <v>41.864112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10222.33</v>
+        <v>10050.77</v>
       </c>
     </row>
     <row r="17">
@@ -3391,17 +3391,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>500</v>
       </c>
       <c r="N17" t="n">
-        <v>162.4</v>
+        <v>162.5</v>
       </c>
       <c r="O17" t="n">
-        <v>81200</v>
+        <v>81250</v>
       </c>
       <c r="P17" t="n">
         <v>174.0753942</v>
@@ -3413,7 +3413,7 @@
         <v>87037.6971</v>
       </c>
       <c r="S17" t="n">
-        <v>-5837.6971</v>
+        <v>-5787.6971</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>81200</v>
+        <v>81250</v>
       </c>
     </row>
     <row r="18">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>44.0648</v>
+        <v>45.335</v>
       </c>
       <c r="O18" t="n">
-        <v>8812.959999999999</v>
+        <v>9067</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3503,7 +3503,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>4107.5575</v>
+        <v>4361.5975</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>8812.959999999999</v>
+        <v>9067</v>
       </c>
     </row>
     <row r="19">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>38.66</v>
+        <v>38.87</v>
       </c>
       <c r="O19" t="n">
-        <v>7732</v>
+        <v>7774</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3593,7 +3593,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>3704.9825</v>
+        <v>3746.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>7732</v>
+        <v>7774</v>
       </c>
     </row>
     <row r="20">
@@ -3661,17 +3661,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>11.7422</v>
+        <v>12.1559</v>
       </c>
       <c r="O20" t="n">
-        <v>-2348.44</v>
+        <v>-2431.18</v>
       </c>
       <c r="P20" t="n">
         <v>6.3929546</v>
@@ -3683,7 +3683,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S20" t="n">
-        <v>-1069.84908</v>
+        <v>-1152.58908</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-2348.44</v>
+        <v>-2431.18</v>
       </c>
     </row>
     <row r="21">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>13.32</v>
+        <v>13.15</v>
       </c>
       <c r="O21" t="n">
-        <v>-2664</v>
+        <v>-2630</v>
       </c>
       <c r="P21" t="n">
         <v>7.3496796</v>
@@ -3773,7 +3773,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S21" t="n">
-        <v>-1194.06408</v>
+        <v>-1160.06408</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-2664</v>
+        <v>-2630</v>
       </c>
     </row>
   </sheetData>
@@ -3833,17 +3833,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$237,132.08</t>
+          <t>$236,838.48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$183,225.04</t>
+          <t>$183,151.69</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$420,357.12</t>
+          <t>$419,990.17</t>
         </is>
       </c>
     </row>
@@ -3855,17 +3855,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$361,911.60</t>
+          <t>$361,887.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$163,387.60</t>
+          <t>$163,268.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$525,299.20</t>
+          <t>$525,155.45</t>
         </is>
       </c>
     </row>
@@ -3883,17 +3883,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$599,043.67</t>
+          <t>$598,725.69</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$346,612.64</t>
+          <t>$346,419.93</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$945,656.32</t>
+          <t>$945,145.62</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30 23:47:15</t>
+          <t>2026-03-31 23:46:23</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2508</v>
+        <v>1.251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,29 +585,29 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>368.7</v>
+        <v>370.75</v>
       </c>
       <c r="O2" t="n">
-        <v>18435</v>
+        <v>22245</v>
       </c>
       <c r="P2" t="n">
-        <v>406.7530481</v>
+        <v>400.28970675</v>
       </c>
       <c r="Q2" t="n">
-        <v>406.7530481</v>
+        <v>400.28970675</v>
       </c>
       <c r="R2" t="n">
-        <v>20337.652405</v>
+        <v>24017.382405</v>
       </c>
       <c r="S2" t="n">
-        <v>-1902.652405</v>
+        <v>-1772.382405</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>23058.498</v>
+        <v>27828.495</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2508</v>
+        <v>1.251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>60.94</v>
+        <v>61.28</v>
       </c>
       <c r="O3" t="n">
-        <v>12188</v>
+        <v>12256</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-886.426667</v>
+        <v>-818.426667</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15244.7504</v>
+        <v>15332.256</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14458</v>
+        <v>0.14517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>60200</v>
+        <v>60000</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-3212.49376</v>
+        <v>-3412.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8703.715999999999</v>
+        <v>8710.199999999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1462</v>
+        <v>1.1553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.0525</v>
+        <v>4.004</v>
       </c>
       <c r="O5" t="n">
-        <v>8105</v>
+        <v>8008</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1219.66</v>
+        <v>-1316.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9289.951000000001</v>
+        <v>9251.642400000001</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1462</v>
+        <v>1.1553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="O6" t="n">
-        <v>7080</v>
+        <v>7650</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>-1264.17</v>
+        <v>-694.17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>8115.096</v>
+        <v>8838.045</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.77441</v>
+        <v>0.7776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>4.883</v>
       </c>
       <c r="O7" t="n">
-        <v>39200</v>
+        <v>39064</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1888.77315</v>
+        <v>1752.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30356.872</v>
+        <v>30376.1664</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77441</v>
+        <v>0.7776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>537.6</v>
+        <v>541.9</v>
       </c>
       <c r="O8" t="n">
-        <v>40320</v>
+        <v>40642.5</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-3914.098992</v>
+        <v>-3591.598992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31224.2112</v>
+        <v>31603.608</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.005</v>
+        <v>6.89</v>
       </c>
       <c r="O9" t="n">
-        <v>7005</v>
+        <v>6890</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-1306.237657</v>
+        <v>-1421.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7005</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>191.86</v>
+        <v>202.98</v>
       </c>
       <c r="O10" t="n">
-        <v>5755.8</v>
+        <v>6089.4</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-787.3</v>
+        <v>-453.7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>5755.8</v>
+        <v>6089.4</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.15</v>
+        <v>9.31</v>
       </c>
       <c r="O11" t="n">
-        <v>915</v>
+        <v>931</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-55.5</v>
+        <v>-39.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>915</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>54.83</v>
+        <v>55.17</v>
       </c>
       <c r="O12" t="n">
-        <v>8772.799999999999</v>
+        <v>8827.200000000001</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>-803.86</v>
+        <v>-749.46</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>8772.799999999999</v>
+        <v>8827.200000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>26.1059</v>
+        <v>26.2202</v>
       </c>
       <c r="O13" t="n">
-        <v>10050.77</v>
+        <v>10094.78</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>35.867178</v>
+        <v>79.877178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10050.77</v>
+        <v>10094.78</v>
       </c>
     </row>
     <row r="14">
@@ -1545,29 +1545,29 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>78.31</v>
+        <v>82.81</v>
       </c>
       <c r="O14" t="n">
-        <v>1566.2</v>
+        <v>3312.4</v>
       </c>
       <c r="P14" t="n">
-        <v>124.315</v>
+        <v>102.0775</v>
       </c>
       <c r="Q14" t="n">
-        <v>124.315</v>
+        <v>102.0775</v>
       </c>
       <c r="R14" t="n">
-        <v>2486.3</v>
+        <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-920.1</v>
+        <v>-770.7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1566.2</v>
+        <v>3312.4</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>400</v>
       </c>
       <c r="N15" t="n">
-        <v>162.5</v>
+        <v>163.46</v>
       </c>
       <c r="O15" t="n">
-        <v>65000</v>
+        <v>65384</v>
       </c>
       <c r="P15" t="n">
         <v>174.135899437</v>
@@ -1647,7 +1647,7 @@
         <v>69654.359775</v>
       </c>
       <c r="S15" t="n">
-        <v>-4654.359775</v>
+        <v>-4270.359775</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>65000</v>
+        <v>65384</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>45.335</v>
+        <v>36.8954</v>
       </c>
       <c r="O16" t="n">
-        <v>9067</v>
+        <v>7379.08</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>4374.9</v>
+        <v>2686.98</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>9067</v>
+        <v>7379.08</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>38.87</v>
+        <v>31.215</v>
       </c>
       <c r="O17" t="n">
-        <v>7774</v>
+        <v>6243</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>3746.5025</v>
+        <v>2215.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>7774</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="18">
@@ -1869,23 +1869,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>META  260501P00520000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>META 01MAY26 520 P</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>425</v>
+        <v>520</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1895,29 +1895,29 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>12.1559</v>
+        <v>12.4537</v>
       </c>
       <c r="O18" t="n">
-        <v>-2431.18</v>
+        <v>-1245.37</v>
       </c>
       <c r="P18" t="n">
-        <v>6.3644671</v>
+        <v>16.3422876</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.3644671</v>
+        <v>16.3422876</v>
       </c>
       <c r="R18" t="n">
-        <v>-1272.89342</v>
+        <v>-1634.22876</v>
       </c>
       <c r="S18" t="n">
-        <v>-1158.28658</v>
+        <v>388.85876</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-2431.18</v>
+        <v>-1245.37</v>
       </c>
     </row>
     <row r="19">
@@ -1959,68 +1959,338 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SPY   261218P00505000</t>
+          <t>MSFT  260501P00355000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 505 P</t>
+          <t>MSFT 01MAY26 355 P</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
+        <v>355</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.1783</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-917.83</v>
+      </c>
+      <c r="P19" t="n">
+        <v>11.0194626</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>11.0194626</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1101.94626</v>
+      </c>
+      <c r="S19" t="n">
+        <v>184.11626</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>-917.83</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>U2739721</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NVDA  260501P00165000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NVDA 01MAY26 165 P</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" t="n">
+        <v>165</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-400</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5.1936876</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.1936876</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-519.36876</v>
+      </c>
+      <c r="S20" t="n">
+        <v>119.36876</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>U2739721</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>QQQ   261218P00425000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>QQQ 18DEC26 425 P</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" t="n">
+        <v>425</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>9.508699999999999</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-1901.74</v>
+      </c>
+      <c r="P21" t="n">
+        <v>6.3644671</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.3644671</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-1272.89342</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-628.84658</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>-1901.74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U2739721</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SPY   261218P00505000</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SPY 18DEC26 505 P</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" t="n">
         <v>505</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>2026-12-18</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
         <v>-2</v>
       </c>
-      <c r="N19" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-2630</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="N22" t="n">
+        <v>10.267</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-2053.4</v>
+      </c>
+      <c r="P22" t="n">
         <v>7.3548796</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q22" t="n">
         <v>7.3548796</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R22" t="n">
         <v>-1470.97592</v>
       </c>
-      <c r="S19" t="n">
-        <v>-1159.02408</v>
-      </c>
-      <c r="T19" t="inlineStr">
+      <c r="S22" t="n">
+        <v>-582.42408</v>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="V19" t="n">
-        <v>-2630</v>
+      <c r="V22" t="n">
+        <v>-2053.4</v>
       </c>
     </row>
   </sheetData>
@@ -2161,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2508</v>
+        <v>1.251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2191,29 +2461,29 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="N2" t="n">
-        <v>368.7</v>
+        <v>370.75</v>
       </c>
       <c r="O2" t="n">
-        <v>25809</v>
+        <v>29660</v>
       </c>
       <c r="P2" t="n">
-        <v>407.503306971</v>
+        <v>402.9867686</v>
       </c>
       <c r="Q2" t="n">
-        <v>407.503306971</v>
+        <v>402.9867686</v>
       </c>
       <c r="R2" t="n">
-        <v>28525.231488</v>
+        <v>32238.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>-2716.231488</v>
+        <v>-2578.941488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2226,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>32281.8972</v>
+        <v>37104.66</v>
       </c>
     </row>
     <row r="3">
@@ -2241,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2508</v>
+        <v>1.251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2271,17 +2541,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>60.94</v>
+        <v>61.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18282</v>
+        <v>18384</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2293,7 +2563,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-1446.8595</v>
+        <v>-1344.8595</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2306,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>22867.1256</v>
+        <v>22998.384</v>
       </c>
     </row>
     <row r="4">
@@ -2321,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14458</v>
+        <v>0.14517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2351,17 +2621,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>60200</v>
+        <v>60000</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2373,7 +2643,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-3192.47719</v>
+        <v>-3392.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2386,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8703.715999999999</v>
+        <v>8710.199999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2401,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1462</v>
+        <v>1.1553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2431,17 +2701,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.0525</v>
+        <v>4.004</v>
       </c>
       <c r="O5" t="n">
-        <v>12157.5</v>
+        <v>12012</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2453,7 +2723,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1817.739091</v>
+        <v>-1963.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2466,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13934.9265</v>
+        <v>13877.4636</v>
       </c>
     </row>
     <row r="6">
@@ -2481,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1462</v>
+        <v>1.1553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2511,17 +2781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>44.71</v>
+        <v>44.75</v>
       </c>
       <c r="O6" t="n">
-        <v>44710</v>
+        <v>44750</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2533,7 +2803,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>1700</v>
+        <v>1740</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2546,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>51246.60200000001</v>
+        <v>51699.675</v>
       </c>
     </row>
     <row r="7">
@@ -2561,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1462</v>
+        <v>1.1553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2591,17 +2861,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="O7" t="n">
-        <v>7080</v>
+        <v>7650</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2613,7 +2883,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>-1264.17</v>
+        <v>-694.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2626,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>8115.096</v>
+        <v>8838.045</v>
       </c>
     </row>
     <row r="8">
@@ -2641,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77441</v>
+        <v>0.7776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2671,17 +2941,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>4.883</v>
       </c>
       <c r="O8" t="n">
-        <v>49000</v>
+        <v>48830</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2693,7 +2963,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11731.8184</v>
+        <v>11561.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2706,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37946.09</v>
+        <v>37970.208</v>
       </c>
     </row>
     <row r="9">
@@ -2721,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.77441</v>
+        <v>0.7776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2751,17 +3021,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>537.6</v>
+        <v>541.9</v>
       </c>
       <c r="O9" t="n">
-        <v>40320</v>
+        <v>40642.5</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -2773,7 +3043,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-3903.3504</v>
+        <v>-3580.8504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2786,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>31224.2112</v>
+        <v>31603.608</v>
       </c>
     </row>
     <row r="10">
@@ -2831,17 +3101,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.005</v>
+        <v>6.89</v>
       </c>
       <c r="O10" t="n">
-        <v>7705.5</v>
+        <v>7579</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -2853,7 +3123,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1437.347947</v>
+        <v>-1563.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2866,7 +3136,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>7705.5</v>
+        <v>7579</v>
       </c>
     </row>
     <row r="11">
@@ -2911,17 +3181,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>191.86</v>
+        <v>202.98</v>
       </c>
       <c r="O11" t="n">
-        <v>5755.8</v>
+        <v>6089.4</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -2933,7 +3203,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-783.4</v>
+        <v>-449.8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2946,7 +3216,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5755.8</v>
+        <v>6089.4</v>
       </c>
     </row>
     <row r="12">
@@ -2991,17 +3261,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.15</v>
+        <v>9.31</v>
       </c>
       <c r="O12" t="n">
-        <v>1830</v>
+        <v>1862</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3013,7 +3283,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-398.5</v>
+        <v>-366.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3026,7 +3296,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1830</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="13">
@@ -3071,17 +3341,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>273.5</v>
+        <v>287.56</v>
       </c>
       <c r="O13" t="n">
-        <v>27350</v>
+        <v>28756</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -3093,7 +3363,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-5837.755</v>
+        <v>-4431.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3106,7 +3376,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>27350</v>
+        <v>28756</v>
       </c>
     </row>
     <row r="14">
@@ -3151,17 +3421,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>54.83</v>
+        <v>55.17</v>
       </c>
       <c r="O14" t="n">
-        <v>8772.799999999999</v>
+        <v>8827.200000000001</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3173,7 +3443,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-859.64</v>
+        <v>-805.24</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3186,7 +3456,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>8772.799999999999</v>
+        <v>8827.200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -3231,17 +3501,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>63.69</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>1072.85</v>
+        <v>1129.78</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3253,7 +3523,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>723.803421</v>
+        <v>780.733421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3266,7 +3536,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1072.85</v>
+        <v>1129.78</v>
       </c>
     </row>
     <row r="16">
@@ -3311,17 +3581,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.1059</v>
+        <v>26.2202</v>
       </c>
       <c r="O16" t="n">
-        <v>10050.77</v>
+        <v>10094.78</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3333,7 +3603,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>41.864112</v>
+        <v>85.874112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3346,7 +3616,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10050.77</v>
+        <v>10094.78</v>
       </c>
     </row>
     <row r="17">
@@ -3391,17 +3661,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>500</v>
       </c>
       <c r="N17" t="n">
-        <v>162.5</v>
+        <v>163.46</v>
       </c>
       <c r="O17" t="n">
-        <v>81250</v>
+        <v>81730</v>
       </c>
       <c r="P17" t="n">
         <v>174.0753942</v>
@@ -3413,7 +3683,7 @@
         <v>87037.6971</v>
       </c>
       <c r="S17" t="n">
-        <v>-5787.6971</v>
+        <v>-5307.6971</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3426,7 +3696,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>81250</v>
+        <v>81730</v>
       </c>
     </row>
     <row r="18">
@@ -3481,17 +3751,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>45.335</v>
+        <v>36.8954</v>
       </c>
       <c r="O18" t="n">
-        <v>9067</v>
+        <v>7379.08</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3503,7 +3773,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>4361.5975</v>
+        <v>2673.6775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3516,7 +3786,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>9067</v>
+        <v>7379.08</v>
       </c>
     </row>
     <row r="19">
@@ -3571,17 +3841,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>38.87</v>
+        <v>31.215</v>
       </c>
       <c r="O19" t="n">
-        <v>7774</v>
+        <v>6243</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3593,7 +3863,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>3746.9825</v>
+        <v>2215.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3606,7 +3876,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>7774</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="20">
@@ -3661,17 +3931,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>12.1559</v>
+        <v>9.508699999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-2431.18</v>
+        <v>-1901.74</v>
       </c>
       <c r="P20" t="n">
         <v>6.3929546</v>
@@ -3683,7 +3953,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S20" t="n">
-        <v>-1152.58908</v>
+        <v>-623.14908</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3696,7 +3966,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-2431.18</v>
+        <v>-1901.74</v>
       </c>
     </row>
     <row r="21">
@@ -3751,17 +4021,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>13.15</v>
+        <v>10.267</v>
       </c>
       <c r="O21" t="n">
-        <v>-2630</v>
+        <v>-2053.4</v>
       </c>
       <c r="P21" t="n">
         <v>7.3496796</v>
@@ -3773,7 +4043,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S21" t="n">
-        <v>-1160.06408</v>
+        <v>-583.46408</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3786,7 +4056,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-2630</v>
+        <v>-2053.4</v>
       </c>
     </row>
   </sheetData>
@@ -3833,17 +4103,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$236,838.48</t>
+          <t>$240,572.93</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$183,151.69</t>
+          <t>$180,353.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$419,990.17</t>
+          <t>$420,926.39</t>
         </is>
       </c>
     </row>
@@ -3855,17 +4125,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$361,887.20</t>
+          <t>$368,537.34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$163,268.24</t>
+          <t>$158,849.12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$525,155.45</t>
+          <t>$527,386.47</t>
         </is>
       </c>
     </row>
@@ -3883,17 +4153,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$598,725.69</t>
+          <t>$609,110.28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$346,419.93</t>
+          <t>$339,202.59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$945,145.62</t>
+          <t>$948,312.86</t>
         </is>
       </c>
     </row>
@@ -3941,11 +4211,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31 23:46:23</t>
+          <t>2026-04-01 23:46:45</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.251</v>
+        <v>1.259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,29 +585,29 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>370.75</v>
+        <v>383.15</v>
       </c>
       <c r="O2" t="n">
-        <v>22245</v>
+        <v>26820.5</v>
       </c>
       <c r="P2" t="n">
-        <v>400.28970675</v>
+        <v>397.727320071</v>
       </c>
       <c r="Q2" t="n">
-        <v>400.28970675</v>
+        <v>397.727320071</v>
       </c>
       <c r="R2" t="n">
-        <v>24017.382405</v>
+        <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>-1772.382405</v>
+        <v>-1020.412405</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>27828.495</v>
+        <v>33767.0095</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.251</v>
+        <v>1.259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>61.28</v>
+        <v>63.21</v>
       </c>
       <c r="O3" t="n">
-        <v>12256</v>
+        <v>12642</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-818.426667</v>
+        <v>-432.426667</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15332.256</v>
+        <v>15916.278</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14517</v>
+        <v>0.1454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>30.32</v>
       </c>
       <c r="O4" t="n">
-        <v>60000</v>
+        <v>60640</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-3412.49376</v>
+        <v>-2772.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8710.199999999999</v>
+        <v>8817.056</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1553</v>
+        <v>1.159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.004</v>
+        <v>4.0625</v>
       </c>
       <c r="O5" t="n">
-        <v>8008</v>
+        <v>8125</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1316.66</v>
+        <v>-1199.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9251.642400000001</v>
+        <v>9416.875</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1553</v>
+        <v>1.159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="O6" t="n">
-        <v>7650</v>
+        <v>7860</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>-694.17</v>
+        <v>-484.17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>8838.045</v>
+        <v>9109.74</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7776</v>
+        <v>0.77925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.883</v>
+        <v>4.99</v>
       </c>
       <c r="O7" t="n">
-        <v>39064</v>
+        <v>39920</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>1752.77315</v>
+        <v>2608.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30376.1664</v>
+        <v>31107.66</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7776</v>
+        <v>0.77925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>541.9</v>
+        <v>557.6</v>
       </c>
       <c r="O8" t="n">
-        <v>40642.5</v>
+        <v>41820</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-3591.598992</v>
+        <v>-2414.098992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31603.608</v>
+        <v>32588.235</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>6.89</v>
+        <v>7.155</v>
       </c>
       <c r="O9" t="n">
-        <v>6890</v>
+        <v>7155</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-1421.237657</v>
+        <v>-1156.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>6890</v>
+        <v>7155</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>202.98</v>
+        <v>210.08</v>
       </c>
       <c r="O10" t="n">
-        <v>6089.4</v>
+        <v>6302.4</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-453.7</v>
+        <v>-240.7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6089.4</v>
+        <v>6302.4</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.31</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-39.5</v>
+        <v>-34.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>931</v>
+        <v>936</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>55.17</v>
+        <v>57.73</v>
       </c>
       <c r="O12" t="n">
-        <v>8827.200000000001</v>
+        <v>9236.799999999999</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>-749.46</v>
+        <v>-339.86</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>8827.200000000001</v>
+        <v>9236.799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>26.2202</v>
+        <v>27.1477</v>
       </c>
       <c r="O13" t="n">
-        <v>10094.78</v>
+        <v>10451.86</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>79.877178</v>
+        <v>436.957178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10094.78</v>
+        <v>10451.86</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>82.81</v>
+        <v>82.16</v>
       </c>
       <c r="O14" t="n">
-        <v>3312.4</v>
+        <v>3286.4</v>
       </c>
       <c r="P14" t="n">
         <v>102.0775</v>
@@ -1567,7 +1567,7 @@
         <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-770.7</v>
+        <v>-796.7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3312.4</v>
+        <v>3286.4</v>
       </c>
     </row>
     <row r="15">
@@ -1625,29 +1625,29 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N15" t="n">
-        <v>163.46</v>
+        <v>168.14</v>
       </c>
       <c r="O15" t="n">
-        <v>65384</v>
+        <v>84070</v>
       </c>
       <c r="P15" t="n">
-        <v>174.135899437</v>
+        <v>172.83405384</v>
       </c>
       <c r="Q15" t="n">
-        <v>174.135899437</v>
+        <v>172.83405384</v>
       </c>
       <c r="R15" t="n">
-        <v>69654.359775</v>
+        <v>86417.02692</v>
       </c>
       <c r="S15" t="n">
-        <v>-4270.359775</v>
+        <v>-2347.02692</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>65384</v>
+        <v>84070</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>36.8954</v>
+        <v>34.2555</v>
       </c>
       <c r="O16" t="n">
-        <v>7379.08</v>
+        <v>6851.1</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2686.98</v>
+        <v>2159</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>7379.08</v>
+        <v>6851.1</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>31.215</v>
+        <v>29.245</v>
       </c>
       <c r="O17" t="n">
-        <v>6243</v>
+        <v>5849</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>2215.5025</v>
+        <v>1821.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>6243</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>12.4537</v>
+        <v>9.875</v>
       </c>
       <c r="O18" t="n">
-        <v>-1245.37</v>
+        <v>-987.5</v>
       </c>
       <c r="P18" t="n">
         <v>16.3422876</v>
@@ -1917,7 +1917,7 @@
         <v>-1634.22876</v>
       </c>
       <c r="S18" t="n">
-        <v>388.85876</v>
+        <v>646.72876</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-1245.37</v>
+        <v>-987.5</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>9.1783</v>
+        <v>8.975</v>
       </c>
       <c r="O19" t="n">
-        <v>-917.83</v>
+        <v>-897.5</v>
       </c>
       <c r="P19" t="n">
         <v>11.0194626</v>
@@ -2007,7 +2007,7 @@
         <v>-1101.94626</v>
       </c>
       <c r="S19" t="n">
-        <v>184.11626</v>
+        <v>204.44626</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-917.83</v>
+        <v>-897.5</v>
       </c>
     </row>
     <row r="20">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-1</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>-400</v>
+        <v>-355</v>
       </c>
       <c r="P20" t="n">
         <v>5.1936876</v>
@@ -2097,7 +2097,7 @@
         <v>-519.36876</v>
       </c>
       <c r="S20" t="n">
-        <v>119.36876</v>
+        <v>164.36876</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-400</v>
+        <v>-355</v>
       </c>
     </row>
     <row r="21">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>9.508699999999999</v>
+        <v>8.795</v>
       </c>
       <c r="O21" t="n">
-        <v>-1901.74</v>
+        <v>-1759</v>
       </c>
       <c r="P21" t="n">
         <v>6.3644671</v>
@@ -2187,7 +2187,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S21" t="n">
-        <v>-628.84658</v>
+        <v>-486.10658</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1901.74</v>
+        <v>-1759</v>
       </c>
     </row>
     <row r="22">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>10.267</v>
+        <v>9.484999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-2053.4</v>
+        <v>-1897</v>
       </c>
       <c r="P22" t="n">
         <v>7.3548796</v>
@@ -2277,7 +2277,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S22" t="n">
-        <v>-582.42408</v>
+        <v>-426.02408</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-2053.4</v>
+        <v>-1897</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.251</v>
+        <v>1.259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,29 +2461,29 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>370.75</v>
+        <v>383.15</v>
       </c>
       <c r="O2" t="n">
-        <v>29660</v>
+        <v>34483.5</v>
       </c>
       <c r="P2" t="n">
-        <v>402.9867686</v>
+        <v>400.699349867</v>
       </c>
       <c r="Q2" t="n">
-        <v>402.9867686</v>
+        <v>400.699349867</v>
       </c>
       <c r="R2" t="n">
-        <v>32238.941488</v>
+        <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>-2578.941488</v>
+        <v>-1579.441488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>37104.66</v>
+        <v>43414.7265</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.251</v>
+        <v>1.259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,17 +2541,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>61.28</v>
+        <v>63.21</v>
       </c>
       <c r="O3" t="n">
-        <v>18384</v>
+        <v>18963</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2563,7 +2563,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-1344.8595</v>
+        <v>-765.8595</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>22998.384</v>
+        <v>23874.417</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14517</v>
+        <v>0.1454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,17 +2621,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>30.32</v>
       </c>
       <c r="O4" t="n">
-        <v>60000</v>
+        <v>60640</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2643,7 +2643,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-3392.47719</v>
+        <v>-2752.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8710.199999999999</v>
+        <v>8817.056</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1553</v>
+        <v>1.159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.004</v>
+        <v>4.0625</v>
       </c>
       <c r="O5" t="n">
-        <v>12012</v>
+        <v>12187.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2723,7 +2723,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1963.239091</v>
+        <v>-1787.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13877.4636</v>
+        <v>14125.3125</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1553</v>
+        <v>1.159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,17 +2781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>44.75</v>
+        <v>46.6</v>
       </c>
       <c r="O6" t="n">
-        <v>44750</v>
+        <v>46600</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2803,7 +2803,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>1740</v>
+        <v>3590</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>51699.675</v>
+        <v>54009.4</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1553</v>
+        <v>1.159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,17 +2861,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="O7" t="n">
-        <v>7650</v>
+        <v>7860</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2883,7 +2883,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>-694.17</v>
+        <v>-484.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>8838.045</v>
+        <v>9109.74</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7776</v>
+        <v>0.77925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,17 +2941,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.883</v>
+        <v>4.99</v>
       </c>
       <c r="O8" t="n">
-        <v>48830</v>
+        <v>49900</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2963,7 +2963,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>11561.8184</v>
+        <v>12631.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37970.208</v>
+        <v>38884.575</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7776</v>
+        <v>0.77925</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,17 +3021,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>541.9</v>
+        <v>557.6</v>
       </c>
       <c r="O9" t="n">
-        <v>40642.5</v>
+        <v>41820</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -3043,7 +3043,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-3580.8504</v>
+        <v>-2403.3504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>31603.608</v>
+        <v>32588.235</v>
       </c>
     </row>
     <row r="10">
@@ -3101,17 +3101,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>6.89</v>
+        <v>7.155</v>
       </c>
       <c r="O10" t="n">
-        <v>7579</v>
+        <v>7870.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -3123,7 +3123,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1563.847947</v>
+        <v>-1272.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>7579</v>
+        <v>7870.5</v>
       </c>
     </row>
     <row r="11">
@@ -3181,17 +3181,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>202.98</v>
+        <v>210.08</v>
       </c>
       <c r="O11" t="n">
-        <v>6089.4</v>
+        <v>6302.4</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -3203,7 +3203,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-449.8</v>
+        <v>-236.8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6089.4</v>
+        <v>6302.4</v>
       </c>
     </row>
     <row r="12">
@@ -3261,17 +3261,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.31</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>1862</v>
+        <v>1872</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3283,7 +3283,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-366.5</v>
+        <v>-356.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1862</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="13">
@@ -3341,17 +3341,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>287.56</v>
+        <v>297.39</v>
       </c>
       <c r="O13" t="n">
-        <v>28756</v>
+        <v>29739</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -3363,7 +3363,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-4431.755</v>
+        <v>-3448.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>28756</v>
+        <v>29739</v>
       </c>
     </row>
     <row r="14">
@@ -3421,17 +3421,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>55.17</v>
+        <v>57.73</v>
       </c>
       <c r="O14" t="n">
-        <v>8827.200000000001</v>
+        <v>9236.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3443,7 +3443,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-805.24</v>
+        <v>-395.64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>8827.200000000001</v>
+        <v>9236.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -3501,17 +3501,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>67.06999999999999</v>
+        <v>67.91</v>
       </c>
       <c r="O15" t="n">
-        <v>1129.78</v>
+        <v>1143.93</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3523,7 +3523,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>780.733421</v>
+        <v>794.883421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1129.78</v>
+        <v>1143.93</v>
       </c>
     </row>
     <row r="16">
@@ -3581,17 +3581,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.2202</v>
+        <v>27.1477</v>
       </c>
       <c r="O16" t="n">
-        <v>10094.78</v>
+        <v>10451.86</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3603,7 +3603,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>85.874112</v>
+        <v>442.954112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10094.78</v>
+        <v>10451.86</v>
       </c>
     </row>
     <row r="17">
@@ -3661,29 +3661,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N17" t="n">
-        <v>163.46</v>
+        <v>168.14</v>
       </c>
       <c r="O17" t="n">
-        <v>81730</v>
+        <v>100884</v>
       </c>
       <c r="P17" t="n">
-        <v>174.0753942</v>
+        <v>172.9987895</v>
       </c>
       <c r="Q17" t="n">
-        <v>174.0753942</v>
+        <v>172.9987895</v>
       </c>
       <c r="R17" t="n">
-        <v>87037.6971</v>
+        <v>103799.2737</v>
       </c>
       <c r="S17" t="n">
-        <v>-5307.6971</v>
+        <v>-2915.2737</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>81730</v>
+        <v>100884</v>
       </c>
     </row>
     <row r="18">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>36.8954</v>
+        <v>34.2555</v>
       </c>
       <c r="O18" t="n">
-        <v>7379.08</v>
+        <v>6851.1</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3773,7 +3773,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>2673.6775</v>
+        <v>2145.6975</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>7379.08</v>
+        <v>6851.1</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>31.215</v>
+        <v>29.245</v>
       </c>
       <c r="O19" t="n">
-        <v>6243</v>
+        <v>5849</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3863,7 +3863,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>2215.9825</v>
+        <v>1821.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>6243</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="20">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>9.508699999999999</v>
+        <v>8.795</v>
       </c>
       <c r="O20" t="n">
-        <v>-1901.74</v>
+        <v>-1759</v>
       </c>
       <c r="P20" t="n">
         <v>6.3929546</v>
@@ -3953,7 +3953,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S20" t="n">
-        <v>-623.14908</v>
+        <v>-480.40908</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1901.74</v>
+        <v>-1759</v>
       </c>
     </row>
     <row r="21">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>10.267</v>
+        <v>9.484999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-2053.4</v>
+        <v>-1897</v>
       </c>
       <c r="P21" t="n">
         <v>7.3496796</v>
@@ -4043,7 +4043,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S21" t="n">
-        <v>-583.46408</v>
+        <v>-427.06408</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-2053.4</v>
+        <v>-1897</v>
       </c>
     </row>
   </sheetData>
@@ -4103,17 +4103,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$240,572.93</t>
+          <t>$268,965.41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$180,353.46</t>
+          <t>$159,071.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$420,926.39</t>
+          <t>$428,036.62</t>
         </is>
       </c>
     </row>
@@ -4125,17 +4125,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$368,537.34</t>
+          <t>$401,368.05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$158,849.12</t>
+          <t>$137,625.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$527,386.47</t>
+          <t>$538,993.71</t>
         </is>
       </c>
     </row>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$609,110.28</t>
+          <t>$670,333.47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$339,202.59</t>
+          <t>$296,696.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$948,312.86</t>
+          <t>$967,030.34</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01 23:46:45</t>
+          <t>2026-04-02 23:46:18</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.259</v>
+        <v>1.2518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>383.15</v>
+        <v>381.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26820.5</v>
+        <v>26694.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>-1020.412405</v>
+        <v>-1146.412405</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>33767.0095</v>
+        <v>33416.1751</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.259</v>
+        <v>1.2518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>63.21</v>
+        <v>62.4</v>
       </c>
       <c r="O3" t="n">
-        <v>12642</v>
+        <v>12480</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-432.426667</v>
+        <v>-594.426667</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15916.278</v>
+        <v>15622.464</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1454</v>
+        <v>0.14514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.32</v>
+        <v>30.08</v>
       </c>
       <c r="O4" t="n">
-        <v>60640</v>
+        <v>60160</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-2772.49376</v>
+        <v>-3252.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8817.056</v>
+        <v>8731.6224</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.159</v>
+        <v>1.1539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.0625</v>
+        <v>4.014</v>
       </c>
       <c r="O5" t="n">
-        <v>8125</v>
+        <v>8028</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1199.66</v>
+        <v>-1296.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9416.875</v>
+        <v>9263.509199999999</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.159</v>
+        <v>1.1539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="O6" t="n">
-        <v>7860</v>
+        <v>7500</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>-484.17</v>
+        <v>-844.17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9109.74</v>
+        <v>8654.25</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.77925</v>
+        <v>0.77781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.99</v>
+        <v>4.945</v>
       </c>
       <c r="O7" t="n">
-        <v>39920</v>
+        <v>39560</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2608.77315</v>
+        <v>2248.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31107.66</v>
+        <v>30770.1636</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77925</v>
+        <v>0.77781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>557.6</v>
+        <v>545</v>
       </c>
       <c r="O8" t="n">
-        <v>41820</v>
+        <v>40875</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-2414.098992</v>
+        <v>-3359.098992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>32588.235</v>
+        <v>31792.98375</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.155</v>
+        <v>6.95</v>
       </c>
       <c r="O9" t="n">
-        <v>7155</v>
+        <v>6950</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-1156.237657</v>
+        <v>-1361.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7155</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>210.08</v>
+        <v>208.54</v>
       </c>
       <c r="O10" t="n">
-        <v>6302.4</v>
+        <v>6256.2</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-240.7</v>
+        <v>-286.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6302.4</v>
+        <v>6256.2</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.359999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-34.5</v>
+        <v>-49.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>936</v>
+        <v>921</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>57.73</v>
+        <v>57.12</v>
       </c>
       <c r="O12" t="n">
-        <v>9236.799999999999</v>
+        <v>9139.200000000001</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>-339.86</v>
+        <v>-437.46</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9236.799999999999</v>
+        <v>9139.200000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>27.1477</v>
+        <v>26.7962</v>
       </c>
       <c r="O13" t="n">
-        <v>10451.86</v>
+        <v>10316.54</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>436.957178</v>
+        <v>301.637178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10451.86</v>
+        <v>10316.54</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>82.16</v>
+        <v>82.28</v>
       </c>
       <c r="O14" t="n">
-        <v>3286.4</v>
+        <v>3291.2</v>
       </c>
       <c r="P14" t="n">
         <v>102.0775</v>
@@ -1567,7 +1567,7 @@
         <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-796.7</v>
+        <v>-791.9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3286.4</v>
+        <v>3291.2</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>500</v>
       </c>
       <c r="N15" t="n">
-        <v>168.14</v>
+        <v>167.08</v>
       </c>
       <c r="O15" t="n">
-        <v>84070</v>
+        <v>83540</v>
       </c>
       <c r="P15" t="n">
         <v>172.83405384</v>
@@ -1647,7 +1647,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S15" t="n">
-        <v>-2347.02692</v>
+        <v>-2877.02692</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>84070</v>
+        <v>83540</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>34.2555</v>
+        <v>33.6104</v>
       </c>
       <c r="O16" t="n">
-        <v>6851.1</v>
+        <v>6722.08</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2159</v>
+        <v>2029.98</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>6851.1</v>
+        <v>6722.08</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>29.245</v>
+        <v>28.595</v>
       </c>
       <c r="O17" t="n">
-        <v>5849</v>
+        <v>5719</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>1821.5025</v>
+        <v>1691.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>5849</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>9.875</v>
+        <v>10.125</v>
       </c>
       <c r="O18" t="n">
-        <v>-987.5</v>
+        <v>-1012.5</v>
       </c>
       <c r="P18" t="n">
         <v>16.3422876</v>
@@ -1917,7 +1917,7 @@
         <v>-1634.22876</v>
       </c>
       <c r="S18" t="n">
-        <v>646.72876</v>
+        <v>621.72876</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-987.5</v>
+        <v>-1012.5</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>8.975</v>
+        <v>7.9836</v>
       </c>
       <c r="O19" t="n">
-        <v>-897.5</v>
+        <v>-798.36</v>
       </c>
       <c r="P19" t="n">
         <v>11.0194626</v>
@@ -2007,7 +2007,7 @@
         <v>-1101.94626</v>
       </c>
       <c r="S19" t="n">
-        <v>204.44626</v>
+        <v>303.58626</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-897.5</v>
+        <v>-798.36</v>
       </c>
     </row>
     <row r="20">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>-355</v>
+        <v>-270</v>
       </c>
       <c r="P20" t="n">
         <v>5.1936876</v>
@@ -2097,7 +2097,7 @@
         <v>-519.36876</v>
       </c>
       <c r="S20" t="n">
-        <v>164.36876</v>
+        <v>249.36876</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-355</v>
+        <v>-270</v>
       </c>
     </row>
     <row r="21">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>8.795</v>
+        <v>8.650700000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-1759</v>
+        <v>-1730.14</v>
       </c>
       <c r="P21" t="n">
         <v>6.3644671</v>
@@ -2187,7 +2187,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S21" t="n">
-        <v>-486.10658</v>
+        <v>-457.24658</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1759</v>
+        <v>-1730.14</v>
       </c>
     </row>
     <row r="22">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>9.484999999999999</v>
+        <v>9.205</v>
       </c>
       <c r="O22" t="n">
-        <v>-1897</v>
+        <v>-1841</v>
       </c>
       <c r="P22" t="n">
         <v>7.3548796</v>
@@ -2277,7 +2277,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S22" t="n">
-        <v>-426.02408</v>
+        <v>-370.02408</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1897</v>
+        <v>-1841</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.259</v>
+        <v>1.2518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,17 +2461,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>383.15</v>
+        <v>381.35</v>
       </c>
       <c r="O2" t="n">
-        <v>34483.5</v>
+        <v>34321.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2483,7 +2483,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>-1579.441488</v>
+        <v>-1741.441488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>43414.7265</v>
+        <v>42963.6537</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.259</v>
+        <v>1.2518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,17 +2541,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>63.21</v>
+        <v>62.4</v>
       </c>
       <c r="O3" t="n">
-        <v>18963</v>
+        <v>18720</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2563,7 +2563,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-765.8595</v>
+        <v>-1008.8595</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23874.417</v>
+        <v>23433.696</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1454</v>
+        <v>0.14514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,17 +2621,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.32</v>
+        <v>30.08</v>
       </c>
       <c r="O4" t="n">
-        <v>60640</v>
+        <v>60160</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2643,7 +2643,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-2752.47719</v>
+        <v>-3232.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8817.056</v>
+        <v>8731.6224</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.159</v>
+        <v>1.1539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.0625</v>
+        <v>4.014</v>
       </c>
       <c r="O5" t="n">
-        <v>12187.5</v>
+        <v>12042</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2723,7 +2723,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1787.739091</v>
+        <v>-1933.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14125.3125</v>
+        <v>13895.2638</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.159</v>
+        <v>1.1539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,17 +2781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.6</v>
+        <v>46.12</v>
       </c>
       <c r="O6" t="n">
-        <v>46600</v>
+        <v>46120</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2803,7 +2803,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>3590</v>
+        <v>3110</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>54009.4</v>
+        <v>53217.86799999999</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.159</v>
+        <v>1.1539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,17 +2861,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="O7" t="n">
-        <v>7860</v>
+        <v>7500</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2883,7 +2883,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>-484.17</v>
+        <v>-844.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>9109.74</v>
+        <v>8654.25</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77925</v>
+        <v>0.77781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,17 +2941,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.99</v>
+        <v>4.945</v>
       </c>
       <c r="O8" t="n">
-        <v>49900</v>
+        <v>49450</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2963,7 +2963,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12631.8184</v>
+        <v>12181.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38884.575</v>
+        <v>38462.7045</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.77925</v>
+        <v>0.77781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,17 +3021,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>557.6</v>
+        <v>545</v>
       </c>
       <c r="O9" t="n">
-        <v>41820</v>
+        <v>40875</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -3043,7 +3043,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-2403.3504</v>
+        <v>-3348.3504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>32588.235</v>
+        <v>31792.98375</v>
       </c>
     </row>
     <row r="10">
@@ -3101,17 +3101,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.155</v>
+        <v>6.95</v>
       </c>
       <c r="O10" t="n">
-        <v>7870.5</v>
+        <v>7645</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -3123,7 +3123,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1272.347947</v>
+        <v>-1497.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>7870.5</v>
+        <v>7645</v>
       </c>
     </row>
     <row r="11">
@@ -3181,17 +3181,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>210.08</v>
+        <v>208.54</v>
       </c>
       <c r="O11" t="n">
-        <v>6302.4</v>
+        <v>6256.2</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -3203,7 +3203,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-236.8</v>
+        <v>-283</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6302.4</v>
+        <v>6256.2</v>
       </c>
     </row>
     <row r="12">
@@ -3261,17 +3261,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1872</v>
+        <v>1842</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3283,7 +3283,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-356.5</v>
+        <v>-386.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1872</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="13">
@@ -3341,17 +3341,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>297.39</v>
+        <v>295.77</v>
       </c>
       <c r="O13" t="n">
-        <v>29739</v>
+        <v>29577</v>
       </c>
       <c r="P13" t="n">
         <v>331.87755</v>
@@ -3363,7 +3363,7 @@
         <v>33187.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-3448.755</v>
+        <v>-3610.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>29739</v>
+        <v>29577</v>
       </c>
     </row>
     <row r="14">
@@ -3421,17 +3421,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>57.73</v>
+        <v>57.12</v>
       </c>
       <c r="O14" t="n">
-        <v>9236.799999999999</v>
+        <v>9139.200000000001</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3443,7 +3443,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-395.64</v>
+        <v>-493.24</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9236.799999999999</v>
+        <v>9139.200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -3501,17 +3501,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>67.91</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>1143.93</v>
+        <v>1141.07</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3523,7 +3523,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>794.883421</v>
+        <v>792.023421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1143.93</v>
+        <v>1141.07</v>
       </c>
     </row>
     <row r="16">
@@ -3581,17 +3581,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.1477</v>
+        <v>26.7962</v>
       </c>
       <c r="O16" t="n">
-        <v>10451.86</v>
+        <v>10316.54</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3603,7 +3603,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>442.954112</v>
+        <v>307.634112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10451.86</v>
+        <v>10316.54</v>
       </c>
     </row>
     <row r="17">
@@ -3661,17 +3661,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>600</v>
       </c>
       <c r="N17" t="n">
-        <v>168.14</v>
+        <v>167.08</v>
       </c>
       <c r="O17" t="n">
-        <v>100884</v>
+        <v>100248</v>
       </c>
       <c r="P17" t="n">
         <v>172.9987895</v>
@@ -3683,7 +3683,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S17" t="n">
-        <v>-2915.2737</v>
+        <v>-3551.2737</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>100884</v>
+        <v>100248</v>
       </c>
     </row>
     <row r="18">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>34.2555</v>
+        <v>33.6104</v>
       </c>
       <c r="O18" t="n">
-        <v>6851.1</v>
+        <v>6722.08</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3773,7 +3773,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>2145.6975</v>
+        <v>2016.6775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>6851.1</v>
+        <v>6722.08</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>29.245</v>
+        <v>28.595</v>
       </c>
       <c r="O19" t="n">
-        <v>5849</v>
+        <v>5719</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3863,7 +3863,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>1821.9825</v>
+        <v>1691.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>5849</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="20">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>8.795</v>
+        <v>8.650700000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-1759</v>
+        <v>-1730.14</v>
       </c>
       <c r="P20" t="n">
         <v>6.3929546</v>
@@ -3953,7 +3953,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S20" t="n">
-        <v>-480.40908</v>
+        <v>-451.54908</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1759</v>
+        <v>-1730.14</v>
       </c>
     </row>
     <row r="21">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>9.484999999999999</v>
+        <v>9.205</v>
       </c>
       <c r="O21" t="n">
-        <v>-1897</v>
+        <v>-1841</v>
       </c>
       <c r="P21" t="n">
         <v>7.3496796</v>
@@ -4043,7 +4043,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S21" t="n">
-        <v>-427.06408</v>
+        <v>-371.06408</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1897</v>
+        <v>-1841</v>
       </c>
     </row>
   </sheetData>
@@ -4103,17 +4103,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$268,965.41</t>
+          <t>$265,454.39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$159,071.21</t>
+          <t>$158,834.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$428,036.62</t>
+          <t>$424,288.39</t>
         </is>
       </c>
     </row>
@@ -4125,17 +4125,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$401,368.05</t>
+          <t>$396,186.99</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$137,625.66</t>
+          <t>$137,339.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$538,993.71</t>
+          <t>$533,526.01</t>
         </is>
       </c>
     </row>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$670,333.47</t>
+          <t>$661,641.38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$296,696.87</t>
+          <t>$296,173.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$967,030.34</t>
+          <t>$957,814.40</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02 23:46:18</t>
+          <t>2026-04-03 23:45:47</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2518</v>
+        <v>1.2489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>33416.1751</v>
+        <v>33338.76104999999</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2518</v>
+        <v>1.2489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15622.464</v>
+        <v>15586.272</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14514</v>
+        <v>0.14521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8731.6224</v>
+        <v>8735.8336</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1539</v>
+        <v>1.1517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9263.509199999999</v>
+        <v>9245.847599999999</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1539</v>
+        <v>1.1517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>8654.25</v>
+        <v>8637.75</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.77781</v>
+        <v>0.777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30770.1636</v>
+        <v>30738.12</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77781</v>
+        <v>0.777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31792.98375</v>
+        <v>31759.875</v>
       </c>
     </row>
     <row r="9">
@@ -1145,7 +1145,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1225,7 +1225,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1305,7 +1305,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1385,7 +1385,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1465,7 +1465,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1545,7 +1545,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1625,7 +1625,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2518</v>
+        <v>1.2489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>42963.6537</v>
+        <v>42864.12134999999</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2518</v>
+        <v>1.2489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23433.696</v>
+        <v>23379.408</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14514</v>
+        <v>0.14521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8731.6224</v>
+        <v>8735.8336</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1539</v>
+        <v>1.1517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13895.2638</v>
+        <v>13868.7714</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1539</v>
+        <v>1.1517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>53217.86799999999</v>
+        <v>53116.40399999999</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1539</v>
+        <v>1.1517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>8654.25</v>
+        <v>8637.75</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77781</v>
+        <v>0.777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38462.7045</v>
+        <v>38422.65</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.77781</v>
+        <v>0.777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>31792.98375</v>
+        <v>31759.875</v>
       </c>
     </row>
     <row r="10">
@@ -3101,7 +3101,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -3181,7 +3181,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -3261,7 +3261,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -3341,7 +3341,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -3421,7 +3421,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -3501,7 +3501,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -3581,7 +3581,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -3661,7 +3661,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -4103,17 +4103,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$265,454.39</t>
+          <t>$265,245.68</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$158,834.00</t>
+          <t>$158,735.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$424,288.39</t>
+          <t>$423,980.78</t>
         </is>
       </c>
     </row>
@@ -4125,17 +4125,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$396,186.99</t>
+          <t>$395,819.76</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$137,339.02</t>
+          <t>$137,207.71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$533,526.01</t>
+          <t>$533,027.47</t>
         </is>
       </c>
     </row>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$661,641.38</t>
+          <t>$661,065.44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$296,173.02</t>
+          <t>$295,942.81</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$957,814.40</t>
+          <t>$957,008.25</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03 23:45:47</t>
+          <t>2026-04-04 23:44:27</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -4211,7 +4211,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:44:27</t>
+          <t>2026-04-05 23:46:21</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -4211,7 +4211,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-05 23:46:21</t>
+          <t>2026-04-06 23:46:54</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2489</v>
+        <v>1.253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>33338.76104999999</v>
+        <v>33448.2085</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2489</v>
+        <v>1.253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15586.272</v>
+        <v>15637.44</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14521</v>
+        <v>0.14545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8735.8336</v>
+        <v>8750.271999999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1517</v>
+        <v>1.1542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9245.847599999999</v>
+        <v>9265.917599999999</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1517</v>
+        <v>1.1542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>8637.75</v>
+        <v>8656.5</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.777</v>
+        <v>0.77833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.945</v>
+        <v>4.987</v>
       </c>
       <c r="O7" t="n">
-        <v>39560</v>
+        <v>39896</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2248.77315</v>
+        <v>2584.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30738.12</v>
+        <v>31052.25368</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.777</v>
+        <v>0.77833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>545</v>
+        <v>554.4</v>
       </c>
       <c r="O8" t="n">
-        <v>40875</v>
+        <v>41580</v>
       </c>
       <c r="P8" t="n">
         <v>589.78798656</v>
@@ -1087,7 +1087,7 @@
         <v>44234.098992</v>
       </c>
       <c r="S8" t="n">
-        <v>-3359.098992</v>
+        <v>-2654.098992</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>31759.875</v>
+        <v>32362.9614</v>
       </c>
     </row>
     <row r="9">
@@ -1145,7 +1145,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>208.54</v>
+        <v>208.5</v>
       </c>
       <c r="O10" t="n">
-        <v>6256.2</v>
+        <v>6255</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-286.9</v>
+        <v>-288.1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6256.2</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.210000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="O11" t="n">
-        <v>921</v>
+        <v>958</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-49.5</v>
+        <v>-12.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>921</v>
+        <v>958</v>
       </c>
     </row>
     <row r="12">
@@ -1385,7 +1385,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1465,7 +1465,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>82.28</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>3291.2</v>
+        <v>3291.6</v>
       </c>
       <c r="P14" t="n">
         <v>102.0775</v>
@@ -1567,7 +1567,7 @@
         <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-791.9</v>
+        <v>-791.5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3291.2</v>
+        <v>3291.6</v>
       </c>
     </row>
     <row r="15">
@@ -1625,7 +1625,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>33.6104</v>
+        <v>32.1946</v>
       </c>
       <c r="O16" t="n">
-        <v>6722.08</v>
+        <v>6438.92</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2029.98</v>
+        <v>1746.82</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>6722.08</v>
+        <v>6438.92</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>28.595</v>
+        <v>27.24</v>
       </c>
       <c r="O17" t="n">
-        <v>5719</v>
+        <v>5448</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>1691.5025</v>
+        <v>1420.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>5719</v>
+        <v>5448</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>10.125</v>
+        <v>9.4139</v>
       </c>
       <c r="O18" t="n">
-        <v>-1012.5</v>
+        <v>-941.39</v>
       </c>
       <c r="P18" t="n">
         <v>16.3422876</v>
@@ -1917,7 +1917,7 @@
         <v>-1634.22876</v>
       </c>
       <c r="S18" t="n">
-        <v>621.72876</v>
+        <v>692.83876</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-1012.5</v>
+        <v>-941.39</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>7.9836</v>
+        <v>7.475</v>
       </c>
       <c r="O19" t="n">
-        <v>-798.36</v>
+        <v>-747.5</v>
       </c>
       <c r="P19" t="n">
         <v>11.0194626</v>
@@ -2007,7 +2007,7 @@
         <v>-1101.94626</v>
       </c>
       <c r="S19" t="n">
-        <v>303.58626</v>
+        <v>354.44626</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-798.36</v>
+        <v>-747.5</v>
       </c>
     </row>
     <row r="20">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="O20" t="n">
-        <v>-270</v>
+        <v>-236</v>
       </c>
       <c r="P20" t="n">
         <v>5.1936876</v>
@@ -2097,7 +2097,7 @@
         <v>-519.36876</v>
       </c>
       <c r="S20" t="n">
-        <v>249.36876</v>
+        <v>283.36876</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-270</v>
+        <v>-236</v>
       </c>
     </row>
     <row r="21">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>8.650700000000001</v>
+        <v>8.1647</v>
       </c>
       <c r="O21" t="n">
-        <v>-1730.14</v>
+        <v>-1632.94</v>
       </c>
       <c r="P21" t="n">
         <v>6.3644671</v>
@@ -2187,7 +2187,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S21" t="n">
-        <v>-457.24658</v>
+        <v>-360.04658</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1730.14</v>
+        <v>-1632.94</v>
       </c>
     </row>
     <row r="22">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>9.205</v>
+        <v>8.734999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1841</v>
+        <v>-1747</v>
       </c>
       <c r="P22" t="n">
         <v>7.3548796</v>
@@ -2277,7 +2277,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S22" t="n">
-        <v>-370.02408</v>
+        <v>-276.02408</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1841</v>
+        <v>-1747</v>
       </c>
     </row>
   </sheetData>
@@ -2304,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2489</v>
+        <v>1.253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>42864.12134999999</v>
+        <v>43004.83949999999</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2489</v>
+        <v>1.253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23379.408</v>
+        <v>23456.16</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14521</v>
+        <v>0.14545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8735.8336</v>
+        <v>8750.271999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1517</v>
+        <v>1.1542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13868.7714</v>
+        <v>13898.8764</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1517</v>
+        <v>1.1542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>53116.40399999999</v>
+        <v>53231.704</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1517</v>
+        <v>1.1542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>8637.75</v>
+        <v>8656.5</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.777</v>
+        <v>0.77833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,17 +2941,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.945</v>
+        <v>4.987</v>
       </c>
       <c r="O8" t="n">
-        <v>49450</v>
+        <v>49870</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2963,7 +2963,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12181.8184</v>
+        <v>12601.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38422.65</v>
+        <v>38815.3171</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.777</v>
+        <v>0.77833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,17 +3021,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>545</v>
+        <v>554.4</v>
       </c>
       <c r="O9" t="n">
-        <v>40875</v>
+        <v>41580</v>
       </c>
       <c r="P9" t="n">
         <v>589.644672</v>
@@ -3043,7 +3043,7 @@
         <v>44223.3504</v>
       </c>
       <c r="S9" t="n">
-        <v>-3348.3504</v>
+        <v>-2643.3504</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>31759.875</v>
+        <v>32362.9614</v>
       </c>
     </row>
     <row r="10">
@@ -3101,7 +3101,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -3181,17 +3181,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>208.54</v>
+        <v>208.5</v>
       </c>
       <c r="O11" t="n">
-        <v>6256.2</v>
+        <v>6255</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -3203,7 +3203,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-283</v>
+        <v>-284.2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6256.2</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="12">
@@ -3261,17 +3261,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.210000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="O12" t="n">
-        <v>1842</v>
+        <v>1916</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3283,7 +3283,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-386.5</v>
+        <v>-312.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1842</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="13">
@@ -3341,29 +3341,29 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>295.77</v>
+        <v>299.99</v>
       </c>
       <c r="O13" t="n">
-        <v>29577</v>
+        <v>59998</v>
       </c>
       <c r="P13" t="n">
-        <v>331.87755</v>
+        <v>314.748775</v>
       </c>
       <c r="Q13" t="n">
-        <v>331.87755</v>
+        <v>314.748775</v>
       </c>
       <c r="R13" t="n">
-        <v>33187.755</v>
+        <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-3610.755</v>
+        <v>-2951.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>29577</v>
+        <v>59998</v>
       </c>
     </row>
     <row r="14">
@@ -3421,7 +3421,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -3501,17 +3501,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>67.73999999999999</v>
+        <v>68.62</v>
       </c>
       <c r="O15" t="n">
-        <v>1141.07</v>
+        <v>1155.89</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3523,7 +3523,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>792.023421</v>
+        <v>806.843421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1141.07</v>
+        <v>1155.89</v>
       </c>
     </row>
     <row r="16">
@@ -3581,7 +3581,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -3661,7 +3661,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>33.6104</v>
+        <v>32.1946</v>
       </c>
       <c r="O18" t="n">
-        <v>6722.08</v>
+        <v>6438.92</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3773,7 +3773,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>2016.6775</v>
+        <v>1733.5175</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>6722.08</v>
+        <v>6438.92</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>28.595</v>
+        <v>27.24</v>
       </c>
       <c r="O19" t="n">
-        <v>5719</v>
+        <v>5448</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3863,7 +3863,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>1691.9825</v>
+        <v>1420.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>5719</v>
+        <v>5448</v>
       </c>
     </row>
     <row r="20">
@@ -3900,60 +3900,60 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>QQQ   261218P00425000</t>
+          <t>GOOGL 260522C00330000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 425 P</t>
+          <t>GOOGL 22MAY26 330 C</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>425</v>
+        <v>330</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>8.650700000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>-1730.14</v>
+        <v>-960</v>
       </c>
       <c r="P20" t="n">
-        <v>6.3929546</v>
+        <v>4.9928846</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.3929546</v>
+        <v>4.9928846</v>
       </c>
       <c r="R20" t="n">
-        <v>-1278.59092</v>
+        <v>-998.57692</v>
       </c>
       <c r="S20" t="n">
-        <v>-451.54908</v>
+        <v>38.57692</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1730.14</v>
+        <v>-960</v>
       </c>
     </row>
     <row r="21">
@@ -3995,19 +3995,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SPY   261218P00505000</t>
+          <t>QQQ   261218P00425000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 505 P</t>
+          <t>QQQ 18DEC26 425 P</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>505</v>
+        <v>425</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -4021,42 +4021,132 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>9.205</v>
+        <v>8.1647</v>
       </c>
       <c r="O21" t="n">
-        <v>-1841</v>
+        <v>-1632.94</v>
       </c>
       <c r="P21" t="n">
+        <v>6.3929546</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.3929546</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-1278.59092</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-354.34908</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>-1632.94</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U6565621</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SPY   261218P00505000</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SPY 18DEC26 505 P</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" t="n">
+        <v>505</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.734999999999999</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1747</v>
+      </c>
+      <c r="P22" t="n">
         <v>7.3496796</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>7.3496796</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>-1469.93592</v>
       </c>
-      <c r="S21" t="n">
-        <v>-371.06408</v>
-      </c>
-      <c r="T21" t="inlineStr">
+      <c r="S22" t="n">
+        <v>-277.06408</v>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="V21" t="n">
-        <v>-1841</v>
+      <c r="V22" t="n">
+        <v>-1747</v>
       </c>
     </row>
   </sheetData>
@@ -4103,17 +4193,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$265,245.68</t>
+          <t>$266,205.98</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$158,735.10</t>
+          <t>$158,993.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$423,980.78</t>
+          <t>$425,199.46</t>
         </is>
       </c>
     </row>
@@ -4125,17 +4215,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$395,819.76</t>
+          <t>$426,397.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$137,207.71</t>
+          <t>$108,695.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$533,027.47</t>
+          <t>$535,092.33</t>
         </is>
       </c>
     </row>
@@ -4153,17 +4243,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$661,065.44</t>
+          <t>$692,603.22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$295,942.81</t>
+          <t>$267,688.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$957,008.25</t>
+          <t>$960,291.79</t>
         </is>
       </c>
     </row>
@@ -4211,14 +4301,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-06 23:46:54</t>
+          <t>2026-04-07 23:47:34</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.253</v>
+        <v>1.2535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>381.35</v>
+        <v>379.5</v>
       </c>
       <c r="O2" t="n">
-        <v>26694.5</v>
+        <v>26565</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>-1146.412405</v>
+        <v>-1275.912405</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>33448.2085</v>
+        <v>33299.2275</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.253</v>
+        <v>1.2535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
       <c r="O3" t="n">
-        <v>12480</v>
+        <v>12500</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-594.426667</v>
+        <v>-574.426667</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15637.44</v>
+        <v>15668.75</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14545</v>
+        <v>0.14586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8750.271999999999</v>
+        <v>8774.937599999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1542</v>
+        <v>1.1597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.014</v>
+        <v>3.9675</v>
       </c>
       <c r="O5" t="n">
-        <v>8028</v>
+        <v>7935</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1296.66</v>
+        <v>-1389.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9265.917599999999</v>
+        <v>9202.219499999999</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1542</v>
+        <v>1.1597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="O6" t="n">
-        <v>7500</v>
+        <v>7920</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>-844.17</v>
+        <v>-424.17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>8656.5</v>
+        <v>9184.824000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.77833</v>
+        <v>0.77998</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.987</v>
+        <v>4.961</v>
       </c>
       <c r="O7" t="n">
-        <v>39896</v>
+        <v>39688</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2584.77315</v>
+        <v>2376.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31052.25368</v>
+        <v>30955.84624</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77833</v>
+        <v>0.77998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,29 +1065,29 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>554.4</v>
+        <v>552.15</v>
       </c>
       <c r="O8" t="n">
-        <v>41580</v>
+        <v>55215</v>
       </c>
       <c r="P8" t="n">
-        <v>589.78798656</v>
+        <v>579.71400048</v>
       </c>
       <c r="Q8" t="n">
-        <v>589.78798656</v>
+        <v>579.71400048</v>
       </c>
       <c r="R8" t="n">
-        <v>44234.098992</v>
+        <v>57971.400048</v>
       </c>
       <c r="S8" t="n">
-        <v>-2654.098992</v>
+        <v>-2756.400048</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>32362.9614</v>
+        <v>43066.5957</v>
       </c>
     </row>
     <row r="9">
@@ -1145,7 +1145,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>208.5</v>
+        <v>209.62</v>
       </c>
       <c r="O10" t="n">
-        <v>6255</v>
+        <v>6288.6</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-288.1</v>
+        <v>-254.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6255</v>
+        <v>6288.6</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.58</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-12.5</v>
+        <v>-23.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>958</v>
+        <v>947</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>57.12</v>
+        <v>56.58</v>
       </c>
       <c r="O12" t="n">
-        <v>9139.200000000001</v>
+        <v>9052.799999999999</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>-437.46</v>
+        <v>-523.86</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9139.200000000001</v>
+        <v>9052.799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>26.7962</v>
+        <v>26.1493</v>
       </c>
       <c r="O13" t="n">
-        <v>10316.54</v>
+        <v>10067.48</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>301.637178</v>
+        <v>52.577178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10316.54</v>
+        <v>10067.48</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>82.29000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="O14" t="n">
-        <v>3291.6</v>
+        <v>3254.4</v>
       </c>
       <c r="P14" t="n">
         <v>102.0775</v>
@@ -1567,7 +1567,7 @@
         <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-791.5</v>
+        <v>-828.7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3291.6</v>
+        <v>3254.4</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>500</v>
       </c>
       <c r="N15" t="n">
-        <v>167.08</v>
+        <v>166.48</v>
       </c>
       <c r="O15" t="n">
-        <v>83540</v>
+        <v>83240</v>
       </c>
       <c r="P15" t="n">
         <v>172.83405384</v>
@@ -1647,7 +1647,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S15" t="n">
-        <v>-2877.02692</v>
+        <v>-3177.02692</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>83540</v>
+        <v>83240</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>32.1946</v>
+        <v>32.5724</v>
       </c>
       <c r="O16" t="n">
-        <v>6438.92</v>
+        <v>6514.48</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1746.82</v>
+        <v>1822.38</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>6438.92</v>
+        <v>6514.48</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>27.24</v>
+        <v>27.64</v>
       </c>
       <c r="O17" t="n">
-        <v>5448</v>
+        <v>5528</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>1420.5025</v>
+        <v>1500.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>5448</v>
+        <v>5528</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>9.4139</v>
+        <v>9.925800000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-941.39</v>
+        <v>-992.58</v>
       </c>
       <c r="P18" t="n">
         <v>16.3422876</v>
@@ -1917,7 +1917,7 @@
         <v>-1634.22876</v>
       </c>
       <c r="S18" t="n">
-        <v>692.83876</v>
+        <v>641.64876</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-941.39</v>
+        <v>-992.58</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>7.475</v>
+        <v>7.975</v>
       </c>
       <c r="O19" t="n">
-        <v>-747.5</v>
+        <v>-797.5</v>
       </c>
       <c r="P19" t="n">
         <v>11.0194626</v>
@@ -2007,7 +2007,7 @@
         <v>-1101.94626</v>
       </c>
       <c r="S19" t="n">
-        <v>354.44626</v>
+        <v>304.44626</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-747.5</v>
+        <v>-797.5</v>
       </c>
     </row>
     <row r="20">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.36</v>
+        <v>2.405</v>
       </c>
       <c r="O20" t="n">
-        <v>-236</v>
+        <v>-240.5</v>
       </c>
       <c r="P20" t="n">
         <v>5.1936876</v>
@@ -2097,7 +2097,7 @@
         <v>-519.36876</v>
       </c>
       <c r="S20" t="n">
-        <v>283.36876</v>
+        <v>278.86876</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-236</v>
+        <v>-240.5</v>
       </c>
     </row>
     <row r="21">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1647</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1632.94</v>
+        <v>-1674</v>
       </c>
       <c r="P21" t="n">
         <v>6.3644671</v>
@@ -2187,7 +2187,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S21" t="n">
-        <v>-360.04658</v>
+        <v>-401.10658</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1632.94</v>
+        <v>-1674</v>
       </c>
     </row>
     <row r="22">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>8.734999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1747</v>
+        <v>-1806</v>
       </c>
       <c r="P22" t="n">
         <v>7.3548796</v>
@@ -2277,7 +2277,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S22" t="n">
-        <v>-276.02408</v>
+        <v>-335.02408</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1747</v>
+        <v>-1806</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.253</v>
+        <v>1.2535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,17 +2461,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>381.35</v>
+        <v>379.5</v>
       </c>
       <c r="O2" t="n">
-        <v>34321.5</v>
+        <v>34155</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2483,7 +2483,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>-1741.441488</v>
+        <v>-1907.941488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>43004.83949999999</v>
+        <v>42813.2925</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.253</v>
+        <v>1.2535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,17 +2541,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
       <c r="O3" t="n">
-        <v>18720</v>
+        <v>18750</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2563,7 +2563,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-1008.8595</v>
+        <v>-978.8595</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23456.16</v>
+        <v>23503.125</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14545</v>
+        <v>0.14586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8750.271999999999</v>
+        <v>8774.937599999999</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1542</v>
+        <v>1.1597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.014</v>
+        <v>3.9675</v>
       </c>
       <c r="O5" t="n">
-        <v>12042</v>
+        <v>11902.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2723,7 +2723,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1933.239091</v>
+        <v>-2072.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13898.8764</v>
+        <v>13803.32925</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1542</v>
+        <v>1.1597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,17 +2781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.12</v>
+        <v>45.73</v>
       </c>
       <c r="O6" t="n">
-        <v>46120</v>
+        <v>45730</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2803,7 +2803,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>3110</v>
+        <v>2720</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>53231.704</v>
+        <v>53033.081</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1542</v>
+        <v>1.1597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,17 +2861,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="O7" t="n">
-        <v>7500</v>
+        <v>7920</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2883,7 +2883,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>-844.17</v>
+        <v>-424.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>8656.5</v>
+        <v>9184.824000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77833</v>
+        <v>0.77998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,17 +2941,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.987</v>
+        <v>4.961</v>
       </c>
       <c r="O8" t="n">
-        <v>49870</v>
+        <v>49610</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2963,7 +2963,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12601.8184</v>
+        <v>12341.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38815.3171</v>
+        <v>38694.8078</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.77833</v>
+        <v>0.77998</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,29 +3021,29 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>554.4</v>
+        <v>552.15</v>
       </c>
       <c r="O9" t="n">
-        <v>41580</v>
+        <v>55215</v>
       </c>
       <c r="P9" t="n">
-        <v>589.644672</v>
+        <v>579.7134</v>
       </c>
       <c r="Q9" t="n">
-        <v>589.644672</v>
+        <v>579.7134</v>
       </c>
       <c r="R9" t="n">
-        <v>44223.3504</v>
+        <v>57971.34</v>
       </c>
       <c r="S9" t="n">
-        <v>-2643.3504</v>
+        <v>-2756.34</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>32362.9614</v>
+        <v>43066.5957</v>
       </c>
     </row>
     <row r="10">
@@ -3101,7 +3101,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -3181,17 +3181,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>208.5</v>
+        <v>209.62</v>
       </c>
       <c r="O11" t="n">
-        <v>6255</v>
+        <v>6288.6</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -3203,7 +3203,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-284.2</v>
+        <v>-250.6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6255</v>
+        <v>6288.6</v>
       </c>
     </row>
     <row r="12">
@@ -3261,17 +3261,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.58</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1916</v>
+        <v>1894</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3283,7 +3283,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-312.5</v>
+        <v>-334.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1916</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="13">
@@ -3341,17 +3341,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>299.99</v>
+        <v>305.46</v>
       </c>
       <c r="O13" t="n">
-        <v>59998</v>
+        <v>61092</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3363,7 +3363,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-2951.755</v>
+        <v>-1857.755</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>59998</v>
+        <v>61092</v>
       </c>
     </row>
     <row r="14">
@@ -3421,17 +3421,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>57.12</v>
+        <v>56.58</v>
       </c>
       <c r="O14" t="n">
-        <v>9139.200000000001</v>
+        <v>9052.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3443,7 +3443,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-493.24</v>
+        <v>-579.64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9139.200000000001</v>
+        <v>9052.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -3501,17 +3501,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>68.62</v>
+        <v>68.11</v>
       </c>
       <c r="O15" t="n">
-        <v>1155.89</v>
+        <v>1147.3</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3523,7 +3523,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>806.843421</v>
+        <v>798.253421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1155.89</v>
+        <v>1147.3</v>
       </c>
     </row>
     <row r="16">
@@ -3581,17 +3581,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.7962</v>
+        <v>26.1493</v>
       </c>
       <c r="O16" t="n">
-        <v>10316.54</v>
+        <v>10067.48</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3603,7 +3603,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>307.634112</v>
+        <v>58.574112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10316.54</v>
+        <v>10067.48</v>
       </c>
     </row>
     <row r="17">
@@ -3661,17 +3661,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>600</v>
       </c>
       <c r="N17" t="n">
-        <v>167.08</v>
+        <v>166.48</v>
       </c>
       <c r="O17" t="n">
-        <v>100248</v>
+        <v>99888</v>
       </c>
       <c r="P17" t="n">
         <v>172.9987895</v>
@@ -3683,7 +3683,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S17" t="n">
-        <v>-3551.2737</v>
+        <v>-3911.2737</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>100248</v>
+        <v>99888</v>
       </c>
     </row>
     <row r="18">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>32.1946</v>
+        <v>32.5724</v>
       </c>
       <c r="O18" t="n">
-        <v>6438.92</v>
+        <v>6514.48</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3773,7 +3773,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>1733.5175</v>
+        <v>1809.0775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>6438.92</v>
+        <v>6514.48</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>27.24</v>
+        <v>27.64</v>
       </c>
       <c r="O19" t="n">
-        <v>5448</v>
+        <v>5528</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3863,7 +3863,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>1420.9825</v>
+        <v>1500.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>5448</v>
+        <v>5528</v>
       </c>
     </row>
     <row r="20">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>6.05</v>
       </c>
       <c r="O20" t="n">
-        <v>-960</v>
+        <v>-1210</v>
       </c>
       <c r="P20" t="n">
         <v>4.9928846</v>
@@ -3953,7 +3953,7 @@
         <v>-998.57692</v>
       </c>
       <c r="S20" t="n">
-        <v>38.57692</v>
+        <v>-211.42308</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-960</v>
+        <v>-1210</v>
       </c>
     </row>
     <row r="21">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1647</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1632.94</v>
+        <v>-1674</v>
       </c>
       <c r="P21" t="n">
         <v>6.3929546</v>
@@ -4043,7 +4043,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S21" t="n">
-        <v>-354.34908</v>
+        <v>-395.40908</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1632.94</v>
+        <v>-1674</v>
       </c>
     </row>
     <row r="22">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>8.734999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1747</v>
+        <v>-1806</v>
       </c>
       <c r="P22" t="n">
         <v>7.3496796</v>
@@ -4133,7 +4133,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S22" t="n">
-        <v>-277.06408</v>
+        <v>-336.06408</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1747</v>
+        <v>-1806</v>
       </c>
     </row>
   </sheetData>
@@ -4193,17 +4193,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$266,205.98</t>
+          <t>$276,484.58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$158,993.48</t>
+          <t>$148,366.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$425,199.46</t>
+          <t>$424,851.06</t>
         </is>
       </c>
     </row>
@@ -4215,17 +4215,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$426,397.24</t>
+          <t>$437,301.65</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$108,695.09</t>
+          <t>$98,098.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$535,092.33</t>
+          <t>$535,400.41</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$692,603.22</t>
+          <t>$713,786.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$267,688.57</t>
+          <t>$246,465.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$960,291.79</t>
+          <t>$960,251.47</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07 23:47:34</t>
+          <t>2026-04-08 23:47:54</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2535</v>
+        <v>1.2637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>379.5</v>
+        <v>395.05</v>
       </c>
       <c r="O2" t="n">
-        <v>26565</v>
+        <v>27653.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>-1275.912405</v>
+        <v>-187.412405</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>33299.2275</v>
+        <v>34945.72795</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2535</v>
+        <v>1.2637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>62.5</v>
+        <v>65.77</v>
       </c>
       <c r="O3" t="n">
-        <v>12500</v>
+        <v>13154</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-574.426667</v>
+        <v>79.57333300000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15668.75</v>
+        <v>16622.7098</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14586</v>
+        <v>0.14635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.08</v>
+        <v>30.92</v>
       </c>
       <c r="O4" t="n">
-        <v>60160</v>
+        <v>61840</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-3252.49376</v>
+        <v>-1572.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8774.937599999999</v>
+        <v>9050.284</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1597</v>
+        <v>1.1662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9675</v>
+        <v>4.1585</v>
       </c>
       <c r="O5" t="n">
-        <v>7935</v>
+        <v>8317</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1389.66</v>
+        <v>-1007.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9202.219499999999</v>
+        <v>9699.285399999999</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1597</v>
+        <v>1.1662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>528</v>
+        <v>596</v>
       </c>
       <c r="O6" t="n">
-        <v>7920</v>
+        <v>8940</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>-424.17</v>
+        <v>595.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9184.824000000001</v>
+        <v>10425.828</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.77998</v>
+        <v>0.7849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.961</v>
+        <v>5.04</v>
       </c>
       <c r="O7" t="n">
-        <v>39688</v>
+        <v>40320</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2376.77315</v>
+        <v>3008.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>30955.84624</v>
+        <v>31647.168</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77998</v>
+        <v>0.7849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>552.15</v>
+        <v>562.12</v>
       </c>
       <c r="O8" t="n">
-        <v>55215</v>
+        <v>56212</v>
       </c>
       <c r="P8" t="n">
         <v>579.71400048</v>
@@ -1087,7 +1087,7 @@
         <v>57971.400048</v>
       </c>
       <c r="S8" t="n">
-        <v>-2756.400048</v>
+        <v>-1759.400048</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>43066.5957</v>
+        <v>44120.7988</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>6.95</v>
+        <v>7.405</v>
       </c>
       <c r="O9" t="n">
-        <v>6950</v>
+        <v>7405</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-1361.237657</v>
+        <v>-906.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>6950</v>
+        <v>7405</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>209.62</v>
+        <v>215.59</v>
       </c>
       <c r="O10" t="n">
-        <v>6288.6</v>
+        <v>6467.7</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-254.5</v>
+        <v>-75.40000000000001</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6288.6</v>
+        <v>6467.7</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>947</v>
+        <v>980</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>-23.5</v>
+        <v>9.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>947</v>
+        <v>980</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>56.58</v>
+        <v>60.01</v>
       </c>
       <c r="O12" t="n">
-        <v>9052.799999999999</v>
+        <v>9601.6</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>-523.86</v>
+        <v>24.94</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9052.799999999999</v>
+        <v>9601.6</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>26.1493</v>
+        <v>27.2691</v>
       </c>
       <c r="O13" t="n">
-        <v>10067.48</v>
+        <v>10498.6</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>52.577178</v>
+        <v>483.697178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10067.48</v>
+        <v>10498.6</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>81.36</v>
+        <v>85.31</v>
       </c>
       <c r="O14" t="n">
-        <v>3254.4</v>
+        <v>3412.4</v>
       </c>
       <c r="P14" t="n">
         <v>102.0775</v>
@@ -1567,7 +1567,7 @@
         <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-828.7</v>
+        <v>-670.7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3254.4</v>
+        <v>3412.4</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>500</v>
       </c>
       <c r="N15" t="n">
-        <v>166.48</v>
+        <v>173.12</v>
       </c>
       <c r="O15" t="n">
-        <v>83240</v>
+        <v>86560</v>
       </c>
       <c r="P15" t="n">
         <v>172.83405384</v>
@@ -1647,7 +1647,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S15" t="n">
-        <v>-3177.02692</v>
+        <v>142.97308</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>83240</v>
+        <v>86560</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>32.5724</v>
+        <v>26.6217</v>
       </c>
       <c r="O16" t="n">
-        <v>6514.48</v>
+        <v>5324.34</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1822.38</v>
+        <v>632.24</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>6514.48</v>
+        <v>5324.34</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>27.64</v>
+        <v>21.925</v>
       </c>
       <c r="O17" t="n">
-        <v>5528</v>
+        <v>4385</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>1500.5025</v>
+        <v>357.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>5528</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="18">
@@ -1869,23 +1869,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>META  260501P00520000</t>
+          <t>META  260522P00565000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>META 01MAY26 520 P</t>
+          <t>META 22MAY26 565 P</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>520</v>
+        <v>565</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1895,29 +1895,29 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>9.925800000000001</v>
+        <v>16.4363</v>
       </c>
       <c r="O18" t="n">
-        <v>-992.58</v>
+        <v>-1643.63</v>
       </c>
       <c r="P18" t="n">
-        <v>16.3422876</v>
+        <v>19.9890756</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.3422876</v>
+        <v>19.9890756</v>
       </c>
       <c r="R18" t="n">
-        <v>-1634.22876</v>
+        <v>-1998.90756</v>
       </c>
       <c r="S18" t="n">
-        <v>641.64876</v>
+        <v>355.27756</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-992.58</v>
+        <v>-1643.63</v>
       </c>
     </row>
     <row r="19">
@@ -1959,23 +1959,23 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MSFT  260501P00355000</t>
+          <t>MSFT  260522P00370000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MSFT 01MAY26 355 P</t>
+          <t>MSFT 22MAY26 370 P</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1985,29 +1985,29 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>7.975</v>
+        <v>15.0789</v>
       </c>
       <c r="O19" t="n">
-        <v>-797.5</v>
+        <v>-1507.89</v>
       </c>
       <c r="P19" t="n">
-        <v>11.0194626</v>
+        <v>12.80919851</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.0194626</v>
+        <v>12.80919851</v>
       </c>
       <c r="R19" t="n">
-        <v>-1101.94626</v>
+        <v>-1280.919851</v>
       </c>
       <c r="S19" t="n">
-        <v>304.44626</v>
+        <v>-226.970149</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-797.5</v>
+        <v>-1507.89</v>
       </c>
     </row>
     <row r="20">
@@ -2049,23 +2049,23 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NVDA  260501P00165000</t>
+          <t>NVDA  260522P00175000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NVDA 01MAY26 165 P</t>
+          <t>NVDA 22MAY26 175 P</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2075,29 +2075,29 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.405</v>
+        <v>6.55</v>
       </c>
       <c r="O20" t="n">
-        <v>-240.5</v>
+        <v>-1310</v>
       </c>
       <c r="P20" t="n">
-        <v>5.1936876</v>
+        <v>6.9928434</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.1936876</v>
+        <v>6.9928434</v>
       </c>
       <c r="R20" t="n">
-        <v>-519.36876</v>
+        <v>-1398.56868</v>
       </c>
       <c r="S20" t="n">
-        <v>278.86876</v>
+        <v>88.56868</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-240.5</v>
+        <v>-1310</v>
       </c>
     </row>
     <row r="21">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>8.369999999999999</v>
+        <v>6.7127</v>
       </c>
       <c r="O21" t="n">
-        <v>-1674</v>
+        <v>-1342.54</v>
       </c>
       <c r="P21" t="n">
         <v>6.3644671</v>
@@ -2187,7 +2187,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S21" t="n">
-        <v>-401.10658</v>
+        <v>-69.64658</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1674</v>
+        <v>-1342.54</v>
       </c>
     </row>
     <row r="22">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>9.029999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="O22" t="n">
-        <v>-1806</v>
+        <v>-1434</v>
       </c>
       <c r="P22" t="n">
         <v>7.3548796</v>
@@ -2277,7 +2277,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S22" t="n">
-        <v>-335.02408</v>
+        <v>36.97592</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1806</v>
+        <v>-1434</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2535</v>
+        <v>1.2637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,17 +2461,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>379.5</v>
+        <v>395.05</v>
       </c>
       <c r="O2" t="n">
-        <v>34155</v>
+        <v>35554.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2483,7 +2483,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>-1907.941488</v>
+        <v>-508.441488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>42813.2925</v>
+        <v>44930.22165</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2535</v>
+        <v>1.2637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,17 +2541,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>62.5</v>
+        <v>65.77</v>
       </c>
       <c r="O3" t="n">
-        <v>18750</v>
+        <v>19731</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2563,7 +2563,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-978.8595</v>
+        <v>2.1405</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23503.125</v>
+        <v>24934.0647</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14586</v>
+        <v>0.14635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,17 +2621,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.08</v>
+        <v>30.92</v>
       </c>
       <c r="O4" t="n">
-        <v>60160</v>
+        <v>61840</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2643,7 +2643,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-3232.47719</v>
+        <v>-1552.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8774.937599999999</v>
+        <v>9050.284</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1597</v>
+        <v>1.1662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9675</v>
+        <v>4.1585</v>
       </c>
       <c r="O5" t="n">
-        <v>11902.5</v>
+        <v>12475.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2723,7 +2723,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-2072.739091</v>
+        <v>-1499.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13803.32925</v>
+        <v>14548.9281</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1597</v>
+        <v>1.1662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,17 +2781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>45.73</v>
+        <v>48.33</v>
       </c>
       <c r="O6" t="n">
-        <v>45730</v>
+        <v>48330</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2803,7 +2803,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>2720</v>
+        <v>5320</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>53033.081</v>
+        <v>56362.446</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1597</v>
+        <v>1.1662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,17 +2861,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>528</v>
+        <v>596</v>
       </c>
       <c r="O7" t="n">
-        <v>7920</v>
+        <v>8940</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2883,7 +2883,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>-424.17</v>
+        <v>595.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>9184.824000000001</v>
+        <v>10425.828</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.77998</v>
+        <v>0.7849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,17 +2941,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.961</v>
+        <v>5.04</v>
       </c>
       <c r="O8" t="n">
-        <v>49610</v>
+        <v>50400</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2963,7 +2963,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12341.8184</v>
+        <v>13131.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>38694.8078</v>
+        <v>39558.96</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.77998</v>
+        <v>0.7849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,17 +3021,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>552.15</v>
+        <v>562.12</v>
       </c>
       <c r="O9" t="n">
-        <v>55215</v>
+        <v>56212</v>
       </c>
       <c r="P9" t="n">
         <v>579.7134</v>
@@ -3043,7 +3043,7 @@
         <v>57971.34</v>
       </c>
       <c r="S9" t="n">
-        <v>-2756.34</v>
+        <v>-1759.34</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>43066.5957</v>
+        <v>44120.7988</v>
       </c>
     </row>
     <row r="10">
@@ -3101,17 +3101,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>6.95</v>
+        <v>7.405</v>
       </c>
       <c r="O10" t="n">
-        <v>7645</v>
+        <v>8145.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -3123,7 +3123,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1497.847947</v>
+        <v>-997.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>7645</v>
+        <v>8145.5</v>
       </c>
     </row>
     <row r="11">
@@ -3181,17 +3181,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>209.62</v>
+        <v>215.59</v>
       </c>
       <c r="O11" t="n">
-        <v>6288.6</v>
+        <v>6467.7</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -3203,7 +3203,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-250.6</v>
+        <v>-71.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6288.6</v>
+        <v>6467.7</v>
       </c>
     </row>
     <row r="12">
@@ -3261,17 +3261,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.470000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1894</v>
+        <v>1960</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3283,7 +3283,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-334.5</v>
+        <v>-268.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1894</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="13">
@@ -3341,17 +3341,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>305.46</v>
+        <v>317.32</v>
       </c>
       <c r="O13" t="n">
-        <v>61092</v>
+        <v>63464</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3363,7 +3363,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>-1857.755</v>
+        <v>514.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>61092</v>
+        <v>63464</v>
       </c>
     </row>
     <row r="14">
@@ -3421,17 +3421,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>56.58</v>
+        <v>60.01</v>
       </c>
       <c r="O14" t="n">
-        <v>9052.799999999999</v>
+        <v>9601.6</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3443,7 +3443,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-579.64</v>
+        <v>-30.84</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9052.799999999999</v>
+        <v>9601.6</v>
       </c>
     </row>
     <row r="15">
@@ -3501,17 +3501,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>68.11</v>
+        <v>72.31</v>
       </c>
       <c r="O15" t="n">
-        <v>1147.3</v>
+        <v>1218.05</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3523,7 +3523,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>798.253421</v>
+        <v>869.003421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1147.3</v>
+        <v>1218.05</v>
       </c>
     </row>
     <row r="16">
@@ -3581,17 +3581,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>26.1493</v>
+        <v>27.2691</v>
       </c>
       <c r="O16" t="n">
-        <v>10067.48</v>
+        <v>10498.6</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3603,7 +3603,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>58.574112</v>
+        <v>489.694112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10067.48</v>
+        <v>10498.6</v>
       </c>
     </row>
     <row r="17">
@@ -3661,17 +3661,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>600</v>
       </c>
       <c r="N17" t="n">
-        <v>166.48</v>
+        <v>173.12</v>
       </c>
       <c r="O17" t="n">
-        <v>99888</v>
+        <v>103872</v>
       </c>
       <c r="P17" t="n">
         <v>172.9987895</v>
@@ -3683,7 +3683,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S17" t="n">
-        <v>-3911.2737</v>
+        <v>72.72629999999999</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>99888</v>
+        <v>103872</v>
       </c>
     </row>
     <row r="18">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>32.5724</v>
+        <v>26.6217</v>
       </c>
       <c r="O18" t="n">
-        <v>6514.48</v>
+        <v>5324.34</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3773,7 +3773,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>1809.0775</v>
+        <v>618.9375</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>6514.48</v>
+        <v>5324.34</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>27.64</v>
+        <v>21.925</v>
       </c>
       <c r="O19" t="n">
-        <v>5528</v>
+        <v>4385</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3863,7 +3863,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>1500.9825</v>
+        <v>357.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>5528</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="20">
@@ -3905,19 +3905,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GOOGL 260522C00330000</t>
+          <t>GOOGL 260522C00345000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>GOOGL 22MAY26 330 C</t>
+          <t>GOOGL 22MAY26 345 C</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -3931,29 +3931,29 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>6.05</v>
+        <v>5.5246</v>
       </c>
       <c r="O20" t="n">
-        <v>-1210</v>
+        <v>-1104.92</v>
       </c>
       <c r="P20" t="n">
-        <v>4.9928846</v>
+        <v>5.1653811</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9928846</v>
+        <v>5.1653811</v>
       </c>
       <c r="R20" t="n">
-        <v>-998.57692</v>
+        <v>-1033.07622</v>
       </c>
       <c r="S20" t="n">
-        <v>-211.42308</v>
+        <v>-71.84378</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1210</v>
+        <v>-1104.92</v>
       </c>
     </row>
     <row r="21">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>8.369999999999999</v>
+        <v>6.7127</v>
       </c>
       <c r="O21" t="n">
-        <v>-1674</v>
+        <v>-1342.54</v>
       </c>
       <c r="P21" t="n">
         <v>6.3929546</v>
@@ -4043,7 +4043,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S21" t="n">
-        <v>-395.40908</v>
+        <v>-63.94908</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1674</v>
+        <v>-1342.54</v>
       </c>
     </row>
     <row r="22">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>9.029999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="O22" t="n">
-        <v>-1806</v>
+        <v>-1434</v>
       </c>
       <c r="P22" t="n">
         <v>7.3496796</v>
@@ -4133,7 +4133,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S22" t="n">
-        <v>-336.06408</v>
+        <v>35.93592</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1806</v>
+        <v>-1434</v>
       </c>
     </row>
   </sheetData>
@@ -4193,17 +4193,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$276,484.58</t>
+          <t>$283,908.38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$148,366.48</t>
+          <t>$152,213.96</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$424,851.06</t>
+          <t>$436,122.34</t>
         </is>
       </c>
     </row>
@@ -4215,17 +4215,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$437,301.65</t>
+          <t>$454,986.86</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$98,098.76</t>
+          <t>$96,977.41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$535,400.41</t>
+          <t>$551,964.27</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$713,786.23</t>
+          <t>$738,895.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$246,465.24</t>
+          <t>$249,191.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$960,251.47</t>
+          <t>$988,086.61</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08 23:47:54</t>
+          <t>2026-04-09 23:47:28</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2637</v>
+        <v>1.2651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>395.05</v>
+        <v>396.35</v>
       </c>
       <c r="O2" t="n">
-        <v>27653.5</v>
+        <v>27744.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>-187.412405</v>
+        <v>-96.41240500000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>34945.72795</v>
+        <v>35099.56695</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2637</v>
+        <v>1.2651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>65.77</v>
+        <v>65.14</v>
       </c>
       <c r="O3" t="n">
-        <v>13154</v>
+        <v>13028</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>79.57333300000001</v>
+        <v>-46.426667</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>16622.7098</v>
+        <v>16481.7228</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14635</v>
+        <v>0.14645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.92</v>
+        <v>30.66</v>
       </c>
       <c r="O4" t="n">
-        <v>61840</v>
+        <v>61320</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-1572.49376</v>
+        <v>-2092.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9050.284</v>
+        <v>8980.314</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1662</v>
+        <v>1.1699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1585</v>
+        <v>4.1075</v>
       </c>
       <c r="O5" t="n">
-        <v>8317</v>
+        <v>8215</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1007.66</v>
+        <v>-1109.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9699.285399999999</v>
+        <v>9610.728499999999</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1662</v>
+        <v>1.1699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10425.828</v>
+        <v>10458.906</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7849</v>
+        <v>0.78554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5.04</v>
+        <v>5.003</v>
       </c>
       <c r="O7" t="n">
-        <v>40320</v>
+        <v>40024</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>3008.77315</v>
+        <v>2712.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31647.168</v>
+        <v>31440.45296</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7849</v>
+        <v>0.78554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>562.12</v>
+        <v>553.4299999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>56212</v>
+        <v>55343</v>
       </c>
       <c r="P8" t="n">
         <v>579.71400048</v>
@@ -1087,7 +1087,7 @@
         <v>57971.400048</v>
       </c>
       <c r="S8" t="n">
-        <v>-1759.400048</v>
+        <v>-2628.400048</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>44120.7988</v>
+        <v>43474.14022</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.405</v>
+        <v>7.395</v>
       </c>
       <c r="O9" t="n">
-        <v>7405</v>
+        <v>7395</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-906.237657</v>
+        <v>-916.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7405</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>215.59</v>
+        <v>216.44</v>
       </c>
       <c r="O10" t="n">
-        <v>6467.7</v>
+        <v>6493.2</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-75.40000000000001</v>
+        <v>-49.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6467.7</v>
+        <v>6493.2</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="O11" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>9.5</v>
+        <v>19.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>60.01</v>
+        <v>60.65</v>
       </c>
       <c r="O12" t="n">
-        <v>9601.6</v>
+        <v>9704</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>24.94</v>
+        <v>127.34</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9601.6</v>
+        <v>9704</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>27.2691</v>
+        <v>27.5276</v>
       </c>
       <c r="O13" t="n">
-        <v>10498.6</v>
+        <v>10598.13</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>483.697178</v>
+        <v>583.227178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10498.6</v>
+        <v>10598.13</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>85.31</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>3412.4</v>
+        <v>3418.4</v>
       </c>
       <c r="P14" t="n">
         <v>102.0775</v>
@@ -1567,7 +1567,7 @@
         <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-670.7</v>
+        <v>-664.7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3412.4</v>
+        <v>3418.4</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>500</v>
       </c>
       <c r="N15" t="n">
-        <v>173.12</v>
+        <v>173.42</v>
       </c>
       <c r="O15" t="n">
-        <v>86560</v>
+        <v>86710</v>
       </c>
       <c r="P15" t="n">
         <v>172.83405384</v>
@@ -1647,7 +1647,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S15" t="n">
-        <v>142.97308</v>
+        <v>292.97308</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>86560</v>
+        <v>86710</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>26.6217</v>
+        <v>24.8275</v>
       </c>
       <c r="O16" t="n">
-        <v>5324.34</v>
+        <v>4965.5</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>632.24</v>
+        <v>273.4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>5324.34</v>
+        <v>4965.5</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>21.925</v>
+        <v>20.4</v>
       </c>
       <c r="O17" t="n">
-        <v>4385</v>
+        <v>4080</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>357.5025</v>
+        <v>52.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>4385</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>16.4363</v>
+        <v>12.185</v>
       </c>
       <c r="O18" t="n">
-        <v>-1643.63</v>
+        <v>-1218.5</v>
       </c>
       <c r="P18" t="n">
         <v>19.9890756</v>
@@ -1917,7 +1917,7 @@
         <v>-1998.90756</v>
       </c>
       <c r="S18" t="n">
-        <v>355.27756</v>
+        <v>780.40756</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-1643.63</v>
+        <v>-1218.5</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>15.0789</v>
+        <v>15.3824</v>
       </c>
       <c r="O19" t="n">
-        <v>-1507.89</v>
+        <v>-1538.24</v>
       </c>
       <c r="P19" t="n">
         <v>12.80919851</v>
@@ -2007,7 +2007,7 @@
         <v>-1280.919851</v>
       </c>
       <c r="S19" t="n">
-        <v>-226.970149</v>
+        <v>-257.320149</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-1507.89</v>
+        <v>-1538.24</v>
       </c>
     </row>
     <row r="20">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>6.55</v>
+        <v>5.775</v>
       </c>
       <c r="O20" t="n">
-        <v>-1310</v>
+        <v>-1155</v>
       </c>
       <c r="P20" t="n">
         <v>6.9928434</v>
@@ -2097,7 +2097,7 @@
         <v>-1398.56868</v>
       </c>
       <c r="S20" t="n">
-        <v>88.56868</v>
+        <v>243.56868</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1310</v>
+        <v>-1155</v>
       </c>
     </row>
     <row r="21">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>6.7127</v>
+        <v>6.2356</v>
       </c>
       <c r="O21" t="n">
-        <v>-1342.54</v>
+        <v>-1247.12</v>
       </c>
       <c r="P21" t="n">
         <v>6.3644671</v>
@@ -2187,7 +2187,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S21" t="n">
-        <v>-69.64658</v>
+        <v>25.77342</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1342.54</v>
+        <v>-1247.12</v>
       </c>
     </row>
     <row r="22">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>7.17</v>
+        <v>6.75</v>
       </c>
       <c r="O22" t="n">
-        <v>-1434</v>
+        <v>-1350</v>
       </c>
       <c r="P22" t="n">
         <v>7.3548796</v>
@@ -2277,7 +2277,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S22" t="n">
-        <v>36.97592</v>
+        <v>120.97592</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1434</v>
+        <v>-1350</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2637</v>
+        <v>1.2651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,17 +2461,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>395.05</v>
+        <v>396.35</v>
       </c>
       <c r="O2" t="n">
-        <v>35554.5</v>
+        <v>35671.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2483,7 +2483,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>-508.441488</v>
+        <v>-391.441488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>44930.22165</v>
+        <v>45128.01465</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2637</v>
+        <v>1.2651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,17 +2541,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>65.77</v>
+        <v>65.14</v>
       </c>
       <c r="O3" t="n">
-        <v>19731</v>
+        <v>19542</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2563,7 +2563,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1405</v>
+        <v>-186.8595</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>24934.0647</v>
+        <v>24722.5842</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14635</v>
+        <v>0.14645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,17 +2621,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.92</v>
+        <v>30.66</v>
       </c>
       <c r="O4" t="n">
-        <v>61840</v>
+        <v>61320</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2643,7 +2643,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-1552.47719</v>
+        <v>-2072.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9050.284</v>
+        <v>8980.314</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1662</v>
+        <v>1.1699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1585</v>
+        <v>4.1075</v>
       </c>
       <c r="O5" t="n">
-        <v>12475.5</v>
+        <v>12322.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2723,7 +2723,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1499.739091</v>
+        <v>-1652.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14548.9281</v>
+        <v>14416.09275</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1662</v>
+        <v>1.1699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,17 +2781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>48.33</v>
+        <v>48.63</v>
       </c>
       <c r="O6" t="n">
-        <v>48330</v>
+        <v>48630</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2803,7 +2803,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>5320</v>
+        <v>5620</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>56362.446</v>
+        <v>56892.23699999999</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1662</v>
+        <v>1.1699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>10425.828</v>
+        <v>10458.906</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7849</v>
+        <v>0.78554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,17 +2941,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>5.04</v>
+        <v>5.003</v>
       </c>
       <c r="O8" t="n">
-        <v>50400</v>
+        <v>50030</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2963,7 +2963,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>13131.8184</v>
+        <v>12761.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39558.96</v>
+        <v>39300.5662</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7849</v>
+        <v>0.78554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,17 +3021,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>562.12</v>
+        <v>553.4299999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>56212</v>
+        <v>55343</v>
       </c>
       <c r="P9" t="n">
         <v>579.7134</v>
@@ -3043,7 +3043,7 @@
         <v>57971.34</v>
       </c>
       <c r="S9" t="n">
-        <v>-1759.34</v>
+        <v>-2628.34</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>44120.7988</v>
+        <v>43474.14022</v>
       </c>
     </row>
     <row r="10">
@@ -3101,17 +3101,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.405</v>
+        <v>7.395</v>
       </c>
       <c r="O10" t="n">
-        <v>8145.5</v>
+        <v>8134.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -3123,7 +3123,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-997.347947</v>
+        <v>-1008.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8145.5</v>
+        <v>8134.5</v>
       </c>
     </row>
     <row r="11">
@@ -3181,17 +3181,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>215.59</v>
+        <v>216.44</v>
       </c>
       <c r="O11" t="n">
-        <v>6467.7</v>
+        <v>6493.2</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -3203,7 +3203,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-71.5</v>
+        <v>-46</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6467.7</v>
+        <v>6493.2</v>
       </c>
     </row>
     <row r="12">
@@ -3261,17 +3261,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1960</v>
+        <v>1980</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3283,7 +3283,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-268.5</v>
+        <v>-248.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1960</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="13">
@@ -3341,17 +3341,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>317.32</v>
+        <v>318.49</v>
       </c>
       <c r="O13" t="n">
-        <v>63464</v>
+        <v>63698</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3363,7 +3363,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>514.245</v>
+        <v>748.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>63464</v>
+        <v>63698</v>
       </c>
     </row>
     <row r="14">
@@ -3421,17 +3421,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>60.01</v>
+        <v>60.65</v>
       </c>
       <c r="O14" t="n">
-        <v>9601.6</v>
+        <v>9704</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3443,7 +3443,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-30.84</v>
+        <v>71.56</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9601.6</v>
+        <v>9704</v>
       </c>
     </row>
     <row r="15">
@@ -3501,17 +3501,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>72.31</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>1218.05</v>
+        <v>1211.65</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3523,7 +3523,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>869.003421</v>
+        <v>862.603421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1218.05</v>
+        <v>1211.65</v>
       </c>
     </row>
     <row r="16">
@@ -3581,17 +3581,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.2691</v>
+        <v>27.5276</v>
       </c>
       <c r="O16" t="n">
-        <v>10498.6</v>
+        <v>10598.13</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3603,7 +3603,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>489.694112</v>
+        <v>589.224112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10498.6</v>
+        <v>10598.13</v>
       </c>
     </row>
     <row r="17">
@@ -3661,17 +3661,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>600</v>
       </c>
       <c r="N17" t="n">
-        <v>173.12</v>
+        <v>173.42</v>
       </c>
       <c r="O17" t="n">
-        <v>103872</v>
+        <v>104052</v>
       </c>
       <c r="P17" t="n">
         <v>172.9987895</v>
@@ -3683,7 +3683,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S17" t="n">
-        <v>72.72629999999999</v>
+        <v>252.7263</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>103872</v>
+        <v>104052</v>
       </c>
     </row>
     <row r="18">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>26.6217</v>
+        <v>24.8275</v>
       </c>
       <c r="O18" t="n">
-        <v>5324.34</v>
+        <v>4965.5</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3773,7 +3773,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>618.9375</v>
+        <v>260.0975</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>5324.34</v>
+        <v>4965.5</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>21.925</v>
+        <v>20.4</v>
       </c>
       <c r="O19" t="n">
-        <v>4385</v>
+        <v>4080</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3863,7 +3863,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>357.9825</v>
+        <v>52.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>4385</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="20">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>5.5246</v>
+        <v>6.1</v>
       </c>
       <c r="O20" t="n">
-        <v>-1104.92</v>
+        <v>-1220</v>
       </c>
       <c r="P20" t="n">
         <v>5.1653811</v>
@@ -3953,7 +3953,7 @@
         <v>-1033.07622</v>
       </c>
       <c r="S20" t="n">
-        <v>-71.84378</v>
+        <v>-186.92378</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1104.92</v>
+        <v>-1220</v>
       </c>
     </row>
     <row r="21">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>6.7127</v>
+        <v>6.2356</v>
       </c>
       <c r="O21" t="n">
-        <v>-1342.54</v>
+        <v>-1247.12</v>
       </c>
       <c r="P21" t="n">
         <v>6.3929546</v>
@@ -4043,7 +4043,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S21" t="n">
-        <v>-63.94908</v>
+        <v>31.47092</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1342.54</v>
+        <v>-1247.12</v>
       </c>
     </row>
     <row r="22">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>7.17</v>
+        <v>6.75</v>
       </c>
       <c r="O22" t="n">
-        <v>-1434</v>
+        <v>-1350</v>
       </c>
       <c r="P22" t="n">
         <v>7.3496796</v>
@@ -4133,7 +4133,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S22" t="n">
-        <v>35.93592</v>
+        <v>119.93592</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1434</v>
+        <v>-1350</v>
       </c>
     </row>
   </sheetData>
@@ -4193,17 +4193,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$283,908.38</t>
+          <t>$283,391.20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$152,213.96</t>
+          <t>$152,266.59</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$436,122.34</t>
+          <t>$435,657.79</t>
         </is>
       </c>
     </row>
@@ -4215,17 +4215,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$454,986.86</t>
+          <t>$454,472.72</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$96,977.41</t>
+          <t>$97,049.18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$551,964.27</t>
+          <t>$551,521.89</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$738,895.24</t>
+          <t>$737,863.92</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$249,191.36</t>
+          <t>$249,315.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$988,086.61</t>
+          <t>$987,179.68</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09 23:47:28</t>
+          <t>2026-04-10 23:47:31</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2651</v>
+        <v>1.2672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>396.35</v>
+        <v>399.55</v>
       </c>
       <c r="O2" t="n">
-        <v>27744.5</v>
+        <v>27968.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>-96.41240500000001</v>
+        <v>127.587595</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35099.56695</v>
+        <v>35441.6832</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2651</v>
+        <v>1.2672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>65.14</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>13028</v>
+        <v>13248</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>-46.426667</v>
+        <v>173.573333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>16481.7228</v>
+        <v>16787.8656</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14645</v>
+        <v>0.1465</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.66</v>
+        <v>31.12</v>
       </c>
       <c r="O4" t="n">
-        <v>61320</v>
+        <v>62240</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-2092.49376</v>
+        <v>-1172.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8980.314</v>
+        <v>9118.16</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1699</v>
+        <v>1.1725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1075</v>
+        <v>4.147</v>
       </c>
       <c r="O5" t="n">
-        <v>8215</v>
+        <v>8294</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1109.66</v>
+        <v>-1030.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9610.728499999999</v>
+        <v>9724.715</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1699</v>
+        <v>1.1725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="O6" t="n">
-        <v>8940</v>
+        <v>8850</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>595.83</v>
+        <v>505.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10458.906</v>
+        <v>10376.625</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78554</v>
+        <v>0.78503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5.003</v>
+        <v>5.03</v>
       </c>
       <c r="O7" t="n">
-        <v>40024</v>
+        <v>40240</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2712.77315</v>
+        <v>2928.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31440.45296</v>
+        <v>31589.6072</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78554</v>
+        <v>0.78503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>553.4299999999999</v>
+        <v>555</v>
       </c>
       <c r="O8" t="n">
-        <v>55343</v>
+        <v>55500</v>
       </c>
       <c r="P8" t="n">
         <v>579.71400048</v>
@@ -1087,7 +1087,7 @@
         <v>57971.400048</v>
       </c>
       <c r="S8" t="n">
-        <v>-2628.400048</v>
+        <v>-2471.400048</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>43474.14022</v>
+        <v>43569.165</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.395</v>
+        <v>7.495</v>
       </c>
       <c r="O9" t="n">
-        <v>7395</v>
+        <v>7495</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-916.237657</v>
+        <v>-816.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7395</v>
+        <v>7495</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>216.44</v>
+        <v>218.75</v>
       </c>
       <c r="O10" t="n">
-        <v>6493.2</v>
+        <v>6562.5</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-49.9</v>
+        <v>19.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6493.2</v>
+        <v>6562.5</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.9</v>
+        <v>10.06</v>
       </c>
       <c r="O11" t="n">
-        <v>990</v>
+        <v>1006</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>19.5</v>
+        <v>35.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>990</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>60.65</v>
+        <v>61.53</v>
       </c>
       <c r="O12" t="n">
-        <v>9704</v>
+        <v>9844.799999999999</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>127.34</v>
+        <v>268.14</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9704</v>
+        <v>9844.799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>27.5276</v>
+        <v>27.9615</v>
       </c>
       <c r="O13" t="n">
-        <v>10598.13</v>
+        <v>10765.18</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>583.227178</v>
+        <v>750.277178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10598.13</v>
+        <v>10765.18</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>85.45999999999999</v>
+        <v>85.92</v>
       </c>
       <c r="O14" t="n">
-        <v>3418.4</v>
+        <v>3436.8</v>
       </c>
       <c r="P14" t="n">
         <v>102.0775</v>
@@ -1567,7 +1567,7 @@
         <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-664.7</v>
+        <v>-646.3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3418.4</v>
+        <v>3436.8</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>500</v>
       </c>
       <c r="N15" t="n">
-        <v>173.42</v>
+        <v>174.26</v>
       </c>
       <c r="O15" t="n">
-        <v>86710</v>
+        <v>87130</v>
       </c>
       <c r="P15" t="n">
         <v>172.83405384</v>
@@ -1647,7 +1647,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S15" t="n">
-        <v>292.97308</v>
+        <v>712.97308</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>86710</v>
+        <v>87130</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>24.8275</v>
+        <v>24.671</v>
       </c>
       <c r="O16" t="n">
-        <v>4965.5</v>
+        <v>4934.2</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>273.4</v>
+        <v>242.1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>4965.5</v>
+        <v>4934.2</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>20.4</v>
+        <v>20.73</v>
       </c>
       <c r="O17" t="n">
-        <v>4080</v>
+        <v>4146</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>52.5025</v>
+        <v>118.5025</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>4080</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>12.185</v>
+        <v>10.9359</v>
       </c>
       <c r="O18" t="n">
-        <v>-1218.5</v>
+        <v>-1093.59</v>
       </c>
       <c r="P18" t="n">
         <v>19.9890756</v>
@@ -1917,7 +1917,7 @@
         <v>-1998.90756</v>
       </c>
       <c r="S18" t="n">
-        <v>780.40756</v>
+        <v>905.31756</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-1218.5</v>
+        <v>-1093.59</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>15.3824</v>
+        <v>16.6</v>
       </c>
       <c r="O19" t="n">
-        <v>-1538.24</v>
+        <v>-1660</v>
       </c>
       <c r="P19" t="n">
         <v>12.80919851</v>
@@ -2007,7 +2007,7 @@
         <v>-1280.919851</v>
       </c>
       <c r="S19" t="n">
-        <v>-257.320149</v>
+        <v>-379.080149</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-1538.24</v>
+        <v>-1660</v>
       </c>
     </row>
     <row r="20">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>5.775</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>-1155</v>
+        <v>-900</v>
       </c>
       <c r="P20" t="n">
         <v>6.9928434</v>
@@ -2097,7 +2097,7 @@
         <v>-1398.56868</v>
       </c>
       <c r="S20" t="n">
-        <v>243.56868</v>
+        <v>498.56868</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1155</v>
+        <v>-900</v>
       </c>
     </row>
     <row r="21">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2356</v>
+        <v>6.1885</v>
       </c>
       <c r="O21" t="n">
-        <v>-1247.12</v>
+        <v>-1237.7</v>
       </c>
       <c r="P21" t="n">
         <v>6.3644671</v>
@@ -2187,7 +2187,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S21" t="n">
-        <v>25.77342</v>
+        <v>35.19342</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1247.12</v>
+        <v>-1237.7</v>
       </c>
     </row>
     <row r="22">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="O22" t="n">
-        <v>-1350</v>
+        <v>-1376</v>
       </c>
       <c r="P22" t="n">
         <v>7.3548796</v>
@@ -2277,7 +2277,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S22" t="n">
-        <v>120.97592</v>
+        <v>94.97592</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1350</v>
+        <v>-1376</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2651</v>
+        <v>1.2672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,17 +2461,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>396.35</v>
+        <v>399.55</v>
       </c>
       <c r="O2" t="n">
-        <v>35671.5</v>
+        <v>35959.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2483,7 +2483,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>-391.441488</v>
+        <v>-103.441488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>45128.01465</v>
+        <v>45567.8784</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2651</v>
+        <v>1.2672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,17 +2541,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>65.14</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>19542</v>
+        <v>19872</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2563,7 +2563,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>-186.8595</v>
+        <v>143.1405</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>24722.5842</v>
+        <v>25181.7984</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14645</v>
+        <v>0.1465</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,17 +2621,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>30.66</v>
+        <v>31.12</v>
       </c>
       <c r="O4" t="n">
-        <v>61320</v>
+        <v>62240</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2643,7 +2643,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-2072.47719</v>
+        <v>-1152.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>8980.314</v>
+        <v>9118.16</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1699</v>
+        <v>1.1725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1075</v>
+        <v>4.147</v>
       </c>
       <c r="O5" t="n">
-        <v>12322.5</v>
+        <v>12441</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2723,7 +2723,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1652.739091</v>
+        <v>-1534.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14416.09275</v>
+        <v>14587.0725</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1699</v>
+        <v>1.1725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,17 +2781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>48.63</v>
+        <v>49.14</v>
       </c>
       <c r="O6" t="n">
-        <v>48630</v>
+        <v>49140</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2803,7 +2803,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>5620</v>
+        <v>6130</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>56892.23699999999</v>
+        <v>57616.65</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1699</v>
+        <v>1.1725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,17 +2861,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="O7" t="n">
-        <v>8940</v>
+        <v>8850</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2883,7 +2883,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>595.83</v>
+        <v>505.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>10458.906</v>
+        <v>10376.625</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78554</v>
+        <v>0.78503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,17 +2941,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>5.003</v>
+        <v>5.03</v>
       </c>
       <c r="O8" t="n">
-        <v>50030</v>
+        <v>50300</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2963,7 +2963,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12761.8184</v>
+        <v>13031.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39300.5662</v>
+        <v>39487.009</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78554</v>
+        <v>0.78503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,17 +3021,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>553.4299999999999</v>
+        <v>555</v>
       </c>
       <c r="O9" t="n">
-        <v>55343</v>
+        <v>55500</v>
       </c>
       <c r="P9" t="n">
         <v>579.7134</v>
@@ -3043,7 +3043,7 @@
         <v>57971.34</v>
       </c>
       <c r="S9" t="n">
-        <v>-2628.34</v>
+        <v>-2471.34</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>43474.14022</v>
+        <v>43569.165</v>
       </c>
     </row>
     <row r="10">
@@ -3101,17 +3101,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.395</v>
+        <v>7.495</v>
       </c>
       <c r="O10" t="n">
-        <v>8134.5</v>
+        <v>8244.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -3123,7 +3123,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1008.347947</v>
+        <v>-898.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8134.5</v>
+        <v>8244.5</v>
       </c>
     </row>
     <row r="11">
@@ -3181,17 +3181,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>216.44</v>
+        <v>218.75</v>
       </c>
       <c r="O11" t="n">
-        <v>6493.2</v>
+        <v>6562.5</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -3203,7 +3203,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-46</v>
+        <v>23.3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6493.2</v>
+        <v>6562.5</v>
       </c>
     </row>
     <row r="12">
@@ -3261,17 +3261,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>9.9</v>
+        <v>10.06</v>
       </c>
       <c r="O12" t="n">
-        <v>1980</v>
+        <v>2012</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3283,7 +3283,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-248.5</v>
+        <v>-216.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1980</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="13">
@@ -3341,17 +3341,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>318.49</v>
+        <v>317.24</v>
       </c>
       <c r="O13" t="n">
-        <v>63698</v>
+        <v>63448</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3363,7 +3363,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>748.245</v>
+        <v>498.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>63698</v>
+        <v>63448</v>
       </c>
     </row>
     <row r="14">
@@ -3421,17 +3421,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>60.65</v>
+        <v>61.53</v>
       </c>
       <c r="O14" t="n">
-        <v>9704</v>
+        <v>9844.799999999999</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3443,7 +3443,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>71.56</v>
+        <v>212.36</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9704</v>
+        <v>9844.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -3501,17 +3501,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>71.93000000000001</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>1211.65</v>
+        <v>1199.52</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3523,7 +3523,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>862.603421</v>
+        <v>850.473421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1211.65</v>
+        <v>1199.52</v>
       </c>
     </row>
     <row r="16">
@@ -3581,17 +3581,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.5276</v>
+        <v>27.9615</v>
       </c>
       <c r="O16" t="n">
-        <v>10598.13</v>
+        <v>10765.18</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3603,7 +3603,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>589.224112</v>
+        <v>756.2741119999999</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10598.13</v>
+        <v>10765.18</v>
       </c>
     </row>
     <row r="17">
@@ -3661,17 +3661,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>600</v>
       </c>
       <c r="N17" t="n">
-        <v>173.42</v>
+        <v>174.26</v>
       </c>
       <c r="O17" t="n">
-        <v>104052</v>
+        <v>104556</v>
       </c>
       <c r="P17" t="n">
         <v>172.9987895</v>
@@ -3683,7 +3683,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S17" t="n">
-        <v>252.7263</v>
+        <v>756.7263</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>104052</v>
+        <v>104556</v>
       </c>
     </row>
     <row r="18">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>24.8275</v>
+        <v>24.671</v>
       </c>
       <c r="O18" t="n">
-        <v>4965.5</v>
+        <v>4934.2</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3773,7 +3773,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>260.0975</v>
+        <v>228.7975</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>4965.5</v>
+        <v>4934.2</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>20.4</v>
+        <v>20.73</v>
       </c>
       <c r="O19" t="n">
-        <v>4080</v>
+        <v>4146</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3863,7 +3863,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>52.9825</v>
+        <v>118.9825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>4080</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="20">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>5.35</v>
       </c>
       <c r="O20" t="n">
-        <v>-1220</v>
+        <v>-1070</v>
       </c>
       <c r="P20" t="n">
         <v>5.1653811</v>
@@ -3953,7 +3953,7 @@
         <v>-1033.07622</v>
       </c>
       <c r="S20" t="n">
-        <v>-186.92378</v>
+        <v>-36.92378</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1220</v>
+        <v>-1070</v>
       </c>
     </row>
     <row r="21">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2356</v>
+        <v>6.1885</v>
       </c>
       <c r="O21" t="n">
-        <v>-1247.12</v>
+        <v>-1237.7</v>
       </c>
       <c r="P21" t="n">
         <v>6.3929546</v>
@@ -4043,7 +4043,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S21" t="n">
-        <v>31.47092</v>
+        <v>40.89092</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1247.12</v>
+        <v>-1237.7</v>
       </c>
     </row>
     <row r="22">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="O22" t="n">
-        <v>-1350</v>
+        <v>-1376</v>
       </c>
       <c r="P22" t="n">
         <v>7.3496796</v>
@@ -4133,7 +4133,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S22" t="n">
-        <v>119.93592</v>
+        <v>93.93592</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1350</v>
+        <v>-1376</v>
       </c>
     </row>
   </sheetData>
@@ -4193,17 +4193,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$283,391.20</t>
+          <t>$285,661.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$152,266.59</t>
+          <t>$152,306.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$435,657.79</t>
+          <t>$437,967.50</t>
         </is>
       </c>
     </row>
@@ -4215,17 +4215,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$454,472.72</t>
+          <t>$457,533.36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$97,049.18</t>
+          <t>$97,075.64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$551,521.89</t>
+          <t>$554,609.00</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$737,863.92</t>
+          <t>$743,194.37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$249,315.77</t>
+          <t>$249,382.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$987,179.68</t>
+          <t>$992,576.50</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-10 23:47:31</t>
+          <t>2026-04-11 23:47:17</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -4301,7 +4301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-11 23:47:17</t>
+          <t>2026-04-12 23:47:07</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -4301,7 +4301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-12 23:47:07</t>
+          <t>2026-04-13 23:48:42</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2672</v>
+        <v>1.2757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>399.55</v>
+        <v>398.9</v>
       </c>
       <c r="O2" t="n">
-        <v>27968.5</v>
+        <v>27923</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>127.587595</v>
+        <v>82.08759499999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35441.6832</v>
+        <v>35621.3711</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2672</v>
+        <v>1.2757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>66.23999999999999</v>
+        <v>65.83</v>
       </c>
       <c r="O3" t="n">
-        <v>13248</v>
+        <v>13166</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>173.573333</v>
+        <v>91.57333300000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>16787.8656</v>
+        <v>16795.8662</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1465</v>
+        <v>0.14667</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.12</v>
+        <v>31.3</v>
       </c>
       <c r="O4" t="n">
-        <v>62240</v>
+        <v>62600</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-1172.49376</v>
+        <v>-812.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9118.16</v>
+        <v>9181.541999999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1725</v>
+        <v>1.1759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.147</v>
+        <v>4.129</v>
       </c>
       <c r="O5" t="n">
-        <v>8294</v>
+        <v>8258</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1030.66</v>
+        <v>-1066.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9724.715</v>
+        <v>9710.582199999999</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1725</v>
+        <v>1.1759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="O6" t="n">
-        <v>8850</v>
+        <v>9210</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>505.83</v>
+        <v>865.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10376.625</v>
+        <v>10830.039</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78503</v>
+        <v>0.7854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>40240</v>
+        <v>40000</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2928.77315</v>
+        <v>2688.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31589.6072</v>
+        <v>31416</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78503</v>
+        <v>0.7854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>555</v>
+        <v>553.01</v>
       </c>
       <c r="O8" t="n">
-        <v>55500</v>
+        <v>55301</v>
       </c>
       <c r="P8" t="n">
         <v>579.71400048</v>
@@ -1087,7 +1087,7 @@
         <v>57971.400048</v>
       </c>
       <c r="S8" t="n">
-        <v>-2471.400048</v>
+        <v>-2670.400048</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>43569.165</v>
+        <v>43433.4054</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.495</v>
+        <v>7.465</v>
       </c>
       <c r="O9" t="n">
-        <v>7495</v>
+        <v>7465</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-816.237657</v>
+        <v>-846.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7495</v>
+        <v>7465</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>218.75</v>
+        <v>217.38</v>
       </c>
       <c r="O10" t="n">
-        <v>6562.5</v>
+        <v>6521.4</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>19.4</v>
+        <v>-21.7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6562.5</v>
+        <v>6521.4</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.06</v>
+        <v>10.07</v>
       </c>
       <c r="O11" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>61.53</v>
+        <v>61.06</v>
       </c>
       <c r="O12" t="n">
-        <v>9844.799999999999</v>
+        <v>9769.6</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>268.14</v>
+        <v>192.94</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9844.799999999999</v>
+        <v>9769.6</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>27.9615</v>
+        <v>27.7328</v>
       </c>
       <c r="O13" t="n">
-        <v>10765.18</v>
+        <v>10677.13</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>750.277178</v>
+        <v>662.227178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10765.18</v>
+        <v>10677.13</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>85.92</v>
+        <v>86.41</v>
       </c>
       <c r="O14" t="n">
-        <v>3436.8</v>
+        <v>3456.4</v>
       </c>
       <c r="P14" t="n">
         <v>102.0775</v>
@@ -1567,7 +1567,7 @@
         <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-646.3</v>
+        <v>-626.7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3436.8</v>
+        <v>3456.4</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>500</v>
       </c>
       <c r="N15" t="n">
-        <v>174.26</v>
+        <v>173.84</v>
       </c>
       <c r="O15" t="n">
-        <v>87130</v>
+        <v>86920</v>
       </c>
       <c r="P15" t="n">
         <v>172.83405384</v>
@@ -1647,7 +1647,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S15" t="n">
-        <v>712.97308</v>
+        <v>502.97308</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>87130</v>
+        <v>86920</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>24.671</v>
+        <v>22.635</v>
       </c>
       <c r="O16" t="n">
-        <v>4934.2</v>
+        <v>4527</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>242.1</v>
+        <v>-165.1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>4934.2</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>20.73</v>
+        <v>18.745</v>
       </c>
       <c r="O17" t="n">
-        <v>4146</v>
+        <v>3749</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>118.5025</v>
+        <v>-278.4975</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>4146</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="18">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>10.9359</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>-1093.59</v>
+        <v>-900</v>
       </c>
       <c r="P18" t="n">
         <v>19.9890756</v>
@@ -1917,7 +1917,7 @@
         <v>-1998.90756</v>
       </c>
       <c r="S18" t="n">
-        <v>905.31756</v>
+        <v>1098.90756</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-1093.59</v>
+        <v>-900</v>
       </c>
     </row>
     <row r="19">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>16.6</v>
+        <v>11.45</v>
       </c>
       <c r="O19" t="n">
-        <v>-1660</v>
+        <v>-1145</v>
       </c>
       <c r="P19" t="n">
         <v>12.80919851</v>
@@ -2007,7 +2007,7 @@
         <v>-1280.919851</v>
       </c>
       <c r="S19" t="n">
-        <v>-379.080149</v>
+        <v>135.919851</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-1660</v>
+        <v>-1145</v>
       </c>
     </row>
     <row r="20">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>-900</v>
+        <v>-860</v>
       </c>
       <c r="P20" t="n">
         <v>6.9928434</v>
@@ -2097,7 +2097,7 @@
         <v>-1398.56868</v>
       </c>
       <c r="S20" t="n">
-        <v>498.56868</v>
+        <v>538.56868</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-900</v>
+        <v>-860</v>
       </c>
     </row>
     <row r="21">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>6.1885</v>
+        <v>5.6442</v>
       </c>
       <c r="O21" t="n">
-        <v>-1237.7</v>
+        <v>-1128.84</v>
       </c>
       <c r="P21" t="n">
         <v>6.3644671</v>
@@ -2187,7 +2187,7 @@
         <v>-1272.89342</v>
       </c>
       <c r="S21" t="n">
-        <v>35.19342</v>
+        <v>144.05342</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1237.7</v>
+        <v>-1128.84</v>
       </c>
     </row>
     <row r="22">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>6.88</v>
+        <v>6.285</v>
       </c>
       <c r="O22" t="n">
-        <v>-1376</v>
+        <v>-1257</v>
       </c>
       <c r="P22" t="n">
         <v>7.3548796</v>
@@ -2277,7 +2277,7 @@
         <v>-1470.97592</v>
       </c>
       <c r="S22" t="n">
-        <v>94.97592</v>
+        <v>213.97592</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1376</v>
+        <v>-1257</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2672</v>
+        <v>1.2757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,17 +2461,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>399.55</v>
+        <v>398.9</v>
       </c>
       <c r="O2" t="n">
-        <v>35959.5</v>
+        <v>35901</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2483,7 +2483,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>-103.441488</v>
+        <v>-161.941488</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>45567.8784</v>
+        <v>45798.9057</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2672</v>
+        <v>1.2757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,17 +2541,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>66.23999999999999</v>
+        <v>65.83</v>
       </c>
       <c r="O3" t="n">
-        <v>19872</v>
+        <v>19749</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2563,7 +2563,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>143.1405</v>
+        <v>20.1405</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>25181.7984</v>
+        <v>25193.7993</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1465</v>
+        <v>0.14667</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,17 +2621,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.12</v>
+        <v>31.3</v>
       </c>
       <c r="O4" t="n">
-        <v>62240</v>
+        <v>62600</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2643,7 +2643,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-1152.47719</v>
+        <v>-792.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9118.16</v>
+        <v>9181.541999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1725</v>
+        <v>1.1759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.147</v>
+        <v>4.129</v>
       </c>
       <c r="O5" t="n">
-        <v>12441</v>
+        <v>12387</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2723,7 +2723,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1534.239091</v>
+        <v>-1588.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14587.0725</v>
+        <v>14565.8733</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1725</v>
+        <v>1.1759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,17 +2781,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>49.14</v>
+        <v>48.24</v>
       </c>
       <c r="O6" t="n">
-        <v>49140</v>
+        <v>48240</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2803,7 +2803,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>6130</v>
+        <v>5230</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>57616.65</v>
+        <v>56725.416</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1725</v>
+        <v>1.1759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,17 +2861,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="O7" t="n">
-        <v>8850</v>
+        <v>9210</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2883,7 +2883,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>505.83</v>
+        <v>865.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>10376.625</v>
+        <v>10830.039</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78503</v>
+        <v>0.7854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,17 +2941,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>50300</v>
+        <v>50000</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2963,7 +2963,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>13031.8184</v>
+        <v>12731.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39487.009</v>
+        <v>39270</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78503</v>
+        <v>0.7854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,17 +3021,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>555</v>
+        <v>553.01</v>
       </c>
       <c r="O9" t="n">
-        <v>55500</v>
+        <v>55301</v>
       </c>
       <c r="P9" t="n">
         <v>579.7134</v>
@@ -3043,7 +3043,7 @@
         <v>57971.34</v>
       </c>
       <c r="S9" t="n">
-        <v>-2471.34</v>
+        <v>-2670.34</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>43569.165</v>
+        <v>43433.4054</v>
       </c>
     </row>
     <row r="10">
@@ -3101,17 +3101,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.495</v>
+        <v>7.465</v>
       </c>
       <c r="O10" t="n">
-        <v>8244.5</v>
+        <v>8211.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -3123,7 +3123,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-898.347947</v>
+        <v>-931.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8244.5</v>
+        <v>8211.5</v>
       </c>
     </row>
     <row r="11">
@@ -3181,17 +3181,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>218.75</v>
+        <v>217.38</v>
       </c>
       <c r="O11" t="n">
-        <v>6562.5</v>
+        <v>6521.4</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -3203,7 +3203,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>23.3</v>
+        <v>-17.8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6562.5</v>
+        <v>6521.4</v>
       </c>
     </row>
     <row r="12">
@@ -3261,17 +3261,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>10.06</v>
+        <v>10.07</v>
       </c>
       <c r="O12" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3283,7 +3283,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-216.5</v>
+        <v>-214.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="13">
@@ -3341,17 +3341,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>317.24</v>
+        <v>321.31</v>
       </c>
       <c r="O13" t="n">
-        <v>63448</v>
+        <v>64262</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3363,7 +3363,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>498.245</v>
+        <v>1312.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>63448</v>
+        <v>64262</v>
       </c>
     </row>
     <row r="14">
@@ -3421,17 +3421,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>61.53</v>
+        <v>61.06</v>
       </c>
       <c r="O14" t="n">
-        <v>9844.799999999999</v>
+        <v>9769.6</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3443,7 +3443,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>212.36</v>
+        <v>137.16</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9844.799999999999</v>
+        <v>9769.6</v>
       </c>
     </row>
     <row r="15">
@@ -3501,17 +3501,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>71.20999999999999</v>
+        <v>74.55</v>
       </c>
       <c r="O15" t="n">
-        <v>1199.52</v>
+        <v>1255.78</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3523,7 +3523,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>850.473421</v>
+        <v>906.733421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1199.52</v>
+        <v>1255.78</v>
       </c>
     </row>
     <row r="16">
@@ -3581,17 +3581,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.9615</v>
+        <v>27.7328</v>
       </c>
       <c r="O16" t="n">
-        <v>10765.18</v>
+        <v>10677.13</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3603,7 +3603,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>756.2741119999999</v>
+        <v>668.224112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10765.18</v>
+        <v>10677.13</v>
       </c>
     </row>
     <row r="17">
@@ -3661,17 +3661,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>600</v>
       </c>
       <c r="N17" t="n">
-        <v>174.26</v>
+        <v>173.84</v>
       </c>
       <c r="O17" t="n">
-        <v>104556</v>
+        <v>104304</v>
       </c>
       <c r="P17" t="n">
         <v>172.9987895</v>
@@ -3683,7 +3683,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S17" t="n">
-        <v>756.7263</v>
+        <v>504.7263</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>104556</v>
+        <v>104304</v>
       </c>
     </row>
     <row r="18">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>24.671</v>
+        <v>22.635</v>
       </c>
       <c r="O18" t="n">
-        <v>4934.2</v>
+        <v>4527</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3773,7 +3773,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>228.7975</v>
+        <v>-178.4025</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>4934.2</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>20.73</v>
+        <v>18.745</v>
       </c>
       <c r="O19" t="n">
-        <v>4146</v>
+        <v>3749</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3863,7 +3863,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>118.9825</v>
+        <v>-278.0175</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>4146</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="20">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>5.35</v>
+        <v>6.3722</v>
       </c>
       <c r="O20" t="n">
-        <v>-1070</v>
+        <v>-1274.44</v>
       </c>
       <c r="P20" t="n">
         <v>5.1653811</v>
@@ -3953,7 +3953,7 @@
         <v>-1033.07622</v>
       </c>
       <c r="S20" t="n">
-        <v>-36.92378</v>
+        <v>-241.36378</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1070</v>
+        <v>-1274.44</v>
       </c>
     </row>
     <row r="21">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>6.1885</v>
+        <v>5.6442</v>
       </c>
       <c r="O21" t="n">
-        <v>-1237.7</v>
+        <v>-1128.84</v>
       </c>
       <c r="P21" t="n">
         <v>6.3929546</v>
@@ -4043,7 +4043,7 @@
         <v>-1278.59092</v>
       </c>
       <c r="S21" t="n">
-        <v>40.89092</v>
+        <v>149.75092</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-1237.7</v>
+        <v>-1128.84</v>
       </c>
     </row>
     <row r="22">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>-2</v>
       </c>
       <c r="N22" t="n">
-        <v>6.88</v>
+        <v>6.285</v>
       </c>
       <c r="O22" t="n">
-        <v>-1376</v>
+        <v>-1257</v>
       </c>
       <c r="P22" t="n">
         <v>7.3496796</v>
@@ -4133,7 +4133,7 @@
         <v>-1469.93592</v>
       </c>
       <c r="S22" t="n">
-        <v>93.93592</v>
+        <v>212.93592</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>-1376</v>
+        <v>-1257</v>
       </c>
     </row>
   </sheetData>
@@ -4193,17 +4193,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$285,661.01</t>
+          <t>$285,790.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$152,306.49</t>
+          <t>$152,526.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$437,967.50</t>
+          <t>$438,316.98</t>
         </is>
       </c>
     </row>
@@ -4215,17 +4215,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$457,533.36</t>
+          <t>$456,630.11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$97,075.64</t>
+          <t>$97,317.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$554,609.00</t>
+          <t>$553,947.33</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$743,194.37</t>
+          <t>$742,420.61</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$249,382.13</t>
+          <t>$249,843.70</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$992,576.50</t>
+          <t>$992,264.31</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13 23:48:42</t>
+          <t>2026-04-14 23:48:22</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2757</v>
+        <v>1.2806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>398.9</v>
+        <v>407.35</v>
       </c>
       <c r="O2" t="n">
-        <v>27923</v>
+        <v>28514.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>82.08759499999999</v>
+        <v>673.587595</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35621.3711</v>
+        <v>36515.6687</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2757</v>
+        <v>1.2806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>65.83</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>13166</v>
+        <v>13402</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>91.57333300000001</v>
+        <v>327.573333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>16795.8662</v>
+        <v>17162.6012</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14667</v>
+        <v>0.14683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.3</v>
+        <v>31.64</v>
       </c>
       <c r="O4" t="n">
-        <v>62600</v>
+        <v>63280</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-812.49376</v>
+        <v>-132.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9181.541999999999</v>
+        <v>9291.402399999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1759</v>
+        <v>1.1796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.129</v>
+        <v>4.2065</v>
       </c>
       <c r="O5" t="n">
-        <v>8258</v>
+        <v>8413</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-1066.66</v>
+        <v>-911.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9710.582199999999</v>
+        <v>9923.9748</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1759</v>
+        <v>1.1796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>614</v>
+        <v>656</v>
       </c>
       <c r="O6" t="n">
-        <v>9210</v>
+        <v>9840</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>865.83</v>
+        <v>1495.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>10830.039</v>
+        <v>11607.264</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7854</v>
+        <v>0.78643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="O7" t="n">
-        <v>40000</v>
+        <v>40320</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2688.77315</v>
+        <v>3008.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31416</v>
+        <v>31708.8576</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7854</v>
+        <v>0.78643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>553.01</v>
+        <v>559.2</v>
       </c>
       <c r="O8" t="n">
-        <v>55301</v>
+        <v>55920</v>
       </c>
       <c r="P8" t="n">
         <v>579.71400048</v>
@@ -1087,7 +1087,7 @@
         <v>57971.400048</v>
       </c>
       <c r="S8" t="n">
-        <v>-2670.400048</v>
+        <v>-2051.400048</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>43433.4054</v>
+        <v>43977.1656</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.465</v>
+        <v>7.64</v>
       </c>
       <c r="O9" t="n">
-        <v>7465</v>
+        <v>7640</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-846.237657</v>
+        <v>-671.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7465</v>
+        <v>7640</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>217.38</v>
+        <v>219.94</v>
       </c>
       <c r="O10" t="n">
-        <v>6521.4</v>
+        <v>6598.2</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-21.7</v>
+        <v>55.1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6521.4</v>
+        <v>6598.2</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.07</v>
+        <v>10.19</v>
       </c>
       <c r="O11" t="n">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>36.5</v>
+        <v>48.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1007</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>61.06</v>
+        <v>62.64</v>
       </c>
       <c r="O12" t="n">
-        <v>9769.6</v>
+        <v>10022.4</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>192.94</v>
+        <v>445.74</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9769.6</v>
+        <v>10022.4</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>27.7328</v>
+        <v>28.926</v>
       </c>
       <c r="O13" t="n">
-        <v>10677.13</v>
+        <v>11136.51</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>662.227178</v>
+        <v>1121.607178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>10677.13</v>
+        <v>11136.51</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>86.41</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>3456.4</v>
+        <v>3424</v>
       </c>
       <c r="P14" t="n">
         <v>102.0775</v>
@@ -1567,7 +1567,7 @@
         <v>4083.1</v>
       </c>
       <c r="S14" t="n">
-        <v>-626.7</v>
+        <v>-659.1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3456.4</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>500</v>
       </c>
       <c r="N15" t="n">
-        <v>173.84</v>
+        <v>177.3</v>
       </c>
       <c r="O15" t="n">
-        <v>86920</v>
+        <v>88650</v>
       </c>
       <c r="P15" t="n">
         <v>172.83405384</v>
@@ -1647,7 +1647,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S15" t="n">
-        <v>502.97308</v>
+        <v>2232.97308</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>86920</v>
+        <v>88650</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>22.635</v>
+        <v>20.4616</v>
       </c>
       <c r="O16" t="n">
-        <v>4527</v>
+        <v>4092.32</v>
       </c>
       <c r="P16" t="n">
         <v>23.4605</v>
@@ -1737,7 +1737,7 @@
         <v>4692.1</v>
       </c>
       <c r="S16" t="n">
-        <v>-165.1</v>
+        <v>-599.78</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>4527</v>
+        <v>4092.32</v>
       </c>
     </row>
     <row r="17">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>18.745</v>
+        <v>17.42</v>
       </c>
       <c r="O17" t="n">
-        <v>3749</v>
+        <v>3484</v>
       </c>
       <c r="P17" t="n">
         <v>20.1374875</v>
@@ -1827,7 +1827,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S17" t="n">
-        <v>-278.4975</v>
+        <v>-543.4974999999999</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>3749</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="18">
@@ -1869,19 +1869,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>META  260522P00565000</t>
+          <t>MSFT  260522P00370000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>META 22MAY26 565 P</t>
+          <t>MSFT 22MAY26 370 P</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>565</v>
+        <v>370</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1895,29 +1895,29 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>-1</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="O18" t="n">
-        <v>-900</v>
+        <v>-890</v>
       </c>
       <c r="P18" t="n">
-        <v>19.9890756</v>
+        <v>12.80919851</v>
       </c>
       <c r="Q18" t="n">
-        <v>19.9890756</v>
+        <v>12.80919851</v>
       </c>
       <c r="R18" t="n">
-        <v>-1998.90756</v>
+        <v>-1280.919851</v>
       </c>
       <c r="S18" t="n">
-        <v>1098.90756</v>
+        <v>390.919851</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1930,367 +1930,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>-900</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>MSFT  260522P00370000</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MSFT 22MAY26 370 P</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" t="n">
-        <v>370</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-1145</v>
-      </c>
-      <c r="P19" t="n">
-        <v>12.80919851</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>12.80919851</v>
-      </c>
-      <c r="R19" t="n">
-        <v>-1280.919851</v>
-      </c>
-      <c r="S19" t="n">
-        <v>135.919851</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>-1145</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NVDA  260522P00175000</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NVDA 22MAY26 175 P</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" t="n">
-        <v>175</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-860</v>
-      </c>
-      <c r="P20" t="n">
-        <v>6.9928434</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.9928434</v>
-      </c>
-      <c r="R20" t="n">
-        <v>-1398.56868</v>
-      </c>
-      <c r="S20" t="n">
-        <v>538.56868</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>-860</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>QQQ   261218P00425000</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>QQQ 18DEC26 425 P</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>100</v>
-      </c>
-      <c r="I21" t="n">
-        <v>425</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.6442</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-1128.84</v>
-      </c>
-      <c r="P21" t="n">
-        <v>6.3644671</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.3644671</v>
-      </c>
-      <c r="R21" t="n">
-        <v>-1272.89342</v>
-      </c>
-      <c r="S21" t="n">
-        <v>144.05342</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>-1128.84</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I22" t="n">
-        <v>505</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6.285</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-1257</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>7.3548796</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-1470.97592</v>
-      </c>
-      <c r="S22" t="n">
-        <v>213.97592</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>-1257</v>
+        <v>-890</v>
       </c>
     </row>
   </sheetData>
@@ -2304,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,7 +2071,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2757</v>
+        <v>1.2806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2461,17 +2101,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>398.9</v>
+        <v>407.35</v>
       </c>
       <c r="O2" t="n">
-        <v>35901</v>
+        <v>36661.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2483,7 +2123,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>-161.941488</v>
+        <v>598.558512</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2496,7 +2136,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>45798.9057</v>
+        <v>46948.7169</v>
       </c>
     </row>
     <row r="3">
@@ -2511,7 +2151,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2757</v>
+        <v>1.2806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2541,17 +2181,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>65.83</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>19749</v>
+        <v>20103</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2563,7 +2203,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>20.1405</v>
+        <v>374.1405</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2576,7 +2216,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>25193.7993</v>
+        <v>25743.9018</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2231,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14667</v>
+        <v>0.14683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2621,17 +2261,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.3</v>
+        <v>31.64</v>
       </c>
       <c r="O4" t="n">
-        <v>62600</v>
+        <v>63280</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2643,7 +2283,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-792.47719</v>
+        <v>-112.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2656,7 +2296,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9181.541999999999</v>
+        <v>9291.402399999999</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2311,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1759</v>
+        <v>1.1796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2701,17 +2341,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.129</v>
+        <v>4.2065</v>
       </c>
       <c r="O5" t="n">
-        <v>12387</v>
+        <v>12619.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2723,7 +2363,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1588.239091</v>
+        <v>-1355.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2736,7 +2376,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14565.8733</v>
+        <v>14885.9622</v>
       </c>
     </row>
     <row r="6">
@@ -2751,7 +2391,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1759</v>
+        <v>1.1796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2781,17 +2421,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>48.24</v>
+        <v>48.77</v>
       </c>
       <c r="O6" t="n">
-        <v>48240</v>
+        <v>48770</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2803,7 +2443,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>5230</v>
+        <v>5760</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2816,7 +2456,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>56725.416</v>
+        <v>57529.092</v>
       </c>
     </row>
     <row r="7">
@@ -2831,7 +2471,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1759</v>
+        <v>1.1796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2861,17 +2501,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>614</v>
+        <v>656</v>
       </c>
       <c r="O7" t="n">
-        <v>9210</v>
+        <v>9840</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2883,7 +2523,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>865.83</v>
+        <v>1495.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2896,7 +2536,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>10830.039</v>
+        <v>11607.264</v>
       </c>
     </row>
     <row r="8">
@@ -2911,7 +2551,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7854</v>
+        <v>0.78643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2941,17 +2581,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="O8" t="n">
-        <v>50000</v>
+        <v>50400</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2963,7 +2603,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12731.8184</v>
+        <v>13131.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2976,7 +2616,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39270</v>
+        <v>39636.072</v>
       </c>
     </row>
     <row r="9">
@@ -2991,7 +2631,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7854</v>
+        <v>0.78643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3021,17 +2661,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>553.01</v>
+        <v>559.2</v>
       </c>
       <c r="O9" t="n">
-        <v>55301</v>
+        <v>55920</v>
       </c>
       <c r="P9" t="n">
         <v>579.7134</v>
@@ -3043,7 +2683,7 @@
         <v>57971.34</v>
       </c>
       <c r="S9" t="n">
-        <v>-2670.34</v>
+        <v>-2051.34</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3056,7 +2696,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>43433.4054</v>
+        <v>43977.1656</v>
       </c>
     </row>
     <row r="10">
@@ -3101,17 +2741,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.465</v>
+        <v>7.64</v>
       </c>
       <c r="O10" t="n">
-        <v>8211.5</v>
+        <v>8404</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -3123,7 +2763,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-931.347947</v>
+        <v>-738.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3136,7 +2776,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8211.5</v>
+        <v>8404</v>
       </c>
     </row>
     <row r="11">
@@ -3181,17 +2821,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>217.38</v>
+        <v>219.94</v>
       </c>
       <c r="O11" t="n">
-        <v>6521.4</v>
+        <v>6598.2</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -3203,7 +2843,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-17.8</v>
+        <v>59</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3216,7 +2856,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6521.4</v>
+        <v>6598.2</v>
       </c>
     </row>
     <row r="12">
@@ -3261,17 +2901,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>10.07</v>
+        <v>10.19</v>
       </c>
       <c r="O12" t="n">
-        <v>2014</v>
+        <v>2038</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3283,7 +2923,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-214.5</v>
+        <v>-190.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3296,7 +2936,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2014</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="13">
@@ -3341,17 +2981,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>321.31</v>
+        <v>332.91</v>
       </c>
       <c r="O13" t="n">
-        <v>64262</v>
+        <v>66582</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3363,7 +3003,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>1312.245</v>
+        <v>3632.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3376,7 +3016,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>64262</v>
+        <v>66582</v>
       </c>
     </row>
     <row r="14">
@@ -3421,17 +3061,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>61.06</v>
+        <v>62.64</v>
       </c>
       <c r="O14" t="n">
-        <v>9769.6</v>
+        <v>10022.4</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3443,7 +3083,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>137.16</v>
+        <v>389.96</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3456,7 +3096,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9769.6</v>
+        <v>10022.4</v>
       </c>
     </row>
     <row r="15">
@@ -3501,17 +3141,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>74.55</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>1255.78</v>
+        <v>1298.73</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3523,7 +3163,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>906.733421</v>
+        <v>949.683421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3536,7 +3176,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1255.78</v>
+        <v>1298.73</v>
       </c>
     </row>
     <row r="16">
@@ -3581,17 +3221,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>27.7328</v>
+        <v>28.926</v>
       </c>
       <c r="O16" t="n">
-        <v>10677.13</v>
+        <v>11136.51</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3603,7 +3243,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>668.224112</v>
+        <v>1127.604112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3616,7 +3256,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>10677.13</v>
+        <v>11136.51</v>
       </c>
     </row>
     <row r="17">
@@ -3661,17 +3301,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>600</v>
       </c>
       <c r="N17" t="n">
-        <v>173.84</v>
+        <v>177.3</v>
       </c>
       <c r="O17" t="n">
-        <v>104304</v>
+        <v>106380</v>
       </c>
       <c r="P17" t="n">
         <v>172.9987895</v>
@@ -3683,7 +3323,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S17" t="n">
-        <v>504.7263</v>
+        <v>2580.7263</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3696,7 +3336,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>104304</v>
+        <v>106380</v>
       </c>
     </row>
     <row r="18">
@@ -3751,17 +3391,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>22.635</v>
+        <v>20.4616</v>
       </c>
       <c r="O18" t="n">
-        <v>4527</v>
+        <v>4092.32</v>
       </c>
       <c r="P18" t="n">
         <v>23.5270125</v>
@@ -3773,7 +3413,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S18" t="n">
-        <v>-178.4025</v>
+        <v>-613.0825</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3786,7 +3426,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>4527</v>
+        <v>4092.32</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3481,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>18.745</v>
+        <v>17.42</v>
       </c>
       <c r="O19" t="n">
-        <v>3749</v>
+        <v>3484</v>
       </c>
       <c r="P19" t="n">
         <v>20.1350875</v>
@@ -3863,7 +3503,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S19" t="n">
-        <v>-278.0175</v>
+        <v>-543.0175</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3876,7 +3516,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>3749</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="20">
@@ -3931,17 +3571,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>-2</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3722</v>
+        <v>10.6422</v>
       </c>
       <c r="O20" t="n">
-        <v>-1274.44</v>
+        <v>-2128.44</v>
       </c>
       <c r="P20" t="n">
         <v>5.1653811</v>
@@ -3953,7 +3593,7 @@
         <v>-1033.07622</v>
       </c>
       <c r="S20" t="n">
-        <v>-241.36378</v>
+        <v>-1095.36378</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3966,187 +3606,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>-1274.44</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>QQQ   261218P00425000</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>QQQ 18DEC26 425 P</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>100</v>
-      </c>
-      <c r="I21" t="n">
-        <v>425</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.6442</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-1128.84</v>
-      </c>
-      <c r="P21" t="n">
-        <v>6.3929546</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.3929546</v>
-      </c>
-      <c r="R21" t="n">
-        <v>-1278.59092</v>
-      </c>
-      <c r="S21" t="n">
-        <v>149.75092</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>-1128.84</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>U6565621</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SPY   261218P00505000</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SPY 18DEC26 505 P</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>100</v>
-      </c>
-      <c r="I22" t="n">
-        <v>505</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6.285</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-1257</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>7.3496796</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-1469.93592</v>
-      </c>
-      <c r="S22" t="n">
-        <v>212.93592</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>-1257</v>
+        <v>-2128.44</v>
       </c>
     </row>
   </sheetData>
@@ -4193,17 +3653,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$285,790.50</t>
+          <t>$295,363.36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$152,526.48</t>
+          <t>$149,174.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$438,316.98</t>
+          <t>$444,538.30</t>
         </is>
       </c>
     </row>
@@ -4215,17 +3675,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$456,630.11</t>
+          <t>$467,527.30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$97,317.22</t>
+          <t>$95,266.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$553,947.33</t>
+          <t>$562,794.08</t>
         </is>
       </c>
     </row>
@@ -4243,17 +3703,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$742,420.61</t>
+          <t>$762,890.66</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$249,843.70</t>
+          <t>$244,441.71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$992,264.31</t>
+          <t>$1,007,332.37</t>
         </is>
       </c>
     </row>
@@ -4301,14 +3761,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-14 23:48:22</t>
+          <t>2026-04-15 23:48:25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2806</v>
+        <v>1.2788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>407.35</v>
+        <v>412.45</v>
       </c>
       <c r="O2" t="n">
-        <v>28514.5</v>
+        <v>28871.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>673.587595</v>
+        <v>1030.587595</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>36515.6687</v>
+        <v>36920.8742</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2806</v>
+        <v>1.2788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>67.01000000000001</v>
+        <v>67.17</v>
       </c>
       <c r="O3" t="n">
-        <v>13402</v>
+        <v>13434</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>327.573333</v>
+        <v>359.573333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>17162.6012</v>
+        <v>17179.3992</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14683</v>
+        <v>0.14666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.64</v>
+        <v>31.54</v>
       </c>
       <c r="O4" t="n">
-        <v>63280</v>
+        <v>63080</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-132.49376</v>
+        <v>-332.49376</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9291.402399999999</v>
+        <v>9251.312800000002</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1796</v>
+        <v>1.1799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2065</v>
+        <v>4.2045</v>
       </c>
       <c r="O5" t="n">
-        <v>8413</v>
+        <v>8409</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-911.66</v>
+        <v>-915.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9923.9748</v>
+        <v>9921.7791</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1796</v>
+        <v>1.1799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="O6" t="n">
-        <v>9840</v>
+        <v>9810</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1495.83</v>
+        <v>1465.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>11607.264</v>
+        <v>11574.819</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78643</v>
+        <v>0.78677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31708.8576</v>
+        <v>31722.5664</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78643</v>
+        <v>0.78677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>559.2</v>
+        <v>562.2</v>
       </c>
       <c r="O8" t="n">
-        <v>55920</v>
+        <v>56220</v>
       </c>
       <c r="P8" t="n">
         <v>579.71400048</v>
@@ -1087,7 +1087,7 @@
         <v>57971.400048</v>
       </c>
       <c r="S8" t="n">
-        <v>-2051.400048</v>
+        <v>-1751.400048</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>43977.1656</v>
+        <v>44232.2094</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.64</v>
+        <v>7.53</v>
       </c>
       <c r="O9" t="n">
-        <v>7640</v>
+        <v>7530</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-671.237657</v>
+        <v>-781.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7640</v>
+        <v>7530</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>219.94</v>
+        <v>214.4</v>
       </c>
       <c r="O10" t="n">
-        <v>6598.2</v>
+        <v>6432</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>55.1</v>
+        <v>-111.1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6598.2</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.19</v>
+        <v>10.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>48.5</v>
+        <v>59.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1019</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>62.64</v>
+        <v>62.02</v>
       </c>
       <c r="O12" t="n">
-        <v>10022.4</v>
+        <v>9923.200000000001</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>445.74</v>
+        <v>346.54</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>10022.4</v>
+        <v>9923.200000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>28.926</v>
+        <v>29.0932</v>
       </c>
       <c r="O13" t="n">
-        <v>11136.51</v>
+        <v>11200.88</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>1121.607178</v>
+        <v>1185.977178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>11136.51</v>
+        <v>11200.88</v>
       </c>
     </row>
     <row r="14">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ADR</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SEA LTD-ADR</t>
+          <t>NEWMONT CORP</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1545,29 +1545,29 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>85.59999999999999</v>
+        <v>113.04</v>
       </c>
       <c r="O14" t="n">
-        <v>3424</v>
+        <v>5652</v>
       </c>
       <c r="P14" t="n">
-        <v>102.0775</v>
+        <v>114.135</v>
       </c>
       <c r="Q14" t="n">
-        <v>102.0775</v>
+        <v>114.135</v>
       </c>
       <c r="R14" t="n">
-        <v>4083.1</v>
+        <v>5706.75</v>
       </c>
       <c r="S14" t="n">
-        <v>-659.1</v>
+        <v>-54.75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3424</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="15">
@@ -1604,17 +1604,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>SEA LTD-ADR</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1625,29 +1625,29 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="N15" t="n">
-        <v>177.3</v>
+        <v>90.33</v>
       </c>
       <c r="O15" t="n">
-        <v>88650</v>
+        <v>3613.2</v>
       </c>
       <c r="P15" t="n">
-        <v>172.83405384</v>
+        <v>102.0775</v>
       </c>
       <c r="Q15" t="n">
-        <v>172.83405384</v>
+        <v>102.0775</v>
       </c>
       <c r="R15" t="n">
-        <v>86417.02692</v>
+        <v>4083.1</v>
       </c>
       <c r="S15" t="n">
-        <v>2232.97308</v>
+        <v>-469.9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1656,11 +1656,11 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>88650</v>
+        <v>3613.2</v>
       </c>
     </row>
     <row r="16">
@@ -1679,65 +1679,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OPT</t>
+          <t>STK</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>QQQ   261218P00560000</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 560 P</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
-      </c>
-      <c r="I16" t="n">
-        <v>560</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="N16" t="n">
-        <v>20.4616</v>
+        <v>177.9</v>
       </c>
       <c r="O16" t="n">
-        <v>4092.32</v>
+        <v>88950</v>
       </c>
       <c r="P16" t="n">
-        <v>23.4605</v>
+        <v>172.83405384</v>
       </c>
       <c r="Q16" t="n">
-        <v>23.4605</v>
+        <v>172.83405384</v>
       </c>
       <c r="R16" t="n">
-        <v>4692.1</v>
+        <v>86417.02692</v>
       </c>
       <c r="S16" t="n">
-        <v>-599.78</v>
+        <v>2532.97308</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1746,11 +1736,11 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>4092.32</v>
+        <v>88950</v>
       </c>
     </row>
     <row r="17">
@@ -1779,19 +1769,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SPY   261218P00620000</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 620 P</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>620</v>
+        <v>560</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1805,29 +1795,29 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>17.42</v>
+        <v>19.3755</v>
       </c>
       <c r="O17" t="n">
-        <v>3484</v>
+        <v>3875.1</v>
       </c>
       <c r="P17" t="n">
-        <v>20.1374875</v>
+        <v>23.4605</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.1374875</v>
+        <v>23.4605</v>
       </c>
       <c r="R17" t="n">
-        <v>4027.4975</v>
+        <v>4692.1</v>
       </c>
       <c r="S17" t="n">
-        <v>-543.4974999999999</v>
+        <v>-817</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1840,7 +1830,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>3484</v>
+        <v>3875.1</v>
       </c>
     </row>
     <row r="18">
@@ -1869,68 +1859,158 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MSFT  260522P00370000</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MSFT 22MAY26 370 P</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
+        <v>620</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>16.645</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3329</v>
+      </c>
+      <c r="P18" t="n">
+        <v>20.1374875</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>20.1374875</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4027.4975</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-698.4974999999999</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>U2739721</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MSFT  260522P00370000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MSFT 22MAY26 370 P</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" t="n">
         <v>370</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
         <v>-1</v>
       </c>
-      <c r="N18" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-890</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="N19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-525</v>
+      </c>
+      <c r="P19" t="n">
         <v>12.80919851</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>12.80919851</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>-1280.919851</v>
       </c>
-      <c r="S18" t="n">
-        <v>390.919851</v>
-      </c>
-      <c r="T18" t="inlineStr">
+      <c r="S19" t="n">
+        <v>755.919851</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="V18" t="n">
-        <v>-890</v>
+      <c r="V19" t="n">
+        <v>-525</v>
       </c>
     </row>
   </sheetData>
@@ -1944,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2071,7 +2151,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2806</v>
+        <v>1.2788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2101,17 +2181,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>407.35</v>
+        <v>412.45</v>
       </c>
       <c r="O2" t="n">
-        <v>36661.5</v>
+        <v>37120.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2123,7 +2203,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>598.558512</v>
+        <v>1057.558512</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2136,7 +2216,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>46948.7169</v>
+        <v>47469.6954</v>
       </c>
     </row>
     <row r="3">
@@ -2151,7 +2231,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2806</v>
+        <v>1.2788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2181,17 +2261,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>67.01000000000001</v>
+        <v>67.17</v>
       </c>
       <c r="O3" t="n">
-        <v>20103</v>
+        <v>20151</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2203,7 +2283,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>374.1405</v>
+        <v>422.1405</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2216,7 +2296,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>25743.9018</v>
+        <v>25769.0988</v>
       </c>
     </row>
     <row r="4">
@@ -2231,7 +2311,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14683</v>
+        <v>0.14666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2261,17 +2341,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.64</v>
+        <v>31.54</v>
       </c>
       <c r="O4" t="n">
-        <v>63280</v>
+        <v>63080</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2283,7 +2363,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-112.47719</v>
+        <v>-312.47719</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2296,7 +2376,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9291.402399999999</v>
+        <v>9251.312800000002</v>
       </c>
     </row>
     <row r="5">
@@ -2311,7 +2391,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1796</v>
+        <v>1.1799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2341,17 +2421,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2065</v>
+        <v>4.2045</v>
       </c>
       <c r="O5" t="n">
-        <v>12619.5</v>
+        <v>12613.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2363,7 +2443,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1355.739091</v>
+        <v>-1361.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2376,7 +2456,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14885.9622</v>
+        <v>14882.66865</v>
       </c>
     </row>
     <row r="6">
@@ -2391,7 +2471,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1796</v>
+        <v>1.1799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2421,17 +2501,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>48.77</v>
+        <v>48.2</v>
       </c>
       <c r="O6" t="n">
-        <v>48770</v>
+        <v>48200</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2443,7 +2523,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>5760</v>
+        <v>5190</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2456,7 +2536,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>57529.092</v>
+        <v>56871.18</v>
       </c>
     </row>
     <row r="7">
@@ -2471,7 +2551,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1796</v>
+        <v>1.1799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2501,17 +2581,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="O7" t="n">
-        <v>9840</v>
+        <v>9810</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2523,7 +2603,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>1495.83</v>
+        <v>1465.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2536,7 +2616,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>11607.264</v>
+        <v>11574.819</v>
       </c>
     </row>
     <row r="8">
@@ -2551,7 +2631,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78643</v>
+        <v>0.78677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2581,7 +2661,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2616,7 +2696,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39636.072</v>
+        <v>39653.208</v>
       </c>
     </row>
     <row r="9">
@@ -2631,7 +2711,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78643</v>
+        <v>0.78677</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2661,17 +2741,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>559.2</v>
+        <v>562.2</v>
       </c>
       <c r="O9" t="n">
-        <v>55920</v>
+        <v>56220</v>
       </c>
       <c r="P9" t="n">
         <v>579.7134</v>
@@ -2683,7 +2763,7 @@
         <v>57971.34</v>
       </c>
       <c r="S9" t="n">
-        <v>-2051.34</v>
+        <v>-1751.34</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2696,7 +2776,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>43977.1656</v>
+        <v>44232.2094</v>
       </c>
     </row>
     <row r="10">
@@ -2741,17 +2821,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.64</v>
+        <v>7.53</v>
       </c>
       <c r="O10" t="n">
-        <v>8404</v>
+        <v>8283</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -2763,7 +2843,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-738.847947</v>
+        <v>-859.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2776,7 +2856,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8404</v>
+        <v>8283</v>
       </c>
     </row>
     <row r="11">
@@ -2821,17 +2901,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>219.94</v>
+        <v>214.4</v>
       </c>
       <c r="O11" t="n">
-        <v>6598.2</v>
+        <v>6432</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -2843,7 +2923,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>59</v>
+        <v>-107.2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2856,7 +2936,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6598.2</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="12">
@@ -2901,17 +2981,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>10.19</v>
+        <v>10.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2038</v>
+        <v>2060</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -2923,7 +3003,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-190.5</v>
+        <v>-168.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2936,7 +3016,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2038</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="13">
@@ -2981,17 +3061,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>332.91</v>
+        <v>337.12</v>
       </c>
       <c r="O13" t="n">
-        <v>66582</v>
+        <v>67424</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3003,7 +3083,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>3632.245</v>
+        <v>4474.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3016,7 +3096,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>66582</v>
+        <v>67424</v>
       </c>
     </row>
     <row r="14">
@@ -3061,17 +3141,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>62.64</v>
+        <v>62.02</v>
       </c>
       <c r="O14" t="n">
-        <v>10022.4</v>
+        <v>9923.200000000001</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3083,7 +3163,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>389.96</v>
+        <v>290.76</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3096,7 +3176,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10022.4</v>
+        <v>9923.200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -3141,17 +3221,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>77.09999999999999</v>
+        <v>79.69</v>
       </c>
       <c r="O15" t="n">
-        <v>1298.73</v>
+        <v>1342.36</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3163,7 +3243,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>949.683421</v>
+        <v>993.3134209999999</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3176,7 +3256,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1298.73</v>
+        <v>1342.36</v>
       </c>
     </row>
     <row r="16">
@@ -3221,17 +3301,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>28.926</v>
+        <v>29.0932</v>
       </c>
       <c r="O16" t="n">
-        <v>11136.51</v>
+        <v>11200.88</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3243,7 +3323,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>1127.604112</v>
+        <v>1191.974112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3256,7 +3336,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>11136.51</v>
+        <v>11200.88</v>
       </c>
     </row>
     <row r="17">
@@ -3280,17 +3360,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VWRA</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>VANG FTSE AW USDA</t>
+          <t>NEWMONT CORP</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -3301,29 +3381,29 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>177.3</v>
+        <v>113.04</v>
       </c>
       <c r="O17" t="n">
-        <v>106380</v>
+        <v>5652</v>
       </c>
       <c r="P17" t="n">
-        <v>172.9987895</v>
+        <v>114.119</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.9987895</v>
+        <v>114.119</v>
       </c>
       <c r="R17" t="n">
-        <v>103799.2737</v>
+        <v>5705.95</v>
       </c>
       <c r="S17" t="n">
-        <v>2580.7263</v>
+        <v>-53.95</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3332,11 +3412,11 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>LSEETF</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>106380</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="18">
@@ -3355,65 +3435,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OPT</t>
+          <t>STK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>QQQ   261218P00560000</t>
+          <t>VWRA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>QQQ 18DEC26 560 P</t>
+          <t>VANG FTSE AW USDA</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" t="n">
-        <v>560</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="N18" t="n">
-        <v>20.4616</v>
+        <v>177.9</v>
       </c>
       <c r="O18" t="n">
-        <v>4092.32</v>
+        <v>106740</v>
       </c>
       <c r="P18" t="n">
-        <v>23.5270125</v>
+        <v>172.9987895</v>
       </c>
       <c r="Q18" t="n">
-        <v>23.5270125</v>
+        <v>172.9987895</v>
       </c>
       <c r="R18" t="n">
-        <v>4705.4025</v>
+        <v>103799.2737</v>
       </c>
       <c r="S18" t="n">
-        <v>-613.0825</v>
+        <v>2940.7263</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3422,11 +3492,11 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>LSEETF</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>4092.32</v>
+        <v>106740</v>
       </c>
     </row>
     <row r="19">
@@ -3455,19 +3525,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SPY   261218P00620000</t>
+          <t>QQQ   261218P00560000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SPY 18DEC26 620 P</t>
+          <t>QQQ 18DEC26 560 P</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>620</v>
+        <v>560</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -3481,29 +3551,29 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>17.42</v>
+        <v>19.3755</v>
       </c>
       <c r="O19" t="n">
-        <v>3484</v>
+        <v>3875.1</v>
       </c>
       <c r="P19" t="n">
-        <v>20.1350875</v>
+        <v>23.5270125</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.1350875</v>
+        <v>23.5270125</v>
       </c>
       <c r="R19" t="n">
-        <v>4027.0175</v>
+        <v>4705.4025</v>
       </c>
       <c r="S19" t="n">
-        <v>-543.0175</v>
+        <v>-830.3025</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3516,7 +3586,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>3484</v>
+        <v>3875.1</v>
       </c>
     </row>
     <row r="20">
@@ -3540,73 +3610,163 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GOOGL 260522C00345000</t>
+          <t>SPY   261218P00620000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>GOOGL 22MAY26 345 C</t>
+          <t>SPY 18DEC26 620 P</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
+        <v>620</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>16.645</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3329</v>
+      </c>
+      <c r="P20" t="n">
+        <v>20.1350875</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>20.1350875</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4027.0175</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-698.0175</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>CBOE</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>U6565621</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>GOOGL 260522C00345000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>GOOGL 22MAY26 345 C</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" t="n">
         <v>345</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
         <v>-2</v>
       </c>
-      <c r="N20" t="n">
-        <v>10.6422</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-2128.44</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="N21" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-2570</v>
+      </c>
+      <c r="P21" t="n">
         <v>5.1653811</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>5.1653811</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>-1033.07622</v>
       </c>
-      <c r="S20" t="n">
-        <v>-1095.36378</v>
-      </c>
-      <c r="T20" t="inlineStr">
+      <c r="S21" t="n">
+        <v>-1536.92378</v>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>CBOE</t>
         </is>
       </c>
-      <c r="V20" t="n">
-        <v>-2128.44</v>
+      <c r="V21" t="n">
+        <v>-2570</v>
       </c>
     </row>
   </sheetData>
@@ -3653,17 +3813,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$295,363.36</t>
+          <t>$301,813.34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$149,174.93</t>
+          <t>$143,427.69</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$444,538.30</t>
+          <t>$445,241.03</t>
         </is>
       </c>
     </row>
@@ -3675,17 +3835,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$467,527.30</t>
+          <t>$473,395.73</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$95,266.78</t>
+          <t>$89,532.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$562,794.08</t>
+          <t>$562,928.51</t>
         </is>
       </c>
     </row>
@@ -3703,17 +3863,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$762,890.66</t>
+          <t>$775,209.07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$244,441.71</t>
+          <t>$232,960.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1,007,332.37</t>
+          <t>$1,008,169.54</t>
         </is>
       </c>
     </row>
@@ -3761,14 +3921,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15 23:48:25</t>
+          <t>2026-04-16 23:48:17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2788</v>
+        <v>1.2762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>412.45</v>
+        <v>417.05</v>
       </c>
       <c r="O2" t="n">
-        <v>28871.5</v>
+        <v>29193.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>1030.587595</v>
+        <v>1352.587595</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>36920.8742</v>
+        <v>37256.7447</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2788</v>
+        <v>1.2762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>67.17</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>13434</v>
+        <v>13586</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>359.573333</v>
+        <v>511.573333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>17179.3992</v>
+        <v>17338.4532</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14666</v>
+        <v>0.14657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.54</v>
+        <v>31.78</v>
       </c>
       <c r="O4" t="n">
-        <v>63080</v>
+        <v>63560</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>-332.49376</v>
+        <v>147.50624</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9251.312800000002</v>
+        <v>9315.9892</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1799</v>
+        <v>1.1782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2045</v>
+        <v>4.319</v>
       </c>
       <c r="O5" t="n">
-        <v>8409</v>
+        <v>8638</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-915.66</v>
+        <v>-686.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>9921.7791</v>
+        <v>10177.2916</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1799</v>
+        <v>1.1782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>654</v>
+        <v>668</v>
       </c>
       <c r="O6" t="n">
-        <v>9810</v>
+        <v>10020</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1465.83</v>
+        <v>1675.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>11574.819</v>
+        <v>11805.564</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78677</v>
+        <v>0.7856300000000001</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5.04</v>
+        <v>5.035</v>
       </c>
       <c r="O7" t="n">
-        <v>40320</v>
+        <v>40280</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>3008.77315</v>
+        <v>2968.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31722.5664</v>
+        <v>31645.1764</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78677</v>
+        <v>0.7856300000000001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,29 +1065,29 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N8" t="n">
-        <v>562.2</v>
+        <v>562.16</v>
       </c>
       <c r="O8" t="n">
-        <v>56220</v>
+        <v>67459.2</v>
       </c>
       <c r="P8" t="n">
-        <v>579.71400048</v>
+        <v>576.9867204</v>
       </c>
       <c r="Q8" t="n">
-        <v>579.71400048</v>
+        <v>576.9867204</v>
       </c>
       <c r="R8" t="n">
-        <v>57971.400048</v>
+        <v>69238.40644799999</v>
       </c>
       <c r="S8" t="n">
-        <v>-1751.400048</v>
+        <v>-1779.206448</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>44232.2094</v>
+        <v>52997.971296</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.53</v>
+        <v>7.7</v>
       </c>
       <c r="O9" t="n">
-        <v>7530</v>
+        <v>7700</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-781.237657</v>
+        <v>-611.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7530</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>214.4</v>
+        <v>214.93</v>
       </c>
       <c r="O10" t="n">
-        <v>6432</v>
+        <v>6447.9</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-111.1</v>
+        <v>-95.2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6432</v>
+        <v>6447.9</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.3</v>
+        <v>10.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>59.5</v>
+        <v>64.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1030</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>62.02</v>
+        <v>62.3</v>
       </c>
       <c r="O12" t="n">
-        <v>9923.200000000001</v>
+        <v>9968</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>346.54</v>
+        <v>391.34</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9923.200000000001</v>
+        <v>9968</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>29.0932</v>
+        <v>28.6179</v>
       </c>
       <c r="O13" t="n">
-        <v>11200.88</v>
+        <v>11017.89</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>1185.977178</v>
+        <v>1002.987178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>11200.88</v>
+        <v>11017.89</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>113.04</v>
+        <v>113.41</v>
       </c>
       <c r="O14" t="n">
-        <v>5652</v>
+        <v>5670.5</v>
       </c>
       <c r="P14" t="n">
         <v>114.135</v>
@@ -1567,7 +1567,7 @@
         <v>5706.75</v>
       </c>
       <c r="S14" t="n">
-        <v>-54.75</v>
+        <v>-36.25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>5652</v>
+        <v>5670.5</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>40</v>
       </c>
       <c r="N15" t="n">
-        <v>90.33</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>3613.2</v>
+        <v>3616</v>
       </c>
       <c r="P15" t="n">
         <v>102.0775</v>
@@ -1647,7 +1647,7 @@
         <v>4083.1</v>
       </c>
       <c r="S15" t="n">
-        <v>-469.9</v>
+        <v>-467.1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>3613.2</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>500</v>
       </c>
       <c r="N16" t="n">
-        <v>177.9</v>
+        <v>178.6</v>
       </c>
       <c r="O16" t="n">
-        <v>88950</v>
+        <v>89300</v>
       </c>
       <c r="P16" t="n">
         <v>172.83405384</v>
@@ -1727,7 +1727,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S16" t="n">
-        <v>2532.97308</v>
+        <v>2882.97308</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>88950</v>
+        <v>89300</v>
       </c>
     </row>
     <row r="17">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>19.3755</v>
+        <v>18.88</v>
       </c>
       <c r="O17" t="n">
-        <v>3875.1</v>
+        <v>3776</v>
       </c>
       <c r="P17" t="n">
         <v>23.4605</v>
@@ -1817,7 +1817,7 @@
         <v>4692.1</v>
       </c>
       <c r="S17" t="n">
-        <v>-817</v>
+        <v>-916.1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>3875.1</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="18">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>16.645</v>
+        <v>16.29</v>
       </c>
       <c r="O18" t="n">
-        <v>3329</v>
+        <v>3258</v>
       </c>
       <c r="P18" t="n">
         <v>20.1374875</v>
@@ -1907,7 +1907,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S18" t="n">
-        <v>-698.4974999999999</v>
+        <v>-769.4974999999999</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3329</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="19">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>5.25</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>-525</v>
+        <v>-395</v>
       </c>
       <c r="P19" t="n">
         <v>12.80919851</v>
@@ -1997,7 +1997,7 @@
         <v>-1280.919851</v>
       </c>
       <c r="S19" t="n">
-        <v>755.919851</v>
+        <v>885.919851</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-525</v>
+        <v>-395</v>
       </c>
     </row>
   </sheetData>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2788</v>
+        <v>1.2762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>412.45</v>
+        <v>417.05</v>
       </c>
       <c r="O2" t="n">
-        <v>37120.5</v>
+        <v>37534.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2203,7 +2203,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>1057.558512</v>
+        <v>1471.558512</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>47469.6954</v>
+        <v>47901.5289</v>
       </c>
     </row>
     <row r="3">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2788</v>
+        <v>1.2762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2261,17 +2261,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>67.17</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>20151</v>
+        <v>20379</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2283,7 +2283,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>422.1405</v>
+        <v>650.1405</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>25769.0988</v>
+        <v>26007.6798</v>
       </c>
     </row>
     <row r="4">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14666</v>
+        <v>0.14657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2341,17 +2341,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.54</v>
+        <v>31.78</v>
       </c>
       <c r="O4" t="n">
-        <v>63080</v>
+        <v>63560</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2363,7 +2363,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>-312.47719</v>
+        <v>167.52281</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9251.312800000002</v>
+        <v>9315.9892</v>
       </c>
     </row>
     <row r="5">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1799</v>
+        <v>1.1782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2045</v>
+        <v>4.319</v>
       </c>
       <c r="O5" t="n">
-        <v>12613.5</v>
+        <v>12957</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2443,7 +2443,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1361.739091</v>
+        <v>-1018.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14882.66865</v>
+        <v>15265.9374</v>
       </c>
     </row>
     <row r="6">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1799</v>
+        <v>1.1782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2501,17 +2501,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>48.2</v>
+        <v>48.64</v>
       </c>
       <c r="O6" t="n">
-        <v>48200</v>
+        <v>48640</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2523,7 +2523,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>5190</v>
+        <v>5630</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>56871.18</v>
+        <v>57307.64799999999</v>
       </c>
     </row>
     <row r="7">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1799</v>
+        <v>1.1782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2581,17 +2581,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>654</v>
+        <v>668</v>
       </c>
       <c r="O7" t="n">
-        <v>9810</v>
+        <v>10020</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2603,7 +2603,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>1465.83</v>
+        <v>1675.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>11574.819</v>
+        <v>11805.564</v>
       </c>
     </row>
     <row r="8">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78677</v>
+        <v>0.7856300000000001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2661,17 +2661,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>5.04</v>
+        <v>5.035</v>
       </c>
       <c r="O8" t="n">
-        <v>50400</v>
+        <v>50350</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2683,7 +2683,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>13131.8184</v>
+        <v>13081.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39653.208</v>
+        <v>39556.4705</v>
       </c>
     </row>
     <row r="9">
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78677</v>
+        <v>0.7856300000000001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2741,29 +2741,29 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N9" t="n">
-        <v>562.2</v>
+        <v>562.16</v>
       </c>
       <c r="O9" t="n">
-        <v>56220</v>
+        <v>70270</v>
       </c>
       <c r="P9" t="n">
-        <v>579.7134</v>
+        <v>576.4427856</v>
       </c>
       <c r="Q9" t="n">
-        <v>579.7134</v>
+        <v>576.4427856</v>
       </c>
       <c r="R9" t="n">
-        <v>57971.34</v>
+        <v>72055.34819999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-1751.34</v>
+        <v>-1785.3482</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>44232.2094</v>
+        <v>55206.22010000001</v>
       </c>
     </row>
     <row r="10">
@@ -2821,17 +2821,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.53</v>
+        <v>7.7</v>
       </c>
       <c r="O10" t="n">
-        <v>8283</v>
+        <v>8470</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -2843,7 +2843,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-859.847947</v>
+        <v>-672.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8283</v>
+        <v>8470</v>
       </c>
     </row>
     <row r="11">
@@ -2901,17 +2901,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>214.4</v>
+        <v>214.93</v>
       </c>
       <c r="O11" t="n">
-        <v>6432</v>
+        <v>6447.9</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -2923,7 +2923,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-107.2</v>
+        <v>-91.3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6432</v>
+        <v>6447.9</v>
       </c>
     </row>
     <row r="12">
@@ -2981,17 +2981,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>10.3</v>
+        <v>10.35</v>
       </c>
       <c r="O12" t="n">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3003,7 +3003,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-168.5</v>
+        <v>-158.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2060</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="13">
@@ -3061,17 +3061,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>337.12</v>
+        <v>336.02</v>
       </c>
       <c r="O13" t="n">
-        <v>67424</v>
+        <v>67204</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3083,7 +3083,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>4474.245</v>
+        <v>4254.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>67424</v>
+        <v>67204</v>
       </c>
     </row>
     <row r="14">
@@ -3141,17 +3141,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>62.02</v>
+        <v>62.3</v>
       </c>
       <c r="O14" t="n">
-        <v>9923.200000000001</v>
+        <v>9968</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3163,7 +3163,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>290.76</v>
+        <v>335.56</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9923.200000000001</v>
+        <v>9968</v>
       </c>
     </row>
     <row r="15">
@@ -3221,17 +3221,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>79.69</v>
+        <v>79.375</v>
       </c>
       <c r="O15" t="n">
-        <v>1342.36</v>
+        <v>1337.06</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3243,7 +3243,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>993.3134209999999</v>
+        <v>988.013421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1342.36</v>
+        <v>1337.06</v>
       </c>
     </row>
     <row r="16">
@@ -3301,17 +3301,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>29.0932</v>
+        <v>28.6179</v>
       </c>
       <c r="O16" t="n">
-        <v>11200.88</v>
+        <v>11017.89</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3323,7 +3323,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>1191.974112</v>
+        <v>1008.984112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>11200.88</v>
+        <v>11017.89</v>
       </c>
     </row>
     <row r="17">
@@ -3381,17 +3381,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>113.04</v>
+        <v>113.41</v>
       </c>
       <c r="O17" t="n">
-        <v>5652</v>
+        <v>5670.5</v>
       </c>
       <c r="P17" t="n">
         <v>114.119</v>
@@ -3403,7 +3403,7 @@
         <v>5705.95</v>
       </c>
       <c r="S17" t="n">
-        <v>-53.95</v>
+        <v>-35.45</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>5652</v>
+        <v>5670.5</v>
       </c>
     </row>
     <row r="18">
@@ -3461,17 +3461,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>600</v>
       </c>
       <c r="N18" t="n">
-        <v>177.9</v>
+        <v>178.6</v>
       </c>
       <c r="O18" t="n">
-        <v>106740</v>
+        <v>107160</v>
       </c>
       <c r="P18" t="n">
         <v>172.9987895</v>
@@ -3483,7 +3483,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S18" t="n">
-        <v>2940.7263</v>
+        <v>3360.7263</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>106740</v>
+        <v>107160</v>
       </c>
     </row>
     <row r="19">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>19.3755</v>
+        <v>18.88</v>
       </c>
       <c r="O19" t="n">
-        <v>3875.1</v>
+        <v>3776</v>
       </c>
       <c r="P19" t="n">
         <v>23.5270125</v>
@@ -3573,7 +3573,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S19" t="n">
-        <v>-830.3025</v>
+        <v>-929.4025</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>3875.1</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="20">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>16.645</v>
+        <v>16.29</v>
       </c>
       <c r="O20" t="n">
-        <v>3329</v>
+        <v>3258</v>
       </c>
       <c r="P20" t="n">
         <v>20.1350875</v>
@@ -3663,7 +3663,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S20" t="n">
-        <v>-698.0175</v>
+        <v>-769.0175</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>3329</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="21">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>12.85</v>
+        <v>12.025</v>
       </c>
       <c r="O21" t="n">
-        <v>-2570</v>
+        <v>-2405</v>
       </c>
       <c r="P21" t="n">
         <v>5.1653811</v>
@@ -3753,7 +3753,7 @@
         <v>-1033.07622</v>
       </c>
       <c r="S21" t="n">
-        <v>-1536.92378</v>
+        <v>-1371.92378</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-2570</v>
+        <v>-2405</v>
       </c>
     </row>
   </sheetData>
@@ -3813,17 +3813,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$301,813.34</t>
+          <t>$311,931.48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$143,427.69</t>
+          <t>$134,482.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$445,241.03</t>
+          <t>$446,413.94</t>
         </is>
       </c>
     </row>
@@ -3835,17 +3835,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$473,395.73</t>
+          <t>$486,341.39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$89,532.78</t>
+          <t>$78,337.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$562,928.51</t>
+          <t>$564,678.74</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$775,209.07</t>
+          <t>$798,272.87</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$232,960.47</t>
+          <t>$212,819.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1,008,169.54</t>
+          <t>$1,011,092.69</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-16 23:48:17</t>
+          <t>2026-04-17 23:47:56</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2762</v>
+        <v>1.2792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>417.05</v>
+        <v>423.25</v>
       </c>
       <c r="O2" t="n">
-        <v>29193.5</v>
+        <v>29627.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>1352.587595</v>
+        <v>1786.587595</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>37256.7447</v>
+        <v>37899.498</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2762</v>
+        <v>1.2792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>67.93000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>13586</v>
+        <v>13780</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>511.573333</v>
+        <v>705.573333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>17338.4532</v>
+        <v>17627.376</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14657</v>
+        <v>0.14672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9315.9892</v>
+        <v>9325.5232</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1782</v>
+        <v>1.1765</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.319</v>
+        <v>4.377</v>
       </c>
       <c r="O5" t="n">
-        <v>8638</v>
+        <v>8754</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-686.66</v>
+        <v>-570.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>10177.2916</v>
+        <v>10299.081</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1782</v>
+        <v>1.1765</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>668</v>
+        <v>690</v>
       </c>
       <c r="O6" t="n">
-        <v>10020</v>
+        <v>10350</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1675.83</v>
+        <v>2005.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>11805.564</v>
+        <v>12176.775</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7856300000000001</v>
+        <v>0.78714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5.035</v>
+        <v>5.023</v>
       </c>
       <c r="O7" t="n">
-        <v>40280</v>
+        <v>40184</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2968.77315</v>
+        <v>2872.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31645.1764</v>
+        <v>31630.43376</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7856300000000001</v>
+        <v>0.78714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>120</v>
       </c>
       <c r="N8" t="n">
-        <v>562.16</v>
+        <v>561.39</v>
       </c>
       <c r="O8" t="n">
-        <v>67459.2</v>
+        <v>67366.8</v>
       </c>
       <c r="P8" t="n">
         <v>576.9867204</v>
@@ -1087,7 +1087,7 @@
         <v>69238.40644799999</v>
       </c>
       <c r="S8" t="n">
-        <v>-1779.206448</v>
+        <v>-1871.606448</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>52997.971296</v>
+        <v>53027.102952</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="O9" t="n">
-        <v>7700</v>
+        <v>7710</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-611.237657</v>
+        <v>-601.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7700</v>
+        <v>7710</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>214.93</v>
+        <v>220.1</v>
       </c>
       <c r="O10" t="n">
-        <v>6447.9</v>
+        <v>6603</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-95.2</v>
+        <v>59.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6447.9</v>
+        <v>6603</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.35</v>
+        <v>10.63</v>
       </c>
       <c r="O11" t="n">
-        <v>1035</v>
+        <v>1063</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>64.5</v>
+        <v>92.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1035</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>62.3</v>
+        <v>63.45</v>
       </c>
       <c r="O12" t="n">
-        <v>9968</v>
+        <v>10152</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>391.34</v>
+        <v>575.34</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>9968</v>
+        <v>10152</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>28.6179</v>
+        <v>28.5973</v>
       </c>
       <c r="O13" t="n">
-        <v>11017.89</v>
+        <v>11009.96</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>1002.987178</v>
+        <v>995.057178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>11017.89</v>
+        <v>11009.96</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>113.41</v>
+        <v>116.5</v>
       </c>
       <c r="O14" t="n">
-        <v>5670.5</v>
+        <v>5825</v>
       </c>
       <c r="P14" t="n">
         <v>114.135</v>
@@ -1567,7 +1567,7 @@
         <v>5706.75</v>
       </c>
       <c r="S14" t="n">
-        <v>-36.25</v>
+        <v>118.25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>5670.5</v>
+        <v>5825</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>40</v>
       </c>
       <c r="N15" t="n">
-        <v>90.40000000000001</v>
+        <v>91.33</v>
       </c>
       <c r="O15" t="n">
-        <v>3616</v>
+        <v>3653.2</v>
       </c>
       <c r="P15" t="n">
         <v>102.0775</v>
@@ -1647,7 +1647,7 @@
         <v>4083.1</v>
       </c>
       <c r="S15" t="n">
-        <v>-467.1</v>
+        <v>-429.9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>3616</v>
+        <v>3653.2</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>500</v>
       </c>
       <c r="N16" t="n">
-        <v>178.6</v>
+        <v>181.46</v>
       </c>
       <c r="O16" t="n">
-        <v>89300</v>
+        <v>90730</v>
       </c>
       <c r="P16" t="n">
         <v>172.83405384</v>
@@ -1727,7 +1727,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S16" t="n">
-        <v>2882.97308</v>
+        <v>4312.97308</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>89300</v>
+        <v>90730</v>
       </c>
     </row>
     <row r="17">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>18.88</v>
+        <v>17.4374</v>
       </c>
       <c r="O17" t="n">
-        <v>3776</v>
+        <v>3487.48</v>
       </c>
       <c r="P17" t="n">
         <v>23.4605</v>
@@ -1817,7 +1817,7 @@
         <v>4692.1</v>
       </c>
       <c r="S17" t="n">
-        <v>-916.1</v>
+        <v>-1204.62</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>3776</v>
+        <v>3487.48</v>
       </c>
     </row>
     <row r="18">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>16.29</v>
+        <v>15.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3258</v>
+        <v>3014</v>
       </c>
       <c r="P18" t="n">
         <v>20.1374875</v>
@@ -1907,7 +1907,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S18" t="n">
-        <v>-769.4974999999999</v>
+        <v>-1013.4975</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3258</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="19">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="O19" t="n">
-        <v>-395</v>
+        <v>-332</v>
       </c>
       <c r="P19" t="n">
         <v>12.80919851</v>
@@ -1997,7 +1997,7 @@
         <v>-1280.919851</v>
       </c>
       <c r="S19" t="n">
-        <v>885.919851</v>
+        <v>948.919851</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-395</v>
+        <v>-332</v>
       </c>
     </row>
   </sheetData>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2762</v>
+        <v>1.2792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>417.05</v>
+        <v>423.25</v>
       </c>
       <c r="O2" t="n">
-        <v>37534.5</v>
+        <v>38092.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2203,7 +2203,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>1471.558512</v>
+        <v>2029.558512</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>47901.5289</v>
+        <v>48727.926</v>
       </c>
     </row>
     <row r="3">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2762</v>
+        <v>1.2792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2261,17 +2261,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>67.93000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>20379</v>
+        <v>20670</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2283,7 +2283,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>650.1405</v>
+        <v>941.1405</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>26007.6798</v>
+        <v>26441.064</v>
       </c>
     </row>
     <row r="4">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14657</v>
+        <v>0.14672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9315.9892</v>
+        <v>9325.5232</v>
       </c>
     </row>
     <row r="5">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1782</v>
+        <v>1.1765</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.319</v>
+        <v>4.377</v>
       </c>
       <c r="O5" t="n">
-        <v>12957</v>
+        <v>13131</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2443,7 +2443,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1018.239091</v>
+        <v>-844.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>15265.9374</v>
+        <v>15448.6215</v>
       </c>
     </row>
     <row r="6">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1782</v>
+        <v>1.1765</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2501,17 +2501,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>48.64</v>
+        <v>50.14</v>
       </c>
       <c r="O6" t="n">
-        <v>48640</v>
+        <v>50140</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2523,7 +2523,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>5630</v>
+        <v>7130</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>57307.64799999999</v>
+        <v>58989.71000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1782</v>
+        <v>1.1765</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2581,17 +2581,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>668</v>
+        <v>690</v>
       </c>
       <c r="O7" t="n">
-        <v>10020</v>
+        <v>10350</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2603,7 +2603,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>1675.83</v>
+        <v>2005.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>11805.564</v>
+        <v>12176.775</v>
       </c>
     </row>
     <row r="8">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7856300000000001</v>
+        <v>0.78714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2661,17 +2661,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>5.035</v>
+        <v>5.023</v>
       </c>
       <c r="O8" t="n">
-        <v>50350</v>
+        <v>50230</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2683,7 +2683,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>13081.8184</v>
+        <v>12961.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39556.4705</v>
+        <v>39538.0422</v>
       </c>
     </row>
     <row r="9">
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7856300000000001</v>
+        <v>0.78714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2741,17 +2741,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>125</v>
       </c>
       <c r="N9" t="n">
-        <v>562.16</v>
+        <v>561.39</v>
       </c>
       <c r="O9" t="n">
-        <v>70270</v>
+        <v>70173.75</v>
       </c>
       <c r="P9" t="n">
         <v>576.4427856</v>
@@ -2763,7 +2763,7 @@
         <v>72055.34819999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-1785.3482</v>
+        <v>-1881.5982</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>55206.22010000001</v>
+        <v>55236.56557499999</v>
       </c>
     </row>
     <row r="10">
@@ -2821,17 +2821,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="O10" t="n">
-        <v>8470</v>
+        <v>8481</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -2843,7 +2843,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-672.847947</v>
+        <v>-661.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8470</v>
+        <v>8481</v>
       </c>
     </row>
     <row r="11">
@@ -2901,17 +2901,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>214.93</v>
+        <v>220.1</v>
       </c>
       <c r="O11" t="n">
-        <v>6447.9</v>
+        <v>6603</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -2923,7 +2923,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-91.3</v>
+        <v>63.8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6447.9</v>
+        <v>6603</v>
       </c>
     </row>
     <row r="12">
@@ -2981,17 +2981,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>10.35</v>
+        <v>10.63</v>
       </c>
       <c r="O12" t="n">
-        <v>2070</v>
+        <v>2126</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3003,7 +3003,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-158.5</v>
+        <v>-102.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2070</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="13">
@@ -3061,17 +3061,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>336.02</v>
+        <v>341.68</v>
       </c>
       <c r="O13" t="n">
-        <v>67204</v>
+        <v>68336</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3083,7 +3083,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>4254.245</v>
+        <v>5386.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>67204</v>
+        <v>68336</v>
       </c>
     </row>
     <row r="14">
@@ -3141,17 +3141,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>62.3</v>
+        <v>63.45</v>
       </c>
       <c r="O14" t="n">
-        <v>9968</v>
+        <v>10152</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3163,7 +3163,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>335.56</v>
+        <v>519.5599999999999</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9968</v>
+        <v>10152</v>
       </c>
     </row>
     <row r="15">
@@ -3221,17 +3221,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>79.375</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>1337.06</v>
+        <v>1376.39</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3243,7 +3243,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>988.013421</v>
+        <v>1027.343421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1337.06</v>
+        <v>1376.39</v>
       </c>
     </row>
     <row r="16">
@@ -3301,17 +3301,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>28.6179</v>
+        <v>28.5973</v>
       </c>
       <c r="O16" t="n">
-        <v>11017.89</v>
+        <v>11009.96</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3323,7 +3323,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>1008.984112</v>
+        <v>1001.054112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>11017.89</v>
+        <v>11009.96</v>
       </c>
     </row>
     <row r="17">
@@ -3381,17 +3381,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>113.41</v>
+        <v>116.5</v>
       </c>
       <c r="O17" t="n">
-        <v>5670.5</v>
+        <v>5825</v>
       </c>
       <c r="P17" t="n">
         <v>114.119</v>
@@ -3403,7 +3403,7 @@
         <v>5705.95</v>
       </c>
       <c r="S17" t="n">
-        <v>-35.45</v>
+        <v>119.05</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>5670.5</v>
+        <v>5825</v>
       </c>
     </row>
     <row r="18">
@@ -3461,17 +3461,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>600</v>
       </c>
       <c r="N18" t="n">
-        <v>178.6</v>
+        <v>181.46</v>
       </c>
       <c r="O18" t="n">
-        <v>107160</v>
+        <v>108876</v>
       </c>
       <c r="P18" t="n">
         <v>172.9987895</v>
@@ -3483,7 +3483,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S18" t="n">
-        <v>3360.7263</v>
+        <v>5076.7263</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>107160</v>
+        <v>108876</v>
       </c>
     </row>
     <row r="19">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>18.88</v>
+        <v>17.4374</v>
       </c>
       <c r="O19" t="n">
-        <v>3776</v>
+        <v>3487.48</v>
       </c>
       <c r="P19" t="n">
         <v>23.5270125</v>
@@ -3573,7 +3573,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S19" t="n">
-        <v>-929.4025</v>
+        <v>-1217.9225</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>3776</v>
+        <v>3487.48</v>
       </c>
     </row>
     <row r="20">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>16.29</v>
+        <v>15.07</v>
       </c>
       <c r="O20" t="n">
-        <v>3258</v>
+        <v>3014</v>
       </c>
       <c r="P20" t="n">
         <v>20.1350875</v>
@@ -3663,7 +3663,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S20" t="n">
-        <v>-769.0175</v>
+        <v>-1013.0175</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>3258</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="21">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>12.025</v>
+        <v>13.85</v>
       </c>
       <c r="O21" t="n">
-        <v>-2405</v>
+        <v>-2770</v>
       </c>
       <c r="P21" t="n">
         <v>5.1653811</v>
@@ -3753,7 +3753,7 @@
         <v>-1033.07622</v>
       </c>
       <c r="S21" t="n">
-        <v>-1371.92378</v>
+        <v>-1736.92378</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-2405</v>
+        <v>-2770</v>
       </c>
     </row>
   </sheetData>
@@ -3813,17 +3813,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$311,931.48</t>
+          <t>$314,901.43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$134,482.46</t>
+          <t>$134,579.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$446,413.94</t>
+          <t>$449,480.98</t>
         </is>
       </c>
     </row>
@@ -3835,17 +3835,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$486,341.39</t>
+          <t>$492,401.06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$78,337.36</t>
+          <t>$78,477.54</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$564,678.74</t>
+          <t>$570,878.59</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$798,272.87</t>
+          <t>$807,302.49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$212,819.82</t>
+          <t>$213,057.08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1,011,092.69</t>
+          <t>$1,020,359.57</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-17 23:47:56</t>
+          <t>2026-04-18 23:47:08</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -3921,7 +3921,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-18 23:47:08</t>
+          <t>2026-04-19 23:47:18</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -3921,7 +3921,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-19 23:47:18</t>
+          <t>2026-04-20 23:48:31</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2792</v>
+        <v>1.2847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>423.25</v>
+        <v>419.75</v>
       </c>
       <c r="O2" t="n">
-        <v>29627.5</v>
+        <v>29382.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>1786.587595</v>
+        <v>1541.587595</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>37899.498</v>
+        <v>37747.69775</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2792</v>
+        <v>1.2847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.19</v>
       </c>
       <c r="O3" t="n">
-        <v>13780</v>
+        <v>13638</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>705.573333</v>
+        <v>563.573333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>17627.376</v>
+        <v>17520.7386</v>
       </c>
     </row>
     <row r="4">
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.78</v>
+        <v>31.9</v>
       </c>
       <c r="O4" t="n">
-        <v>63560</v>
+        <v>63800</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>147.50624</v>
+        <v>387.50624</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9325.5232</v>
+        <v>9360.735999999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1765</v>
+        <v>1.1788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.377</v>
+        <v>4.3615</v>
       </c>
       <c r="O5" t="n">
-        <v>8754</v>
+        <v>8723</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-570.66</v>
+        <v>-601.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>10299.081</v>
+        <v>10282.6724</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1765</v>
+        <v>1.1788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O6" t="n">
-        <v>10350</v>
+        <v>10380</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>2005.83</v>
+        <v>2035.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>12176.775</v>
+        <v>12235.944</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78714</v>
+        <v>0.78749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5.023</v>
+        <v>5.01</v>
       </c>
       <c r="O7" t="n">
-        <v>40184</v>
+        <v>40080</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2872.77315</v>
+        <v>2768.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31630.43376</v>
+        <v>31562.5992</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78714</v>
+        <v>0.78749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>120</v>
       </c>
       <c r="N8" t="n">
-        <v>561.39</v>
+        <v>559.51</v>
       </c>
       <c r="O8" t="n">
-        <v>67366.8</v>
+        <v>67141.2</v>
       </c>
       <c r="P8" t="n">
         <v>576.9867204</v>
@@ -1087,7 +1087,7 @@
         <v>69238.40644799999</v>
       </c>
       <c r="S8" t="n">
-        <v>-1871.606448</v>
+        <v>-2097.206448</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>53027.102952</v>
+        <v>52873.023588</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.71</v>
+        <v>7.815</v>
       </c>
       <c r="O9" t="n">
-        <v>7710</v>
+        <v>7815</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-601.237657</v>
+        <v>-496.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7710</v>
+        <v>7815</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>220.1</v>
+        <v>216.39</v>
       </c>
       <c r="O10" t="n">
-        <v>6603</v>
+        <v>6491.7</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>59.9</v>
+        <v>-51.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6603</v>
+        <v>6491.7</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.63</v>
+        <v>10.46</v>
       </c>
       <c r="O11" t="n">
-        <v>1063</v>
+        <v>1046</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>92.5</v>
+        <v>75.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1063</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>63.45</v>
+        <v>63.26</v>
       </c>
       <c r="O12" t="n">
-        <v>10152</v>
+        <v>10121.6</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>575.34</v>
+        <v>544.9400000000001</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>10152</v>
+        <v>10121.6</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>28.5973</v>
+        <v>28.7997</v>
       </c>
       <c r="O13" t="n">
-        <v>11009.96</v>
+        <v>11087.88</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>995.057178</v>
+        <v>1072.977178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>11009.96</v>
+        <v>11087.88</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>116.5</v>
+        <v>114.84</v>
       </c>
       <c r="O14" t="n">
-        <v>5825</v>
+        <v>5742</v>
       </c>
       <c r="P14" t="n">
         <v>114.135</v>
@@ -1567,7 +1567,7 @@
         <v>5706.75</v>
       </c>
       <c r="S14" t="n">
-        <v>118.25</v>
+        <v>35.25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>5825</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>40</v>
       </c>
       <c r="N15" t="n">
-        <v>91.33</v>
+        <v>89.34</v>
       </c>
       <c r="O15" t="n">
-        <v>3653.2</v>
+        <v>3573.6</v>
       </c>
       <c r="P15" t="n">
         <v>102.0775</v>
@@ -1647,7 +1647,7 @@
         <v>4083.1</v>
       </c>
       <c r="S15" t="n">
-        <v>-429.9</v>
+        <v>-509.5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>3653.2</v>
+        <v>3573.6</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>500</v>
       </c>
       <c r="N16" t="n">
-        <v>181.46</v>
+        <v>180.08</v>
       </c>
       <c r="O16" t="n">
-        <v>90730</v>
+        <v>90040</v>
       </c>
       <c r="P16" t="n">
         <v>172.83405384</v>
@@ -1727,7 +1727,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S16" t="n">
-        <v>4312.97308</v>
+        <v>3622.97308</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>90730</v>
+        <v>90040</v>
       </c>
     </row>
     <row r="17">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>17.4374</v>
+        <v>17.8016</v>
       </c>
       <c r="O17" t="n">
-        <v>3487.48</v>
+        <v>3560.32</v>
       </c>
       <c r="P17" t="n">
         <v>23.4605</v>
@@ -1817,7 +1817,7 @@
         <v>4692.1</v>
       </c>
       <c r="S17" t="n">
-        <v>-1204.62</v>
+        <v>-1131.78</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>3487.48</v>
+        <v>3560.32</v>
       </c>
     </row>
     <row r="18">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>15.07</v>
+        <v>15.575</v>
       </c>
       <c r="O18" t="n">
-        <v>3014</v>
+        <v>3115</v>
       </c>
       <c r="P18" t="n">
         <v>20.1374875</v>
@@ -1907,7 +1907,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S18" t="n">
-        <v>-1013.4975</v>
+        <v>-912.4974999999999</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3014</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="19">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>-332</v>
+        <v>-320</v>
       </c>
       <c r="P19" t="n">
         <v>12.80919851</v>
@@ -1997,7 +1997,7 @@
         <v>-1280.919851</v>
       </c>
       <c r="S19" t="n">
-        <v>948.919851</v>
+        <v>960.919851</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-332</v>
+        <v>-320</v>
       </c>
     </row>
   </sheetData>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2792</v>
+        <v>1.2847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>423.25</v>
+        <v>419.75</v>
       </c>
       <c r="O2" t="n">
-        <v>38092.5</v>
+        <v>37777.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2203,7 +2203,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>2029.558512</v>
+        <v>1714.558512</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>48727.926</v>
+        <v>48532.75425</v>
       </c>
     </row>
     <row r="3">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2792</v>
+        <v>1.2847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2261,17 +2261,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.19</v>
       </c>
       <c r="O3" t="n">
-        <v>20670</v>
+        <v>20457</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2283,7 +2283,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>941.1405</v>
+        <v>728.1405</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>26441.064</v>
+        <v>26281.1079</v>
       </c>
     </row>
     <row r="4">
@@ -2341,17 +2341,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.78</v>
+        <v>31.9</v>
       </c>
       <c r="O4" t="n">
-        <v>63560</v>
+        <v>63800</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2363,7 +2363,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>167.52281</v>
+        <v>407.52281</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9325.5232</v>
+        <v>9360.735999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1765</v>
+        <v>1.1788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.377</v>
+        <v>4.3615</v>
       </c>
       <c r="O5" t="n">
-        <v>13131</v>
+        <v>13084.5</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2443,7 +2443,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-844.239091</v>
+        <v>-890.739091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>15448.6215</v>
+        <v>15424.0086</v>
       </c>
     </row>
     <row r="6">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1765</v>
+        <v>1.1788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2501,17 +2501,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>50.14</v>
+        <v>49.89</v>
       </c>
       <c r="O6" t="n">
-        <v>50140</v>
+        <v>49890</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2523,7 +2523,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>7130</v>
+        <v>6880</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>58989.71000000001</v>
+        <v>58810.332</v>
       </c>
     </row>
     <row r="7">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1765</v>
+        <v>1.1788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2581,17 +2581,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O7" t="n">
-        <v>10350</v>
+        <v>10380</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2603,7 +2603,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>2005.83</v>
+        <v>2035.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>12176.775</v>
+        <v>12235.944</v>
       </c>
     </row>
     <row r="8">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78714</v>
+        <v>0.78749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2661,17 +2661,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>5.023</v>
+        <v>5.01</v>
       </c>
       <c r="O8" t="n">
-        <v>50230</v>
+        <v>50100</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2683,7 +2683,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12961.8184</v>
+        <v>12831.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39538.0422</v>
+        <v>39453.249</v>
       </c>
     </row>
     <row r="9">
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78714</v>
+        <v>0.78749</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2741,17 +2741,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>125</v>
       </c>
       <c r="N9" t="n">
-        <v>561.39</v>
+        <v>559.51</v>
       </c>
       <c r="O9" t="n">
-        <v>70173.75</v>
+        <v>69938.75</v>
       </c>
       <c r="P9" t="n">
         <v>576.4427856</v>
@@ -2763,7 +2763,7 @@
         <v>72055.34819999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-1881.5982</v>
+        <v>-2116.5982</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>55236.56557499999</v>
+        <v>55076.0662375</v>
       </c>
     </row>
     <row r="10">
@@ -2821,17 +2821,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.71</v>
+        <v>7.815</v>
       </c>
       <c r="O10" t="n">
-        <v>8481</v>
+        <v>8596.5</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -2843,7 +2843,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-661.847947</v>
+        <v>-546.347947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8481</v>
+        <v>8596.5</v>
       </c>
     </row>
     <row r="11">
@@ -2901,17 +2901,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>220.1</v>
+        <v>216.39</v>
       </c>
       <c r="O11" t="n">
-        <v>6603</v>
+        <v>6491.7</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -2923,7 +2923,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>63.8</v>
+        <v>-47.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6603</v>
+        <v>6491.7</v>
       </c>
     </row>
     <row r="12">
@@ -2981,17 +2981,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>10.63</v>
+        <v>10.46</v>
       </c>
       <c r="O12" t="n">
-        <v>2126</v>
+        <v>2092</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3003,7 +3003,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-102.5</v>
+        <v>-136.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2126</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="13">
@@ -3061,17 +3061,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>341.68</v>
+        <v>337.42</v>
       </c>
       <c r="O13" t="n">
-        <v>68336</v>
+        <v>67484</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3083,7 +3083,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>5386.245</v>
+        <v>4534.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>68336</v>
+        <v>67484</v>
       </c>
     </row>
     <row r="14">
@@ -3141,17 +3141,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>63.45</v>
+        <v>63.26</v>
       </c>
       <c r="O14" t="n">
-        <v>10152</v>
+        <v>10121.6</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3163,7 +3163,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>519.5599999999999</v>
+        <v>489.16</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10152</v>
+        <v>10121.6</v>
       </c>
     </row>
     <row r="15">
@@ -3221,17 +3221,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>81.70999999999999</v>
+        <v>81.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1376.39</v>
+        <v>1368.64</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3243,7 +3243,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>1027.343421</v>
+        <v>1019.593421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1376.39</v>
+        <v>1368.64</v>
       </c>
     </row>
     <row r="16">
@@ -3301,17 +3301,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>28.5973</v>
+        <v>28.7997</v>
       </c>
       <c r="O16" t="n">
-        <v>11009.96</v>
+        <v>11087.88</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3323,7 +3323,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>1001.054112</v>
+        <v>1078.974112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>11009.96</v>
+        <v>11087.88</v>
       </c>
     </row>
     <row r="17">
@@ -3381,17 +3381,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>116.5</v>
+        <v>114.84</v>
       </c>
       <c r="O17" t="n">
-        <v>5825</v>
+        <v>5742</v>
       </c>
       <c r="P17" t="n">
         <v>114.119</v>
@@ -3403,7 +3403,7 @@
         <v>5705.95</v>
       </c>
       <c r="S17" t="n">
-        <v>119.05</v>
+        <v>36.05</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>5825</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="18">
@@ -3461,17 +3461,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>600</v>
       </c>
       <c r="N18" t="n">
-        <v>181.46</v>
+        <v>180.08</v>
       </c>
       <c r="O18" t="n">
-        <v>108876</v>
+        <v>108048</v>
       </c>
       <c r="P18" t="n">
         <v>172.9987895</v>
@@ -3483,7 +3483,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S18" t="n">
-        <v>5076.7263</v>
+        <v>4248.7263</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>108876</v>
+        <v>108048</v>
       </c>
     </row>
     <row r="19">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>17.4374</v>
+        <v>17.8016</v>
       </c>
       <c r="O19" t="n">
-        <v>3487.48</v>
+        <v>3560.32</v>
       </c>
       <c r="P19" t="n">
         <v>23.5270125</v>
@@ -3573,7 +3573,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S19" t="n">
-        <v>-1217.9225</v>
+        <v>-1145.0825</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>3487.48</v>
+        <v>3560.32</v>
       </c>
     </row>
     <row r="20">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>15.07</v>
+        <v>15.575</v>
       </c>
       <c r="O20" t="n">
-        <v>3014</v>
+        <v>3115</v>
       </c>
       <c r="P20" t="n">
         <v>20.1350875</v>
@@ -3663,7 +3663,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S20" t="n">
-        <v>-1013.0175</v>
+        <v>-912.0175</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>3014</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="21">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>13.85</v>
+        <v>11.375</v>
       </c>
       <c r="O21" t="n">
-        <v>-2770</v>
+        <v>-2275</v>
       </c>
       <c r="P21" t="n">
         <v>5.1653811</v>
@@ -3753,7 +3753,7 @@
         <v>-1033.07622</v>
       </c>
       <c r="S21" t="n">
-        <v>-1736.92378</v>
+        <v>-1241.92378</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-2770</v>
+        <v>-2275</v>
       </c>
     </row>
   </sheetData>
@@ -3813,17 +3813,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$314,901.43</t>
+          <t>$313,856.51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$134,579.55</t>
+          <t>$134,717.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$449,480.98</t>
+          <t>$448,573.73</t>
         </is>
       </c>
     </row>
@@ -3835,17 +3835,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$492,401.06</t>
+          <t>$490,606.84</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$78,477.54</t>
+          <t>$78,635.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$570,878.59</t>
+          <t>$569,241.87</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$807,302.49</t>
+          <t>$804,463.35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$213,057.08</t>
+          <t>$213,352.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1,020,359.57</t>
+          <t>$1,017,815.60</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20 23:48:31</t>
+          <t>2026-04-21 23:47:10</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2847</v>
+        <v>1.2807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>419.75</v>
+        <v>420.75</v>
       </c>
       <c r="O2" t="n">
-        <v>29382.5</v>
+        <v>29452.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>1541.587595</v>
+        <v>1611.587595</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>37747.69775</v>
+        <v>37719.81675</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2847</v>
+        <v>1.2807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>68.19</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>13638</v>
+        <v>13564</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>563.573333</v>
+        <v>489.573333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>17520.7386</v>
+        <v>17371.4148</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14672</v>
+        <v>0.14645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.9</v>
+        <v>32.04</v>
       </c>
       <c r="O4" t="n">
-        <v>63800</v>
+        <v>64080</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>387.50624</v>
+        <v>667.50624</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9360.735999999999</v>
+        <v>9384.516</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1788</v>
+        <v>1.1744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3615</v>
+        <v>4.298</v>
       </c>
       <c r="O5" t="n">
-        <v>8723</v>
+        <v>8596</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-601.66</v>
+        <v>-728.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>10282.6724</v>
+        <v>10095.1424</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1788</v>
+        <v>1.1744</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="O6" t="n">
-        <v>10380</v>
+        <v>10440</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>2035.83</v>
+        <v>2095.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>12235.944</v>
+        <v>12260.736</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78749</v>
+        <v>0.7850200000000001</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
       <c r="O7" t="n">
-        <v>40080</v>
+        <v>40240</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2768.77315</v>
+        <v>2928.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31562.5992</v>
+        <v>31589.2048</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78749</v>
+        <v>0.7850200000000001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>120</v>
       </c>
       <c r="N8" t="n">
-        <v>559.51</v>
+        <v>559.89</v>
       </c>
       <c r="O8" t="n">
-        <v>67141.2</v>
+        <v>67186.8</v>
       </c>
       <c r="P8" t="n">
         <v>576.9867204</v>
@@ -1087,7 +1087,7 @@
         <v>69238.40644799999</v>
       </c>
       <c r="S8" t="n">
-        <v>-2097.206448</v>
+        <v>-2051.606448</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>52873.023588</v>
+        <v>52742.98173600001</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.815</v>
+        <v>7.83</v>
       </c>
       <c r="O9" t="n">
-        <v>7815</v>
+        <v>7830</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-496.237657</v>
+        <v>-481.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7815</v>
+        <v>7830</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>216.39</v>
+        <v>203.09</v>
       </c>
       <c r="O10" t="n">
-        <v>6491.7</v>
+        <v>6092.7</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-51.4</v>
+        <v>-450.4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6491.7</v>
+        <v>6092.7</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.46</v>
+        <v>10.29</v>
       </c>
       <c r="O11" t="n">
-        <v>1046</v>
+        <v>1029</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>75.5</v>
+        <v>58.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1046</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>63.26</v>
+        <v>63.11</v>
       </c>
       <c r="O12" t="n">
-        <v>10121.6</v>
+        <v>10097.6</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>544.9400000000001</v>
+        <v>520.9400000000001</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>10121.6</v>
+        <v>10097.6</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>28.7997</v>
+        <v>28.9314</v>
       </c>
       <c r="O13" t="n">
-        <v>11087.88</v>
+        <v>11138.59</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>1072.977178</v>
+        <v>1123.687178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>11087.88</v>
+        <v>11138.59</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>114.84</v>
+        <v>109.3</v>
       </c>
       <c r="O14" t="n">
-        <v>5742</v>
+        <v>5465</v>
       </c>
       <c r="P14" t="n">
         <v>114.135</v>
@@ -1567,7 +1567,7 @@
         <v>5706.75</v>
       </c>
       <c r="S14" t="n">
-        <v>35.25</v>
+        <v>-241.75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>5742</v>
+        <v>5465</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>40</v>
       </c>
       <c r="N15" t="n">
-        <v>89.34</v>
+        <v>86.83</v>
       </c>
       <c r="O15" t="n">
-        <v>3573.6</v>
+        <v>3473.2</v>
       </c>
       <c r="P15" t="n">
         <v>102.0775</v>
@@ -1647,7 +1647,7 @@
         <v>4083.1</v>
       </c>
       <c r="S15" t="n">
-        <v>-509.5</v>
+        <v>-609.9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>3573.6</v>
+        <v>3473.2</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>500</v>
       </c>
       <c r="N16" t="n">
-        <v>180.08</v>
+        <v>179.32</v>
       </c>
       <c r="O16" t="n">
-        <v>90040</v>
+        <v>89660</v>
       </c>
       <c r="P16" t="n">
         <v>172.83405384</v>
@@ -1727,7 +1727,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S16" t="n">
-        <v>3622.97308</v>
+        <v>3242.97308</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>90040</v>
+        <v>89660</v>
       </c>
     </row>
     <row r="17">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>17.8016</v>
+        <v>18.7727</v>
       </c>
       <c r="O17" t="n">
-        <v>3560.32</v>
+        <v>3754.54</v>
       </c>
       <c r="P17" t="n">
         <v>23.4605</v>
@@ -1817,7 +1817,7 @@
         <v>4692.1</v>
       </c>
       <c r="S17" t="n">
-        <v>-1131.78</v>
+        <v>-937.5599999999999</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>3560.32</v>
+        <v>3754.54</v>
       </c>
     </row>
     <row r="18">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>15.575</v>
+        <v>16.5621</v>
       </c>
       <c r="O18" t="n">
-        <v>3115</v>
+        <v>3312.42</v>
       </c>
       <c r="P18" t="n">
         <v>20.1374875</v>
@@ -1907,7 +1907,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S18" t="n">
-        <v>-912.4974999999999</v>
+        <v>-715.0775</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3115</v>
+        <v>3312.42</v>
       </c>
     </row>
     <row r="19">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>2.845</v>
       </c>
       <c r="O19" t="n">
-        <v>-320</v>
+        <v>-284.5</v>
       </c>
       <c r="P19" t="n">
         <v>12.80919851</v>
@@ -1997,7 +1997,7 @@
         <v>-1280.919851</v>
       </c>
       <c r="S19" t="n">
-        <v>960.919851</v>
+        <v>996.419851</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>-320</v>
+        <v>-284.5</v>
       </c>
     </row>
   </sheetData>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2847</v>
+        <v>1.2807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>419.75</v>
+        <v>420.75</v>
       </c>
       <c r="O2" t="n">
-        <v>37777.5</v>
+        <v>37867.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2203,7 +2203,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>1714.558512</v>
+        <v>1804.558512</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>48532.75425</v>
+        <v>48496.90725</v>
       </c>
     </row>
     <row r="3">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2847</v>
+        <v>1.2807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2261,17 +2261,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>68.19</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>20457</v>
+        <v>20346</v>
       </c>
       <c r="P3" t="n">
         <v>65.76286500000001</v>
@@ -2283,7 +2283,7 @@
         <v>19728.8595</v>
       </c>
       <c r="S3" t="n">
-        <v>728.1405</v>
+        <v>617.1405</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>26281.1079</v>
+        <v>26057.1222</v>
       </c>
     </row>
     <row r="4">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14672</v>
+        <v>0.14645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2341,17 +2341,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>31.9</v>
+        <v>32.04</v>
       </c>
       <c r="O4" t="n">
-        <v>63800</v>
+        <v>64080</v>
       </c>
       <c r="P4" t="n">
         <v>31.696238595</v>
@@ -2363,7 +2363,7 @@
         <v>63392.47719</v>
       </c>
       <c r="S4" t="n">
-        <v>407.52281</v>
+        <v>687.52281</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9360.735999999999</v>
+        <v>9384.516</v>
       </c>
     </row>
     <row r="5">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1788</v>
+        <v>1.1744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3615</v>
+        <v>4.298</v>
       </c>
       <c r="O5" t="n">
-        <v>13084.5</v>
+        <v>12894</v>
       </c>
       <c r="P5" t="n">
         <v>4.65841303</v>
@@ -2443,7 +2443,7 @@
         <v>13975.239091</v>
       </c>
       <c r="S5" t="n">
-        <v>-890.739091</v>
+        <v>-1081.239091</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>15424.0086</v>
+        <v>15142.7136</v>
       </c>
     </row>
     <row r="6">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1788</v>
+        <v>1.1744</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2501,17 +2501,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1000</v>
       </c>
       <c r="N6" t="n">
-        <v>49.89</v>
+        <v>49.28</v>
       </c>
       <c r="O6" t="n">
-        <v>49890</v>
+        <v>49280</v>
       </c>
       <c r="P6" t="n">
         <v>43.01</v>
@@ -2523,7 +2523,7 @@
         <v>43010</v>
       </c>
       <c r="S6" t="n">
-        <v>6880</v>
+        <v>6270</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>58810.332</v>
+        <v>57874.43200000001</v>
       </c>
     </row>
     <row r="7">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1788</v>
+        <v>1.1744</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2581,17 +2581,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="O7" t="n">
-        <v>10380</v>
+        <v>10440</v>
       </c>
       <c r="P7" t="n">
         <v>556.278</v>
@@ -2603,7 +2603,7 @@
         <v>8344.17</v>
       </c>
       <c r="S7" t="n">
-        <v>2035.83</v>
+        <v>2095.83</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>12235.944</v>
+        <v>12260.736</v>
       </c>
     </row>
     <row r="8">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78749</v>
+        <v>0.7850200000000001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2661,17 +2661,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>10000</v>
       </c>
       <c r="N8" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
       <c r="O8" t="n">
-        <v>50100</v>
+        <v>50300</v>
       </c>
       <c r="P8" t="n">
         <v>3.72681816</v>
@@ -2683,7 +2683,7 @@
         <v>37268.1816</v>
       </c>
       <c r="S8" t="n">
-        <v>12831.8184</v>
+        <v>13031.8184</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>39453.249</v>
+        <v>39486.506</v>
       </c>
     </row>
     <row r="9">
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78749</v>
+        <v>0.7850200000000001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2741,17 +2741,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>125</v>
       </c>
       <c r="N9" t="n">
-        <v>559.51</v>
+        <v>559.89</v>
       </c>
       <c r="O9" t="n">
-        <v>69938.75</v>
+        <v>69986.25</v>
       </c>
       <c r="P9" t="n">
         <v>576.4427856</v>
@@ -2763,7 +2763,7 @@
         <v>72055.34819999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-2116.5982</v>
+        <v>-2069.0982</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>55076.0662375</v>
+        <v>54940.60597500001</v>
       </c>
     </row>
     <row r="10">
@@ -2821,17 +2821,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>1100</v>
       </c>
       <c r="N10" t="n">
-        <v>7.815</v>
+        <v>7.83</v>
       </c>
       <c r="O10" t="n">
-        <v>8596.5</v>
+        <v>8613</v>
       </c>
       <c r="P10" t="n">
         <v>8.311679952</v>
@@ -2843,7 +2843,7 @@
         <v>9142.847947</v>
       </c>
       <c r="S10" t="n">
-        <v>-546.347947</v>
+        <v>-529.847947</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>8596.5</v>
+        <v>8613</v>
       </c>
     </row>
     <row r="11">
@@ -2901,17 +2901,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>216.39</v>
+        <v>203.09</v>
       </c>
       <c r="O11" t="n">
-        <v>6491.7</v>
+        <v>6092.7</v>
       </c>
       <c r="P11" t="n">
         <v>217.973333333</v>
@@ -2923,7 +2923,7 @@
         <v>6539.2</v>
       </c>
       <c r="S11" t="n">
-        <v>-47.5</v>
+        <v>-446.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>6491.7</v>
+        <v>6092.7</v>
       </c>
     </row>
     <row r="12">
@@ -2981,17 +2981,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>200</v>
       </c>
       <c r="N12" t="n">
-        <v>10.46</v>
+        <v>10.29</v>
       </c>
       <c r="O12" t="n">
-        <v>2092</v>
+        <v>2058</v>
       </c>
       <c r="P12" t="n">
         <v>11.1425</v>
@@ -3003,7 +3003,7 @@
         <v>2228.5</v>
       </c>
       <c r="S12" t="n">
-        <v>-136.5</v>
+        <v>-170.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2092</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="13">
@@ -3061,17 +3061,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>200</v>
       </c>
       <c r="N13" t="n">
-        <v>337.42</v>
+        <v>332.29</v>
       </c>
       <c r="O13" t="n">
-        <v>67484</v>
+        <v>66458</v>
       </c>
       <c r="P13" t="n">
         <v>314.748775</v>
@@ -3083,7 +3083,7 @@
         <v>62949.755</v>
       </c>
       <c r="S13" t="n">
-        <v>4534.245</v>
+        <v>3508.245</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>67484</v>
+        <v>66458</v>
       </c>
     </row>
     <row r="14">
@@ -3141,17 +3141,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>63.26</v>
+        <v>63.11</v>
       </c>
       <c r="O14" t="n">
-        <v>10121.6</v>
+        <v>10097.6</v>
       </c>
       <c r="P14" t="n">
         <v>60.20275</v>
@@ -3163,7 +3163,7 @@
         <v>9632.440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>489.16</v>
+        <v>465.16</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>10121.6</v>
+        <v>10097.6</v>
       </c>
     </row>
     <row r="15">
@@ -3221,17 +3221,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>16.8448</v>
       </c>
       <c r="N15" t="n">
-        <v>81.25</v>
+        <v>79.62</v>
       </c>
       <c r="O15" t="n">
-        <v>1368.64</v>
+        <v>1341.18</v>
       </c>
       <c r="P15" t="n">
         <v>20.721325216</v>
@@ -3243,7 +3243,7 @@
         <v>349.046579</v>
       </c>
       <c r="S15" t="n">
-        <v>1019.593421</v>
+        <v>992.133421</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1368.64</v>
+        <v>1341.18</v>
       </c>
     </row>
     <row r="16">
@@ -3301,17 +3301,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>385</v>
       </c>
       <c r="N16" t="n">
-        <v>28.7997</v>
+        <v>28.9314</v>
       </c>
       <c r="O16" t="n">
-        <v>11087.88</v>
+        <v>11138.59</v>
       </c>
       <c r="P16" t="n">
         <v>25.997158151</v>
@@ -3323,7 +3323,7 @@
         <v>10008.905888</v>
       </c>
       <c r="S16" t="n">
-        <v>1078.974112</v>
+        <v>1129.684112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>11087.88</v>
+        <v>11138.59</v>
       </c>
     </row>
     <row r="17">
@@ -3381,17 +3381,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>114.84</v>
+        <v>109.3</v>
       </c>
       <c r="O17" t="n">
-        <v>5742</v>
+        <v>5465</v>
       </c>
       <c r="P17" t="n">
         <v>114.119</v>
@@ -3403,7 +3403,7 @@
         <v>5705.95</v>
       </c>
       <c r="S17" t="n">
-        <v>36.05</v>
+        <v>-240.95</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>5742</v>
+        <v>5465</v>
       </c>
     </row>
     <row r="18">
@@ -3461,17 +3461,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>600</v>
       </c>
       <c r="N18" t="n">
-        <v>180.08</v>
+        <v>179.32</v>
       </c>
       <c r="O18" t="n">
-        <v>108048</v>
+        <v>107592</v>
       </c>
       <c r="P18" t="n">
         <v>172.9987895</v>
@@ -3483,7 +3483,7 @@
         <v>103799.2737</v>
       </c>
       <c r="S18" t="n">
-        <v>4248.7263</v>
+        <v>3792.7263</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>108048</v>
+        <v>107592</v>
       </c>
     </row>
     <row r="19">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>17.8016</v>
+        <v>18.7727</v>
       </c>
       <c r="O19" t="n">
-        <v>3560.32</v>
+        <v>3754.54</v>
       </c>
       <c r="P19" t="n">
         <v>23.5270125</v>
@@ -3573,7 +3573,7 @@
         <v>4705.4025</v>
       </c>
       <c r="S19" t="n">
-        <v>-1145.0825</v>
+        <v>-950.8625</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>3560.32</v>
+        <v>3754.54</v>
       </c>
     </row>
     <row r="20">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>15.575</v>
+        <v>16.5621</v>
       </c>
       <c r="O20" t="n">
-        <v>3115</v>
+        <v>3312.42</v>
       </c>
       <c r="P20" t="n">
         <v>20.1350875</v>
@@ -3663,7 +3663,7 @@
         <v>4027.0175</v>
       </c>
       <c r="S20" t="n">
-        <v>-912.0175</v>
+        <v>-714.5975</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>3115</v>
+        <v>3312.42</v>
       </c>
     </row>
     <row r="21">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>-2</v>
       </c>
       <c r="N21" t="n">
-        <v>11.375</v>
+        <v>9.2232</v>
       </c>
       <c r="O21" t="n">
-        <v>-2275</v>
+        <v>-1844.64</v>
       </c>
       <c r="P21" t="n">
         <v>5.1653811</v>
@@ -3753,7 +3753,7 @@
         <v>-1033.07622</v>
       </c>
       <c r="S21" t="n">
-        <v>-1241.92378</v>
+        <v>-811.56378</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>-2275</v>
+        <v>-1844.64</v>
       </c>
     </row>
   </sheetData>
@@ -3813,17 +3813,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$313,856.51</t>
+          <t>$312,732.36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$134,717.22</t>
+          <t>$134,579.59</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$448,573.73</t>
+          <t>$447,311.95</t>
         </is>
       </c>
     </row>
@@ -3835,17 +3835,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$490,606.84</t>
+          <t>$487,721.93</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$78,635.03</t>
+          <t>$78,429.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$569,241.87</t>
+          <t>$566,151.26</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$804,463.35</t>
+          <t>$800,454.29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$213,352.25</t>
+          <t>$213,008.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1,017,815.60</t>
+          <t>$1,013,463.21</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-21 23:47:10</t>
+          <t>2026-04-22 23:48:37</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/projects/fetch-ibkr-positions.xlsx
+++ b/projects/fetch-ibkr-positions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2807</v>
+        <v>1.2742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -585,17 +585,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>70</v>
       </c>
       <c r="N2" t="n">
-        <v>420.75</v>
+        <v>424.95</v>
       </c>
       <c r="O2" t="n">
-        <v>29452.5</v>
+        <v>29746.5</v>
       </c>
       <c r="P2" t="n">
         <v>397.727320071</v>
@@ -607,7 +607,7 @@
         <v>27840.912405</v>
       </c>
       <c r="S2" t="n">
-        <v>1611.587595</v>
+        <v>1905.587595</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>37719.81675</v>
+        <v>37902.9903</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2807</v>
+        <v>1.2742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>67.81999999999999</v>
+        <v>68.47</v>
       </c>
       <c r="O3" t="n">
-        <v>13564</v>
+        <v>13694</v>
       </c>
       <c r="P3" t="n">
         <v>65.372133335</v>
@@ -687,7 +687,7 @@
         <v>13074.426667</v>
       </c>
       <c r="S3" t="n">
-        <v>489.573333</v>
+        <v>619.573333</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>17371.4148</v>
+        <v>17448.8948</v>
       </c>
     </row>
     <row r="4">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.14645</v>
+        <v>0.14637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,17 +745,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>32.04</v>
+        <v>32.24</v>
       </c>
       <c r="O4" t="n">
-        <v>64080</v>
+        <v>64480</v>
       </c>
       <c r="P4" t="n">
         <v>31.70624688</v>
@@ -767,7 +767,7 @@
         <v>63412.49376</v>
       </c>
       <c r="S4" t="n">
-        <v>667.50624</v>
+        <v>1067.50624</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9384.516</v>
+        <v>9437.937599999999</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1744</v>
+        <v>1.1706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -825,17 +825,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.298</v>
+        <v>4.3615</v>
       </c>
       <c r="O5" t="n">
-        <v>8596</v>
+        <v>8723</v>
       </c>
       <c r="P5" t="n">
         <v>4.66233</v>
@@ -847,7 +847,7 @@
         <v>9324.66</v>
       </c>
       <c r="S5" t="n">
-        <v>-728.66</v>
+        <v>-601.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>10095.1424</v>
+        <v>10211.1438</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1744</v>
+        <v>1.1706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>696</v>
+        <v>742</v>
       </c>
       <c r="O6" t="n">
-        <v>10440</v>
+        <v>11130</v>
       </c>
       <c r="P6" t="n">
         <v>556.278</v>
@@ -927,7 +927,7 @@
         <v>8344.17</v>
       </c>
       <c r="S6" t="n">
-        <v>2095.83</v>
+        <v>2785.83</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>12260.736</v>
+        <v>13028.778</v>
       </c>
     </row>
     <row r="7">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7850200000000001</v>
+        <v>0.78393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -985,17 +985,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>8000</v>
       </c>
       <c r="N7" t="n">
-        <v>5.03</v>
+        <v>5.016</v>
       </c>
       <c r="O7" t="n">
-        <v>40240</v>
+        <v>40128</v>
       </c>
       <c r="P7" t="n">
         <v>4.663903356</v>
@@ -1007,7 +1007,7 @@
         <v>37311.22685</v>
       </c>
       <c r="S7" t="n">
-        <v>2928.77315</v>
+        <v>2816.77315</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31589.2048</v>
+        <v>31457.54304</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7850200000000001</v>
+        <v>0.78393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>120</v>
       </c>
       <c r="N8" t="n">
-        <v>559.89</v>
+        <v>556.7</v>
       </c>
       <c r="O8" t="n">
-        <v>67186.8</v>
+        <v>66804</v>
       </c>
       <c r="P8" t="n">
         <v>576.9867204</v>
@@ -1087,7 +1087,7 @@
         <v>69238.40644799999</v>
       </c>
       <c r="S8" t="n">
-        <v>-2051.606448</v>
+        <v>-2434.406448</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>52742.98173600001</v>
+        <v>52369.65972</v>
       </c>
     </row>
     <row r="9">
@@ -1145,17 +1145,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>1000</v>
       </c>
       <c r="N9" t="n">
-        <v>7.83</v>
+        <v>7.905</v>
       </c>
       <c r="O9" t="n">
-        <v>7830</v>
+        <v>7905</v>
       </c>
       <c r="P9" t="n">
         <v>8.311237657</v>
@@ -1167,7 +1167,7 @@
         <v>8311.237657</v>
       </c>
       <c r="S9" t="n">
-        <v>-481.237657</v>
+        <v>-406.237657</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7830</v>
+        <v>7905</v>
       </c>
     </row>
     <row r="10">
@@ -1225,17 +1225,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>203.09</v>
+        <v>204.07</v>
       </c>
       <c r="O10" t="n">
-        <v>6092.7</v>
+        <v>6122.1</v>
       </c>
       <c r="P10" t="n">
         <v>218.103333333</v>
@@ -1247,7 +1247,7 @@
         <v>6543.1</v>
       </c>
       <c r="S10" t="n">
-        <v>-450.4</v>
+        <v>-421</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>6092.7</v>
+        <v>6122.1</v>
       </c>
     </row>
     <row r="11">
@@ -1305,17 +1305,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>10.29</v>
+        <v>10.82</v>
       </c>
       <c r="O11" t="n">
-        <v>1029</v>
+        <v>1082</v>
       </c>
       <c r="P11" t="n">
         <v>9.705</v>
@@ -1327,7 +1327,7 @@
         <v>970.5</v>
       </c>
       <c r="S11" t="n">
-        <v>58.5</v>
+        <v>111.5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1029</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="12">
@@ -1385,17 +1385,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>160</v>
       </c>
       <c r="N12" t="n">
-        <v>63.11</v>
+        <v>63.75</v>
       </c>
       <c r="O12" t="n">
-        <v>10097.6</v>
+        <v>10200</v>
       </c>
       <c r="P12" t="n">
         <v>59.854125</v>
@@ -1407,7 +1407,7 @@
         <v>9576.66</v>
       </c>
       <c r="S12" t="n">
-        <v>520.9400000000001</v>
+        <v>623.34</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>10097.6</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="13">
@@ -1465,17 +1465,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>28.9314</v>
+        <v>29.2363</v>
       </c>
       <c r="O13" t="n">
-        <v>11138.59</v>
+        <v>11255.98</v>
       </c>
       <c r="P13" t="n">
         <v>26.012734603</v>
@@ -1487,7 +1487,7 @@
         <v>10014.902822</v>
       </c>
       <c r="S13" t="n">
-        <v>1123.687178</v>
+        <v>1241.077178</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>11138.59</v>
+        <v>11255.98</v>
       </c>
     </row>
     <row r="14">
@@ -1545,17 +1545,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>109.3</v>
+        <v>111.85</v>
       </c>
       <c r="O14" t="n">
-        <v>5465</v>
+        <v>5592.5</v>
       </c>
       <c r="P14" t="n">
         <v>114.135</v>
@@ -1567,7 +1567,7 @@
         <v>5706.75</v>
       </c>
       <c r="S14" t="n">
-        <v>-241.75</v>
+        <v>-114.25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>5465</v>
+        <v>5592.5</v>
       </c>
     </row>
     <row r="15">
@@ -1625,17 +1625,17 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>40</v>
       </c>
       <c r="N15" t="n">
-        <v>86.83</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>3473.2</v>
+        <v>3451.6</v>
       </c>
       <c r="P15" t="n">
         <v>102.0775</v>
@@ -1647,7 +1647,7 @@
         <v>4083.1</v>
       </c>
       <c r="S15" t="n">
-        <v>-609.9</v>
+        <v>-631.5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>3473.2</v>
+        <v>3451.6</v>
       </c>
     </row>
     <row r="16">
@@ -1705,17 +1705,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>500</v>
       </c>
       <c r="N16" t="n">
-        <v>179.32</v>
+        <v>179.86</v>
       </c>
       <c r="O16" t="n">
-        <v>89660</v>
+        <v>89930</v>
       </c>
       <c r="P16" t="n">
         <v>172.83405384</v>
@@ -1727,7 +1727,7 @@
         <v>86417.02692</v>
       </c>
       <c r="S16" t="n">
-        <v>3242.97308</v>
+        <v>3512.97308</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>89660</v>
+        <v>89930</v>
       </c>
     </row>
     <row r="17">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>18.7727</v>
+        <v>17.0743</v>
       </c>
       <c r="O17" t="n">
-        <v>3754.54</v>
+        <v>3414.86</v>
       </c>
       <c r="P17" t="n">
         <v>23.4605</v>
@@ -1817,7 +1817,7 @@
         <v>4692.1</v>
       </c>
       <c r="S17" t="n">
-        <v>-937.5599999999999</v>
+        <v>-1277.24</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>3754.54</v>
+        <v>3414.86</v>
       </c>
     </row>
     <row r="18">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>16.5621</v>
+        <v>15.19</v>
       </c>
       <c r="O18" t="n">
-        <v>3312.42</v>
+        <v>3038</v>
       </c>
       <c r="P18" t="n">
         <v>20.1374875</v>
@@ -1907,7 +1907,7 @@
         <v>4027.4975</v>
       </c>
       <c r="S18" t="n">
-        <v>-715.0775</v>
+        <v>-989.4974999999999</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1920,97 +1920,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3312.42</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>U2739721</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>MSFT  260522P00370000</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MSFT 22MAY26 370 P</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" t="n">
-        <v>370</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.845</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-284.5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>12.80919851</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>12.80919851</v>
-      </c>
-      <c r="R19" t="n">
-        <v>-1280.919851</v>
-      </c>
-      <c r="S19" t="n">
-        <v>996.419851</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>CBOE</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>-284.5</v>
+        <v>3038</v>
       </c>
     </row>
   </sheetData>
@@ -2151,7 +2061,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2807</v>
+        <v>1.2742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2181,17 +2091,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>420.75</v>
+        <v>424.95</v>
       </c>
       <c r="O2" t="n">
-        <v>37867.5</v>
+        <v>38245.5</v>
       </c>
       <c r="P2" t="n">
         <v>400.699349867</v>
@@ -2203,7 +2113,7 @@
         <v>36062.941488</v>
       </c>
       <c r="S2" t="n">
-        <v>1804.558512</v>
+        <v>2182.558512</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -2216,7 +2126,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>48496.90725</v>
+        <v>48732.4161</v>
       </c>
     </row>
     <row r="3">
@@ -2231,7 +2141,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2807</v>
+        <v>1.2742</v>
      